--- a/public/docs/datas/f1.xlsx
+++ b/public/docs/datas/f1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\vue_platform\public\docs\datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{747B6434-CF61-4700-AEAE-E37D8E753DA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7F37524-9BF0-4172-AA84-C71D10B5DFCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16728" yWindow="6204" windowWidth="21216" windowHeight="18828" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11556" yWindow="3708" windowWidth="21216" windowHeight="15924" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="rounds" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2439" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2623" uniqueCount="220">
   <si>
     <t>year</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -925,7 +925,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -951,6 +951,9 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="20" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2890,6 +2893,5766 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>681</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>682</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1025" name="AutoShape 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7BC57E91-3409-753C-D667-1CB218FD0123}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="9395460" y="119352060"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>681</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>682</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1026" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BC261385-980A-8B5C-5163-A3D87FCF611B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="10005060" y="119352060"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>682</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>683</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1027" name="AutoShape 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EF8E56C4-2D53-76B9-0DAB-5E8B29DB5402}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="9395460" y="119702580"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>682</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>683</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1028" name="AutoShape 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4166C80F-5F22-A123-D733-9C14CEE50585}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="10005060" y="119702580"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>683</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>684</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1029" name="AutoShape 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9A628B5-A92E-E696-F88F-FFF4837B9FFD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="9395460" y="120053100"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>683</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>684</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1030" name="AutoShape 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EEB8F80B-52A8-BEFB-29FB-79C45955EEC6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="10005060" y="120053100"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>684</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>685</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1031" name="AutoShape 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{530DE4DC-E728-85EC-2047-78810410DE71}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="9395460" y="120578880"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>684</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>685</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1032" name="AutoShape 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD61A14B-75C8-DA4E-F5AE-E294D35EEC34}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="10005060" y="120578880"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>685</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>686</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1033" name="AutoShape 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{14C062D7-AC1E-27A3-8F0F-AF2FF3A064B3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="9395460" y="120929400"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>685</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>686</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1034" name="AutoShape 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{519DE775-97DD-3740-A1AE-84715118F153}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="10005060" y="120929400"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>686</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>687</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1035" name="AutoShape 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8057919A-91E7-F841-12AA-E8AC3D6635F1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="9395460" y="121279920"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>686</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>687</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1036" name="AutoShape 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D6EF8F81-55D0-E302-F05A-D4C619AE1005}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="10005060" y="121279920"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>687</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>688</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1037" name="AutoShape 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{94260E9D-0F18-932E-26F8-0B03176649D8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="9395460" y="121630440"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>687</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>688</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1038" name="AutoShape 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B56CD907-2E52-7D04-ABC9-3B3CA0B40D3E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="10005060" y="121630440"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>688</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>689</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1039" name="AutoShape 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6154F1AC-8F64-B556-40EB-E6ED0976B986}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="9395460" y="121980960"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>688</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>689</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1040" name="AutoShape 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A719C8DC-3617-899A-08CB-F51252C234A8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="10005060" y="121980960"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>689</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>690</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1041" name="AutoShape 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{47A574D7-4E0B-AC0B-F1ED-3D2BE71C1AB7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="9395460" y="122331480"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>689</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>690</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1042" name="AutoShape 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{614EA7B9-3D99-21DA-4107-872E2D35B06F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="10005060" y="122331480"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>690</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>691</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1043" name="AutoShape 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9C603B79-13F9-786F-9A14-530C5EF30DD8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="9395460" y="122682000"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>690</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>691</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1044" name="AutoShape 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9F13FBFD-C2C9-F910-0A0D-8B307D5CDA6C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="10005060" y="122682000"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>691</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>692</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1045" name="AutoShape 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D096DEC8-DC7C-B364-C314-BFBE63F8CC55}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="9395460" y="123032520"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>691</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>692</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1046" name="AutoShape 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F415AE2-7EEE-6EFA-87A3-A12870DDBD43}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="10005060" y="123032520"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>692</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>693</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1047" name="AutoShape 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1C45DB0C-B961-8772-2760-E882AF77F1ED}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="9395460" y="123383040"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>692</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>693</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1048" name="AutoShape 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2195EFEB-F442-5ED2-243F-8D825F8A28E7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="10005060" y="123383040"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>693</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>694</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1049" name="AutoShape 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AF00B631-B0F0-5869-BAD3-DF3E5A07A189}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="9395460" y="123733560"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>693</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>694</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1050" name="AutoShape 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7164D885-BCFB-A31A-816C-770039557B01}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="10005060" y="123733560"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>694</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>695</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1051" name="AutoShape 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{35B80F18-03FA-AF00-EBC2-F796D9E2454B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="9395460" y="124084080"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>694</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>695</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1052" name="AutoShape 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{51815C0A-4C92-431C-E1FC-1BE848472979}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="10005060" y="124084080"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>695</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>696</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1053" name="AutoShape 29">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{38B9A0FB-3AB4-D1CA-3696-2FA5C7C993A1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="9395460" y="124434600"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>695</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>696</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1054" name="AutoShape 30">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C00DA528-968F-15E1-2EBE-6B7F1B8F2815}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="10005060" y="124434600"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>696</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>697</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1055" name="AutoShape 31">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5B2DA1FF-8317-7F91-FEFE-55F7AD9ADA8A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="9395460" y="124785120"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>696</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>697</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1056" name="AutoShape 32">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7CFE8D79-36B7-A723-3868-6BE892D4DE3F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="10005060" y="124785120"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>697</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>698</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1057" name="AutoShape 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5FE5EADD-A1AA-0662-A0D6-8879C2EA523D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="9395460" y="125310900"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>697</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>698</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1058" name="AutoShape 34">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32142157-F7BA-154A-C6D0-5713664EE1B4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="10005060" y="125310900"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>698</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>699</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1059" name="AutoShape 35">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0A2825DF-76F1-D1C6-AE37-B2B840602CAD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="9395460" y="125836680"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>698</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>699</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1060" name="AutoShape 36">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F64B257D-549A-BCB7-43D3-25C929E21FAE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="10005060" y="125836680"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>699</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>700</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1061" name="AutoShape 37">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D6F83687-FCD2-971C-6EE0-C12D92E0D721}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="9395460" y="126187200"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>699</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>700</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1062" name="AutoShape 38">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8A320FA5-184F-5F10-92BB-FEB717C81FFB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="10005060" y="126187200"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>700</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>701</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1063" name="AutoShape 39">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FCC46CEF-336B-6F2C-03E7-588F29DE486F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="9395460" y="126537720"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>700</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>701</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1064" name="AutoShape 40">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B193F8E0-02AD-420B-951E-EFFDF3EB42D1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="10005060" y="126537720"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>701</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>702</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1065" name="AutoShape 41">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{20EE77D9-F13F-9C18-927E-F7407CB66FC6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3025140" y="122857260"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>701</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>702</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1066" name="AutoShape 42">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FA9441A9-7998-BDB4-9C4E-B7418001B290}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4152900" y="122857260"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>702</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>703</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1067" name="AutoShape 43">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D3D3188C-2BDF-399B-44F2-89B6FD460EF6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3025140" y="123032520"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>702</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>703</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1068" name="AutoShape 44">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F8DF527C-4FDD-4E8C-52FC-F639A8057828}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4152900" y="123032520"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>703</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>704</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1069" name="AutoShape 45">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3A341831-A9C5-AC7B-A50A-163EC43F9CD3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3025140" y="123207780"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>703</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>704</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1070" name="AutoShape 46">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1C093E53-0788-5498-8088-7A7130DECF33}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4152900" y="123207780"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>704</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>705</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1071" name="AutoShape 47">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EFA3C8ED-9AB0-F6D6-C5E8-2CEB54C49C8C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3025140" y="123383040"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>704</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>705</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1072" name="AutoShape 48">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5CBD58A2-E2B8-1F56-AB90-823409483C8F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4152900" y="123383040"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>705</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>706</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1073" name="AutoShape 49">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{40FB1663-05F7-2E68-E8E2-1370F2739F8B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3025140" y="123558300"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>705</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>706</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1074" name="AutoShape 50">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{058DBD46-7D2C-1BF7-4AF7-148C6847311C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4152900" y="123558300"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>706</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>707</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1075" name="AutoShape 51">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F17BF864-0186-DE52-197B-EAA7DF0567F4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3025140" y="123733560"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>706</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>707</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1076" name="AutoShape 52">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6EFF7681-AACE-EC97-DFB0-0F4A229896DB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4152900" y="123733560"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>707</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>708</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1077" name="AutoShape 53">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F0D02E3-DC0F-0290-0581-72C99D29D855}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3025140" y="123908820"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>707</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>708</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1078" name="AutoShape 54">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E3CA179-B697-90E9-FE51-80F81C2B9CF5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4152900" y="123908820"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>708</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>709</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1079" name="AutoShape 55">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F6A524F8-3762-A06B-AFEE-0F48CDB20C72}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3025140" y="124084080"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>708</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>709</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1080" name="AutoShape 56">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F0713B9E-18C0-B4F0-B049-1F188F8BE4D9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4152900" y="124084080"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>709</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>710</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1081" name="AutoShape 57">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{95A00A2E-D6BE-27D7-7E6C-48F45EFFD6AE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3025140" y="124259340"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>709</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>710</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1082" name="AutoShape 58">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EA60520F-C1CC-67B0-A1B7-F6F300949F93}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4152900" y="124259340"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>710</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>711</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1083" name="AutoShape 59">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7FCFEE88-7D1F-D5F4-D063-CB1F4EC34B33}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3025140" y="124434600"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>710</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>711</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1084" name="AutoShape 60">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5511EBCA-5C59-D95F-FBA9-310E71F875FD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4152900" y="124434600"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>711</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>712</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1085" name="AutoShape 61">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{186EF60D-3EE9-B9B5-FC14-833E7673DE43}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3025140" y="124609860"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>711</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>712</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1086" name="AutoShape 62">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{289BBB4C-6B77-A6BF-BF55-F5C6A9295CE6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4152900" y="124609860"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>712</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>713</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1087" name="AutoShape 63">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D64C7450-C759-2D64-773A-9E25EABC95D5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3025140" y="124785120"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>712</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>713</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1088" name="AutoShape 64">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{70F4D287-4721-CAE4-C5B4-D4CCB8233566}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4152900" y="124785120"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>713</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>714</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1089" name="AutoShape 65">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0640F955-DD83-2FAC-410A-8D87729A62F7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3025140" y="124960380"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>713</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>714</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1090" name="AutoShape 66">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{73F73574-8E59-EF3E-DE24-C6813EC2B74A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4152900" y="124960380"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>714</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>715</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1091" name="AutoShape 67">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{29A0E317-C4B3-2CD9-2260-73E3D80BB778}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3025140" y="125135640"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>714</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>715</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1092" name="AutoShape 68">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D681D87B-B7CE-4909-9B74-5E3D8ACF5916}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4152900" y="125135640"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>715</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>716</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1093" name="AutoShape 69">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5A60BDB8-DFC4-253A-EF9A-659DC0B9A78D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3025140" y="125310900"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>715</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>716</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1094" name="AutoShape 70">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{12D6A5F3-FE04-B443-A9DC-96EA78EE48C4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4152900" y="125310900"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>716</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>717</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1095" name="AutoShape 71">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DC159220-62EB-376C-2CDD-772B3F99FA91}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3025140" y="125486160"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>716</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>717</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1096" name="AutoShape 72">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5C6A2050-227C-FE8C-BF8E-C23F43AF84C3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4152900" y="125486160"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>717</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>718</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1097" name="AutoShape 73">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D845DBA4-4147-CBBA-1D66-D7E766345319}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3025140" y="125661420"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>717</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>718</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1098" name="AutoShape 74">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5DB1D135-3989-DA53-0E56-3FC10B703E5F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4152900" y="125661420"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>718</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>719</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1099" name="AutoShape 75">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C4742536-BB37-572C-01B5-3D28DF6206AB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3025140" y="125836680"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>718</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>719</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1100" name="AutoShape 76">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D5FB46E1-458E-A3E6-3E2E-B256D6266BD8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4152900" y="125836680"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>719</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>720</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1101" name="AutoShape 77">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5201B775-2559-DC9D-97DD-7E6A445D8039}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3025140" y="126011940"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>719</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>720</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1102" name="AutoShape 78">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FFAF11C8-5364-C6E5-C298-5DA00E5A38CE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4152900" y="126011940"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>720</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>721</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1103" name="AutoShape 79">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5841144D-510F-AC75-26CC-ECCFCECC8309}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3025140" y="126187200"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>720</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>721</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1104" name="AutoShape 80">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{848C3BD9-3000-A73C-3B85-123763E9F69E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4152900" y="126187200"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>721</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>722</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="AutoShape 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9723AA0A-E021-ED54-DFFC-A889183C52F9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3025140" y="126362460"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>721</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>722</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F137BDB3-AC91-1794-C4FD-7AF9D3720B08}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4152900" y="126362460"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>722</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>723</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="AutoShape 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{993A788C-2438-6E7D-E59C-F911BD52923F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3025140" y="126537720"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>722</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>723</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="AutoShape 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D310EFE3-D89A-6261-6BAF-9DE43B6F0987}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4152900" y="126537720"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>723</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>724</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="AutoShape 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B35E418B-7971-9868-5A3E-D9612591EC35}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3025140" y="126712980"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>723</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>724</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="AutoShape 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F356922-4659-BF73-09B7-436C4EE095F7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4152900" y="126712980"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>724</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>725</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="AutoShape 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2D80A92F-E50F-7ACF-6AA7-9A7C0B541372}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3025140" y="126888240"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>724</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>725</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="AutoShape 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B24CA894-3F91-8A87-4B88-D1C1496B485A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4152900" y="126888240"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>725</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>726</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="AutoShape 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DC396DB5-F44F-031E-2838-03815EBF1A6F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3025140" y="127063500"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>725</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>726</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="AutoShape 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{782998E4-3B59-A1E3-ACE0-09353D93CB00}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4152900" y="127063500"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>726</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>727</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="AutoShape 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7A874636-FD9A-3837-B457-65B838A99A30}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3025140" y="127238760"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>726</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>727</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="AutoShape 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8F30E5C9-BABD-465E-9A1C-64C96DFF5329}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4152900" y="127238760"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>727</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>728</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="AutoShape 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8ED7A262-A53C-6358-0171-3393F9F3D0F3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3025140" y="127414020"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>727</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>728</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="AutoShape 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6A982CE7-12A8-A29C-C3BB-49BD827AA1EF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4152900" y="127414020"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>728</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>729</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="AutoShape 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E7E8DA9B-F402-5CC0-5B36-1B0C40A5D90C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3025140" y="127589280"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>728</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>729</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name="AutoShape 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D256F25D-2748-EF76-7EC9-DF0544CDC57E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4152900" y="127589280"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>729</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>730</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="AutoShape 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BDCBA148-92CF-FF67-6F5F-B1DDC30BAD1A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3025140" y="127764540"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>729</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>730</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="AutoShape 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1F640964-124F-834B-2D9E-20BCA616F653}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4152900" y="127764540"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>730</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>731</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name="AutoShape 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8A1B1697-772E-4D39-4B2C-6D56CB3F0162}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3025140" y="127939800"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>730</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>731</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="21" name="AutoShape 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E7C7AA92-59FF-53E5-155D-844100540998}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4152900" y="127939800"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>731</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>732</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="22" name="AutoShape 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3D8E77EB-F19C-8805-0DD1-739D4E69BB92}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3025140" y="128115060"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>731</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>732</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="23" name="AutoShape 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F90565F0-4B96-4A68-4664-7D900E4D37CF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4152900" y="128115060"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>732</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>733</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="24" name="AutoShape 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1A1DCECD-9604-6EC1-DA0D-CF78CE4CB110}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3025140" y="128290320"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>732</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>733</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="25" name="AutoShape 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B4FC6C85-C7AD-24DA-316A-A30D904F9ED1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4152900" y="128290320"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>733</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>734</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="26" name="AutoShape 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C94A291-39F6-7806-A74A-AB2A13E9140E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3025140" y="128465580"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>733</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>734</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="27" name="AutoShape 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A0F5955E-48EB-8E3F-BAA0-5FA5D2AFBF05}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4152900" y="128465580"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>734</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>735</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="28" name="AutoShape 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D2EEFF86-6D19-3EC7-25E9-6C128C1A7308}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3025140" y="128640840"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>734</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>735</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="29" name="AutoShape 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6BCE8144-BA8A-F582-704C-9956F6C0B9F9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4152900" y="128640840"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>735</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>736</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="30" name="AutoShape 29">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{202A1ACE-AF3A-1725-0AE1-AA986CAA671D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3025140" y="128816100"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>735</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>736</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="31" name="AutoShape 30">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6AF0A94E-0FBE-F6CD-5C39-821D704BBAB1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4152900" y="128816100"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>736</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>737</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="32" name="AutoShape 31">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{57001B32-64D7-4760-BBEE-42FD6ED5332F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3025140" y="128991360"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>736</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>737</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="33" name="AutoShape 32">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DDB522CE-F433-8115-FD22-185B763D7AF1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4152900" y="128991360"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>737</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>738</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="34" name="AutoShape 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3847F70D-54D5-5D5D-808E-C1796C20EC6D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3025140" y="129166620"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>737</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>738</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="35" name="AutoShape 34">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F009AA84-6C21-5921-6FDB-701812CD9052}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4152900" y="129166620"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>738</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>739</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="36" name="AutoShape 35">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7B68944-0C92-0303-29AE-4F898F95D683}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3025140" y="129341880"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>738</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>739</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="37" name="AutoShape 36">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EEF88405-7911-5EBC-BD6F-3EA2F0FC7796}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4152900" y="129341880"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>739</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>740</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="38" name="AutoShape 37">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A50B6BA5-B328-3ABC-C828-BD7ADEDB65D4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3025140" y="129517140"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>739</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>740</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="39" name="AutoShape 38">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5DFE352A-AB4F-51AF-325F-3356AFEAA589}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4152900" y="129517140"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>740</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>741</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="40" name="AutoShape 39">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7DEA54A7-9811-70FE-8FFA-39F619D68C7D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3025140" y="129692400"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>740</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>741</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="41" name="AutoShape 40">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F25A8546-3E62-6ADD-8907-48F80CD16E16}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4152900" y="129692400"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -4014,114 +9777,115 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>2025</v>
-      </c>
-      <c r="B7">
+      <c r="A7" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B7" s="9">
         <v>2</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7" s="13">
         <v>45737</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="14">
         <v>0.47916666666666669</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="14">
         <v>0.52083333333333337</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>2025</v>
-      </c>
-      <c r="B8">
+      <c r="A8" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B8" s="9">
         <v>2</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8" s="13">
         <v>45737</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="14">
         <v>0.64583333333333337</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="14">
         <v>0.67638888888888893</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="9">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>2025</v>
-      </c>
-      <c r="B9">
+      <c r="A9" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B9" s="9">
         <v>2</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9" s="13">
         <v>45738</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="14">
         <v>0.45833333333333331</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="14">
         <v>0.5</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="9">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>2025</v>
-      </c>
-      <c r="B10">
+      <c r="A10" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B10" s="9">
         <v>2</v>
       </c>
-      <c r="C10" t="s">
-        <v>11</v>
-      </c>
-      <c r="D10" s="1">
+      <c r="C10" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="13">
         <v>45738</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10" s="14">
         <v>0.625</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="14">
         <v>0.66666666666666663</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="9">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>2025</v>
-      </c>
-      <c r="B11">
+      <c r="A11" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B11" s="9">
         <v>2</v>
       </c>
-      <c r="C11" t="s">
-        <v>14</v>
-      </c>
-      <c r="D11" s="1">
+      <c r="C11" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="13">
         <v>45739</v>
       </c>
-      <c r="E11" s="2">
+      <c r="E11" s="14">
         <v>0.625</v>
       </c>
-      <c r="G11">
+      <c r="F11" s="9"/>
+      <c r="G11" s="9">
         <v>1</v>
       </c>
     </row>
@@ -4238,114 +10002,115 @@
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>2025</v>
-      </c>
-      <c r="B17">
+      <c r="A17" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B17" s="9">
         <v>4</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="D17" s="1">
+      <c r="D17" s="13">
         <v>45758</v>
       </c>
-      <c r="E17" s="2">
+      <c r="E17" s="14">
         <v>0.8125</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17" s="14">
         <v>0.85416666666666663</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>2025</v>
-      </c>
-      <c r="B18">
+      <c r="A18" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B18" s="9">
         <v>4</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="D18" s="1">
+      <c r="D18" s="13">
         <v>45758</v>
       </c>
-      <c r="E18" s="2">
+      <c r="E18" s="14">
         <v>0.95833333333333337</v>
       </c>
-      <c r="F18" s="2">
+      <c r="F18" s="14">
         <v>0</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>2025</v>
-      </c>
-      <c r="B19">
+      <c r="A19" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B19" s="9">
         <v>4</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="D19" s="1">
+      <c r="D19" s="13">
         <v>45759</v>
       </c>
-      <c r="E19" s="2">
+      <c r="E19" s="14">
         <v>0.85416666666666663</v>
       </c>
-      <c r="F19" s="2">
+      <c r="F19" s="14">
         <v>0.89583333333333337</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>2025</v>
-      </c>
-      <c r="B20">
+      <c r="A20" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B20" s="9">
         <v>4</v>
       </c>
-      <c r="C20" t="s">
-        <v>11</v>
-      </c>
-      <c r="D20" s="1">
+      <c r="C20" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20" s="13">
         <v>45760</v>
       </c>
-      <c r="E20" s="2">
+      <c r="E20" s="14">
         <v>0</v>
       </c>
-      <c r="F20" s="2">
+      <c r="F20" s="14">
         <v>4.1666666666666664E-2</v>
       </c>
-      <c r="G20">
+      <c r="G20" s="9">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>2025</v>
-      </c>
-      <c r="B21">
+      <c r="A21" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B21" s="9">
         <v>4</v>
       </c>
-      <c r="C21" t="s">
-        <v>14</v>
-      </c>
-      <c r="D21" s="1">
+      <c r="C21" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21" s="13">
         <v>45760</v>
       </c>
-      <c r="E21" s="2">
+      <c r="E21" s="14">
         <v>0.95833333333333337</v>
       </c>
-      <c r="G21">
+      <c r="F21" s="9"/>
+      <c r="G21" s="9">
         <v>1</v>
       </c>
     </row>
@@ -4462,115 +10227,115 @@
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>2025</v>
-      </c>
-      <c r="B27">
+      <c r="A27" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B27" s="9">
         <v>6</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="D27" s="1">
+      <c r="D27" s="13">
         <v>45780</v>
       </c>
-      <c r="E27" s="2">
+      <c r="E27" s="14">
         <v>2.0833333333333332E-2</v>
       </c>
-      <c r="F27" s="2">
+      <c r="F27" s="14">
         <v>6.25E-2</v>
       </c>
-      <c r="G27">
+      <c r="G27" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>2025</v>
-      </c>
-      <c r="B28">
+      <c r="A28" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B28" s="9">
         <v>6</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="D28" s="1">
+      <c r="D28" s="13">
         <v>45780</v>
       </c>
-      <c r="E28" s="2">
+      <c r="E28" s="14">
         <v>0.1875</v>
       </c>
-      <c r="F28" s="2">
+      <c r="F28" s="14">
         <v>0.21805555555555556</v>
       </c>
-      <c r="G28">
+      <c r="G28" s="9">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>2025</v>
-      </c>
-      <c r="B29">
+      <c r="A29" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B29" s="9">
         <v>6</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="D29" s="1">
+      <c r="D29" s="13">
         <v>45781</v>
       </c>
-      <c r="E29" s="2">
+      <c r="E29" s="14">
         <v>0</v>
       </c>
-      <c r="F29" s="2">
+      <c r="F29" s="14">
         <v>4.1666666666666664E-2</v>
       </c>
-      <c r="G29">
+      <c r="G29" s="9">
         <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>2025</v>
-      </c>
-      <c r="B30">
+      <c r="A30" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B30" s="9">
         <v>6</v>
       </c>
-      <c r="C30" t="s">
-        <v>11</v>
-      </c>
-      <c r="D30" s="1">
+      <c r="C30" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30" s="13">
         <v>45781</v>
       </c>
-      <c r="E30" s="2">
+      <c r="E30" s="14">
         <v>0.16666666666666666</v>
       </c>
-      <c r="F30" s="2">
+      <c r="F30" s="14">
         <v>0.20833333333333334</v>
       </c>
-      <c r="G30">
+      <c r="G30" s="9">
         <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>2025</v>
-      </c>
-      <c r="B31">
+      <c r="A31" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B31" s="9">
         <v>6</v>
       </c>
-      <c r="C31" t="s">
-        <v>14</v>
-      </c>
-      <c r="D31" s="1">
+      <c r="C31" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D31" s="13">
         <v>45782</v>
       </c>
-      <c r="E31" s="2">
+      <c r="E31" s="14">
         <v>0.16666666666666666</v>
       </c>
-      <c r="F31" s="2"/>
-      <c r="G31">
+      <c r="F31" s="14"/>
+      <c r="G31" s="9">
         <v>1</v>
       </c>
     </row>
@@ -4687,114 +10452,115 @@
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <v>2025</v>
-      </c>
-      <c r="B37">
+      <c r="A37" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B37" s="9">
         <v>8</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C37" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="D37" s="1">
+      <c r="D37" s="13">
         <v>45800</v>
       </c>
-      <c r="E37" s="2">
+      <c r="E37" s="14">
         <v>0.8125</v>
       </c>
-      <c r="F37" s="2">
+      <c r="F37" s="14">
         <v>0.85416666666666663</v>
       </c>
-      <c r="G37">
+      <c r="G37" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38">
-        <v>2025</v>
-      </c>
-      <c r="B38">
+      <c r="A38" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B38" s="9">
         <v>8</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="D38" s="1">
+      <c r="D38" s="13">
         <v>45800</v>
       </c>
-      <c r="E38" s="2">
+      <c r="E38" s="14">
         <v>0.95833333333333337</v>
       </c>
-      <c r="F38" s="2">
+      <c r="F38" s="14">
         <v>0</v>
       </c>
-      <c r="G38">
+      <c r="G38" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39">
-        <v>2025</v>
-      </c>
-      <c r="B39">
+      <c r="A39" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B39" s="9">
         <v>8</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="D39" s="1">
+      <c r="D39" s="13">
         <v>45801</v>
       </c>
-      <c r="E39" s="2">
+      <c r="E39" s="14">
         <v>0.77083333333333337</v>
       </c>
-      <c r="F39" s="2">
+      <c r="F39" s="14">
         <v>0.8125</v>
       </c>
-      <c r="G39">
+      <c r="G39" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40">
-        <v>2025</v>
-      </c>
-      <c r="B40">
+      <c r="A40" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B40" s="9">
         <v>8</v>
       </c>
-      <c r="C40" t="s">
-        <v>11</v>
-      </c>
-      <c r="D40" s="1">
+      <c r="C40" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D40" s="13">
         <v>45801</v>
       </c>
-      <c r="E40" s="2">
+      <c r="E40" s="14">
         <v>0.91666666666666663</v>
       </c>
-      <c r="F40" s="2">
+      <c r="F40" s="14">
         <v>0.95833333333333337</v>
       </c>
-      <c r="G40">
+      <c r="G40" s="9">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41">
-        <v>2025</v>
-      </c>
-      <c r="B41">
+      <c r="A41" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B41" s="9">
         <v>8</v>
       </c>
-      <c r="C41" t="s">
-        <v>14</v>
-      </c>
-      <c r="D41" s="1">
+      <c r="C41" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D41" s="13">
         <v>45802</v>
       </c>
-      <c r="E41" s="2">
+      <c r="E41" s="14">
         <v>0.875</v>
       </c>
-      <c r="G41">
+      <c r="F41" s="9"/>
+      <c r="G41" s="9">
         <v>1</v>
       </c>
     </row>
@@ -4911,114 +10677,115 @@
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47">
-        <v>2025</v>
-      </c>
-      <c r="B47">
+      <c r="A47" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B47" s="9">
         <v>10</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C47" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="D47" s="1">
+      <c r="D47" s="13">
         <v>45822</v>
       </c>
-      <c r="E47" s="2">
+      <c r="E47" s="14">
         <v>6.25E-2</v>
       </c>
-      <c r="F47" s="2">
+      <c r="F47" s="14">
         <v>0.10416666666666667</v>
       </c>
-      <c r="G47">
+      <c r="G47" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48">
-        <v>2025</v>
-      </c>
-      <c r="B48">
+      <c r="A48" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B48" s="9">
         <v>10</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C48" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="D48" s="1">
+      <c r="D48" s="13">
         <v>45822</v>
       </c>
-      <c r="E48" s="2">
+      <c r="E48" s="14">
         <v>0.20833333333333334</v>
       </c>
-      <c r="F48" s="2">
+      <c r="F48" s="14">
         <v>0.25</v>
       </c>
-      <c r="G48">
+      <c r="G48" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49">
-        <v>2025</v>
-      </c>
-      <c r="B49">
+      <c r="A49" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B49" s="9">
         <v>10</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C49" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="D49" s="1">
+      <c r="D49" s="13">
         <v>45823</v>
       </c>
-      <c r="E49" s="2">
+      <c r="E49" s="14">
         <v>2.0833333333333332E-2</v>
       </c>
-      <c r="F49" s="2">
+      <c r="F49" s="14">
         <v>6.25E-2</v>
       </c>
-      <c r="G49">
+      <c r="G49" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50">
-        <v>2025</v>
-      </c>
-      <c r="B50">
+      <c r="A50" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B50" s="9">
         <v>10</v>
       </c>
-      <c r="C50" t="s">
-        <v>11</v>
-      </c>
-      <c r="D50" s="1">
+      <c r="C50" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D50" s="13">
         <v>45823</v>
       </c>
-      <c r="E50" s="2">
+      <c r="E50" s="14">
         <v>0.16666666666666666</v>
       </c>
-      <c r="F50" s="2">
+      <c r="F50" s="14">
         <v>0.20833333333333334</v>
       </c>
-      <c r="G50">
+      <c r="G50" s="9">
         <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51">
-        <v>2025</v>
-      </c>
-      <c r="B51">
+      <c r="A51" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B51" s="9">
         <v>10</v>
       </c>
-      <c r="C51" t="s">
-        <v>14</v>
-      </c>
-      <c r="D51" s="1">
+      <c r="C51" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D51" s="13">
         <v>45824</v>
       </c>
-      <c r="E51" s="2">
+      <c r="E51" s="14">
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="G51">
+      <c r="F51" s="9"/>
+      <c r="G51" s="9">
         <v>1</v>
       </c>
     </row>
@@ -5135,114 +10902,115 @@
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57">
-        <v>2025</v>
-      </c>
-      <c r="B57">
+      <c r="A57" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B57" s="9">
         <v>12</v>
       </c>
-      <c r="C57" t="s">
+      <c r="C57" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="D57" s="1">
+      <c r="D57" s="13">
         <v>45842</v>
       </c>
-      <c r="E57" s="2">
+      <c r="E57" s="14">
         <v>0.8125</v>
       </c>
-      <c r="F57" s="2">
+      <c r="F57" s="14">
         <v>0.85416666666666663</v>
       </c>
-      <c r="G57">
+      <c r="G57" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58">
-        <v>2025</v>
-      </c>
-      <c r="B58">
+      <c r="A58" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B58" s="9">
         <v>12</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C58" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="D58" s="1">
+      <c r="D58" s="13">
         <v>45842</v>
       </c>
-      <c r="E58" s="2">
+      <c r="E58" s="14">
         <v>0.95833333333333337</v>
       </c>
-      <c r="F58" s="2">
+      <c r="F58" s="14">
         <v>0</v>
       </c>
-      <c r="G58">
+      <c r="G58" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59">
-        <v>2025</v>
-      </c>
-      <c r="B59">
+      <c r="A59" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B59" s="9">
         <v>12</v>
       </c>
-      <c r="C59" t="s">
+      <c r="C59" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="D59" s="1">
+      <c r="D59" s="13">
         <v>45843</v>
       </c>
-      <c r="E59" s="2">
+      <c r="E59" s="14">
         <v>0.77083333333333337</v>
       </c>
-      <c r="F59" s="2">
+      <c r="F59" s="14">
         <v>0.8125</v>
       </c>
-      <c r="G59">
+      <c r="G59" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60">
-        <v>2025</v>
-      </c>
-      <c r="B60">
+      <c r="A60" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B60" s="9">
         <v>12</v>
       </c>
-      <c r="C60" t="s">
-        <v>11</v>
-      </c>
-      <c r="D60" s="1">
+      <c r="C60" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D60" s="13">
         <v>45843</v>
       </c>
-      <c r="E60" s="2">
+      <c r="E60" s="14">
         <v>0.91666666666666663</v>
       </c>
-      <c r="F60" s="2">
+      <c r="F60" s="14">
         <v>0.95833333333333337</v>
       </c>
-      <c r="G60">
+      <c r="G60" s="9">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61">
-        <v>2025</v>
-      </c>
-      <c r="B61">
+      <c r="A61" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B61" s="9">
         <v>12</v>
       </c>
-      <c r="C61" t="s">
-        <v>14</v>
-      </c>
-      <c r="D61" s="1">
+      <c r="C61" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D61" s="13">
         <v>45844</v>
       </c>
-      <c r="E61" s="2">
+      <c r="E61" s="14">
         <v>0.91666666666666663</v>
       </c>
-      <c r="G61">
+      <c r="F61" s="9"/>
+      <c r="G61" s="9">
         <v>1</v>
       </c>
     </row>
@@ -5359,114 +11127,115 @@
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A67">
-        <v>2025</v>
-      </c>
-      <c r="B67">
-        <v>14</v>
-      </c>
-      <c r="C67" t="s">
+      <c r="A67" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B67" s="9">
+        <v>14</v>
+      </c>
+      <c r="C67" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="D67" s="1">
+      <c r="D67" s="13">
         <v>45870</v>
       </c>
-      <c r="E67" s="2">
+      <c r="E67" s="14">
         <v>0.8125</v>
       </c>
-      <c r="F67" s="2">
+      <c r="F67" s="14">
         <v>0.85416666666666663</v>
       </c>
-      <c r="G67">
+      <c r="G67" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68">
-        <v>2025</v>
-      </c>
-      <c r="B68">
-        <v>14</v>
-      </c>
-      <c r="C68" t="s">
+      <c r="A68" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B68" s="9">
+        <v>14</v>
+      </c>
+      <c r="C68" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="D68" s="1">
+      <c r="D68" s="13">
         <v>45870</v>
       </c>
-      <c r="E68" s="2">
+      <c r="E68" s="14">
         <v>0.95833333333333337</v>
       </c>
-      <c r="F68" s="2">
+      <c r="F68" s="14">
         <v>0</v>
       </c>
-      <c r="G68">
+      <c r="G68" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69">
-        <v>2025</v>
-      </c>
-      <c r="B69">
-        <v>14</v>
-      </c>
-      <c r="C69" t="s">
+      <c r="A69" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B69" s="9">
+        <v>14</v>
+      </c>
+      <c r="C69" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="D69" s="1">
+      <c r="D69" s="13">
         <v>45871</v>
       </c>
-      <c r="E69" s="2">
+      <c r="E69" s="14">
         <v>0.77083333333333337</v>
       </c>
-      <c r="F69" s="2">
+      <c r="F69" s="14">
         <v>0.8125</v>
       </c>
-      <c r="G69">
+      <c r="G69" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70">
-        <v>2025</v>
-      </c>
-      <c r="B70">
-        <v>14</v>
-      </c>
-      <c r="C70" t="s">
-        <v>11</v>
-      </c>
-      <c r="D70" s="1">
+      <c r="A70" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B70" s="9">
+        <v>14</v>
+      </c>
+      <c r="C70" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D70" s="13">
         <v>45871</v>
       </c>
-      <c r="E70" s="2">
+      <c r="E70" s="14">
         <v>0.91666666666666663</v>
       </c>
-      <c r="F70" s="2">
+      <c r="F70" s="14">
         <v>0.95833333333333337</v>
       </c>
-      <c r="G70">
+      <c r="G70" s="9">
         <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71">
-        <v>2025</v>
-      </c>
-      <c r="B71">
-        <v>14</v>
-      </c>
-      <c r="C71" t="s">
-        <v>14</v>
-      </c>
-      <c r="D71" s="1">
+      <c r="A71" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B71" s="9">
+        <v>14</v>
+      </c>
+      <c r="C71" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D71" s="13">
         <v>45872</v>
       </c>
-      <c r="E71" s="2">
+      <c r="E71" s="14">
         <v>0.875</v>
       </c>
-      <c r="G71">
+      <c r="F71" s="9"/>
+      <c r="G71" s="9">
         <v>1</v>
       </c>
     </row>
@@ -5483,6 +11252,12 @@
       <c r="D72" s="1">
         <v>45898</v>
       </c>
+      <c r="E72" s="2">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="F72" s="2">
+        <v>0.8125</v>
+      </c>
       <c r="G72">
         <v>0</v>
       </c>
@@ -5500,6 +11275,12 @@
       <c r="D73" s="1">
         <v>45898</v>
       </c>
+      <c r="E73" s="2">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="F73" s="2">
+        <v>0.95833333333333337</v>
+      </c>
       <c r="G73">
         <v>0</v>
       </c>
@@ -5517,6 +11298,12 @@
       <c r="D74" s="1">
         <v>45899</v>
       </c>
+      <c r="E74" s="2">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="F74" s="2">
+        <v>0.77083333333333337</v>
+      </c>
       <c r="G74">
         <v>0</v>
       </c>
@@ -5534,6 +11321,12 @@
       <c r="D75" s="1">
         <v>45899</v>
       </c>
+      <c r="E75" s="2">
+        <v>0.875</v>
+      </c>
+      <c r="F75" s="2">
+        <v>0.91666666666666663</v>
+      </c>
       <c r="G75">
         <v>1</v>
       </c>
@@ -5551,92 +11344,124 @@
       <c r="D76" s="1">
         <v>45900</v>
       </c>
+      <c r="E76" s="2">
+        <v>0.875</v>
+      </c>
+      <c r="F76" s="2"/>
       <c r="G76">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77">
-        <v>2025</v>
-      </c>
-      <c r="B77">
+      <c r="A77" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B77" s="9">
         <v>16</v>
       </c>
-      <c r="C77" t="s">
+      <c r="C77" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="D77" s="1">
+      <c r="D77" s="13">
         <v>45905</v>
       </c>
-      <c r="G77">
+      <c r="E77" s="14">
+        <v>0.8125</v>
+      </c>
+      <c r="F77" s="14">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="G77" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78">
-        <v>2025</v>
-      </c>
-      <c r="B78">
+      <c r="A78" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B78" s="9">
         <v>16</v>
       </c>
-      <c r="C78" t="s">
+      <c r="C78" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="D78" s="1">
+      <c r="D78" s="13">
         <v>45905</v>
       </c>
-      <c r="G78">
+      <c r="E78" s="14">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="F78" s="14">
         <v>0</v>
       </c>
+      <c r="G78" s="9">
+        <v>0</v>
+      </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79">
-        <v>2025</v>
-      </c>
-      <c r="B79">
+      <c r="A79" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B79" s="9">
         <v>16</v>
       </c>
-      <c r="C79" t="s">
+      <c r="C79" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="D79" s="1">
+      <c r="D79" s="13">
         <v>45906</v>
       </c>
-      <c r="G79">
+      <c r="E79" s="14">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="F79" s="14">
+        <v>0.8125</v>
+      </c>
+      <c r="G79" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80">
-        <v>2025</v>
-      </c>
-      <c r="B80">
+      <c r="A80" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B80" s="9">
         <v>16</v>
       </c>
-      <c r="C80" t="s">
-        <v>11</v>
-      </c>
-      <c r="D80" s="1">
+      <c r="C80" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D80" s="13">
         <v>45906</v>
       </c>
-      <c r="G80">
+      <c r="E80" s="14">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="F80" s="14">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="G80" s="9">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A81">
-        <v>2025</v>
-      </c>
-      <c r="B81">
+      <c r="A81" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B81" s="9">
         <v>16</v>
       </c>
-      <c r="C81" t="s">
-        <v>14</v>
-      </c>
-      <c r="D81" s="1">
+      <c r="C81" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D81" s="13">
         <v>45907</v>
       </c>
-      <c r="G81">
+      <c r="E81" s="14">
+        <v>0.875</v>
+      </c>
+      <c r="F81" s="9"/>
+      <c r="G81" s="9">
         <v>1</v>
       </c>
     </row>
@@ -6328,7 +12153,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{247AF3E6-8BD7-40DE-ACC7-21D4F916BD21}">
-  <dimension ref="A1:R681"/>
+  <dimension ref="A1:R741"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -24339,7 +30164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="673" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A673" s="9">
         <v>2025</v>
       </c>
@@ -24365,7 +30190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="674" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A674" s="9">
         <v>2025</v>
       </c>
@@ -24391,7 +30216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="675" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A675" s="9">
         <v>2025</v>
       </c>
@@ -24417,7 +30242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="676" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A676" s="9">
         <v>2025</v>
       </c>
@@ -24443,7 +30268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="677" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A677" s="9">
         <v>2025</v>
       </c>
@@ -24469,7 +30294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="678" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A678" s="9">
         <v>2025</v>
       </c>
@@ -24495,7 +30320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="679" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A679" s="9">
         <v>2025</v>
       </c>
@@ -24521,7 +30346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="680" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A680" s="9">
         <v>2025</v>
       </c>
@@ -24547,7 +30372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="681" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A681" s="9">
         <v>2025</v>
       </c>
@@ -24572,6 +30397,1666 @@
       <c r="H681" s="9">
         <v>0</v>
       </c>
+    </row>
+    <row r="682" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A682">
+        <v>2025</v>
+      </c>
+      <c r="B682">
+        <v>15</v>
+      </c>
+      <c r="C682" t="s">
+        <v>11</v>
+      </c>
+      <c r="D682" s="3">
+        <v>1</v>
+      </c>
+      <c r="E682" s="3">
+        <v>81</v>
+      </c>
+      <c r="F682" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G682" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="N682" s="4"/>
+      <c r="O682" s="4"/>
+      <c r="P682" s="4"/>
+      <c r="Q682" s="3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="683" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A683">
+        <v>2025</v>
+      </c>
+      <c r="B683">
+        <v>15</v>
+      </c>
+      <c r="C683" t="s">
+        <v>11</v>
+      </c>
+      <c r="D683" s="3">
+        <v>2</v>
+      </c>
+      <c r="E683" s="3">
+        <v>4</v>
+      </c>
+      <c r="F683" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G683" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="N683" s="4"/>
+      <c r="O683" s="4"/>
+      <c r="P683" s="4"/>
+      <c r="Q683" s="3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="684" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A684">
+        <v>2025</v>
+      </c>
+      <c r="B684">
+        <v>15</v>
+      </c>
+      <c r="C684" t="s">
+        <v>11</v>
+      </c>
+      <c r="D684" s="3">
+        <v>3</v>
+      </c>
+      <c r="E684" s="3">
+        <v>1</v>
+      </c>
+      <c r="F684" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G684" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="N684" s="4"/>
+      <c r="O684" s="4"/>
+      <c r="P684" s="4"/>
+      <c r="Q684" s="3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="685" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A685">
+        <v>2025</v>
+      </c>
+      <c r="B685">
+        <v>15</v>
+      </c>
+      <c r="C685" t="s">
+        <v>11</v>
+      </c>
+      <c r="D685" s="3">
+        <v>4</v>
+      </c>
+      <c r="E685" s="3">
+        <v>6</v>
+      </c>
+      <c r="F685" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G685" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="N685" s="4"/>
+      <c r="O685" s="4"/>
+      <c r="P685" s="4"/>
+      <c r="Q685" s="3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="686" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A686">
+        <v>2025</v>
+      </c>
+      <c r="B686">
+        <v>15</v>
+      </c>
+      <c r="C686" t="s">
+        <v>11</v>
+      </c>
+      <c r="D686" s="3">
+        <v>5</v>
+      </c>
+      <c r="E686" s="3">
+        <v>63</v>
+      </c>
+      <c r="F686" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G686" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N686" s="4"/>
+      <c r="O686" s="4"/>
+      <c r="P686" s="4"/>
+      <c r="Q686" s="3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="687" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A687">
+        <v>2025</v>
+      </c>
+      <c r="B687">
+        <v>15</v>
+      </c>
+      <c r="C687" t="s">
+        <v>11</v>
+      </c>
+      <c r="D687" s="3">
+        <v>6</v>
+      </c>
+      <c r="E687" s="3">
+        <v>16</v>
+      </c>
+      <c r="F687" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G687" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="N687" s="4"/>
+      <c r="O687" s="4"/>
+      <c r="P687" s="4"/>
+      <c r="Q687" s="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="688" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A688">
+        <v>2025</v>
+      </c>
+      <c r="B688">
+        <v>15</v>
+      </c>
+      <c r="C688" t="s">
+        <v>11</v>
+      </c>
+      <c r="D688" s="3">
+        <v>7</v>
+      </c>
+      <c r="E688" s="3">
+        <v>44</v>
+      </c>
+      <c r="F688" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G688" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="N688" s="4"/>
+      <c r="O688" s="4"/>
+      <c r="P688" s="4"/>
+      <c r="Q688" s="3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="689" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A689">
+        <v>2025</v>
+      </c>
+      <c r="B689">
+        <v>15</v>
+      </c>
+      <c r="C689" t="s">
+        <v>11</v>
+      </c>
+      <c r="D689" s="3">
+        <v>8</v>
+      </c>
+      <c r="E689" s="3">
+        <v>30</v>
+      </c>
+      <c r="F689" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G689" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="N689" s="4"/>
+      <c r="O689" s="4"/>
+      <c r="P689" s="4"/>
+      <c r="Q689" s="3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="690" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A690">
+        <v>2025</v>
+      </c>
+      <c r="B690">
+        <v>15</v>
+      </c>
+      <c r="C690" t="s">
+        <v>11</v>
+      </c>
+      <c r="D690" s="3">
+        <v>9</v>
+      </c>
+      <c r="E690" s="3">
+        <v>55</v>
+      </c>
+      <c r="F690" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G690" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="N690" s="4"/>
+      <c r="O690" s="4"/>
+      <c r="P690" s="4"/>
+      <c r="Q690" s="3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="691" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A691">
+        <v>2025</v>
+      </c>
+      <c r="B691">
+        <v>15</v>
+      </c>
+      <c r="C691" t="s">
+        <v>11</v>
+      </c>
+      <c r="D691" s="3">
+        <v>10</v>
+      </c>
+      <c r="E691" s="3">
+        <v>14</v>
+      </c>
+      <c r="F691" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G691" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="N691" s="4"/>
+      <c r="O691" s="4"/>
+      <c r="P691" s="4"/>
+      <c r="Q691" s="3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="692" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A692">
+        <v>2025</v>
+      </c>
+      <c r="B692">
+        <v>15</v>
+      </c>
+      <c r="C692" t="s">
+        <v>11</v>
+      </c>
+      <c r="D692" s="3">
+        <v>11</v>
+      </c>
+      <c r="E692" s="3">
+        <v>12</v>
+      </c>
+      <c r="F692" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G692" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N692" s="4"/>
+      <c r="O692" s="4"/>
+      <c r="P692" s="3"/>
+      <c r="Q692" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="693" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A693">
+        <v>2025</v>
+      </c>
+      <c r="B693">
+        <v>15</v>
+      </c>
+      <c r="C693" t="s">
+        <v>11</v>
+      </c>
+      <c r="D693" s="3">
+        <v>12</v>
+      </c>
+      <c r="E693" s="3">
+        <v>22</v>
+      </c>
+      <c r="F693" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G693" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="N693" s="4"/>
+      <c r="O693" s="4"/>
+      <c r="P693" s="3"/>
+      <c r="Q693" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="694" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A694">
+        <v>2025</v>
+      </c>
+      <c r="B694">
+        <v>15</v>
+      </c>
+      <c r="C694" t="s">
+        <v>11</v>
+      </c>
+      <c r="D694" s="3">
+        <v>13</v>
+      </c>
+      <c r="E694" s="3">
+        <v>5</v>
+      </c>
+      <c r="F694" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G694" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="N694" s="4"/>
+      <c r="O694" s="4"/>
+      <c r="P694" s="3"/>
+      <c r="Q694" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="695" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A695">
+        <v>2025</v>
+      </c>
+      <c r="B695">
+        <v>15</v>
+      </c>
+      <c r="C695" t="s">
+        <v>11</v>
+      </c>
+      <c r="D695" s="3">
+        <v>14</v>
+      </c>
+      <c r="E695" s="3">
+        <v>10</v>
+      </c>
+      <c r="F695" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G695" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="N695" s="4"/>
+      <c r="O695" s="4"/>
+      <c r="P695" s="3"/>
+      <c r="Q695" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="696" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A696">
+        <v>2025</v>
+      </c>
+      <c r="B696">
+        <v>15</v>
+      </c>
+      <c r="C696" t="s">
+        <v>11</v>
+      </c>
+      <c r="D696" s="3">
+        <v>15</v>
+      </c>
+      <c r="E696" s="3">
+        <v>23</v>
+      </c>
+      <c r="F696" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G696" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="N696" s="4"/>
+      <c r="O696" s="4"/>
+      <c r="P696" s="3"/>
+      <c r="Q696" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="697" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A697">
+        <v>2025</v>
+      </c>
+      <c r="B697">
+        <v>15</v>
+      </c>
+      <c r="C697" t="s">
+        <v>11</v>
+      </c>
+      <c r="D697" s="3">
+        <v>16</v>
+      </c>
+      <c r="E697" s="3">
+        <v>43</v>
+      </c>
+      <c r="F697" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="G697" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="N697" s="4"/>
+      <c r="O697" s="3"/>
+      <c r="P697" s="3"/>
+      <c r="Q697" s="3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="698" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A698">
+        <v>2025</v>
+      </c>
+      <c r="B698">
+        <v>15</v>
+      </c>
+      <c r="C698" t="s">
+        <v>11</v>
+      </c>
+      <c r="D698" s="3">
+        <v>17</v>
+      </c>
+      <c r="E698" s="3">
+        <v>27</v>
+      </c>
+      <c r="F698" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G698" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="N698" s="4"/>
+      <c r="O698" s="3"/>
+      <c r="P698" s="3"/>
+      <c r="Q698" s="3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="699" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A699">
+        <v>2025</v>
+      </c>
+      <c r="B699">
+        <v>15</v>
+      </c>
+      <c r="C699" t="s">
+        <v>11</v>
+      </c>
+      <c r="D699" s="3">
+        <v>18</v>
+      </c>
+      <c r="E699" s="3">
+        <v>31</v>
+      </c>
+      <c r="F699" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G699" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="N699" s="4"/>
+      <c r="O699" s="3"/>
+      <c r="P699" s="3"/>
+      <c r="Q699" s="3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="700" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A700">
+        <v>2025</v>
+      </c>
+      <c r="B700">
+        <v>15</v>
+      </c>
+      <c r="C700" t="s">
+        <v>11</v>
+      </c>
+      <c r="D700" s="3">
+        <v>19</v>
+      </c>
+      <c r="E700" s="3">
+        <v>87</v>
+      </c>
+      <c r="F700" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G700" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="N700" s="4"/>
+      <c r="O700" s="3"/>
+      <c r="P700" s="3"/>
+      <c r="Q700" s="3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="701" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A701">
+        <v>2025</v>
+      </c>
+      <c r="B701">
+        <v>15</v>
+      </c>
+      <c r="C701" t="s">
+        <v>11</v>
+      </c>
+      <c r="D701" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="E701" s="3">
+        <v>18</v>
+      </c>
+      <c r="F701" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G701" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="N701" s="3"/>
+      <c r="O701" s="3"/>
+      <c r="P701" s="3"/>
+      <c r="Q701" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="702" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A702" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B702" s="9">
+        <v>15</v>
+      </c>
+      <c r="C702" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D702" s="12">
+        <v>1</v>
+      </c>
+      <c r="E702" s="12">
+        <v>81</v>
+      </c>
+      <c r="F702" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G702" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="H702" s="12">
+        <v>25</v>
+      </c>
+      <c r="I702" s="4"/>
+    </row>
+    <row r="703" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A703" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B703" s="9">
+        <v>15</v>
+      </c>
+      <c r="C703" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D703" s="12">
+        <v>2</v>
+      </c>
+      <c r="E703" s="12">
+        <v>1</v>
+      </c>
+      <c r="F703" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G703" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="H703" s="12">
+        <v>18</v>
+      </c>
+      <c r="I703" s="3"/>
+    </row>
+    <row r="704" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A704" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B704" s="9">
+        <v>15</v>
+      </c>
+      <c r="C704" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D704" s="12">
+        <v>3</v>
+      </c>
+      <c r="E704" s="12">
+        <v>6</v>
+      </c>
+      <c r="F704" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="G704" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="H704" s="12">
+        <v>15</v>
+      </c>
+      <c r="I704" s="3"/>
+    </row>
+    <row r="705" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A705" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B705" s="9">
+        <v>15</v>
+      </c>
+      <c r="C705" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D705" s="12">
+        <v>4</v>
+      </c>
+      <c r="E705" s="12">
+        <v>63</v>
+      </c>
+      <c r="F705" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G705" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="H705" s="12">
+        <v>12</v>
+      </c>
+      <c r="I705" s="3"/>
+    </row>
+    <row r="706" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A706" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B706" s="9">
+        <v>15</v>
+      </c>
+      <c r="C706" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D706" s="12">
+        <v>5</v>
+      </c>
+      <c r="E706" s="12">
+        <v>23</v>
+      </c>
+      <c r="F706" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="G706" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="H706" s="12">
+        <v>10</v>
+      </c>
+      <c r="I706" s="3"/>
+    </row>
+    <row r="707" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A707" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B707" s="9">
+        <v>15</v>
+      </c>
+      <c r="C707" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D707" s="12">
+        <v>6</v>
+      </c>
+      <c r="E707" s="12">
+        <v>87</v>
+      </c>
+      <c r="F707" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="G707" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="H707" s="12">
+        <v>8</v>
+      </c>
+      <c r="I707" s="3"/>
+    </row>
+    <row r="708" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A708" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B708" s="9">
+        <v>15</v>
+      </c>
+      <c r="C708" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D708" s="12">
+        <v>7</v>
+      </c>
+      <c r="E708" s="12">
+        <v>18</v>
+      </c>
+      <c r="F708" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="G708" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="H708" s="12">
+        <v>6</v>
+      </c>
+      <c r="I708" s="3"/>
+    </row>
+    <row r="709" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A709" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B709" s="9">
+        <v>15</v>
+      </c>
+      <c r="C709" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D709" s="12">
+        <v>8</v>
+      </c>
+      <c r="E709" s="12">
+        <v>14</v>
+      </c>
+      <c r="F709" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="G709" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="H709" s="12">
+        <v>4</v>
+      </c>
+      <c r="I709" s="3"/>
+    </row>
+    <row r="710" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A710" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B710" s="9">
+        <v>15</v>
+      </c>
+      <c r="C710" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D710" s="12">
+        <v>9</v>
+      </c>
+      <c r="E710" s="12">
+        <v>22</v>
+      </c>
+      <c r="F710" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G710" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="H710" s="12">
+        <v>2</v>
+      </c>
+      <c r="I710" s="3"/>
+    </row>
+    <row r="711" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A711" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B711" s="9">
+        <v>15</v>
+      </c>
+      <c r="C711" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D711" s="12">
+        <v>10</v>
+      </c>
+      <c r="E711" s="12">
+        <v>31</v>
+      </c>
+      <c r="F711" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="G711" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="H711" s="12">
+        <v>1</v>
+      </c>
+      <c r="I711" s="3"/>
+    </row>
+    <row r="712" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A712" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B712" s="9">
+        <v>15</v>
+      </c>
+      <c r="C712" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D712" s="12">
+        <v>11</v>
+      </c>
+      <c r="E712" s="12">
+        <v>43</v>
+      </c>
+      <c r="F712" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="G712" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="H712" s="12">
+        <v>0</v>
+      </c>
+      <c r="I712" s="3"/>
+    </row>
+    <row r="713" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A713" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B713" s="9">
+        <v>15</v>
+      </c>
+      <c r="C713" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D713" s="12">
+        <v>12</v>
+      </c>
+      <c r="E713" s="12">
+        <v>30</v>
+      </c>
+      <c r="F713" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="G713" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="H713" s="12">
+        <v>0</v>
+      </c>
+      <c r="I713" s="3"/>
+    </row>
+    <row r="714" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A714" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B714" s="9">
+        <v>15</v>
+      </c>
+      <c r="C714" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D714" s="12">
+        <v>13</v>
+      </c>
+      <c r="E714" s="12">
+        <v>55</v>
+      </c>
+      <c r="F714" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="G714" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="H714" s="12">
+        <v>0</v>
+      </c>
+      <c r="I714" s="3"/>
+    </row>
+    <row r="715" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A715" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B715" s="9">
+        <v>15</v>
+      </c>
+      <c r="C715" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D715" s="12">
+        <v>14</v>
+      </c>
+      <c r="E715" s="12">
+        <v>27</v>
+      </c>
+      <c r="F715" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="G715" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="H715" s="12">
+        <v>0</v>
+      </c>
+      <c r="I715" s="3"/>
+    </row>
+    <row r="716" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A716" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B716" s="9">
+        <v>15</v>
+      </c>
+      <c r="C716" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D716" s="12">
+        <v>15</v>
+      </c>
+      <c r="E716" s="12">
+        <v>5</v>
+      </c>
+      <c r="F716" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="G716" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="H716" s="12">
+        <v>0</v>
+      </c>
+      <c r="I716" s="3"/>
+    </row>
+    <row r="717" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A717" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B717" s="9">
+        <v>15</v>
+      </c>
+      <c r="C717" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D717" s="12">
+        <v>16</v>
+      </c>
+      <c r="E717" s="12">
+        <v>12</v>
+      </c>
+      <c r="F717" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="G717" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="H717" s="12">
+        <v>0</v>
+      </c>
+      <c r="I717" s="3"/>
+    </row>
+    <row r="718" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A718" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B718" s="9">
+        <v>15</v>
+      </c>
+      <c r="C718" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D718" s="12">
+        <v>17</v>
+      </c>
+      <c r="E718" s="12">
+        <v>10</v>
+      </c>
+      <c r="F718" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G718" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="H718" s="12">
+        <v>0</v>
+      </c>
+      <c r="I718" s="3"/>
+    </row>
+    <row r="719" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A719" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B719" s="9">
+        <v>15</v>
+      </c>
+      <c r="C719" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D719" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="E719" s="12">
+        <v>4</v>
+      </c>
+      <c r="F719" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="G719" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="H719" s="12">
+        <v>0</v>
+      </c>
+      <c r="I719" s="3"/>
+    </row>
+    <row r="720" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A720" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B720" s="9">
+        <v>15</v>
+      </c>
+      <c r="C720" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D720" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="E720" s="12">
+        <v>16</v>
+      </c>
+      <c r="F720" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="G720" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="H720" s="12">
+        <v>0</v>
+      </c>
+      <c r="I720" s="3"/>
+    </row>
+    <row r="721" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A721" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B721" s="9">
+        <v>15</v>
+      </c>
+      <c r="C721" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D721" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="E721" s="12">
+        <v>44</v>
+      </c>
+      <c r="F721" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="G721" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="H721" s="12">
+        <v>0</v>
+      </c>
+      <c r="I721" s="3"/>
+    </row>
+    <row r="722" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A722">
+        <v>2025</v>
+      </c>
+      <c r="B722" s="15">
+        <v>16</v>
+      </c>
+      <c r="C722" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D722" s="3">
+        <v>1</v>
+      </c>
+      <c r="E722" s="3">
+        <v>1</v>
+      </c>
+      <c r="F722" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G722" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="H722" s="4"/>
+      <c r="I722" s="4"/>
+      <c r="J722" s="4"/>
+      <c r="K722" s="3"/>
+    </row>
+    <row r="723" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A723">
+        <v>2025</v>
+      </c>
+      <c r="B723" s="15">
+        <v>16</v>
+      </c>
+      <c r="C723" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D723" s="3">
+        <v>2</v>
+      </c>
+      <c r="E723" s="3">
+        <v>4</v>
+      </c>
+      <c r="F723" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G723" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H723" s="4"/>
+      <c r="I723" s="4"/>
+      <c r="J723" s="4"/>
+      <c r="K723" s="3"/>
+    </row>
+    <row r="724" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A724">
+        <v>2025</v>
+      </c>
+      <c r="B724" s="15">
+        <v>16</v>
+      </c>
+      <c r="C724" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D724" s="3">
+        <v>3</v>
+      </c>
+      <c r="E724" s="3">
+        <v>81</v>
+      </c>
+      <c r="F724" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G724" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H724" s="4"/>
+      <c r="I724" s="4"/>
+      <c r="J724" s="4"/>
+      <c r="K724" s="3"/>
+    </row>
+    <row r="725" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A725">
+        <v>2025</v>
+      </c>
+      <c r="B725" s="15">
+        <v>16</v>
+      </c>
+      <c r="C725" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D725" s="3">
+        <v>4</v>
+      </c>
+      <c r="E725" s="3">
+        <v>16</v>
+      </c>
+      <c r="F725" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G725" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H725" s="4"/>
+      <c r="I725" s="4"/>
+      <c r="J725" s="4"/>
+      <c r="K725" s="3"/>
+    </row>
+    <row r="726" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A726">
+        <v>2025</v>
+      </c>
+      <c r="B726" s="15">
+        <v>16</v>
+      </c>
+      <c r="C726" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D726" s="3">
+        <v>5</v>
+      </c>
+      <c r="E726" s="3">
+        <v>44</v>
+      </c>
+      <c r="F726" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G726" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H726" s="4"/>
+      <c r="I726" s="4"/>
+      <c r="J726" s="4"/>
+      <c r="K726" s="3"/>
+    </row>
+    <row r="727" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A727">
+        <v>2025</v>
+      </c>
+      <c r="B727" s="15">
+        <v>16</v>
+      </c>
+      <c r="C727" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D727" s="3">
+        <v>6</v>
+      </c>
+      <c r="E727" s="3">
+        <v>63</v>
+      </c>
+      <c r="F727" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G727" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H727" s="4"/>
+      <c r="I727" s="4"/>
+      <c r="J727" s="4"/>
+      <c r="K727" s="3"/>
+    </row>
+    <row r="728" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A728">
+        <v>2025</v>
+      </c>
+      <c r="B728" s="15">
+        <v>16</v>
+      </c>
+      <c r="C728" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D728" s="3">
+        <v>7</v>
+      </c>
+      <c r="E728" s="3">
+        <v>12</v>
+      </c>
+      <c r="F728" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G728" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H728" s="4"/>
+      <c r="I728" s="4"/>
+      <c r="J728" s="4"/>
+      <c r="K728" s="3"/>
+    </row>
+    <row r="729" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A729">
+        <v>2025</v>
+      </c>
+      <c r="B729" s="15">
+        <v>16</v>
+      </c>
+      <c r="C729" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D729" s="3">
+        <v>8</v>
+      </c>
+      <c r="E729" s="3">
+        <v>5</v>
+      </c>
+      <c r="F729" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G729" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="H729" s="4"/>
+      <c r="I729" s="4"/>
+      <c r="J729" s="4"/>
+      <c r="K729" s="3"/>
+    </row>
+    <row r="730" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A730">
+        <v>2025</v>
+      </c>
+      <c r="B730" s="15">
+        <v>16</v>
+      </c>
+      <c r="C730" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D730" s="3">
+        <v>9</v>
+      </c>
+      <c r="E730" s="3">
+        <v>14</v>
+      </c>
+      <c r="F730" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G730" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="H730" s="4"/>
+      <c r="I730" s="4"/>
+      <c r="J730" s="4"/>
+      <c r="K730" s="3"/>
+    </row>
+    <row r="731" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A731">
+        <v>2025</v>
+      </c>
+      <c r="B731" s="15">
+        <v>16</v>
+      </c>
+      <c r="C731" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D731" s="3">
+        <v>10</v>
+      </c>
+      <c r="E731" s="3">
+        <v>22</v>
+      </c>
+      <c r="F731" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G731" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="H731" s="4"/>
+      <c r="I731" s="4"/>
+      <c r="J731" s="4"/>
+      <c r="K731" s="3"/>
+    </row>
+    <row r="732" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A732">
+        <v>2025</v>
+      </c>
+      <c r="B732" s="15">
+        <v>16</v>
+      </c>
+      <c r="C732" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D732" s="3">
+        <v>11</v>
+      </c>
+      <c r="E732" s="3">
+        <v>87</v>
+      </c>
+      <c r="F732" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G732" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="H732" s="4"/>
+      <c r="I732" s="4"/>
+      <c r="J732" s="3"/>
+      <c r="K732" s="3"/>
+    </row>
+    <row r="733" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A733">
+        <v>2025</v>
+      </c>
+      <c r="B733" s="15">
+        <v>16</v>
+      </c>
+      <c r="C733" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D733" s="3">
+        <v>12</v>
+      </c>
+      <c r="E733" s="3">
+        <v>27</v>
+      </c>
+      <c r="F733" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G733" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="H733" s="4"/>
+      <c r="I733" s="4"/>
+      <c r="J733" s="3"/>
+      <c r="K733" s="3"/>
+    </row>
+    <row r="734" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A734">
+        <v>2025</v>
+      </c>
+      <c r="B734" s="15">
+        <v>16</v>
+      </c>
+      <c r="C734" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D734" s="3">
+        <v>13</v>
+      </c>
+      <c r="E734" s="3">
+        <v>55</v>
+      </c>
+      <c r="F734" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G734" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="H734" s="4"/>
+      <c r="I734" s="4"/>
+      <c r="J734" s="3"/>
+      <c r="K734" s="3"/>
+    </row>
+    <row r="735" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A735">
+        <v>2025</v>
+      </c>
+      <c r="B735" s="15">
+        <v>16</v>
+      </c>
+      <c r="C735" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D735" s="3">
+        <v>14</v>
+      </c>
+      <c r="E735" s="3">
+        <v>23</v>
+      </c>
+      <c r="F735" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G735" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="H735" s="4"/>
+      <c r="I735" s="4"/>
+      <c r="J735" s="3"/>
+      <c r="K735" s="3"/>
+    </row>
+    <row r="736" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A736">
+        <v>2025</v>
+      </c>
+      <c r="B736" s="15">
+        <v>16</v>
+      </c>
+      <c r="C736" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D736" s="3">
+        <v>15</v>
+      </c>
+      <c r="E736" s="3">
+        <v>31</v>
+      </c>
+      <c r="F736" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G736" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="H736" s="4"/>
+      <c r="I736" s="4"/>
+      <c r="J736" s="3"/>
+      <c r="K736" s="3"/>
+    </row>
+    <row r="737" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A737">
+        <v>2025</v>
+      </c>
+      <c r="B737" s="15">
+        <v>16</v>
+      </c>
+      <c r="C737" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D737" s="3">
+        <v>16</v>
+      </c>
+      <c r="E737" s="3">
+        <v>6</v>
+      </c>
+      <c r="F737" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G737" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="H737" s="4"/>
+      <c r="I737" s="3"/>
+      <c r="J737" s="3"/>
+      <c r="K737" s="3"/>
+    </row>
+    <row r="738" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A738">
+        <v>2025</v>
+      </c>
+      <c r="B738" s="15">
+        <v>16</v>
+      </c>
+      <c r="C738" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D738" s="3">
+        <v>17</v>
+      </c>
+      <c r="E738" s="3">
+        <v>18</v>
+      </c>
+      <c r="F738" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G738" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="H738" s="4"/>
+      <c r="I738" s="3"/>
+      <c r="J738" s="3"/>
+      <c r="K738" s="3"/>
+    </row>
+    <row r="739" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A739">
+        <v>2025</v>
+      </c>
+      <c r="B739" s="15">
+        <v>16</v>
+      </c>
+      <c r="C739" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D739" s="3">
+        <v>18</v>
+      </c>
+      <c r="E739" s="3">
+        <v>43</v>
+      </c>
+      <c r="F739" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="G739" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="H739" s="4"/>
+      <c r="I739" s="3"/>
+      <c r="J739" s="3"/>
+      <c r="K739" s="3"/>
+    </row>
+    <row r="740" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A740">
+        <v>2025</v>
+      </c>
+      <c r="B740" s="15">
+        <v>16</v>
+      </c>
+      <c r="C740" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D740" s="3">
+        <v>19</v>
+      </c>
+      <c r="E740" s="3">
+        <v>10</v>
+      </c>
+      <c r="F740" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G740" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="H740" s="4"/>
+      <c r="I740" s="3"/>
+      <c r="J740" s="3"/>
+      <c r="K740" s="3"/>
+    </row>
+    <row r="741" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A741">
+        <v>2025</v>
+      </c>
+      <c r="B741" s="15">
+        <v>16</v>
+      </c>
+      <c r="C741" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D741" s="3">
+        <v>20</v>
+      </c>
+      <c r="E741" s="3">
+        <v>30</v>
+      </c>
+      <c r="F741" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G741" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="H741" s="4"/>
+      <c r="I741" s="3"/>
+      <c r="J741" s="3"/>
+      <c r="K741" s="3"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:H561" xr:uid="{247AF3E6-8BD7-40DE-ACC7-21D4F916BD21}"/>

--- a/public/docs/datas/f1.xlsx
+++ b/public/docs/datas/f1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\vue_platform\public\docs\datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7F37524-9BF0-4172-AA84-C71D10B5DFCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF6C2E38-3AD0-4E6A-8F81-516FBFC1CBA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11556" yWindow="3708" windowWidth="21216" windowHeight="15924" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11556" yWindow="3708" windowWidth="21216" windowHeight="15924" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="rounds" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2623" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2685" uniqueCount="220">
   <si>
     <t>year</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -925,7 +925,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -953,7 +953,6 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="20" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -969,7691 +968,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>581</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>582</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3153" name="AutoShape 81">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6C1F7592-2054-B57E-C943-A55A166D8DE1}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3025140" y="101826060"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>581</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>582</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3154" name="AutoShape 82">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{672DB597-3D24-1E9F-0D73-2C221718FC03}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4152900" y="101826060"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>582</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>583</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3155" name="AutoShape 83">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3E85D10C-13EF-56CE-138F-DCBEE96E5BC2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3025140" y="102001320"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>582</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>583</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3156" name="AutoShape 84">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B9F84F4F-C9AC-E101-BDCE-16939E39BD6D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4152900" y="102001320"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>583</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>584</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3157" name="AutoShape 85">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9CAD4C19-2B02-8C3D-27EA-FFD44DFB661F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3025140" y="102176580"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>583</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>584</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3158" name="AutoShape 86">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{664EC55E-7F31-FE30-7DEE-67302CDBAB77}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4152900" y="102176580"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>584</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>585</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3159" name="AutoShape 87">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BC83C424-F00E-DD55-6221-2BF2A2616F1A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3025140" y="102351840"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>584</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>585</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3160" name="AutoShape 88">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B11E00B0-CDAB-62CF-5D17-FD7EBE92A0C9}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4152900" y="102351840"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>585</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>586</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3161" name="AutoShape 89">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{33209DE9-85A5-70E5-833D-2B6118700504}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3025140" y="102527100"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>585</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>586</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3162" name="AutoShape 90">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5FC74CE6-0864-A999-8335-275349DA2ACC}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4152900" y="102527100"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>586</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>587</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3163" name="AutoShape 91">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5270EE43-8F71-B4B9-052F-5312514A1790}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3025140" y="102702360"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>586</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>587</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3164" name="AutoShape 92">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2EDA486E-44EB-1F95-A5DF-4D75B13B8476}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4152900" y="102702360"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>587</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>588</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3165" name="AutoShape 93">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4C32A49C-8BDA-4D6B-B0F1-FCC3603533CD}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3025140" y="102877620"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>587</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>588</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3166" name="AutoShape 94">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CCECC00E-91B9-397E-3ED6-6695E371A3E4}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4152900" y="102877620"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>588</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>589</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3167" name="AutoShape 95">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C5D9A736-CA52-2C7A-113A-9C7EF7307EC9}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3025140" y="103052880"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>588</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>589</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3168" name="AutoShape 96">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C7B4B545-25BC-44F2-EEB0-8628497207DA}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4152900" y="103052880"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>589</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>590</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3169" name="AutoShape 97">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EA553B0A-E8ED-0FA1-975F-004A678B7726}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3025140" y="103228140"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>589</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>590</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3170" name="AutoShape 98">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{72E69B2A-8A4C-62DC-C6BE-9E4F19483947}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4152900" y="103228140"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>590</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>591</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3171" name="AutoShape 99">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A8608FBC-1164-5F70-981F-2727D406227B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3025140" y="103403400"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>590</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>591</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3172" name="AutoShape 100">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{045BDAB3-D9FE-189E-1E3B-93C4EE8ADE8D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4152900" y="103403400"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>591</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>592</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3173" name="AutoShape 101">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{80E93BFA-DE07-886D-5CA2-B1E1F13C560C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3025140" y="103578660"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>591</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>592</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3174" name="AutoShape 102">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1024DE9A-BA76-E5AB-1F90-2A27772C3911}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4152900" y="103578660"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>592</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>593</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3175" name="AutoShape 103">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6640290E-2EB7-71BA-EDFC-1D56D8F88377}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3025140" y="103753920"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>592</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>593</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3176" name="AutoShape 104">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4C472805-9B24-9027-0F40-AA47A43F7620}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4152900" y="103753920"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>593</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>594</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3177" name="AutoShape 105">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3334953C-1300-4044-50ED-C60C6FE7BEDD}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3025140" y="103929180"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>593</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>594</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3178" name="AutoShape 106">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3BBA1F81-A103-E775-9EF6-1A3111DF11CE}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4152900" y="103929180"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>594</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>595</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3179" name="AutoShape 107">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E20B471-0822-5C5B-3DF0-093AF364338A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3025140" y="104104440"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>594</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>595</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3180" name="AutoShape 108">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{09E432A0-5CE5-AD7D-259D-496B6922F01C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4152900" y="104104440"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>595</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>596</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3181" name="AutoShape 109">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D26DE36-95CD-FCDF-CC1D-0C301655BFB4}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3025140" y="104279700"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>595</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>596</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3182" name="AutoShape 110">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1A357113-F285-ABA3-551D-60487C75AA69}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4152900" y="104279700"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>596</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>597</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3183" name="AutoShape 111">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0E18AF99-0F9E-CC36-D948-481310E494D9}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3025140" y="104454960"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>596</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>597</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3184" name="AutoShape 112">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{87362D51-D576-D50C-1A5D-F7EC470D6461}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4152900" y="104454960"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>597</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>598</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3185" name="AutoShape 113">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{87F94E4A-E2E0-3677-E006-31675E33B04A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3025140" y="104630220"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>597</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>598</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3186" name="AutoShape 114">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{02E6B4B5-CA8E-F296-E13F-262245C200CE}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4152900" y="104630220"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>598</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>599</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3187" name="AutoShape 115">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9DEBFE6D-1EF1-BD00-143C-F57FE85F70D0}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3025140" y="104805480"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>598</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>599</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3188" name="AutoShape 116">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{01CBFCB7-F573-C847-637E-4FE82DA100DD}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4152900" y="104805480"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>599</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>600</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3189" name="AutoShape 117">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5AC558CF-821F-F1D6-8AFC-05F57CA166F2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3025140" y="104980740"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>599</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>600</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3190" name="AutoShape 118">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AA05CD41-B9F3-9207-D3F4-087CF62FBD9E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4152900" y="104980740"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>600</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>601</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3191" name="AutoShape 119">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{16E7E008-784C-8AD8-987E-DA1D639C1669}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3025140" y="105156000"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>600</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>601</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3192" name="AutoShape 120">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D739D42-3E05-1F8D-8B84-35E61986BFE9}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4152900" y="105156000"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>681</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>682</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1025" name="AutoShape 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7BC57E91-3409-753C-D667-1CB218FD0123}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="9395460" y="119352060"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>681</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>682</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1026" name="AutoShape 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BC261385-980A-8B5C-5163-A3D87FCF611B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="10005060" y="119352060"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>682</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>683</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1027" name="AutoShape 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EF8E56C4-2D53-76B9-0DAB-5E8B29DB5402}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="9395460" y="119702580"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>682</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>683</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1028" name="AutoShape 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4166C80F-5F22-A123-D733-9C14CEE50585}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="10005060" y="119702580"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>683</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>684</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1029" name="AutoShape 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9A628B5-A92E-E696-F88F-FFF4837B9FFD}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="9395460" y="120053100"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>683</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>684</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1030" name="AutoShape 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EEB8F80B-52A8-BEFB-29FB-79C45955EEC6}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="10005060" y="120053100"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>684</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>685</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1031" name="AutoShape 7">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{530DE4DC-E728-85EC-2047-78810410DE71}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="9395460" y="120578880"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>684</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>685</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1032" name="AutoShape 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD61A14B-75C8-DA4E-F5AE-E294D35EEC34}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="10005060" y="120578880"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>685</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>686</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1033" name="AutoShape 9">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{14C062D7-AC1E-27A3-8F0F-AF2FF3A064B3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="9395460" y="120929400"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>685</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>686</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1034" name="AutoShape 10">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{519DE775-97DD-3740-A1AE-84715118F153}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="10005060" y="120929400"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>686</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>687</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1035" name="AutoShape 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8057919A-91E7-F841-12AA-E8AC3D6635F1}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="9395460" y="121279920"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>686</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>687</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1036" name="AutoShape 12">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D6EF8F81-55D0-E302-F05A-D4C619AE1005}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="10005060" y="121279920"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>687</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>688</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1037" name="AutoShape 13">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{94260E9D-0F18-932E-26F8-0B03176649D8}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="9395460" y="121630440"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>687</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>688</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1038" name="AutoShape 14">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B56CD907-2E52-7D04-ABC9-3B3CA0B40D3E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="10005060" y="121630440"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>688</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>689</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1039" name="AutoShape 15">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6154F1AC-8F64-B556-40EB-E6ED0976B986}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="9395460" y="121980960"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>688</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>689</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1040" name="AutoShape 16">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A719C8DC-3617-899A-08CB-F51252C234A8}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="10005060" y="121980960"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>689</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>690</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1041" name="AutoShape 17">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{47A574D7-4E0B-AC0B-F1ED-3D2BE71C1AB7}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="9395460" y="122331480"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>689</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>690</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1042" name="AutoShape 18">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{614EA7B9-3D99-21DA-4107-872E2D35B06F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="10005060" y="122331480"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>690</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>691</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1043" name="AutoShape 19">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9C603B79-13F9-786F-9A14-530C5EF30DD8}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="9395460" y="122682000"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>690</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>691</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1044" name="AutoShape 20">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9F13FBFD-C2C9-F910-0A0D-8B307D5CDA6C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="10005060" y="122682000"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>691</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>692</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1045" name="AutoShape 21">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D096DEC8-DC7C-B364-C314-BFBE63F8CC55}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="9395460" y="123032520"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>691</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>692</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1046" name="AutoShape 22">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F415AE2-7EEE-6EFA-87A3-A12870DDBD43}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="10005060" y="123032520"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>692</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>693</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1047" name="AutoShape 23">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1C45DB0C-B961-8772-2760-E882AF77F1ED}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="9395460" y="123383040"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>692</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>693</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1048" name="AutoShape 24">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2195EFEB-F442-5ED2-243F-8D825F8A28E7}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="10005060" y="123383040"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>693</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>694</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1049" name="AutoShape 25">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AF00B631-B0F0-5869-BAD3-DF3E5A07A189}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="9395460" y="123733560"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>693</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>694</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1050" name="AutoShape 26">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7164D885-BCFB-A31A-816C-770039557B01}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="10005060" y="123733560"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>694</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>695</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1051" name="AutoShape 27">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{35B80F18-03FA-AF00-EBC2-F796D9E2454B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="9395460" y="124084080"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>694</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>695</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1052" name="AutoShape 28">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{51815C0A-4C92-431C-E1FC-1BE848472979}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="10005060" y="124084080"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>695</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>696</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1053" name="AutoShape 29">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{38B9A0FB-3AB4-D1CA-3696-2FA5C7C993A1}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="9395460" y="124434600"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>695</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>696</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1054" name="AutoShape 30">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C00DA528-968F-15E1-2EBE-6B7F1B8F2815}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="10005060" y="124434600"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>696</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>697</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1055" name="AutoShape 31">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5B2DA1FF-8317-7F91-FEFE-55F7AD9ADA8A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="9395460" y="124785120"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>696</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>697</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1056" name="AutoShape 32">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7CFE8D79-36B7-A723-3868-6BE892D4DE3F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="10005060" y="124785120"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>697</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>698</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1057" name="AutoShape 33">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5FE5EADD-A1AA-0662-A0D6-8879C2EA523D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="9395460" y="125310900"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>697</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>698</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1058" name="AutoShape 34">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32142157-F7BA-154A-C6D0-5713664EE1B4}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="10005060" y="125310900"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>698</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>699</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1059" name="AutoShape 35">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0A2825DF-76F1-D1C6-AE37-B2B840602CAD}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="9395460" y="125836680"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>698</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>699</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1060" name="AutoShape 36">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F64B257D-549A-BCB7-43D3-25C929E21FAE}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="10005060" y="125836680"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>699</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>700</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1061" name="AutoShape 37">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D6F83687-FCD2-971C-6EE0-C12D92E0D721}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="9395460" y="126187200"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>699</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>700</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1062" name="AutoShape 38">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8A320FA5-184F-5F10-92BB-FEB717C81FFB}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="10005060" y="126187200"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>700</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>701</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1063" name="AutoShape 39">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FCC46CEF-336B-6F2C-03E7-588F29DE486F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="9395460" y="126537720"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>700</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>701</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1064" name="AutoShape 40">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B193F8E0-02AD-420B-951E-EFFDF3EB42D1}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="10005060" y="126537720"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>701</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>702</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1065" name="AutoShape 41">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{20EE77D9-F13F-9C18-927E-F7407CB66FC6}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3025140" y="122857260"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>701</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>702</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1066" name="AutoShape 42">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FA9441A9-7998-BDB4-9C4E-B7418001B290}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4152900" y="122857260"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>702</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>703</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1067" name="AutoShape 43">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D3D3188C-2BDF-399B-44F2-89B6FD460EF6}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3025140" y="123032520"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>702</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>703</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1068" name="AutoShape 44">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F8DF527C-4FDD-4E8C-52FC-F639A8057828}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4152900" y="123032520"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>703</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>704</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1069" name="AutoShape 45">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3A341831-A9C5-AC7B-A50A-163EC43F9CD3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3025140" y="123207780"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>703</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>704</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1070" name="AutoShape 46">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1C093E53-0788-5498-8088-7A7130DECF33}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4152900" y="123207780"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>704</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>705</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1071" name="AutoShape 47">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EFA3C8ED-9AB0-F6D6-C5E8-2CEB54C49C8C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3025140" y="123383040"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>704</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>705</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1072" name="AutoShape 48">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5CBD58A2-E2B8-1F56-AB90-823409483C8F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4152900" y="123383040"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>705</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>706</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1073" name="AutoShape 49">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{40FB1663-05F7-2E68-E8E2-1370F2739F8B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3025140" y="123558300"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>705</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>706</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1074" name="AutoShape 50">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{058DBD46-7D2C-1BF7-4AF7-148C6847311C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4152900" y="123558300"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>706</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>707</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1075" name="AutoShape 51">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F17BF864-0186-DE52-197B-EAA7DF0567F4}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3025140" y="123733560"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>706</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>707</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1076" name="AutoShape 52">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6EFF7681-AACE-EC97-DFB0-0F4A229896DB}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4152900" y="123733560"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>707</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>708</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1077" name="AutoShape 53">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F0D02E3-DC0F-0290-0581-72C99D29D855}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3025140" y="123908820"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>707</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>708</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1078" name="AutoShape 54">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E3CA179-B697-90E9-FE51-80F81C2B9CF5}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4152900" y="123908820"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>708</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>709</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1079" name="AutoShape 55">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F6A524F8-3762-A06B-AFEE-0F48CDB20C72}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3025140" y="124084080"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>708</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>709</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1080" name="AutoShape 56">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F0713B9E-18C0-B4F0-B049-1F188F8BE4D9}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4152900" y="124084080"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>709</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>710</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1081" name="AutoShape 57">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{95A00A2E-D6BE-27D7-7E6C-48F45EFFD6AE}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3025140" y="124259340"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>709</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>710</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1082" name="AutoShape 58">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EA60520F-C1CC-67B0-A1B7-F6F300949F93}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4152900" y="124259340"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>710</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>711</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1083" name="AutoShape 59">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7FCFEE88-7D1F-D5F4-D063-CB1F4EC34B33}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3025140" y="124434600"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>710</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>711</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1084" name="AutoShape 60">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5511EBCA-5C59-D95F-FBA9-310E71F875FD}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4152900" y="124434600"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>711</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>712</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1085" name="AutoShape 61">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{186EF60D-3EE9-B9B5-FC14-833E7673DE43}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3025140" y="124609860"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>711</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>712</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1086" name="AutoShape 62">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{289BBB4C-6B77-A6BF-BF55-F5C6A9295CE6}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4152900" y="124609860"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>712</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>713</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1087" name="AutoShape 63">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D64C7450-C759-2D64-773A-9E25EABC95D5}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3025140" y="124785120"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>712</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>713</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1088" name="AutoShape 64">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{70F4D287-4721-CAE4-C5B4-D4CCB8233566}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4152900" y="124785120"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>713</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>714</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1089" name="AutoShape 65">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0640F955-DD83-2FAC-410A-8D87729A62F7}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3025140" y="124960380"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>713</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>714</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1090" name="AutoShape 66">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{73F73574-8E59-EF3E-DE24-C6813EC2B74A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4152900" y="124960380"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>714</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>715</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1091" name="AutoShape 67">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{29A0E317-C4B3-2CD9-2260-73E3D80BB778}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3025140" y="125135640"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>714</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>715</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1092" name="AutoShape 68">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D681D87B-B7CE-4909-9B74-5E3D8ACF5916}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4152900" y="125135640"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>715</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>716</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1093" name="AutoShape 69">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5A60BDB8-DFC4-253A-EF9A-659DC0B9A78D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3025140" y="125310900"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>715</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>716</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1094" name="AutoShape 70">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{12D6A5F3-FE04-B443-A9DC-96EA78EE48C4}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4152900" y="125310900"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>716</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>717</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1095" name="AutoShape 71">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DC159220-62EB-376C-2CDD-772B3F99FA91}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3025140" y="125486160"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>716</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>717</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1096" name="AutoShape 72">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5C6A2050-227C-FE8C-BF8E-C23F43AF84C3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4152900" y="125486160"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>717</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>718</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1097" name="AutoShape 73">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D845DBA4-4147-CBBA-1D66-D7E766345319}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3025140" y="125661420"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>717</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>718</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1098" name="AutoShape 74">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5DB1D135-3989-DA53-0E56-3FC10B703E5F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4152900" y="125661420"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>718</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>719</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1099" name="AutoShape 75">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C4742536-BB37-572C-01B5-3D28DF6206AB}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3025140" y="125836680"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>718</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>719</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1100" name="AutoShape 76">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D5FB46E1-458E-A3E6-3E2E-B256D6266BD8}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4152900" y="125836680"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>719</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>720</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1101" name="AutoShape 77">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5201B775-2559-DC9D-97DD-7E6A445D8039}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3025140" y="126011940"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>719</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>720</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1102" name="AutoShape 78">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FFAF11C8-5364-C6E5-C298-5DA00E5A38CE}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4152900" y="126011940"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>720</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>721</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1103" name="AutoShape 79">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5841144D-510F-AC75-26CC-ECCFCECC8309}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3025140" y="126187200"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>720</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>721</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1104" name="AutoShape 80">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{848C3BD9-3000-A73C-3B85-123763E9F69E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4152900" y="126187200"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>721</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>722</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="AutoShape 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9723AA0A-E021-ED54-DFFC-A889183C52F9}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3025140" y="126362460"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>721</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>722</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="AutoShape 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F137BDB3-AC91-1794-C4FD-7AF9D3720B08}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4152900" y="126362460"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>722</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>723</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="AutoShape 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{993A788C-2438-6E7D-E59C-F911BD52923F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3025140" y="126537720"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>722</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>723</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="AutoShape 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D310EFE3-D89A-6261-6BAF-9DE43B6F0987}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4152900" y="126537720"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>723</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>724</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="AutoShape 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B35E418B-7971-9868-5A3E-D9612591EC35}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3025140" y="126712980"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>723</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>724</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="7" name="AutoShape 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F356922-4659-BF73-09B7-436C4EE095F7}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4152900" y="126712980"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>724</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>725</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="8" name="AutoShape 7">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2D80A92F-E50F-7ACF-6AA7-9A7C0B541372}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3025140" y="126888240"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>724</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>725</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="9" name="AutoShape 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B24CA894-3F91-8A87-4B88-D1C1496B485A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4152900" y="126888240"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>725</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>726</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="10" name="AutoShape 9">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DC396DB5-F44F-031E-2838-03815EBF1A6F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3025140" y="127063500"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>725</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>726</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="11" name="AutoShape 10">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{782998E4-3B59-A1E3-ACE0-09353D93CB00}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4152900" y="127063500"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>726</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>727</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="12" name="AutoShape 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7A874636-FD9A-3837-B457-65B838A99A30}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3025140" y="127238760"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>726</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>727</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="13" name="AutoShape 12">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8F30E5C9-BABD-465E-9A1C-64C96DFF5329}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4152900" y="127238760"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>727</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>728</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="14" name="AutoShape 13">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8ED7A262-A53C-6358-0171-3393F9F3D0F3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3025140" y="127414020"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>727</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>728</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="15" name="AutoShape 14">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6A982CE7-12A8-A29C-C3BB-49BD827AA1EF}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4152900" y="127414020"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>728</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>729</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="16" name="AutoShape 15">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E7E8DA9B-F402-5CC0-5B36-1B0C40A5D90C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3025140" y="127589280"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>728</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>729</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="17" name="AutoShape 16">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D256F25D-2748-EF76-7EC9-DF0544CDC57E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4152900" y="127589280"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>729</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>730</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="18" name="AutoShape 17">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BDCBA148-92CF-FF67-6F5F-B1DDC30BAD1A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3025140" y="127764540"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>729</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>730</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="19" name="AutoShape 18">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1F640964-124F-834B-2D9E-20BCA616F653}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4152900" y="127764540"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>730</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>731</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="20" name="AutoShape 19">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8A1B1697-772E-4D39-4B2C-6D56CB3F0162}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3025140" y="127939800"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>730</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>731</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="21" name="AutoShape 20">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E7C7AA92-59FF-53E5-155D-844100540998}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4152900" y="127939800"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>731</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>732</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="22" name="AutoShape 21">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3D8E77EB-F19C-8805-0DD1-739D4E69BB92}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3025140" y="128115060"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>731</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>732</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="23" name="AutoShape 22">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F90565F0-4B96-4A68-4664-7D900E4D37CF}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4152900" y="128115060"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>732</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>733</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="24" name="AutoShape 23">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1A1DCECD-9604-6EC1-DA0D-CF78CE4CB110}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3025140" y="128290320"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>732</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>733</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="25" name="AutoShape 24">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B4FC6C85-C7AD-24DA-316A-A30D904F9ED1}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4152900" y="128290320"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>733</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>734</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="26" name="AutoShape 25">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C94A291-39F6-7806-A74A-AB2A13E9140E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3025140" y="128465580"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>733</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>734</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="27" name="AutoShape 26">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A0F5955E-48EB-8E3F-BAA0-5FA5D2AFBF05}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4152900" y="128465580"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>734</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>735</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="28" name="AutoShape 27">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D2EEFF86-6D19-3EC7-25E9-6C128C1A7308}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3025140" y="128640840"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>734</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>735</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="29" name="AutoShape 28">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6BCE8144-BA8A-F582-704C-9956F6C0B9F9}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4152900" y="128640840"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>735</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>736</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="30" name="AutoShape 29">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{202A1ACE-AF3A-1725-0AE1-AA986CAA671D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3025140" y="128816100"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>735</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>736</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="31" name="AutoShape 30">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6AF0A94E-0FBE-F6CD-5C39-821D704BBAB1}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4152900" y="128816100"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>736</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>737</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="32" name="AutoShape 31">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{57001B32-64D7-4760-BBEE-42FD6ED5332F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3025140" y="128991360"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>736</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>737</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="33" name="AutoShape 32">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DDB522CE-F433-8115-FD22-185B763D7AF1}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4152900" y="128991360"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>737</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>738</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="34" name="AutoShape 33">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3847F70D-54D5-5D5D-808E-C1796C20EC6D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3025140" y="129166620"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>737</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>738</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="35" name="AutoShape 34">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F009AA84-6C21-5921-6FDB-701812CD9052}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4152900" y="129166620"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>738</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>739</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="36" name="AutoShape 35">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7B68944-0C92-0303-29AE-4F898F95D683}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3025140" y="129341880"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>738</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>739</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="37" name="AutoShape 36">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EEF88405-7911-5EBC-BD6F-3EA2F0FC7796}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4152900" y="129341880"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>739</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>740</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="38" name="AutoShape 37">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A50B6BA5-B328-3ABC-C828-BD7ADEDB65D4}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3025140" y="129517140"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>739</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>740</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="39" name="AutoShape 38">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5DFE352A-AB4F-51AF-325F-3356AFEAA589}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4152900" y="129517140"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>740</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>741</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="40" name="AutoShape 39">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7DEA54A7-9811-70FE-8FFA-39F619D68C7D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3025140" y="129692400"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>740</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>741</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="41" name="AutoShape 40">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F25A8546-3E62-6ADD-8907-48F80CD16E16}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4152900" y="129692400"/>
-          <a:ext cx="304800" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -12153,7 +4467,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{247AF3E6-8BD7-40DE-ACC7-21D4F916BD21}">
-  <dimension ref="A1:R741"/>
+  <dimension ref="A1:R761"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -31522,10 +23836,10 @@
       <c r="A722">
         <v>2025</v>
       </c>
-      <c r="B722" s="15">
+      <c r="B722">
         <v>16</v>
       </c>
-      <c r="C722" s="15" t="s">
+      <c r="C722" t="s">
         <v>11</v>
       </c>
       <c r="D722" s="3">
@@ -31549,10 +23863,10 @@
       <c r="A723">
         <v>2025</v>
       </c>
-      <c r="B723" s="15">
+      <c r="B723">
         <v>16</v>
       </c>
-      <c r="C723" s="15" t="s">
+      <c r="C723" t="s">
         <v>11</v>
       </c>
       <c r="D723" s="3">
@@ -31576,10 +23890,10 @@
       <c r="A724">
         <v>2025</v>
       </c>
-      <c r="B724" s="15">
+      <c r="B724">
         <v>16</v>
       </c>
-      <c r="C724" s="15" t="s">
+      <c r="C724" t="s">
         <v>11</v>
       </c>
       <c r="D724" s="3">
@@ -31603,10 +23917,10 @@
       <c r="A725">
         <v>2025</v>
       </c>
-      <c r="B725" s="15">
+      <c r="B725">
         <v>16</v>
       </c>
-      <c r="C725" s="15" t="s">
+      <c r="C725" t="s">
         <v>11</v>
       </c>
       <c r="D725" s="3">
@@ -31630,10 +23944,10 @@
       <c r="A726">
         <v>2025</v>
       </c>
-      <c r="B726" s="15">
+      <c r="B726">
         <v>16</v>
       </c>
-      <c r="C726" s="15" t="s">
+      <c r="C726" t="s">
         <v>11</v>
       </c>
       <c r="D726" s="3">
@@ -31657,10 +23971,10 @@
       <c r="A727">
         <v>2025</v>
       </c>
-      <c r="B727" s="15">
+      <c r="B727">
         <v>16</v>
       </c>
-      <c r="C727" s="15" t="s">
+      <c r="C727" t="s">
         <v>11</v>
       </c>
       <c r="D727" s="3">
@@ -31684,10 +23998,10 @@
       <c r="A728">
         <v>2025</v>
       </c>
-      <c r="B728" s="15">
+      <c r="B728">
         <v>16</v>
       </c>
-      <c r="C728" s="15" t="s">
+      <c r="C728" t="s">
         <v>11</v>
       </c>
       <c r="D728" s="3">
@@ -31711,10 +24025,10 @@
       <c r="A729">
         <v>2025</v>
       </c>
-      <c r="B729" s="15">
+      <c r="B729">
         <v>16</v>
       </c>
-      <c r="C729" s="15" t="s">
+      <c r="C729" t="s">
         <v>11</v>
       </c>
       <c r="D729" s="3">
@@ -31738,10 +24052,10 @@
       <c r="A730">
         <v>2025</v>
       </c>
-      <c r="B730" s="15">
+      <c r="B730">
         <v>16</v>
       </c>
-      <c r="C730" s="15" t="s">
+      <c r="C730" t="s">
         <v>11</v>
       </c>
       <c r="D730" s="3">
@@ -31765,10 +24079,10 @@
       <c r="A731">
         <v>2025</v>
       </c>
-      <c r="B731" s="15">
+      <c r="B731">
         <v>16</v>
       </c>
-      <c r="C731" s="15" t="s">
+      <c r="C731" t="s">
         <v>11</v>
       </c>
       <c r="D731" s="3">
@@ -31792,10 +24106,10 @@
       <c r="A732">
         <v>2025</v>
       </c>
-      <c r="B732" s="15">
+      <c r="B732">
         <v>16</v>
       </c>
-      <c r="C732" s="15" t="s">
+      <c r="C732" t="s">
         <v>11</v>
       </c>
       <c r="D732" s="3">
@@ -31819,10 +24133,10 @@
       <c r="A733">
         <v>2025</v>
       </c>
-      <c r="B733" s="15">
+      <c r="B733">
         <v>16</v>
       </c>
-      <c r="C733" s="15" t="s">
+      <c r="C733" t="s">
         <v>11</v>
       </c>
       <c r="D733" s="3">
@@ -31846,10 +24160,10 @@
       <c r="A734">
         <v>2025</v>
       </c>
-      <c r="B734" s="15">
+      <c r="B734">
         <v>16</v>
       </c>
-      <c r="C734" s="15" t="s">
+      <c r="C734" t="s">
         <v>11</v>
       </c>
       <c r="D734" s="3">
@@ -31873,10 +24187,10 @@
       <c r="A735">
         <v>2025</v>
       </c>
-      <c r="B735" s="15">
+      <c r="B735">
         <v>16</v>
       </c>
-      <c r="C735" s="15" t="s">
+      <c r="C735" t="s">
         <v>11</v>
       </c>
       <c r="D735" s="3">
@@ -31900,10 +24214,10 @@
       <c r="A736">
         <v>2025</v>
       </c>
-      <c r="B736" s="15">
+      <c r="B736">
         <v>16</v>
       </c>
-      <c r="C736" s="15" t="s">
+      <c r="C736" t="s">
         <v>11</v>
       </c>
       <c r="D736" s="3">
@@ -31927,10 +24241,10 @@
       <c r="A737">
         <v>2025</v>
       </c>
-      <c r="B737" s="15">
+      <c r="B737">
         <v>16</v>
       </c>
-      <c r="C737" s="15" t="s">
+      <c r="C737" t="s">
         <v>11</v>
       </c>
       <c r="D737" s="3">
@@ -31954,10 +24268,10 @@
       <c r="A738">
         <v>2025</v>
       </c>
-      <c r="B738" s="15">
+      <c r="B738">
         <v>16</v>
       </c>
-      <c r="C738" s="15" t="s">
+      <c r="C738" t="s">
         <v>11</v>
       </c>
       <c r="D738" s="3">
@@ -31981,10 +24295,10 @@
       <c r="A739">
         <v>2025</v>
       </c>
-      <c r="B739" s="15">
+      <c r="B739">
         <v>16</v>
       </c>
-      <c r="C739" s="15" t="s">
+      <c r="C739" t="s">
         <v>11</v>
       </c>
       <c r="D739" s="3">
@@ -32008,10 +24322,10 @@
       <c r="A740">
         <v>2025</v>
       </c>
-      <c r="B740" s="15">
+      <c r="B740">
         <v>16</v>
       </c>
-      <c r="C740" s="15" t="s">
+      <c r="C740" t="s">
         <v>11</v>
       </c>
       <c r="D740" s="3">
@@ -32035,10 +24349,10 @@
       <c r="A741">
         <v>2025</v>
       </c>
-      <c r="B741" s="15">
+      <c r="B741">
         <v>16</v>
       </c>
-      <c r="C741" s="15" t="s">
+      <c r="C741" t="s">
         <v>11</v>
       </c>
       <c r="D741" s="3">
@@ -32057,13 +24371,472 @@
       <c r="I741" s="3"/>
       <c r="J741" s="3"/>
       <c r="K741" s="3"/>
+    </row>
+    <row r="742" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A742" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B742" s="9">
+        <v>16</v>
+      </c>
+      <c r="C742" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D742" s="12">
+        <v>1</v>
+      </c>
+      <c r="E742" s="12">
+        <v>1</v>
+      </c>
+      <c r="F742" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G742" s="12" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="743" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A743" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B743" s="9">
+        <v>16</v>
+      </c>
+      <c r="C743" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D743" s="12">
+        <v>2</v>
+      </c>
+      <c r="E743" s="12">
+        <v>4</v>
+      </c>
+      <c r="F743" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="G743" s="12" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="744" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A744" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B744" s="9">
+        <v>16</v>
+      </c>
+      <c r="C744" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D744" s="12">
+        <v>3</v>
+      </c>
+      <c r="E744" s="12">
+        <v>81</v>
+      </c>
+      <c r="F744" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G744" s="12" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="745" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A745" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B745" s="9">
+        <v>16</v>
+      </c>
+      <c r="C745" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D745" s="12">
+        <v>4</v>
+      </c>
+      <c r="E745" s="12">
+        <v>16</v>
+      </c>
+      <c r="F745" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="G745" s="12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="746" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A746" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B746" s="9">
+        <v>16</v>
+      </c>
+      <c r="C746" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D746" s="12">
+        <v>5</v>
+      </c>
+      <c r="E746" s="12">
+        <v>63</v>
+      </c>
+      <c r="F746" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G746" s="12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="747" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A747" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B747" s="9">
+        <v>16</v>
+      </c>
+      <c r="C747" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D747" s="12">
+        <v>6</v>
+      </c>
+      <c r="E747" s="12">
+        <v>44</v>
+      </c>
+      <c r="F747" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="G747" s="12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="748" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A748" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B748" s="9">
+        <v>16</v>
+      </c>
+      <c r="C748" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D748" s="12">
+        <v>7</v>
+      </c>
+      <c r="E748" s="12">
+        <v>23</v>
+      </c>
+      <c r="F748" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="G748" s="12" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="749" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A749" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B749" s="9">
+        <v>16</v>
+      </c>
+      <c r="C749" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D749" s="12">
+        <v>8</v>
+      </c>
+      <c r="E749" s="12">
+        <v>5</v>
+      </c>
+      <c r="F749" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="G749" s="12" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="750" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A750" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B750" s="9">
+        <v>16</v>
+      </c>
+      <c r="C750" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D750" s="12">
+        <v>9</v>
+      </c>
+      <c r="E750" s="12">
+        <v>12</v>
+      </c>
+      <c r="F750" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="G750" s="12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="751" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A751" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B751" s="9">
+        <v>16</v>
+      </c>
+      <c r="C751" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D751" s="12">
+        <v>10</v>
+      </c>
+      <c r="E751" s="12">
+        <v>6</v>
+      </c>
+      <c r="F751" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="G751" s="12" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="752" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A752" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B752" s="9">
+        <v>16</v>
+      </c>
+      <c r="C752" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D752" s="12">
+        <v>11</v>
+      </c>
+      <c r="E752" s="12">
+        <v>55</v>
+      </c>
+      <c r="F752" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="G752" s="12" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="753" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A753" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B753" s="9">
+        <v>16</v>
+      </c>
+      <c r="C753" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D753" s="12">
+        <v>12</v>
+      </c>
+      <c r="E753" s="12">
+        <v>87</v>
+      </c>
+      <c r="F753" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="G753" s="12" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="754" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A754" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B754" s="9">
+        <v>16</v>
+      </c>
+      <c r="C754" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D754" s="12">
+        <v>13</v>
+      </c>
+      <c r="E754" s="12">
+        <v>22</v>
+      </c>
+      <c r="F754" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G754" s="12" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="755" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A755" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B755" s="9">
+        <v>16</v>
+      </c>
+      <c r="C755" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D755" s="12">
+        <v>14</v>
+      </c>
+      <c r="E755" s="12">
+        <v>30</v>
+      </c>
+      <c r="F755" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="G755" s="12" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="756" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A756" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B756" s="9">
+        <v>16</v>
+      </c>
+      <c r="C756" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D756" s="12">
+        <v>15</v>
+      </c>
+      <c r="E756" s="12">
+        <v>31</v>
+      </c>
+      <c r="F756" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="G756" s="12" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="757" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A757" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B757" s="9">
+        <v>16</v>
+      </c>
+      <c r="C757" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D757" s="12">
+        <v>16</v>
+      </c>
+      <c r="E757" s="12">
+        <v>10</v>
+      </c>
+      <c r="F757" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G757" s="12" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="758" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A758" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B758" s="9">
+        <v>16</v>
+      </c>
+      <c r="C758" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D758" s="12">
+        <v>17</v>
+      </c>
+      <c r="E758" s="12">
+        <v>43</v>
+      </c>
+      <c r="F758" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="G758" s="12" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="759" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A759" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B759" s="9">
+        <v>16</v>
+      </c>
+      <c r="C759" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D759" s="12">
+        <v>18</v>
+      </c>
+      <c r="E759" s="12">
+        <v>18</v>
+      </c>
+      <c r="F759" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="G759" s="12" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="760" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A760" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B760" s="9">
+        <v>16</v>
+      </c>
+      <c r="C760" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D760" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="E760" s="12">
+        <v>14</v>
+      </c>
+      <c r="F760" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="G760" s="12" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="761" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A761" s="9">
+        <v>2025</v>
+      </c>
+      <c r="B761" s="9">
+        <v>16</v>
+      </c>
+      <c r="C761" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D761" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="E761" s="12">
+        <v>27</v>
+      </c>
+      <c r="F761" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="G761" s="12" t="s">
+        <v>184</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H561" xr:uid="{247AF3E6-8BD7-40DE-ACC7-21D4F916BD21}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/public/docs/datas/f1.xlsx
+++ b/public/docs/datas/f1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\vue_platform\public\docs\datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF6C2E38-3AD0-4E6A-8F81-516FBFC1CBA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B17E1F57-1A34-4238-88C0-057E8ADE74F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11556" yWindow="3708" windowWidth="21216" windowHeight="15924" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24394,6 +24394,9 @@
       <c r="G742" s="12" t="s">
         <v>188</v>
       </c>
+      <c r="H742" s="12">
+        <v>25</v>
+      </c>
     </row>
     <row r="743" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A743" s="9">
@@ -24417,6 +24420,9 @@
       <c r="G743" s="12" t="s">
         <v>183</v>
       </c>
+      <c r="H743" s="12">
+        <v>18</v>
+      </c>
     </row>
     <row r="744" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A744" s="9">
@@ -24440,6 +24446,9 @@
       <c r="G744" s="12" t="s">
         <v>183</v>
       </c>
+      <c r="H744" s="12">
+        <v>15</v>
+      </c>
     </row>
     <row r="745" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A745" s="9">
@@ -24463,6 +24472,9 @@
       <c r="G745" s="12" t="s">
         <v>28</v>
       </c>
+      <c r="H745" s="12">
+        <v>12</v>
+      </c>
     </row>
     <row r="746" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A746" s="9">
@@ -24486,6 +24498,9 @@
       <c r="G746" s="12" t="s">
         <v>22</v>
       </c>
+      <c r="H746" s="12">
+        <v>10</v>
+      </c>
     </row>
     <row r="747" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A747" s="9">
@@ -24509,6 +24524,9 @@
       <c r="G747" s="12" t="s">
         <v>28</v>
       </c>
+      <c r="H747" s="12">
+        <v>8</v>
+      </c>
     </row>
     <row r="748" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A748" s="9">
@@ -24532,6 +24550,9 @@
       <c r="G748" s="12" t="s">
         <v>189</v>
       </c>
+      <c r="H748" s="12">
+        <v>6</v>
+      </c>
     </row>
     <row r="749" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A749" s="9">
@@ -24555,6 +24576,9 @@
       <c r="G749" s="12" t="s">
         <v>184</v>
       </c>
+      <c r="H749" s="12">
+        <v>4</v>
+      </c>
     </row>
     <row r="750" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A750" s="9">
@@ -24578,6 +24602,9 @@
       <c r="G750" s="12" t="s">
         <v>22</v>
       </c>
+      <c r="H750" s="12">
+        <v>2</v>
+      </c>
     </row>
     <row r="751" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A751" s="9">
@@ -24601,6 +24628,9 @@
       <c r="G751" s="12" t="s">
         <v>185</v>
       </c>
+      <c r="H751" s="12">
+        <v>1</v>
+      </c>
     </row>
     <row r="752" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A752" s="9">
@@ -24624,8 +24654,11 @@
       <c r="G752" s="12" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="753" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H752" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="753" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A753" s="9">
         <v>2025</v>
       </c>
@@ -24647,8 +24680,11 @@
       <c r="G753" s="12" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="754" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H753" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="754" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A754" s="9">
         <v>2025</v>
       </c>
@@ -24670,8 +24706,11 @@
       <c r="G754" s="12" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="755" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H754" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="755" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A755" s="9">
         <v>2025</v>
       </c>
@@ -24693,8 +24732,11 @@
       <c r="G755" s="12" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="756" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H755" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="756" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A756" s="9">
         <v>2025</v>
       </c>
@@ -24716,8 +24758,11 @@
       <c r="G756" s="12" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="757" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H756" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="757" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A757" s="9">
         <v>2025</v>
       </c>
@@ -24739,8 +24784,11 @@
       <c r="G757" s="12" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="758" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H757" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="758" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A758" s="9">
         <v>2025</v>
       </c>
@@ -24762,8 +24810,11 @@
       <c r="G758" s="12" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="759" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H758" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="759" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A759" s="9">
         <v>2025</v>
       </c>
@@ -24785,8 +24836,11 @@
       <c r="G759" s="12" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="760" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H759" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="760" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A760" s="9">
         <v>2025</v>
       </c>
@@ -24808,8 +24862,11 @@
       <c r="G760" s="12" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="761" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H760" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="761" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A761" s="9">
         <v>2025</v>
       </c>
@@ -24830,6 +24887,9 @@
       </c>
       <c r="G761" s="12" t="s">
         <v>184</v>
+      </c>
+      <c r="H761" s="12">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/public/docs/datas/f1.xlsx
+++ b/public/docs/datas/f1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\vue_platform\public\docs\datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B17E1F57-1A34-4238-88C0-057E8ADE74F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0006052F-D340-4F4F-9235-6569B2DC45CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11556" yWindow="3708" windowWidth="21216" windowHeight="15924" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15312" yWindow="2016" windowWidth="21600" windowHeight="15936" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="rounds" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2685" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2807" uniqueCount="222">
   <si>
     <t>year</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -849,6 +849,13 @@
   <si>
     <t>Australia</t>
   </si>
+  <si>
+    <t>DQ</t>
+  </si>
+  <si>
+    <t>DNS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -3792,6 +3799,12 @@
       <c r="D82" s="1">
         <v>45919</v>
       </c>
+      <c r="E82" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="F82" s="2">
+        <v>0.72916666666666663</v>
+      </c>
       <c r="G82">
         <v>0</v>
       </c>
@@ -3809,6 +3822,12 @@
       <c r="D83" s="1">
         <v>45919</v>
       </c>
+      <c r="E83" s="2">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="F83" s="2">
+        <v>0.875</v>
+      </c>
       <c r="G83">
         <v>0</v>
       </c>
@@ -3826,6 +3845,12 @@
       <c r="D84" s="1">
         <v>45920</v>
       </c>
+      <c r="E84" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="F84" s="2">
+        <v>0.72916666666666663</v>
+      </c>
       <c r="G84">
         <v>0</v>
       </c>
@@ -3843,6 +3868,12 @@
       <c r="D85" s="1">
         <v>45920</v>
       </c>
+      <c r="E85" s="2">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="F85" s="2">
+        <v>0.875</v>
+      </c>
       <c r="G85">
         <v>1</v>
       </c>
@@ -3859,6 +3890,9 @@
       </c>
       <c r="D86" s="1">
         <v>45921</v>
+      </c>
+      <c r="E86" s="2">
+        <v>0.79166666666666663</v>
       </c>
       <c r="G86">
         <v>1</v>
@@ -4467,7 +4501,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{247AF3E6-8BD7-40DE-ACC7-21D4F916BD21}">
-  <dimension ref="A1:R761"/>
+  <dimension ref="A1:R801"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -24658,7 +24692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="753" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A753" s="9">
         <v>2025</v>
       </c>
@@ -24684,7 +24718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="754" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A754" s="9">
         <v>2025</v>
       </c>
@@ -24710,7 +24744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="755" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A755" s="9">
         <v>2025</v>
       </c>
@@ -24736,7 +24770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="756" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A756" s="9">
         <v>2025</v>
       </c>
@@ -24762,7 +24796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="757" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A757" s="9">
         <v>2025</v>
       </c>
@@ -24788,7 +24822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="758" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A758" s="9">
         <v>2025</v>
       </c>
@@ -24814,7 +24848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="759" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A759" s="9">
         <v>2025</v>
       </c>
@@ -24840,7 +24874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="760" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A760" s="9">
         <v>2025</v>
       </c>
@@ -24866,7 +24900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="761" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A761" s="9">
         <v>2025</v>
       </c>
@@ -24889,6 +24923,1027 @@
         <v>184</v>
       </c>
       <c r="H761" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="762" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A762">
+        <v>2025</v>
+      </c>
+      <c r="B762">
+        <v>17</v>
+      </c>
+      <c r="C762" t="s">
+        <v>11</v>
+      </c>
+      <c r="D762">
+        <v>1</v>
+      </c>
+      <c r="E762">
+        <v>1</v>
+      </c>
+      <c r="F762" t="s">
+        <v>19</v>
+      </c>
+      <c r="G762" t="s">
+        <v>188</v>
+      </c>
+      <c r="N762" s="8"/>
+      <c r="O762" s="8"/>
+      <c r="P762" s="8"/>
+    </row>
+    <row r="763" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A763">
+        <v>2025</v>
+      </c>
+      <c r="B763">
+        <v>17</v>
+      </c>
+      <c r="C763" t="s">
+        <v>11</v>
+      </c>
+      <c r="D763">
+        <v>2</v>
+      </c>
+      <c r="E763">
+        <v>55</v>
+      </c>
+      <c r="F763" t="s">
+        <v>32</v>
+      </c>
+      <c r="G763" t="s">
+        <v>189</v>
+      </c>
+      <c r="N763" s="8"/>
+      <c r="O763" s="8"/>
+      <c r="P763" s="8"/>
+    </row>
+    <row r="764" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A764">
+        <v>2025</v>
+      </c>
+      <c r="B764">
+        <v>17</v>
+      </c>
+      <c r="C764" t="s">
+        <v>11</v>
+      </c>
+      <c r="D764">
+        <v>3</v>
+      </c>
+      <c r="E764">
+        <v>30</v>
+      </c>
+      <c r="F764" t="s">
+        <v>42</v>
+      </c>
+      <c r="G764" t="s">
+        <v>185</v>
+      </c>
+      <c r="N764" s="8"/>
+      <c r="O764" s="8"/>
+      <c r="P764" s="8"/>
+    </row>
+    <row r="765" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A765">
+        <v>2025</v>
+      </c>
+      <c r="B765">
+        <v>17</v>
+      </c>
+      <c r="C765" t="s">
+        <v>11</v>
+      </c>
+      <c r="D765">
+        <v>4</v>
+      </c>
+      <c r="E765">
+        <v>12</v>
+      </c>
+      <c r="F765" t="s">
+        <v>40</v>
+      </c>
+      <c r="G765" t="s">
+        <v>22</v>
+      </c>
+      <c r="N765" s="8"/>
+      <c r="O765" s="8"/>
+      <c r="P765" s="8"/>
+    </row>
+    <row r="766" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A766">
+        <v>2025</v>
+      </c>
+      <c r="B766">
+        <v>17</v>
+      </c>
+      <c r="C766" t="s">
+        <v>11</v>
+      </c>
+      <c r="D766">
+        <v>5</v>
+      </c>
+      <c r="E766">
+        <v>63</v>
+      </c>
+      <c r="F766" t="s">
+        <v>21</v>
+      </c>
+      <c r="G766" t="s">
+        <v>22</v>
+      </c>
+      <c r="N766" s="8"/>
+      <c r="O766" s="8"/>
+      <c r="P766" s="8"/>
+    </row>
+    <row r="767" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A767">
+        <v>2025</v>
+      </c>
+      <c r="B767">
+        <v>17</v>
+      </c>
+      <c r="C767" t="s">
+        <v>11</v>
+      </c>
+      <c r="D767">
+        <v>6</v>
+      </c>
+      <c r="E767">
+        <v>22</v>
+      </c>
+      <c r="F767" t="s">
+        <v>23</v>
+      </c>
+      <c r="G767" t="s">
+        <v>188</v>
+      </c>
+      <c r="N767" s="8"/>
+      <c r="O767" s="8"/>
+      <c r="P767" s="8"/>
+    </row>
+    <row r="768" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A768">
+        <v>2025</v>
+      </c>
+      <c r="B768">
+        <v>17</v>
+      </c>
+      <c r="C768" t="s">
+        <v>11</v>
+      </c>
+      <c r="D768">
+        <v>7</v>
+      </c>
+      <c r="E768">
+        <v>4</v>
+      </c>
+      <c r="F768" t="s">
+        <v>16</v>
+      </c>
+      <c r="G768" t="s">
+        <v>183</v>
+      </c>
+      <c r="N768" s="8"/>
+      <c r="O768" s="8"/>
+      <c r="P768" s="8"/>
+    </row>
+    <row r="769" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A769">
+        <v>2025</v>
+      </c>
+      <c r="B769">
+        <v>17</v>
+      </c>
+      <c r="C769" t="s">
+        <v>11</v>
+      </c>
+      <c r="D769">
+        <v>8</v>
+      </c>
+      <c r="E769">
+        <v>6</v>
+      </c>
+      <c r="F769" t="s">
+        <v>33</v>
+      </c>
+      <c r="G769" t="s">
+        <v>185</v>
+      </c>
+      <c r="N769" s="8"/>
+      <c r="O769" s="8"/>
+      <c r="P769" s="8"/>
+    </row>
+    <row r="770" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A770">
+        <v>2025</v>
+      </c>
+      <c r="B770">
+        <v>17</v>
+      </c>
+      <c r="C770" t="s">
+        <v>11</v>
+      </c>
+      <c r="D770">
+        <v>9</v>
+      </c>
+      <c r="E770">
+        <v>81</v>
+      </c>
+      <c r="F770" t="s">
+        <v>18</v>
+      </c>
+      <c r="G770" t="s">
+        <v>183</v>
+      </c>
+      <c r="N770" s="8"/>
+      <c r="O770" s="8"/>
+    </row>
+    <row r="771" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A771">
+        <v>2025</v>
+      </c>
+      <c r="B771">
+        <v>17</v>
+      </c>
+      <c r="C771" t="s">
+        <v>11</v>
+      </c>
+      <c r="D771">
+        <v>10</v>
+      </c>
+      <c r="E771">
+        <v>16</v>
+      </c>
+      <c r="F771" t="s">
+        <v>27</v>
+      </c>
+      <c r="G771" t="s">
+        <v>28</v>
+      </c>
+      <c r="N771" s="8"/>
+      <c r="O771" s="8"/>
+    </row>
+    <row r="772" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A772">
+        <v>2025</v>
+      </c>
+      <c r="B772">
+        <v>17</v>
+      </c>
+      <c r="C772" t="s">
+        <v>11</v>
+      </c>
+      <c r="D772">
+        <v>11</v>
+      </c>
+      <c r="E772">
+        <v>14</v>
+      </c>
+      <c r="F772" t="s">
+        <v>34</v>
+      </c>
+      <c r="G772" t="s">
+        <v>187</v>
+      </c>
+      <c r="N772" s="8"/>
+      <c r="O772" s="8"/>
+    </row>
+    <row r="773" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A773">
+        <v>2025</v>
+      </c>
+      <c r="B773">
+        <v>17</v>
+      </c>
+      <c r="C773" t="s">
+        <v>11</v>
+      </c>
+      <c r="D773">
+        <v>12</v>
+      </c>
+      <c r="E773">
+        <v>44</v>
+      </c>
+      <c r="F773" t="s">
+        <v>29</v>
+      </c>
+      <c r="G773" t="s">
+        <v>28</v>
+      </c>
+      <c r="N773" s="8"/>
+      <c r="O773" s="8"/>
+    </row>
+    <row r="774" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A774">
+        <v>2025</v>
+      </c>
+      <c r="B774">
+        <v>17</v>
+      </c>
+      <c r="C774" t="s">
+        <v>11</v>
+      </c>
+      <c r="D774">
+        <v>13</v>
+      </c>
+      <c r="E774">
+        <v>5</v>
+      </c>
+      <c r="F774" t="s">
+        <v>38</v>
+      </c>
+      <c r="G774" t="s">
+        <v>184</v>
+      </c>
+      <c r="N774" s="8"/>
+      <c r="O774" s="8"/>
+    </row>
+    <row r="775" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A775">
+        <v>2025</v>
+      </c>
+      <c r="B775">
+        <v>17</v>
+      </c>
+      <c r="C775" t="s">
+        <v>11</v>
+      </c>
+      <c r="D775">
+        <v>14</v>
+      </c>
+      <c r="E775">
+        <v>18</v>
+      </c>
+      <c r="F775" t="s">
+        <v>36</v>
+      </c>
+      <c r="G775" t="s">
+        <v>187</v>
+      </c>
+      <c r="N775" s="8"/>
+      <c r="O775" s="8"/>
+    </row>
+    <row r="776" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A776">
+        <v>2025</v>
+      </c>
+      <c r="B776">
+        <v>17</v>
+      </c>
+      <c r="C776" t="s">
+        <v>11</v>
+      </c>
+      <c r="D776">
+        <v>15</v>
+      </c>
+      <c r="E776">
+        <v>87</v>
+      </c>
+      <c r="F776" t="s">
+        <v>45</v>
+      </c>
+      <c r="G776" t="s">
+        <v>190</v>
+      </c>
+      <c r="N776" s="8"/>
+    </row>
+    <row r="777" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A777">
+        <v>2025</v>
+      </c>
+      <c r="B777">
+        <v>17</v>
+      </c>
+      <c r="C777" t="s">
+        <v>11</v>
+      </c>
+      <c r="D777">
+        <v>16</v>
+      </c>
+      <c r="E777">
+        <v>43</v>
+      </c>
+      <c r="F777" t="s">
+        <v>180</v>
+      </c>
+      <c r="G777" t="s">
+        <v>186</v>
+      </c>
+      <c r="N777" s="8"/>
+    </row>
+    <row r="778" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A778">
+        <v>2025</v>
+      </c>
+      <c r="B778">
+        <v>17</v>
+      </c>
+      <c r="C778" t="s">
+        <v>11</v>
+      </c>
+      <c r="D778">
+        <v>17</v>
+      </c>
+      <c r="E778">
+        <v>27</v>
+      </c>
+      <c r="F778" t="s">
+        <v>41</v>
+      </c>
+      <c r="G778" t="s">
+        <v>184</v>
+      </c>
+      <c r="N778" s="8"/>
+    </row>
+    <row r="779" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A779">
+        <v>2025</v>
+      </c>
+      <c r="B779">
+        <v>17</v>
+      </c>
+      <c r="C779" t="s">
+        <v>11</v>
+      </c>
+      <c r="D779">
+        <v>18</v>
+      </c>
+      <c r="E779">
+        <v>10</v>
+      </c>
+      <c r="F779" t="s">
+        <v>30</v>
+      </c>
+      <c r="G779" t="s">
+        <v>186</v>
+      </c>
+      <c r="N779" s="8"/>
+    </row>
+    <row r="780" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A780">
+        <v>2025</v>
+      </c>
+      <c r="B780">
+        <v>17</v>
+      </c>
+      <c r="C780" t="s">
+        <v>11</v>
+      </c>
+      <c r="D780">
+        <v>19</v>
+      </c>
+      <c r="E780">
+        <v>23</v>
+      </c>
+      <c r="F780" t="s">
+        <v>25</v>
+      </c>
+      <c r="G780" t="s">
+        <v>189</v>
+      </c>
+      <c r="N780" s="8"/>
+    </row>
+    <row r="781" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A781">
+        <v>2025</v>
+      </c>
+      <c r="B781">
+        <v>17</v>
+      </c>
+      <c r="C781" t="s">
+        <v>11</v>
+      </c>
+      <c r="D781" t="s">
+        <v>220</v>
+      </c>
+      <c r="E781">
+        <v>31</v>
+      </c>
+      <c r="F781" t="s">
+        <v>43</v>
+      </c>
+      <c r="G781" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="782" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A782">
+        <v>2025</v>
+      </c>
+      <c r="B782">
+        <v>17</v>
+      </c>
+      <c r="C782" t="s">
+        <v>14</v>
+      </c>
+      <c r="D782" s="12">
+        <v>1</v>
+      </c>
+      <c r="E782">
+        <v>1</v>
+      </c>
+      <c r="F782" t="s">
+        <v>19</v>
+      </c>
+      <c r="G782" t="s">
+        <v>188</v>
+      </c>
+      <c r="H782" s="12">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="783" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A783">
+        <v>2025</v>
+      </c>
+      <c r="B783">
+        <v>17</v>
+      </c>
+      <c r="C783" t="s">
+        <v>14</v>
+      </c>
+      <c r="D783" s="12">
+        <v>2</v>
+      </c>
+      <c r="E783">
+        <v>63</v>
+      </c>
+      <c r="F783" t="s">
+        <v>21</v>
+      </c>
+      <c r="G783" t="s">
+        <v>22</v>
+      </c>
+      <c r="H783" s="12">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="784" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A784">
+        <v>2025</v>
+      </c>
+      <c r="B784">
+        <v>17</v>
+      </c>
+      <c r="C784" t="s">
+        <v>14</v>
+      </c>
+      <c r="D784" s="12">
+        <v>3</v>
+      </c>
+      <c r="E784">
+        <v>55</v>
+      </c>
+      <c r="F784" t="s">
+        <v>32</v>
+      </c>
+      <c r="G784" t="s">
+        <v>189</v>
+      </c>
+      <c r="H784" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="785" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A785">
+        <v>2025</v>
+      </c>
+      <c r="B785">
+        <v>17</v>
+      </c>
+      <c r="C785" t="s">
+        <v>14</v>
+      </c>
+      <c r="D785" s="12">
+        <v>4</v>
+      </c>
+      <c r="E785">
+        <v>12</v>
+      </c>
+      <c r="F785" t="s">
+        <v>40</v>
+      </c>
+      <c r="G785" t="s">
+        <v>22</v>
+      </c>
+      <c r="H785" s="12">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="786" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A786">
+        <v>2025</v>
+      </c>
+      <c r="B786">
+        <v>17</v>
+      </c>
+      <c r="C786" t="s">
+        <v>14</v>
+      </c>
+      <c r="D786" s="12">
+        <v>5</v>
+      </c>
+      <c r="E786">
+        <v>30</v>
+      </c>
+      <c r="F786" t="s">
+        <v>42</v>
+      </c>
+      <c r="G786" t="s">
+        <v>185</v>
+      </c>
+      <c r="H786" s="12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="787" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A787">
+        <v>2025</v>
+      </c>
+      <c r="B787">
+        <v>17</v>
+      </c>
+      <c r="C787" t="s">
+        <v>14</v>
+      </c>
+      <c r="D787" s="12">
+        <v>6</v>
+      </c>
+      <c r="E787">
+        <v>22</v>
+      </c>
+      <c r="F787" t="s">
+        <v>23</v>
+      </c>
+      <c r="G787" t="s">
+        <v>188</v>
+      </c>
+      <c r="H787" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="788" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A788">
+        <v>2025</v>
+      </c>
+      <c r="B788">
+        <v>17</v>
+      </c>
+      <c r="C788" t="s">
+        <v>14</v>
+      </c>
+      <c r="D788" s="12">
+        <v>7</v>
+      </c>
+      <c r="E788">
+        <v>4</v>
+      </c>
+      <c r="F788" t="s">
+        <v>16</v>
+      </c>
+      <c r="G788" t="s">
+        <v>183</v>
+      </c>
+      <c r="H788" s="12">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="789" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A789">
+        <v>2025</v>
+      </c>
+      <c r="B789">
+        <v>17</v>
+      </c>
+      <c r="C789" t="s">
+        <v>14</v>
+      </c>
+      <c r="D789" s="12">
+        <v>8</v>
+      </c>
+      <c r="E789">
+        <v>44</v>
+      </c>
+      <c r="F789" t="s">
+        <v>29</v>
+      </c>
+      <c r="G789" t="s">
+        <v>28</v>
+      </c>
+      <c r="H789" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="790" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A790">
+        <v>2025</v>
+      </c>
+      <c r="B790">
+        <v>17</v>
+      </c>
+      <c r="C790" t="s">
+        <v>14</v>
+      </c>
+      <c r="D790" s="12">
+        <v>9</v>
+      </c>
+      <c r="E790">
+        <v>16</v>
+      </c>
+      <c r="F790" t="s">
+        <v>27</v>
+      </c>
+      <c r="G790" t="s">
+        <v>28</v>
+      </c>
+      <c r="H790" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="791" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A791">
+        <v>2025</v>
+      </c>
+      <c r="B791">
+        <v>17</v>
+      </c>
+      <c r="C791" t="s">
+        <v>14</v>
+      </c>
+      <c r="D791" s="12">
+        <v>10</v>
+      </c>
+      <c r="E791">
+        <v>6</v>
+      </c>
+      <c r="F791" t="s">
+        <v>33</v>
+      </c>
+      <c r="G791" t="s">
+        <v>185</v>
+      </c>
+      <c r="H791" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="792" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A792">
+        <v>2025</v>
+      </c>
+      <c r="B792">
+        <v>17</v>
+      </c>
+      <c r="C792" t="s">
+        <v>14</v>
+      </c>
+      <c r="D792" s="12">
+        <v>11</v>
+      </c>
+      <c r="E792">
+        <v>5</v>
+      </c>
+      <c r="F792" t="s">
+        <v>38</v>
+      </c>
+      <c r="G792" t="s">
+        <v>184</v>
+      </c>
+      <c r="H792" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="793" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A793">
+        <v>2025</v>
+      </c>
+      <c r="B793">
+        <v>17</v>
+      </c>
+      <c r="C793" t="s">
+        <v>14</v>
+      </c>
+      <c r="D793" s="12">
+        <v>12</v>
+      </c>
+      <c r="E793">
+        <v>87</v>
+      </c>
+      <c r="F793" t="s">
+        <v>45</v>
+      </c>
+      <c r="G793" t="s">
+        <v>190</v>
+      </c>
+      <c r="H793" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="794" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A794">
+        <v>2025</v>
+      </c>
+      <c r="B794">
+        <v>17</v>
+      </c>
+      <c r="C794" t="s">
+        <v>14</v>
+      </c>
+      <c r="D794" s="12">
+        <v>13</v>
+      </c>
+      <c r="E794">
+        <v>23</v>
+      </c>
+      <c r="F794" t="s">
+        <v>25</v>
+      </c>
+      <c r="G794" t="s">
+        <v>189</v>
+      </c>
+      <c r="H794" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="795" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A795">
+        <v>2025</v>
+      </c>
+      <c r="B795">
+        <v>17</v>
+      </c>
+      <c r="C795" t="s">
+        <v>14</v>
+      </c>
+      <c r="D795" s="12">
+        <v>14</v>
+      </c>
+      <c r="E795">
+        <v>31</v>
+      </c>
+      <c r="F795" t="s">
+        <v>43</v>
+      </c>
+      <c r="G795" t="s">
+        <v>190</v>
+      </c>
+      <c r="H795" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="796" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A796">
+        <v>2025</v>
+      </c>
+      <c r="B796">
+        <v>17</v>
+      </c>
+      <c r="C796" t="s">
+        <v>14</v>
+      </c>
+      <c r="D796" s="12">
+        <v>15</v>
+      </c>
+      <c r="E796">
+        <v>14</v>
+      </c>
+      <c r="F796" t="s">
+        <v>34</v>
+      </c>
+      <c r="G796" t="s">
+        <v>187</v>
+      </c>
+      <c r="H796" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="797" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A797">
+        <v>2025</v>
+      </c>
+      <c r="B797">
+        <v>17</v>
+      </c>
+      <c r="C797" t="s">
+        <v>14</v>
+      </c>
+      <c r="D797" s="12">
+        <v>16</v>
+      </c>
+      <c r="E797">
+        <v>27</v>
+      </c>
+      <c r="F797" t="s">
+        <v>41</v>
+      </c>
+      <c r="G797" t="s">
+        <v>184</v>
+      </c>
+      <c r="H797" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="798" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A798">
+        <v>2025</v>
+      </c>
+      <c r="B798">
+        <v>17</v>
+      </c>
+      <c r="C798" t="s">
+        <v>14</v>
+      </c>
+      <c r="D798" s="12">
+        <v>17</v>
+      </c>
+      <c r="E798">
+        <v>18</v>
+      </c>
+      <c r="F798" t="s">
+        <v>36</v>
+      </c>
+      <c r="G798" t="s">
+        <v>187</v>
+      </c>
+      <c r="H798" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="799" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A799">
+        <v>2025</v>
+      </c>
+      <c r="B799">
+        <v>17</v>
+      </c>
+      <c r="C799" t="s">
+        <v>14</v>
+      </c>
+      <c r="D799" s="12">
+        <v>18</v>
+      </c>
+      <c r="E799">
+        <v>10</v>
+      </c>
+      <c r="F799" t="s">
+        <v>30</v>
+      </c>
+      <c r="G799" t="s">
+        <v>186</v>
+      </c>
+      <c r="H799" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="800" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A800">
+        <v>2025</v>
+      </c>
+      <c r="B800">
+        <v>17</v>
+      </c>
+      <c r="C800" t="s">
+        <v>14</v>
+      </c>
+      <c r="D800" s="12">
+        <v>19</v>
+      </c>
+      <c r="E800">
+        <v>43</v>
+      </c>
+      <c r="F800" t="s">
+        <v>180</v>
+      </c>
+      <c r="G800" t="s">
+        <v>186</v>
+      </c>
+      <c r="H800" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="801" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A801">
+        <v>2025</v>
+      </c>
+      <c r="B801">
+        <v>17</v>
+      </c>
+      <c r="C801" t="s">
+        <v>14</v>
+      </c>
+      <c r="D801" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="E801">
+        <v>81</v>
+      </c>
+      <c r="F801" t="s">
+        <v>18</v>
+      </c>
+      <c r="G801" t="s">
+        <v>183</v>
+      </c>
+      <c r="H801" s="12">
         <v>0</v>
       </c>
     </row>

--- a/public/docs/datas/f1.xlsx
+++ b/public/docs/datas/f1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26800" windowHeight="18060" activeTab="2"/>
+    <workbookView windowHeight="15300" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="rounds" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
     <sheet name="teams" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">result!$A$1:$H$821</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">result!$A$1:$H$841</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -4447,6 +4447,12 @@
       <c r="D92" s="10">
         <v>45948</v>
       </c>
+      <c r="E92" s="12">
+        <v>0.0625</v>
+      </c>
+      <c r="F92" s="12">
+        <v>0.104166666666667</v>
+      </c>
       <c r="G92">
         <v>0</v>
       </c>
@@ -4464,6 +4470,12 @@
       <c r="D93" s="10">
         <v>45948</v>
       </c>
+      <c r="E93" s="12">
+        <v>0.229166666666667</v>
+      </c>
+      <c r="F93" s="12">
+        <v>0.259722222222222</v>
+      </c>
       <c r="G93">
         <v>1</v>
       </c>
@@ -4481,6 +4493,12 @@
       <c r="D94" s="10">
         <v>45949</v>
       </c>
+      <c r="E94" s="12">
+        <v>0.0416666666666667</v>
+      </c>
+      <c r="F94" s="12">
+        <v>0.0625</v>
+      </c>
       <c r="G94">
         <v>1</v>
       </c>
@@ -4498,6 +4516,12 @@
       <c r="D95" s="10">
         <v>45949</v>
       </c>
+      <c r="E95" s="12">
+        <v>0.208333333333333</v>
+      </c>
+      <c r="F95" s="12">
+        <v>0.25</v>
+      </c>
       <c r="G95">
         <v>1</v>
       </c>
@@ -4514,6 +4538,9 @@
       </c>
       <c r="D96" s="10">
         <v>45950</v>
+      </c>
+      <c r="E96" s="12">
+        <v>0.125</v>
       </c>
       <c r="G96">
         <v>1</v>
@@ -27380,7 +27407,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H821" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H841" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/docs/datas/f1.xlsx
+++ b/public/docs/datas/f1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Coding\vue_platform\public\docs\datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{400A348C-1C3C-47D6-8496-C921BBD5C5C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B8CF7B6-1838-43D5-B9AF-D0D850A549B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1776" yWindow="1620" windowWidth="27960" windowHeight="15936" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11556" yWindow="12372" windowWidth="22188" windowHeight="12648" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="rounds" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2990" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3116" uniqueCount="213">
   <si>
     <t>year</t>
   </si>
@@ -667,9 +667,6 @@
   <si>
     <t>Haas F1 Team</t>
   </si>
-  <si>
-    <t>NC</t>
-  </si>
 </sst>
 </file>
 
@@ -4507,7 +4504,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:R861"/>
+  <dimension ref="A1:R901"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -27424,7 +27421,7 @@
         <v>93</v>
       </c>
       <c r="D861" t="s">
-        <v>213</v>
+        <v>131</v>
       </c>
       <c r="E861">
         <v>5</v>
@@ -27434,6 +27431,1031 @@
       </c>
       <c r="G861" t="s">
         <v>136</v>
+      </c>
+    </row>
+    <row r="862" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A862">
+        <v>2025</v>
+      </c>
+      <c r="B862">
+        <v>19</v>
+      </c>
+      <c r="C862" t="s">
+        <v>94</v>
+      </c>
+      <c r="D862">
+        <v>1</v>
+      </c>
+      <c r="E862">
+        <v>1</v>
+      </c>
+      <c r="F862" t="s">
+        <v>103</v>
+      </c>
+      <c r="G862" t="s">
+        <v>140</v>
+      </c>
+      <c r="H862">
+        <v>8</v>
+      </c>
+      <c r="I862" s="8"/>
+    </row>
+    <row r="863" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A863">
+        <v>2025</v>
+      </c>
+      <c r="B863">
+        <v>19</v>
+      </c>
+      <c r="C863" t="s">
+        <v>94</v>
+      </c>
+      <c r="D863">
+        <v>2</v>
+      </c>
+      <c r="E863">
+        <v>63</v>
+      </c>
+      <c r="F863" t="s">
+        <v>105</v>
+      </c>
+      <c r="G863" t="s">
+        <v>106</v>
+      </c>
+      <c r="H863">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="864" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A864">
+        <v>2025</v>
+      </c>
+      <c r="B864">
+        <v>19</v>
+      </c>
+      <c r="C864" t="s">
+        <v>94</v>
+      </c>
+      <c r="D864">
+        <v>3</v>
+      </c>
+      <c r="E864">
+        <v>55</v>
+      </c>
+      <c r="F864" t="s">
+        <v>116</v>
+      </c>
+      <c r="G864" t="s">
+        <v>141</v>
+      </c>
+      <c r="H864">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="865" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A865">
+        <v>2025</v>
+      </c>
+      <c r="B865">
+        <v>19</v>
+      </c>
+      <c r="C865" t="s">
+        <v>94</v>
+      </c>
+      <c r="D865">
+        <v>4</v>
+      </c>
+      <c r="E865">
+        <v>44</v>
+      </c>
+      <c r="F865" t="s">
+        <v>113</v>
+      </c>
+      <c r="G865" t="s">
+        <v>112</v>
+      </c>
+      <c r="H865">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="866" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A866">
+        <v>2025</v>
+      </c>
+      <c r="B866">
+        <v>19</v>
+      </c>
+      <c r="C866" t="s">
+        <v>94</v>
+      </c>
+      <c r="D866">
+        <v>5</v>
+      </c>
+      <c r="E866">
+        <v>16</v>
+      </c>
+      <c r="F866" t="s">
+        <v>111</v>
+      </c>
+      <c r="G866" t="s">
+        <v>112</v>
+      </c>
+      <c r="H866">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="867" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A867">
+        <v>2025</v>
+      </c>
+      <c r="B867">
+        <v>19</v>
+      </c>
+      <c r="C867" t="s">
+        <v>94</v>
+      </c>
+      <c r="D867">
+        <v>6</v>
+      </c>
+      <c r="E867">
+        <v>23</v>
+      </c>
+      <c r="F867" t="s">
+        <v>109</v>
+      </c>
+      <c r="G867" t="s">
+        <v>141</v>
+      </c>
+      <c r="H867">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="868" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A868">
+        <v>2025</v>
+      </c>
+      <c r="B868">
+        <v>19</v>
+      </c>
+      <c r="C868" t="s">
+        <v>94</v>
+      </c>
+      <c r="D868">
+        <v>7</v>
+      </c>
+      <c r="E868">
+        <v>22</v>
+      </c>
+      <c r="F868" t="s">
+        <v>107</v>
+      </c>
+      <c r="G868" t="s">
+        <v>140</v>
+      </c>
+      <c r="H868">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="869" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A869">
+        <v>2025</v>
+      </c>
+      <c r="B869">
+        <v>19</v>
+      </c>
+      <c r="C869" t="s">
+        <v>94</v>
+      </c>
+      <c r="D869">
+        <v>8</v>
+      </c>
+      <c r="E869">
+        <v>12</v>
+      </c>
+      <c r="F869" t="s">
+        <v>124</v>
+      </c>
+      <c r="G869" t="s">
+        <v>106</v>
+      </c>
+      <c r="H869">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="870" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A870">
+        <v>2025</v>
+      </c>
+      <c r="B870">
+        <v>19</v>
+      </c>
+      <c r="C870" t="s">
+        <v>94</v>
+      </c>
+      <c r="D870">
+        <v>9</v>
+      </c>
+      <c r="E870">
+        <v>30</v>
+      </c>
+      <c r="F870" t="s">
+        <v>126</v>
+      </c>
+      <c r="G870" t="s">
+        <v>137</v>
+      </c>
+      <c r="H870">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="871" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A871">
+        <v>2025</v>
+      </c>
+      <c r="B871">
+        <v>19</v>
+      </c>
+      <c r="C871" t="s">
+        <v>94</v>
+      </c>
+      <c r="D871">
+        <v>10</v>
+      </c>
+      <c r="E871">
+        <v>10</v>
+      </c>
+      <c r="F871" t="s">
+        <v>114</v>
+      </c>
+      <c r="G871" t="s">
+        <v>138</v>
+      </c>
+      <c r="H871">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="872" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A872">
+        <v>2025</v>
+      </c>
+      <c r="B872">
+        <v>19</v>
+      </c>
+      <c r="C872" t="s">
+        <v>94</v>
+      </c>
+      <c r="D872">
+        <v>11</v>
+      </c>
+      <c r="E872">
+        <v>5</v>
+      </c>
+      <c r="F872" t="s">
+        <v>122</v>
+      </c>
+      <c r="G872" t="s">
+        <v>136</v>
+      </c>
+      <c r="H872">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="873" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A873">
+        <v>2025</v>
+      </c>
+      <c r="B873">
+        <v>19</v>
+      </c>
+      <c r="C873" t="s">
+        <v>94</v>
+      </c>
+      <c r="D873">
+        <v>12</v>
+      </c>
+      <c r="E873">
+        <v>6</v>
+      </c>
+      <c r="F873" t="s">
+        <v>117</v>
+      </c>
+      <c r="G873" t="s">
+        <v>137</v>
+      </c>
+      <c r="H873">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="874" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A874">
+        <v>2025</v>
+      </c>
+      <c r="B874">
+        <v>19</v>
+      </c>
+      <c r="C874" t="s">
+        <v>94</v>
+      </c>
+      <c r="D874">
+        <v>13</v>
+      </c>
+      <c r="E874">
+        <v>27</v>
+      </c>
+      <c r="F874" t="s">
+        <v>125</v>
+      </c>
+      <c r="G874" t="s">
+        <v>136</v>
+      </c>
+      <c r="H874">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="875" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A875">
+        <v>2025</v>
+      </c>
+      <c r="B875">
+        <v>19</v>
+      </c>
+      <c r="C875" t="s">
+        <v>94</v>
+      </c>
+      <c r="D875">
+        <v>14</v>
+      </c>
+      <c r="E875">
+        <v>43</v>
+      </c>
+      <c r="F875" t="s">
+        <v>133</v>
+      </c>
+      <c r="G875" t="s">
+        <v>138</v>
+      </c>
+      <c r="H875">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="876" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A876">
+        <v>2025</v>
+      </c>
+      <c r="B876">
+        <v>19</v>
+      </c>
+      <c r="C876" t="s">
+        <v>94</v>
+      </c>
+      <c r="D876">
+        <v>15</v>
+      </c>
+      <c r="E876">
+        <v>87</v>
+      </c>
+      <c r="F876" t="s">
+        <v>130</v>
+      </c>
+      <c r="G876" t="s">
+        <v>212</v>
+      </c>
+      <c r="H876">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="877" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A877">
+        <v>2025</v>
+      </c>
+      <c r="B877">
+        <v>19</v>
+      </c>
+      <c r="C877" t="s">
+        <v>94</v>
+      </c>
+      <c r="D877" t="s">
+        <v>131</v>
+      </c>
+      <c r="E877">
+        <v>31</v>
+      </c>
+      <c r="F877" t="s">
+        <v>127</v>
+      </c>
+      <c r="G877" t="s">
+        <v>212</v>
+      </c>
+      <c r="H877">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="878" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A878">
+        <v>2025</v>
+      </c>
+      <c r="B878">
+        <v>19</v>
+      </c>
+      <c r="C878" t="s">
+        <v>94</v>
+      </c>
+      <c r="D878" t="s">
+        <v>131</v>
+      </c>
+      <c r="E878">
+        <v>18</v>
+      </c>
+      <c r="F878" t="s">
+        <v>120</v>
+      </c>
+      <c r="G878" t="s">
+        <v>139</v>
+      </c>
+      <c r="H878">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="879" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A879">
+        <v>2025</v>
+      </c>
+      <c r="B879">
+        <v>19</v>
+      </c>
+      <c r="C879" t="s">
+        <v>94</v>
+      </c>
+      <c r="D879" t="s">
+        <v>131</v>
+      </c>
+      <c r="E879">
+        <v>4</v>
+      </c>
+      <c r="F879" t="s">
+        <v>100</v>
+      </c>
+      <c r="G879" t="s">
+        <v>135</v>
+      </c>
+      <c r="H879">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="880" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A880">
+        <v>2025</v>
+      </c>
+      <c r="B880">
+        <v>19</v>
+      </c>
+      <c r="C880" t="s">
+        <v>94</v>
+      </c>
+      <c r="D880" t="s">
+        <v>131</v>
+      </c>
+      <c r="E880">
+        <v>81</v>
+      </c>
+      <c r="F880" t="s">
+        <v>102</v>
+      </c>
+      <c r="G880" t="s">
+        <v>135</v>
+      </c>
+      <c r="H880">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="881" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A881">
+        <v>2025</v>
+      </c>
+      <c r="B881">
+        <v>19</v>
+      </c>
+      <c r="C881" t="s">
+        <v>94</v>
+      </c>
+      <c r="D881" t="s">
+        <v>131</v>
+      </c>
+      <c r="E881">
+        <v>14</v>
+      </c>
+      <c r="F881" t="s">
+        <v>118</v>
+      </c>
+      <c r="G881" t="s">
+        <v>139</v>
+      </c>
+      <c r="H881">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="882" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A882">
+        <v>2025</v>
+      </c>
+      <c r="B882">
+        <v>19</v>
+      </c>
+      <c r="C882" t="s">
+        <v>91</v>
+      </c>
+      <c r="D882">
+        <v>1</v>
+      </c>
+      <c r="E882">
+        <v>1</v>
+      </c>
+      <c r="F882" t="s">
+        <v>103</v>
+      </c>
+      <c r="G882" t="s">
+        <v>140</v>
+      </c>
+      <c r="H882" s="8"/>
+      <c r="I882" s="8"/>
+      <c r="J882" s="8"/>
+    </row>
+    <row r="883" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A883">
+        <v>2025</v>
+      </c>
+      <c r="B883">
+        <v>19</v>
+      </c>
+      <c r="C883" t="s">
+        <v>91</v>
+      </c>
+      <c r="D883">
+        <v>2</v>
+      </c>
+      <c r="E883">
+        <v>4</v>
+      </c>
+      <c r="F883" t="s">
+        <v>100</v>
+      </c>
+      <c r="G883" t="s">
+        <v>135</v>
+      </c>
+      <c r="H883" s="8"/>
+      <c r="I883" s="8"/>
+      <c r="J883" s="8"/>
+    </row>
+    <row r="884" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A884">
+        <v>2025</v>
+      </c>
+      <c r="B884">
+        <v>19</v>
+      </c>
+      <c r="C884" t="s">
+        <v>91</v>
+      </c>
+      <c r="D884">
+        <v>3</v>
+      </c>
+      <c r="E884">
+        <v>16</v>
+      </c>
+      <c r="F884" t="s">
+        <v>111</v>
+      </c>
+      <c r="G884" t="s">
+        <v>112</v>
+      </c>
+      <c r="H884" s="8"/>
+      <c r="I884" s="8"/>
+      <c r="J884" s="8"/>
+    </row>
+    <row r="885" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A885">
+        <v>2025</v>
+      </c>
+      <c r="B885">
+        <v>19</v>
+      </c>
+      <c r="C885" t="s">
+        <v>91</v>
+      </c>
+      <c r="D885">
+        <v>4</v>
+      </c>
+      <c r="E885">
+        <v>63</v>
+      </c>
+      <c r="F885" t="s">
+        <v>105</v>
+      </c>
+      <c r="G885" t="s">
+        <v>106</v>
+      </c>
+      <c r="H885" s="8"/>
+      <c r="I885" s="8"/>
+      <c r="J885" s="8"/>
+    </row>
+    <row r="886" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A886">
+        <v>2025</v>
+      </c>
+      <c r="B886">
+        <v>19</v>
+      </c>
+      <c r="C886" t="s">
+        <v>91</v>
+      </c>
+      <c r="D886">
+        <v>5</v>
+      </c>
+      <c r="E886">
+        <v>44</v>
+      </c>
+      <c r="F886" t="s">
+        <v>113</v>
+      </c>
+      <c r="G886" t="s">
+        <v>112</v>
+      </c>
+      <c r="H886" s="8"/>
+      <c r="I886" s="8"/>
+      <c r="J886" s="8"/>
+    </row>
+    <row r="887" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A887">
+        <v>2025</v>
+      </c>
+      <c r="B887">
+        <v>19</v>
+      </c>
+      <c r="C887" t="s">
+        <v>91</v>
+      </c>
+      <c r="D887">
+        <v>6</v>
+      </c>
+      <c r="E887">
+        <v>81</v>
+      </c>
+      <c r="F887" t="s">
+        <v>102</v>
+      </c>
+      <c r="G887" t="s">
+        <v>135</v>
+      </c>
+      <c r="H887" s="8"/>
+      <c r="I887" s="8"/>
+      <c r="J887" s="8"/>
+    </row>
+    <row r="888" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A888">
+        <v>2025</v>
+      </c>
+      <c r="B888">
+        <v>19</v>
+      </c>
+      <c r="C888" t="s">
+        <v>91</v>
+      </c>
+      <c r="D888">
+        <v>7</v>
+      </c>
+      <c r="E888">
+        <v>12</v>
+      </c>
+      <c r="F888" t="s">
+        <v>124</v>
+      </c>
+      <c r="G888" t="s">
+        <v>106</v>
+      </c>
+      <c r="H888" s="8"/>
+      <c r="I888" s="8"/>
+      <c r="J888" s="8"/>
+    </row>
+    <row r="889" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A889">
+        <v>2025</v>
+      </c>
+      <c r="B889">
+        <v>19</v>
+      </c>
+      <c r="C889" t="s">
+        <v>91</v>
+      </c>
+      <c r="D889">
+        <v>8</v>
+      </c>
+      <c r="E889">
+        <v>87</v>
+      </c>
+      <c r="F889" t="s">
+        <v>130</v>
+      </c>
+      <c r="G889" t="s">
+        <v>212</v>
+      </c>
+      <c r="H889" s="8"/>
+      <c r="I889" s="8"/>
+      <c r="J889" s="8"/>
+    </row>
+    <row r="890" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A890">
+        <v>2025</v>
+      </c>
+      <c r="B890">
+        <v>19</v>
+      </c>
+      <c r="C890" t="s">
+        <v>91</v>
+      </c>
+      <c r="D890">
+        <v>9</v>
+      </c>
+      <c r="E890">
+        <v>55</v>
+      </c>
+      <c r="F890" t="s">
+        <v>116</v>
+      </c>
+      <c r="G890" t="s">
+        <v>141</v>
+      </c>
+      <c r="H890" s="8"/>
+      <c r="I890" s="8"/>
+      <c r="J890" s="8"/>
+    </row>
+    <row r="891" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A891">
+        <v>2025</v>
+      </c>
+      <c r="B891">
+        <v>19</v>
+      </c>
+      <c r="C891" t="s">
+        <v>91</v>
+      </c>
+      <c r="D891">
+        <v>10</v>
+      </c>
+      <c r="E891">
+        <v>14</v>
+      </c>
+      <c r="F891" t="s">
+        <v>118</v>
+      </c>
+      <c r="G891" t="s">
+        <v>139</v>
+      </c>
+      <c r="H891" s="8"/>
+      <c r="I891" s="8"/>
+      <c r="J891" s="8"/>
+    </row>
+    <row r="892" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A892">
+        <v>2025</v>
+      </c>
+      <c r="B892">
+        <v>19</v>
+      </c>
+      <c r="C892" t="s">
+        <v>91</v>
+      </c>
+      <c r="D892">
+        <v>11</v>
+      </c>
+      <c r="E892">
+        <v>27</v>
+      </c>
+      <c r="F892" t="s">
+        <v>125</v>
+      </c>
+      <c r="G892" t="s">
+        <v>136</v>
+      </c>
+      <c r="H892" s="8"/>
+      <c r="I892" s="8"/>
+    </row>
+    <row r="893" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A893">
+        <v>2025</v>
+      </c>
+      <c r="B893">
+        <v>19</v>
+      </c>
+      <c r="C893" t="s">
+        <v>91</v>
+      </c>
+      <c r="D893">
+        <v>12</v>
+      </c>
+      <c r="E893">
+        <v>30</v>
+      </c>
+      <c r="F893" t="s">
+        <v>126</v>
+      </c>
+      <c r="G893" t="s">
+        <v>137</v>
+      </c>
+      <c r="H893" s="8"/>
+      <c r="I893" s="8"/>
+    </row>
+    <row r="894" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A894">
+        <v>2025</v>
+      </c>
+      <c r="B894">
+        <v>19</v>
+      </c>
+      <c r="C894" t="s">
+        <v>91</v>
+      </c>
+      <c r="D894">
+        <v>13</v>
+      </c>
+      <c r="E894">
+        <v>22</v>
+      </c>
+      <c r="F894" t="s">
+        <v>107</v>
+      </c>
+      <c r="G894" t="s">
+        <v>140</v>
+      </c>
+      <c r="H894" s="8"/>
+      <c r="I894" s="8"/>
+    </row>
+    <row r="895" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A895">
+        <v>2025</v>
+      </c>
+      <c r="B895">
+        <v>19</v>
+      </c>
+      <c r="C895" t="s">
+        <v>91</v>
+      </c>
+      <c r="D895">
+        <v>14</v>
+      </c>
+      <c r="E895">
+        <v>10</v>
+      </c>
+      <c r="F895" t="s">
+        <v>114</v>
+      </c>
+      <c r="G895" t="s">
+        <v>138</v>
+      </c>
+      <c r="H895" s="8"/>
+      <c r="I895" s="8"/>
+    </row>
+    <row r="896" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A896">
+        <v>2025</v>
+      </c>
+      <c r="B896">
+        <v>19</v>
+      </c>
+      <c r="C896" t="s">
+        <v>91</v>
+      </c>
+      <c r="D896">
+        <v>15</v>
+      </c>
+      <c r="E896">
+        <v>43</v>
+      </c>
+      <c r="F896" t="s">
+        <v>133</v>
+      </c>
+      <c r="G896" t="s">
+        <v>138</v>
+      </c>
+      <c r="H896" s="8"/>
+      <c r="I896" s="8"/>
+    </row>
+    <row r="897" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A897">
+        <v>2025</v>
+      </c>
+      <c r="B897">
+        <v>19</v>
+      </c>
+      <c r="C897" t="s">
+        <v>91</v>
+      </c>
+      <c r="D897">
+        <v>16</v>
+      </c>
+      <c r="E897">
+        <v>5</v>
+      </c>
+      <c r="F897" t="s">
+        <v>122</v>
+      </c>
+      <c r="G897" t="s">
+        <v>136</v>
+      </c>
+      <c r="H897" s="8"/>
+    </row>
+    <row r="898" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A898">
+        <v>2025</v>
+      </c>
+      <c r="B898">
+        <v>19</v>
+      </c>
+      <c r="C898" t="s">
+        <v>91</v>
+      </c>
+      <c r="D898">
+        <v>17</v>
+      </c>
+      <c r="E898">
+        <v>31</v>
+      </c>
+      <c r="F898" t="s">
+        <v>127</v>
+      </c>
+      <c r="G898" t="s">
+        <v>212</v>
+      </c>
+      <c r="H898" s="8"/>
+    </row>
+    <row r="899" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A899">
+        <v>2025</v>
+      </c>
+      <c r="B899">
+        <v>19</v>
+      </c>
+      <c r="C899" t="s">
+        <v>91</v>
+      </c>
+      <c r="D899">
+        <v>18</v>
+      </c>
+      <c r="E899">
+        <v>18</v>
+      </c>
+      <c r="F899" t="s">
+        <v>120</v>
+      </c>
+      <c r="G899" t="s">
+        <v>139</v>
+      </c>
+      <c r="H899" s="8"/>
+    </row>
+    <row r="900" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A900">
+        <v>2025</v>
+      </c>
+      <c r="B900">
+        <v>19</v>
+      </c>
+      <c r="C900" t="s">
+        <v>91</v>
+      </c>
+      <c r="D900">
+        <v>19</v>
+      </c>
+      <c r="E900">
+        <v>23</v>
+      </c>
+      <c r="F900" t="s">
+        <v>109</v>
+      </c>
+      <c r="G900" t="s">
+        <v>141</v>
+      </c>
+      <c r="H900" s="8"/>
+    </row>
+    <row r="901" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A901">
+        <v>2025</v>
+      </c>
+      <c r="B901">
+        <v>19</v>
+      </c>
+      <c r="C901" t="s">
+        <v>91</v>
+      </c>
+      <c r="D901" t="s">
+        <v>131</v>
+      </c>
+      <c r="E901">
+        <v>6</v>
+      </c>
+      <c r="F901" t="s">
+        <v>117</v>
+      </c>
+      <c r="G901" t="s">
+        <v>137</v>
       </c>
     </row>
   </sheetData>

--- a/public/docs/datas/f1.xlsx
+++ b/public/docs/datas/f1.xlsx
@@ -15,7 +15,7 @@
     <sheet name="teams" sheetId="5" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">result!$A$1:$H$921</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">result!$A$1:$H$961</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3386" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3567" uniqueCount="214">
   <si>
     <t>year</t>
   </si>
@@ -689,7 +689,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -700,13 +700,6 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1201,13 +1194,16 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1216,122 +1212,119 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1366,12 +1359,13 @@
     </xf>
     <xf numFmtId="47" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="20" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="20" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="20" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="20" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2473,13 +2467,13 @@
       <c r="C2" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D2" s="16">
+      <c r="D2" s="17">
         <v>45730</v>
       </c>
-      <c r="E2" s="18">
+      <c r="E2" s="19">
         <v>0.395833333333333</v>
       </c>
-      <c r="F2" s="18">
+      <c r="F2" s="19">
         <v>0.4375</v>
       </c>
       <c r="G2" s="2">
@@ -2496,13 +2490,13 @@
       <c r="C3" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D3" s="16">
+      <c r="D3" s="17">
         <v>45730</v>
       </c>
-      <c r="E3" s="18">
+      <c r="E3" s="19">
         <v>0.541666666666667</v>
       </c>
-      <c r="F3" s="18">
+      <c r="F3" s="19">
         <v>0.583333333333333</v>
       </c>
       <c r="G3" s="2">
@@ -2519,13 +2513,13 @@
       <c r="C4" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D4" s="16">
+      <c r="D4" s="17">
         <v>45731</v>
       </c>
-      <c r="E4" s="18">
+      <c r="E4" s="19">
         <v>0.395833333333333</v>
       </c>
-      <c r="F4" s="18">
+      <c r="F4" s="19">
         <v>0.4375</v>
       </c>
       <c r="G4" s="2">
@@ -2542,13 +2536,13 @@
       <c r="C5" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D5" s="16">
+      <c r="D5" s="17">
         <v>45731</v>
       </c>
-      <c r="E5" s="18">
+      <c r="E5" s="19">
         <v>0.541666666666667</v>
       </c>
-      <c r="F5" s="18">
+      <c r="F5" s="19">
         <v>0.583333333333333</v>
       </c>
       <c r="G5" s="2">
@@ -2565,13 +2559,13 @@
       <c r="C6" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D6" s="16">
+      <c r="D6" s="17">
         <v>45732</v>
       </c>
-      <c r="E6" s="18">
+      <c r="E6" s="19">
         <v>0.5</v>
       </c>
-      <c r="F6" s="18"/>
+      <c r="F6" s="19"/>
       <c r="G6" s="2">
         <v>1</v>
       </c>
@@ -2586,13 +2580,13 @@
       <c r="C7" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D7" s="17">
+      <c r="D7" s="18">
         <v>45737</v>
       </c>
-      <c r="E7" s="19">
+      <c r="E7" s="20">
         <v>0.479166666666667</v>
       </c>
-      <c r="F7" s="19">
+      <c r="F7" s="20">
         <v>0.520833333333333</v>
       </c>
       <c r="G7" s="6">
@@ -2609,13 +2603,13 @@
       <c r="C8" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="D8" s="17">
+      <c r="D8" s="18">
         <v>45737</v>
       </c>
-      <c r="E8" s="19">
+      <c r="E8" s="20">
         <v>0.645833333333333</v>
       </c>
-      <c r="F8" s="19">
+      <c r="F8" s="20">
         <v>0.676388888888889</v>
       </c>
       <c r="G8" s="6">
@@ -2632,13 +2626,13 @@
       <c r="C9" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="D9" s="17">
+      <c r="D9" s="18">
         <v>45738</v>
       </c>
-      <c r="E9" s="19">
+      <c r="E9" s="20">
         <v>0.458333333333333</v>
       </c>
-      <c r="F9" s="19">
+      <c r="F9" s="20">
         <v>0.5</v>
       </c>
       <c r="G9" s="6">
@@ -2655,13 +2649,13 @@
       <c r="C10" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D10" s="17">
+      <c r="D10" s="18">
         <v>45738</v>
       </c>
-      <c r="E10" s="19">
+      <c r="E10" s="20">
         <v>0.625</v>
       </c>
-      <c r="F10" s="19">
+      <c r="F10" s="20">
         <v>0.666666666666667</v>
       </c>
       <c r="G10" s="6">
@@ -2678,10 +2672,10 @@
       <c r="C11" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D11" s="17">
+      <c r="D11" s="18">
         <v>45739</v>
       </c>
-      <c r="E11" s="19">
+      <c r="E11" s="20">
         <v>0.625</v>
       </c>
       <c r="F11" s="6"/>
@@ -2699,13 +2693,13 @@
       <c r="C12" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D12" s="16">
+      <c r="D12" s="17">
         <v>45751</v>
       </c>
-      <c r="E12" s="18">
+      <c r="E12" s="19">
         <v>0.4375</v>
       </c>
-      <c r="F12" s="18">
+      <c r="F12" s="19">
         <v>0.479166666666667</v>
       </c>
       <c r="G12" s="2">
@@ -2722,13 +2716,13 @@
       <c r="C13" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D13" s="16">
+      <c r="D13" s="17">
         <v>45751</v>
       </c>
-      <c r="E13" s="18">
+      <c r="E13" s="19">
         <v>0.583333333333333</v>
       </c>
-      <c r="F13" s="18">
+      <c r="F13" s="19">
         <v>0.625</v>
       </c>
       <c r="G13" s="2">
@@ -2745,13 +2739,13 @@
       <c r="C14" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D14" s="16">
+      <c r="D14" s="17">
         <v>45752</v>
       </c>
-      <c r="E14" s="18">
+      <c r="E14" s="19">
         <v>0.4375</v>
       </c>
-      <c r="F14" s="18">
+      <c r="F14" s="19">
         <v>0.479166666666667</v>
       </c>
       <c r="G14" s="2">
@@ -2768,13 +2762,13 @@
       <c r="C15" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D15" s="16">
+      <c r="D15" s="17">
         <v>45752</v>
       </c>
-      <c r="E15" s="18">
+      <c r="E15" s="19">
         <v>0.583333333333333</v>
       </c>
-      <c r="F15" s="18">
+      <c r="F15" s="19">
         <v>0.625</v>
       </c>
       <c r="G15" s="2">
@@ -2791,10 +2785,10 @@
       <c r="C16" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D16" s="16">
+      <c r="D16" s="17">
         <v>45753</v>
       </c>
-      <c r="E16" s="18">
+      <c r="E16" s="19">
         <v>0.541666666666667</v>
       </c>
       <c r="F16" s="2"/>
@@ -2812,13 +2806,13 @@
       <c r="C17" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D17" s="17">
+      <c r="D17" s="18">
         <v>45758</v>
       </c>
-      <c r="E17" s="19">
+      <c r="E17" s="20">
         <v>0.8125</v>
       </c>
-      <c r="F17" s="19">
+      <c r="F17" s="20">
         <v>0.854166666666667</v>
       </c>
       <c r="G17" s="6">
@@ -2835,13 +2829,13 @@
       <c r="C18" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="D18" s="17">
+      <c r="D18" s="18">
         <v>45758</v>
       </c>
-      <c r="E18" s="19">
+      <c r="E18" s="20">
         <v>0.958333333333333</v>
       </c>
-      <c r="F18" s="19">
+      <c r="F18" s="20">
         <v>0</v>
       </c>
       <c r="G18" s="6">
@@ -2858,13 +2852,13 @@
       <c r="C19" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D19" s="17">
+      <c r="D19" s="18">
         <v>45759</v>
       </c>
-      <c r="E19" s="19">
+      <c r="E19" s="20">
         <v>0.854166666666667</v>
       </c>
-      <c r="F19" s="19">
+      <c r="F19" s="20">
         <v>0.895833333333333</v>
       </c>
       <c r="G19" s="6">
@@ -2881,13 +2875,13 @@
       <c r="C20" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D20" s="17">
+      <c r="D20" s="18">
         <v>45760</v>
       </c>
-      <c r="E20" s="19">
-        <v>0</v>
-      </c>
-      <c r="F20" s="19">
+      <c r="E20" s="20">
+        <v>0</v>
+      </c>
+      <c r="F20" s="20">
         <v>0.0416666666666667</v>
       </c>
       <c r="G20" s="6">
@@ -2904,10 +2898,10 @@
       <c r="C21" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D21" s="17">
+      <c r="D21" s="18">
         <v>45760</v>
       </c>
-      <c r="E21" s="19">
+      <c r="E21" s="20">
         <v>0.958333333333333</v>
       </c>
       <c r="F21" s="6"/>
@@ -2925,13 +2919,13 @@
       <c r="C22" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D22" s="16">
+      <c r="D22" s="17">
         <v>45765</v>
       </c>
-      <c r="E22" s="18">
+      <c r="E22" s="19">
         <v>0.895833333333333</v>
       </c>
-      <c r="F22" s="18">
+      <c r="F22" s="19">
         <v>0.9375</v>
       </c>
       <c r="G22" s="2">
@@ -2948,13 +2942,13 @@
       <c r="C23" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D23" s="16">
+      <c r="D23" s="17">
         <v>45766</v>
       </c>
-      <c r="E23" s="18">
+      <c r="E23" s="19">
         <v>0.0416666666666667</v>
       </c>
-      <c r="F23" s="18">
+      <c r="F23" s="19">
         <v>0.0833333333333333</v>
       </c>
       <c r="G23" s="2">
@@ -2971,13 +2965,13 @@
       <c r="C24" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D24" s="16">
+      <c r="D24" s="17">
         <v>45766</v>
       </c>
-      <c r="E24" s="18">
+      <c r="E24" s="19">
         <v>0.895833333333333</v>
       </c>
-      <c r="F24" s="18">
+      <c r="F24" s="19">
         <v>0.9375</v>
       </c>
       <c r="G24" s="2">
@@ -2994,13 +2988,13 @@
       <c r="C25" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D25" s="16">
+      <c r="D25" s="17">
         <v>45767</v>
       </c>
-      <c r="E25" s="18">
+      <c r="E25" s="19">
         <v>0.0416666666666667</v>
       </c>
-      <c r="F25" s="18">
+      <c r="F25" s="19">
         <v>0.0833333333333333</v>
       </c>
       <c r="G25" s="2">
@@ -3017,10 +3011,10 @@
       <c r="C26" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D26" s="16">
+      <c r="D26" s="17">
         <v>45767</v>
       </c>
-      <c r="E26" s="18">
+      <c r="E26" s="19">
         <v>0.0416666666666667</v>
       </c>
       <c r="F26" s="2"/>
@@ -3038,13 +3032,13 @@
       <c r="C27" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D27" s="17">
+      <c r="D27" s="18">
         <v>45780</v>
       </c>
-      <c r="E27" s="19">
+      <c r="E27" s="20">
         <v>0.0208333333333333</v>
       </c>
-      <c r="F27" s="19">
+      <c r="F27" s="20">
         <v>0.0625</v>
       </c>
       <c r="G27" s="6">
@@ -3061,13 +3055,13 @@
       <c r="C28" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="D28" s="17">
+      <c r="D28" s="18">
         <v>45780</v>
       </c>
-      <c r="E28" s="19">
+      <c r="E28" s="20">
         <v>0.1875</v>
       </c>
-      <c r="F28" s="19">
+      <c r="F28" s="20">
         <v>0.218055555555556</v>
       </c>
       <c r="G28" s="6">
@@ -3084,13 +3078,13 @@
       <c r="C29" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="D29" s="17">
+      <c r="D29" s="18">
         <v>45781</v>
       </c>
-      <c r="E29" s="19">
-        <v>0</v>
-      </c>
-      <c r="F29" s="19">
+      <c r="E29" s="20">
+        <v>0</v>
+      </c>
+      <c r="F29" s="20">
         <v>0.0416666666666667</v>
       </c>
       <c r="G29" s="6">
@@ -3107,13 +3101,13 @@
       <c r="C30" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D30" s="17">
+      <c r="D30" s="18">
         <v>45781</v>
       </c>
-      <c r="E30" s="19">
+      <c r="E30" s="20">
         <v>0.166666666666667</v>
       </c>
-      <c r="F30" s="19">
+      <c r="F30" s="20">
         <v>0.208333333333333</v>
       </c>
       <c r="G30" s="6">
@@ -3130,13 +3124,13 @@
       <c r="C31" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D31" s="17">
+      <c r="D31" s="18">
         <v>45782</v>
       </c>
-      <c r="E31" s="19">
+      <c r="E31" s="20">
         <v>0.166666666666667</v>
       </c>
-      <c r="F31" s="19"/>
+      <c r="F31" s="20"/>
       <c r="G31" s="6">
         <v>1</v>
       </c>
@@ -3151,13 +3145,13 @@
       <c r="C32" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D32" s="16">
+      <c r="D32" s="17">
         <v>45793</v>
       </c>
-      <c r="E32" s="18">
+      <c r="E32" s="19">
         <v>0.8125</v>
       </c>
-      <c r="F32" s="18">
+      <c r="F32" s="19">
         <v>0.854166666666667</v>
       </c>
       <c r="G32" s="2">
@@ -3174,13 +3168,13 @@
       <c r="C33" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D33" s="16">
+      <c r="D33" s="17">
         <v>45793</v>
       </c>
-      <c r="E33" s="18">
+      <c r="E33" s="19">
         <v>0.958333333333333</v>
       </c>
-      <c r="F33" s="18">
+      <c r="F33" s="19">
         <v>0</v>
       </c>
       <c r="G33" s="2">
@@ -3197,13 +3191,13 @@
       <c r="C34" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D34" s="16">
+      <c r="D34" s="17">
         <v>45794</v>
       </c>
-      <c r="E34" s="18">
+      <c r="E34" s="19">
         <v>0.770833333333333</v>
       </c>
-      <c r="F34" s="18">
+      <c r="F34" s="19">
         <v>0.8125</v>
       </c>
       <c r="G34" s="2">
@@ -3220,13 +3214,13 @@
       <c r="C35" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D35" s="16">
+      <c r="D35" s="17">
         <v>45794</v>
       </c>
-      <c r="E35" s="18">
+      <c r="E35" s="19">
         <v>0.916666666666667</v>
       </c>
-      <c r="F35" s="18">
+      <c r="F35" s="19">
         <v>0.958333333333333</v>
       </c>
       <c r="G35" s="2">
@@ -3243,10 +3237,10 @@
       <c r="C36" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D36" s="16">
+      <c r="D36" s="17">
         <v>45795</v>
       </c>
-      <c r="E36" s="18">
+      <c r="E36" s="19">
         <v>0.875</v>
       </c>
       <c r="F36" s="2"/>
@@ -3264,13 +3258,13 @@
       <c r="C37" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D37" s="17">
+      <c r="D37" s="18">
         <v>45800</v>
       </c>
-      <c r="E37" s="19">
+      <c r="E37" s="20">
         <v>0.8125</v>
       </c>
-      <c r="F37" s="19">
+      <c r="F37" s="20">
         <v>0.854166666666667</v>
       </c>
       <c r="G37" s="6">
@@ -3287,13 +3281,13 @@
       <c r="C38" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="D38" s="17">
+      <c r="D38" s="18">
         <v>45800</v>
       </c>
-      <c r="E38" s="19">
+      <c r="E38" s="20">
         <v>0.958333333333333</v>
       </c>
-      <c r="F38" s="19">
+      <c r="F38" s="20">
         <v>0</v>
       </c>
       <c r="G38" s="6">
@@ -3310,13 +3304,13 @@
       <c r="C39" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D39" s="17">
+      <c r="D39" s="18">
         <v>45801</v>
       </c>
-      <c r="E39" s="19">
+      <c r="E39" s="20">
         <v>0.770833333333333</v>
       </c>
-      <c r="F39" s="19">
+      <c r="F39" s="20">
         <v>0.8125</v>
       </c>
       <c r="G39" s="6">
@@ -3333,13 +3327,13 @@
       <c r="C40" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D40" s="17">
+      <c r="D40" s="18">
         <v>45801</v>
       </c>
-      <c r="E40" s="19">
+      <c r="E40" s="20">
         <v>0.916666666666667</v>
       </c>
-      <c r="F40" s="19">
+      <c r="F40" s="20">
         <v>0.958333333333333</v>
       </c>
       <c r="G40" s="6">
@@ -3356,10 +3350,10 @@
       <c r="C41" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D41" s="17">
+      <c r="D41" s="18">
         <v>45802</v>
       </c>
-      <c r="E41" s="19">
+      <c r="E41" s="20">
         <v>0.875</v>
       </c>
       <c r="F41" s="6"/>
@@ -3377,13 +3371,13 @@
       <c r="C42" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D42" s="16">
+      <c r="D42" s="17">
         <v>45807</v>
       </c>
-      <c r="E42" s="18">
+      <c r="E42" s="19">
         <v>0.8125</v>
       </c>
-      <c r="F42" s="18">
+      <c r="F42" s="19">
         <v>0.854166666666667</v>
       </c>
       <c r="G42" s="2">
@@ -3400,13 +3394,13 @@
       <c r="C43" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D43" s="16">
+      <c r="D43" s="17">
         <v>45807</v>
       </c>
-      <c r="E43" s="18">
+      <c r="E43" s="19">
         <v>0.958333333333333</v>
       </c>
-      <c r="F43" s="18">
+      <c r="F43" s="19">
         <v>0</v>
       </c>
       <c r="G43" s="2">
@@ -3423,13 +3417,13 @@
       <c r="C44" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D44" s="16">
+      <c r="D44" s="17">
         <v>45808</v>
       </c>
-      <c r="E44" s="18">
+      <c r="E44" s="19">
         <v>0.770833333333333</v>
       </c>
-      <c r="F44" s="18">
+      <c r="F44" s="19">
         <v>0.8125</v>
       </c>
       <c r="G44" s="2">
@@ -3446,13 +3440,13 @@
       <c r="C45" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D45" s="16">
+      <c r="D45" s="17">
         <v>45808</v>
       </c>
-      <c r="E45" s="18">
+      <c r="E45" s="19">
         <v>0.916666666666667</v>
       </c>
-      <c r="F45" s="18">
+      <c r="F45" s="19">
         <v>0.958333333333333</v>
       </c>
       <c r="G45" s="2">
@@ -3469,10 +3463,10 @@
       <c r="C46" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D46" s="16">
+      <c r="D46" s="17">
         <v>45809</v>
       </c>
-      <c r="E46" s="18">
+      <c r="E46" s="19">
         <v>0.875</v>
       </c>
       <c r="F46" s="2"/>
@@ -3490,13 +3484,13 @@
       <c r="C47" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D47" s="17">
+      <c r="D47" s="18">
         <v>45822</v>
       </c>
-      <c r="E47" s="19">
+      <c r="E47" s="20">
         <v>0.0625</v>
       </c>
-      <c r="F47" s="19">
+      <c r="F47" s="20">
         <v>0.104166666666667</v>
       </c>
       <c r="G47" s="6">
@@ -3513,13 +3507,13 @@
       <c r="C48" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="D48" s="17">
+      <c r="D48" s="18">
         <v>45822</v>
       </c>
-      <c r="E48" s="19">
+      <c r="E48" s="20">
         <v>0.208333333333333</v>
       </c>
-      <c r="F48" s="19">
+      <c r="F48" s="20">
         <v>0.25</v>
       </c>
       <c r="G48" s="6">
@@ -3536,13 +3530,13 @@
       <c r="C49" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D49" s="17">
+      <c r="D49" s="18">
         <v>45823</v>
       </c>
-      <c r="E49" s="19">
+      <c r="E49" s="20">
         <v>0.0208333333333333</v>
       </c>
-      <c r="F49" s="19">
+      <c r="F49" s="20">
         <v>0.0625</v>
       </c>
       <c r="G49" s="6">
@@ -3559,13 +3553,13 @@
       <c r="C50" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D50" s="17">
+      <c r="D50" s="18">
         <v>45823</v>
       </c>
-      <c r="E50" s="19">
+      <c r="E50" s="20">
         <v>0.166666666666667</v>
       </c>
-      <c r="F50" s="19">
+      <c r="F50" s="20">
         <v>0.208333333333333</v>
       </c>
       <c r="G50" s="6">
@@ -3582,10 +3576,10 @@
       <c r="C51" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D51" s="17">
+      <c r="D51" s="18">
         <v>45824</v>
       </c>
-      <c r="E51" s="19">
+      <c r="E51" s="20">
         <v>0.0833333333333333</v>
       </c>
       <c r="F51" s="6"/>
@@ -3603,13 +3597,13 @@
       <c r="C52" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D52" s="16">
+      <c r="D52" s="17">
         <v>45835</v>
       </c>
-      <c r="E52" s="18">
+      <c r="E52" s="19">
         <v>0.8125</v>
       </c>
-      <c r="F52" s="18">
+      <c r="F52" s="19">
         <v>0.854166666666667</v>
       </c>
       <c r="G52" s="2">
@@ -3626,13 +3620,13 @@
       <c r="C53" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D53" s="16">
+      <c r="D53" s="17">
         <v>45835</v>
       </c>
-      <c r="E53" s="18">
+      <c r="E53" s="19">
         <v>0.958333333333333</v>
       </c>
-      <c r="F53" s="18">
+      <c r="F53" s="19">
         <v>0</v>
       </c>
       <c r="G53" s="2">
@@ -3649,13 +3643,13 @@
       <c r="C54" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D54" s="16">
+      <c r="D54" s="17">
         <v>45836</v>
       </c>
-      <c r="E54" s="18">
+      <c r="E54" s="19">
         <v>0.770833333333333</v>
       </c>
-      <c r="F54" s="18">
+      <c r="F54" s="19">
         <v>0.8125</v>
       </c>
       <c r="G54" s="2">
@@ -3672,13 +3666,13 @@
       <c r="C55" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D55" s="16">
+      <c r="D55" s="17">
         <v>45836</v>
       </c>
-      <c r="E55" s="18">
+      <c r="E55" s="19">
         <v>0.916666666666667</v>
       </c>
-      <c r="F55" s="18">
+      <c r="F55" s="19">
         <v>0.958333333333333</v>
       </c>
       <c r="G55" s="2">
@@ -3695,10 +3689,10 @@
       <c r="C56" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D56" s="16">
+      <c r="D56" s="17">
         <v>45837</v>
       </c>
-      <c r="E56" s="18">
+      <c r="E56" s="19">
         <v>0.875</v>
       </c>
       <c r="F56" s="2"/>
@@ -3716,13 +3710,13 @@
       <c r="C57" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D57" s="17">
+      <c r="D57" s="18">
         <v>45842</v>
       </c>
-      <c r="E57" s="19">
+      <c r="E57" s="20">
         <v>0.8125</v>
       </c>
-      <c r="F57" s="19">
+      <c r="F57" s="20">
         <v>0.854166666666667</v>
       </c>
       <c r="G57" s="6">
@@ -3739,13 +3733,13 @@
       <c r="C58" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="D58" s="17">
+      <c r="D58" s="18">
         <v>45842</v>
       </c>
-      <c r="E58" s="19">
+      <c r="E58" s="20">
         <v>0.958333333333333</v>
       </c>
-      <c r="F58" s="19">
+      <c r="F58" s="20">
         <v>0</v>
       </c>
       <c r="G58" s="6">
@@ -3762,13 +3756,13 @@
       <c r="C59" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D59" s="17">
+      <c r="D59" s="18">
         <v>45843</v>
       </c>
-      <c r="E59" s="19">
+      <c r="E59" s="20">
         <v>0.770833333333333</v>
       </c>
-      <c r="F59" s="19">
+      <c r="F59" s="20">
         <v>0.8125</v>
       </c>
       <c r="G59" s="6">
@@ -3785,13 +3779,13 @@
       <c r="C60" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D60" s="17">
+      <c r="D60" s="18">
         <v>45843</v>
       </c>
-      <c r="E60" s="19">
+      <c r="E60" s="20">
         <v>0.916666666666667</v>
       </c>
-      <c r="F60" s="19">
+      <c r="F60" s="20">
         <v>0.958333333333333</v>
       </c>
       <c r="G60" s="6">
@@ -3808,10 +3802,10 @@
       <c r="C61" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D61" s="17">
+      <c r="D61" s="18">
         <v>45844</v>
       </c>
-      <c r="E61" s="19">
+      <c r="E61" s="20">
         <v>0.916666666666667</v>
       </c>
       <c r="F61" s="6"/>
@@ -3829,13 +3823,13 @@
       <c r="C62" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D62" s="16">
+      <c r="D62" s="17">
         <v>45863</v>
       </c>
-      <c r="E62" s="18">
+      <c r="E62" s="19">
         <v>0.8125</v>
       </c>
-      <c r="F62" s="18">
+      <c r="F62" s="19">
         <v>0.854166666666667</v>
       </c>
       <c r="G62" s="2">
@@ -3852,13 +3846,13 @@
       <c r="C63" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D63" s="16">
+      <c r="D63" s="17">
         <v>45863</v>
       </c>
-      <c r="E63" s="18">
+      <c r="E63" s="19">
         <v>0.9375</v>
       </c>
-      <c r="F63" s="18">
+      <c r="F63" s="19">
         <v>0.968055555555556</v>
       </c>
       <c r="G63" s="2">
@@ -3875,13 +3869,13 @@
       <c r="C64" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D64" s="16">
+      <c r="D64" s="17">
         <v>45864</v>
       </c>
-      <c r="E64" s="18">
+      <c r="E64" s="19">
         <v>0.75</v>
       </c>
-      <c r="F64" s="18">
+      <c r="F64" s="19">
         <v>0.791666666666667</v>
       </c>
       <c r="G64" s="2">
@@ -3898,13 +3892,13 @@
       <c r="C65" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D65" s="16">
+      <c r="D65" s="17">
         <v>45864</v>
       </c>
-      <c r="E65" s="18">
+      <c r="E65" s="19">
         <v>0.916666666666667</v>
       </c>
-      <c r="F65" s="18">
+      <c r="F65" s="19">
         <v>0.958333333333333</v>
       </c>
       <c r="G65" s="2">
@@ -3921,10 +3915,10 @@
       <c r="C66" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D66" s="16">
+      <c r="D66" s="17">
         <v>45865</v>
       </c>
-      <c r="E66" s="18">
+      <c r="E66" s="19">
         <v>0.875</v>
       </c>
       <c r="F66" s="2"/>
@@ -3942,13 +3936,13 @@
       <c r="C67" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D67" s="17">
+      <c r="D67" s="18">
         <v>45870</v>
       </c>
-      <c r="E67" s="19">
+      <c r="E67" s="20">
         <v>0.8125</v>
       </c>
-      <c r="F67" s="19">
+      <c r="F67" s="20">
         <v>0.854166666666667</v>
       </c>
       <c r="G67" s="6">
@@ -3965,13 +3959,13 @@
       <c r="C68" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="D68" s="17">
+      <c r="D68" s="18">
         <v>45870</v>
       </c>
-      <c r="E68" s="19">
+      <c r="E68" s="20">
         <v>0.958333333333333</v>
       </c>
-      <c r="F68" s="19">
+      <c r="F68" s="20">
         <v>0</v>
       </c>
       <c r="G68" s="6">
@@ -3988,13 +3982,13 @@
       <c r="C69" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D69" s="17">
+      <c r="D69" s="18">
         <v>45871</v>
       </c>
-      <c r="E69" s="19">
+      <c r="E69" s="20">
         <v>0.770833333333333</v>
       </c>
-      <c r="F69" s="19">
+      <c r="F69" s="20">
         <v>0.8125</v>
       </c>
       <c r="G69" s="6">
@@ -4011,13 +4005,13 @@
       <c r="C70" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D70" s="17">
+      <c r="D70" s="18">
         <v>45871</v>
       </c>
-      <c r="E70" s="19">
+      <c r="E70" s="20">
         <v>0.916666666666667</v>
       </c>
-      <c r="F70" s="19">
+      <c r="F70" s="20">
         <v>0.958333333333333</v>
       </c>
       <c r="G70" s="6">
@@ -4034,10 +4028,10 @@
       <c r="C71" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D71" s="17">
+      <c r="D71" s="18">
         <v>45872</v>
       </c>
-      <c r="E71" s="19">
+      <c r="E71" s="20">
         <v>0.875</v>
       </c>
       <c r="F71" s="6"/>
@@ -4055,13 +4049,13 @@
       <c r="C72" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D72" s="16">
+      <c r="D72" s="17">
         <v>45898</v>
       </c>
-      <c r="E72" s="18">
+      <c r="E72" s="19">
         <v>0.770833333333333</v>
       </c>
-      <c r="F72" s="18">
+      <c r="F72" s="19">
         <v>0.8125</v>
       </c>
       <c r="G72" s="2">
@@ -4078,13 +4072,13 @@
       <c r="C73" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D73" s="16">
+      <c r="D73" s="17">
         <v>45898</v>
       </c>
-      <c r="E73" s="18">
+      <c r="E73" s="19">
         <v>0.916666666666667</v>
       </c>
-      <c r="F73" s="18">
+      <c r="F73" s="19">
         <v>0.958333333333333</v>
       </c>
       <c r="G73" s="2">
@@ -4101,13 +4095,13 @@
       <c r="C74" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D74" s="16">
+      <c r="D74" s="17">
         <v>45899</v>
       </c>
-      <c r="E74" s="18">
+      <c r="E74" s="19">
         <v>0.729166666666667</v>
       </c>
-      <c r="F74" s="18">
+      <c r="F74" s="19">
         <v>0.770833333333333</v>
       </c>
       <c r="G74" s="2">
@@ -4124,13 +4118,13 @@
       <c r="C75" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D75" s="16">
+      <c r="D75" s="17">
         <v>45899</v>
       </c>
-      <c r="E75" s="18">
+      <c r="E75" s="19">
         <v>0.875</v>
       </c>
-      <c r="F75" s="18">
+      <c r="F75" s="19">
         <v>0.916666666666667</v>
       </c>
       <c r="G75" s="2">
@@ -4147,13 +4141,13 @@
       <c r="C76" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D76" s="16">
+      <c r="D76" s="17">
         <v>45900</v>
       </c>
-      <c r="E76" s="18">
+      <c r="E76" s="19">
         <v>0.875</v>
       </c>
-      <c r="F76" s="18"/>
+      <c r="F76" s="19"/>
       <c r="G76" s="2">
         <v>1</v>
       </c>
@@ -4168,13 +4162,13 @@
       <c r="C77" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D77" s="17">
+      <c r="D77" s="18">
         <v>45905</v>
       </c>
-      <c r="E77" s="19">
+      <c r="E77" s="20">
         <v>0.8125</v>
       </c>
-      <c r="F77" s="19">
+      <c r="F77" s="20">
         <v>0.854166666666667</v>
       </c>
       <c r="G77" s="6">
@@ -4191,13 +4185,13 @@
       <c r="C78" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="D78" s="17">
+      <c r="D78" s="18">
         <v>45905</v>
       </c>
-      <c r="E78" s="19">
+      <c r="E78" s="20">
         <v>0.958333333333333</v>
       </c>
-      <c r="F78" s="19">
+      <c r="F78" s="20">
         <v>0</v>
       </c>
       <c r="G78" s="6">
@@ -4214,13 +4208,13 @@
       <c r="C79" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D79" s="17">
+      <c r="D79" s="18">
         <v>45906</v>
       </c>
-      <c r="E79" s="19">
+      <c r="E79" s="20">
         <v>0.770833333333333</v>
       </c>
-      <c r="F79" s="19">
+      <c r="F79" s="20">
         <v>0.8125</v>
       </c>
       <c r="G79" s="6">
@@ -4237,13 +4231,13 @@
       <c r="C80" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D80" s="17">
+      <c r="D80" s="18">
         <v>45906</v>
       </c>
-      <c r="E80" s="19">
+      <c r="E80" s="20">
         <v>0.916666666666667</v>
       </c>
-      <c r="F80" s="19">
+      <c r="F80" s="20">
         <v>0.958333333333333</v>
       </c>
       <c r="G80" s="6">
@@ -4260,10 +4254,10 @@
       <c r="C81" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D81" s="17">
+      <c r="D81" s="18">
         <v>45907</v>
       </c>
-      <c r="E81" s="19">
+      <c r="E81" s="20">
         <v>0.875</v>
       </c>
       <c r="F81" s="6"/>
@@ -4281,13 +4275,13 @@
       <c r="C82" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D82" s="16">
+      <c r="D82" s="17">
         <v>45919</v>
       </c>
-      <c r="E82" s="18">
+      <c r="E82" s="19">
         <v>0.6875</v>
       </c>
-      <c r="F82" s="18">
+      <c r="F82" s="19">
         <v>0.729166666666667</v>
       </c>
       <c r="G82" s="2">
@@ -4304,13 +4298,13 @@
       <c r="C83" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D83" s="16">
+      <c r="D83" s="17">
         <v>45919</v>
       </c>
-      <c r="E83" s="18">
+      <c r="E83" s="19">
         <v>0.833333333333333</v>
       </c>
-      <c r="F83" s="18">
+      <c r="F83" s="19">
         <v>0.875</v>
       </c>
       <c r="G83" s="2">
@@ -4327,13 +4321,13 @@
       <c r="C84" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D84" s="16">
+      <c r="D84" s="17">
         <v>45920</v>
       </c>
-      <c r="E84" s="18">
+      <c r="E84" s="19">
         <v>0.6875</v>
       </c>
-      <c r="F84" s="18">
+      <c r="F84" s="19">
         <v>0.729166666666667</v>
       </c>
       <c r="G84" s="2">
@@ -4350,13 +4344,13 @@
       <c r="C85" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D85" s="16">
+      <c r="D85" s="17">
         <v>45920</v>
       </c>
-      <c r="E85" s="18">
+      <c r="E85" s="19">
         <v>0.833333333333333</v>
       </c>
-      <c r="F85" s="18">
+      <c r="F85" s="19">
         <v>0.875</v>
       </c>
       <c r="G85" s="2">
@@ -4373,10 +4367,10 @@
       <c r="C86" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D86" s="16">
+      <c r="D86" s="17">
         <v>45921</v>
       </c>
-      <c r="E86" s="18">
+      <c r="E86" s="19">
         <v>0.791666666666667</v>
       </c>
       <c r="F86" s="2"/>
@@ -4394,13 +4388,13 @@
       <c r="C87" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D87" s="17">
+      <c r="D87" s="18">
         <v>45933</v>
       </c>
-      <c r="E87" s="19">
+      <c r="E87" s="20">
         <v>0.729166666666667</v>
       </c>
-      <c r="F87" s="19">
+      <c r="F87" s="20">
         <v>0.770833333333333</v>
       </c>
       <c r="G87" s="6">
@@ -4417,13 +4411,13 @@
       <c r="C88" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="D88" s="17">
+      <c r="D88" s="18">
         <v>45933</v>
       </c>
-      <c r="E88" s="19">
+      <c r="E88" s="20">
         <v>0.875</v>
       </c>
-      <c r="F88" s="19">
+      <c r="F88" s="20">
         <v>0.916666666666667</v>
       </c>
       <c r="G88" s="6">
@@ -4440,13 +4434,13 @@
       <c r="C89" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D89" s="17">
+      <c r="D89" s="18">
         <v>45934</v>
       </c>
-      <c r="E89" s="19">
+      <c r="E89" s="20">
         <v>0.729166666666667</v>
       </c>
-      <c r="F89" s="19">
+      <c r="F89" s="20">
         <v>0.770833333333333</v>
       </c>
       <c r="G89" s="6">
@@ -4463,13 +4457,13 @@
       <c r="C90" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D90" s="17">
+      <c r="D90" s="18">
         <v>45934</v>
       </c>
-      <c r="E90" s="19">
+      <c r="E90" s="20">
         <v>0.875</v>
       </c>
-      <c r="F90" s="19">
+      <c r="F90" s="20">
         <v>0.916666666666667</v>
       </c>
       <c r="G90" s="6">
@@ -4486,10 +4480,10 @@
       <c r="C91" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D91" s="17">
+      <c r="D91" s="18">
         <v>45935</v>
       </c>
-      <c r="E91" s="19">
+      <c r="E91" s="20">
         <v>0.833333333333333</v>
       </c>
       <c r="F91" s="6"/>
@@ -4507,13 +4501,13 @@
       <c r="C92" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D92" s="16">
+      <c r="D92" s="17">
         <v>45948</v>
       </c>
-      <c r="E92" s="18">
+      <c r="E92" s="19">
         <v>0.0625</v>
       </c>
-      <c r="F92" s="18">
+      <c r="F92" s="19">
         <v>0.104166666666667</v>
       </c>
       <c r="G92" s="2">
@@ -4530,13 +4524,13 @@
       <c r="C93" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D93" s="16">
+      <c r="D93" s="17">
         <v>45948</v>
       </c>
-      <c r="E93" s="18">
+      <c r="E93" s="19">
         <v>0.229166666666667</v>
       </c>
-      <c r="F93" s="18">
+      <c r="F93" s="19">
         <v>0.259722222222222</v>
       </c>
       <c r="G93" s="2">
@@ -4553,13 +4547,13 @@
       <c r="C94" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D94" s="16">
+      <c r="D94" s="17">
         <v>45949</v>
       </c>
-      <c r="E94" s="18">
+      <c r="E94" s="19">
         <v>0.0416666666666667</v>
       </c>
-      <c r="F94" s="18">
+      <c r="F94" s="19">
         <v>0.0625</v>
       </c>
       <c r="G94" s="2">
@@ -4576,13 +4570,13 @@
       <c r="C95" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D95" s="16">
+      <c r="D95" s="17">
         <v>45949</v>
       </c>
-      <c r="E95" s="18">
+      <c r="E95" s="19">
         <v>0.208333333333333</v>
       </c>
-      <c r="F95" s="18">
+      <c r="F95" s="19">
         <v>0.25</v>
       </c>
       <c r="G95" s="2">
@@ -4599,10 +4593,10 @@
       <c r="C96" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D96" s="16">
+      <c r="D96" s="17">
         <v>45950</v>
       </c>
-      <c r="E96" s="18">
+      <c r="E96" s="19">
         <v>0.125</v>
       </c>
       <c r="F96" s="2"/>
@@ -4620,13 +4614,13 @@
       <c r="C97" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D97" s="17">
+      <c r="D97" s="18">
         <v>45955</v>
       </c>
-      <c r="E97" s="19">
+      <c r="E97" s="20">
         <v>0.104166666666667</v>
       </c>
-      <c r="F97" s="19">
+      <c r="F97" s="20">
         <v>0.145833333333333</v>
       </c>
       <c r="G97" s="6">
@@ -4643,13 +4637,13 @@
       <c r="C98" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="D98" s="17">
+      <c r="D98" s="18">
         <v>45955</v>
       </c>
-      <c r="E98" s="19">
+      <c r="E98" s="20">
         <v>0.25</v>
       </c>
-      <c r="F98" s="19">
+      <c r="F98" s="20">
         <v>0.291666666666667</v>
       </c>
       <c r="G98" s="6">
@@ -4666,13 +4660,13 @@
       <c r="C99" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D99" s="17">
+      <c r="D99" s="18">
         <v>45956</v>
       </c>
-      <c r="E99" s="19">
+      <c r="E99" s="20">
         <v>0.0625</v>
       </c>
-      <c r="F99" s="19">
+      <c r="F99" s="20">
         <v>0.104166666666667</v>
       </c>
       <c r="G99" s="6">
@@ -4689,13 +4683,13 @@
       <c r="C100" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D100" s="17">
+      <c r="D100" s="18">
         <v>45956</v>
       </c>
-      <c r="E100" s="19">
+      <c r="E100" s="20">
         <v>0.208333333333333</v>
       </c>
-      <c r="F100" s="19">
+      <c r="F100" s="20">
         <v>0.25</v>
       </c>
       <c r="G100" s="6">
@@ -4712,10 +4706,10 @@
       <c r="C101" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D101" s="17">
+      <c r="D101" s="18">
         <v>45957</v>
       </c>
-      <c r="E101" s="19">
+      <c r="E101" s="20">
         <v>0.166666666666667</v>
       </c>
       <c r="F101" s="6"/>
@@ -4733,13 +4727,13 @@
       <c r="C102" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D102" s="16">
+      <c r="D102" s="17">
         <v>45968</v>
       </c>
-      <c r="E102" s="18">
+      <c r="E102" s="19">
         <v>0.9375</v>
       </c>
-      <c r="F102" s="18">
+      <c r="F102" s="19">
         <v>0.979166666666667</v>
       </c>
       <c r="G102" s="2">
@@ -4756,13 +4750,13 @@
       <c r="C103" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D103" s="16">
+      <c r="D103" s="17">
         <v>45969</v>
       </c>
-      <c r="E103" s="18">
+      <c r="E103" s="19">
         <v>0.104166666666667</v>
       </c>
-      <c r="F103" s="18">
+      <c r="F103" s="19">
         <v>0.134722222222222</v>
       </c>
       <c r="G103" s="2">
@@ -4779,13 +4773,13 @@
       <c r="C104" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D104" s="16">
+      <c r="D104" s="17">
         <v>45969</v>
       </c>
-      <c r="E104" s="18">
+      <c r="E104" s="19">
         <v>0.916666666666667</v>
       </c>
-      <c r="F104" s="18">
+      <c r="F104" s="19">
         <v>0.958333333333333</v>
       </c>
       <c r="G104" s="2">
@@ -4802,13 +4796,13 @@
       <c r="C105" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D105" s="16">
+      <c r="D105" s="17">
         <v>45970</v>
       </c>
-      <c r="E105" s="18">
+      <c r="E105" s="19">
         <v>0.0833333333333333</v>
       </c>
-      <c r="F105" s="18">
+      <c r="F105" s="19">
         <v>0.125</v>
       </c>
       <c r="G105" s="2">
@@ -4825,10 +4819,10 @@
       <c r="C106" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D106" s="16">
+      <c r="D106" s="17">
         <v>45971</v>
       </c>
-      <c r="E106" s="18">
+      <c r="E106" s="19">
         <v>0.0416666666666667</v>
       </c>
       <c r="F106" s="2"/>
@@ -4846,13 +4840,13 @@
       <c r="C107" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D107" s="17">
+      <c r="D107" s="18">
         <v>45982</v>
       </c>
-      <c r="E107" s="19">
+      <c r="E107" s="20">
         <v>0.354166666666667</v>
       </c>
-      <c r="F107" s="19">
+      <c r="F107" s="20">
         <v>0.395833333333333</v>
       </c>
       <c r="G107" s="6">
@@ -4869,13 +4863,13 @@
       <c r="C108" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="D108" s="17">
+      <c r="D108" s="18">
         <v>45982</v>
       </c>
-      <c r="E108" s="19">
+      <c r="E108" s="20">
         <v>0.5</v>
       </c>
-      <c r="F108" s="19">
+      <c r="F108" s="20">
         <v>0.541666666666667</v>
       </c>
       <c r="G108" s="6">
@@ -4892,13 +4886,13 @@
       <c r="C109" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D109" s="17">
+      <c r="D109" s="18">
         <v>45983</v>
       </c>
-      <c r="E109" s="20">
+      <c r="E109" s="21">
         <v>0.354166666666667</v>
       </c>
-      <c r="F109" s="20">
+      <c r="F109" s="21">
         <v>0.395833333333333</v>
       </c>
       <c r="G109" s="6">
@@ -4915,13 +4909,13 @@
       <c r="C110" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D110" s="17">
+      <c r="D110" s="18">
         <v>45983</v>
       </c>
-      <c r="E110" s="20">
+      <c r="E110" s="21">
         <v>0.5</v>
       </c>
-      <c r="F110" s="20">
+      <c r="F110" s="21">
         <v>0.541666666666667</v>
       </c>
       <c r="G110" s="6">
@@ -4938,10 +4932,10 @@
       <c r="C111" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D111" s="17">
+      <c r="D111" s="18">
         <v>45984</v>
       </c>
-      <c r="E111" s="20">
+      <c r="E111" s="21">
         <v>0.5</v>
       </c>
       <c r="F111" s="6"/>
@@ -4959,13 +4953,13 @@
       <c r="C112" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D112" s="16">
+      <c r="D112" s="17">
         <v>45989</v>
       </c>
-      <c r="E112" s="21">
+      <c r="E112" s="22">
         <v>0.895833333333333</v>
       </c>
-      <c r="F112" s="21">
+      <c r="F112" s="22">
         <v>0.9375</v>
       </c>
       <c r="G112" s="2">
@@ -4982,13 +4976,13 @@
       <c r="C113" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D113" s="16">
+      <c r="D113" s="17">
         <v>45990</v>
       </c>
-      <c r="E113" s="21">
+      <c r="E113" s="22">
         <v>0.0625</v>
       </c>
-      <c r="F113" s="21">
+      <c r="F113" s="22">
         <v>0.0930555555555556</v>
       </c>
       <c r="G113" s="2">
@@ -5005,13 +4999,13 @@
       <c r="C114" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D114" s="16">
+      <c r="D114" s="17">
         <v>45990</v>
       </c>
-      <c r="E114" s="21">
+      <c r="E114" s="22">
         <v>0.916666666666667</v>
       </c>
-      <c r="F114" s="21">
+      <c r="F114" s="22">
         <v>0.958333333333333</v>
       </c>
       <c r="G114" s="2">
@@ -5028,13 +5022,13 @@
       <c r="C115" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D115" s="16">
+      <c r="D115" s="17">
         <v>45991</v>
       </c>
-      <c r="E115" s="21">
+      <c r="E115" s="22">
         <v>0.0833333333333333</v>
       </c>
-      <c r="F115" s="21">
+      <c r="F115" s="22">
         <v>0.125</v>
       </c>
       <c r="G115" s="2">
@@ -5051,10 +5045,10 @@
       <c r="C116" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D116" s="16">
+      <c r="D116" s="17">
         <v>45992</v>
       </c>
-      <c r="E116" s="21">
+      <c r="E116" s="22">
         <v>0</v>
       </c>
       <c r="F116" s="2"/>
@@ -5072,13 +5066,13 @@
       <c r="C117" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D117" s="17">
+      <c r="D117" s="18">
         <v>45996</v>
       </c>
-      <c r="E117" s="20">
+      <c r="E117" s="21">
         <v>0.729166666666667</v>
       </c>
-      <c r="F117" s="20">
+      <c r="F117" s="21">
         <v>0.770833333333333</v>
       </c>
       <c r="G117" s="6">
@@ -5095,13 +5089,13 @@
       <c r="C118" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="D118" s="17">
+      <c r="D118" s="18">
         <v>45996</v>
       </c>
-      <c r="E118" s="20">
+      <c r="E118" s="21">
         <v>0.875</v>
       </c>
-      <c r="F118" s="20">
+      <c r="F118" s="21">
         <v>0.916666666666667</v>
       </c>
       <c r="G118" s="6">
@@ -5118,13 +5112,13 @@
       <c r="C119" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D119" s="17">
+      <c r="D119" s="18">
         <v>45997</v>
       </c>
-      <c r="E119" s="20">
+      <c r="E119" s="21">
         <v>0.770833333333333</v>
       </c>
-      <c r="F119" s="20">
+      <c r="F119" s="21">
         <v>0.8125</v>
       </c>
       <c r="G119" s="6">
@@ -5141,13 +5135,13 @@
       <c r="C120" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D120" s="17">
+      <c r="D120" s="18">
         <v>45997</v>
       </c>
-      <c r="E120" s="20">
+      <c r="E120" s="21">
         <v>0.916666666666667</v>
       </c>
-      <c r="F120" s="20">
+      <c r="F120" s="21">
         <v>0.958333333333333</v>
       </c>
       <c r="G120" s="6">
@@ -5164,10 +5158,10 @@
       <c r="C121" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D121" s="17">
+      <c r="D121" s="18">
         <v>45998</v>
       </c>
-      <c r="E121" s="20">
+      <c r="E121" s="21">
         <v>0.875</v>
       </c>
       <c r="F121" s="6"/>
@@ -5184,7 +5178,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R961"/>
+  <dimension ref="A1:R1021"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -29900,484 +29894,484 @@
       </c>
     </row>
     <row r="922" spans="1:8">
-      <c r="A922" s="15">
-        <v>2025</v>
-      </c>
-      <c r="B922" s="15">
+      <c r="A922" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B922" s="2">
         <v>20</v>
       </c>
       <c r="C922" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D922" s="15">
+      <c r="D922" s="2">
         <v>1</v>
       </c>
-      <c r="E922" s="15">
+      <c r="E922" s="2">
         <v>4</v>
       </c>
-      <c r="F922" s="15" t="s">
+      <c r="F922" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="G922" s="15" t="s">
+      <c r="G922" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="H922" s="15"/>
+      <c r="H922" s="2"/>
     </row>
     <row r="923" spans="1:8">
-      <c r="A923" s="15">
-        <v>2025</v>
-      </c>
-      <c r="B923" s="15">
+      <c r="A923" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B923" s="2">
         <v>20</v>
       </c>
       <c r="C923" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D923" s="15">
+      <c r="D923" s="2">
         <v>2</v>
       </c>
-      <c r="E923" s="15">
+      <c r="E923" s="2">
         <v>16</v>
       </c>
-      <c r="F923" s="15" t="s">
+      <c r="F923" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="G923" s="15" t="s">
+      <c r="G923" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="H923" s="15"/>
+      <c r="H923" s="2"/>
     </row>
     <row r="924" spans="1:8">
-      <c r="A924" s="15">
-        <v>2025</v>
-      </c>
-      <c r="B924" s="15">
+      <c r="A924" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B924" s="2">
         <v>20</v>
       </c>
       <c r="C924" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D924" s="15">
+      <c r="D924" s="2">
         <v>3</v>
       </c>
-      <c r="E924" s="15">
+      <c r="E924" s="2">
         <v>44</v>
       </c>
-      <c r="F924" s="15" t="s">
+      <c r="F924" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="G924" s="15" t="s">
+      <c r="G924" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="H924" s="15"/>
+      <c r="H924" s="2"/>
     </row>
     <row r="925" spans="1:8">
-      <c r="A925" s="15">
-        <v>2025</v>
-      </c>
-      <c r="B925" s="15">
+      <c r="A925" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B925" s="2">
         <v>20</v>
       </c>
       <c r="C925" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D925" s="15">
+      <c r="D925" s="2">
         <v>4</v>
       </c>
-      <c r="E925" s="15">
+      <c r="E925" s="2">
         <v>63</v>
       </c>
-      <c r="F925" s="15" t="s">
+      <c r="F925" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="G925" s="15" t="s">
+      <c r="G925" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="H925" s="15"/>
+      <c r="H925" s="2"/>
     </row>
     <row r="926" spans="1:8">
-      <c r="A926" s="15">
-        <v>2025</v>
-      </c>
-      <c r="B926" s="15">
+      <c r="A926" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B926" s="2">
         <v>20</v>
       </c>
       <c r="C926" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D926" s="15">
+      <c r="D926" s="2">
         <v>5</v>
       </c>
-      <c r="E926" s="15">
+      <c r="E926" s="2">
         <v>1</v>
       </c>
-      <c r="F926" s="15" t="s">
+      <c r="F926" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="G926" s="15" t="s">
+      <c r="G926" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="H926" s="15"/>
+      <c r="H926" s="2"/>
     </row>
     <row r="927" spans="1:8">
-      <c r="A927" s="15">
-        <v>2025</v>
-      </c>
-      <c r="B927" s="15">
+      <c r="A927" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B927" s="2">
         <v>20</v>
       </c>
       <c r="C927" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D927" s="15">
+      <c r="D927" s="2">
         <v>6</v>
       </c>
-      <c r="E927" s="15">
+      <c r="E927" s="2">
         <v>12</v>
       </c>
-      <c r="F927" s="15" t="s">
+      <c r="F927" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="G927" s="15" t="s">
+      <c r="G927" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="H927" s="15"/>
+      <c r="H927" s="2"/>
     </row>
     <row r="928" spans="1:8">
-      <c r="A928" s="15">
-        <v>2025</v>
-      </c>
-      <c r="B928" s="15">
+      <c r="A928" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B928" s="2">
         <v>20</v>
       </c>
       <c r="C928" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D928" s="15">
+      <c r="D928" s="2">
         <v>7</v>
       </c>
-      <c r="E928" s="15">
+      <c r="E928" s="2">
         <v>55</v>
       </c>
-      <c r="F928" s="15" t="s">
+      <c r="F928" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="G928" s="15" t="s">
+      <c r="G928" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="H928" s="15"/>
+      <c r="H928" s="2"/>
     </row>
     <row r="929" spans="1:8">
-      <c r="A929" s="15">
-        <v>2025</v>
-      </c>
-      <c r="B929" s="15">
+      <c r="A929" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B929" s="2">
         <v>20</v>
       </c>
       <c r="C929" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D929" s="15">
+      <c r="D929" s="2">
         <v>8</v>
       </c>
-      <c r="E929" s="15">
+      <c r="E929" s="2">
         <v>81</v>
       </c>
-      <c r="F929" s="15" t="s">
+      <c r="F929" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="G929" s="15" t="s">
+      <c r="G929" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="H929" s="15"/>
+      <c r="H929" s="2"/>
     </row>
     <row r="930" spans="1:8">
-      <c r="A930" s="15">
-        <v>2025</v>
-      </c>
-      <c r="B930" s="15">
+      <c r="A930" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B930" s="2">
         <v>20</v>
       </c>
       <c r="C930" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D930" s="15">
+      <c r="D930" s="2">
         <v>9</v>
       </c>
-      <c r="E930" s="15">
+      <c r="E930" s="2">
         <v>6</v>
       </c>
-      <c r="F930" s="15" t="s">
+      <c r="F930" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="G930" s="15" t="s">
+      <c r="G930" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="H930" s="15"/>
+      <c r="H930" s="2"/>
     </row>
     <row r="931" spans="1:8">
-      <c r="A931" s="15">
-        <v>2025</v>
-      </c>
-      <c r="B931" s="15">
+      <c r="A931" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B931" s="2">
         <v>20</v>
       </c>
       <c r="C931" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D931" s="15">
+      <c r="D931" s="2">
         <v>10</v>
       </c>
-      <c r="E931" s="15">
+      <c r="E931" s="2">
         <v>87</v>
       </c>
-      <c r="F931" s="15" t="s">
+      <c r="F931" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="G931" s="15" t="s">
+      <c r="G931" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="H931" s="15"/>
+      <c r="H931" s="2"/>
     </row>
     <row r="932" spans="1:8">
-      <c r="A932" s="15">
-        <v>2025</v>
-      </c>
-      <c r="B932" s="15">
+      <c r="A932" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B932" s="2">
         <v>20</v>
       </c>
       <c r="C932" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D932" s="15">
+      <c r="D932" s="2">
         <v>11</v>
       </c>
-      <c r="E932" s="15">
+      <c r="E932" s="2">
         <v>22</v>
       </c>
-      <c r="F932" s="15" t="s">
+      <c r="F932" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="G932" s="15" t="s">
+      <c r="G932" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="H932" s="15"/>
+      <c r="H932" s="2"/>
     </row>
     <row r="933" spans="1:8">
-      <c r="A933" s="15">
-        <v>2025</v>
-      </c>
-      <c r="B933" s="15">
+      <c r="A933" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B933" s="2">
         <v>20</v>
       </c>
       <c r="C933" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D933" s="15">
+      <c r="D933" s="2">
         <v>12</v>
       </c>
-      <c r="E933" s="15">
+      <c r="E933" s="2">
         <v>31</v>
       </c>
-      <c r="F933" s="15" t="s">
+      <c r="F933" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="G933" s="15" t="s">
+      <c r="G933" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="H933" s="15"/>
+      <c r="H933" s="2"/>
     </row>
     <row r="934" spans="1:8">
-      <c r="A934" s="15">
-        <v>2025</v>
-      </c>
-      <c r="B934" s="15">
+      <c r="A934" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B934" s="2">
         <v>20</v>
       </c>
       <c r="C934" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D934" s="15">
+      <c r="D934" s="2">
         <v>13</v>
       </c>
-      <c r="E934" s="15">
+      <c r="E934" s="2">
         <v>27</v>
       </c>
-      <c r="F934" s="15" t="s">
+      <c r="F934" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="G934" s="15" t="s">
+      <c r="G934" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="H934" s="15"/>
+      <c r="H934" s="2"/>
     </row>
     <row r="935" spans="1:8">
-      <c r="A935" s="15">
-        <v>2025</v>
-      </c>
-      <c r="B935" s="15">
+      <c r="A935" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B935" s="2">
         <v>20</v>
       </c>
       <c r="C935" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D935" s="15">
+      <c r="D935" s="2">
         <v>14</v>
       </c>
-      <c r="E935" s="15">
+      <c r="E935" s="2">
         <v>14</v>
       </c>
-      <c r="F935" s="15" t="s">
+      <c r="F935" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="G935" s="15" t="s">
+      <c r="G935" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="H935" s="15"/>
+      <c r="H935" s="2"/>
     </row>
     <row r="936" spans="1:8">
-      <c r="A936" s="15">
-        <v>2025</v>
-      </c>
-      <c r="B936" s="15">
+      <c r="A936" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B936" s="2">
         <v>20</v>
       </c>
       <c r="C936" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D936" s="15">
+      <c r="D936" s="2">
         <v>15</v>
       </c>
-      <c r="E936" s="15">
+      <c r="E936" s="2">
         <v>30</v>
       </c>
-      <c r="F936" s="15" t="s">
+      <c r="F936" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="G936" s="15" t="s">
+      <c r="G936" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="H936" s="15"/>
+      <c r="H936" s="2"/>
     </row>
     <row r="937" spans="1:8">
-      <c r="A937" s="15">
-        <v>2025</v>
-      </c>
-      <c r="B937" s="15">
+      <c r="A937" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B937" s="2">
         <v>20</v>
       </c>
       <c r="C937" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D937" s="15">
+      <c r="D937" s="2">
         <v>16</v>
       </c>
-      <c r="E937" s="15">
+      <c r="E937" s="2">
         <v>5</v>
       </c>
-      <c r="F937" s="15" t="s">
+      <c r="F937" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="G937" s="15" t="s">
+      <c r="G937" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="H937" s="15"/>
+      <c r="H937" s="2"/>
     </row>
     <row r="938" spans="1:8">
-      <c r="A938" s="15">
-        <v>2025</v>
-      </c>
-      <c r="B938" s="15">
+      <c r="A938" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B938" s="2">
         <v>20</v>
       </c>
       <c r="C938" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D938" s="15">
+      <c r="D938" s="2">
         <v>17</v>
       </c>
-      <c r="E938" s="15">
+      <c r="E938" s="2">
         <v>23</v>
       </c>
-      <c r="F938" s="15" t="s">
+      <c r="F938" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="G938" s="15" t="s">
+      <c r="G938" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="H938" s="15"/>
+      <c r="H938" s="2"/>
     </row>
     <row r="939" spans="1:8">
-      <c r="A939" s="15">
-        <v>2025</v>
-      </c>
-      <c r="B939" s="15">
+      <c r="A939" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B939" s="2">
         <v>20</v>
       </c>
       <c r="C939" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D939" s="15">
+      <c r="D939" s="2">
         <v>18</v>
       </c>
-      <c r="E939" s="15">
+      <c r="E939" s="2">
         <v>10</v>
       </c>
-      <c r="F939" s="15" t="s">
+      <c r="F939" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="G939" s="15" t="s">
+      <c r="G939" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="H939" s="15"/>
+      <c r="H939" s="2"/>
     </row>
     <row r="940" spans="1:8">
-      <c r="A940" s="15">
-        <v>2025</v>
-      </c>
-      <c r="B940" s="15">
+      <c r="A940" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B940" s="2">
         <v>20</v>
       </c>
       <c r="C940" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D940" s="15">
+      <c r="D940" s="2">
         <v>19</v>
       </c>
-      <c r="E940" s="15">
+      <c r="E940" s="2">
         <v>18</v>
       </c>
-      <c r="F940" s="15" t="s">
+      <c r="F940" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="G940" s="15" t="s">
+      <c r="G940" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="H940" s="15"/>
+      <c r="H940" s="2"/>
     </row>
     <row r="941" spans="1:8">
-      <c r="A941" s="15">
-        <v>2025</v>
-      </c>
-      <c r="B941" s="15">
+      <c r="A941" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B941" s="2">
         <v>20</v>
       </c>
       <c r="C941" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D941" s="15">
+      <c r="D941" s="2">
         <v>20</v>
       </c>
-      <c r="E941" s="15">
+      <c r="E941" s="2">
         <v>43</v>
       </c>
-      <c r="F941" s="15" t="s">
+      <c r="F941" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="G941" s="15" t="s">
+      <c r="G941" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="H941" s="15"/>
+      <c r="H941" s="2"/>
     </row>
     <row r="942" spans="1:8">
       <c r="A942" s="6">
@@ -30899,8 +30893,1482 @@
         <v>0</v>
       </c>
     </row>
+    <row r="962" spans="1:8">
+      <c r="A962" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B962" s="15">
+        <v>21</v>
+      </c>
+      <c r="C962" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="D962" s="15">
+        <v>1</v>
+      </c>
+      <c r="E962" s="15">
+        <v>4</v>
+      </c>
+      <c r="F962" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="G962" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="H962" s="15"/>
+    </row>
+    <row r="963" spans="1:8">
+      <c r="A963" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B963" s="15">
+        <v>21</v>
+      </c>
+      <c r="C963" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="D963" s="15">
+        <v>2</v>
+      </c>
+      <c r="E963" s="15">
+        <v>12</v>
+      </c>
+      <c r="F963" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="G963" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="H963" s="15"/>
+    </row>
+    <row r="964" spans="1:8">
+      <c r="A964" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B964" s="15">
+        <v>21</v>
+      </c>
+      <c r="C964" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="D964" s="15">
+        <v>3</v>
+      </c>
+      <c r="E964" s="15">
+        <v>81</v>
+      </c>
+      <c r="F964" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="G964" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="H964" s="15"/>
+    </row>
+    <row r="965" spans="1:8">
+      <c r="A965" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B965" s="15">
+        <v>21</v>
+      </c>
+      <c r="C965" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="D965" s="15">
+        <v>4</v>
+      </c>
+      <c r="E965" s="15">
+        <v>63</v>
+      </c>
+      <c r="F965" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="G965" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="H965" s="15"/>
+    </row>
+    <row r="966" spans="1:8">
+      <c r="A966" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B966" s="15">
+        <v>21</v>
+      </c>
+      <c r="C966" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="D966" s="15">
+        <v>5</v>
+      </c>
+      <c r="E966" s="15">
+        <v>14</v>
+      </c>
+      <c r="F966" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="G966" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="H966" s="15"/>
+    </row>
+    <row r="967" spans="1:8">
+      <c r="A967" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B967" s="15">
+        <v>21</v>
+      </c>
+      <c r="C967" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="D967" s="15">
+        <v>6</v>
+      </c>
+      <c r="E967" s="15">
+        <v>1</v>
+      </c>
+      <c r="F967" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="G967" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="H967" s="15"/>
+    </row>
+    <row r="968" spans="1:8">
+      <c r="A968" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B968" s="15">
+        <v>21</v>
+      </c>
+      <c r="C968" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="D968" s="15">
+        <v>7</v>
+      </c>
+      <c r="E968" s="15">
+        <v>18</v>
+      </c>
+      <c r="F968" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="G968" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="H968" s="15"/>
+    </row>
+    <row r="969" spans="1:8">
+      <c r="A969" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B969" s="15">
+        <v>21</v>
+      </c>
+      <c r="C969" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="D969" s="15">
+        <v>8</v>
+      </c>
+      <c r="E969" s="15">
+        <v>16</v>
+      </c>
+      <c r="F969" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="G969" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="H969" s="15"/>
+    </row>
+    <row r="970" spans="1:8">
+      <c r="A970" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B970" s="15">
+        <v>21</v>
+      </c>
+      <c r="C970" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="D970" s="15">
+        <v>9</v>
+      </c>
+      <c r="E970" s="15">
+        <v>6</v>
+      </c>
+      <c r="F970" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="G970" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="H970" s="15"/>
+    </row>
+    <row r="971" spans="1:8">
+      <c r="A971" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B971" s="15">
+        <v>21</v>
+      </c>
+      <c r="C971" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="D971" s="15">
+        <v>10</v>
+      </c>
+      <c r="E971" s="15">
+        <v>27</v>
+      </c>
+      <c r="F971" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="G971" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="H971" s="15"/>
+    </row>
+    <row r="972" spans="1:8">
+      <c r="A972" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B972" s="15">
+        <v>21</v>
+      </c>
+      <c r="C972" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="D972" s="15">
+        <v>11</v>
+      </c>
+      <c r="E972" s="15">
+        <v>44</v>
+      </c>
+      <c r="F972" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="G972" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="H972" s="15"/>
+    </row>
+    <row r="973" spans="1:8">
+      <c r="A973" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B973" s="15">
+        <v>21</v>
+      </c>
+      <c r="C973" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="D973" s="15">
+        <v>12</v>
+      </c>
+      <c r="E973" s="15">
+        <v>23</v>
+      </c>
+      <c r="F973" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="G973" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="H973" s="15"/>
+    </row>
+    <row r="974" spans="1:8">
+      <c r="A974" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B974" s="15">
+        <v>21</v>
+      </c>
+      <c r="C974" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="D974" s="15">
+        <v>13</v>
+      </c>
+      <c r="E974" s="15">
+        <v>10</v>
+      </c>
+      <c r="F974" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="G974" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="H974" s="15"/>
+    </row>
+    <row r="975" spans="1:8">
+      <c r="A975" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B975" s="15">
+        <v>21</v>
+      </c>
+      <c r="C975" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="D975" s="15">
+        <v>14</v>
+      </c>
+      <c r="E975" s="15">
+        <v>5</v>
+      </c>
+      <c r="F975" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="G975" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="H975" s="15"/>
+    </row>
+    <row r="976" spans="1:8">
+      <c r="A976" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B976" s="15">
+        <v>21</v>
+      </c>
+      <c r="C976" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="D976" s="15">
+        <v>15</v>
+      </c>
+      <c r="E976" s="15">
+        <v>87</v>
+      </c>
+      <c r="F976" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="G976" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="H976" s="15"/>
+    </row>
+    <row r="977" spans="1:8">
+      <c r="A977" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B977" s="15">
+        <v>21</v>
+      </c>
+      <c r="C977" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="D977" s="15">
+        <v>16</v>
+      </c>
+      <c r="E977" s="15">
+        <v>43</v>
+      </c>
+      <c r="F977" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="G977" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="H977" s="15"/>
+    </row>
+    <row r="978" spans="1:8">
+      <c r="A978" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B978" s="15">
+        <v>21</v>
+      </c>
+      <c r="C978" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="D978" s="15">
+        <v>17</v>
+      </c>
+      <c r="E978" s="15">
+        <v>30</v>
+      </c>
+      <c r="F978" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="G978" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="H978" s="15"/>
+    </row>
+    <row r="979" spans="1:8">
+      <c r="A979" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B979" s="15">
+        <v>21</v>
+      </c>
+      <c r="C979" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="D979" s="15">
+        <v>18</v>
+      </c>
+      <c r="E979" s="15">
+        <v>22</v>
+      </c>
+      <c r="F979" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="G979" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="H979" s="15"/>
+    </row>
+    <row r="980" spans="1:8">
+      <c r="A980" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B980" s="15">
+        <v>21</v>
+      </c>
+      <c r="C980" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="D980" s="15">
+        <v>19</v>
+      </c>
+      <c r="E980" s="15">
+        <v>31</v>
+      </c>
+      <c r="F980" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="G980" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="H980" s="15"/>
+    </row>
+    <row r="981" spans="1:8">
+      <c r="A981" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B981" s="15">
+        <v>21</v>
+      </c>
+      <c r="C981" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="D981" s="15">
+        <v>20</v>
+      </c>
+      <c r="E981" s="15">
+        <v>55</v>
+      </c>
+      <c r="F981" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="G981" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="H981" s="15"/>
+    </row>
+    <row r="982" spans="1:8">
+      <c r="A982" s="16">
+        <v>2025</v>
+      </c>
+      <c r="B982" s="16">
+        <v>21</v>
+      </c>
+      <c r="C982" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="D982" s="16">
+        <v>1</v>
+      </c>
+      <c r="E982" s="16">
+        <v>4</v>
+      </c>
+      <c r="F982" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="G982" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="H982" s="16">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="983" spans="1:8">
+      <c r="A983" s="16">
+        <v>2025</v>
+      </c>
+      <c r="B983" s="16">
+        <v>21</v>
+      </c>
+      <c r="C983" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="D983" s="16">
+        <v>2</v>
+      </c>
+      <c r="E983" s="16">
+        <v>12</v>
+      </c>
+      <c r="F983" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="G983" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="H983" s="16">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="984" spans="1:8">
+      <c r="A984" s="16">
+        <v>2025</v>
+      </c>
+      <c r="B984" s="16">
+        <v>21</v>
+      </c>
+      <c r="C984" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="D984" s="16">
+        <v>3</v>
+      </c>
+      <c r="E984" s="16">
+        <v>63</v>
+      </c>
+      <c r="F984" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="G984" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="H984" s="16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="985" spans="1:8">
+      <c r="A985" s="16">
+        <v>2025</v>
+      </c>
+      <c r="B985" s="16">
+        <v>21</v>
+      </c>
+      <c r="C985" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="D985" s="16">
+        <v>4</v>
+      </c>
+      <c r="E985" s="16">
+        <v>1</v>
+      </c>
+      <c r="F985" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="G985" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="H985" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="986" spans="1:8">
+      <c r="A986" s="16">
+        <v>2025</v>
+      </c>
+      <c r="B986" s="16">
+        <v>21</v>
+      </c>
+      <c r="C986" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="D986" s="16">
+        <v>5</v>
+      </c>
+      <c r="E986" s="16">
+        <v>16</v>
+      </c>
+      <c r="F986" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="G986" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="H986" s="16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="987" spans="1:8">
+      <c r="A987" s="16">
+        <v>2025</v>
+      </c>
+      <c r="B987" s="16">
+        <v>21</v>
+      </c>
+      <c r="C987" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="D987" s="16">
+        <v>6</v>
+      </c>
+      <c r="E987" s="16">
+        <v>14</v>
+      </c>
+      <c r="F987" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="G987" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="H987" s="16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="988" spans="1:8">
+      <c r="A988" s="16">
+        <v>2025</v>
+      </c>
+      <c r="B988" s="16">
+        <v>21</v>
+      </c>
+      <c r="C988" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="D988" s="16">
+        <v>7</v>
+      </c>
+      <c r="E988" s="16">
+        <v>44</v>
+      </c>
+      <c r="F988" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="G988" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="H988" s="16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="989" spans="1:8">
+      <c r="A989" s="16">
+        <v>2025</v>
+      </c>
+      <c r="B989" s="16">
+        <v>21</v>
+      </c>
+      <c r="C989" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="D989" s="16">
+        <v>8</v>
+      </c>
+      <c r="E989" s="16">
+        <v>10</v>
+      </c>
+      <c r="F989" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="G989" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="H989" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="990" spans="1:8">
+      <c r="A990" s="16">
+        <v>2025</v>
+      </c>
+      <c r="B990" s="16">
+        <v>21</v>
+      </c>
+      <c r="C990" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="D990" s="16">
+        <v>9</v>
+      </c>
+      <c r="E990" s="16">
+        <v>18</v>
+      </c>
+      <c r="F990" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="G990" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="H990" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="991" spans="1:8">
+      <c r="A991" s="16">
+        <v>2025</v>
+      </c>
+      <c r="B991" s="16">
+        <v>21</v>
+      </c>
+      <c r="C991" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="D991" s="16">
+        <v>10</v>
+      </c>
+      <c r="E991" s="16">
+        <v>6</v>
+      </c>
+      <c r="F991" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="G991" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="H991" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="992" spans="1:8">
+      <c r="A992" s="16">
+        <v>2025</v>
+      </c>
+      <c r="B992" s="16">
+        <v>21</v>
+      </c>
+      <c r="C992" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="D992" s="16">
+        <v>11</v>
+      </c>
+      <c r="E992" s="16">
+        <v>31</v>
+      </c>
+      <c r="F992" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="G992" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="H992" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="993" spans="1:8">
+      <c r="A993" s="16">
+        <v>2025</v>
+      </c>
+      <c r="B993" s="16">
+        <v>21</v>
+      </c>
+      <c r="C993" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="D993" s="16">
+        <v>12</v>
+      </c>
+      <c r="E993" s="16">
+        <v>87</v>
+      </c>
+      <c r="F993" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="G993" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="H993" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="994" spans="1:8">
+      <c r="A994" s="16">
+        <v>2025</v>
+      </c>
+      <c r="B994" s="16">
+        <v>21</v>
+      </c>
+      <c r="C994" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="D994" s="16">
+        <v>13</v>
+      </c>
+      <c r="E994" s="16">
+        <v>22</v>
+      </c>
+      <c r="F994" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="G994" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="H994" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="995" spans="1:8">
+      <c r="A995" s="16">
+        <v>2025</v>
+      </c>
+      <c r="B995" s="16">
+        <v>21</v>
+      </c>
+      <c r="C995" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="D995" s="16">
+        <v>14</v>
+      </c>
+      <c r="E995" s="16">
+        <v>55</v>
+      </c>
+      <c r="F995" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="G995" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="H995" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="996" spans="1:8">
+      <c r="A996" s="16">
+        <v>2025</v>
+      </c>
+      <c r="B996" s="16">
+        <v>21</v>
+      </c>
+      <c r="C996" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="D996" s="16">
+        <v>15</v>
+      </c>
+      <c r="E996" s="16">
+        <v>27</v>
+      </c>
+      <c r="F996" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="G996" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="H996" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="997" spans="1:8">
+      <c r="A997" s="16">
+        <v>2025</v>
+      </c>
+      <c r="B997" s="16">
+        <v>21</v>
+      </c>
+      <c r="C997" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="D997" s="16">
+        <v>16</v>
+      </c>
+      <c r="E997" s="16">
+        <v>30</v>
+      </c>
+      <c r="F997" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="G997" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="H997" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="998" spans="1:8">
+      <c r="A998" s="16">
+        <v>2025</v>
+      </c>
+      <c r="B998" s="16">
+        <v>21</v>
+      </c>
+      <c r="C998" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="D998" s="16">
+        <v>17</v>
+      </c>
+      <c r="E998" s="16">
+        <v>23</v>
+      </c>
+      <c r="F998" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G998" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="H998" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="999" spans="1:8">
+      <c r="A999" s="16">
+        <v>2025</v>
+      </c>
+      <c r="B999" s="16">
+        <v>21</v>
+      </c>
+      <c r="C999" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="D999" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="E999" s="16">
+        <v>5</v>
+      </c>
+      <c r="F999" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="G999" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="H999" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1000" spans="1:8">
+      <c r="A1000" s="16">
+        <v>2025</v>
+      </c>
+      <c r="B1000" s="16">
+        <v>21</v>
+      </c>
+      <c r="C1000" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="D1000" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="E1000" s="16">
+        <v>81</v>
+      </c>
+      <c r="F1000" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="G1000" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="H1000" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1001" spans="1:8">
+      <c r="A1001" s="16">
+        <v>2025</v>
+      </c>
+      <c r="B1001" s="16">
+        <v>21</v>
+      </c>
+      <c r="C1001" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="D1001" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="E1001" s="16">
+        <v>43</v>
+      </c>
+      <c r="F1001" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="G1001" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="H1001" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1002" spans="1:8">
+      <c r="A1002" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B1002" s="15">
+        <v>21</v>
+      </c>
+      <c r="C1002" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1002" s="15">
+        <v>1</v>
+      </c>
+      <c r="E1002" s="15">
+        <v>4</v>
+      </c>
+      <c r="F1002" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="G1002" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="H1002" s="15"/>
+    </row>
+    <row r="1003" spans="1:8">
+      <c r="A1003" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B1003" s="15">
+        <v>21</v>
+      </c>
+      <c r="C1003" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1003" s="15">
+        <v>2</v>
+      </c>
+      <c r="E1003" s="15">
+        <v>12</v>
+      </c>
+      <c r="F1003" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="G1003" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="H1003" s="15"/>
+    </row>
+    <row r="1004" spans="1:8">
+      <c r="A1004" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B1004" s="15">
+        <v>21</v>
+      </c>
+      <c r="C1004" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1004" s="15">
+        <v>3</v>
+      </c>
+      <c r="E1004" s="15">
+        <v>16</v>
+      </c>
+      <c r="F1004" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="G1004" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="H1004" s="15"/>
+    </row>
+    <row r="1005" spans="1:8">
+      <c r="A1005" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B1005" s="15">
+        <v>21</v>
+      </c>
+      <c r="C1005" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1005" s="15">
+        <v>4</v>
+      </c>
+      <c r="E1005" s="15">
+        <v>81</v>
+      </c>
+      <c r="F1005" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="G1005" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="H1005" s="15"/>
+    </row>
+    <row r="1006" spans="1:8">
+      <c r="A1006" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B1006" s="15">
+        <v>21</v>
+      </c>
+      <c r="C1006" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1006" s="15">
+        <v>5</v>
+      </c>
+      <c r="E1006" s="15">
+        <v>6</v>
+      </c>
+      <c r="F1006" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="G1006" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="H1006" s="15"/>
+    </row>
+    <row r="1007" spans="1:8">
+      <c r="A1007" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B1007" s="15">
+        <v>21</v>
+      </c>
+      <c r="C1007" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1007" s="15">
+        <v>6</v>
+      </c>
+      <c r="E1007" s="15">
+        <v>63</v>
+      </c>
+      <c r="F1007" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="G1007" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="H1007" s="15"/>
+    </row>
+    <row r="1008" spans="1:8">
+      <c r="A1008" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B1008" s="15">
+        <v>21</v>
+      </c>
+      <c r="C1008" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1008" s="15">
+        <v>7</v>
+      </c>
+      <c r="E1008" s="15">
+        <v>30</v>
+      </c>
+      <c r="F1008" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="G1008" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="H1008" s="15"/>
+    </row>
+    <row r="1009" spans="1:8">
+      <c r="A1009" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B1009" s="15">
+        <v>21</v>
+      </c>
+      <c r="C1009" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1009" s="15">
+        <v>8</v>
+      </c>
+      <c r="E1009" s="15">
+        <v>87</v>
+      </c>
+      <c r="F1009" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="G1009" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="H1009" s="15"/>
+    </row>
+    <row r="1010" spans="1:8">
+      <c r="A1010" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B1010" s="15">
+        <v>21</v>
+      </c>
+      <c r="C1010" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1010" s="15">
+        <v>9</v>
+      </c>
+      <c r="E1010" s="15">
+        <v>10</v>
+      </c>
+      <c r="F1010" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="G1010" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="H1010" s="15"/>
+    </row>
+    <row r="1011" spans="1:8">
+      <c r="A1011" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B1011" s="15">
+        <v>21</v>
+      </c>
+      <c r="C1011" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1011" s="15">
+        <v>10</v>
+      </c>
+      <c r="E1011" s="15">
+        <v>27</v>
+      </c>
+      <c r="F1011" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="G1011" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="H1011" s="15"/>
+    </row>
+    <row r="1012" spans="1:8">
+      <c r="A1012" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B1012" s="15">
+        <v>21</v>
+      </c>
+      <c r="C1012" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1012" s="15">
+        <v>11</v>
+      </c>
+      <c r="E1012" s="15">
+        <v>14</v>
+      </c>
+      <c r="F1012" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="G1012" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="H1012" s="15"/>
+    </row>
+    <row r="1013" spans="1:8">
+      <c r="A1013" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B1013" s="15">
+        <v>21</v>
+      </c>
+      <c r="C1013" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1013" s="15">
+        <v>12</v>
+      </c>
+      <c r="E1013" s="15">
+        <v>23</v>
+      </c>
+      <c r="F1013" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="G1013" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="H1013" s="15"/>
+    </row>
+    <row r="1014" spans="1:8">
+      <c r="A1014" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B1014" s="15">
+        <v>21</v>
+      </c>
+      <c r="C1014" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1014" s="15">
+        <v>13</v>
+      </c>
+      <c r="E1014" s="15">
+        <v>44</v>
+      </c>
+      <c r="F1014" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="G1014" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="H1014" s="15"/>
+    </row>
+    <row r="1015" spans="1:8">
+      <c r="A1015" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B1015" s="15">
+        <v>21</v>
+      </c>
+      <c r="C1015" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1015" s="15">
+        <v>14</v>
+      </c>
+      <c r="E1015" s="15">
+        <v>18</v>
+      </c>
+      <c r="F1015" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1015" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="H1015" s="15"/>
+    </row>
+    <row r="1016" spans="1:8">
+      <c r="A1016" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B1016" s="15">
+        <v>21</v>
+      </c>
+      <c r="C1016" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1016" s="15">
+        <v>15</v>
+      </c>
+      <c r="E1016" s="15">
+        <v>55</v>
+      </c>
+      <c r="F1016" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="G1016" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="H1016" s="15"/>
+    </row>
+    <row r="1017" spans="1:8">
+      <c r="A1017" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B1017" s="15">
+        <v>21</v>
+      </c>
+      <c r="C1017" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1017" s="15">
+        <v>16</v>
+      </c>
+      <c r="E1017" s="15">
+        <v>1</v>
+      </c>
+      <c r="F1017" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="G1017" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="H1017" s="15"/>
+    </row>
+    <row r="1018" spans="1:8">
+      <c r="A1018" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B1018" s="15">
+        <v>21</v>
+      </c>
+      <c r="C1018" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1018" s="15">
+        <v>17</v>
+      </c>
+      <c r="E1018" s="15">
+        <v>31</v>
+      </c>
+      <c r="F1018" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="G1018" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="H1018" s="15"/>
+    </row>
+    <row r="1019" spans="1:8">
+      <c r="A1019" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B1019" s="15">
+        <v>21</v>
+      </c>
+      <c r="C1019" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1019" s="15">
+        <v>18</v>
+      </c>
+      <c r="E1019" s="15">
+        <v>43</v>
+      </c>
+      <c r="F1019" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="G1019" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="H1019" s="15"/>
+    </row>
+    <row r="1020" spans="1:8">
+      <c r="A1020" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B1020" s="15">
+        <v>21</v>
+      </c>
+      <c r="C1020" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1020" s="15">
+        <v>19</v>
+      </c>
+      <c r="E1020" s="15">
+        <v>22</v>
+      </c>
+      <c r="F1020" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="G1020" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="H1020" s="15"/>
+    </row>
+    <row r="1021" spans="1:8">
+      <c r="A1021" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B1021" s="15">
+        <v>21</v>
+      </c>
+      <c r="C1021" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1021" s="15">
+        <v>20</v>
+      </c>
+      <c r="E1021" s="15"/>
+      <c r="F1021" s="15"/>
+      <c r="G1021" s="15"/>
+      <c r="H1021" s="15"/>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H921" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H961" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/docs/datas/f1.xlsx
+++ b/public/docs/datas/f1.xlsx
@@ -15,7 +15,7 @@
     <sheet name="teams" sheetId="5" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">result!$A$1:$H$961</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">result!$A$1:$H$1021</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3567" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3630" uniqueCount="214">
   <si>
     <t>year</t>
   </si>
@@ -1324,7 +1324,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1359,7 +1359,6 @@
     </xf>
     <xf numFmtId="47" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -2467,13 +2466,13 @@
       <c r="C2" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D2" s="17">
+      <c r="D2" s="16">
         <v>45730</v>
       </c>
-      <c r="E2" s="19">
+      <c r="E2" s="18">
         <v>0.395833333333333</v>
       </c>
-      <c r="F2" s="19">
+      <c r="F2" s="18">
         <v>0.4375</v>
       </c>
       <c r="G2" s="2">
@@ -2490,13 +2489,13 @@
       <c r="C3" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D3" s="17">
+      <c r="D3" s="16">
         <v>45730</v>
       </c>
-      <c r="E3" s="19">
+      <c r="E3" s="18">
         <v>0.541666666666667</v>
       </c>
-      <c r="F3" s="19">
+      <c r="F3" s="18">
         <v>0.583333333333333</v>
       </c>
       <c r="G3" s="2">
@@ -2513,13 +2512,13 @@
       <c r="C4" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D4" s="17">
+      <c r="D4" s="16">
         <v>45731</v>
       </c>
-      <c r="E4" s="19">
+      <c r="E4" s="18">
         <v>0.395833333333333</v>
       </c>
-      <c r="F4" s="19">
+      <c r="F4" s="18">
         <v>0.4375</v>
       </c>
       <c r="G4" s="2">
@@ -2536,13 +2535,13 @@
       <c r="C5" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="16">
         <v>45731</v>
       </c>
-      <c r="E5" s="19">
+      <c r="E5" s="18">
         <v>0.541666666666667</v>
       </c>
-      <c r="F5" s="19">
+      <c r="F5" s="18">
         <v>0.583333333333333</v>
       </c>
       <c r="G5" s="2">
@@ -2559,13 +2558,13 @@
       <c r="C6" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D6" s="17">
+      <c r="D6" s="16">
         <v>45732</v>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="18">
         <v>0.5</v>
       </c>
-      <c r="F6" s="19"/>
+      <c r="F6" s="18"/>
       <c r="G6" s="2">
         <v>1</v>
       </c>
@@ -2580,13 +2579,13 @@
       <c r="C7" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D7" s="18">
+      <c r="D7" s="17">
         <v>45737</v>
       </c>
-      <c r="E7" s="20">
+      <c r="E7" s="19">
         <v>0.479166666666667</v>
       </c>
-      <c r="F7" s="20">
+      <c r="F7" s="19">
         <v>0.520833333333333</v>
       </c>
       <c r="G7" s="6">
@@ -2603,13 +2602,13 @@
       <c r="C8" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="D8" s="18">
+      <c r="D8" s="17">
         <v>45737</v>
       </c>
-      <c r="E8" s="20">
+      <c r="E8" s="19">
         <v>0.645833333333333</v>
       </c>
-      <c r="F8" s="20">
+      <c r="F8" s="19">
         <v>0.676388888888889</v>
       </c>
       <c r="G8" s="6">
@@ -2626,13 +2625,13 @@
       <c r="C9" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="D9" s="18">
+      <c r="D9" s="17">
         <v>45738</v>
       </c>
-      <c r="E9" s="20">
+      <c r="E9" s="19">
         <v>0.458333333333333</v>
       </c>
-      <c r="F9" s="20">
+      <c r="F9" s="19">
         <v>0.5</v>
       </c>
       <c r="G9" s="6">
@@ -2649,13 +2648,13 @@
       <c r="C10" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D10" s="18">
+      <c r="D10" s="17">
         <v>45738</v>
       </c>
-      <c r="E10" s="20">
+      <c r="E10" s="19">
         <v>0.625</v>
       </c>
-      <c r="F10" s="20">
+      <c r="F10" s="19">
         <v>0.666666666666667</v>
       </c>
       <c r="G10" s="6">
@@ -2672,10 +2671,10 @@
       <c r="C11" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D11" s="18">
+      <c r="D11" s="17">
         <v>45739</v>
       </c>
-      <c r="E11" s="20">
+      <c r="E11" s="19">
         <v>0.625</v>
       </c>
       <c r="F11" s="6"/>
@@ -2693,13 +2692,13 @@
       <c r="C12" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D12" s="17">
+      <c r="D12" s="16">
         <v>45751</v>
       </c>
-      <c r="E12" s="19">
+      <c r="E12" s="18">
         <v>0.4375</v>
       </c>
-      <c r="F12" s="19">
+      <c r="F12" s="18">
         <v>0.479166666666667</v>
       </c>
       <c r="G12" s="2">
@@ -2716,13 +2715,13 @@
       <c r="C13" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D13" s="17">
+      <c r="D13" s="16">
         <v>45751</v>
       </c>
-      <c r="E13" s="19">
+      <c r="E13" s="18">
         <v>0.583333333333333</v>
       </c>
-      <c r="F13" s="19">
+      <c r="F13" s="18">
         <v>0.625</v>
       </c>
       <c r="G13" s="2">
@@ -2739,13 +2738,13 @@
       <c r="C14" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D14" s="17">
+      <c r="D14" s="16">
         <v>45752</v>
       </c>
-      <c r="E14" s="19">
+      <c r="E14" s="18">
         <v>0.4375</v>
       </c>
-      <c r="F14" s="19">
+      <c r="F14" s="18">
         <v>0.479166666666667</v>
       </c>
       <c r="G14" s="2">
@@ -2762,13 +2761,13 @@
       <c r="C15" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D15" s="17">
+      <c r="D15" s="16">
         <v>45752</v>
       </c>
-      <c r="E15" s="19">
+      <c r="E15" s="18">
         <v>0.583333333333333</v>
       </c>
-      <c r="F15" s="19">
+      <c r="F15" s="18">
         <v>0.625</v>
       </c>
       <c r="G15" s="2">
@@ -2785,10 +2784,10 @@
       <c r="C16" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D16" s="17">
+      <c r="D16" s="16">
         <v>45753</v>
       </c>
-      <c r="E16" s="19">
+      <c r="E16" s="18">
         <v>0.541666666666667</v>
       </c>
       <c r="F16" s="2"/>
@@ -2806,13 +2805,13 @@
       <c r="C17" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D17" s="18">
+      <c r="D17" s="17">
         <v>45758</v>
       </c>
-      <c r="E17" s="20">
+      <c r="E17" s="19">
         <v>0.8125</v>
       </c>
-      <c r="F17" s="20">
+      <c r="F17" s="19">
         <v>0.854166666666667</v>
       </c>
       <c r="G17" s="6">
@@ -2829,13 +2828,13 @@
       <c r="C18" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="D18" s="18">
+      <c r="D18" s="17">
         <v>45758</v>
       </c>
-      <c r="E18" s="20">
+      <c r="E18" s="19">
         <v>0.958333333333333</v>
       </c>
-      <c r="F18" s="20">
+      <c r="F18" s="19">
         <v>0</v>
       </c>
       <c r="G18" s="6">
@@ -2852,13 +2851,13 @@
       <c r="C19" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D19" s="18">
+      <c r="D19" s="17">
         <v>45759</v>
       </c>
-      <c r="E19" s="20">
+      <c r="E19" s="19">
         <v>0.854166666666667</v>
       </c>
-      <c r="F19" s="20">
+      <c r="F19" s="19">
         <v>0.895833333333333</v>
       </c>
       <c r="G19" s="6">
@@ -2875,13 +2874,13 @@
       <c r="C20" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D20" s="18">
+      <c r="D20" s="17">
         <v>45760</v>
       </c>
-      <c r="E20" s="20">
-        <v>0</v>
-      </c>
-      <c r="F20" s="20">
+      <c r="E20" s="19">
+        <v>0</v>
+      </c>
+      <c r="F20" s="19">
         <v>0.0416666666666667</v>
       </c>
       <c r="G20" s="6">
@@ -2898,10 +2897,10 @@
       <c r="C21" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D21" s="18">
+      <c r="D21" s="17">
         <v>45760</v>
       </c>
-      <c r="E21" s="20">
+      <c r="E21" s="19">
         <v>0.958333333333333</v>
       </c>
       <c r="F21" s="6"/>
@@ -2919,13 +2918,13 @@
       <c r="C22" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D22" s="17">
+      <c r="D22" s="16">
         <v>45765</v>
       </c>
-      <c r="E22" s="19">
+      <c r="E22" s="18">
         <v>0.895833333333333</v>
       </c>
-      <c r="F22" s="19">
+      <c r="F22" s="18">
         <v>0.9375</v>
       </c>
       <c r="G22" s="2">
@@ -2942,13 +2941,13 @@
       <c r="C23" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D23" s="17">
+      <c r="D23" s="16">
         <v>45766</v>
       </c>
-      <c r="E23" s="19">
+      <c r="E23" s="18">
         <v>0.0416666666666667</v>
       </c>
-      <c r="F23" s="19">
+      <c r="F23" s="18">
         <v>0.0833333333333333</v>
       </c>
       <c r="G23" s="2">
@@ -2965,13 +2964,13 @@
       <c r="C24" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D24" s="17">
+      <c r="D24" s="16">
         <v>45766</v>
       </c>
-      <c r="E24" s="19">
+      <c r="E24" s="18">
         <v>0.895833333333333</v>
       </c>
-      <c r="F24" s="19">
+      <c r="F24" s="18">
         <v>0.9375</v>
       </c>
       <c r="G24" s="2">
@@ -2988,13 +2987,13 @@
       <c r="C25" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D25" s="17">
+      <c r="D25" s="16">
         <v>45767</v>
       </c>
-      <c r="E25" s="19">
+      <c r="E25" s="18">
         <v>0.0416666666666667</v>
       </c>
-      <c r="F25" s="19">
+      <c r="F25" s="18">
         <v>0.0833333333333333</v>
       </c>
       <c r="G25" s="2">
@@ -3011,10 +3010,10 @@
       <c r="C26" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D26" s="17">
+      <c r="D26" s="16">
         <v>45767</v>
       </c>
-      <c r="E26" s="19">
+      <c r="E26" s="18">
         <v>0.0416666666666667</v>
       </c>
       <c r="F26" s="2"/>
@@ -3032,13 +3031,13 @@
       <c r="C27" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D27" s="18">
+      <c r="D27" s="17">
         <v>45780</v>
       </c>
-      <c r="E27" s="20">
+      <c r="E27" s="19">
         <v>0.0208333333333333</v>
       </c>
-      <c r="F27" s="20">
+      <c r="F27" s="19">
         <v>0.0625</v>
       </c>
       <c r="G27" s="6">
@@ -3055,13 +3054,13 @@
       <c r="C28" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="D28" s="18">
+      <c r="D28" s="17">
         <v>45780</v>
       </c>
-      <c r="E28" s="20">
+      <c r="E28" s="19">
         <v>0.1875</v>
       </c>
-      <c r="F28" s="20">
+      <c r="F28" s="19">
         <v>0.218055555555556</v>
       </c>
       <c r="G28" s="6">
@@ -3078,13 +3077,13 @@
       <c r="C29" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="D29" s="18">
+      <c r="D29" s="17">
         <v>45781</v>
       </c>
-      <c r="E29" s="20">
-        <v>0</v>
-      </c>
-      <c r="F29" s="20">
+      <c r="E29" s="19">
+        <v>0</v>
+      </c>
+      <c r="F29" s="19">
         <v>0.0416666666666667</v>
       </c>
       <c r="G29" s="6">
@@ -3101,13 +3100,13 @@
       <c r="C30" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D30" s="18">
+      <c r="D30" s="17">
         <v>45781</v>
       </c>
-      <c r="E30" s="20">
+      <c r="E30" s="19">
         <v>0.166666666666667</v>
       </c>
-      <c r="F30" s="20">
+      <c r="F30" s="19">
         <v>0.208333333333333</v>
       </c>
       <c r="G30" s="6">
@@ -3124,13 +3123,13 @@
       <c r="C31" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D31" s="18">
+      <c r="D31" s="17">
         <v>45782</v>
       </c>
-      <c r="E31" s="20">
+      <c r="E31" s="19">
         <v>0.166666666666667</v>
       </c>
-      <c r="F31" s="20"/>
+      <c r="F31" s="19"/>
       <c r="G31" s="6">
         <v>1</v>
       </c>
@@ -3145,13 +3144,13 @@
       <c r="C32" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D32" s="17">
+      <c r="D32" s="16">
         <v>45793</v>
       </c>
-      <c r="E32" s="19">
+      <c r="E32" s="18">
         <v>0.8125</v>
       </c>
-      <c r="F32" s="19">
+      <c r="F32" s="18">
         <v>0.854166666666667</v>
       </c>
       <c r="G32" s="2">
@@ -3168,13 +3167,13 @@
       <c r="C33" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D33" s="17">
+      <c r="D33" s="16">
         <v>45793</v>
       </c>
-      <c r="E33" s="19">
+      <c r="E33" s="18">
         <v>0.958333333333333</v>
       </c>
-      <c r="F33" s="19">
+      <c r="F33" s="18">
         <v>0</v>
       </c>
       <c r="G33" s="2">
@@ -3191,13 +3190,13 @@
       <c r="C34" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D34" s="17">
+      <c r="D34" s="16">
         <v>45794</v>
       </c>
-      <c r="E34" s="19">
+      <c r="E34" s="18">
         <v>0.770833333333333</v>
       </c>
-      <c r="F34" s="19">
+      <c r="F34" s="18">
         <v>0.8125</v>
       </c>
       <c r="G34" s="2">
@@ -3214,13 +3213,13 @@
       <c r="C35" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D35" s="17">
+      <c r="D35" s="16">
         <v>45794</v>
       </c>
-      <c r="E35" s="19">
+      <c r="E35" s="18">
         <v>0.916666666666667</v>
       </c>
-      <c r="F35" s="19">
+      <c r="F35" s="18">
         <v>0.958333333333333</v>
       </c>
       <c r="G35" s="2">
@@ -3237,10 +3236,10 @@
       <c r="C36" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D36" s="17">
+      <c r="D36" s="16">
         <v>45795</v>
       </c>
-      <c r="E36" s="19">
+      <c r="E36" s="18">
         <v>0.875</v>
       </c>
       <c r="F36" s="2"/>
@@ -3258,13 +3257,13 @@
       <c r="C37" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D37" s="18">
+      <c r="D37" s="17">
         <v>45800</v>
       </c>
-      <c r="E37" s="20">
+      <c r="E37" s="19">
         <v>0.8125</v>
       </c>
-      <c r="F37" s="20">
+      <c r="F37" s="19">
         <v>0.854166666666667</v>
       </c>
       <c r="G37" s="6">
@@ -3281,13 +3280,13 @@
       <c r="C38" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="D38" s="18">
+      <c r="D38" s="17">
         <v>45800</v>
       </c>
-      <c r="E38" s="20">
+      <c r="E38" s="19">
         <v>0.958333333333333</v>
       </c>
-      <c r="F38" s="20">
+      <c r="F38" s="19">
         <v>0</v>
       </c>
       <c r="G38" s="6">
@@ -3304,13 +3303,13 @@
       <c r="C39" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D39" s="18">
+      <c r="D39" s="17">
         <v>45801</v>
       </c>
-      <c r="E39" s="20">
+      <c r="E39" s="19">
         <v>0.770833333333333</v>
       </c>
-      <c r="F39" s="20">
+      <c r="F39" s="19">
         <v>0.8125</v>
       </c>
       <c r="G39" s="6">
@@ -3327,13 +3326,13 @@
       <c r="C40" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D40" s="18">
+      <c r="D40" s="17">
         <v>45801</v>
       </c>
-      <c r="E40" s="20">
+      <c r="E40" s="19">
         <v>0.916666666666667</v>
       </c>
-      <c r="F40" s="20">
+      <c r="F40" s="19">
         <v>0.958333333333333</v>
       </c>
       <c r="G40" s="6">
@@ -3350,10 +3349,10 @@
       <c r="C41" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D41" s="18">
+      <c r="D41" s="17">
         <v>45802</v>
       </c>
-      <c r="E41" s="20">
+      <c r="E41" s="19">
         <v>0.875</v>
       </c>
       <c r="F41" s="6"/>
@@ -3371,13 +3370,13 @@
       <c r="C42" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D42" s="17">
+      <c r="D42" s="16">
         <v>45807</v>
       </c>
-      <c r="E42" s="19">
+      <c r="E42" s="18">
         <v>0.8125</v>
       </c>
-      <c r="F42" s="19">
+      <c r="F42" s="18">
         <v>0.854166666666667</v>
       </c>
       <c r="G42" s="2">
@@ -3394,13 +3393,13 @@
       <c r="C43" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D43" s="17">
+      <c r="D43" s="16">
         <v>45807</v>
       </c>
-      <c r="E43" s="19">
+      <c r="E43" s="18">
         <v>0.958333333333333</v>
       </c>
-      <c r="F43" s="19">
+      <c r="F43" s="18">
         <v>0</v>
       </c>
       <c r="G43" s="2">
@@ -3417,13 +3416,13 @@
       <c r="C44" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D44" s="17">
+      <c r="D44" s="16">
         <v>45808</v>
       </c>
-      <c r="E44" s="19">
+      <c r="E44" s="18">
         <v>0.770833333333333</v>
       </c>
-      <c r="F44" s="19">
+      <c r="F44" s="18">
         <v>0.8125</v>
       </c>
       <c r="G44" s="2">
@@ -3440,13 +3439,13 @@
       <c r="C45" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D45" s="17">
+      <c r="D45" s="16">
         <v>45808</v>
       </c>
-      <c r="E45" s="19">
+      <c r="E45" s="18">
         <v>0.916666666666667</v>
       </c>
-      <c r="F45" s="19">
+      <c r="F45" s="18">
         <v>0.958333333333333</v>
       </c>
       <c r="G45" s="2">
@@ -3463,10 +3462,10 @@
       <c r="C46" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D46" s="17">
+      <c r="D46" s="16">
         <v>45809</v>
       </c>
-      <c r="E46" s="19">
+      <c r="E46" s="18">
         <v>0.875</v>
       </c>
       <c r="F46" s="2"/>
@@ -3484,13 +3483,13 @@
       <c r="C47" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D47" s="18">
+      <c r="D47" s="17">
         <v>45822</v>
       </c>
-      <c r="E47" s="20">
+      <c r="E47" s="19">
         <v>0.0625</v>
       </c>
-      <c r="F47" s="20">
+      <c r="F47" s="19">
         <v>0.104166666666667</v>
       </c>
       <c r="G47" s="6">
@@ -3507,13 +3506,13 @@
       <c r="C48" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="D48" s="18">
+      <c r="D48" s="17">
         <v>45822</v>
       </c>
-      <c r="E48" s="20">
+      <c r="E48" s="19">
         <v>0.208333333333333</v>
       </c>
-      <c r="F48" s="20">
+      <c r="F48" s="19">
         <v>0.25</v>
       </c>
       <c r="G48" s="6">
@@ -3530,13 +3529,13 @@
       <c r="C49" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D49" s="18">
+      <c r="D49" s="17">
         <v>45823</v>
       </c>
-      <c r="E49" s="20">
+      <c r="E49" s="19">
         <v>0.0208333333333333</v>
       </c>
-      <c r="F49" s="20">
+      <c r="F49" s="19">
         <v>0.0625</v>
       </c>
       <c r="G49" s="6">
@@ -3553,13 +3552,13 @@
       <c r="C50" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D50" s="18">
+      <c r="D50" s="17">
         <v>45823</v>
       </c>
-      <c r="E50" s="20">
+      <c r="E50" s="19">
         <v>0.166666666666667</v>
       </c>
-      <c r="F50" s="20">
+      <c r="F50" s="19">
         <v>0.208333333333333</v>
       </c>
       <c r="G50" s="6">
@@ -3576,10 +3575,10 @@
       <c r="C51" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D51" s="18">
+      <c r="D51" s="17">
         <v>45824</v>
       </c>
-      <c r="E51" s="20">
+      <c r="E51" s="19">
         <v>0.0833333333333333</v>
       </c>
       <c r="F51" s="6"/>
@@ -3597,13 +3596,13 @@
       <c r="C52" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D52" s="17">
+      <c r="D52" s="16">
         <v>45835</v>
       </c>
-      <c r="E52" s="19">
+      <c r="E52" s="18">
         <v>0.8125</v>
       </c>
-      <c r="F52" s="19">
+      <c r="F52" s="18">
         <v>0.854166666666667</v>
       </c>
       <c r="G52" s="2">
@@ -3620,13 +3619,13 @@
       <c r="C53" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D53" s="17">
+      <c r="D53" s="16">
         <v>45835</v>
       </c>
-      <c r="E53" s="19">
+      <c r="E53" s="18">
         <v>0.958333333333333</v>
       </c>
-      <c r="F53" s="19">
+      <c r="F53" s="18">
         <v>0</v>
       </c>
       <c r="G53" s="2">
@@ -3643,13 +3642,13 @@
       <c r="C54" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D54" s="17">
+      <c r="D54" s="16">
         <v>45836</v>
       </c>
-      <c r="E54" s="19">
+      <c r="E54" s="18">
         <v>0.770833333333333</v>
       </c>
-      <c r="F54" s="19">
+      <c r="F54" s="18">
         <v>0.8125</v>
       </c>
       <c r="G54" s="2">
@@ -3666,13 +3665,13 @@
       <c r="C55" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D55" s="17">
+      <c r="D55" s="16">
         <v>45836</v>
       </c>
-      <c r="E55" s="19">
+      <c r="E55" s="18">
         <v>0.916666666666667</v>
       </c>
-      <c r="F55" s="19">
+      <c r="F55" s="18">
         <v>0.958333333333333</v>
       </c>
       <c r="G55" s="2">
@@ -3689,10 +3688,10 @@
       <c r="C56" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D56" s="17">
+      <c r="D56" s="16">
         <v>45837</v>
       </c>
-      <c r="E56" s="19">
+      <c r="E56" s="18">
         <v>0.875</v>
       </c>
       <c r="F56" s="2"/>
@@ -3710,13 +3709,13 @@
       <c r="C57" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D57" s="18">
+      <c r="D57" s="17">
         <v>45842</v>
       </c>
-      <c r="E57" s="20">
+      <c r="E57" s="19">
         <v>0.8125</v>
       </c>
-      <c r="F57" s="20">
+      <c r="F57" s="19">
         <v>0.854166666666667</v>
       </c>
       <c r="G57" s="6">
@@ -3733,13 +3732,13 @@
       <c r="C58" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="D58" s="18">
+      <c r="D58" s="17">
         <v>45842</v>
       </c>
-      <c r="E58" s="20">
+      <c r="E58" s="19">
         <v>0.958333333333333</v>
       </c>
-      <c r="F58" s="20">
+      <c r="F58" s="19">
         <v>0</v>
       </c>
       <c r="G58" s="6">
@@ -3756,13 +3755,13 @@
       <c r="C59" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D59" s="18">
+      <c r="D59" s="17">
         <v>45843</v>
       </c>
-      <c r="E59" s="20">
+      <c r="E59" s="19">
         <v>0.770833333333333</v>
       </c>
-      <c r="F59" s="20">
+      <c r="F59" s="19">
         <v>0.8125</v>
       </c>
       <c r="G59" s="6">
@@ -3779,13 +3778,13 @@
       <c r="C60" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D60" s="18">
+      <c r="D60" s="17">
         <v>45843</v>
       </c>
-      <c r="E60" s="20">
+      <c r="E60" s="19">
         <v>0.916666666666667</v>
       </c>
-      <c r="F60" s="20">
+      <c r="F60" s="19">
         <v>0.958333333333333</v>
       </c>
       <c r="G60" s="6">
@@ -3802,10 +3801,10 @@
       <c r="C61" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D61" s="18">
+      <c r="D61" s="17">
         <v>45844</v>
       </c>
-      <c r="E61" s="20">
+      <c r="E61" s="19">
         <v>0.916666666666667</v>
       </c>
       <c r="F61" s="6"/>
@@ -3823,13 +3822,13 @@
       <c r="C62" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D62" s="17">
+      <c r="D62" s="16">
         <v>45863</v>
       </c>
-      <c r="E62" s="19">
+      <c r="E62" s="18">
         <v>0.8125</v>
       </c>
-      <c r="F62" s="19">
+      <c r="F62" s="18">
         <v>0.854166666666667</v>
       </c>
       <c r="G62" s="2">
@@ -3846,13 +3845,13 @@
       <c r="C63" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D63" s="17">
+      <c r="D63" s="16">
         <v>45863</v>
       </c>
-      <c r="E63" s="19">
+      <c r="E63" s="18">
         <v>0.9375</v>
       </c>
-      <c r="F63" s="19">
+      <c r="F63" s="18">
         <v>0.968055555555556</v>
       </c>
       <c r="G63" s="2">
@@ -3869,13 +3868,13 @@
       <c r="C64" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D64" s="17">
+      <c r="D64" s="16">
         <v>45864</v>
       </c>
-      <c r="E64" s="19">
+      <c r="E64" s="18">
         <v>0.75</v>
       </c>
-      <c r="F64" s="19">
+      <c r="F64" s="18">
         <v>0.791666666666667</v>
       </c>
       <c r="G64" s="2">
@@ -3892,13 +3891,13 @@
       <c r="C65" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D65" s="17">
+      <c r="D65" s="16">
         <v>45864</v>
       </c>
-      <c r="E65" s="19">
+      <c r="E65" s="18">
         <v>0.916666666666667</v>
       </c>
-      <c r="F65" s="19">
+      <c r="F65" s="18">
         <v>0.958333333333333</v>
       </c>
       <c r="G65" s="2">
@@ -3915,10 +3914,10 @@
       <c r="C66" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D66" s="17">
+      <c r="D66" s="16">
         <v>45865</v>
       </c>
-      <c r="E66" s="19">
+      <c r="E66" s="18">
         <v>0.875</v>
       </c>
       <c r="F66" s="2"/>
@@ -3936,13 +3935,13 @@
       <c r="C67" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D67" s="18">
+      <c r="D67" s="17">
         <v>45870</v>
       </c>
-      <c r="E67" s="20">
+      <c r="E67" s="19">
         <v>0.8125</v>
       </c>
-      <c r="F67" s="20">
+      <c r="F67" s="19">
         <v>0.854166666666667</v>
       </c>
       <c r="G67" s="6">
@@ -3959,13 +3958,13 @@
       <c r="C68" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="D68" s="18">
+      <c r="D68" s="17">
         <v>45870</v>
       </c>
-      <c r="E68" s="20">
+      <c r="E68" s="19">
         <v>0.958333333333333</v>
       </c>
-      <c r="F68" s="20">
+      <c r="F68" s="19">
         <v>0</v>
       </c>
       <c r="G68" s="6">
@@ -3982,13 +3981,13 @@
       <c r="C69" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D69" s="18">
+      <c r="D69" s="17">
         <v>45871</v>
       </c>
-      <c r="E69" s="20">
+      <c r="E69" s="19">
         <v>0.770833333333333</v>
       </c>
-      <c r="F69" s="20">
+      <c r="F69" s="19">
         <v>0.8125</v>
       </c>
       <c r="G69" s="6">
@@ -4005,13 +4004,13 @@
       <c r="C70" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D70" s="18">
+      <c r="D70" s="17">
         <v>45871</v>
       </c>
-      <c r="E70" s="20">
+      <c r="E70" s="19">
         <v>0.916666666666667</v>
       </c>
-      <c r="F70" s="20">
+      <c r="F70" s="19">
         <v>0.958333333333333</v>
       </c>
       <c r="G70" s="6">
@@ -4028,10 +4027,10 @@
       <c r="C71" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D71" s="18">
+      <c r="D71" s="17">
         <v>45872</v>
       </c>
-      <c r="E71" s="20">
+      <c r="E71" s="19">
         <v>0.875</v>
       </c>
       <c r="F71" s="6"/>
@@ -4049,13 +4048,13 @@
       <c r="C72" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D72" s="17">
+      <c r="D72" s="16">
         <v>45898</v>
       </c>
-      <c r="E72" s="19">
+      <c r="E72" s="18">
         <v>0.770833333333333</v>
       </c>
-      <c r="F72" s="19">
+      <c r="F72" s="18">
         <v>0.8125</v>
       </c>
       <c r="G72" s="2">
@@ -4072,13 +4071,13 @@
       <c r="C73" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D73" s="17">
+      <c r="D73" s="16">
         <v>45898</v>
       </c>
-      <c r="E73" s="19">
+      <c r="E73" s="18">
         <v>0.916666666666667</v>
       </c>
-      <c r="F73" s="19">
+      <c r="F73" s="18">
         <v>0.958333333333333</v>
       </c>
       <c r="G73" s="2">
@@ -4095,13 +4094,13 @@
       <c r="C74" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D74" s="17">
+      <c r="D74" s="16">
         <v>45899</v>
       </c>
-      <c r="E74" s="19">
+      <c r="E74" s="18">
         <v>0.729166666666667</v>
       </c>
-      <c r="F74" s="19">
+      <c r="F74" s="18">
         <v>0.770833333333333</v>
       </c>
       <c r="G74" s="2">
@@ -4118,13 +4117,13 @@
       <c r="C75" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D75" s="17">
+      <c r="D75" s="16">
         <v>45899</v>
       </c>
-      <c r="E75" s="19">
+      <c r="E75" s="18">
         <v>0.875</v>
       </c>
-      <c r="F75" s="19">
+      <c r="F75" s="18">
         <v>0.916666666666667</v>
       </c>
       <c r="G75" s="2">
@@ -4141,13 +4140,13 @@
       <c r="C76" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D76" s="17">
+      <c r="D76" s="16">
         <v>45900</v>
       </c>
-      <c r="E76" s="19">
+      <c r="E76" s="18">
         <v>0.875</v>
       </c>
-      <c r="F76" s="19"/>
+      <c r="F76" s="18"/>
       <c r="G76" s="2">
         <v>1</v>
       </c>
@@ -4162,13 +4161,13 @@
       <c r="C77" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D77" s="18">
+      <c r="D77" s="17">
         <v>45905</v>
       </c>
-      <c r="E77" s="20">
+      <c r="E77" s="19">
         <v>0.8125</v>
       </c>
-      <c r="F77" s="20">
+      <c r="F77" s="19">
         <v>0.854166666666667</v>
       </c>
       <c r="G77" s="6">
@@ -4185,13 +4184,13 @@
       <c r="C78" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="D78" s="18">
+      <c r="D78" s="17">
         <v>45905</v>
       </c>
-      <c r="E78" s="20">
+      <c r="E78" s="19">
         <v>0.958333333333333</v>
       </c>
-      <c r="F78" s="20">
+      <c r="F78" s="19">
         <v>0</v>
       </c>
       <c r="G78" s="6">
@@ -4208,13 +4207,13 @@
       <c r="C79" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D79" s="18">
+      <c r="D79" s="17">
         <v>45906</v>
       </c>
-      <c r="E79" s="20">
+      <c r="E79" s="19">
         <v>0.770833333333333</v>
       </c>
-      <c r="F79" s="20">
+      <c r="F79" s="19">
         <v>0.8125</v>
       </c>
       <c r="G79" s="6">
@@ -4231,13 +4230,13 @@
       <c r="C80" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D80" s="18">
+      <c r="D80" s="17">
         <v>45906</v>
       </c>
-      <c r="E80" s="20">
+      <c r="E80" s="19">
         <v>0.916666666666667</v>
       </c>
-      <c r="F80" s="20">
+      <c r="F80" s="19">
         <v>0.958333333333333</v>
       </c>
       <c r="G80" s="6">
@@ -4254,10 +4253,10 @@
       <c r="C81" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D81" s="18">
+      <c r="D81" s="17">
         <v>45907</v>
       </c>
-      <c r="E81" s="20">
+      <c r="E81" s="19">
         <v>0.875</v>
       </c>
       <c r="F81" s="6"/>
@@ -4275,13 +4274,13 @@
       <c r="C82" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D82" s="17">
+      <c r="D82" s="16">
         <v>45919</v>
       </c>
-      <c r="E82" s="19">
+      <c r="E82" s="18">
         <v>0.6875</v>
       </c>
-      <c r="F82" s="19">
+      <c r="F82" s="18">
         <v>0.729166666666667</v>
       </c>
       <c r="G82" s="2">
@@ -4298,13 +4297,13 @@
       <c r="C83" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D83" s="17">
+      <c r="D83" s="16">
         <v>45919</v>
       </c>
-      <c r="E83" s="19">
+      <c r="E83" s="18">
         <v>0.833333333333333</v>
       </c>
-      <c r="F83" s="19">
+      <c r="F83" s="18">
         <v>0.875</v>
       </c>
       <c r="G83" s="2">
@@ -4321,13 +4320,13 @@
       <c r="C84" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D84" s="17">
+      <c r="D84" s="16">
         <v>45920</v>
       </c>
-      <c r="E84" s="19">
+      <c r="E84" s="18">
         <v>0.6875</v>
       </c>
-      <c r="F84" s="19">
+      <c r="F84" s="18">
         <v>0.729166666666667</v>
       </c>
       <c r="G84" s="2">
@@ -4344,13 +4343,13 @@
       <c r="C85" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D85" s="17">
+      <c r="D85" s="16">
         <v>45920</v>
       </c>
-      <c r="E85" s="19">
+      <c r="E85" s="18">
         <v>0.833333333333333</v>
       </c>
-      <c r="F85" s="19">
+      <c r="F85" s="18">
         <v>0.875</v>
       </c>
       <c r="G85" s="2">
@@ -4367,10 +4366,10 @@
       <c r="C86" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D86" s="17">
+      <c r="D86" s="16">
         <v>45921</v>
       </c>
-      <c r="E86" s="19">
+      <c r="E86" s="18">
         <v>0.791666666666667</v>
       </c>
       <c r="F86" s="2"/>
@@ -4388,13 +4387,13 @@
       <c r="C87" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D87" s="18">
+      <c r="D87" s="17">
         <v>45933</v>
       </c>
-      <c r="E87" s="20">
+      <c r="E87" s="19">
         <v>0.729166666666667</v>
       </c>
-      <c r="F87" s="20">
+      <c r="F87" s="19">
         <v>0.770833333333333</v>
       </c>
       <c r="G87" s="6">
@@ -4411,13 +4410,13 @@
       <c r="C88" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="D88" s="18">
+      <c r="D88" s="17">
         <v>45933</v>
       </c>
-      <c r="E88" s="20">
+      <c r="E88" s="19">
         <v>0.875</v>
       </c>
-      <c r="F88" s="20">
+      <c r="F88" s="19">
         <v>0.916666666666667</v>
       </c>
       <c r="G88" s="6">
@@ -4434,13 +4433,13 @@
       <c r="C89" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D89" s="18">
+      <c r="D89" s="17">
         <v>45934</v>
       </c>
-      <c r="E89" s="20">
+      <c r="E89" s="19">
         <v>0.729166666666667</v>
       </c>
-      <c r="F89" s="20">
+      <c r="F89" s="19">
         <v>0.770833333333333</v>
       </c>
       <c r="G89" s="6">
@@ -4457,13 +4456,13 @@
       <c r="C90" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D90" s="18">
+      <c r="D90" s="17">
         <v>45934</v>
       </c>
-      <c r="E90" s="20">
+      <c r="E90" s="19">
         <v>0.875</v>
       </c>
-      <c r="F90" s="20">
+      <c r="F90" s="19">
         <v>0.916666666666667</v>
       </c>
       <c r="G90" s="6">
@@ -4480,10 +4479,10 @@
       <c r="C91" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D91" s="18">
+      <c r="D91" s="17">
         <v>45935</v>
       </c>
-      <c r="E91" s="20">
+      <c r="E91" s="19">
         <v>0.833333333333333</v>
       </c>
       <c r="F91" s="6"/>
@@ -4501,13 +4500,13 @@
       <c r="C92" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D92" s="17">
+      <c r="D92" s="16">
         <v>45948</v>
       </c>
-      <c r="E92" s="19">
+      <c r="E92" s="18">
         <v>0.0625</v>
       </c>
-      <c r="F92" s="19">
+      <c r="F92" s="18">
         <v>0.104166666666667</v>
       </c>
       <c r="G92" s="2">
@@ -4524,13 +4523,13 @@
       <c r="C93" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D93" s="17">
+      <c r="D93" s="16">
         <v>45948</v>
       </c>
-      <c r="E93" s="19">
+      <c r="E93" s="18">
         <v>0.229166666666667</v>
       </c>
-      <c r="F93" s="19">
+      <c r="F93" s="18">
         <v>0.259722222222222</v>
       </c>
       <c r="G93" s="2">
@@ -4547,13 +4546,13 @@
       <c r="C94" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D94" s="17">
+      <c r="D94" s="16">
         <v>45949</v>
       </c>
-      <c r="E94" s="19">
+      <c r="E94" s="18">
         <v>0.0416666666666667</v>
       </c>
-      <c r="F94" s="19">
+      <c r="F94" s="18">
         <v>0.0625</v>
       </c>
       <c r="G94" s="2">
@@ -4570,13 +4569,13 @@
       <c r="C95" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D95" s="17">
+      <c r="D95" s="16">
         <v>45949</v>
       </c>
-      <c r="E95" s="19">
+      <c r="E95" s="18">
         <v>0.208333333333333</v>
       </c>
-      <c r="F95" s="19">
+      <c r="F95" s="18">
         <v>0.25</v>
       </c>
       <c r="G95" s="2">
@@ -4593,10 +4592,10 @@
       <c r="C96" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D96" s="17">
+      <c r="D96" s="16">
         <v>45950</v>
       </c>
-      <c r="E96" s="19">
+      <c r="E96" s="18">
         <v>0.125</v>
       </c>
       <c r="F96" s="2"/>
@@ -4614,13 +4613,13 @@
       <c r="C97" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D97" s="18">
+      <c r="D97" s="17">
         <v>45955</v>
       </c>
-      <c r="E97" s="20">
+      <c r="E97" s="19">
         <v>0.104166666666667</v>
       </c>
-      <c r="F97" s="20">
+      <c r="F97" s="19">
         <v>0.145833333333333</v>
       </c>
       <c r="G97" s="6">
@@ -4637,13 +4636,13 @@
       <c r="C98" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="D98" s="18">
+      <c r="D98" s="17">
         <v>45955</v>
       </c>
-      <c r="E98" s="20">
+      <c r="E98" s="19">
         <v>0.25</v>
       </c>
-      <c r="F98" s="20">
+      <c r="F98" s="19">
         <v>0.291666666666667</v>
       </c>
       <c r="G98" s="6">
@@ -4660,13 +4659,13 @@
       <c r="C99" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D99" s="18">
+      <c r="D99" s="17">
         <v>45956</v>
       </c>
-      <c r="E99" s="20">
+      <c r="E99" s="19">
         <v>0.0625</v>
       </c>
-      <c r="F99" s="20">
+      <c r="F99" s="19">
         <v>0.104166666666667</v>
       </c>
       <c r="G99" s="6">
@@ -4683,13 +4682,13 @@
       <c r="C100" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D100" s="18">
+      <c r="D100" s="17">
         <v>45956</v>
       </c>
-      <c r="E100" s="20">
+      <c r="E100" s="19">
         <v>0.208333333333333</v>
       </c>
-      <c r="F100" s="20">
+      <c r="F100" s="19">
         <v>0.25</v>
       </c>
       <c r="G100" s="6">
@@ -4706,10 +4705,10 @@
       <c r="C101" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D101" s="18">
+      <c r="D101" s="17">
         <v>45957</v>
       </c>
-      <c r="E101" s="20">
+      <c r="E101" s="19">
         <v>0.166666666666667</v>
       </c>
       <c r="F101" s="6"/>
@@ -4727,13 +4726,13 @@
       <c r="C102" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D102" s="17">
+      <c r="D102" s="16">
         <v>45968</v>
       </c>
-      <c r="E102" s="19">
+      <c r="E102" s="18">
         <v>0.9375</v>
       </c>
-      <c r="F102" s="19">
+      <c r="F102" s="18">
         <v>0.979166666666667</v>
       </c>
       <c r="G102" s="2">
@@ -4750,13 +4749,13 @@
       <c r="C103" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D103" s="17">
+      <c r="D103" s="16">
         <v>45969</v>
       </c>
-      <c r="E103" s="19">
+      <c r="E103" s="18">
         <v>0.104166666666667</v>
       </c>
-      <c r="F103" s="19">
+      <c r="F103" s="18">
         <v>0.134722222222222</v>
       </c>
       <c r="G103" s="2">
@@ -4773,13 +4772,13 @@
       <c r="C104" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D104" s="17">
+      <c r="D104" s="16">
         <v>45969</v>
       </c>
-      <c r="E104" s="19">
+      <c r="E104" s="18">
         <v>0.916666666666667</v>
       </c>
-      <c r="F104" s="19">
+      <c r="F104" s="18">
         <v>0.958333333333333</v>
       </c>
       <c r="G104" s="2">
@@ -4796,13 +4795,13 @@
       <c r="C105" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D105" s="17">
+      <c r="D105" s="16">
         <v>45970</v>
       </c>
-      <c r="E105" s="19">
+      <c r="E105" s="18">
         <v>0.0833333333333333</v>
       </c>
-      <c r="F105" s="19">
+      <c r="F105" s="18">
         <v>0.125</v>
       </c>
       <c r="G105" s="2">
@@ -4819,10 +4818,10 @@
       <c r="C106" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D106" s="17">
+      <c r="D106" s="16">
         <v>45971</v>
       </c>
-      <c r="E106" s="19">
+      <c r="E106" s="18">
         <v>0.0416666666666667</v>
       </c>
       <c r="F106" s="2"/>
@@ -4840,13 +4839,13 @@
       <c r="C107" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D107" s="18">
+      <c r="D107" s="17">
         <v>45982</v>
       </c>
-      <c r="E107" s="20">
+      <c r="E107" s="19">
         <v>0.354166666666667</v>
       </c>
-      <c r="F107" s="20">
+      <c r="F107" s="19">
         <v>0.395833333333333</v>
       </c>
       <c r="G107" s="6">
@@ -4863,13 +4862,13 @@
       <c r="C108" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="D108" s="18">
+      <c r="D108" s="17">
         <v>45982</v>
       </c>
-      <c r="E108" s="20">
+      <c r="E108" s="19">
         <v>0.5</v>
       </c>
-      <c r="F108" s="20">
+      <c r="F108" s="19">
         <v>0.541666666666667</v>
       </c>
       <c r="G108" s="6">
@@ -4886,13 +4885,13 @@
       <c r="C109" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D109" s="18">
+      <c r="D109" s="17">
         <v>45983</v>
       </c>
-      <c r="E109" s="21">
+      <c r="E109" s="20">
         <v>0.354166666666667</v>
       </c>
-      <c r="F109" s="21">
+      <c r="F109" s="20">
         <v>0.395833333333333</v>
       </c>
       <c r="G109" s="6">
@@ -4909,13 +4908,13 @@
       <c r="C110" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D110" s="18">
+      <c r="D110" s="17">
         <v>45983</v>
       </c>
-      <c r="E110" s="21">
+      <c r="E110" s="20">
         <v>0.5</v>
       </c>
-      <c r="F110" s="21">
+      <c r="F110" s="20">
         <v>0.541666666666667</v>
       </c>
       <c r="G110" s="6">
@@ -4932,10 +4931,10 @@
       <c r="C111" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D111" s="18">
+      <c r="D111" s="17">
         <v>45984</v>
       </c>
-      <c r="E111" s="21">
+      <c r="E111" s="20">
         <v>0.5</v>
       </c>
       <c r="F111" s="6"/>
@@ -4953,13 +4952,13 @@
       <c r="C112" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D112" s="17">
+      <c r="D112" s="16">
         <v>45989</v>
       </c>
-      <c r="E112" s="22">
+      <c r="E112" s="21">
         <v>0.895833333333333</v>
       </c>
-      <c r="F112" s="22">
+      <c r="F112" s="21">
         <v>0.9375</v>
       </c>
       <c r="G112" s="2">
@@ -4976,13 +4975,13 @@
       <c r="C113" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D113" s="17">
+      <c r="D113" s="16">
         <v>45990</v>
       </c>
-      <c r="E113" s="22">
+      <c r="E113" s="21">
         <v>0.0625</v>
       </c>
-      <c r="F113" s="22">
+      <c r="F113" s="21">
         <v>0.0930555555555556</v>
       </c>
       <c r="G113" s="2">
@@ -4999,13 +4998,13 @@
       <c r="C114" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D114" s="17">
+      <c r="D114" s="16">
         <v>45990</v>
       </c>
-      <c r="E114" s="22">
+      <c r="E114" s="21">
         <v>0.916666666666667</v>
       </c>
-      <c r="F114" s="22">
+      <c r="F114" s="21">
         <v>0.958333333333333</v>
       </c>
       <c r="G114" s="2">
@@ -5022,13 +5021,13 @@
       <c r="C115" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D115" s="17">
+      <c r="D115" s="16">
         <v>45991</v>
       </c>
-      <c r="E115" s="22">
+      <c r="E115" s="21">
         <v>0.0833333333333333</v>
       </c>
-      <c r="F115" s="22">
+      <c r="F115" s="21">
         <v>0.125</v>
       </c>
       <c r="G115" s="2">
@@ -5045,10 +5044,10 @@
       <c r="C116" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D116" s="17">
+      <c r="D116" s="16">
         <v>45992</v>
       </c>
-      <c r="E116" s="22">
+      <c r="E116" s="21">
         <v>0</v>
       </c>
       <c r="F116" s="2"/>
@@ -5066,13 +5065,13 @@
       <c r="C117" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D117" s="18">
+      <c r="D117" s="17">
         <v>45996</v>
       </c>
-      <c r="E117" s="21">
+      <c r="E117" s="20">
         <v>0.729166666666667</v>
       </c>
-      <c r="F117" s="21">
+      <c r="F117" s="20">
         <v>0.770833333333333</v>
       </c>
       <c r="G117" s="6">
@@ -5089,13 +5088,13 @@
       <c r="C118" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="D118" s="18">
+      <c r="D118" s="17">
         <v>45996</v>
       </c>
-      <c r="E118" s="21">
+      <c r="E118" s="20">
         <v>0.875</v>
       </c>
-      <c r="F118" s="21">
+      <c r="F118" s="20">
         <v>0.916666666666667</v>
       </c>
       <c r="G118" s="6">
@@ -5112,13 +5111,13 @@
       <c r="C119" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D119" s="18">
+      <c r="D119" s="17">
         <v>45997</v>
       </c>
-      <c r="E119" s="21">
+      <c r="E119" s="20">
         <v>0.770833333333333</v>
       </c>
-      <c r="F119" s="21">
+      <c r="F119" s="20">
         <v>0.8125</v>
       </c>
       <c r="G119" s="6">
@@ -5135,13 +5134,13 @@
       <c r="C120" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D120" s="18">
+      <c r="D120" s="17">
         <v>45997</v>
       </c>
-      <c r="E120" s="21">
+      <c r="E120" s="20">
         <v>0.916666666666667</v>
       </c>
-      <c r="F120" s="21">
+      <c r="F120" s="20">
         <v>0.958333333333333</v>
       </c>
       <c r="G120" s="6">
@@ -5158,10 +5157,10 @@
       <c r="C121" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D121" s="18">
+      <c r="D121" s="17">
         <v>45998</v>
       </c>
-      <c r="E121" s="21">
+      <c r="E121" s="20">
         <v>0.875</v>
       </c>
       <c r="F121" s="6"/>
@@ -5178,7 +5177,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R1021"/>
+  <dimension ref="A1:R1041"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -30894,1481 +30893,2001 @@
       </c>
     </row>
     <row r="962" spans="1:8">
-      <c r="A962" s="15">
-        <v>2025</v>
-      </c>
-      <c r="B962" s="15">
+      <c r="A962" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B962" s="2">
         <v>21</v>
       </c>
-      <c r="C962" s="15" t="s">
+      <c r="C962" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D962" s="15">
+      <c r="D962" s="2">
         <v>1</v>
       </c>
-      <c r="E962" s="15">
+      <c r="E962" s="2">
         <v>4</v>
       </c>
-      <c r="F962" s="15" t="s">
+      <c r="F962" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="G962" s="15" t="s">
+      <c r="G962" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="H962" s="15"/>
+      <c r="H962" s="2"/>
     </row>
     <row r="963" spans="1:8">
-      <c r="A963" s="15">
-        <v>2025</v>
-      </c>
-      <c r="B963" s="15">
+      <c r="A963" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B963" s="2">
         <v>21</v>
       </c>
-      <c r="C963" s="15" t="s">
+      <c r="C963" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D963" s="15">
+      <c r="D963" s="2">
         <v>2</v>
       </c>
-      <c r="E963" s="15">
+      <c r="E963" s="2">
         <v>12</v>
       </c>
-      <c r="F963" s="15" t="s">
+      <c r="F963" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="G963" s="15" t="s">
+      <c r="G963" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="H963" s="15"/>
+      <c r="H963" s="2"/>
     </row>
     <row r="964" spans="1:8">
-      <c r="A964" s="15">
-        <v>2025</v>
-      </c>
-      <c r="B964" s="15">
+      <c r="A964" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B964" s="2">
         <v>21</v>
       </c>
-      <c r="C964" s="15" t="s">
+      <c r="C964" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D964" s="15">
+      <c r="D964" s="2">
         <v>3</v>
       </c>
-      <c r="E964" s="15">
+      <c r="E964" s="2">
         <v>81</v>
       </c>
-      <c r="F964" s="15" t="s">
+      <c r="F964" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="G964" s="15" t="s">
+      <c r="G964" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="H964" s="15"/>
+      <c r="H964" s="2"/>
     </row>
     <row r="965" spans="1:8">
-      <c r="A965" s="15">
-        <v>2025</v>
-      </c>
-      <c r="B965" s="15">
+      <c r="A965" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B965" s="2">
         <v>21</v>
       </c>
-      <c r="C965" s="15" t="s">
+      <c r="C965" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D965" s="15">
+      <c r="D965" s="2">
         <v>4</v>
       </c>
-      <c r="E965" s="15">
+      <c r="E965" s="2">
         <v>63</v>
       </c>
-      <c r="F965" s="15" t="s">
+      <c r="F965" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="G965" s="15" t="s">
+      <c r="G965" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="H965" s="15"/>
+      <c r="H965" s="2"/>
     </row>
     <row r="966" spans="1:8">
-      <c r="A966" s="15">
-        <v>2025</v>
-      </c>
-      <c r="B966" s="15">
+      <c r="A966" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B966" s="2">
         <v>21</v>
       </c>
-      <c r="C966" s="15" t="s">
+      <c r="C966" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D966" s="15">
+      <c r="D966" s="2">
         <v>5</v>
       </c>
-      <c r="E966" s="15">
+      <c r="E966" s="2">
         <v>14</v>
       </c>
-      <c r="F966" s="15" t="s">
+      <c r="F966" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="G966" s="15" t="s">
+      <c r="G966" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="H966" s="15"/>
+      <c r="H966" s="2"/>
     </row>
     <row r="967" spans="1:8">
-      <c r="A967" s="15">
-        <v>2025</v>
-      </c>
-      <c r="B967" s="15">
+      <c r="A967" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B967" s="2">
         <v>21</v>
       </c>
-      <c r="C967" s="15" t="s">
+      <c r="C967" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D967" s="15">
+      <c r="D967" s="2">
         <v>6</v>
       </c>
-      <c r="E967" s="15">
+      <c r="E967" s="2">
         <v>1</v>
       </c>
-      <c r="F967" s="15" t="s">
+      <c r="F967" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="G967" s="15" t="s">
+      <c r="G967" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="H967" s="15"/>
+      <c r="H967" s="2"/>
     </row>
     <row r="968" spans="1:8">
-      <c r="A968" s="15">
-        <v>2025</v>
-      </c>
-      <c r="B968" s="15">
+      <c r="A968" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B968" s="2">
         <v>21</v>
       </c>
-      <c r="C968" s="15" t="s">
+      <c r="C968" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D968" s="15">
+      <c r="D968" s="2">
         <v>7</v>
       </c>
-      <c r="E968" s="15">
+      <c r="E968" s="2">
         <v>18</v>
       </c>
-      <c r="F968" s="15" t="s">
+      <c r="F968" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="G968" s="15" t="s">
+      <c r="G968" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="H968" s="15"/>
+      <c r="H968" s="2"/>
     </row>
     <row r="969" spans="1:8">
-      <c r="A969" s="15">
-        <v>2025</v>
-      </c>
-      <c r="B969" s="15">
+      <c r="A969" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B969" s="2">
         <v>21</v>
       </c>
-      <c r="C969" s="15" t="s">
+      <c r="C969" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D969" s="15">
+      <c r="D969" s="2">
         <v>8</v>
       </c>
-      <c r="E969" s="15">
+      <c r="E969" s="2">
         <v>16</v>
       </c>
-      <c r="F969" s="15" t="s">
+      <c r="F969" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="G969" s="15" t="s">
+      <c r="G969" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="H969" s="15"/>
+      <c r="H969" s="2"/>
     </row>
     <row r="970" spans="1:8">
-      <c r="A970" s="15">
-        <v>2025</v>
-      </c>
-      <c r="B970" s="15">
+      <c r="A970" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B970" s="2">
         <v>21</v>
       </c>
-      <c r="C970" s="15" t="s">
+      <c r="C970" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D970" s="15">
+      <c r="D970" s="2">
         <v>9</v>
       </c>
-      <c r="E970" s="15">
+      <c r="E970" s="2">
         <v>6</v>
       </c>
-      <c r="F970" s="15" t="s">
+      <c r="F970" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="G970" s="15" t="s">
+      <c r="G970" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="H970" s="15"/>
+      <c r="H970" s="2"/>
     </row>
     <row r="971" spans="1:8">
-      <c r="A971" s="15">
-        <v>2025</v>
-      </c>
-      <c r="B971" s="15">
+      <c r="A971" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B971" s="2">
         <v>21</v>
       </c>
-      <c r="C971" s="15" t="s">
+      <c r="C971" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D971" s="15">
+      <c r="D971" s="2">
         <v>10</v>
       </c>
-      <c r="E971" s="15">
+      <c r="E971" s="2">
         <v>27</v>
       </c>
-      <c r="F971" s="15" t="s">
+      <c r="F971" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="G971" s="15" t="s">
+      <c r="G971" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="H971" s="15"/>
+      <c r="H971" s="2"/>
     </row>
     <row r="972" spans="1:8">
-      <c r="A972" s="15">
-        <v>2025</v>
-      </c>
-      <c r="B972" s="15">
+      <c r="A972" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B972" s="2">
         <v>21</v>
       </c>
-      <c r="C972" s="15" t="s">
+      <c r="C972" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D972" s="15">
+      <c r="D972" s="2">
         <v>11</v>
       </c>
-      <c r="E972" s="15">
+      <c r="E972" s="2">
         <v>44</v>
       </c>
-      <c r="F972" s="15" t="s">
+      <c r="F972" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="G972" s="15" t="s">
+      <c r="G972" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="H972" s="15"/>
+      <c r="H972" s="2"/>
     </row>
     <row r="973" spans="1:8">
-      <c r="A973" s="15">
-        <v>2025</v>
-      </c>
-      <c r="B973" s="15">
+      <c r="A973" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B973" s="2">
         <v>21</v>
       </c>
-      <c r="C973" s="15" t="s">
+      <c r="C973" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D973" s="15">
+      <c r="D973" s="2">
         <v>12</v>
       </c>
-      <c r="E973" s="15">
+      <c r="E973" s="2">
         <v>23</v>
       </c>
-      <c r="F973" s="15" t="s">
+      <c r="F973" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="G973" s="15" t="s">
+      <c r="G973" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="H973" s="15"/>
+      <c r="H973" s="2"/>
     </row>
     <row r="974" spans="1:8">
-      <c r="A974" s="15">
-        <v>2025</v>
-      </c>
-      <c r="B974" s="15">
+      <c r="A974" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B974" s="2">
         <v>21</v>
       </c>
-      <c r="C974" s="15" t="s">
+      <c r="C974" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D974" s="15">
+      <c r="D974" s="2">
         <v>13</v>
       </c>
-      <c r="E974" s="15">
+      <c r="E974" s="2">
         <v>10</v>
       </c>
-      <c r="F974" s="15" t="s">
+      <c r="F974" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="G974" s="15" t="s">
+      <c r="G974" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="H974" s="15"/>
+      <c r="H974" s="2"/>
     </row>
     <row r="975" spans="1:8">
-      <c r="A975" s="15">
-        <v>2025</v>
-      </c>
-      <c r="B975" s="15">
+      <c r="A975" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B975" s="2">
         <v>21</v>
       </c>
-      <c r="C975" s="15" t="s">
+      <c r="C975" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D975" s="15">
+      <c r="D975" s="2">
         <v>14</v>
       </c>
-      <c r="E975" s="15">
+      <c r="E975" s="2">
         <v>5</v>
       </c>
-      <c r="F975" s="15" t="s">
+      <c r="F975" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="G975" s="15" t="s">
+      <c r="G975" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="H975" s="15"/>
+      <c r="H975" s="2"/>
     </row>
     <row r="976" spans="1:8">
-      <c r="A976" s="15">
-        <v>2025</v>
-      </c>
-      <c r="B976" s="15">
+      <c r="A976" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B976" s="2">
         <v>21</v>
       </c>
-      <c r="C976" s="15" t="s">
+      <c r="C976" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D976" s="15">
+      <c r="D976" s="2">
         <v>15</v>
       </c>
-      <c r="E976" s="15">
+      <c r="E976" s="2">
         <v>87</v>
       </c>
-      <c r="F976" s="15" t="s">
+      <c r="F976" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="G976" s="15" t="s">
+      <c r="G976" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="H976" s="15"/>
+      <c r="H976" s="2"/>
     </row>
     <row r="977" spans="1:8">
-      <c r="A977" s="15">
-        <v>2025</v>
-      </c>
-      <c r="B977" s="15">
+      <c r="A977" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B977" s="2">
         <v>21</v>
       </c>
-      <c r="C977" s="15" t="s">
+      <c r="C977" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D977" s="15">
+      <c r="D977" s="2">
         <v>16</v>
       </c>
-      <c r="E977" s="15">
+      <c r="E977" s="2">
         <v>43</v>
       </c>
-      <c r="F977" s="15" t="s">
+      <c r="F977" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="G977" s="15" t="s">
+      <c r="G977" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="H977" s="15"/>
+      <c r="H977" s="2"/>
     </row>
     <row r="978" spans="1:8">
-      <c r="A978" s="15">
-        <v>2025</v>
-      </c>
-      <c r="B978" s="15">
+      <c r="A978" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B978" s="2">
         <v>21</v>
       </c>
-      <c r="C978" s="15" t="s">
+      <c r="C978" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D978" s="15">
+      <c r="D978" s="2">
         <v>17</v>
       </c>
-      <c r="E978" s="15">
+      <c r="E978" s="2">
         <v>30</v>
       </c>
-      <c r="F978" s="15" t="s">
+      <c r="F978" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="G978" s="15" t="s">
+      <c r="G978" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="H978" s="15"/>
+      <c r="H978" s="2"/>
     </row>
     <row r="979" spans="1:8">
-      <c r="A979" s="15">
-        <v>2025</v>
-      </c>
-      <c r="B979" s="15">
+      <c r="A979" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B979" s="2">
         <v>21</v>
       </c>
-      <c r="C979" s="15" t="s">
+      <c r="C979" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D979" s="15">
+      <c r="D979" s="2">
         <v>18</v>
       </c>
-      <c r="E979" s="15">
+      <c r="E979" s="2">
         <v>22</v>
       </c>
-      <c r="F979" s="15" t="s">
+      <c r="F979" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="G979" s="15" t="s">
+      <c r="G979" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="H979" s="15"/>
+      <c r="H979" s="2"/>
     </row>
     <row r="980" spans="1:8">
-      <c r="A980" s="15">
-        <v>2025</v>
-      </c>
-      <c r="B980" s="15">
+      <c r="A980" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B980" s="2">
         <v>21</v>
       </c>
-      <c r="C980" s="15" t="s">
+      <c r="C980" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D980" s="15">
+      <c r="D980" s="2">
         <v>19</v>
       </c>
-      <c r="E980" s="15">
+      <c r="E980" s="2">
         <v>31</v>
       </c>
-      <c r="F980" s="15" t="s">
+      <c r="F980" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="G980" s="15" t="s">
+      <c r="G980" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="H980" s="15"/>
+      <c r="H980" s="2"/>
     </row>
     <row r="981" spans="1:8">
-      <c r="A981" s="15">
-        <v>2025</v>
-      </c>
-      <c r="B981" s="15">
+      <c r="A981" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B981" s="2">
         <v>21</v>
       </c>
-      <c r="C981" s="15" t="s">
+      <c r="C981" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D981" s="15">
+      <c r="D981" s="2">
         <v>20</v>
       </c>
-      <c r="E981" s="15">
+      <c r="E981" s="2">
         <v>55</v>
       </c>
-      <c r="F981" s="15" t="s">
+      <c r="F981" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="G981" s="15" t="s">
+      <c r="G981" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="H981" s="15"/>
+      <c r="H981" s="2"/>
     </row>
     <row r="982" spans="1:8">
-      <c r="A982" s="16">
-        <v>2025</v>
-      </c>
-      <c r="B982" s="16">
+      <c r="A982" s="6">
+        <v>2025</v>
+      </c>
+      <c r="B982" s="6">
         <v>21</v>
       </c>
-      <c r="C982" s="16" t="s">
+      <c r="C982" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="D982" s="16">
+      <c r="D982" s="6">
         <v>1</v>
       </c>
-      <c r="E982" s="16">
+      <c r="E982" s="6">
         <v>4</v>
       </c>
-      <c r="F982" s="16" t="s">
+      <c r="F982" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="G982" s="16" t="s">
+      <c r="G982" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="H982" s="16">
+      <c r="H982" s="6">
         <v>8</v>
       </c>
     </row>
     <row r="983" spans="1:8">
-      <c r="A983" s="16">
-        <v>2025</v>
-      </c>
-      <c r="B983" s="16">
+      <c r="A983" s="6">
+        <v>2025</v>
+      </c>
+      <c r="B983" s="6">
         <v>21</v>
       </c>
-      <c r="C983" s="16" t="s">
+      <c r="C983" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="D983" s="16">
+      <c r="D983" s="6">
         <v>2</v>
       </c>
-      <c r="E983" s="16">
+      <c r="E983" s="6">
         <v>12</v>
       </c>
-      <c r="F983" s="16" t="s">
+      <c r="F983" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="G983" s="16" t="s">
+      <c r="G983" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="H983" s="16">
+      <c r="H983" s="6">
         <v>7</v>
       </c>
     </row>
     <row r="984" spans="1:8">
-      <c r="A984" s="16">
-        <v>2025</v>
-      </c>
-      <c r="B984" s="16">
+      <c r="A984" s="6">
+        <v>2025</v>
+      </c>
+      <c r="B984" s="6">
         <v>21</v>
       </c>
-      <c r="C984" s="16" t="s">
+      <c r="C984" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="D984" s="16">
+      <c r="D984" s="6">
         <v>3</v>
       </c>
-      <c r="E984" s="16">
+      <c r="E984" s="6">
         <v>63</v>
       </c>
-      <c r="F984" s="16" t="s">
+      <c r="F984" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="G984" s="16" t="s">
+      <c r="G984" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="H984" s="16">
+      <c r="H984" s="6">
         <v>6</v>
       </c>
     </row>
     <row r="985" spans="1:8">
-      <c r="A985" s="16">
-        <v>2025</v>
-      </c>
-      <c r="B985" s="16">
+      <c r="A985" s="6">
+        <v>2025</v>
+      </c>
+      <c r="B985" s="6">
         <v>21</v>
       </c>
-      <c r="C985" s="16" t="s">
+      <c r="C985" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="D985" s="16">
+      <c r="D985" s="6">
         <v>4</v>
       </c>
-      <c r="E985" s="16">
+      <c r="E985" s="6">
         <v>1</v>
       </c>
-      <c r="F985" s="16" t="s">
+      <c r="F985" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="G985" s="16" t="s">
+      <c r="G985" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="H985" s="16">
+      <c r="H985" s="6">
         <v>5</v>
       </c>
     </row>
     <row r="986" spans="1:8">
-      <c r="A986" s="16">
-        <v>2025</v>
-      </c>
-      <c r="B986" s="16">
+      <c r="A986" s="6">
+        <v>2025</v>
+      </c>
+      <c r="B986" s="6">
         <v>21</v>
       </c>
-      <c r="C986" s="16" t="s">
+      <c r="C986" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="D986" s="16">
+      <c r="D986" s="6">
         <v>5</v>
       </c>
-      <c r="E986" s="16">
+      <c r="E986" s="6">
         <v>16</v>
       </c>
-      <c r="F986" s="16" t="s">
+      <c r="F986" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="G986" s="16" t="s">
+      <c r="G986" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="H986" s="16">
+      <c r="H986" s="6">
         <v>4</v>
       </c>
     </row>
     <row r="987" spans="1:8">
-      <c r="A987" s="16">
-        <v>2025</v>
-      </c>
-      <c r="B987" s="16">
+      <c r="A987" s="6">
+        <v>2025</v>
+      </c>
+      <c r="B987" s="6">
         <v>21</v>
       </c>
-      <c r="C987" s="16" t="s">
+      <c r="C987" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="D987" s="16">
+      <c r="D987" s="6">
         <v>6</v>
       </c>
-      <c r="E987" s="16">
+      <c r="E987" s="6">
         <v>14</v>
       </c>
-      <c r="F987" s="16" t="s">
+      <c r="F987" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="G987" s="16" t="s">
+      <c r="G987" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="H987" s="16">
+      <c r="H987" s="6">
         <v>3</v>
       </c>
     </row>
     <row r="988" spans="1:8">
-      <c r="A988" s="16">
-        <v>2025</v>
-      </c>
-      <c r="B988" s="16">
+      <c r="A988" s="6">
+        <v>2025</v>
+      </c>
+      <c r="B988" s="6">
         <v>21</v>
       </c>
-      <c r="C988" s="16" t="s">
+      <c r="C988" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="D988" s="16">
+      <c r="D988" s="6">
         <v>7</v>
       </c>
-      <c r="E988" s="16">
+      <c r="E988" s="6">
         <v>44</v>
       </c>
-      <c r="F988" s="16" t="s">
+      <c r="F988" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="G988" s="16" t="s">
+      <c r="G988" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="H988" s="16">
+      <c r="H988" s="6">
         <v>2</v>
       </c>
     </row>
     <row r="989" spans="1:8">
-      <c r="A989" s="16">
-        <v>2025</v>
-      </c>
-      <c r="B989" s="16">
+      <c r="A989" s="6">
+        <v>2025</v>
+      </c>
+      <c r="B989" s="6">
         <v>21</v>
       </c>
-      <c r="C989" s="16" t="s">
+      <c r="C989" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="D989" s="16">
+      <c r="D989" s="6">
         <v>8</v>
       </c>
-      <c r="E989" s="16">
+      <c r="E989" s="6">
         <v>10</v>
       </c>
-      <c r="F989" s="16" t="s">
+      <c r="F989" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="G989" s="16" t="s">
+      <c r="G989" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="H989" s="16">
+      <c r="H989" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="990" spans="1:8">
-      <c r="A990" s="16">
-        <v>2025</v>
-      </c>
-      <c r="B990" s="16">
+      <c r="A990" s="6">
+        <v>2025</v>
+      </c>
+      <c r="B990" s="6">
         <v>21</v>
       </c>
-      <c r="C990" s="16" t="s">
+      <c r="C990" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="D990" s="16">
+      <c r="D990" s="6">
         <v>9</v>
       </c>
-      <c r="E990" s="16">
+      <c r="E990" s="6">
         <v>18</v>
       </c>
-      <c r="F990" s="16" t="s">
+      <c r="F990" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="G990" s="16" t="s">
+      <c r="G990" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="H990" s="16">
+      <c r="H990" s="6">
         <v>0</v>
       </c>
     </row>
     <row r="991" spans="1:8">
-      <c r="A991" s="16">
-        <v>2025</v>
-      </c>
-      <c r="B991" s="16">
+      <c r="A991" s="6">
+        <v>2025</v>
+      </c>
+      <c r="B991" s="6">
         <v>21</v>
       </c>
-      <c r="C991" s="16" t="s">
+      <c r="C991" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="D991" s="16">
+      <c r="D991" s="6">
         <v>10</v>
       </c>
-      <c r="E991" s="16">
+      <c r="E991" s="6">
         <v>6</v>
       </c>
-      <c r="F991" s="16" t="s">
+      <c r="F991" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="G991" s="16" t="s">
+      <c r="G991" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="H991" s="16">
+      <c r="H991" s="6">
         <v>0</v>
       </c>
     </row>
     <row r="992" spans="1:8">
-      <c r="A992" s="16">
-        <v>2025</v>
-      </c>
-      <c r="B992" s="16">
+      <c r="A992" s="6">
+        <v>2025</v>
+      </c>
+      <c r="B992" s="6">
         <v>21</v>
       </c>
-      <c r="C992" s="16" t="s">
+      <c r="C992" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="D992" s="16">
+      <c r="D992" s="6">
         <v>11</v>
       </c>
-      <c r="E992" s="16">
+      <c r="E992" s="6">
         <v>31</v>
       </c>
-      <c r="F992" s="16" t="s">
+      <c r="F992" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="G992" s="16" t="s">
+      <c r="G992" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="H992" s="16">
+      <c r="H992" s="6">
         <v>0</v>
       </c>
     </row>
     <row r="993" spans="1:8">
-      <c r="A993" s="16">
-        <v>2025</v>
-      </c>
-      <c r="B993" s="16">
+      <c r="A993" s="6">
+        <v>2025</v>
+      </c>
+      <c r="B993" s="6">
         <v>21</v>
       </c>
-      <c r="C993" s="16" t="s">
+      <c r="C993" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="D993" s="16">
+      <c r="D993" s="6">
         <v>12</v>
       </c>
-      <c r="E993" s="16">
+      <c r="E993" s="6">
         <v>87</v>
       </c>
-      <c r="F993" s="16" t="s">
+      <c r="F993" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="G993" s="16" t="s">
+      <c r="G993" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="H993" s="16">
+      <c r="H993" s="6">
         <v>0</v>
       </c>
     </row>
     <row r="994" spans="1:8">
-      <c r="A994" s="16">
-        <v>2025</v>
-      </c>
-      <c r="B994" s="16">
+      <c r="A994" s="6">
+        <v>2025</v>
+      </c>
+      <c r="B994" s="6">
         <v>21</v>
       </c>
-      <c r="C994" s="16" t="s">
+      <c r="C994" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="D994" s="16">
+      <c r="D994" s="6">
         <v>13</v>
       </c>
-      <c r="E994" s="16">
+      <c r="E994" s="6">
         <v>22</v>
       </c>
-      <c r="F994" s="16" t="s">
+      <c r="F994" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="G994" s="16" t="s">
+      <c r="G994" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="H994" s="16">
+      <c r="H994" s="6">
         <v>0</v>
       </c>
     </row>
     <row r="995" spans="1:8">
-      <c r="A995" s="16">
-        <v>2025</v>
-      </c>
-      <c r="B995" s="16">
+      <c r="A995" s="6">
+        <v>2025</v>
+      </c>
+      <c r="B995" s="6">
         <v>21</v>
       </c>
-      <c r="C995" s="16" t="s">
+      <c r="C995" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="D995" s="16">
+      <c r="D995" s="6">
         <v>14</v>
       </c>
-      <c r="E995" s="16">
+      <c r="E995" s="6">
         <v>55</v>
       </c>
-      <c r="F995" s="16" t="s">
+      <c r="F995" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="G995" s="16" t="s">
+      <c r="G995" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="H995" s="16">
+      <c r="H995" s="6">
         <v>0</v>
       </c>
     </row>
     <row r="996" spans="1:8">
-      <c r="A996" s="16">
-        <v>2025</v>
-      </c>
-      <c r="B996" s="16">
+      <c r="A996" s="6">
+        <v>2025</v>
+      </c>
+      <c r="B996" s="6">
         <v>21</v>
       </c>
-      <c r="C996" s="16" t="s">
+      <c r="C996" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="D996" s="16">
+      <c r="D996" s="6">
         <v>15</v>
       </c>
-      <c r="E996" s="16">
+      <c r="E996" s="6">
         <v>27</v>
       </c>
-      <c r="F996" s="16" t="s">
+      <c r="F996" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="G996" s="16" t="s">
+      <c r="G996" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="H996" s="16">
+      <c r="H996" s="6">
         <v>0</v>
       </c>
     </row>
     <row r="997" spans="1:8">
-      <c r="A997" s="16">
-        <v>2025</v>
-      </c>
-      <c r="B997" s="16">
+      <c r="A997" s="6">
+        <v>2025</v>
+      </c>
+      <c r="B997" s="6">
         <v>21</v>
       </c>
-      <c r="C997" s="16" t="s">
+      <c r="C997" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="D997" s="16">
+      <c r="D997" s="6">
         <v>16</v>
       </c>
-      <c r="E997" s="16">
+      <c r="E997" s="6">
         <v>30</v>
       </c>
-      <c r="F997" s="16" t="s">
+      <c r="F997" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="G997" s="16" t="s">
+      <c r="G997" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="H997" s="16">
+      <c r="H997" s="6">
         <v>0</v>
       </c>
     </row>
     <row r="998" spans="1:8">
-      <c r="A998" s="16">
-        <v>2025</v>
-      </c>
-      <c r="B998" s="16">
+      <c r="A998" s="6">
+        <v>2025</v>
+      </c>
+      <c r="B998" s="6">
         <v>21</v>
       </c>
-      <c r="C998" s="16" t="s">
+      <c r="C998" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="D998" s="16">
+      <c r="D998" s="6">
         <v>17</v>
       </c>
-      <c r="E998" s="16">
+      <c r="E998" s="6">
         <v>23</v>
       </c>
-      <c r="F998" s="16" t="s">
+      <c r="F998" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="G998" s="16" t="s">
+      <c r="G998" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="H998" s="16">
+      <c r="H998" s="6">
         <v>0</v>
       </c>
     </row>
     <row r="999" spans="1:8">
-      <c r="A999" s="16">
-        <v>2025</v>
-      </c>
-      <c r="B999" s="16">
+      <c r="A999" s="6">
+        <v>2025</v>
+      </c>
+      <c r="B999" s="6">
         <v>21</v>
       </c>
-      <c r="C999" s="16" t="s">
+      <c r="C999" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="D999" s="16" t="s">
+      <c r="D999" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="E999" s="16">
+      <c r="E999" s="6">
         <v>5</v>
       </c>
-      <c r="F999" s="16" t="s">
+      <c r="F999" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="G999" s="16" t="s">
+      <c r="G999" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="H999" s="16">
+      <c r="H999" s="6">
         <v>0</v>
       </c>
     </row>
     <row r="1000" spans="1:8">
-      <c r="A1000" s="16">
-        <v>2025</v>
-      </c>
-      <c r="B1000" s="16">
+      <c r="A1000" s="6">
+        <v>2025</v>
+      </c>
+      <c r="B1000" s="6">
         <v>21</v>
       </c>
-      <c r="C1000" s="16" t="s">
+      <c r="C1000" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="D1000" s="16" t="s">
+      <c r="D1000" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="E1000" s="16">
+      <c r="E1000" s="6">
         <v>81</v>
       </c>
-      <c r="F1000" s="16" t="s">
+      <c r="F1000" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="G1000" s="16" t="s">
+      <c r="G1000" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="H1000" s="16">
+      <c r="H1000" s="6">
         <v>0</v>
       </c>
     </row>
     <row r="1001" spans="1:8">
-      <c r="A1001" s="16">
-        <v>2025</v>
-      </c>
-      <c r="B1001" s="16">
+      <c r="A1001" s="6">
+        <v>2025</v>
+      </c>
+      <c r="B1001" s="6">
         <v>21</v>
       </c>
-      <c r="C1001" s="16" t="s">
+      <c r="C1001" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="D1001" s="16" t="s">
+      <c r="D1001" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="E1001" s="16">
+      <c r="E1001" s="6">
         <v>43</v>
       </c>
-      <c r="F1001" s="16" t="s">
+      <c r="F1001" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="G1001" s="16" t="s">
+      <c r="G1001" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="H1001" s="16">
+      <c r="H1001" s="6">
         <v>0</v>
       </c>
     </row>
     <row r="1002" spans="1:8">
-      <c r="A1002" s="15">
-        <v>2025</v>
-      </c>
-      <c r="B1002" s="15">
+      <c r="A1002" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B1002" s="2">
         <v>21</v>
       </c>
-      <c r="C1002" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="D1002" s="15">
+      <c r="C1002" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1002" s="2">
         <v>1</v>
       </c>
-      <c r="E1002" s="15">
+      <c r="E1002" s="2">
         <v>4</v>
       </c>
-      <c r="F1002" s="15" t="s">
+      <c r="F1002" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="G1002" s="15" t="s">
+      <c r="G1002" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="H1002" s="15"/>
+      <c r="H1002" s="2"/>
     </row>
     <row r="1003" spans="1:8">
-      <c r="A1003" s="15">
-        <v>2025</v>
-      </c>
-      <c r="B1003" s="15">
+      <c r="A1003" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B1003" s="2">
         <v>21</v>
       </c>
-      <c r="C1003" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="D1003" s="15">
+      <c r="C1003" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1003" s="2">
         <v>2</v>
       </c>
-      <c r="E1003" s="15">
+      <c r="E1003" s="2">
         <v>12</v>
       </c>
-      <c r="F1003" s="15" t="s">
+      <c r="F1003" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="G1003" s="15" t="s">
+      <c r="G1003" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="H1003" s="15"/>
+      <c r="H1003" s="2"/>
     </row>
     <row r="1004" spans="1:8">
-      <c r="A1004" s="15">
-        <v>2025</v>
-      </c>
-      <c r="B1004" s="15">
+      <c r="A1004" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B1004" s="2">
         <v>21</v>
       </c>
-      <c r="C1004" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="D1004" s="15">
+      <c r="C1004" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1004" s="2">
         <v>3</v>
       </c>
-      <c r="E1004" s="15">
+      <c r="E1004" s="2">
         <v>16</v>
       </c>
-      <c r="F1004" s="15" t="s">
+      <c r="F1004" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="G1004" s="15" t="s">
+      <c r="G1004" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="H1004" s="15"/>
+      <c r="H1004" s="2"/>
     </row>
     <row r="1005" spans="1:8">
-      <c r="A1005" s="15">
-        <v>2025</v>
-      </c>
-      <c r="B1005" s="15">
+      <c r="A1005" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B1005" s="2">
         <v>21</v>
       </c>
-      <c r="C1005" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="D1005" s="15">
+      <c r="C1005" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1005" s="2">
         <v>4</v>
       </c>
-      <c r="E1005" s="15">
+      <c r="E1005" s="2">
         <v>81</v>
       </c>
-      <c r="F1005" s="15" t="s">
+      <c r="F1005" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="G1005" s="15" t="s">
+      <c r="G1005" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="H1005" s="15"/>
+      <c r="H1005" s="2"/>
     </row>
     <row r="1006" spans="1:8">
-      <c r="A1006" s="15">
-        <v>2025</v>
-      </c>
-      <c r="B1006" s="15">
+      <c r="A1006" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B1006" s="2">
         <v>21</v>
       </c>
-      <c r="C1006" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="D1006" s="15">
+      <c r="C1006" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1006" s="2">
         <v>5</v>
       </c>
-      <c r="E1006" s="15">
+      <c r="E1006" s="2">
         <v>6</v>
       </c>
-      <c r="F1006" s="15" t="s">
+      <c r="F1006" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="G1006" s="15" t="s">
+      <c r="G1006" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="H1006" s="15"/>
+      <c r="H1006" s="2"/>
     </row>
     <row r="1007" spans="1:8">
-      <c r="A1007" s="15">
-        <v>2025</v>
-      </c>
-      <c r="B1007" s="15">
+      <c r="A1007" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B1007" s="2">
         <v>21</v>
       </c>
-      <c r="C1007" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="D1007" s="15">
+      <c r="C1007" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1007" s="2">
         <v>6</v>
       </c>
-      <c r="E1007" s="15">
+      <c r="E1007" s="2">
         <v>63</v>
       </c>
-      <c r="F1007" s="15" t="s">
+      <c r="F1007" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="G1007" s="15" t="s">
+      <c r="G1007" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="H1007" s="15"/>
+      <c r="H1007" s="2"/>
     </row>
     <row r="1008" spans="1:8">
-      <c r="A1008" s="15">
-        <v>2025</v>
-      </c>
-      <c r="B1008" s="15">
+      <c r="A1008" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B1008" s="2">
         <v>21</v>
       </c>
-      <c r="C1008" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="D1008" s="15">
+      <c r="C1008" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1008" s="2">
         <v>7</v>
       </c>
-      <c r="E1008" s="15">
+      <c r="E1008" s="2">
         <v>30</v>
       </c>
-      <c r="F1008" s="15" t="s">
+      <c r="F1008" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="G1008" s="15" t="s">
+      <c r="G1008" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="H1008" s="15"/>
+      <c r="H1008" s="2"/>
     </row>
     <row r="1009" spans="1:8">
-      <c r="A1009" s="15">
-        <v>2025</v>
-      </c>
-      <c r="B1009" s="15">
+      <c r="A1009" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B1009" s="2">
         <v>21</v>
       </c>
-      <c r="C1009" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="D1009" s="15">
+      <c r="C1009" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1009" s="2">
         <v>8</v>
       </c>
-      <c r="E1009" s="15">
+      <c r="E1009" s="2">
         <v>87</v>
       </c>
-      <c r="F1009" s="15" t="s">
+      <c r="F1009" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="G1009" s="15" t="s">
+      <c r="G1009" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="H1009" s="15"/>
+      <c r="H1009" s="2"/>
     </row>
     <row r="1010" spans="1:8">
-      <c r="A1010" s="15">
-        <v>2025</v>
-      </c>
-      <c r="B1010" s="15">
+      <c r="A1010" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B1010" s="2">
         <v>21</v>
       </c>
-      <c r="C1010" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="D1010" s="15">
+      <c r="C1010" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1010" s="2">
         <v>9</v>
       </c>
-      <c r="E1010" s="15">
+      <c r="E1010" s="2">
         <v>10</v>
       </c>
-      <c r="F1010" s="15" t="s">
+      <c r="F1010" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="G1010" s="15" t="s">
+      <c r="G1010" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="H1010" s="15"/>
+      <c r="H1010" s="2"/>
     </row>
     <row r="1011" spans="1:8">
-      <c r="A1011" s="15">
-        <v>2025</v>
-      </c>
-      <c r="B1011" s="15">
+      <c r="A1011" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B1011" s="2">
         <v>21</v>
       </c>
-      <c r="C1011" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="D1011" s="15">
+      <c r="C1011" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1011" s="2">
         <v>10</v>
       </c>
-      <c r="E1011" s="15">
+      <c r="E1011" s="2">
         <v>27</v>
       </c>
-      <c r="F1011" s="15" t="s">
+      <c r="F1011" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="G1011" s="15" t="s">
+      <c r="G1011" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="H1011" s="15"/>
+      <c r="H1011" s="2"/>
     </row>
     <row r="1012" spans="1:8">
-      <c r="A1012" s="15">
-        <v>2025</v>
-      </c>
-      <c r="B1012" s="15">
+      <c r="A1012" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B1012" s="2">
         <v>21</v>
       </c>
-      <c r="C1012" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="D1012" s="15">
+      <c r="C1012" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1012" s="2">
         <v>11</v>
       </c>
-      <c r="E1012" s="15">
+      <c r="E1012" s="2">
         <v>14</v>
       </c>
-      <c r="F1012" s="15" t="s">
+      <c r="F1012" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="G1012" s="15" t="s">
+      <c r="G1012" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="H1012" s="15"/>
+      <c r="H1012" s="2"/>
     </row>
     <row r="1013" spans="1:8">
-      <c r="A1013" s="15">
-        <v>2025</v>
-      </c>
-      <c r="B1013" s="15">
+      <c r="A1013" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B1013" s="2">
         <v>21</v>
       </c>
-      <c r="C1013" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="D1013" s="15">
+      <c r="C1013" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1013" s="2">
         <v>12</v>
       </c>
-      <c r="E1013" s="15">
+      <c r="E1013" s="2">
         <v>23</v>
       </c>
-      <c r="F1013" s="15" t="s">
+      <c r="F1013" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="G1013" s="15" t="s">
+      <c r="G1013" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="H1013" s="15"/>
+      <c r="H1013" s="2"/>
     </row>
     <row r="1014" spans="1:8">
-      <c r="A1014" s="15">
-        <v>2025</v>
-      </c>
-      <c r="B1014" s="15">
+      <c r="A1014" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B1014" s="2">
         <v>21</v>
       </c>
-      <c r="C1014" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="D1014" s="15">
+      <c r="C1014" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1014" s="2">
         <v>13</v>
       </c>
-      <c r="E1014" s="15">
+      <c r="E1014" s="2">
         <v>44</v>
       </c>
-      <c r="F1014" s="15" t="s">
+      <c r="F1014" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="G1014" s="15" t="s">
+      <c r="G1014" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="H1014" s="15"/>
+      <c r="H1014" s="2"/>
     </row>
     <row r="1015" spans="1:8">
-      <c r="A1015" s="15">
-        <v>2025</v>
-      </c>
-      <c r="B1015" s="15">
+      <c r="A1015" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B1015" s="2">
         <v>21</v>
       </c>
-      <c r="C1015" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="D1015" s="15">
+      <c r="C1015" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1015" s="2">
         <v>14</v>
       </c>
-      <c r="E1015" s="15">
+      <c r="E1015" s="2">
         <v>18</v>
       </c>
-      <c r="F1015" s="15" t="s">
+      <c r="F1015" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="G1015" s="15" t="s">
+      <c r="G1015" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="H1015" s="15"/>
+      <c r="H1015" s="2"/>
     </row>
     <row r="1016" spans="1:8">
-      <c r="A1016" s="15">
-        <v>2025</v>
-      </c>
-      <c r="B1016" s="15">
+      <c r="A1016" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B1016" s="2">
         <v>21</v>
       </c>
-      <c r="C1016" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="D1016" s="15">
+      <c r="C1016" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1016" s="2">
         <v>15</v>
       </c>
-      <c r="E1016" s="15">
+      <c r="E1016" s="2">
         <v>55</v>
       </c>
-      <c r="F1016" s="15" t="s">
+      <c r="F1016" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="G1016" s="15" t="s">
+      <c r="G1016" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="H1016" s="15"/>
+      <c r="H1016" s="2"/>
     </row>
     <row r="1017" spans="1:8">
-      <c r="A1017" s="15">
-        <v>2025</v>
-      </c>
-      <c r="B1017" s="15">
+      <c r="A1017" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B1017" s="2">
         <v>21</v>
       </c>
-      <c r="C1017" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="D1017" s="15">
+      <c r="C1017" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1017" s="2">
         <v>16</v>
       </c>
-      <c r="E1017" s="15">
+      <c r="E1017" s="2">
         <v>1</v>
       </c>
-      <c r="F1017" s="15" t="s">
+      <c r="F1017" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="G1017" s="15" t="s">
+      <c r="G1017" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="H1017" s="15"/>
+      <c r="H1017" s="2"/>
     </row>
     <row r="1018" spans="1:8">
-      <c r="A1018" s="15">
-        <v>2025</v>
-      </c>
-      <c r="B1018" s="15">
+      <c r="A1018" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B1018" s="2">
         <v>21</v>
       </c>
-      <c r="C1018" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="D1018" s="15">
+      <c r="C1018" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1018" s="2">
         <v>17</v>
       </c>
-      <c r="E1018" s="15">
+      <c r="E1018" s="2">
         <v>31</v>
       </c>
-      <c r="F1018" s="15" t="s">
+      <c r="F1018" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="G1018" s="15" t="s">
+      <c r="G1018" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="H1018" s="15"/>
+      <c r="H1018" s="2"/>
     </row>
     <row r="1019" spans="1:8">
-      <c r="A1019" s="15">
-        <v>2025</v>
-      </c>
-      <c r="B1019" s="15">
+      <c r="A1019" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B1019" s="2">
         <v>21</v>
       </c>
-      <c r="C1019" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="D1019" s="15">
+      <c r="C1019" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1019" s="2">
         <v>18</v>
       </c>
-      <c r="E1019" s="15">
+      <c r="E1019" s="2">
         <v>43</v>
       </c>
-      <c r="F1019" s="15" t="s">
+      <c r="F1019" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="G1019" s="15" t="s">
+      <c r="G1019" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="H1019" s="15"/>
+      <c r="H1019" s="2"/>
     </row>
     <row r="1020" spans="1:8">
-      <c r="A1020" s="15">
-        <v>2025</v>
-      </c>
-      <c r="B1020" s="15">
+      <c r="A1020" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B1020" s="2">
         <v>21</v>
       </c>
-      <c r="C1020" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="D1020" s="15">
+      <c r="C1020" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1020" s="2">
         <v>19</v>
       </c>
-      <c r="E1020" s="15">
+      <c r="E1020" s="2">
         <v>22</v>
       </c>
-      <c r="F1020" s="15" t="s">
+      <c r="F1020" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="G1020" s="15" t="s">
+      <c r="G1020" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="H1020" s="15"/>
+      <c r="H1020" s="2"/>
     </row>
     <row r="1021" spans="1:8">
-      <c r="A1021" s="15">
-        <v>2025</v>
-      </c>
-      <c r="B1021" s="15">
+      <c r="A1021" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B1021" s="2">
         <v>21</v>
       </c>
-      <c r="C1021" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="D1021" s="15">
+      <c r="C1021" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1021" s="2">
         <v>20</v>
       </c>
-      <c r="E1021" s="15"/>
-      <c r="F1021" s="15"/>
-      <c r="G1021" s="15"/>
-      <c r="H1021" s="15"/>
+      <c r="E1021" s="2"/>
+      <c r="F1021" s="2"/>
+      <c r="G1021" s="2"/>
+      <c r="H1021" s="2"/>
+    </row>
+    <row r="1022" spans="1:8">
+      <c r="A1022" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B1022" s="2">
+        <v>21</v>
+      </c>
+      <c r="C1022" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1022" s="15">
+        <v>1</v>
+      </c>
+      <c r="E1022" s="15">
+        <v>4</v>
+      </c>
+      <c r="F1022" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="G1022" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="H1022" s="15">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1023" spans="1:8">
+      <c r="A1023" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B1023" s="2">
+        <v>21</v>
+      </c>
+      <c r="C1023" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1023" s="15">
+        <v>2</v>
+      </c>
+      <c r="E1023" s="15">
+        <v>12</v>
+      </c>
+      <c r="F1023" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="G1023" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="H1023" s="15">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1024" spans="1:8">
+      <c r="A1024" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B1024" s="2">
+        <v>21</v>
+      </c>
+      <c r="C1024" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1024" s="15">
+        <v>3</v>
+      </c>
+      <c r="E1024" s="15">
+        <v>1</v>
+      </c>
+      <c r="F1024" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="G1024" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="H1024" s="15">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1025" spans="1:8">
+      <c r="A1025" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B1025" s="2">
+        <v>21</v>
+      </c>
+      <c r="C1025" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1025" s="15">
+        <v>4</v>
+      </c>
+      <c r="E1025" s="15">
+        <v>63</v>
+      </c>
+      <c r="F1025" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="G1025" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="H1025" s="15">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1026" spans="1:8">
+      <c r="A1026" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B1026" s="2">
+        <v>21</v>
+      </c>
+      <c r="C1026" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1026" s="15">
+        <v>5</v>
+      </c>
+      <c r="E1026" s="15">
+        <v>81</v>
+      </c>
+      <c r="F1026" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="G1026" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="H1026" s="15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1027" spans="1:8">
+      <c r="A1027" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B1027" s="2">
+        <v>21</v>
+      </c>
+      <c r="C1027" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1027" s="15">
+        <v>6</v>
+      </c>
+      <c r="E1027" s="15">
+        <v>87</v>
+      </c>
+      <c r="F1027" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="G1027" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="H1027" s="15">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1028" spans="1:8">
+      <c r="A1028" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B1028" s="2">
+        <v>21</v>
+      </c>
+      <c r="C1028" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1028" s="15">
+        <v>7</v>
+      </c>
+      <c r="E1028" s="15">
+        <v>30</v>
+      </c>
+      <c r="F1028" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="G1028" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="H1028" s="15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1029" spans="1:8">
+      <c r="A1029" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B1029" s="2">
+        <v>21</v>
+      </c>
+      <c r="C1029" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1029" s="15">
+        <v>8</v>
+      </c>
+      <c r="E1029" s="15">
+        <v>6</v>
+      </c>
+      <c r="F1029" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="G1029" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="H1029" s="15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1030" spans="1:8">
+      <c r="A1030" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B1030" s="2">
+        <v>21</v>
+      </c>
+      <c r="C1030" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1030" s="15">
+        <v>9</v>
+      </c>
+      <c r="E1030" s="15">
+        <v>27</v>
+      </c>
+      <c r="F1030" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="G1030" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="H1030" s="15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1031" spans="1:8">
+      <c r="A1031" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B1031" s="2">
+        <v>21</v>
+      </c>
+      <c r="C1031" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1031" s="15">
+        <v>10</v>
+      </c>
+      <c r="E1031" s="15">
+        <v>10</v>
+      </c>
+      <c r="F1031" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="G1031" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="H1031" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1032" spans="1:8">
+      <c r="A1032" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B1032" s="2">
+        <v>21</v>
+      </c>
+      <c r="C1032" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1032" s="15">
+        <v>11</v>
+      </c>
+      <c r="E1032" s="15">
+        <v>23</v>
+      </c>
+      <c r="F1032" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="G1032" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="H1032" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1033" spans="1:8">
+      <c r="A1033" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B1033" s="2">
+        <v>21</v>
+      </c>
+      <c r="C1033" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1033" s="15">
+        <v>12</v>
+      </c>
+      <c r="E1033" s="15">
+        <v>31</v>
+      </c>
+      <c r="F1033" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="G1033" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="H1033" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1034" spans="1:8">
+      <c r="A1034" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B1034" s="2">
+        <v>21</v>
+      </c>
+      <c r="C1034" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1034" s="15">
+        <v>13</v>
+      </c>
+      <c r="E1034" s="15">
+        <v>55</v>
+      </c>
+      <c r="F1034" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="G1034" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="H1034" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1035" spans="1:8">
+      <c r="A1035" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B1035" s="2">
+        <v>21</v>
+      </c>
+      <c r="C1035" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1035" s="15">
+        <v>14</v>
+      </c>
+      <c r="E1035" s="15">
+        <v>14</v>
+      </c>
+      <c r="F1035" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="G1035" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="H1035" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1036" spans="1:8">
+      <c r="A1036" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B1036" s="2">
+        <v>21</v>
+      </c>
+      <c r="C1036" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1036" s="15">
+        <v>15</v>
+      </c>
+      <c r="E1036" s="15">
+        <v>43</v>
+      </c>
+      <c r="F1036" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="G1036" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="H1036" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1037" spans="1:8">
+      <c r="A1037" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B1037" s="2">
+        <v>21</v>
+      </c>
+      <c r="C1037" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1037" s="15">
+        <v>16</v>
+      </c>
+      <c r="E1037" s="15">
+        <v>18</v>
+      </c>
+      <c r="F1037" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1037" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="H1037" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1038" spans="1:8">
+      <c r="A1038" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B1038" s="2">
+        <v>21</v>
+      </c>
+      <c r="C1038" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1038" s="15">
+        <v>17</v>
+      </c>
+      <c r="E1038" s="15">
+        <v>22</v>
+      </c>
+      <c r="F1038" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="G1038" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="H1038" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1039" spans="1:8">
+      <c r="A1039" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B1039" s="2">
+        <v>21</v>
+      </c>
+      <c r="C1039" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1039" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="E1039" s="15">
+        <v>44</v>
+      </c>
+      <c r="F1039" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="G1039" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="H1039" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1040" spans="1:8">
+      <c r="A1040" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B1040" s="2">
+        <v>21</v>
+      </c>
+      <c r="C1040" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1040" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="E1040" s="15">
+        <v>16</v>
+      </c>
+      <c r="F1040" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="G1040" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="H1040" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1041" spans="1:8">
+      <c r="A1041" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B1041" s="2">
+        <v>21</v>
+      </c>
+      <c r="C1041" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1041" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="E1041" s="15">
+        <v>5</v>
+      </c>
+      <c r="F1041" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="G1041" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="H1041" s="15">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H961" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H1021" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/docs/datas/f1.xlsx
+++ b/public/docs/datas/f1.xlsx
@@ -15,7 +15,7 @@
     <sheet name="teams" sheetId="5" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">result!$A$1:$H$1021</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">result!$A$1:$H$1061</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3630" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3755" uniqueCount="214">
   <si>
     <t>year</t>
   </si>
@@ -1324,7 +1324,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1358,7 +1358,8 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="47" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -2466,13 +2467,13 @@
       <c r="C2" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D2" s="16">
+      <c r="D2" s="17">
         <v>45730</v>
       </c>
-      <c r="E2" s="18">
+      <c r="E2" s="19">
         <v>0.395833333333333</v>
       </c>
-      <c r="F2" s="18">
+      <c r="F2" s="19">
         <v>0.4375</v>
       </c>
       <c r="G2" s="2">
@@ -2489,13 +2490,13 @@
       <c r="C3" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D3" s="16">
+      <c r="D3" s="17">
         <v>45730</v>
       </c>
-      <c r="E3" s="18">
+      <c r="E3" s="19">
         <v>0.541666666666667</v>
       </c>
-      <c r="F3" s="18">
+      <c r="F3" s="19">
         <v>0.583333333333333</v>
       </c>
       <c r="G3" s="2">
@@ -2512,13 +2513,13 @@
       <c r="C4" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D4" s="16">
+      <c r="D4" s="17">
         <v>45731</v>
       </c>
-      <c r="E4" s="18">
+      <c r="E4" s="19">
         <v>0.395833333333333</v>
       </c>
-      <c r="F4" s="18">
+      <c r="F4" s="19">
         <v>0.4375</v>
       </c>
       <c r="G4" s="2">
@@ -2535,13 +2536,13 @@
       <c r="C5" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D5" s="16">
+      <c r="D5" s="17">
         <v>45731</v>
       </c>
-      <c r="E5" s="18">
+      <c r="E5" s="19">
         <v>0.541666666666667</v>
       </c>
-      <c r="F5" s="18">
+      <c r="F5" s="19">
         <v>0.583333333333333</v>
       </c>
       <c r="G5" s="2">
@@ -2558,13 +2559,13 @@
       <c r="C6" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D6" s="16">
+      <c r="D6" s="17">
         <v>45732</v>
       </c>
-      <c r="E6" s="18">
+      <c r="E6" s="19">
         <v>0.5</v>
       </c>
-      <c r="F6" s="18"/>
+      <c r="F6" s="19"/>
       <c r="G6" s="2">
         <v>1</v>
       </c>
@@ -2579,13 +2580,13 @@
       <c r="C7" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D7" s="17">
+      <c r="D7" s="18">
         <v>45737</v>
       </c>
-      <c r="E7" s="19">
+      <c r="E7" s="20">
         <v>0.479166666666667</v>
       </c>
-      <c r="F7" s="19">
+      <c r="F7" s="20">
         <v>0.520833333333333</v>
       </c>
       <c r="G7" s="6">
@@ -2602,13 +2603,13 @@
       <c r="C8" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="D8" s="17">
+      <c r="D8" s="18">
         <v>45737</v>
       </c>
-      <c r="E8" s="19">
+      <c r="E8" s="20">
         <v>0.645833333333333</v>
       </c>
-      <c r="F8" s="19">
+      <c r="F8" s="20">
         <v>0.676388888888889</v>
       </c>
       <c r="G8" s="6">
@@ -2625,13 +2626,13 @@
       <c r="C9" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="D9" s="17">
+      <c r="D9" s="18">
         <v>45738</v>
       </c>
-      <c r="E9" s="19">
+      <c r="E9" s="20">
         <v>0.458333333333333</v>
       </c>
-      <c r="F9" s="19">
+      <c r="F9" s="20">
         <v>0.5</v>
       </c>
       <c r="G9" s="6">
@@ -2648,13 +2649,13 @@
       <c r="C10" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D10" s="17">
+      <c r="D10" s="18">
         <v>45738</v>
       </c>
-      <c r="E10" s="19">
+      <c r="E10" s="20">
         <v>0.625</v>
       </c>
-      <c r="F10" s="19">
+      <c r="F10" s="20">
         <v>0.666666666666667</v>
       </c>
       <c r="G10" s="6">
@@ -2671,10 +2672,10 @@
       <c r="C11" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D11" s="17">
+      <c r="D11" s="18">
         <v>45739</v>
       </c>
-      <c r="E11" s="19">
+      <c r="E11" s="20">
         <v>0.625</v>
       </c>
       <c r="F11" s="6"/>
@@ -2692,13 +2693,13 @@
       <c r="C12" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D12" s="16">
+      <c r="D12" s="17">
         <v>45751</v>
       </c>
-      <c r="E12" s="18">
+      <c r="E12" s="19">
         <v>0.4375</v>
       </c>
-      <c r="F12" s="18">
+      <c r="F12" s="19">
         <v>0.479166666666667</v>
       </c>
       <c r="G12" s="2">
@@ -2715,13 +2716,13 @@
       <c r="C13" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D13" s="16">
+      <c r="D13" s="17">
         <v>45751</v>
       </c>
-      <c r="E13" s="18">
+      <c r="E13" s="19">
         <v>0.583333333333333</v>
       </c>
-      <c r="F13" s="18">
+      <c r="F13" s="19">
         <v>0.625</v>
       </c>
       <c r="G13" s="2">
@@ -2738,13 +2739,13 @@
       <c r="C14" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D14" s="16">
+      <c r="D14" s="17">
         <v>45752</v>
       </c>
-      <c r="E14" s="18">
+      <c r="E14" s="19">
         <v>0.4375</v>
       </c>
-      <c r="F14" s="18">
+      <c r="F14" s="19">
         <v>0.479166666666667</v>
       </c>
       <c r="G14" s="2">
@@ -2761,13 +2762,13 @@
       <c r="C15" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D15" s="16">
+      <c r="D15" s="17">
         <v>45752</v>
       </c>
-      <c r="E15" s="18">
+      <c r="E15" s="19">
         <v>0.583333333333333</v>
       </c>
-      <c r="F15" s="18">
+      <c r="F15" s="19">
         <v>0.625</v>
       </c>
       <c r="G15" s="2">
@@ -2784,10 +2785,10 @@
       <c r="C16" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D16" s="16">
+      <c r="D16" s="17">
         <v>45753</v>
       </c>
-      <c r="E16" s="18">
+      <c r="E16" s="19">
         <v>0.541666666666667</v>
       </c>
       <c r="F16" s="2"/>
@@ -2805,13 +2806,13 @@
       <c r="C17" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D17" s="17">
+      <c r="D17" s="18">
         <v>45758</v>
       </c>
-      <c r="E17" s="19">
+      <c r="E17" s="20">
         <v>0.8125</v>
       </c>
-      <c r="F17" s="19">
+      <c r="F17" s="20">
         <v>0.854166666666667</v>
       </c>
       <c r="G17" s="6">
@@ -2828,13 +2829,13 @@
       <c r="C18" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="D18" s="17">
+      <c r="D18" s="18">
         <v>45758</v>
       </c>
-      <c r="E18" s="19">
+      <c r="E18" s="20">
         <v>0.958333333333333</v>
       </c>
-      <c r="F18" s="19">
+      <c r="F18" s="20">
         <v>0</v>
       </c>
       <c r="G18" s="6">
@@ -2851,13 +2852,13 @@
       <c r="C19" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D19" s="17">
+      <c r="D19" s="18">
         <v>45759</v>
       </c>
-      <c r="E19" s="19">
+      <c r="E19" s="20">
         <v>0.854166666666667</v>
       </c>
-      <c r="F19" s="19">
+      <c r="F19" s="20">
         <v>0.895833333333333</v>
       </c>
       <c r="G19" s="6">
@@ -2874,13 +2875,13 @@
       <c r="C20" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D20" s="17">
+      <c r="D20" s="18">
         <v>45760</v>
       </c>
-      <c r="E20" s="19">
-        <v>0</v>
-      </c>
-      <c r="F20" s="19">
+      <c r="E20" s="20">
+        <v>0</v>
+      </c>
+      <c r="F20" s="20">
         <v>0.0416666666666667</v>
       </c>
       <c r="G20" s="6">
@@ -2897,10 +2898,10 @@
       <c r="C21" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D21" s="17">
+      <c r="D21" s="18">
         <v>45760</v>
       </c>
-      <c r="E21" s="19">
+      <c r="E21" s="20">
         <v>0.958333333333333</v>
       </c>
       <c r="F21" s="6"/>
@@ -2918,13 +2919,13 @@
       <c r="C22" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D22" s="16">
+      <c r="D22" s="17">
         <v>45765</v>
       </c>
-      <c r="E22" s="18">
+      <c r="E22" s="19">
         <v>0.895833333333333</v>
       </c>
-      <c r="F22" s="18">
+      <c r="F22" s="19">
         <v>0.9375</v>
       </c>
       <c r="G22" s="2">
@@ -2941,13 +2942,13 @@
       <c r="C23" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D23" s="16">
+      <c r="D23" s="17">
         <v>45766</v>
       </c>
-      <c r="E23" s="18">
+      <c r="E23" s="19">
         <v>0.0416666666666667</v>
       </c>
-      <c r="F23" s="18">
+      <c r="F23" s="19">
         <v>0.0833333333333333</v>
       </c>
       <c r="G23" s="2">
@@ -2964,13 +2965,13 @@
       <c r="C24" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D24" s="16">
+      <c r="D24" s="17">
         <v>45766</v>
       </c>
-      <c r="E24" s="18">
+      <c r="E24" s="19">
         <v>0.895833333333333</v>
       </c>
-      <c r="F24" s="18">
+      <c r="F24" s="19">
         <v>0.9375</v>
       </c>
       <c r="G24" s="2">
@@ -2987,13 +2988,13 @@
       <c r="C25" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D25" s="16">
+      <c r="D25" s="17">
         <v>45767</v>
       </c>
-      <c r="E25" s="18">
+      <c r="E25" s="19">
         <v>0.0416666666666667</v>
       </c>
-      <c r="F25" s="18">
+      <c r="F25" s="19">
         <v>0.0833333333333333</v>
       </c>
       <c r="G25" s="2">
@@ -3010,10 +3011,10 @@
       <c r="C26" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D26" s="16">
+      <c r="D26" s="17">
         <v>45767</v>
       </c>
-      <c r="E26" s="18">
+      <c r="E26" s="19">
         <v>0.0416666666666667</v>
       </c>
       <c r="F26" s="2"/>
@@ -3031,13 +3032,13 @@
       <c r="C27" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D27" s="17">
+      <c r="D27" s="18">
         <v>45780</v>
       </c>
-      <c r="E27" s="19">
+      <c r="E27" s="20">
         <v>0.0208333333333333</v>
       </c>
-      <c r="F27" s="19">
+      <c r="F27" s="20">
         <v>0.0625</v>
       </c>
       <c r="G27" s="6">
@@ -3054,13 +3055,13 @@
       <c r="C28" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="D28" s="17">
+      <c r="D28" s="18">
         <v>45780</v>
       </c>
-      <c r="E28" s="19">
+      <c r="E28" s="20">
         <v>0.1875</v>
       </c>
-      <c r="F28" s="19">
+      <c r="F28" s="20">
         <v>0.218055555555556</v>
       </c>
       <c r="G28" s="6">
@@ -3077,13 +3078,13 @@
       <c r="C29" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="D29" s="17">
+      <c r="D29" s="18">
         <v>45781</v>
       </c>
-      <c r="E29" s="19">
-        <v>0</v>
-      </c>
-      <c r="F29" s="19">
+      <c r="E29" s="20">
+        <v>0</v>
+      </c>
+      <c r="F29" s="20">
         <v>0.0416666666666667</v>
       </c>
       <c r="G29" s="6">
@@ -3100,13 +3101,13 @@
       <c r="C30" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D30" s="17">
+      <c r="D30" s="18">
         <v>45781</v>
       </c>
-      <c r="E30" s="19">
+      <c r="E30" s="20">
         <v>0.166666666666667</v>
       </c>
-      <c r="F30" s="19">
+      <c r="F30" s="20">
         <v>0.208333333333333</v>
       </c>
       <c r="G30" s="6">
@@ -3123,13 +3124,13 @@
       <c r="C31" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D31" s="17">
+      <c r="D31" s="18">
         <v>45782</v>
       </c>
-      <c r="E31" s="19">
+      <c r="E31" s="20">
         <v>0.166666666666667</v>
       </c>
-      <c r="F31" s="19"/>
+      <c r="F31" s="20"/>
       <c r="G31" s="6">
         <v>1</v>
       </c>
@@ -3144,13 +3145,13 @@
       <c r="C32" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D32" s="16">
+      <c r="D32" s="17">
         <v>45793</v>
       </c>
-      <c r="E32" s="18">
+      <c r="E32" s="19">
         <v>0.8125</v>
       </c>
-      <c r="F32" s="18">
+      <c r="F32" s="19">
         <v>0.854166666666667</v>
       </c>
       <c r="G32" s="2">
@@ -3167,13 +3168,13 @@
       <c r="C33" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D33" s="16">
+      <c r="D33" s="17">
         <v>45793</v>
       </c>
-      <c r="E33" s="18">
+      <c r="E33" s="19">
         <v>0.958333333333333</v>
       </c>
-      <c r="F33" s="18">
+      <c r="F33" s="19">
         <v>0</v>
       </c>
       <c r="G33" s="2">
@@ -3190,13 +3191,13 @@
       <c r="C34" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D34" s="16">
+      <c r="D34" s="17">
         <v>45794</v>
       </c>
-      <c r="E34" s="18">
+      <c r="E34" s="19">
         <v>0.770833333333333</v>
       </c>
-      <c r="F34" s="18">
+      <c r="F34" s="19">
         <v>0.8125</v>
       </c>
       <c r="G34" s="2">
@@ -3213,13 +3214,13 @@
       <c r="C35" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D35" s="16">
+      <c r="D35" s="17">
         <v>45794</v>
       </c>
-      <c r="E35" s="18">
+      <c r="E35" s="19">
         <v>0.916666666666667</v>
       </c>
-      <c r="F35" s="18">
+      <c r="F35" s="19">
         <v>0.958333333333333</v>
       </c>
       <c r="G35" s="2">
@@ -3236,10 +3237,10 @@
       <c r="C36" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D36" s="16">
+      <c r="D36" s="17">
         <v>45795</v>
       </c>
-      <c r="E36" s="18">
+      <c r="E36" s="19">
         <v>0.875</v>
       </c>
       <c r="F36" s="2"/>
@@ -3257,13 +3258,13 @@
       <c r="C37" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D37" s="17">
+      <c r="D37" s="18">
         <v>45800</v>
       </c>
-      <c r="E37" s="19">
+      <c r="E37" s="20">
         <v>0.8125</v>
       </c>
-      <c r="F37" s="19">
+      <c r="F37" s="20">
         <v>0.854166666666667</v>
       </c>
       <c r="G37" s="6">
@@ -3280,13 +3281,13 @@
       <c r="C38" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="D38" s="17">
+      <c r="D38" s="18">
         <v>45800</v>
       </c>
-      <c r="E38" s="19">
+      <c r="E38" s="20">
         <v>0.958333333333333</v>
       </c>
-      <c r="F38" s="19">
+      <c r="F38" s="20">
         <v>0</v>
       </c>
       <c r="G38" s="6">
@@ -3303,13 +3304,13 @@
       <c r="C39" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D39" s="17">
+      <c r="D39" s="18">
         <v>45801</v>
       </c>
-      <c r="E39" s="19">
+      <c r="E39" s="20">
         <v>0.770833333333333</v>
       </c>
-      <c r="F39" s="19">
+      <c r="F39" s="20">
         <v>0.8125</v>
       </c>
       <c r="G39" s="6">
@@ -3326,13 +3327,13 @@
       <c r="C40" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D40" s="17">
+      <c r="D40" s="18">
         <v>45801</v>
       </c>
-      <c r="E40" s="19">
+      <c r="E40" s="20">
         <v>0.916666666666667</v>
       </c>
-      <c r="F40" s="19">
+      <c r="F40" s="20">
         <v>0.958333333333333</v>
       </c>
       <c r="G40" s="6">
@@ -3349,10 +3350,10 @@
       <c r="C41" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D41" s="17">
+      <c r="D41" s="18">
         <v>45802</v>
       </c>
-      <c r="E41" s="19">
+      <c r="E41" s="20">
         <v>0.875</v>
       </c>
       <c r="F41" s="6"/>
@@ -3370,13 +3371,13 @@
       <c r="C42" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D42" s="16">
+      <c r="D42" s="17">
         <v>45807</v>
       </c>
-      <c r="E42" s="18">
+      <c r="E42" s="19">
         <v>0.8125</v>
       </c>
-      <c r="F42" s="18">
+      <c r="F42" s="19">
         <v>0.854166666666667</v>
       </c>
       <c r="G42" s="2">
@@ -3393,13 +3394,13 @@
       <c r="C43" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D43" s="16">
+      <c r="D43" s="17">
         <v>45807</v>
       </c>
-      <c r="E43" s="18">
+      <c r="E43" s="19">
         <v>0.958333333333333</v>
       </c>
-      <c r="F43" s="18">
+      <c r="F43" s="19">
         <v>0</v>
       </c>
       <c r="G43" s="2">
@@ -3416,13 +3417,13 @@
       <c r="C44" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D44" s="16">
+      <c r="D44" s="17">
         <v>45808</v>
       </c>
-      <c r="E44" s="18">
+      <c r="E44" s="19">
         <v>0.770833333333333</v>
       </c>
-      <c r="F44" s="18">
+      <c r="F44" s="19">
         <v>0.8125</v>
       </c>
       <c r="G44" s="2">
@@ -3439,13 +3440,13 @@
       <c r="C45" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D45" s="16">
+      <c r="D45" s="17">
         <v>45808</v>
       </c>
-      <c r="E45" s="18">
+      <c r="E45" s="19">
         <v>0.916666666666667</v>
       </c>
-      <c r="F45" s="18">
+      <c r="F45" s="19">
         <v>0.958333333333333</v>
       </c>
       <c r="G45" s="2">
@@ -3462,10 +3463,10 @@
       <c r="C46" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D46" s="16">
+      <c r="D46" s="17">
         <v>45809</v>
       </c>
-      <c r="E46" s="18">
+      <c r="E46" s="19">
         <v>0.875</v>
       </c>
       <c r="F46" s="2"/>
@@ -3483,13 +3484,13 @@
       <c r="C47" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D47" s="17">
+      <c r="D47" s="18">
         <v>45822</v>
       </c>
-      <c r="E47" s="19">
+      <c r="E47" s="20">
         <v>0.0625</v>
       </c>
-      <c r="F47" s="19">
+      <c r="F47" s="20">
         <v>0.104166666666667</v>
       </c>
       <c r="G47" s="6">
@@ -3506,13 +3507,13 @@
       <c r="C48" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="D48" s="17">
+      <c r="D48" s="18">
         <v>45822</v>
       </c>
-      <c r="E48" s="19">
+      <c r="E48" s="20">
         <v>0.208333333333333</v>
       </c>
-      <c r="F48" s="19">
+      <c r="F48" s="20">
         <v>0.25</v>
       </c>
       <c r="G48" s="6">
@@ -3529,13 +3530,13 @@
       <c r="C49" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D49" s="17">
+      <c r="D49" s="18">
         <v>45823</v>
       </c>
-      <c r="E49" s="19">
+      <c r="E49" s="20">
         <v>0.0208333333333333</v>
       </c>
-      <c r="F49" s="19">
+      <c r="F49" s="20">
         <v>0.0625</v>
       </c>
       <c r="G49" s="6">
@@ -3552,13 +3553,13 @@
       <c r="C50" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D50" s="17">
+      <c r="D50" s="18">
         <v>45823</v>
       </c>
-      <c r="E50" s="19">
+      <c r="E50" s="20">
         <v>0.166666666666667</v>
       </c>
-      <c r="F50" s="19">
+      <c r="F50" s="20">
         <v>0.208333333333333</v>
       </c>
       <c r="G50" s="6">
@@ -3575,10 +3576,10 @@
       <c r="C51" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D51" s="17">
+      <c r="D51" s="18">
         <v>45824</v>
       </c>
-      <c r="E51" s="19">
+      <c r="E51" s="20">
         <v>0.0833333333333333</v>
       </c>
       <c r="F51" s="6"/>
@@ -3596,13 +3597,13 @@
       <c r="C52" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D52" s="16">
+      <c r="D52" s="17">
         <v>45835</v>
       </c>
-      <c r="E52" s="18">
+      <c r="E52" s="19">
         <v>0.8125</v>
       </c>
-      <c r="F52" s="18">
+      <c r="F52" s="19">
         <v>0.854166666666667</v>
       </c>
       <c r="G52" s="2">
@@ -3619,13 +3620,13 @@
       <c r="C53" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D53" s="16">
+      <c r="D53" s="17">
         <v>45835</v>
       </c>
-      <c r="E53" s="18">
+      <c r="E53" s="19">
         <v>0.958333333333333</v>
       </c>
-      <c r="F53" s="18">
+      <c r="F53" s="19">
         <v>0</v>
       </c>
       <c r="G53" s="2">
@@ -3642,13 +3643,13 @@
       <c r="C54" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D54" s="16">
+      <c r="D54" s="17">
         <v>45836</v>
       </c>
-      <c r="E54" s="18">
+      <c r="E54" s="19">
         <v>0.770833333333333</v>
       </c>
-      <c r="F54" s="18">
+      <c r="F54" s="19">
         <v>0.8125</v>
       </c>
       <c r="G54" s="2">
@@ -3665,13 +3666,13 @@
       <c r="C55" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D55" s="16">
+      <c r="D55" s="17">
         <v>45836</v>
       </c>
-      <c r="E55" s="18">
+      <c r="E55" s="19">
         <v>0.916666666666667</v>
       </c>
-      <c r="F55" s="18">
+      <c r="F55" s="19">
         <v>0.958333333333333</v>
       </c>
       <c r="G55" s="2">
@@ -3688,10 +3689,10 @@
       <c r="C56" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D56" s="16">
+      <c r="D56" s="17">
         <v>45837</v>
       </c>
-      <c r="E56" s="18">
+      <c r="E56" s="19">
         <v>0.875</v>
       </c>
       <c r="F56" s="2"/>
@@ -3709,13 +3710,13 @@
       <c r="C57" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D57" s="17">
+      <c r="D57" s="18">
         <v>45842</v>
       </c>
-      <c r="E57" s="19">
+      <c r="E57" s="20">
         <v>0.8125</v>
       </c>
-      <c r="F57" s="19">
+      <c r="F57" s="20">
         <v>0.854166666666667</v>
       </c>
       <c r="G57" s="6">
@@ -3732,13 +3733,13 @@
       <c r="C58" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="D58" s="17">
+      <c r="D58" s="18">
         <v>45842</v>
       </c>
-      <c r="E58" s="19">
+      <c r="E58" s="20">
         <v>0.958333333333333</v>
       </c>
-      <c r="F58" s="19">
+      <c r="F58" s="20">
         <v>0</v>
       </c>
       <c r="G58" s="6">
@@ -3755,13 +3756,13 @@
       <c r="C59" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D59" s="17">
+      <c r="D59" s="18">
         <v>45843</v>
       </c>
-      <c r="E59" s="19">
+      <c r="E59" s="20">
         <v>0.770833333333333</v>
       </c>
-      <c r="F59" s="19">
+      <c r="F59" s="20">
         <v>0.8125</v>
       </c>
       <c r="G59" s="6">
@@ -3778,13 +3779,13 @@
       <c r="C60" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D60" s="17">
+      <c r="D60" s="18">
         <v>45843</v>
       </c>
-      <c r="E60" s="19">
+      <c r="E60" s="20">
         <v>0.916666666666667</v>
       </c>
-      <c r="F60" s="19">
+      <c r="F60" s="20">
         <v>0.958333333333333</v>
       </c>
       <c r="G60" s="6">
@@ -3801,10 +3802,10 @@
       <c r="C61" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D61" s="17">
+      <c r="D61" s="18">
         <v>45844</v>
       </c>
-      <c r="E61" s="19">
+      <c r="E61" s="20">
         <v>0.916666666666667</v>
       </c>
       <c r="F61" s="6"/>
@@ -3822,13 +3823,13 @@
       <c r="C62" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D62" s="16">
+      <c r="D62" s="17">
         <v>45863</v>
       </c>
-      <c r="E62" s="18">
+      <c r="E62" s="19">
         <v>0.8125</v>
       </c>
-      <c r="F62" s="18">
+      <c r="F62" s="19">
         <v>0.854166666666667</v>
       </c>
       <c r="G62" s="2">
@@ -3845,13 +3846,13 @@
       <c r="C63" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D63" s="16">
+      <c r="D63" s="17">
         <v>45863</v>
       </c>
-      <c r="E63" s="18">
+      <c r="E63" s="19">
         <v>0.9375</v>
       </c>
-      <c r="F63" s="18">
+      <c r="F63" s="19">
         <v>0.968055555555556</v>
       </c>
       <c r="G63" s="2">
@@ -3868,13 +3869,13 @@
       <c r="C64" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D64" s="16">
+      <c r="D64" s="17">
         <v>45864</v>
       </c>
-      <c r="E64" s="18">
+      <c r="E64" s="19">
         <v>0.75</v>
       </c>
-      <c r="F64" s="18">
+      <c r="F64" s="19">
         <v>0.791666666666667</v>
       </c>
       <c r="G64" s="2">
@@ -3891,13 +3892,13 @@
       <c r="C65" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D65" s="16">
+      <c r="D65" s="17">
         <v>45864</v>
       </c>
-      <c r="E65" s="18">
+      <c r="E65" s="19">
         <v>0.916666666666667</v>
       </c>
-      <c r="F65" s="18">
+      <c r="F65" s="19">
         <v>0.958333333333333</v>
       </c>
       <c r="G65" s="2">
@@ -3914,10 +3915,10 @@
       <c r="C66" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D66" s="16">
+      <c r="D66" s="17">
         <v>45865</v>
       </c>
-      <c r="E66" s="18">
+      <c r="E66" s="19">
         <v>0.875</v>
       </c>
       <c r="F66" s="2"/>
@@ -3935,13 +3936,13 @@
       <c r="C67" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D67" s="17">
+      <c r="D67" s="18">
         <v>45870</v>
       </c>
-      <c r="E67" s="19">
+      <c r="E67" s="20">
         <v>0.8125</v>
       </c>
-      <c r="F67" s="19">
+      <c r="F67" s="20">
         <v>0.854166666666667</v>
       </c>
       <c r="G67" s="6">
@@ -3958,13 +3959,13 @@
       <c r="C68" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="D68" s="17">
+      <c r="D68" s="18">
         <v>45870</v>
       </c>
-      <c r="E68" s="19">
+      <c r="E68" s="20">
         <v>0.958333333333333</v>
       </c>
-      <c r="F68" s="19">
+      <c r="F68" s="20">
         <v>0</v>
       </c>
       <c r="G68" s="6">
@@ -3981,13 +3982,13 @@
       <c r="C69" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D69" s="17">
+      <c r="D69" s="18">
         <v>45871</v>
       </c>
-      <c r="E69" s="19">
+      <c r="E69" s="20">
         <v>0.770833333333333</v>
       </c>
-      <c r="F69" s="19">
+      <c r="F69" s="20">
         <v>0.8125</v>
       </c>
       <c r="G69" s="6">
@@ -4004,13 +4005,13 @@
       <c r="C70" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D70" s="17">
+      <c r="D70" s="18">
         <v>45871</v>
       </c>
-      <c r="E70" s="19">
+      <c r="E70" s="20">
         <v>0.916666666666667</v>
       </c>
-      <c r="F70" s="19">
+      <c r="F70" s="20">
         <v>0.958333333333333</v>
       </c>
       <c r="G70" s="6">
@@ -4027,10 +4028,10 @@
       <c r="C71" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D71" s="17">
+      <c r="D71" s="18">
         <v>45872</v>
       </c>
-      <c r="E71" s="19">
+      <c r="E71" s="20">
         <v>0.875</v>
       </c>
       <c r="F71" s="6"/>
@@ -4048,13 +4049,13 @@
       <c r="C72" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D72" s="16">
+      <c r="D72" s="17">
         <v>45898</v>
       </c>
-      <c r="E72" s="18">
+      <c r="E72" s="19">
         <v>0.770833333333333</v>
       </c>
-      <c r="F72" s="18">
+      <c r="F72" s="19">
         <v>0.8125</v>
       </c>
       <c r="G72" s="2">
@@ -4071,13 +4072,13 @@
       <c r="C73" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D73" s="16">
+      <c r="D73" s="17">
         <v>45898</v>
       </c>
-      <c r="E73" s="18">
+      <c r="E73" s="19">
         <v>0.916666666666667</v>
       </c>
-      <c r="F73" s="18">
+      <c r="F73" s="19">
         <v>0.958333333333333</v>
       </c>
       <c r="G73" s="2">
@@ -4094,13 +4095,13 @@
       <c r="C74" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D74" s="16">
+      <c r="D74" s="17">
         <v>45899</v>
       </c>
-      <c r="E74" s="18">
+      <c r="E74" s="19">
         <v>0.729166666666667</v>
       </c>
-      <c r="F74" s="18">
+      <c r="F74" s="19">
         <v>0.770833333333333</v>
       </c>
       <c r="G74" s="2">
@@ -4117,13 +4118,13 @@
       <c r="C75" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D75" s="16">
+      <c r="D75" s="17">
         <v>45899</v>
       </c>
-      <c r="E75" s="18">
+      <c r="E75" s="19">
         <v>0.875</v>
       </c>
-      <c r="F75" s="18">
+      <c r="F75" s="19">
         <v>0.916666666666667</v>
       </c>
       <c r="G75" s="2">
@@ -4140,13 +4141,13 @@
       <c r="C76" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D76" s="16">
+      <c r="D76" s="17">
         <v>45900</v>
       </c>
-      <c r="E76" s="18">
+      <c r="E76" s="19">
         <v>0.875</v>
       </c>
-      <c r="F76" s="18"/>
+      <c r="F76" s="19"/>
       <c r="G76" s="2">
         <v>1</v>
       </c>
@@ -4161,13 +4162,13 @@
       <c r="C77" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D77" s="17">
+      <c r="D77" s="18">
         <v>45905</v>
       </c>
-      <c r="E77" s="19">
+      <c r="E77" s="20">
         <v>0.8125</v>
       </c>
-      <c r="F77" s="19">
+      <c r="F77" s="20">
         <v>0.854166666666667</v>
       </c>
       <c r="G77" s="6">
@@ -4184,13 +4185,13 @@
       <c r="C78" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="D78" s="17">
+      <c r="D78" s="18">
         <v>45905</v>
       </c>
-      <c r="E78" s="19">
+      <c r="E78" s="20">
         <v>0.958333333333333</v>
       </c>
-      <c r="F78" s="19">
+      <c r="F78" s="20">
         <v>0</v>
       </c>
       <c r="G78" s="6">
@@ -4207,13 +4208,13 @@
       <c r="C79" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D79" s="17">
+      <c r="D79" s="18">
         <v>45906</v>
       </c>
-      <c r="E79" s="19">
+      <c r="E79" s="20">
         <v>0.770833333333333</v>
       </c>
-      <c r="F79" s="19">
+      <c r="F79" s="20">
         <v>0.8125</v>
       </c>
       <c r="G79" s="6">
@@ -4230,13 +4231,13 @@
       <c r="C80" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D80" s="17">
+      <c r="D80" s="18">
         <v>45906</v>
       </c>
-      <c r="E80" s="19">
+      <c r="E80" s="20">
         <v>0.916666666666667</v>
       </c>
-      <c r="F80" s="19">
+      <c r="F80" s="20">
         <v>0.958333333333333</v>
       </c>
       <c r="G80" s="6">
@@ -4253,10 +4254,10 @@
       <c r="C81" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D81" s="17">
+      <c r="D81" s="18">
         <v>45907</v>
       </c>
-      <c r="E81" s="19">
+      <c r="E81" s="20">
         <v>0.875</v>
       </c>
       <c r="F81" s="6"/>
@@ -4274,13 +4275,13 @@
       <c r="C82" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D82" s="16">
+      <c r="D82" s="17">
         <v>45919</v>
       </c>
-      <c r="E82" s="18">
+      <c r="E82" s="19">
         <v>0.6875</v>
       </c>
-      <c r="F82" s="18">
+      <c r="F82" s="19">
         <v>0.729166666666667</v>
       </c>
       <c r="G82" s="2">
@@ -4297,13 +4298,13 @@
       <c r="C83" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D83" s="16">
+      <c r="D83" s="17">
         <v>45919</v>
       </c>
-      <c r="E83" s="18">
+      <c r="E83" s="19">
         <v>0.833333333333333</v>
       </c>
-      <c r="F83" s="18">
+      <c r="F83" s="19">
         <v>0.875</v>
       </c>
       <c r="G83" s="2">
@@ -4320,13 +4321,13 @@
       <c r="C84" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D84" s="16">
+      <c r="D84" s="17">
         <v>45920</v>
       </c>
-      <c r="E84" s="18">
+      <c r="E84" s="19">
         <v>0.6875</v>
       </c>
-      <c r="F84" s="18">
+      <c r="F84" s="19">
         <v>0.729166666666667</v>
       </c>
       <c r="G84" s="2">
@@ -4343,13 +4344,13 @@
       <c r="C85" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D85" s="16">
+      <c r="D85" s="17">
         <v>45920</v>
       </c>
-      <c r="E85" s="18">
+      <c r="E85" s="19">
         <v>0.833333333333333</v>
       </c>
-      <c r="F85" s="18">
+      <c r="F85" s="19">
         <v>0.875</v>
       </c>
       <c r="G85" s="2">
@@ -4366,10 +4367,10 @@
       <c r="C86" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D86" s="16">
+      <c r="D86" s="17">
         <v>45921</v>
       </c>
-      <c r="E86" s="18">
+      <c r="E86" s="19">
         <v>0.791666666666667</v>
       </c>
       <c r="F86" s="2"/>
@@ -4387,13 +4388,13 @@
       <c r="C87" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D87" s="17">
+      <c r="D87" s="18">
         <v>45933</v>
       </c>
-      <c r="E87" s="19">
+      <c r="E87" s="20">
         <v>0.729166666666667</v>
       </c>
-      <c r="F87" s="19">
+      <c r="F87" s="20">
         <v>0.770833333333333</v>
       </c>
       <c r="G87" s="6">
@@ -4410,13 +4411,13 @@
       <c r="C88" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="D88" s="17">
+      <c r="D88" s="18">
         <v>45933</v>
       </c>
-      <c r="E88" s="19">
+      <c r="E88" s="20">
         <v>0.875</v>
       </c>
-      <c r="F88" s="19">
+      <c r="F88" s="20">
         <v>0.916666666666667</v>
       </c>
       <c r="G88" s="6">
@@ -4433,13 +4434,13 @@
       <c r="C89" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D89" s="17">
+      <c r="D89" s="18">
         <v>45934</v>
       </c>
-      <c r="E89" s="19">
+      <c r="E89" s="20">
         <v>0.729166666666667</v>
       </c>
-      <c r="F89" s="19">
+      <c r="F89" s="20">
         <v>0.770833333333333</v>
       </c>
       <c r="G89" s="6">
@@ -4456,13 +4457,13 @@
       <c r="C90" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D90" s="17">
+      <c r="D90" s="18">
         <v>45934</v>
       </c>
-      <c r="E90" s="19">
+      <c r="E90" s="20">
         <v>0.875</v>
       </c>
-      <c r="F90" s="19">
+      <c r="F90" s="20">
         <v>0.916666666666667</v>
       </c>
       <c r="G90" s="6">
@@ -4479,10 +4480,10 @@
       <c r="C91" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D91" s="17">
+      <c r="D91" s="18">
         <v>45935</v>
       </c>
-      <c r="E91" s="19">
+      <c r="E91" s="20">
         <v>0.833333333333333</v>
       </c>
       <c r="F91" s="6"/>
@@ -4500,13 +4501,13 @@
       <c r="C92" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D92" s="16">
+      <c r="D92" s="17">
         <v>45948</v>
       </c>
-      <c r="E92" s="18">
+      <c r="E92" s="19">
         <v>0.0625</v>
       </c>
-      <c r="F92" s="18">
+      <c r="F92" s="19">
         <v>0.104166666666667</v>
       </c>
       <c r="G92" s="2">
@@ -4523,13 +4524,13 @@
       <c r="C93" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D93" s="16">
+      <c r="D93" s="17">
         <v>45948</v>
       </c>
-      <c r="E93" s="18">
+      <c r="E93" s="19">
         <v>0.229166666666667</v>
       </c>
-      <c r="F93" s="18">
+      <c r="F93" s="19">
         <v>0.259722222222222</v>
       </c>
       <c r="G93" s="2">
@@ -4546,13 +4547,13 @@
       <c r="C94" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D94" s="16">
+      <c r="D94" s="17">
         <v>45949</v>
       </c>
-      <c r="E94" s="18">
+      <c r="E94" s="19">
         <v>0.0416666666666667</v>
       </c>
-      <c r="F94" s="18">
+      <c r="F94" s="19">
         <v>0.0625</v>
       </c>
       <c r="G94" s="2">
@@ -4569,13 +4570,13 @@
       <c r="C95" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D95" s="16">
+      <c r="D95" s="17">
         <v>45949</v>
       </c>
-      <c r="E95" s="18">
+      <c r="E95" s="19">
         <v>0.208333333333333</v>
       </c>
-      <c r="F95" s="18">
+      <c r="F95" s="19">
         <v>0.25</v>
       </c>
       <c r="G95" s="2">
@@ -4592,10 +4593,10 @@
       <c r="C96" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D96" s="16">
+      <c r="D96" s="17">
         <v>45950</v>
       </c>
-      <c r="E96" s="18">
+      <c r="E96" s="19">
         <v>0.125</v>
       </c>
       <c r="F96" s="2"/>
@@ -4613,13 +4614,13 @@
       <c r="C97" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D97" s="17">
+      <c r="D97" s="18">
         <v>45955</v>
       </c>
-      <c r="E97" s="19">
+      <c r="E97" s="20">
         <v>0.104166666666667</v>
       </c>
-      <c r="F97" s="19">
+      <c r="F97" s="20">
         <v>0.145833333333333</v>
       </c>
       <c r="G97" s="6">
@@ -4636,13 +4637,13 @@
       <c r="C98" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="D98" s="17">
+      <c r="D98" s="18">
         <v>45955</v>
       </c>
-      <c r="E98" s="19">
+      <c r="E98" s="20">
         <v>0.25</v>
       </c>
-      <c r="F98" s="19">
+      <c r="F98" s="20">
         <v>0.291666666666667</v>
       </c>
       <c r="G98" s="6">
@@ -4659,13 +4660,13 @@
       <c r="C99" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D99" s="17">
+      <c r="D99" s="18">
         <v>45956</v>
       </c>
-      <c r="E99" s="19">
+      <c r="E99" s="20">
         <v>0.0625</v>
       </c>
-      <c r="F99" s="19">
+      <c r="F99" s="20">
         <v>0.104166666666667</v>
       </c>
       <c r="G99" s="6">
@@ -4682,13 +4683,13 @@
       <c r="C100" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D100" s="17">
+      <c r="D100" s="18">
         <v>45956</v>
       </c>
-      <c r="E100" s="19">
+      <c r="E100" s="20">
         <v>0.208333333333333</v>
       </c>
-      <c r="F100" s="19">
+      <c r="F100" s="20">
         <v>0.25</v>
       </c>
       <c r="G100" s="6">
@@ -4705,10 +4706,10 @@
       <c r="C101" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D101" s="17">
+      <c r="D101" s="18">
         <v>45957</v>
       </c>
-      <c r="E101" s="19">
+      <c r="E101" s="20">
         <v>0.166666666666667</v>
       </c>
       <c r="F101" s="6"/>
@@ -4726,13 +4727,13 @@
       <c r="C102" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D102" s="16">
+      <c r="D102" s="17">
         <v>45968</v>
       </c>
-      <c r="E102" s="18">
+      <c r="E102" s="19">
         <v>0.9375</v>
       </c>
-      <c r="F102" s="18">
+      <c r="F102" s="19">
         <v>0.979166666666667</v>
       </c>
       <c r="G102" s="2">
@@ -4749,13 +4750,13 @@
       <c r="C103" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D103" s="16">
+      <c r="D103" s="17">
         <v>45969</v>
       </c>
-      <c r="E103" s="18">
+      <c r="E103" s="19">
         <v>0.104166666666667</v>
       </c>
-      <c r="F103" s="18">
+      <c r="F103" s="19">
         <v>0.134722222222222</v>
       </c>
       <c r="G103" s="2">
@@ -4772,13 +4773,13 @@
       <c r="C104" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D104" s="16">
+      <c r="D104" s="17">
         <v>45969</v>
       </c>
-      <c r="E104" s="18">
+      <c r="E104" s="19">
         <v>0.916666666666667</v>
       </c>
-      <c r="F104" s="18">
+      <c r="F104" s="19">
         <v>0.958333333333333</v>
       </c>
       <c r="G104" s="2">
@@ -4795,13 +4796,13 @@
       <c r="C105" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D105" s="16">
+      <c r="D105" s="17">
         <v>45970</v>
       </c>
-      <c r="E105" s="18">
+      <c r="E105" s="19">
         <v>0.0833333333333333</v>
       </c>
-      <c r="F105" s="18">
+      <c r="F105" s="19">
         <v>0.125</v>
       </c>
       <c r="G105" s="2">
@@ -4818,10 +4819,10 @@
       <c r="C106" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D106" s="16">
+      <c r="D106" s="17">
         <v>45971</v>
       </c>
-      <c r="E106" s="18">
+      <c r="E106" s="19">
         <v>0.0416666666666667</v>
       </c>
       <c r="F106" s="2"/>
@@ -4839,13 +4840,13 @@
       <c r="C107" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D107" s="17">
+      <c r="D107" s="18">
         <v>45982</v>
       </c>
-      <c r="E107" s="19">
+      <c r="E107" s="20">
         <v>0.354166666666667</v>
       </c>
-      <c r="F107" s="19">
+      <c r="F107" s="20">
         <v>0.395833333333333</v>
       </c>
       <c r="G107" s="6">
@@ -4862,13 +4863,13 @@
       <c r="C108" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="D108" s="17">
+      <c r="D108" s="18">
         <v>45982</v>
       </c>
-      <c r="E108" s="19">
+      <c r="E108" s="20">
         <v>0.5</v>
       </c>
-      <c r="F108" s="19">
+      <c r="F108" s="20">
         <v>0.541666666666667</v>
       </c>
       <c r="G108" s="6">
@@ -4885,13 +4886,13 @@
       <c r="C109" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D109" s="17">
+      <c r="D109" s="18">
         <v>45983</v>
       </c>
-      <c r="E109" s="20">
+      <c r="E109" s="21">
         <v>0.354166666666667</v>
       </c>
-      <c r="F109" s="20">
+      <c r="F109" s="21">
         <v>0.395833333333333</v>
       </c>
       <c r="G109" s="6">
@@ -4908,13 +4909,13 @@
       <c r="C110" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D110" s="17">
+      <c r="D110" s="18">
         <v>45983</v>
       </c>
-      <c r="E110" s="20">
+      <c r="E110" s="21">
         <v>0.5</v>
       </c>
-      <c r="F110" s="20">
+      <c r="F110" s="21">
         <v>0.541666666666667</v>
       </c>
       <c r="G110" s="6">
@@ -4931,10 +4932,10 @@
       <c r="C111" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D111" s="17">
+      <c r="D111" s="18">
         <v>45984</v>
       </c>
-      <c r="E111" s="20">
+      <c r="E111" s="21">
         <v>0.5</v>
       </c>
       <c r="F111" s="6"/>
@@ -4952,13 +4953,13 @@
       <c r="C112" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D112" s="16">
+      <c r="D112" s="17">
         <v>45989</v>
       </c>
-      <c r="E112" s="21">
+      <c r="E112" s="22">
         <v>0.895833333333333</v>
       </c>
-      <c r="F112" s="21">
+      <c r="F112" s="22">
         <v>0.9375</v>
       </c>
       <c r="G112" s="2">
@@ -4975,13 +4976,13 @@
       <c r="C113" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D113" s="16">
+      <c r="D113" s="17">
         <v>45990</v>
       </c>
-      <c r="E113" s="21">
+      <c r="E113" s="22">
         <v>0.0625</v>
       </c>
-      <c r="F113" s="21">
+      <c r="F113" s="22">
         <v>0.0930555555555556</v>
       </c>
       <c r="G113" s="2">
@@ -4998,13 +4999,13 @@
       <c r="C114" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D114" s="16">
+      <c r="D114" s="17">
         <v>45990</v>
       </c>
-      <c r="E114" s="21">
+      <c r="E114" s="22">
         <v>0.916666666666667</v>
       </c>
-      <c r="F114" s="21">
+      <c r="F114" s="22">
         <v>0.958333333333333</v>
       </c>
       <c r="G114" s="2">
@@ -5021,13 +5022,13 @@
       <c r="C115" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D115" s="16">
+      <c r="D115" s="17">
         <v>45991</v>
       </c>
-      <c r="E115" s="21">
+      <c r="E115" s="22">
         <v>0.0833333333333333</v>
       </c>
-      <c r="F115" s="21">
+      <c r="F115" s="22">
         <v>0.125</v>
       </c>
       <c r="G115" s="2">
@@ -5044,10 +5045,10 @@
       <c r="C116" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D116" s="16">
+      <c r="D116" s="17">
         <v>45992</v>
       </c>
-      <c r="E116" s="21">
+      <c r="E116" s="22">
         <v>0</v>
       </c>
       <c r="F116" s="2"/>
@@ -5065,13 +5066,13 @@
       <c r="C117" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D117" s="17">
+      <c r="D117" s="18">
         <v>45996</v>
       </c>
-      <c r="E117" s="20">
+      <c r="E117" s="21">
         <v>0.729166666666667</v>
       </c>
-      <c r="F117" s="20">
+      <c r="F117" s="21">
         <v>0.770833333333333</v>
       </c>
       <c r="G117" s="6">
@@ -5088,13 +5089,13 @@
       <c r="C118" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="D118" s="17">
+      <c r="D118" s="18">
         <v>45996</v>
       </c>
-      <c r="E118" s="20">
+      <c r="E118" s="21">
         <v>0.875</v>
       </c>
-      <c r="F118" s="20">
+      <c r="F118" s="21">
         <v>0.916666666666667</v>
       </c>
       <c r="G118" s="6">
@@ -5111,13 +5112,13 @@
       <c r="C119" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D119" s="17">
+      <c r="D119" s="18">
         <v>45997</v>
       </c>
-      <c r="E119" s="20">
+      <c r="E119" s="21">
         <v>0.770833333333333</v>
       </c>
-      <c r="F119" s="20">
+      <c r="F119" s="21">
         <v>0.8125</v>
       </c>
       <c r="G119" s="6">
@@ -5134,13 +5135,13 @@
       <c r="C120" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D120" s="17">
+      <c r="D120" s="18">
         <v>45997</v>
       </c>
-      <c r="E120" s="20">
+      <c r="E120" s="21">
         <v>0.916666666666667</v>
       </c>
-      <c r="F120" s="20">
+      <c r="F120" s="21">
         <v>0.958333333333333</v>
       </c>
       <c r="G120" s="6">
@@ -5157,10 +5158,10 @@
       <c r="C121" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D121" s="17">
+      <c r="D121" s="18">
         <v>45998</v>
       </c>
-      <c r="E121" s="20">
+      <c r="E121" s="21">
         <v>0.875</v>
       </c>
       <c r="F121" s="6"/>
@@ -5177,7 +5178,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R1041"/>
+  <dimension ref="A1:R1081"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -5187,6 +5188,7 @@
     <col min="5" max="5" width="8.85714285714286" customWidth="1"/>
     <col min="6" max="6" width="16.4285714285714" customWidth="1"/>
     <col min="7" max="7" width="31.1428571428571" customWidth="1"/>
+    <col min="8" max="10" width="12.7857142857143"/>
     <col min="11" max="11" width="18.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
@@ -32376,19 +32378,19 @@
       <c r="C1022" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D1022" s="15">
+      <c r="D1022" s="2">
         <v>1</v>
       </c>
-      <c r="E1022" s="15">
+      <c r="E1022" s="2">
         <v>4</v>
       </c>
-      <c r="F1022" s="15" t="s">
+      <c r="F1022" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="G1022" s="15" t="s">
+      <c r="G1022" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="H1022" s="15">
+      <c r="H1022" s="2">
         <v>25</v>
       </c>
     </row>
@@ -32402,19 +32404,19 @@
       <c r="C1023" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D1023" s="15">
+      <c r="D1023" s="2">
         <v>2</v>
       </c>
-      <c r="E1023" s="15">
+      <c r="E1023" s="2">
         <v>12</v>
       </c>
-      <c r="F1023" s="15" t="s">
+      <c r="F1023" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="G1023" s="15" t="s">
+      <c r="G1023" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="H1023" s="15">
+      <c r="H1023" s="2">
         <v>18</v>
       </c>
     </row>
@@ -32428,19 +32430,19 @@
       <c r="C1024" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D1024" s="15">
+      <c r="D1024" s="2">
         <v>3</v>
       </c>
-      <c r="E1024" s="15">
+      <c r="E1024" s="2">
         <v>1</v>
       </c>
-      <c r="F1024" s="15" t="s">
+      <c r="F1024" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="G1024" s="15" t="s">
+      <c r="G1024" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="H1024" s="15">
+      <c r="H1024" s="2">
         <v>15</v>
       </c>
     </row>
@@ -32454,19 +32456,19 @@
       <c r="C1025" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D1025" s="15">
+      <c r="D1025" s="2">
         <v>4</v>
       </c>
-      <c r="E1025" s="15">
+      <c r="E1025" s="2">
         <v>63</v>
       </c>
-      <c r="F1025" s="15" t="s">
+      <c r="F1025" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="G1025" s="15" t="s">
+      <c r="G1025" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="H1025" s="15">
+      <c r="H1025" s="2">
         <v>12</v>
       </c>
     </row>
@@ -32480,19 +32482,19 @@
       <c r="C1026" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D1026" s="15">
+      <c r="D1026" s="2">
         <v>5</v>
       </c>
-      <c r="E1026" s="15">
+      <c r="E1026" s="2">
         <v>81</v>
       </c>
-      <c r="F1026" s="15" t="s">
+      <c r="F1026" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="G1026" s="15" t="s">
+      <c r="G1026" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="H1026" s="15">
+      <c r="H1026" s="2">
         <v>10</v>
       </c>
     </row>
@@ -32506,19 +32508,19 @@
       <c r="C1027" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D1027" s="15">
+      <c r="D1027" s="2">
         <v>6</v>
       </c>
-      <c r="E1027" s="15">
+      <c r="E1027" s="2">
         <v>87</v>
       </c>
-      <c r="F1027" s="15" t="s">
+      <c r="F1027" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="G1027" s="15" t="s">
+      <c r="G1027" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="H1027" s="15">
+      <c r="H1027" s="2">
         <v>8</v>
       </c>
     </row>
@@ -32532,19 +32534,19 @@
       <c r="C1028" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D1028" s="15">
+      <c r="D1028" s="2">
         <v>7</v>
       </c>
-      <c r="E1028" s="15">
+      <c r="E1028" s="2">
         <v>30</v>
       </c>
-      <c r="F1028" s="15" t="s">
+      <c r="F1028" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="G1028" s="15" t="s">
+      <c r="G1028" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="H1028" s="15">
+      <c r="H1028" s="2">
         <v>6</v>
       </c>
     </row>
@@ -32558,19 +32560,19 @@
       <c r="C1029" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D1029" s="15">
+      <c r="D1029" s="2">
         <v>8</v>
       </c>
-      <c r="E1029" s="15">
+      <c r="E1029" s="2">
         <v>6</v>
       </c>
-      <c r="F1029" s="15" t="s">
+      <c r="F1029" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="G1029" s="15" t="s">
+      <c r="G1029" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="H1029" s="15">
+      <c r="H1029" s="2">
         <v>4</v>
       </c>
     </row>
@@ -32584,19 +32586,19 @@
       <c r="C1030" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D1030" s="15">
+      <c r="D1030" s="2">
         <v>9</v>
       </c>
-      <c r="E1030" s="15">
+      <c r="E1030" s="2">
         <v>27</v>
       </c>
-      <c r="F1030" s="15" t="s">
+      <c r="F1030" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="G1030" s="15" t="s">
+      <c r="G1030" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="H1030" s="15">
+      <c r="H1030" s="2">
         <v>2</v>
       </c>
     </row>
@@ -32610,19 +32612,19 @@
       <c r="C1031" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D1031" s="15">
+      <c r="D1031" s="2">
         <v>10</v>
       </c>
-      <c r="E1031" s="15">
+      <c r="E1031" s="2">
         <v>10</v>
       </c>
-      <c r="F1031" s="15" t="s">
+      <c r="F1031" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="G1031" s="15" t="s">
+      <c r="G1031" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="H1031" s="15">
+      <c r="H1031" s="2">
         <v>1</v>
       </c>
     </row>
@@ -32636,19 +32638,19 @@
       <c r="C1032" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D1032" s="15">
+      <c r="D1032" s="2">
         <v>11</v>
       </c>
-      <c r="E1032" s="15">
+      <c r="E1032" s="2">
         <v>23</v>
       </c>
-      <c r="F1032" s="15" t="s">
+      <c r="F1032" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="G1032" s="15" t="s">
+      <c r="G1032" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="H1032" s="15">
+      <c r="H1032" s="2">
         <v>0</v>
       </c>
     </row>
@@ -32662,19 +32664,19 @@
       <c r="C1033" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D1033" s="15">
+      <c r="D1033" s="2">
         <v>12</v>
       </c>
-      <c r="E1033" s="15">
+      <c r="E1033" s="2">
         <v>31</v>
       </c>
-      <c r="F1033" s="15" t="s">
+      <c r="F1033" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="G1033" s="15" t="s">
+      <c r="G1033" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="H1033" s="15">
+      <c r="H1033" s="2">
         <v>0</v>
       </c>
     </row>
@@ -32688,19 +32690,19 @@
       <c r="C1034" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D1034" s="15">
+      <c r="D1034" s="2">
         <v>13</v>
       </c>
-      <c r="E1034" s="15">
+      <c r="E1034" s="2">
         <v>55</v>
       </c>
-      <c r="F1034" s="15" t="s">
+      <c r="F1034" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="G1034" s="15" t="s">
+      <c r="G1034" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="H1034" s="15">
+      <c r="H1034" s="2">
         <v>0</v>
       </c>
     </row>
@@ -32714,19 +32716,19 @@
       <c r="C1035" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D1035" s="15">
+      <c r="D1035" s="2">
         <v>14</v>
       </c>
-      <c r="E1035" s="15">
+      <c r="E1035" s="2">
         <v>14</v>
       </c>
-      <c r="F1035" s="15" t="s">
+      <c r="F1035" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="G1035" s="15" t="s">
+      <c r="G1035" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="H1035" s="15">
+      <c r="H1035" s="2">
         <v>0</v>
       </c>
     </row>
@@ -32740,19 +32742,19 @@
       <c r="C1036" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D1036" s="15">
+      <c r="D1036" s="2">
         <v>15</v>
       </c>
-      <c r="E1036" s="15">
+      <c r="E1036" s="2">
         <v>43</v>
       </c>
-      <c r="F1036" s="15" t="s">
+      <c r="F1036" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="G1036" s="15" t="s">
+      <c r="G1036" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="H1036" s="15">
+      <c r="H1036" s="2">
         <v>0</v>
       </c>
     </row>
@@ -32766,19 +32768,19 @@
       <c r="C1037" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D1037" s="15">
+      <c r="D1037" s="2">
         <v>16</v>
       </c>
-      <c r="E1037" s="15">
+      <c r="E1037" s="2">
         <v>18</v>
       </c>
-      <c r="F1037" s="15" t="s">
+      <c r="F1037" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="G1037" s="15" t="s">
+      <c r="G1037" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="H1037" s="15">
+      <c r="H1037" s="2">
         <v>0</v>
       </c>
     </row>
@@ -32792,19 +32794,19 @@
       <c r="C1038" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D1038" s="15">
+      <c r="D1038" s="2">
         <v>17</v>
       </c>
-      <c r="E1038" s="15">
+      <c r="E1038" s="2">
         <v>22</v>
       </c>
-      <c r="F1038" s="15" t="s">
+      <c r="F1038" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="G1038" s="15" t="s">
+      <c r="G1038" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="H1038" s="15">
+      <c r="H1038" s="2">
         <v>0</v>
       </c>
     </row>
@@ -32818,19 +32820,19 @@
       <c r="C1039" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D1039" s="15" t="s">
+      <c r="D1039" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="E1039" s="15">
+      <c r="E1039" s="2">
         <v>44</v>
       </c>
-      <c r="F1039" s="15" t="s">
+      <c r="F1039" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="G1039" s="15" t="s">
+      <c r="G1039" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="H1039" s="15">
+      <c r="H1039" s="2">
         <v>0</v>
       </c>
     </row>
@@ -32844,19 +32846,19 @@
       <c r="C1040" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D1040" s="15" t="s">
+      <c r="D1040" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="E1040" s="15">
+      <c r="E1040" s="2">
         <v>16</v>
       </c>
-      <c r="F1040" s="15" t="s">
+      <c r="F1040" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="G1040" s="15" t="s">
+      <c r="G1040" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="H1040" s="15">
+      <c r="H1040" s="2">
         <v>0</v>
       </c>
     </row>
@@ -32870,24 +32872,1024 @@
       <c r="C1041" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D1041" s="15" t="s">
+      <c r="D1041" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="E1041" s="15">
+      <c r="E1041" s="2">
         <v>5</v>
       </c>
-      <c r="F1041" s="15" t="s">
+      <c r="F1041" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="G1041" s="15" t="s">
+      <c r="G1041" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="H1041" s="15">
+      <c r="H1041" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1042" spans="1:8">
+      <c r="A1042" s="6">
+        <v>2025</v>
+      </c>
+      <c r="B1042" s="6">
+        <v>22</v>
+      </c>
+      <c r="C1042" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1042" s="6">
+        <v>1</v>
+      </c>
+      <c r="E1042" s="6">
+        <v>4</v>
+      </c>
+      <c r="F1042" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="G1042" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="H1042" s="6"/>
+    </row>
+    <row r="1043" spans="1:8">
+      <c r="A1043" s="6">
+        <v>2025</v>
+      </c>
+      <c r="B1043" s="6">
+        <v>22</v>
+      </c>
+      <c r="C1043" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1043" s="6">
+        <v>2</v>
+      </c>
+      <c r="E1043" s="6">
+        <v>1</v>
+      </c>
+      <c r="F1043" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="G1043" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="H1043" s="6"/>
+    </row>
+    <row r="1044" spans="1:8">
+      <c r="A1044" s="6">
+        <v>2025</v>
+      </c>
+      <c r="B1044" s="6">
+        <v>22</v>
+      </c>
+      <c r="C1044" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1044" s="6">
+        <v>3</v>
+      </c>
+      <c r="E1044" s="6">
+        <v>55</v>
+      </c>
+      <c r="F1044" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="G1044" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="H1044" s="6"/>
+    </row>
+    <row r="1045" spans="1:8">
+      <c r="A1045" s="6">
+        <v>2025</v>
+      </c>
+      <c r="B1045" s="6">
+        <v>22</v>
+      </c>
+      <c r="C1045" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1045" s="6">
+        <v>4</v>
+      </c>
+      <c r="E1045" s="6">
+        <v>63</v>
+      </c>
+      <c r="F1045" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="G1045" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="H1045" s="6"/>
+    </row>
+    <row r="1046" spans="1:8">
+      <c r="A1046" s="6">
+        <v>2025</v>
+      </c>
+      <c r="B1046" s="6">
+        <v>22</v>
+      </c>
+      <c r="C1046" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1046" s="6">
+        <v>5</v>
+      </c>
+      <c r="E1046" s="6">
+        <v>81</v>
+      </c>
+      <c r="F1046" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="G1046" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="H1046" s="6"/>
+    </row>
+    <row r="1047" spans="1:8">
+      <c r="A1047" s="6">
+        <v>2025</v>
+      </c>
+      <c r="B1047" s="6">
+        <v>22</v>
+      </c>
+      <c r="C1047" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1047" s="6">
+        <v>6</v>
+      </c>
+      <c r="E1047" s="6">
+        <v>30</v>
+      </c>
+      <c r="F1047" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="G1047" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="H1047" s="6"/>
+    </row>
+    <row r="1048" spans="1:8">
+      <c r="A1048" s="6">
+        <v>2025</v>
+      </c>
+      <c r="B1048" s="6">
+        <v>22</v>
+      </c>
+      <c r="C1048" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1048" s="6">
+        <v>7</v>
+      </c>
+      <c r="E1048" s="6">
+        <v>14</v>
+      </c>
+      <c r="F1048" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="G1048" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="H1048" s="6"/>
+    </row>
+    <row r="1049" spans="1:8">
+      <c r="A1049" s="6">
+        <v>2025</v>
+      </c>
+      <c r="B1049" s="6">
+        <v>22</v>
+      </c>
+      <c r="C1049" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1049" s="6">
+        <v>8</v>
+      </c>
+      <c r="E1049" s="6">
+        <v>6</v>
+      </c>
+      <c r="F1049" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="G1049" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="H1049" s="6"/>
+    </row>
+    <row r="1050" spans="1:8">
+      <c r="A1050" s="6">
+        <v>2025</v>
+      </c>
+      <c r="B1050" s="6">
+        <v>22</v>
+      </c>
+      <c r="C1050" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1050" s="6">
+        <v>9</v>
+      </c>
+      <c r="E1050" s="6">
+        <v>16</v>
+      </c>
+      <c r="F1050" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="G1050" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="H1050" s="6"/>
+    </row>
+    <row r="1051" spans="1:8">
+      <c r="A1051" s="6">
+        <v>2025</v>
+      </c>
+      <c r="B1051" s="6">
+        <v>22</v>
+      </c>
+      <c r="C1051" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1051" s="6">
+        <v>10</v>
+      </c>
+      <c r="E1051" s="6">
+        <v>10</v>
+      </c>
+      <c r="F1051" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="G1051" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="H1051" s="6"/>
+    </row>
+    <row r="1052" spans="1:8">
+      <c r="A1052" s="6">
+        <v>2025</v>
+      </c>
+      <c r="B1052" s="6">
+        <v>22</v>
+      </c>
+      <c r="C1052" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1052" s="6">
+        <v>11</v>
+      </c>
+      <c r="E1052" s="6">
+        <v>27</v>
+      </c>
+      <c r="F1052" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="G1052" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="H1052" s="6"/>
+    </row>
+    <row r="1053" spans="1:8">
+      <c r="A1053" s="6">
+        <v>2025</v>
+      </c>
+      <c r="B1053" s="6">
+        <v>22</v>
+      </c>
+      <c r="C1053" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1053" s="6">
+        <v>12</v>
+      </c>
+      <c r="E1053" s="6">
+        <v>18</v>
+      </c>
+      <c r="F1053" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1053" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="H1053" s="6"/>
+    </row>
+    <row r="1054" spans="1:8">
+      <c r="A1054" s="6">
+        <v>2025</v>
+      </c>
+      <c r="B1054" s="6">
+        <v>22</v>
+      </c>
+      <c r="C1054" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1054" s="6">
+        <v>13</v>
+      </c>
+      <c r="E1054" s="6">
+        <v>31</v>
+      </c>
+      <c r="F1054" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="G1054" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="H1054" s="6"/>
+    </row>
+    <row r="1055" spans="1:8">
+      <c r="A1055" s="6">
+        <v>2025</v>
+      </c>
+      <c r="B1055" s="6">
+        <v>22</v>
+      </c>
+      <c r="C1055" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1055" s="6">
+        <v>14</v>
+      </c>
+      <c r="E1055" s="6">
+        <v>87</v>
+      </c>
+      <c r="F1055" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="G1055" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="H1055" s="6"/>
+    </row>
+    <row r="1056" spans="1:8">
+      <c r="A1056" s="6">
+        <v>2025</v>
+      </c>
+      <c r="B1056" s="6">
+        <v>22</v>
+      </c>
+      <c r="C1056" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1056" s="6">
+        <v>15</v>
+      </c>
+      <c r="E1056" s="6">
+        <v>43</v>
+      </c>
+      <c r="F1056" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="G1056" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="H1056" s="6"/>
+    </row>
+    <row r="1057" spans="1:8">
+      <c r="A1057" s="6">
+        <v>2025</v>
+      </c>
+      <c r="B1057" s="6">
+        <v>22</v>
+      </c>
+      <c r="C1057" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1057" s="6">
+        <v>16</v>
+      </c>
+      <c r="E1057" s="6">
+        <v>23</v>
+      </c>
+      <c r="F1057" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="G1057" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="H1057" s="6"/>
+    </row>
+    <row r="1058" spans="1:8">
+      <c r="A1058" s="6">
+        <v>2025</v>
+      </c>
+      <c r="B1058" s="6">
+        <v>22</v>
+      </c>
+      <c r="C1058" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1058" s="6">
+        <v>17</v>
+      </c>
+      <c r="E1058" s="6">
+        <v>12</v>
+      </c>
+      <c r="F1058" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="G1058" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="H1058" s="6"/>
+    </row>
+    <row r="1059" spans="1:8">
+      <c r="A1059" s="6">
+        <v>2025</v>
+      </c>
+      <c r="B1059" s="6">
+        <v>22</v>
+      </c>
+      <c r="C1059" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1059" s="6">
+        <v>18</v>
+      </c>
+      <c r="E1059" s="6">
+        <v>5</v>
+      </c>
+      <c r="F1059" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="G1059" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="H1059" s="6"/>
+    </row>
+    <row r="1060" spans="1:8">
+      <c r="A1060" s="6">
+        <v>2025</v>
+      </c>
+      <c r="B1060" s="6">
+        <v>22</v>
+      </c>
+      <c r="C1060" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1060" s="6">
+        <v>19</v>
+      </c>
+      <c r="E1060" s="6">
+        <v>22</v>
+      </c>
+      <c r="F1060" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="G1060" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="H1060" s="6"/>
+    </row>
+    <row r="1061" spans="1:8">
+      <c r="A1061" s="6">
+        <v>2025</v>
+      </c>
+      <c r="B1061" s="6">
+        <v>22</v>
+      </c>
+      <c r="C1061" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1061" s="6">
+        <v>20</v>
+      </c>
+      <c r="E1061" s="6">
+        <v>44</v>
+      </c>
+      <c r="F1061" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="G1061" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="H1061" s="6"/>
+    </row>
+    <row r="1062" spans="1:8">
+      <c r="A1062" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B1062" s="15">
+        <v>22</v>
+      </c>
+      <c r="C1062" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1062" s="16">
+        <v>1</v>
+      </c>
+      <c r="E1062" s="16">
+        <v>1</v>
+      </c>
+      <c r="F1062" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="G1062" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="H1062" s="16">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1063" spans="1:8">
+      <c r="A1063" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B1063" s="15">
+        <v>22</v>
+      </c>
+      <c r="C1063" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1063" s="16">
+        <v>2</v>
+      </c>
+      <c r="E1063" s="16">
+        <v>63</v>
+      </c>
+      <c r="F1063" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="G1063" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="H1063" s="16">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1064" spans="1:8">
+      <c r="A1064" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B1064" s="15">
+        <v>22</v>
+      </c>
+      <c r="C1064" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1064" s="16">
+        <v>3</v>
+      </c>
+      <c r="E1064" s="16">
+        <v>12</v>
+      </c>
+      <c r="F1064" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="G1064" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="H1064" s="16">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1065" spans="1:8">
+      <c r="A1065" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B1065" s="15">
+        <v>22</v>
+      </c>
+      <c r="C1065" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1065" s="16">
+        <v>4</v>
+      </c>
+      <c r="E1065" s="16">
+        <v>16</v>
+      </c>
+      <c r="F1065" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="G1065" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="H1065" s="16">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1066" spans="1:8">
+      <c r="A1066" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B1066" s="15">
+        <v>22</v>
+      </c>
+      <c r="C1066" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1066" s="16">
+        <v>5</v>
+      </c>
+      <c r="E1066" s="16">
+        <v>55</v>
+      </c>
+      <c r="F1066" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="G1066" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="H1066" s="16">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1067" spans="1:8">
+      <c r="A1067" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B1067" s="15">
+        <v>22</v>
+      </c>
+      <c r="C1067" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1067" s="16">
+        <v>6</v>
+      </c>
+      <c r="E1067" s="16">
+        <v>6</v>
+      </c>
+      <c r="F1067" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="G1067" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="H1067" s="16">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1068" spans="1:8">
+      <c r="A1068" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B1068" s="15">
+        <v>22</v>
+      </c>
+      <c r="C1068" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1068" s="16">
+        <v>7</v>
+      </c>
+      <c r="E1068" s="16">
+        <v>27</v>
+      </c>
+      <c r="F1068" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="G1068" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="H1068" s="16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1069" spans="1:8">
+      <c r="A1069" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B1069" s="15">
+        <v>22</v>
+      </c>
+      <c r="C1069" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1069" s="16">
+        <v>8</v>
+      </c>
+      <c r="E1069" s="16">
+        <v>44</v>
+      </c>
+      <c r="F1069" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="G1069" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="H1069" s="16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1070" spans="1:8">
+      <c r="A1070" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B1070" s="15">
+        <v>22</v>
+      </c>
+      <c r="C1070" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1070" s="16">
+        <v>9</v>
+      </c>
+      <c r="E1070" s="16">
+        <v>31</v>
+      </c>
+      <c r="F1070" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="G1070" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="H1070" s="16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1071" spans="1:8">
+      <c r="A1071" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B1071" s="15">
+        <v>22</v>
+      </c>
+      <c r="C1071" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1071" s="16">
+        <v>10</v>
+      </c>
+      <c r="E1071" s="16">
+        <v>87</v>
+      </c>
+      <c r="F1071" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="G1071" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="H1071" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1072" spans="1:8">
+      <c r="A1072" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B1072" s="15">
+        <v>22</v>
+      </c>
+      <c r="C1072" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1072" s="16">
+        <v>11</v>
+      </c>
+      <c r="E1072" s="16">
+        <v>14</v>
+      </c>
+      <c r="F1072" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="G1072" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="H1072" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1073" spans="1:8">
+      <c r="A1073" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B1073" s="15">
+        <v>22</v>
+      </c>
+      <c r="C1073" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1073" s="16">
+        <v>12</v>
+      </c>
+      <c r="E1073" s="16">
+        <v>22</v>
+      </c>
+      <c r="F1073" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="G1073" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="H1073" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1074" spans="1:8">
+      <c r="A1074" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B1074" s="15">
+        <v>22</v>
+      </c>
+      <c r="C1074" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1074" s="16">
+        <v>13</v>
+      </c>
+      <c r="E1074" s="16">
+        <v>10</v>
+      </c>
+      <c r="F1074" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="G1074" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="H1074" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1075" spans="1:8">
+      <c r="A1075" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B1075" s="15">
+        <v>22</v>
+      </c>
+      <c r="C1075" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1075" s="16">
+        <v>14</v>
+      </c>
+      <c r="E1075" s="16">
+        <v>30</v>
+      </c>
+      <c r="F1075" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="G1075" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="H1075" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1076" spans="1:8">
+      <c r="A1076" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B1076" s="15">
+        <v>22</v>
+      </c>
+      <c r="C1076" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1076" s="16">
+        <v>15</v>
+      </c>
+      <c r="E1076" s="16">
+        <v>43</v>
+      </c>
+      <c r="F1076" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="G1076" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="H1076" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1077" spans="1:8">
+      <c r="A1077" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B1077" s="15">
+        <v>22</v>
+      </c>
+      <c r="C1077" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1077" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="E1077" s="16">
+        <v>4</v>
+      </c>
+      <c r="F1077" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="G1077" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="H1077" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1078" spans="1:8">
+      <c r="A1078" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B1078" s="15">
+        <v>22</v>
+      </c>
+      <c r="C1078" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1078" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="E1078" s="16">
+        <v>81</v>
+      </c>
+      <c r="F1078" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="G1078" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="H1078" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1079" spans="1:8">
+      <c r="A1079" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B1079" s="15">
+        <v>22</v>
+      </c>
+      <c r="C1079" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1079" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="E1079" s="16">
+        <v>23</v>
+      </c>
+      <c r="F1079" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G1079" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="H1079" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1080" spans="1:8">
+      <c r="A1080" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B1080" s="15">
+        <v>22</v>
+      </c>
+      <c r="C1080" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1080" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="E1080" s="16">
+        <v>5</v>
+      </c>
+      <c r="F1080" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="G1080" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="H1080" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1081" spans="1:8">
+      <c r="A1081" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B1081" s="15">
+        <v>22</v>
+      </c>
+      <c r="C1081" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1081" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="E1081" s="16">
+        <v>18</v>
+      </c>
+      <c r="F1081" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1081" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="H1081" s="16">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H1021" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H1061" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -32913,7 +33915,7 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>2</v>
+        <v>146</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>3</v>
@@ -32935,7 +33937,9 @@
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="2"/>
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
       <c r="B2" s="2" t="s">
         <v>10</v>
       </c>
@@ -32954,7 +33958,9 @@
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="2"/>
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
       <c r="B3" s="2" t="s">
         <v>13</v>
       </c>
@@ -32973,7 +33979,9 @@
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="2"/>
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
       <c r="B4" s="2" t="s">
         <v>16</v>
       </c>
@@ -32992,7 +34000,9 @@
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="2"/>
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
       <c r="B5" s="2" t="s">
         <v>19</v>
       </c>
@@ -33011,7 +34021,9 @@
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="2"/>
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
       <c r="B6" s="2" t="s">
         <v>22</v>
       </c>
@@ -33030,7 +34042,9 @@
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="2"/>
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
       <c r="B7" s="2" t="s">
         <v>25</v>
       </c>
@@ -33051,7 +34065,9 @@
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="2"/>
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
       <c r="B8" s="2" t="s">
         <v>29</v>
       </c>
@@ -33072,7 +34088,9 @@
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="2"/>
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
       <c r="B9" s="2" t="s">
         <v>33</v>
       </c>
@@ -33091,7 +34109,9 @@
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="2"/>
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
       <c r="B10" s="2" t="s">
         <v>36</v>
       </c>
@@ -33110,7 +34130,9 @@
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="2"/>
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
       <c r="B11" s="2" t="s">
         <v>39</v>
       </c>
@@ -33129,7 +34151,9 @@
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="2"/>
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
       <c r="B12" s="2" t="s">
         <v>42</v>
       </c>
@@ -33148,7 +34172,9 @@
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="2"/>
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
       <c r="B13" s="2" t="s">
         <v>45</v>
       </c>
@@ -33167,7 +34193,9 @@
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="2"/>
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
       <c r="B14" s="2" t="s">
         <v>48</v>
       </c>
@@ -33186,7 +34214,9 @@
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="2"/>
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
       <c r="B15" s="2" t="s">
         <v>51</v>
       </c>
@@ -33205,7 +34235,9 @@
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="2"/>
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
       <c r="B16" s="2" t="s">
         <v>54</v>
       </c>
@@ -33224,7 +34256,9 @@
       </c>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="2"/>
+      <c r="A17" s="2">
+        <v>16</v>
+      </c>
       <c r="B17" s="2" t="s">
         <v>29</v>
       </c>
@@ -33245,7 +34279,9 @@
       </c>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="2"/>
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
       <c r="B18" s="2" t="s">
         <v>60</v>
       </c>
@@ -33264,7 +34300,9 @@
       </c>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="2"/>
+      <c r="A19" s="2">
+        <v>18</v>
+      </c>
       <c r="B19" s="2" t="s">
         <v>63</v>
       </c>
@@ -33283,7 +34321,9 @@
       </c>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="2"/>
+      <c r="A20" s="2">
+        <v>19</v>
+      </c>
       <c r="B20" s="2" t="s">
         <v>25</v>
       </c>
@@ -33304,7 +34344,9 @@
       </c>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="2"/>
+      <c r="A21" s="2">
+        <v>20</v>
+      </c>
       <c r="B21" s="2" t="s">
         <v>69</v>
       </c>
@@ -33323,7 +34365,9 @@
       </c>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="2"/>
+      <c r="A22" s="2">
+        <v>21</v>
+      </c>
       <c r="B22" s="2" t="s">
         <v>72</v>
       </c>
@@ -33342,7 +34386,9 @@
       </c>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="2"/>
+      <c r="A23" s="2">
+        <v>22</v>
+      </c>
       <c r="B23" s="2" t="s">
         <v>25</v>
       </c>
@@ -33363,7 +34409,9 @@
       </c>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="2"/>
+      <c r="A24" s="2">
+        <v>23</v>
+      </c>
       <c r="B24" s="2" t="s">
         <v>78</v>
       </c>
@@ -33382,7 +34430,9 @@
       </c>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="2"/>
+      <c r="A25" s="2">
+        <v>24</v>
+      </c>
       <c r="B25" s="2" t="s">
         <v>81</v>
       </c>

--- a/public/docs/datas/f1.xlsx
+++ b/public/docs/datas/f1.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Docs\byMe\vue_platform\public\docs\datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8103B34-C4FD-4DBF-A32F-56AFB3A23F17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="28860" windowHeight="12860" activeTab="5"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11835" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="rounds" sheetId="1" r:id="rId1"/>
@@ -35,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4204" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4209" uniqueCount="218">
   <si>
     <t>year</t>
   </si>
@@ -694,174 +700,24 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="21">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="35">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -880,194 +736,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1090,251 +760,9 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1378,61 +806,17 @@
     <xf numFmtId="20" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1690,23 +1074,23 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J49"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="5.57142857142857" customWidth="1"/>
-    <col min="2" max="2" width="6.71428571428571" customWidth="1"/>
-    <col min="3" max="3" width="12.2857142857143" customWidth="1"/>
+    <col min="1" max="1" width="5.5703125" customWidth="1"/>
+    <col min="2" max="2" width="6.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="14.2857142857143" customWidth="1"/>
-    <col min="6" max="6" width="43.7142857142857" customWidth="1"/>
-    <col min="7" max="7" width="11.1428571428571" customWidth="1"/>
-    <col min="8" max="8" width="4.85714285714286" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" customWidth="1"/>
+    <col min="6" max="6" width="43.7109375" customWidth="1"/>
+    <col min="7" max="7" width="11.140625" customWidth="1"/>
+    <col min="8" max="8" width="4.85546875" customWidth="1"/>
     <col min="9" max="9" width="7" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1764,7 +1148,7 @@
         <v>58</v>
       </c>
       <c r="I2" s="2">
-        <v>5.278</v>
+        <v>5.2779999999999996</v>
       </c>
       <c r="J2" s="2">
         <v>1</v>
@@ -1792,7 +1176,7 @@
         <v>56</v>
       </c>
       <c r="I3" s="2">
-        <v>5.451</v>
+        <v>5.4509999999999996</v>
       </c>
       <c r="J3" s="2">
         <v>1</v>
@@ -1820,7 +1204,7 @@
         <v>53</v>
       </c>
       <c r="I4" s="2">
-        <v>5.807</v>
+        <v>5.8070000000000004</v>
       </c>
       <c r="J4" s="2">
         <v>1</v>
@@ -1848,7 +1232,7 @@
         <v>57</v>
       </c>
       <c r="I5" s="2">
-        <v>5.412</v>
+        <v>5.4119999999999999</v>
       </c>
       <c r="J5" s="2">
         <v>1</v>
@@ -1876,7 +1260,7 @@
         <v>50</v>
       </c>
       <c r="I6" s="2">
-        <v>5.174</v>
+        <v>5.1740000000000004</v>
       </c>
       <c r="J6" s="2">
         <v>1</v>
@@ -1906,7 +1290,7 @@
         <v>57</v>
       </c>
       <c r="I7" s="2">
-        <v>5.412</v>
+        <v>5.4119999999999999</v>
       </c>
       <c r="J7" s="2">
         <v>1</v>
@@ -1936,7 +1320,7 @@
         <v>63</v>
       </c>
       <c r="I8" s="2">
-        <v>4.909</v>
+        <v>4.9089999999999998</v>
       </c>
       <c r="J8" s="2">
         <v>1</v>
@@ -1964,7 +1348,7 @@
         <v>78</v>
       </c>
       <c r="I9" s="2">
-        <v>3.337</v>
+        <v>3.3370000000000002</v>
       </c>
       <c r="J9" s="2">
         <v>1</v>
@@ -2020,7 +1404,7 @@
         <v>70</v>
       </c>
       <c r="I11" s="2">
-        <v>4.361</v>
+        <v>4.3609999999999998</v>
       </c>
       <c r="J11" s="2">
         <v>1</v>
@@ -2048,7 +1432,7 @@
         <v>71</v>
       </c>
       <c r="I12" s="2">
-        <v>4.318</v>
+        <v>4.3179999999999996</v>
       </c>
       <c r="J12" s="2">
         <v>1</v>
@@ -2104,7 +1488,7 @@
         <v>44</v>
       </c>
       <c r="I14" s="2">
-        <v>7.004</v>
+        <v>7.0039999999999996</v>
       </c>
       <c r="J14" s="2">
         <v>1</v>
@@ -2132,7 +1516,7 @@
         <v>70</v>
       </c>
       <c r="I15" s="2">
-        <v>4.381</v>
+        <v>4.3810000000000002</v>
       </c>
       <c r="J15" s="2">
         <v>1</v>
@@ -2160,7 +1544,7 @@
         <v>72</v>
       </c>
       <c r="I16" s="2">
-        <v>4.259</v>
+        <v>4.2590000000000003</v>
       </c>
       <c r="J16" s="2">
         <v>1</v>
@@ -2190,7 +1574,7 @@
         <v>53</v>
       </c>
       <c r="I17" s="2">
-        <v>5.793</v>
+        <v>5.7930000000000001</v>
       </c>
       <c r="J17" s="2">
         <v>1</v>
@@ -2218,7 +1602,7 @@
         <v>51</v>
       </c>
       <c r="I18" s="2">
-        <v>6.003</v>
+        <v>6.0030000000000001</v>
       </c>
       <c r="J18" s="2">
         <v>1</v>
@@ -2276,7 +1660,7 @@
         <v>56</v>
       </c>
       <c r="I20" s="2">
-        <v>5.513</v>
+        <v>5.5129999999999999</v>
       </c>
       <c r="J20" s="2">
         <v>1</v>
@@ -2304,7 +1688,7 @@
         <v>71</v>
       </c>
       <c r="I21" s="2">
-        <v>4.304</v>
+        <v>4.3040000000000003</v>
       </c>
       <c r="J21" s="2">
         <v>1</v>
@@ -2332,7 +1716,7 @@
         <v>71</v>
       </c>
       <c r="I22" s="2">
-        <v>4.309</v>
+        <v>4.3090000000000002</v>
       </c>
       <c r="J22" s="2">
         <v>1</v>
@@ -2362,7 +1746,7 @@
         <v>50</v>
       </c>
       <c r="I23" s="2">
-        <v>6.201</v>
+        <v>6.2009999999999996</v>
       </c>
       <c r="J23" s="2">
         <v>1</v>
@@ -2390,7 +1774,7 @@
         <v>57</v>
       </c>
       <c r="I24" s="2">
-        <v>5.419</v>
+        <v>5.4189999999999996</v>
       </c>
       <c r="J24" s="2">
         <v>1</v>
@@ -2418,7 +1802,7 @@
         <v>58</v>
       </c>
       <c r="I25" s="2">
-        <v>5.281</v>
+        <v>5.2809999999999997</v>
       </c>
       <c r="J25" s="2">
         <v>1</v>
@@ -2445,7 +1829,7 @@
         <v>58</v>
       </c>
       <c r="I26" s="2">
-        <v>5.278</v>
+        <v>5.2779999999999996</v>
       </c>
       <c r="J26" s="2">
         <v>0</v>
@@ -2472,7 +1856,7 @@
         <v>56</v>
       </c>
       <c r="I27" s="2">
-        <v>5.451</v>
+        <v>5.4509999999999996</v>
       </c>
       <c r="J27" s="2">
         <v>0</v>
@@ -2499,7 +1883,7 @@
         <v>53</v>
       </c>
       <c r="I28" s="2">
-        <v>5.807</v>
+        <v>5.8070000000000004</v>
       </c>
       <c r="J28" s="2">
         <v>0</v>
@@ -2526,7 +1910,7 @@
         <v>57</v>
       </c>
       <c r="I29" s="2">
-        <v>5.412</v>
+        <v>5.4119999999999999</v>
       </c>
       <c r="J29" s="2">
         <v>0</v>
@@ -2553,7 +1937,7 @@
         <v>50</v>
       </c>
       <c r="I30" s="2">
-        <v>5.174</v>
+        <v>5.1740000000000004</v>
       </c>
       <c r="J30" s="2">
         <v>0</v>
@@ -2582,7 +1966,7 @@
         <v>57</v>
       </c>
       <c r="I31" s="2">
-        <v>5.412</v>
+        <v>5.4119999999999999</v>
       </c>
       <c r="J31" s="2">
         <v>0</v>
@@ -2609,7 +1993,7 @@
         <v>70</v>
       </c>
       <c r="I32" s="2">
-        <v>4.361</v>
+        <v>4.3609999999999998</v>
       </c>
       <c r="J32" s="2">
         <v>0</v>
@@ -2636,7 +2020,7 @@
         <v>78</v>
       </c>
       <c r="I33" s="2">
-        <v>3.337</v>
+        <v>3.3370000000000002</v>
       </c>
       <c r="J33" s="2">
         <v>0</v>
@@ -2692,7 +2076,7 @@
         <v>71</v>
       </c>
       <c r="I35" s="2">
-        <v>4.318</v>
+        <v>4.3179999999999996</v>
       </c>
       <c r="J35" s="2">
         <v>0</v>
@@ -2746,7 +2130,7 @@
         <v>44</v>
       </c>
       <c r="I37" s="2">
-        <v>7.004</v>
+        <v>7.0039999999999996</v>
       </c>
       <c r="J37" s="2">
         <v>0</v>
@@ -2773,7 +2157,7 @@
         <v>70</v>
       </c>
       <c r="I38" s="2">
-        <v>4.381</v>
+        <v>4.3810000000000002</v>
       </c>
       <c r="J38" s="2">
         <v>0</v>
@@ -2800,7 +2184,7 @@
         <v>72</v>
       </c>
       <c r="I39" s="2">
-        <v>4.259</v>
+        <v>4.2590000000000003</v>
       </c>
       <c r="J39" s="2">
         <v>0</v>
@@ -2829,7 +2213,7 @@
         <v>53</v>
       </c>
       <c r="I40" s="2">
-        <v>5.793</v>
+        <v>5.7930000000000001</v>
       </c>
       <c r="J40" s="2">
         <v>0</v>
@@ -2858,7 +2242,7 @@
         <v>57</v>
       </c>
       <c r="I41" s="2">
-        <v>5.416</v>
+        <v>5.4160000000000004</v>
       </c>
       <c r="J41" s="2">
         <v>0</v>
@@ -2885,7 +2269,7 @@
         <v>51</v>
       </c>
       <c r="I42" s="2">
-        <v>6.003</v>
+        <v>6.0030000000000001</v>
       </c>
       <c r="J42" s="2">
         <v>0</v>
@@ -2941,7 +2325,7 @@
         <v>56</v>
       </c>
       <c r="I44" s="2">
-        <v>5.513</v>
+        <v>5.5129999999999999</v>
       </c>
       <c r="J44" s="2">
         <v>0</v>
@@ -2968,7 +2352,7 @@
         <v>71</v>
       </c>
       <c r="I45" s="2">
-        <v>4.304</v>
+        <v>4.3040000000000003</v>
       </c>
       <c r="J45" s="2">
         <v>0</v>
@@ -2995,7 +2379,7 @@
         <v>71</v>
       </c>
       <c r="I46" s="2">
-        <v>4.309</v>
+        <v>4.3090000000000002</v>
       </c>
       <c r="J46" s="2">
         <v>0</v>
@@ -3024,7 +2408,7 @@
         <v>50</v>
       </c>
       <c r="I47" s="2">
-        <v>6.201</v>
+        <v>6.2009999999999996</v>
       </c>
       <c r="J47" s="2">
         <v>0</v>
@@ -3051,7 +2435,7 @@
         <v>57</v>
       </c>
       <c r="I48" s="2">
-        <v>5.419</v>
+        <v>5.4189999999999996</v>
       </c>
       <c r="J48" s="2">
         <v>0</v>
@@ -3078,7 +2462,7 @@
         <v>58</v>
       </c>
       <c r="I49" s="2">
-        <v>5.281</v>
+        <v>5.2809999999999997</v>
       </c>
       <c r="J49" s="2">
         <v>0</v>
@@ -3087,22 +2471,20 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:G121"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:G126"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="5.57142857142857" customWidth="1"/>
-    <col min="2" max="2" width="6.71428571428571" customWidth="1"/>
-    <col min="3" max="3" width="19.7142857142857" customWidth="1"/>
-    <col min="4" max="4" width="11.2857142857143" customWidth="1"/>
-    <col min="5" max="6" width="9.42857142857143" customWidth="1"/>
-    <col min="7" max="7" width="7.42857142857143" customWidth="1"/>
+    <col min="1" max="1" width="5.5703125" customWidth="1"/>
+    <col min="2" max="2" width="6.7109375" customWidth="1"/>
+    <col min="3" max="3" width="19.7109375" customWidth="1"/>
+    <col min="4" max="4" width="11.28515625" customWidth="1"/>
+    <col min="5" max="6" width="9.42578125" customWidth="1"/>
+    <col min="7" max="7" width="7.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -3142,7 +2524,7 @@
         <v>45730</v>
       </c>
       <c r="E2" s="17">
-        <v>0.395833333333333</v>
+        <v>0.39583333333333298</v>
       </c>
       <c r="F2" s="17">
         <v>0.4375</v>
@@ -3165,10 +2547,10 @@
         <v>45730</v>
       </c>
       <c r="E3" s="17">
-        <v>0.541666666666667</v>
+        <v>0.54166666666666696</v>
       </c>
       <c r="F3" s="17">
-        <v>0.583333333333333</v>
+        <v>0.58333333333333304</v>
       </c>
       <c r="G3" s="2">
         <v>0</v>
@@ -3188,7 +2570,7 @@
         <v>45731</v>
       </c>
       <c r="E4" s="17">
-        <v>0.395833333333333</v>
+        <v>0.39583333333333298</v>
       </c>
       <c r="F4" s="17">
         <v>0.4375</v>
@@ -3211,10 +2593,10 @@
         <v>45731</v>
       </c>
       <c r="E5" s="17">
-        <v>0.541666666666667</v>
+        <v>0.54166666666666696</v>
       </c>
       <c r="F5" s="17">
-        <v>0.583333333333333</v>
+        <v>0.58333333333333304</v>
       </c>
       <c r="G5" s="2">
         <v>1</v>
@@ -3255,10 +2637,10 @@
         <v>45737</v>
       </c>
       <c r="E7" s="19">
-        <v>0.479166666666667</v>
+        <v>0.47916666666666702</v>
       </c>
       <c r="F7" s="19">
-        <v>0.520833333333333</v>
+        <v>0.52083333333333304</v>
       </c>
       <c r="G7" s="7">
         <v>0</v>
@@ -3278,10 +2660,10 @@
         <v>45737</v>
       </c>
       <c r="E8" s="19">
-        <v>0.645833333333333</v>
+        <v>0.64583333333333304</v>
       </c>
       <c r="F8" s="19">
-        <v>0.676388888888889</v>
+        <v>0.67638888888888904</v>
       </c>
       <c r="G8" s="7">
         <v>1</v>
@@ -3301,7 +2683,7 @@
         <v>45738</v>
       </c>
       <c r="E9" s="19">
-        <v>0.458333333333333</v>
+        <v>0.45833333333333298</v>
       </c>
       <c r="F9" s="19">
         <v>0.5</v>
@@ -3327,7 +2709,7 @@
         <v>0.625</v>
       </c>
       <c r="F10" s="19">
-        <v>0.666666666666667</v>
+        <v>0.66666666666666696</v>
       </c>
       <c r="G10" s="7">
         <v>1</v>
@@ -3371,7 +2753,7 @@
         <v>0.4375</v>
       </c>
       <c r="F12" s="17">
-        <v>0.479166666666667</v>
+        <v>0.47916666666666702</v>
       </c>
       <c r="G12" s="2">
         <v>0</v>
@@ -3391,7 +2773,7 @@
         <v>45751</v>
       </c>
       <c r="E13" s="17">
-        <v>0.583333333333333</v>
+        <v>0.58333333333333304</v>
       </c>
       <c r="F13" s="17">
         <v>0.625</v>
@@ -3417,7 +2799,7 @@
         <v>0.4375</v>
       </c>
       <c r="F14" s="17">
-        <v>0.479166666666667</v>
+        <v>0.47916666666666702</v>
       </c>
       <c r="G14" s="2">
         <v>0</v>
@@ -3437,7 +2819,7 @@
         <v>45752</v>
       </c>
       <c r="E15" s="17">
-        <v>0.583333333333333</v>
+        <v>0.58333333333333304</v>
       </c>
       <c r="F15" s="17">
         <v>0.625</v>
@@ -3460,7 +2842,7 @@
         <v>45753</v>
       </c>
       <c r="E16" s="17">
-        <v>0.541666666666667</v>
+        <v>0.54166666666666696</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2">
@@ -3484,7 +2866,7 @@
         <v>0.8125</v>
       </c>
       <c r="F17" s="19">
-        <v>0.854166666666667</v>
+        <v>0.85416666666666696</v>
       </c>
       <c r="G17" s="7">
         <v>0</v>
@@ -3504,7 +2886,7 @@
         <v>45758</v>
       </c>
       <c r="E18" s="19">
-        <v>0.958333333333333</v>
+        <v>0.95833333333333304</v>
       </c>
       <c r="F18" s="19">
         <v>0</v>
@@ -3527,10 +2909,10 @@
         <v>45759</v>
       </c>
       <c r="E19" s="19">
-        <v>0.854166666666667</v>
+        <v>0.85416666666666696</v>
       </c>
       <c r="F19" s="19">
-        <v>0.895833333333333</v>
+        <v>0.89583333333333304</v>
       </c>
       <c r="G19" s="7">
         <v>0</v>
@@ -3553,7 +2935,7 @@
         <v>0</v>
       </c>
       <c r="F20" s="19">
-        <v>0.0416666666666667</v>
+        <v>4.1666666666666699E-2</v>
       </c>
       <c r="G20" s="7">
         <v>1</v>
@@ -3573,7 +2955,7 @@
         <v>45760</v>
       </c>
       <c r="E21" s="19">
-        <v>0.958333333333333</v>
+        <v>0.95833333333333304</v>
       </c>
       <c r="F21" s="7"/>
       <c r="G21" s="7">
@@ -3594,7 +2976,7 @@
         <v>45765</v>
       </c>
       <c r="E22" s="17">
-        <v>0.895833333333333</v>
+        <v>0.89583333333333304</v>
       </c>
       <c r="F22" s="17">
         <v>0.9375</v>
@@ -3617,10 +2999,10 @@
         <v>45766</v>
       </c>
       <c r="E23" s="17">
-        <v>0.0416666666666667</v>
+        <v>4.1666666666666699E-2</v>
       </c>
       <c r="F23" s="17">
-        <v>0.0833333333333333</v>
+        <v>8.3333333333333301E-2</v>
       </c>
       <c r="G23" s="2">
         <v>0</v>
@@ -3640,7 +3022,7 @@
         <v>45766</v>
       </c>
       <c r="E24" s="17">
-        <v>0.895833333333333</v>
+        <v>0.89583333333333304</v>
       </c>
       <c r="F24" s="17">
         <v>0.9375</v>
@@ -3663,10 +3045,10 @@
         <v>45767</v>
       </c>
       <c r="E25" s="17">
-        <v>0.0416666666666667</v>
+        <v>4.1666666666666699E-2</v>
       </c>
       <c r="F25" s="17">
-        <v>0.0833333333333333</v>
+        <v>8.3333333333333301E-2</v>
       </c>
       <c r="G25" s="2">
         <v>1</v>
@@ -3686,7 +3068,7 @@
         <v>45767</v>
       </c>
       <c r="E26" s="17">
-        <v>0.0416666666666667</v>
+        <v>4.1666666666666699E-2</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2">
@@ -3707,10 +3089,10 @@
         <v>45780</v>
       </c>
       <c r="E27" s="19">
-        <v>0.0208333333333333</v>
+        <v>2.0833333333333301E-2</v>
       </c>
       <c r="F27" s="19">
-        <v>0.0625</v>
+        <v>6.25E-2</v>
       </c>
       <c r="G27" s="7">
         <v>0</v>
@@ -3756,7 +3138,7 @@
         <v>0</v>
       </c>
       <c r="F29" s="19">
-        <v>0.0416666666666667</v>
+        <v>4.1666666666666699E-2</v>
       </c>
       <c r="G29" s="7">
         <v>1</v>
@@ -3776,10 +3158,10 @@
         <v>45781</v>
       </c>
       <c r="E30" s="19">
-        <v>0.166666666666667</v>
+        <v>0.16666666666666699</v>
       </c>
       <c r="F30" s="19">
-        <v>0.208333333333333</v>
+        <v>0.20833333333333301</v>
       </c>
       <c r="G30" s="7">
         <v>1</v>
@@ -3799,7 +3181,7 @@
         <v>45782</v>
       </c>
       <c r="E31" s="19">
-        <v>0.166666666666667</v>
+        <v>0.16666666666666699</v>
       </c>
       <c r="F31" s="19"/>
       <c r="G31" s="7">
@@ -3823,7 +3205,7 @@
         <v>0.8125</v>
       </c>
       <c r="F32" s="17">
-        <v>0.854166666666667</v>
+        <v>0.85416666666666696</v>
       </c>
       <c r="G32" s="2">
         <v>0</v>
@@ -3843,7 +3225,7 @@
         <v>45793</v>
       </c>
       <c r="E33" s="17">
-        <v>0.958333333333333</v>
+        <v>0.95833333333333304</v>
       </c>
       <c r="F33" s="17">
         <v>0</v>
@@ -3866,7 +3248,7 @@
         <v>45794</v>
       </c>
       <c r="E34" s="17">
-        <v>0.770833333333333</v>
+        <v>0.77083333333333304</v>
       </c>
       <c r="F34" s="17">
         <v>0.8125</v>
@@ -3889,10 +3271,10 @@
         <v>45794</v>
       </c>
       <c r="E35" s="17">
-        <v>0.916666666666667</v>
+        <v>0.91666666666666696</v>
       </c>
       <c r="F35" s="17">
-        <v>0.958333333333333</v>
+        <v>0.95833333333333304</v>
       </c>
       <c r="G35" s="2">
         <v>1</v>
@@ -3936,7 +3318,7 @@
         <v>0.8125</v>
       </c>
       <c r="F37" s="19">
-        <v>0.854166666666667</v>
+        <v>0.85416666666666696</v>
       </c>
       <c r="G37" s="7">
         <v>0</v>
@@ -3956,7 +3338,7 @@
         <v>45800</v>
       </c>
       <c r="E38" s="19">
-        <v>0.958333333333333</v>
+        <v>0.95833333333333304</v>
       </c>
       <c r="F38" s="19">
         <v>0</v>
@@ -3979,7 +3361,7 @@
         <v>45801</v>
       </c>
       <c r="E39" s="19">
-        <v>0.770833333333333</v>
+        <v>0.77083333333333304</v>
       </c>
       <c r="F39" s="19">
         <v>0.8125</v>
@@ -4002,10 +3384,10 @@
         <v>45801</v>
       </c>
       <c r="E40" s="19">
-        <v>0.916666666666667</v>
+        <v>0.91666666666666696</v>
       </c>
       <c r="F40" s="19">
-        <v>0.958333333333333</v>
+        <v>0.95833333333333304</v>
       </c>
       <c r="G40" s="7">
         <v>1</v>
@@ -4049,7 +3431,7 @@
         <v>0.8125</v>
       </c>
       <c r="F42" s="17">
-        <v>0.854166666666667</v>
+        <v>0.85416666666666696</v>
       </c>
       <c r="G42" s="2">
         <v>0</v>
@@ -4069,7 +3451,7 @@
         <v>45807</v>
       </c>
       <c r="E43" s="17">
-        <v>0.958333333333333</v>
+        <v>0.95833333333333304</v>
       </c>
       <c r="F43" s="17">
         <v>0</v>
@@ -4092,7 +3474,7 @@
         <v>45808</v>
       </c>
       <c r="E44" s="17">
-        <v>0.770833333333333</v>
+        <v>0.77083333333333304</v>
       </c>
       <c r="F44" s="17">
         <v>0.8125</v>
@@ -4115,10 +3497,10 @@
         <v>45808</v>
       </c>
       <c r="E45" s="17">
-        <v>0.916666666666667</v>
+        <v>0.91666666666666696</v>
       </c>
       <c r="F45" s="17">
-        <v>0.958333333333333</v>
+        <v>0.95833333333333304</v>
       </c>
       <c r="G45" s="2">
         <v>1</v>
@@ -4159,7 +3541,7 @@
         <v>45822</v>
       </c>
       <c r="E47" s="19">
-        <v>0.0625</v>
+        <v>6.25E-2</v>
       </c>
       <c r="F47" s="19">
         <v>0.104166666666667</v>
@@ -4182,7 +3564,7 @@
         <v>45822</v>
       </c>
       <c r="E48" s="19">
-        <v>0.208333333333333</v>
+        <v>0.20833333333333301</v>
       </c>
       <c r="F48" s="19">
         <v>0.25</v>
@@ -4205,10 +3587,10 @@
         <v>45823</v>
       </c>
       <c r="E49" s="19">
-        <v>0.0208333333333333</v>
+        <v>2.0833333333333301E-2</v>
       </c>
       <c r="F49" s="19">
-        <v>0.0625</v>
+        <v>6.25E-2</v>
       </c>
       <c r="G49" s="7">
         <v>0</v>
@@ -4228,10 +3610,10 @@
         <v>45823</v>
       </c>
       <c r="E50" s="19">
-        <v>0.166666666666667</v>
+        <v>0.16666666666666699</v>
       </c>
       <c r="F50" s="19">
-        <v>0.208333333333333</v>
+        <v>0.20833333333333301</v>
       </c>
       <c r="G50" s="7">
         <v>1</v>
@@ -4251,7 +3633,7 @@
         <v>45824</v>
       </c>
       <c r="E51" s="19">
-        <v>0.0833333333333333</v>
+        <v>8.3333333333333301E-2</v>
       </c>
       <c r="F51" s="7"/>
       <c r="G51" s="7">
@@ -4275,7 +3657,7 @@
         <v>0.8125</v>
       </c>
       <c r="F52" s="17">
-        <v>0.854166666666667</v>
+        <v>0.85416666666666696</v>
       </c>
       <c r="G52" s="2">
         <v>0</v>
@@ -4295,7 +3677,7 @@
         <v>45835</v>
       </c>
       <c r="E53" s="17">
-        <v>0.958333333333333</v>
+        <v>0.95833333333333304</v>
       </c>
       <c r="F53" s="17">
         <v>0</v>
@@ -4318,7 +3700,7 @@
         <v>45836</v>
       </c>
       <c r="E54" s="17">
-        <v>0.770833333333333</v>
+        <v>0.77083333333333304</v>
       </c>
       <c r="F54" s="17">
         <v>0.8125</v>
@@ -4341,10 +3723,10 @@
         <v>45836</v>
       </c>
       <c r="E55" s="17">
-        <v>0.916666666666667</v>
+        <v>0.91666666666666696</v>
       </c>
       <c r="F55" s="17">
-        <v>0.958333333333333</v>
+        <v>0.95833333333333304</v>
       </c>
       <c r="G55" s="2">
         <v>1</v>
@@ -4388,7 +3770,7 @@
         <v>0.8125</v>
       </c>
       <c r="F57" s="19">
-        <v>0.854166666666667</v>
+        <v>0.85416666666666696</v>
       </c>
       <c r="G57" s="7">
         <v>0</v>
@@ -4408,7 +3790,7 @@
         <v>45842</v>
       </c>
       <c r="E58" s="19">
-        <v>0.958333333333333</v>
+        <v>0.95833333333333304</v>
       </c>
       <c r="F58" s="19">
         <v>0</v>
@@ -4431,7 +3813,7 @@
         <v>45843</v>
       </c>
       <c r="E59" s="19">
-        <v>0.770833333333333</v>
+        <v>0.77083333333333304</v>
       </c>
       <c r="F59" s="19">
         <v>0.8125</v>
@@ -4454,10 +3836,10 @@
         <v>45843</v>
       </c>
       <c r="E60" s="19">
-        <v>0.916666666666667</v>
+        <v>0.91666666666666696</v>
       </c>
       <c r="F60" s="19">
-        <v>0.958333333333333</v>
+        <v>0.95833333333333304</v>
       </c>
       <c r="G60" s="7">
         <v>1</v>
@@ -4477,7 +3859,7 @@
         <v>45844</v>
       </c>
       <c r="E61" s="19">
-        <v>0.916666666666667</v>
+        <v>0.91666666666666696</v>
       </c>
       <c r="F61" s="7"/>
       <c r="G61" s="7">
@@ -4501,7 +3883,7 @@
         <v>0.8125</v>
       </c>
       <c r="F62" s="17">
-        <v>0.854166666666667</v>
+        <v>0.85416666666666696</v>
       </c>
       <c r="G62" s="2">
         <v>0</v>
@@ -4547,7 +3929,7 @@
         <v>0.75</v>
       </c>
       <c r="F64" s="17">
-        <v>0.791666666666667</v>
+        <v>0.79166666666666696</v>
       </c>
       <c r="G64" s="2">
         <v>1</v>
@@ -4567,10 +3949,10 @@
         <v>45864</v>
       </c>
       <c r="E65" s="17">
-        <v>0.916666666666667</v>
+        <v>0.91666666666666696</v>
       </c>
       <c r="F65" s="17">
-        <v>0.958333333333333</v>
+        <v>0.95833333333333304</v>
       </c>
       <c r="G65" s="2">
         <v>1</v>
@@ -4614,7 +3996,7 @@
         <v>0.8125</v>
       </c>
       <c r="F67" s="19">
-        <v>0.854166666666667</v>
+        <v>0.85416666666666696</v>
       </c>
       <c r="G67" s="7">
         <v>0</v>
@@ -4634,7 +4016,7 @@
         <v>45870</v>
       </c>
       <c r="E68" s="19">
-        <v>0.958333333333333</v>
+        <v>0.95833333333333304</v>
       </c>
       <c r="F68" s="19">
         <v>0</v>
@@ -4657,7 +4039,7 @@
         <v>45871</v>
       </c>
       <c r="E69" s="19">
-        <v>0.770833333333333</v>
+        <v>0.77083333333333304</v>
       </c>
       <c r="F69" s="19">
         <v>0.8125</v>
@@ -4680,10 +4062,10 @@
         <v>45871</v>
       </c>
       <c r="E70" s="19">
-        <v>0.916666666666667</v>
+        <v>0.91666666666666696</v>
       </c>
       <c r="F70" s="19">
-        <v>0.958333333333333</v>
+        <v>0.95833333333333304</v>
       </c>
       <c r="G70" s="7">
         <v>1</v>
@@ -4724,7 +4106,7 @@
         <v>45898</v>
       </c>
       <c r="E72" s="17">
-        <v>0.770833333333333</v>
+        <v>0.77083333333333304</v>
       </c>
       <c r="F72" s="17">
         <v>0.8125</v>
@@ -4747,10 +4129,10 @@
         <v>45898</v>
       </c>
       <c r="E73" s="17">
-        <v>0.916666666666667</v>
+        <v>0.91666666666666696</v>
       </c>
       <c r="F73" s="17">
-        <v>0.958333333333333</v>
+        <v>0.95833333333333304</v>
       </c>
       <c r="G73" s="2">
         <v>0</v>
@@ -4770,10 +4152,10 @@
         <v>45899</v>
       </c>
       <c r="E74" s="17">
-        <v>0.729166666666667</v>
+        <v>0.72916666666666696</v>
       </c>
       <c r="F74" s="17">
-        <v>0.770833333333333</v>
+        <v>0.77083333333333304</v>
       </c>
       <c r="G74" s="2">
         <v>0</v>
@@ -4796,7 +4178,7 @@
         <v>0.875</v>
       </c>
       <c r="F75" s="17">
-        <v>0.916666666666667</v>
+        <v>0.91666666666666696</v>
       </c>
       <c r="G75" s="2">
         <v>1</v>
@@ -4840,7 +4222,7 @@
         <v>0.8125</v>
       </c>
       <c r="F77" s="19">
-        <v>0.854166666666667</v>
+        <v>0.85416666666666696</v>
       </c>
       <c r="G77" s="7">
         <v>0</v>
@@ -4860,7 +4242,7 @@
         <v>45905</v>
       </c>
       <c r="E78" s="19">
-        <v>0.958333333333333</v>
+        <v>0.95833333333333304</v>
       </c>
       <c r="F78" s="19">
         <v>0</v>
@@ -4883,7 +4265,7 @@
         <v>45906</v>
       </c>
       <c r="E79" s="19">
-        <v>0.770833333333333</v>
+        <v>0.77083333333333304</v>
       </c>
       <c r="F79" s="19">
         <v>0.8125</v>
@@ -4906,10 +4288,10 @@
         <v>45906</v>
       </c>
       <c r="E80" s="19">
-        <v>0.916666666666667</v>
+        <v>0.91666666666666696</v>
       </c>
       <c r="F80" s="19">
-        <v>0.958333333333333</v>
+        <v>0.95833333333333304</v>
       </c>
       <c r="G80" s="7">
         <v>1</v>
@@ -4953,7 +4335,7 @@
         <v>0.6875</v>
       </c>
       <c r="F82" s="17">
-        <v>0.729166666666667</v>
+        <v>0.72916666666666696</v>
       </c>
       <c r="G82" s="2">
         <v>0</v>
@@ -4973,7 +4355,7 @@
         <v>45919</v>
       </c>
       <c r="E83" s="17">
-        <v>0.833333333333333</v>
+        <v>0.83333333333333304</v>
       </c>
       <c r="F83" s="17">
         <v>0.875</v>
@@ -4999,7 +4381,7 @@
         <v>0.6875</v>
       </c>
       <c r="F84" s="17">
-        <v>0.729166666666667</v>
+        <v>0.72916666666666696</v>
       </c>
       <c r="G84" s="2">
         <v>0</v>
@@ -5019,7 +4401,7 @@
         <v>45920</v>
       </c>
       <c r="E85" s="17">
-        <v>0.833333333333333</v>
+        <v>0.83333333333333304</v>
       </c>
       <c r="F85" s="17">
         <v>0.875</v>
@@ -5042,7 +4424,7 @@
         <v>45921</v>
       </c>
       <c r="E86" s="17">
-        <v>0.791666666666667</v>
+        <v>0.79166666666666696</v>
       </c>
       <c r="F86" s="2"/>
       <c r="G86" s="2">
@@ -5063,10 +4445,10 @@
         <v>45933</v>
       </c>
       <c r="E87" s="19">
-        <v>0.729166666666667</v>
+        <v>0.72916666666666696</v>
       </c>
       <c r="F87" s="19">
-        <v>0.770833333333333</v>
+        <v>0.77083333333333304</v>
       </c>
       <c r="G87" s="7">
         <v>0</v>
@@ -5089,7 +4471,7 @@
         <v>0.875</v>
       </c>
       <c r="F88" s="19">
-        <v>0.916666666666667</v>
+        <v>0.91666666666666696</v>
       </c>
       <c r="G88" s="7">
         <v>0</v>
@@ -5109,10 +4491,10 @@
         <v>45934</v>
       </c>
       <c r="E89" s="19">
-        <v>0.729166666666667</v>
+        <v>0.72916666666666696</v>
       </c>
       <c r="F89" s="19">
-        <v>0.770833333333333</v>
+        <v>0.77083333333333304</v>
       </c>
       <c r="G89" s="7">
         <v>0</v>
@@ -5135,7 +4517,7 @@
         <v>0.875</v>
       </c>
       <c r="F90" s="19">
-        <v>0.916666666666667</v>
+        <v>0.91666666666666696</v>
       </c>
       <c r="G90" s="7">
         <v>1</v>
@@ -5155,7 +4537,7 @@
         <v>45935</v>
       </c>
       <c r="E91" s="19">
-        <v>0.833333333333333</v>
+        <v>0.83333333333333304</v>
       </c>
       <c r="F91" s="7"/>
       <c r="G91" s="7">
@@ -5176,7 +4558,7 @@
         <v>45948</v>
       </c>
       <c r="E92" s="17">
-        <v>0.0625</v>
+        <v>6.25E-2</v>
       </c>
       <c r="F92" s="17">
         <v>0.104166666666667</v>
@@ -5199,10 +4581,10 @@
         <v>45948</v>
       </c>
       <c r="E93" s="17">
-        <v>0.229166666666667</v>
+        <v>0.22916666666666699</v>
       </c>
       <c r="F93" s="17">
-        <v>0.259722222222222</v>
+        <v>0.25972222222222202</v>
       </c>
       <c r="G93" s="2">
         <v>1</v>
@@ -5222,10 +4604,10 @@
         <v>45949</v>
       </c>
       <c r="E94" s="17">
-        <v>0.0416666666666667</v>
+        <v>4.1666666666666699E-2</v>
       </c>
       <c r="F94" s="17">
-        <v>0.0625</v>
+        <v>6.25E-2</v>
       </c>
       <c r="G94" s="2">
         <v>1</v>
@@ -5245,7 +4627,7 @@
         <v>45949</v>
       </c>
       <c r="E95" s="17">
-        <v>0.208333333333333</v>
+        <v>0.20833333333333301</v>
       </c>
       <c r="F95" s="17">
         <v>0.25</v>
@@ -5292,7 +4674,7 @@
         <v>0.104166666666667</v>
       </c>
       <c r="F97" s="19">
-        <v>0.145833333333333</v>
+        <v>0.14583333333333301</v>
       </c>
       <c r="G97" s="7">
         <v>0</v>
@@ -5315,7 +4697,7 @@
         <v>0.25</v>
       </c>
       <c r="F98" s="19">
-        <v>0.291666666666667</v>
+        <v>0.29166666666666702</v>
       </c>
       <c r="G98" s="7">
         <v>0</v>
@@ -5335,7 +4717,7 @@
         <v>45956</v>
       </c>
       <c r="E99" s="19">
-        <v>0.0625</v>
+        <v>6.25E-2</v>
       </c>
       <c r="F99" s="19">
         <v>0.104166666666667</v>
@@ -5358,7 +4740,7 @@
         <v>45956</v>
       </c>
       <c r="E100" s="19">
-        <v>0.208333333333333</v>
+        <v>0.20833333333333301</v>
       </c>
       <c r="F100" s="19">
         <v>0.25</v>
@@ -5381,7 +4763,7 @@
         <v>45957</v>
       </c>
       <c r="E101" s="19">
-        <v>0.166666666666667</v>
+        <v>0.16666666666666699</v>
       </c>
       <c r="F101" s="7"/>
       <c r="G101" s="7">
@@ -5405,7 +4787,7 @@
         <v>0.9375</v>
       </c>
       <c r="F102" s="17">
-        <v>0.979166666666667</v>
+        <v>0.97916666666666696</v>
       </c>
       <c r="G102" s="2">
         <v>0</v>
@@ -5428,7 +4810,7 @@
         <v>0.104166666666667</v>
       </c>
       <c r="F103" s="17">
-        <v>0.134722222222222</v>
+        <v>0.13472222222222199</v>
       </c>
       <c r="G103" s="2">
         <v>1</v>
@@ -5448,10 +4830,10 @@
         <v>45969</v>
       </c>
       <c r="E104" s="17">
-        <v>0.916666666666667</v>
+        <v>0.91666666666666696</v>
       </c>
       <c r="F104" s="17">
-        <v>0.958333333333333</v>
+        <v>0.95833333333333304</v>
       </c>
       <c r="G104" s="2">
         <v>1</v>
@@ -5471,7 +4853,7 @@
         <v>45970</v>
       </c>
       <c r="E105" s="17">
-        <v>0.0833333333333333</v>
+        <v>8.3333333333333301E-2</v>
       </c>
       <c r="F105" s="17">
         <v>0.125</v>
@@ -5494,7 +4876,7 @@
         <v>45971</v>
       </c>
       <c r="E106" s="17">
-        <v>0.0416666666666667</v>
+        <v>4.1666666666666699E-2</v>
       </c>
       <c r="F106" s="2"/>
       <c r="G106" s="2">
@@ -5515,10 +4897,10 @@
         <v>45982</v>
       </c>
       <c r="E107" s="19">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="F107" s="19">
-        <v>0.395833333333333</v>
+        <v>0.39583333333333298</v>
       </c>
       <c r="G107" s="7">
         <v>0</v>
@@ -5541,7 +4923,7 @@
         <v>0.5</v>
       </c>
       <c r="F108" s="19">
-        <v>0.541666666666667</v>
+        <v>0.54166666666666696</v>
       </c>
       <c r="G108" s="7">
         <v>0</v>
@@ -5561,10 +4943,10 @@
         <v>45983</v>
       </c>
       <c r="E109" s="20">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="F109" s="20">
-        <v>0.395833333333333</v>
+        <v>0.39583333333333298</v>
       </c>
       <c r="G109" s="7">
         <v>0</v>
@@ -5587,7 +4969,7 @@
         <v>0.5</v>
       </c>
       <c r="F110" s="20">
-        <v>0.541666666666667</v>
+        <v>0.54166666666666696</v>
       </c>
       <c r="G110" s="7">
         <v>1</v>
@@ -5628,7 +5010,7 @@
         <v>45989</v>
       </c>
       <c r="E112" s="21">
-        <v>0.895833333333333</v>
+        <v>0.89583333333333304</v>
       </c>
       <c r="F112" s="21">
         <v>0.9375</v>
@@ -5651,10 +5033,10 @@
         <v>45990</v>
       </c>
       <c r="E113" s="21">
-        <v>0.0625</v>
+        <v>6.25E-2</v>
       </c>
       <c r="F113" s="21">
-        <v>0.0930555555555556</v>
+        <v>9.30555555555556E-2</v>
       </c>
       <c r="G113" s="2">
         <v>1</v>
@@ -5674,10 +5056,10 @@
         <v>45990</v>
       </c>
       <c r="E114" s="21">
-        <v>0.916666666666667</v>
+        <v>0.91666666666666696</v>
       </c>
       <c r="F114" s="21">
-        <v>0.958333333333333</v>
+        <v>0.95833333333333304</v>
       </c>
       <c r="G114" s="2">
         <v>1</v>
@@ -5697,7 +5079,7 @@
         <v>45991</v>
       </c>
       <c r="E115" s="21">
-        <v>0.0833333333333333</v>
+        <v>8.3333333333333301E-2</v>
       </c>
       <c r="F115" s="21">
         <v>0.125</v>
@@ -5741,10 +5123,10 @@
         <v>45996</v>
       </c>
       <c r="E117" s="20">
-        <v>0.729166666666667</v>
+        <v>0.72916666666666696</v>
       </c>
       <c r="F117" s="20">
-        <v>0.770833333333333</v>
+        <v>0.77083333333333304</v>
       </c>
       <c r="G117" s="7">
         <v>0</v>
@@ -5767,7 +5149,7 @@
         <v>0.875</v>
       </c>
       <c r="F118" s="20">
-        <v>0.916666666666667</v>
+        <v>0.91666666666666696</v>
       </c>
       <c r="G118" s="7">
         <v>0</v>
@@ -5787,7 +5169,7 @@
         <v>45997</v>
       </c>
       <c r="E119" s="20">
-        <v>0.770833333333333</v>
+        <v>0.77083333333333304</v>
       </c>
       <c r="F119" s="20">
         <v>0.8125</v>
@@ -5810,10 +5192,10 @@
         <v>45997</v>
       </c>
       <c r="E120" s="20">
-        <v>0.916666666666667</v>
+        <v>0.91666666666666696</v>
       </c>
       <c r="F120" s="20">
-        <v>0.958333333333333</v>
+        <v>0.95833333333333304</v>
       </c>
       <c r="G120" s="7">
         <v>1</v>
@@ -5840,27 +5222,138 @@
         <v>1</v>
       </c>
     </row>
+    <row r="122" spans="1:7">
+      <c r="A122" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B122" s="2">
+        <v>1</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D122" s="16">
+        <v>46095</v>
+      </c>
+      <c r="E122" s="17">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="F122" s="17">
+        <v>0.4375</v>
+      </c>
+      <c r="G122" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7">
+      <c r="A123" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B123" s="2">
+        <v>1</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D123" s="16">
+        <v>46095</v>
+      </c>
+      <c r="E123" s="17">
+        <v>0.54166666666666696</v>
+      </c>
+      <c r="F123" s="17">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="G123" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7">
+      <c r="A124" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B124" s="2">
+        <v>1</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D124" s="16">
+        <v>46096</v>
+      </c>
+      <c r="E124" s="17">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="F124" s="17">
+        <v>0.4375</v>
+      </c>
+      <c r="G124" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7">
+      <c r="A125" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B125" s="2">
+        <v>1</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D125" s="16">
+        <v>46096</v>
+      </c>
+      <c r="E125" s="17">
+        <v>0.54166666666666696</v>
+      </c>
+      <c r="F125" s="17">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="G125" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7">
+      <c r="A126" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B126" s="2">
+        <v>1</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D126" s="16">
+        <v>46097</v>
+      </c>
+      <c r="E126" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="F126" s="17"/>
+      <c r="G126" s="2">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:R1201"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
-    <col min="2" max="2" width="6.28571428571429" customWidth="1"/>
-    <col min="3" max="3" width="15.5714285714286" customWidth="1"/>
-    <col min="4" max="4" width="8.28571428571429" customWidth="1"/>
-    <col min="5" max="5" width="8.85714285714286" customWidth="1"/>
-    <col min="6" max="6" width="16.4285714285714" customWidth="1"/>
-    <col min="7" max="7" width="31.1428571428571" customWidth="1"/>
-    <col min="8" max="10" width="12.7857142857143"/>
-    <col min="11" max="11" width="18.7142857142857" customWidth="1"/>
+    <col min="2" max="2" width="6.28515625" customWidth="1"/>
+    <col min="3" max="3" width="15.5703125" customWidth="1"/>
+    <col min="4" max="4" width="8.28515625" customWidth="1"/>
+    <col min="5" max="5" width="8.85546875" customWidth="1"/>
+    <col min="6" max="6" width="16.42578125" customWidth="1"/>
+    <col min="7" max="7" width="31.140625" customWidth="1"/>
+    <col min="8" max="10" width="12.7109375"/>
+    <col min="11" max="11" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17">
@@ -17234,7 +16727,7 @@
       <c r="N421" s="6"/>
       <c r="O421" s="5"/>
     </row>
-    <row r="422" ht="17" spans="1:15">
+    <row r="422" spans="1:15">
       <c r="A422" s="7">
         <v>2025</v>
       </c>
@@ -17267,7 +16760,7 @@
       <c r="N422" s="5"/>
       <c r="O422" s="5"/>
     </row>
-    <row r="423" ht="17" spans="1:15">
+    <row r="423" spans="1:15">
       <c r="A423" s="7">
         <v>2025</v>
       </c>
@@ -17300,7 +16793,7 @@
       <c r="N423" s="5"/>
       <c r="O423" s="5"/>
     </row>
-    <row r="424" ht="17" spans="1:15">
+    <row r="424" spans="1:15">
       <c r="A424" s="7">
         <v>2025</v>
       </c>
@@ -17333,7 +16826,7 @@
       <c r="N424" s="5"/>
       <c r="O424" s="5"/>
     </row>
-    <row r="425" ht="17" spans="1:15">
+    <row r="425" spans="1:15">
       <c r="A425" s="7">
         <v>2025</v>
       </c>
@@ -17366,7 +16859,7 @@
       <c r="N425" s="5"/>
       <c r="O425" s="5"/>
     </row>
-    <row r="426" ht="17" spans="1:15">
+    <row r="426" spans="1:15">
       <c r="A426" s="7">
         <v>2025</v>
       </c>
@@ -17399,7 +16892,7 @@
       <c r="N426" s="5"/>
       <c r="O426" s="5"/>
     </row>
-    <row r="427" ht="17" spans="1:15">
+    <row r="427" spans="1:15">
       <c r="A427" s="7">
         <v>2025</v>
       </c>
@@ -17432,7 +16925,7 @@
       <c r="N427" s="5"/>
       <c r="O427" s="5"/>
     </row>
-    <row r="428" ht="17" spans="1:15">
+    <row r="428" spans="1:15">
       <c r="A428" s="7">
         <v>2025</v>
       </c>
@@ -17465,7 +16958,7 @@
       <c r="N428" s="5"/>
       <c r="O428" s="5"/>
     </row>
-    <row r="429" ht="17" spans="1:15">
+    <row r="429" spans="1:15">
       <c r="A429" s="7">
         <v>2025</v>
       </c>
@@ -17498,7 +16991,7 @@
       <c r="N429" s="5"/>
       <c r="O429" s="5"/>
     </row>
-    <row r="430" ht="17" spans="1:15">
+    <row r="430" spans="1:15">
       <c r="A430" s="7">
         <v>2025</v>
       </c>
@@ -17531,7 +17024,7 @@
       <c r="N430" s="5"/>
       <c r="O430" s="5"/>
     </row>
-    <row r="431" ht="17" spans="1:15">
+    <row r="431" spans="1:15">
       <c r="A431" s="7">
         <v>2025</v>
       </c>
@@ -17564,7 +17057,7 @@
       <c r="N431" s="5"/>
       <c r="O431" s="5"/>
     </row>
-    <row r="432" ht="17" spans="1:15">
+    <row r="432" spans="1:15">
       <c r="A432" s="7">
         <v>2025</v>
       </c>
@@ -17597,7 +17090,7 @@
       <c r="N432" s="5"/>
       <c r="O432" s="5"/>
     </row>
-    <row r="433" ht="17" spans="1:15">
+    <row r="433" spans="1:15">
       <c r="A433" s="7">
         <v>2025</v>
       </c>
@@ -17630,7 +17123,7 @@
       <c r="N433" s="5"/>
       <c r="O433" s="5"/>
     </row>
-    <row r="434" ht="17" spans="1:15">
+    <row r="434" spans="1:15">
       <c r="A434" s="7">
         <v>2025</v>
       </c>
@@ -17663,7 +17156,7 @@
       <c r="N434" s="5"/>
       <c r="O434" s="5"/>
     </row>
-    <row r="435" ht="17" spans="1:15">
+    <row r="435" spans="1:15">
       <c r="A435" s="7">
         <v>2025</v>
       </c>
@@ -17696,7 +17189,7 @@
       <c r="N435" s="5"/>
       <c r="O435" s="5"/>
     </row>
-    <row r="436" ht="17" spans="1:15">
+    <row r="436" spans="1:15">
       <c r="A436" s="7">
         <v>2025</v>
       </c>
@@ -17729,7 +17222,7 @@
       <c r="N436" s="5"/>
       <c r="O436" s="5"/>
     </row>
-    <row r="437" ht="17" spans="1:15">
+    <row r="437" spans="1:15">
       <c r="A437" s="7">
         <v>2025</v>
       </c>
@@ -17762,7 +17255,7 @@
       <c r="N437" s="5"/>
       <c r="O437" s="5"/>
     </row>
-    <row r="438" ht="17" spans="1:15">
+    <row r="438" spans="1:15">
       <c r="A438" s="7">
         <v>2025</v>
       </c>
@@ -17795,7 +17288,7 @@
       <c r="N438" s="5"/>
       <c r="O438" s="5"/>
     </row>
-    <row r="439" ht="17" spans="1:15">
+    <row r="439" spans="1:15">
       <c r="A439" s="7">
         <v>2025</v>
       </c>
@@ -17828,7 +17321,7 @@
       <c r="N439" s="5"/>
       <c r="O439" s="5"/>
     </row>
-    <row r="440" ht="17" spans="1:15">
+    <row r="440" spans="1:15">
       <c r="A440" s="7">
         <v>2025</v>
       </c>
@@ -17854,7 +17347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="441" ht="17" spans="1:15">
+    <row r="441" spans="1:15">
       <c r="A441" s="7">
         <v>2025</v>
       </c>
@@ -17878,7 +17371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="442" ht="17" spans="1:15">
+    <row r="442" spans="1:15">
       <c r="A442" s="2">
         <v>2025</v>
       </c>
@@ -17905,7 +17398,7 @@
       <c r="J442" s="6"/>
       <c r="K442" s="5"/>
     </row>
-    <row r="443" ht="17" spans="1:15">
+    <row r="443" spans="1:15">
       <c r="A443" s="2">
         <v>2025</v>
       </c>
@@ -17932,7 +17425,7 @@
       <c r="J443" s="6"/>
       <c r="K443" s="5"/>
     </row>
-    <row r="444" ht="17" spans="1:15">
+    <row r="444" spans="1:15">
       <c r="A444" s="2">
         <v>2025</v>
       </c>
@@ -17959,7 +17452,7 @@
       <c r="J444" s="6"/>
       <c r="K444" s="5"/>
     </row>
-    <row r="445" ht="17" spans="1:15">
+    <row r="445" spans="1:15">
       <c r="A445" s="2">
         <v>2025</v>
       </c>
@@ -17986,7 +17479,7 @@
       <c r="J445" s="6"/>
       <c r="K445" s="5"/>
     </row>
-    <row r="446" ht="17" spans="1:15">
+    <row r="446" spans="1:15">
       <c r="A446" s="2">
         <v>2025</v>
       </c>
@@ -18013,7 +17506,7 @@
       <c r="J446" s="6"/>
       <c r="K446" s="5"/>
     </row>
-    <row r="447" ht="17" spans="1:15">
+    <row r="447" spans="1:15">
       <c r="A447" s="2">
         <v>2025</v>
       </c>
@@ -18040,7 +17533,7 @@
       <c r="J447" s="6"/>
       <c r="K447" s="5"/>
     </row>
-    <row r="448" ht="17" spans="1:15">
+    <row r="448" spans="1:15">
       <c r="A448" s="2">
         <v>2025</v>
       </c>
@@ -18067,7 +17560,7 @@
       <c r="J448" s="6"/>
       <c r="K448" s="5"/>
     </row>
-    <row r="449" ht="17" spans="1:11">
+    <row r="449" spans="1:11">
       <c r="A449" s="2">
         <v>2025</v>
       </c>
@@ -18094,7 +17587,7 @@
       <c r="J449" s="6"/>
       <c r="K449" s="5"/>
     </row>
-    <row r="450" ht="17" spans="1:11">
+    <row r="450" spans="1:11">
       <c r="A450" s="2">
         <v>2025</v>
       </c>
@@ -18121,7 +17614,7 @@
       <c r="J450" s="6"/>
       <c r="K450" s="5"/>
     </row>
-    <row r="451" ht="17" spans="1:11">
+    <row r="451" spans="1:11">
       <c r="A451" s="2">
         <v>2025</v>
       </c>
@@ -18148,7 +17641,7 @@
       <c r="J451" s="6"/>
       <c r="K451" s="5"/>
     </row>
-    <row r="452" ht="17" spans="1:11">
+    <row r="452" spans="1:11">
       <c r="A452" s="2">
         <v>2025</v>
       </c>
@@ -18175,7 +17668,7 @@
       <c r="J452" s="5"/>
       <c r="K452" s="5"/>
     </row>
-    <row r="453" ht="17" spans="1:11">
+    <row r="453" spans="1:11">
       <c r="A453" s="2">
         <v>2025</v>
       </c>
@@ -18202,7 +17695,7 @@
       <c r="J453" s="5"/>
       <c r="K453" s="5"/>
     </row>
-    <row r="454" ht="17" spans="1:11">
+    <row r="454" spans="1:11">
       <c r="A454" s="2">
         <v>2025</v>
       </c>
@@ -18229,7 +17722,7 @@
       <c r="J454" s="5"/>
       <c r="K454" s="5"/>
     </row>
-    <row r="455" ht="17" spans="1:11">
+    <row r="455" spans="1:11">
       <c r="A455" s="2">
         <v>2025</v>
       </c>
@@ -18256,7 +17749,7 @@
       <c r="J455" s="5"/>
       <c r="K455" s="5"/>
     </row>
-    <row r="456" ht="17" spans="1:11">
+    <row r="456" spans="1:11">
       <c r="A456" s="2">
         <v>2025</v>
       </c>
@@ -18283,7 +17776,7 @@
       <c r="J456" s="5"/>
       <c r="K456" s="5"/>
     </row>
-    <row r="457" ht="17" spans="1:11">
+    <row r="457" spans="1:11">
       <c r="A457" s="2">
         <v>2025</v>
       </c>
@@ -18310,7 +17803,7 @@
       <c r="J457" s="5"/>
       <c r="K457" s="5"/>
     </row>
-    <row r="458" ht="17" spans="1:11">
+    <row r="458" spans="1:11">
       <c r="A458" s="2">
         <v>2025</v>
       </c>
@@ -18337,7 +17830,7 @@
       <c r="J458" s="5"/>
       <c r="K458" s="5"/>
     </row>
-    <row r="459" ht="17" spans="1:11">
+    <row r="459" spans="1:11">
       <c r="A459" s="2">
         <v>2025</v>
       </c>
@@ -18364,7 +17857,7 @@
       <c r="J459" s="5"/>
       <c r="K459" s="5"/>
     </row>
-    <row r="460" ht="17" spans="1:11">
+    <row r="460" spans="1:11">
       <c r="A460" s="2">
         <v>2025</v>
       </c>
@@ -18391,7 +17884,7 @@
       <c r="J460" s="5"/>
       <c r="K460" s="5"/>
     </row>
-    <row r="461" ht="17" spans="1:11">
+    <row r="461" spans="1:11">
       <c r="A461" s="2">
         <v>2025</v>
       </c>
@@ -18418,7 +17911,7 @@
       <c r="J461" s="5"/>
       <c r="K461" s="5"/>
     </row>
-    <row r="462" ht="17" spans="1:11">
+    <row r="462" spans="1:11">
       <c r="A462" s="7">
         <v>2025</v>
       </c>
@@ -18446,7 +17939,7 @@
       <c r="I462" s="6"/>
       <c r="J462" s="5"/>
     </row>
-    <row r="463" ht="17" spans="1:11">
+    <row r="463" spans="1:11">
       <c r="A463" s="7">
         <v>2025</v>
       </c>
@@ -18474,7 +17967,7 @@
       <c r="I463" s="5"/>
       <c r="J463" s="5"/>
     </row>
-    <row r="464" ht="17" spans="1:11">
+    <row r="464" spans="1:11">
       <c r="A464" s="7">
         <v>2025</v>
       </c>
@@ -18502,7 +17995,7 @@
       <c r="I464" s="5"/>
       <c r="J464" s="5"/>
     </row>
-    <row r="465" ht="17" spans="1:10">
+    <row r="465" spans="1:10">
       <c r="A465" s="7">
         <v>2025</v>
       </c>
@@ -18530,7 +18023,7 @@
       <c r="I465" s="5"/>
       <c r="J465" s="5"/>
     </row>
-    <row r="466" ht="17" spans="1:10">
+    <row r="466" spans="1:10">
       <c r="A466" s="7">
         <v>2025</v>
       </c>
@@ -18558,7 +18051,7 @@
       <c r="I466" s="5"/>
       <c r="J466" s="5"/>
     </row>
-    <row r="467" ht="17" spans="1:10">
+    <row r="467" spans="1:10">
       <c r="A467" s="7">
         <v>2025</v>
       </c>
@@ -18586,7 +18079,7 @@
       <c r="I467" s="5"/>
       <c r="J467" s="5"/>
     </row>
-    <row r="468" ht="17" spans="1:10">
+    <row r="468" spans="1:10">
       <c r="A468" s="7">
         <v>2025</v>
       </c>
@@ -18614,7 +18107,7 @@
       <c r="I468" s="5"/>
       <c r="J468" s="5"/>
     </row>
-    <row r="469" ht="17" spans="1:10">
+    <row r="469" spans="1:10">
       <c r="A469" s="7">
         <v>2025</v>
       </c>
@@ -18642,7 +18135,7 @@
       <c r="I469" s="5"/>
       <c r="J469" s="5"/>
     </row>
-    <row r="470" ht="17" spans="1:10">
+    <row r="470" spans="1:10">
       <c r="A470" s="7">
         <v>2025</v>
       </c>
@@ -18670,7 +18163,7 @@
       <c r="I470" s="5"/>
       <c r="J470" s="5"/>
     </row>
-    <row r="471" ht="17" spans="1:10">
+    <row r="471" spans="1:10">
       <c r="A471" s="7">
         <v>2025</v>
       </c>
@@ -18698,7 +18191,7 @@
       <c r="I471" s="5"/>
       <c r="J471" s="5"/>
     </row>
-    <row r="472" ht="17" spans="1:10">
+    <row r="472" spans="1:10">
       <c r="A472" s="7">
         <v>2025</v>
       </c>
@@ -18726,7 +18219,7 @@
       <c r="I472" s="5"/>
       <c r="J472" s="5"/>
     </row>
-    <row r="473" ht="17" spans="1:10">
+    <row r="473" spans="1:10">
       <c r="A473" s="7">
         <v>2025</v>
       </c>
@@ -18754,7 +18247,7 @@
       <c r="I473" s="5"/>
       <c r="J473" s="5"/>
     </row>
-    <row r="474" ht="17" spans="1:10">
+    <row r="474" spans="1:10">
       <c r="A474" s="7">
         <v>2025</v>
       </c>
@@ -18782,7 +18275,7 @@
       <c r="I474" s="5"/>
       <c r="J474" s="5"/>
     </row>
-    <row r="475" ht="17" spans="1:10">
+    <row r="475" spans="1:10">
       <c r="A475" s="7">
         <v>2025</v>
       </c>
@@ -18810,7 +18303,7 @@
       <c r="I475" s="5"/>
       <c r="J475" s="5"/>
     </row>
-    <row r="476" ht="17" spans="1:10">
+    <row r="476" spans="1:10">
       <c r="A476" s="7">
         <v>2025</v>
       </c>
@@ -18838,7 +18331,7 @@
       <c r="I476" s="5"/>
       <c r="J476" s="5"/>
     </row>
-    <row r="477" ht="17" spans="1:10">
+    <row r="477" spans="1:10">
       <c r="A477" s="7">
         <v>2025</v>
       </c>
@@ -18866,7 +18359,7 @@
       <c r="I477" s="5"/>
       <c r="J477" s="5"/>
     </row>
-    <row r="478" ht="17" spans="1:10">
+    <row r="478" spans="1:10">
       <c r="A478" s="7">
         <v>2025</v>
       </c>
@@ -18894,7 +18387,7 @@
       <c r="I478" s="5"/>
       <c r="J478" s="5"/>
     </row>
-    <row r="479" ht="17" spans="1:10">
+    <row r="479" spans="1:10">
       <c r="A479" s="7">
         <v>2025</v>
       </c>
@@ -18922,7 +18415,7 @@
       <c r="I479" s="5"/>
       <c r="J479" s="5"/>
     </row>
-    <row r="480" ht="17" spans="1:10">
+    <row r="480" spans="1:10">
       <c r="A480" s="7">
         <v>2025</v>
       </c>
@@ -18950,7 +18443,7 @@
       <c r="I480" s="5"/>
       <c r="J480" s="5"/>
     </row>
-    <row r="481" ht="17" spans="1:11">
+    <row r="481" spans="1:11">
       <c r="A481" s="7">
         <v>2025</v>
       </c>
@@ -18978,7 +18471,7 @@
       <c r="I481" s="5"/>
       <c r="J481" s="5"/>
     </row>
-    <row r="482" ht="17" spans="1:11">
+    <row r="482" spans="1:11">
       <c r="A482" s="2">
         <v>2025</v>
       </c>
@@ -19005,7 +18498,7 @@
       <c r="J482" s="6"/>
       <c r="K482" s="5"/>
     </row>
-    <row r="483" ht="17" spans="1:11">
+    <row r="483" spans="1:11">
       <c r="A483" s="2">
         <v>2025</v>
       </c>
@@ -19032,7 +18525,7 @@
       <c r="J483" s="6"/>
       <c r="K483" s="5"/>
     </row>
-    <row r="484" ht="17" spans="1:11">
+    <row r="484" spans="1:11">
       <c r="A484" s="2">
         <v>2025</v>
       </c>
@@ -19059,7 +18552,7 @@
       <c r="J484" s="6"/>
       <c r="K484" s="5"/>
     </row>
-    <row r="485" ht="17" spans="1:11">
+    <row r="485" spans="1:11">
       <c r="A485" s="2">
         <v>2025</v>
       </c>
@@ -19086,7 +18579,7 @@
       <c r="J485" s="6"/>
       <c r="K485" s="5"/>
     </row>
-    <row r="486" ht="17" spans="1:11">
+    <row r="486" spans="1:11">
       <c r="A486" s="2">
         <v>2025</v>
       </c>
@@ -19113,7 +18606,7 @@
       <c r="J486" s="6"/>
       <c r="K486" s="5"/>
     </row>
-    <row r="487" ht="17" spans="1:11">
+    <row r="487" spans="1:11">
       <c r="A487" s="2">
         <v>2025</v>
       </c>
@@ -19140,7 +18633,7 @@
       <c r="J487" s="6"/>
       <c r="K487" s="5"/>
     </row>
-    <row r="488" ht="17" spans="1:11">
+    <row r="488" spans="1:11">
       <c r="A488" s="2">
         <v>2025</v>
       </c>
@@ -19167,7 +18660,7 @@
       <c r="J488" s="6"/>
       <c r="K488" s="5"/>
     </row>
-    <row r="489" ht="17" spans="1:11">
+    <row r="489" spans="1:11">
       <c r="A489" s="2">
         <v>2025</v>
       </c>
@@ -19194,7 +18687,7 @@
       <c r="J489" s="6"/>
       <c r="K489" s="5"/>
     </row>
-    <row r="490" ht="17" spans="1:11">
+    <row r="490" spans="1:11">
       <c r="A490" s="2">
         <v>2025</v>
       </c>
@@ -19221,7 +18714,7 @@
       <c r="J490" s="6"/>
       <c r="K490" s="5"/>
     </row>
-    <row r="491" ht="17" spans="1:11">
+    <row r="491" spans="1:11">
       <c r="A491" s="2">
         <v>2025</v>
       </c>
@@ -19248,7 +18741,7 @@
       <c r="J491" s="6"/>
       <c r="K491" s="5"/>
     </row>
-    <row r="492" ht="17" spans="1:11">
+    <row r="492" spans="1:11">
       <c r="A492" s="2">
         <v>2025</v>
       </c>
@@ -19275,7 +18768,7 @@
       <c r="J492" s="5"/>
       <c r="K492" s="5"/>
     </row>
-    <row r="493" ht="17" spans="1:11">
+    <row r="493" spans="1:11">
       <c r="A493" s="2">
         <v>2025</v>
       </c>
@@ -19302,7 +18795,7 @@
       <c r="J493" s="5"/>
       <c r="K493" s="5"/>
     </row>
-    <row r="494" ht="17" spans="1:11">
+    <row r="494" spans="1:11">
       <c r="A494" s="2">
         <v>2025</v>
       </c>
@@ -19329,7 +18822,7 @@
       <c r="J494" s="5"/>
       <c r="K494" s="5"/>
     </row>
-    <row r="495" ht="17" spans="1:11">
+    <row r="495" spans="1:11">
       <c r="A495" s="2">
         <v>2025</v>
       </c>
@@ -19356,7 +18849,7 @@
       <c r="J495" s="5"/>
       <c r="K495" s="5"/>
     </row>
-    <row r="496" ht="17" spans="1:11">
+    <row r="496" spans="1:11">
       <c r="A496" s="2">
         <v>2025</v>
       </c>
@@ -19383,7 +18876,7 @@
       <c r="J496" s="5"/>
       <c r="K496" s="5"/>
     </row>
-    <row r="497" ht="17" spans="1:11">
+    <row r="497" spans="1:11">
       <c r="A497" s="2">
         <v>2025</v>
       </c>
@@ -19410,7 +18903,7 @@
       <c r="J497" s="5"/>
       <c r="K497" s="5"/>
     </row>
-    <row r="498" ht="17" spans="1:11">
+    <row r="498" spans="1:11">
       <c r="A498" s="2">
         <v>2025</v>
       </c>
@@ -19437,7 +18930,7 @@
       <c r="J498" s="5"/>
       <c r="K498" s="5"/>
     </row>
-    <row r="499" ht="17" spans="1:11">
+    <row r="499" spans="1:11">
       <c r="A499" s="2">
         <v>2025</v>
       </c>
@@ -19464,7 +18957,7 @@
       <c r="J499" s="5"/>
       <c r="K499" s="5"/>
     </row>
-    <row r="500" ht="17" spans="1:11">
+    <row r="500" spans="1:11">
       <c r="A500" s="2">
         <v>2025</v>
       </c>
@@ -19491,7 +18984,7 @@
       <c r="J500" s="5"/>
       <c r="K500" s="5"/>
     </row>
-    <row r="501" ht="17" spans="1:11">
+    <row r="501" spans="1:11">
       <c r="A501" s="2">
         <v>2025</v>
       </c>
@@ -19518,7 +19011,7 @@
       <c r="J501" s="5"/>
       <c r="K501" s="5"/>
     </row>
-    <row r="502" ht="17" spans="1:11">
+    <row r="502" spans="1:11">
       <c r="A502" s="7">
         <v>2025</v>
       </c>
@@ -19546,7 +19039,7 @@
       <c r="I502" s="6"/>
       <c r="J502" s="5"/>
     </row>
-    <row r="503" ht="17" spans="1:11">
+    <row r="503" spans="1:11">
       <c r="A503" s="7">
         <v>2025</v>
       </c>
@@ -19574,7 +19067,7 @@
       <c r="I503" s="5"/>
       <c r="J503" s="5"/>
     </row>
-    <row r="504" ht="17" spans="1:11">
+    <row r="504" spans="1:11">
       <c r="A504" s="7">
         <v>2025</v>
       </c>
@@ -19602,7 +19095,7 @@
       <c r="I504" s="5"/>
       <c r="J504" s="5"/>
     </row>
-    <row r="505" ht="17" spans="1:11">
+    <row r="505" spans="1:11">
       <c r="A505" s="7">
         <v>2025</v>
       </c>
@@ -19630,7 +19123,7 @@
       <c r="I505" s="5"/>
       <c r="J505" s="5"/>
     </row>
-    <row r="506" ht="17" spans="1:11">
+    <row r="506" spans="1:11">
       <c r="A506" s="7">
         <v>2025</v>
       </c>
@@ -19658,7 +19151,7 @@
       <c r="I506" s="5"/>
       <c r="J506" s="5"/>
     </row>
-    <row r="507" ht="17" spans="1:11">
+    <row r="507" spans="1:11">
       <c r="A507" s="7">
         <v>2025</v>
       </c>
@@ -19686,7 +19179,7 @@
       <c r="I507" s="5"/>
       <c r="J507" s="5"/>
     </row>
-    <row r="508" ht="17" spans="1:11">
+    <row r="508" spans="1:11">
       <c r="A508" s="7">
         <v>2025</v>
       </c>
@@ -19714,7 +19207,7 @@
       <c r="I508" s="5"/>
       <c r="J508" s="5"/>
     </row>
-    <row r="509" ht="17" spans="1:11">
+    <row r="509" spans="1:11">
       <c r="A509" s="7">
         <v>2025</v>
       </c>
@@ -19742,7 +19235,7 @@
       <c r="I509" s="5"/>
       <c r="J509" s="5"/>
     </row>
-    <row r="510" ht="17" spans="1:11">
+    <row r="510" spans="1:11">
       <c r="A510" s="7">
         <v>2025</v>
       </c>
@@ -19770,7 +19263,7 @@
       <c r="I510" s="5"/>
       <c r="J510" s="5"/>
     </row>
-    <row r="511" ht="17" spans="1:11">
+    <row r="511" spans="1:11">
       <c r="A511" s="7">
         <v>2025</v>
       </c>
@@ -19798,7 +19291,7 @@
       <c r="I511" s="5"/>
       <c r="J511" s="5"/>
     </row>
-    <row r="512" ht="17" spans="1:11">
+    <row r="512" spans="1:11">
       <c r="A512" s="7">
         <v>2025</v>
       </c>
@@ -19826,7 +19319,7 @@
       <c r="I512" s="5"/>
       <c r="J512" s="5"/>
     </row>
-    <row r="513" ht="17" spans="1:11">
+    <row r="513" spans="1:11">
       <c r="A513" s="7">
         <v>2025</v>
       </c>
@@ -19854,7 +19347,7 @@
       <c r="I513" s="5"/>
       <c r="J513" s="5"/>
     </row>
-    <row r="514" ht="17" spans="1:11">
+    <row r="514" spans="1:11">
       <c r="A514" s="7">
         <v>2025</v>
       </c>
@@ -19882,7 +19375,7 @@
       <c r="I514" s="5"/>
       <c r="J514" s="5"/>
     </row>
-    <row r="515" ht="17" spans="1:11">
+    <row r="515" spans="1:11">
       <c r="A515" s="7">
         <v>2025</v>
       </c>
@@ -19910,7 +19403,7 @@
       <c r="I515" s="5"/>
       <c r="J515" s="5"/>
     </row>
-    <row r="516" ht="17" spans="1:11">
+    <row r="516" spans="1:11">
       <c r="A516" s="7">
         <v>2025</v>
       </c>
@@ -19938,7 +19431,7 @@
       <c r="I516" s="5"/>
       <c r="J516" s="5"/>
     </row>
-    <row r="517" ht="17" spans="1:11">
+    <row r="517" spans="1:11">
       <c r="A517" s="7">
         <v>2025</v>
       </c>
@@ -19966,7 +19459,7 @@
       <c r="I517" s="5"/>
       <c r="J517" s="5"/>
     </row>
-    <row r="518" ht="17" spans="1:11">
+    <row r="518" spans="1:11">
       <c r="A518" s="7">
         <v>2025</v>
       </c>
@@ -19994,7 +19487,7 @@
       <c r="I518" s="5"/>
       <c r="J518" s="5"/>
     </row>
-    <row r="519" ht="17" spans="1:11">
+    <row r="519" spans="1:11">
       <c r="A519" s="7">
         <v>2025</v>
       </c>
@@ -20022,7 +19515,7 @@
       <c r="I519" s="5"/>
       <c r="J519" s="5"/>
     </row>
-    <row r="520" ht="17" spans="1:11">
+    <row r="520" spans="1:11">
       <c r="A520" s="7">
         <v>2025</v>
       </c>
@@ -20050,7 +19543,7 @@
       <c r="I520" s="5"/>
       <c r="J520" s="5"/>
     </row>
-    <row r="521" ht="17" spans="1:11">
+    <row r="521" spans="1:11">
       <c r="A521" s="7">
         <v>2025</v>
       </c>
@@ -20078,7 +19571,7 @@
       <c r="I521" s="5"/>
       <c r="J521" s="5"/>
     </row>
-    <row r="522" ht="17" spans="1:11">
+    <row r="522" spans="1:11">
       <c r="A522" s="2">
         <v>2025</v>
       </c>
@@ -20105,7 +19598,7 @@
       <c r="J522" s="6"/>
       <c r="K522" s="5"/>
     </row>
-    <row r="523" ht="17" spans="1:11">
+    <row r="523" spans="1:11">
       <c r="A523" s="2">
         <v>2025</v>
       </c>
@@ -20132,7 +19625,7 @@
       <c r="J523" s="6"/>
       <c r="K523" s="5"/>
     </row>
-    <row r="524" ht="17" spans="1:11">
+    <row r="524" spans="1:11">
       <c r="A524" s="2">
         <v>2025</v>
       </c>
@@ -20159,7 +19652,7 @@
       <c r="J524" s="6"/>
       <c r="K524" s="5"/>
     </row>
-    <row r="525" ht="17" spans="1:11">
+    <row r="525" spans="1:11">
       <c r="A525" s="2">
         <v>2025</v>
       </c>
@@ -20186,7 +19679,7 @@
       <c r="J525" s="6"/>
       <c r="K525" s="5"/>
     </row>
-    <row r="526" ht="17" spans="1:11">
+    <row r="526" spans="1:11">
       <c r="A526" s="2">
         <v>2025</v>
       </c>
@@ -20213,7 +19706,7 @@
       <c r="J526" s="6"/>
       <c r="K526" s="5"/>
     </row>
-    <row r="527" ht="17" spans="1:11">
+    <row r="527" spans="1:11">
       <c r="A527" s="2">
         <v>2025</v>
       </c>
@@ -20240,7 +19733,7 @@
       <c r="J527" s="6"/>
       <c r="K527" s="5"/>
     </row>
-    <row r="528" ht="17" spans="1:11">
+    <row r="528" spans="1:11">
       <c r="A528" s="2">
         <v>2025</v>
       </c>
@@ -20267,7 +19760,7 @@
       <c r="J528" s="6"/>
       <c r="K528" s="5"/>
     </row>
-    <row r="529" ht="17" spans="1:11">
+    <row r="529" spans="1:11">
       <c r="A529" s="2">
         <v>2025</v>
       </c>
@@ -20294,7 +19787,7 @@
       <c r="J529" s="6"/>
       <c r="K529" s="5"/>
     </row>
-    <row r="530" ht="17" spans="1:11">
+    <row r="530" spans="1:11">
       <c r="A530" s="2">
         <v>2025</v>
       </c>
@@ -20321,7 +19814,7 @@
       <c r="J530" s="6"/>
       <c r="K530" s="5"/>
     </row>
-    <row r="531" ht="17" spans="1:11">
+    <row r="531" spans="1:11">
       <c r="A531" s="2">
         <v>2025</v>
       </c>
@@ -20348,7 +19841,7 @@
       <c r="J531" s="6"/>
       <c r="K531" s="5"/>
     </row>
-    <row r="532" ht="17" spans="1:11">
+    <row r="532" spans="1:11">
       <c r="A532" s="2">
         <v>2025</v>
       </c>
@@ -20375,7 +19868,7 @@
       <c r="J532" s="5"/>
       <c r="K532" s="5"/>
     </row>
-    <row r="533" ht="17" spans="1:11">
+    <row r="533" spans="1:11">
       <c r="A533" s="2">
         <v>2025</v>
       </c>
@@ -20402,7 +19895,7 @@
       <c r="J533" s="5"/>
       <c r="K533" s="5"/>
     </row>
-    <row r="534" ht="17" spans="1:11">
+    <row r="534" spans="1:11">
       <c r="A534" s="2">
         <v>2025</v>
       </c>
@@ -20429,7 +19922,7 @@
       <c r="J534" s="5"/>
       <c r="K534" s="5"/>
     </row>
-    <row r="535" ht="17" spans="1:11">
+    <row r="535" spans="1:11">
       <c r="A535" s="2">
         <v>2025</v>
       </c>
@@ -20456,7 +19949,7 @@
       <c r="J535" s="5"/>
       <c r="K535" s="5"/>
     </row>
-    <row r="536" ht="17" spans="1:11">
+    <row r="536" spans="1:11">
       <c r="A536" s="2">
         <v>2025</v>
       </c>
@@ -20483,7 +19976,7 @@
       <c r="J536" s="5"/>
       <c r="K536" s="5"/>
     </row>
-    <row r="537" ht="17" spans="1:11">
+    <row r="537" spans="1:11">
       <c r="A537" s="2">
         <v>2025</v>
       </c>
@@ -20510,7 +20003,7 @@
       <c r="J537" s="5"/>
       <c r="K537" s="5"/>
     </row>
-    <row r="538" ht="17" spans="1:11">
+    <row r="538" spans="1:11">
       <c r="A538" s="2">
         <v>2025</v>
       </c>
@@ -20537,7 +20030,7 @@
       <c r="J538" s="5"/>
       <c r="K538" s="5"/>
     </row>
-    <row r="539" ht="17" spans="1:11">
+    <row r="539" spans="1:11">
       <c r="A539" s="2">
         <v>2025</v>
       </c>
@@ -20564,7 +20057,7 @@
       <c r="J539" s="5"/>
       <c r="K539" s="5"/>
     </row>
-    <row r="540" ht="17" spans="1:11">
+    <row r="540" spans="1:11">
       <c r="A540" s="2">
         <v>2025</v>
       </c>
@@ -20591,7 +20084,7 @@
       <c r="J540" s="5"/>
       <c r="K540" s="5"/>
     </row>
-    <row r="541" ht="17" spans="1:11">
+    <row r="541" spans="1:11">
       <c r="A541" s="2">
         <v>2025</v>
       </c>
@@ -20618,7 +20111,7 @@
       <c r="J541" s="5"/>
       <c r="K541" s="5"/>
     </row>
-    <row r="542" ht="17" spans="1:11">
+    <row r="542" spans="1:11">
       <c r="A542" s="7">
         <v>2025</v>
       </c>
@@ -20646,7 +20139,7 @@
       <c r="I542" s="6"/>
       <c r="J542" s="5"/>
     </row>
-    <row r="543" ht="17" spans="1:11">
+    <row r="543" spans="1:11">
       <c r="A543" s="7">
         <v>2025</v>
       </c>
@@ -20674,7 +20167,7 @@
       <c r="I543" s="5"/>
       <c r="J543" s="5"/>
     </row>
-    <row r="544" ht="17" spans="1:11">
+    <row r="544" spans="1:11">
       <c r="A544" s="7">
         <v>2025</v>
       </c>
@@ -20702,7 +20195,7 @@
       <c r="I544" s="5"/>
       <c r="J544" s="5"/>
     </row>
-    <row r="545" ht="17" spans="1:10">
+    <row r="545" spans="1:10">
       <c r="A545" s="7">
         <v>2025</v>
       </c>
@@ -20730,7 +20223,7 @@
       <c r="I545" s="5"/>
       <c r="J545" s="5"/>
     </row>
-    <row r="546" ht="17" spans="1:10">
+    <row r="546" spans="1:10">
       <c r="A546" s="7">
         <v>2025</v>
       </c>
@@ -20758,7 +20251,7 @@
       <c r="I546" s="5"/>
       <c r="J546" s="5"/>
     </row>
-    <row r="547" ht="17" spans="1:10">
+    <row r="547" spans="1:10">
       <c r="A547" s="7">
         <v>2025</v>
       </c>
@@ -20786,7 +20279,7 @@
       <c r="I547" s="5"/>
       <c r="J547" s="5"/>
     </row>
-    <row r="548" ht="17" spans="1:10">
+    <row r="548" spans="1:10">
       <c r="A548" s="7">
         <v>2025</v>
       </c>
@@ -20814,7 +20307,7 @@
       <c r="I548" s="5"/>
       <c r="J548" s="5"/>
     </row>
-    <row r="549" ht="17" spans="1:10">
+    <row r="549" spans="1:10">
       <c r="A549" s="7">
         <v>2025</v>
       </c>
@@ -20842,7 +20335,7 @@
       <c r="I549" s="5"/>
       <c r="J549" s="5"/>
     </row>
-    <row r="550" ht="17" spans="1:10">
+    <row r="550" spans="1:10">
       <c r="A550" s="7">
         <v>2025</v>
       </c>
@@ -20870,7 +20363,7 @@
       <c r="I550" s="5"/>
       <c r="J550" s="5"/>
     </row>
-    <row r="551" ht="17" spans="1:10">
+    <row r="551" spans="1:10">
       <c r="A551" s="7">
         <v>2025</v>
       </c>
@@ -20898,7 +20391,7 @@
       <c r="I551" s="5"/>
       <c r="J551" s="5"/>
     </row>
-    <row r="552" ht="17" spans="1:10">
+    <row r="552" spans="1:10">
       <c r="A552" s="7">
         <v>2025</v>
       </c>
@@ -20926,7 +20419,7 @@
       <c r="I552" s="5"/>
       <c r="J552" s="5"/>
     </row>
-    <row r="553" ht="17" spans="1:10">
+    <row r="553" spans="1:10">
       <c r="A553" s="7">
         <v>2025</v>
       </c>
@@ -20954,7 +20447,7 @@
       <c r="I553" s="5"/>
       <c r="J553" s="5"/>
     </row>
-    <row r="554" ht="17" spans="1:10">
+    <row r="554" spans="1:10">
       <c r="A554" s="7">
         <v>2025</v>
       </c>
@@ -20982,7 +20475,7 @@
       <c r="I554" s="5"/>
       <c r="J554" s="5"/>
     </row>
-    <row r="555" ht="17" spans="1:10">
+    <row r="555" spans="1:10">
       <c r="A555" s="7">
         <v>2025</v>
       </c>
@@ -21010,7 +20503,7 @@
       <c r="I555" s="5"/>
       <c r="J555" s="5"/>
     </row>
-    <row r="556" ht="17" spans="1:10">
+    <row r="556" spans="1:10">
       <c r="A556" s="7">
         <v>2025</v>
       </c>
@@ -21038,7 +20531,7 @@
       <c r="I556" s="5"/>
       <c r="J556" s="5"/>
     </row>
-    <row r="557" ht="17" spans="1:10">
+    <row r="557" spans="1:10">
       <c r="A557" s="7">
         <v>2025</v>
       </c>
@@ -21066,7 +20559,7 @@
       <c r="I557" s="5"/>
       <c r="J557" s="5"/>
     </row>
-    <row r="558" ht="17" spans="1:10">
+    <row r="558" spans="1:10">
       <c r="A558" s="7">
         <v>2025</v>
       </c>
@@ -21094,7 +20587,7 @@
       <c r="I558" s="5"/>
       <c r="J558" s="5"/>
     </row>
-    <row r="559" ht="17" spans="1:10">
+    <row r="559" spans="1:10">
       <c r="A559" s="7">
         <v>2025</v>
       </c>
@@ -21122,7 +20615,7 @@
       <c r="I559" s="5"/>
       <c r="J559" s="5"/>
     </row>
-    <row r="560" ht="17" spans="1:10">
+    <row r="560" spans="1:10">
       <c r="A560" s="7">
         <v>2025</v>
       </c>
@@ -21150,7 +20643,7 @@
       <c r="I560" s="5"/>
       <c r="J560" s="5"/>
     </row>
-    <row r="561" ht="17" spans="1:16">
+    <row r="561" spans="1:16">
       <c r="A561" s="7">
         <v>2025</v>
       </c>
@@ -21703,7 +21196,7 @@
       <c r="H581" s="2"/>
       <c r="N581" s="11"/>
     </row>
-    <row r="582" ht="17" spans="1:14">
+    <row r="582" spans="1:14">
       <c r="A582" s="7">
         <v>2025</v>
       </c>
@@ -21731,7 +21224,7 @@
       <c r="I582" s="6"/>
       <c r="J582" s="5"/>
     </row>
-    <row r="583" ht="17" spans="1:14">
+    <row r="583" spans="1:14">
       <c r="A583" s="7">
         <v>2025</v>
       </c>
@@ -21759,7 +21252,7 @@
       <c r="I583" s="5"/>
       <c r="J583" s="5"/>
     </row>
-    <row r="584" ht="17" spans="1:14">
+    <row r="584" spans="1:14">
       <c r="A584" s="7">
         <v>2025</v>
       </c>
@@ -21787,7 +21280,7 @@
       <c r="I584" s="5"/>
       <c r="J584" s="5"/>
     </row>
-    <row r="585" ht="17" spans="1:14">
+    <row r="585" spans="1:14">
       <c r="A585" s="7">
         <v>2025</v>
       </c>
@@ -21815,7 +21308,7 @@
       <c r="I585" s="5"/>
       <c r="J585" s="5"/>
     </row>
-    <row r="586" ht="17" spans="1:14">
+    <row r="586" spans="1:14">
       <c r="A586" s="7">
         <v>2025</v>
       </c>
@@ -21843,7 +21336,7 @@
       <c r="I586" s="5"/>
       <c r="J586" s="5"/>
     </row>
-    <row r="587" ht="17" spans="1:14">
+    <row r="587" spans="1:14">
       <c r="A587" s="7">
         <v>2025</v>
       </c>
@@ -21871,7 +21364,7 @@
       <c r="I587" s="5"/>
       <c r="J587" s="5"/>
     </row>
-    <row r="588" ht="17" spans="1:14">
+    <row r="588" spans="1:14">
       <c r="A588" s="7">
         <v>2025</v>
       </c>
@@ -21899,7 +21392,7 @@
       <c r="I588" s="5"/>
       <c r="J588" s="5"/>
     </row>
-    <row r="589" ht="17" spans="1:14">
+    <row r="589" spans="1:14">
       <c r="A589" s="7">
         <v>2025</v>
       </c>
@@ -21927,7 +21420,7 @@
       <c r="I589" s="5"/>
       <c r="J589" s="5"/>
     </row>
-    <row r="590" ht="17" spans="1:14">
+    <row r="590" spans="1:14">
       <c r="A590" s="7">
         <v>2025</v>
       </c>
@@ -21955,7 +21448,7 @@
       <c r="I590" s="5"/>
       <c r="J590" s="5"/>
     </row>
-    <row r="591" ht="17" spans="1:14">
+    <row r="591" spans="1:14">
       <c r="A591" s="7">
         <v>2025</v>
       </c>
@@ -21983,7 +21476,7 @@
       <c r="I591" s="5"/>
       <c r="J591" s="5"/>
     </row>
-    <row r="592" ht="17" spans="1:14">
+    <row r="592" spans="1:14">
       <c r="A592" s="7">
         <v>2025</v>
       </c>
@@ -22011,7 +21504,7 @@
       <c r="I592" s="5"/>
       <c r="J592" s="5"/>
     </row>
-    <row r="593" ht="17" spans="1:10">
+    <row r="593" spans="1:10">
       <c r="A593" s="7">
         <v>2025</v>
       </c>
@@ -22039,7 +21532,7 @@
       <c r="I593" s="5"/>
       <c r="J593" s="5"/>
     </row>
-    <row r="594" ht="17" spans="1:10">
+    <row r="594" spans="1:10">
       <c r="A594" s="7">
         <v>2025</v>
       </c>
@@ -22067,7 +21560,7 @@
       <c r="I594" s="5"/>
       <c r="J594" s="5"/>
     </row>
-    <row r="595" ht="17" spans="1:10">
+    <row r="595" spans="1:10">
       <c r="A595" s="7">
         <v>2025</v>
       </c>
@@ -22095,7 +21588,7 @@
       <c r="I595" s="5"/>
       <c r="J595" s="5"/>
     </row>
-    <row r="596" ht="17" spans="1:10">
+    <row r="596" spans="1:10">
       <c r="A596" s="7">
         <v>2025</v>
       </c>
@@ -22123,7 +21616,7 @@
       <c r="I596" s="5"/>
       <c r="J596" s="5"/>
     </row>
-    <row r="597" ht="17" spans="1:10">
+    <row r="597" spans="1:10">
       <c r="A597" s="7">
         <v>2025</v>
       </c>
@@ -22151,7 +21644,7 @@
       <c r="I597" s="5"/>
       <c r="J597" s="5"/>
     </row>
-    <row r="598" ht="17" spans="1:10">
+    <row r="598" spans="1:10">
       <c r="A598" s="7">
         <v>2025</v>
       </c>
@@ -22179,7 +21672,7 @@
       <c r="I598" s="5"/>
       <c r="J598" s="5"/>
     </row>
-    <row r="599" ht="17" spans="1:10">
+    <row r="599" spans="1:10">
       <c r="A599" s="7">
         <v>2025</v>
       </c>
@@ -22207,7 +21700,7 @@
       <c r="I599" s="5"/>
       <c r="J599" s="5"/>
     </row>
-    <row r="600" ht="17" spans="1:10">
+    <row r="600" spans="1:10">
       <c r="A600" s="7">
         <v>2025</v>
       </c>
@@ -22235,7 +21728,7 @@
       <c r="I600" s="5"/>
       <c r="J600" s="5"/>
     </row>
-    <row r="601" ht="17" spans="1:10">
+    <row r="601" spans="1:10">
       <c r="A601" s="7">
         <v>2025</v>
       </c>
@@ -24288,7 +23781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="681" ht="17" spans="1:17">
+    <row r="681" spans="1:17">
       <c r="A681" s="7">
         <v>2025</v>
       </c>
@@ -24314,7 +23807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="682" ht="17" spans="1:17">
+    <row r="682" spans="1:17">
       <c r="A682" s="2">
         <v>2025</v>
       </c>
@@ -24342,7 +23835,7 @@
       <c r="P682" s="6"/>
       <c r="Q682" s="5"/>
     </row>
-    <row r="683" ht="17" spans="1:17">
+    <row r="683" spans="1:17">
       <c r="A683" s="2">
         <v>2025</v>
       </c>
@@ -24370,7 +23863,7 @@
       <c r="P683" s="6"/>
       <c r="Q683" s="5"/>
     </row>
-    <row r="684" ht="17" spans="1:17">
+    <row r="684" spans="1:17">
       <c r="A684" s="2">
         <v>2025</v>
       </c>
@@ -24398,7 +23891,7 @@
       <c r="P684" s="6"/>
       <c r="Q684" s="5"/>
     </row>
-    <row r="685" ht="17" spans="1:17">
+    <row r="685" spans="1:17">
       <c r="A685" s="2">
         <v>2025</v>
       </c>
@@ -24426,7 +23919,7 @@
       <c r="P685" s="6"/>
       <c r="Q685" s="5"/>
     </row>
-    <row r="686" ht="17" spans="1:17">
+    <row r="686" spans="1:17">
       <c r="A686" s="2">
         <v>2025</v>
       </c>
@@ -24454,7 +23947,7 @@
       <c r="P686" s="6"/>
       <c r="Q686" s="5"/>
     </row>
-    <row r="687" ht="17" spans="1:17">
+    <row r="687" spans="1:17">
       <c r="A687" s="2">
         <v>2025</v>
       </c>
@@ -24482,7 +23975,7 @@
       <c r="P687" s="6"/>
       <c r="Q687" s="5"/>
     </row>
-    <row r="688" ht="17" spans="1:17">
+    <row r="688" spans="1:17">
       <c r="A688" s="2">
         <v>2025</v>
       </c>
@@ -24510,7 +24003,7 @@
       <c r="P688" s="6"/>
       <c r="Q688" s="5"/>
     </row>
-    <row r="689" ht="17" spans="1:17">
+    <row r="689" spans="1:17">
       <c r="A689" s="2">
         <v>2025</v>
       </c>
@@ -24538,7 +24031,7 @@
       <c r="P689" s="6"/>
       <c r="Q689" s="5"/>
     </row>
-    <row r="690" ht="17" spans="1:17">
+    <row r="690" spans="1:17">
       <c r="A690" s="2">
         <v>2025</v>
       </c>
@@ -24566,7 +24059,7 @@
       <c r="P690" s="6"/>
       <c r="Q690" s="5"/>
     </row>
-    <row r="691" ht="17" spans="1:17">
+    <row r="691" spans="1:17">
       <c r="A691" s="2">
         <v>2025</v>
       </c>
@@ -24594,7 +24087,7 @@
       <c r="P691" s="6"/>
       <c r="Q691" s="5"/>
     </row>
-    <row r="692" ht="17" spans="1:17">
+    <row r="692" spans="1:17">
       <c r="A692" s="2">
         <v>2025</v>
       </c>
@@ -24622,7 +24115,7 @@
       <c r="P692" s="5"/>
       <c r="Q692" s="5"/>
     </row>
-    <row r="693" ht="17" spans="1:17">
+    <row r="693" spans="1:17">
       <c r="A693" s="2">
         <v>2025</v>
       </c>
@@ -24650,7 +24143,7 @@
       <c r="P693" s="5"/>
       <c r="Q693" s="5"/>
     </row>
-    <row r="694" ht="17" spans="1:17">
+    <row r="694" spans="1:17">
       <c r="A694" s="2">
         <v>2025</v>
       </c>
@@ -24678,7 +24171,7 @@
       <c r="P694" s="5"/>
       <c r="Q694" s="5"/>
     </row>
-    <row r="695" ht="17" spans="1:17">
+    <row r="695" spans="1:17">
       <c r="A695" s="2">
         <v>2025</v>
       </c>
@@ -24706,7 +24199,7 @@
       <c r="P695" s="5"/>
       <c r="Q695" s="5"/>
     </row>
-    <row r="696" ht="17" spans="1:17">
+    <row r="696" spans="1:17">
       <c r="A696" s="2">
         <v>2025</v>
       </c>
@@ -24734,7 +24227,7 @@
       <c r="P696" s="5"/>
       <c r="Q696" s="5"/>
     </row>
-    <row r="697" ht="17" spans="1:17">
+    <row r="697" spans="1:17">
       <c r="A697" s="2">
         <v>2025</v>
       </c>
@@ -24762,7 +24255,7 @@
       <c r="P697" s="5"/>
       <c r="Q697" s="5"/>
     </row>
-    <row r="698" ht="17" spans="1:17">
+    <row r="698" spans="1:17">
       <c r="A698" s="2">
         <v>2025</v>
       </c>
@@ -24790,7 +24283,7 @@
       <c r="P698" s="5"/>
       <c r="Q698" s="5"/>
     </row>
-    <row r="699" ht="17" spans="1:17">
+    <row r="699" spans="1:17">
       <c r="A699" s="2">
         <v>2025</v>
       </c>
@@ -24818,7 +24311,7 @@
       <c r="P699" s="5"/>
       <c r="Q699" s="5"/>
     </row>
-    <row r="700" ht="17" spans="1:17">
+    <row r="700" spans="1:17">
       <c r="A700" s="2">
         <v>2025</v>
       </c>
@@ -24846,7 +24339,7 @@
       <c r="P700" s="5"/>
       <c r="Q700" s="5"/>
     </row>
-    <row r="701" ht="17" spans="1:17">
+    <row r="701" spans="1:17">
       <c r="A701" s="2">
         <v>2025</v>
       </c>
@@ -24874,7 +24367,7 @@
       <c r="P701" s="5"/>
       <c r="Q701" s="5"/>
     </row>
-    <row r="702" ht="17" spans="1:17">
+    <row r="702" spans="1:17">
       <c r="A702" s="7">
         <v>2025</v>
       </c>
@@ -24901,7 +24394,7 @@
       </c>
       <c r="I702" s="6"/>
     </row>
-    <row r="703" ht="17" spans="1:17">
+    <row r="703" spans="1:17">
       <c r="A703" s="7">
         <v>2025</v>
       </c>
@@ -24928,7 +24421,7 @@
       </c>
       <c r="I703" s="5"/>
     </row>
-    <row r="704" ht="17" spans="1:17">
+    <row r="704" spans="1:17">
       <c r="A704" s="7">
         <v>2025</v>
       </c>
@@ -24955,7 +24448,7 @@
       </c>
       <c r="I704" s="5"/>
     </row>
-    <row r="705" ht="17" spans="1:9">
+    <row r="705" spans="1:9">
       <c r="A705" s="7">
         <v>2025</v>
       </c>
@@ -24982,7 +24475,7 @@
       </c>
       <c r="I705" s="5"/>
     </row>
-    <row r="706" ht="17" spans="1:9">
+    <row r="706" spans="1:9">
       <c r="A706" s="7">
         <v>2025</v>
       </c>
@@ -25009,7 +24502,7 @@
       </c>
       <c r="I706" s="5"/>
     </row>
-    <row r="707" ht="17" spans="1:9">
+    <row r="707" spans="1:9">
       <c r="A707" s="7">
         <v>2025</v>
       </c>
@@ -25036,7 +24529,7 @@
       </c>
       <c r="I707" s="5"/>
     </row>
-    <row r="708" ht="17" spans="1:9">
+    <row r="708" spans="1:9">
       <c r="A708" s="7">
         <v>2025</v>
       </c>
@@ -25063,7 +24556,7 @@
       </c>
       <c r="I708" s="5"/>
     </row>
-    <row r="709" ht="17" spans="1:9">
+    <row r="709" spans="1:9">
       <c r="A709" s="7">
         <v>2025</v>
       </c>
@@ -25090,7 +24583,7 @@
       </c>
       <c r="I709" s="5"/>
     </row>
-    <row r="710" ht="17" spans="1:9">
+    <row r="710" spans="1:9">
       <c r="A710" s="7">
         <v>2025</v>
       </c>
@@ -25117,7 +24610,7 @@
       </c>
       <c r="I710" s="5"/>
     </row>
-    <row r="711" ht="17" spans="1:9">
+    <row r="711" spans="1:9">
       <c r="A711" s="7">
         <v>2025</v>
       </c>
@@ -25144,7 +24637,7 @@
       </c>
       <c r="I711" s="5"/>
     </row>
-    <row r="712" ht="17" spans="1:9">
+    <row r="712" spans="1:9">
       <c r="A712" s="7">
         <v>2025</v>
       </c>
@@ -25171,7 +24664,7 @@
       </c>
       <c r="I712" s="5"/>
     </row>
-    <row r="713" ht="17" spans="1:9">
+    <row r="713" spans="1:9">
       <c r="A713" s="7">
         <v>2025</v>
       </c>
@@ -25198,7 +24691,7 @@
       </c>
       <c r="I713" s="5"/>
     </row>
-    <row r="714" ht="17" spans="1:9">
+    <row r="714" spans="1:9">
       <c r="A714" s="7">
         <v>2025</v>
       </c>
@@ -25225,7 +24718,7 @@
       </c>
       <c r="I714" s="5"/>
     </row>
-    <row r="715" ht="17" spans="1:9">
+    <row r="715" spans="1:9">
       <c r="A715" s="7">
         <v>2025</v>
       </c>
@@ -25252,7 +24745,7 @@
       </c>
       <c r="I715" s="5"/>
     </row>
-    <row r="716" ht="17" spans="1:9">
+    <row r="716" spans="1:9">
       <c r="A716" s="7">
         <v>2025</v>
       </c>
@@ -25279,7 +24772,7 @@
       </c>
       <c r="I716" s="5"/>
     </row>
-    <row r="717" ht="17" spans="1:9">
+    <row r="717" spans="1:9">
       <c r="A717" s="7">
         <v>2025</v>
       </c>
@@ -25306,7 +24799,7 @@
       </c>
       <c r="I717" s="5"/>
     </row>
-    <row r="718" ht="17" spans="1:9">
+    <row r="718" spans="1:9">
       <c r="A718" s="7">
         <v>2025</v>
       </c>
@@ -25333,7 +24826,7 @@
       </c>
       <c r="I718" s="5"/>
     </row>
-    <row r="719" ht="17" spans="1:9">
+    <row r="719" spans="1:9">
       <c r="A719" s="7">
         <v>2025</v>
       </c>
@@ -25360,7 +24853,7 @@
       </c>
       <c r="I719" s="5"/>
     </row>
-    <row r="720" ht="17" spans="1:9">
+    <row r="720" spans="1:9">
       <c r="A720" s="7">
         <v>2025</v>
       </c>
@@ -25387,7 +24880,7 @@
       </c>
       <c r="I720" s="5"/>
     </row>
-    <row r="721" ht="17" spans="1:11">
+    <row r="721" spans="1:11">
       <c r="A721" s="7">
         <v>2025</v>
       </c>
@@ -25414,7 +24907,7 @@
       </c>
       <c r="I721" s="5"/>
     </row>
-    <row r="722" ht="17" spans="1:11">
+    <row r="722" spans="1:11">
       <c r="A722" s="2">
         <v>2025</v>
       </c>
@@ -25441,7 +24934,7 @@
       <c r="J722" s="6"/>
       <c r="K722" s="5"/>
     </row>
-    <row r="723" ht="17" spans="1:11">
+    <row r="723" spans="1:11">
       <c r="A723" s="2">
         <v>2025</v>
       </c>
@@ -25468,7 +24961,7 @@
       <c r="J723" s="6"/>
       <c r="K723" s="5"/>
     </row>
-    <row r="724" ht="17" spans="1:11">
+    <row r="724" spans="1:11">
       <c r="A724" s="2">
         <v>2025</v>
       </c>
@@ -25495,7 +24988,7 @@
       <c r="J724" s="6"/>
       <c r="K724" s="5"/>
     </row>
-    <row r="725" ht="17" spans="1:11">
+    <row r="725" spans="1:11">
       <c r="A725" s="2">
         <v>2025</v>
       </c>
@@ -25522,7 +25015,7 @@
       <c r="J725" s="6"/>
       <c r="K725" s="5"/>
     </row>
-    <row r="726" ht="17" spans="1:11">
+    <row r="726" spans="1:11">
       <c r="A726" s="2">
         <v>2025</v>
       </c>
@@ -25549,7 +25042,7 @@
       <c r="J726" s="6"/>
       <c r="K726" s="5"/>
     </row>
-    <row r="727" ht="17" spans="1:11">
+    <row r="727" spans="1:11">
       <c r="A727" s="2">
         <v>2025</v>
       </c>
@@ -25576,7 +25069,7 @@
       <c r="J727" s="6"/>
       <c r="K727" s="5"/>
     </row>
-    <row r="728" ht="17" spans="1:11">
+    <row r="728" spans="1:11">
       <c r="A728" s="2">
         <v>2025</v>
       </c>
@@ -25603,7 +25096,7 @@
       <c r="J728" s="6"/>
       <c r="K728" s="5"/>
     </row>
-    <row r="729" ht="17" spans="1:11">
+    <row r="729" spans="1:11">
       <c r="A729" s="2">
         <v>2025</v>
       </c>
@@ -25630,7 +25123,7 @@
       <c r="J729" s="6"/>
       <c r="K729" s="5"/>
     </row>
-    <row r="730" ht="17" spans="1:11">
+    <row r="730" spans="1:11">
       <c r="A730" s="2">
         <v>2025</v>
       </c>
@@ -25657,7 +25150,7 @@
       <c r="J730" s="6"/>
       <c r="K730" s="5"/>
     </row>
-    <row r="731" ht="17" spans="1:11">
+    <row r="731" spans="1:11">
       <c r="A731" s="2">
         <v>2025</v>
       </c>
@@ -25684,7 +25177,7 @@
       <c r="J731" s="6"/>
       <c r="K731" s="5"/>
     </row>
-    <row r="732" ht="17" spans="1:11">
+    <row r="732" spans="1:11">
       <c r="A732" s="2">
         <v>2025</v>
       </c>
@@ -25711,7 +25204,7 @@
       <c r="J732" s="5"/>
       <c r="K732" s="5"/>
     </row>
-    <row r="733" ht="17" spans="1:11">
+    <row r="733" spans="1:11">
       <c r="A733" s="2">
         <v>2025</v>
       </c>
@@ -25738,7 +25231,7 @@
       <c r="J733" s="5"/>
       <c r="K733" s="5"/>
     </row>
-    <row r="734" ht="17" spans="1:11">
+    <row r="734" spans="1:11">
       <c r="A734" s="2">
         <v>2025</v>
       </c>
@@ -25765,7 +25258,7 @@
       <c r="J734" s="5"/>
       <c r="K734" s="5"/>
     </row>
-    <row r="735" ht="17" spans="1:11">
+    <row r="735" spans="1:11">
       <c r="A735" s="2">
         <v>2025</v>
       </c>
@@ -25792,7 +25285,7 @@
       <c r="J735" s="5"/>
       <c r="K735" s="5"/>
     </row>
-    <row r="736" ht="17" spans="1:11">
+    <row r="736" spans="1:11">
       <c r="A736" s="2">
         <v>2025</v>
       </c>
@@ -25819,7 +25312,7 @@
       <c r="J736" s="5"/>
       <c r="K736" s="5"/>
     </row>
-    <row r="737" ht="17" spans="1:11">
+    <row r="737" spans="1:11">
       <c r="A737" s="2">
         <v>2025</v>
       </c>
@@ -25846,7 +25339,7 @@
       <c r="J737" s="5"/>
       <c r="K737" s="5"/>
     </row>
-    <row r="738" ht="17" spans="1:11">
+    <row r="738" spans="1:11">
       <c r="A738" s="2">
         <v>2025</v>
       </c>
@@ -25873,7 +25366,7 @@
       <c r="J738" s="5"/>
       <c r="K738" s="5"/>
     </row>
-    <row r="739" ht="17" spans="1:11">
+    <row r="739" spans="1:11">
       <c r="A739" s="2">
         <v>2025</v>
       </c>
@@ -25900,7 +25393,7 @@
       <c r="J739" s="5"/>
       <c r="K739" s="5"/>
     </row>
-    <row r="740" ht="17" spans="1:11">
+    <row r="740" spans="1:11">
       <c r="A740" s="2">
         <v>2025</v>
       </c>
@@ -25927,7 +25420,7 @@
       <c r="J740" s="5"/>
       <c r="K740" s="5"/>
     </row>
-    <row r="741" ht="17" spans="1:11">
+    <row r="741" spans="1:11">
       <c r="A741" s="2">
         <v>2025</v>
       </c>
@@ -25954,7 +25447,7 @@
       <c r="J741" s="5"/>
       <c r="K741" s="5"/>
     </row>
-    <row r="742" ht="17" spans="1:11">
+    <row r="742" spans="1:11">
       <c r="A742" s="7">
         <v>2025</v>
       </c>
@@ -25980,7 +25473,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="743" ht="17" spans="1:11">
+    <row r="743" spans="1:11">
       <c r="A743" s="7">
         <v>2025</v>
       </c>
@@ -26006,7 +25499,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="744" ht="17" spans="1:11">
+    <row r="744" spans="1:11">
       <c r="A744" s="7">
         <v>2025</v>
       </c>
@@ -26032,7 +25525,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="745" ht="17" spans="1:11">
+    <row r="745" spans="1:11">
       <c r="A745" s="7">
         <v>2025</v>
       </c>
@@ -26058,7 +25551,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="746" ht="17" spans="1:11">
+    <row r="746" spans="1:11">
       <c r="A746" s="7">
         <v>2025</v>
       </c>
@@ -26084,7 +25577,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="747" ht="17" spans="1:11">
+    <row r="747" spans="1:11">
       <c r="A747" s="7">
         <v>2025</v>
       </c>
@@ -26110,7 +25603,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="748" ht="17" spans="1:11">
+    <row r="748" spans="1:11">
       <c r="A748" s="7">
         <v>2025</v>
       </c>
@@ -26136,7 +25629,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="749" ht="17" spans="1:11">
+    <row r="749" spans="1:11">
       <c r="A749" s="7">
         <v>2025</v>
       </c>
@@ -26162,7 +25655,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="750" ht="17" spans="1:11">
+    <row r="750" spans="1:11">
       <c r="A750" s="7">
         <v>2025</v>
       </c>
@@ -26188,7 +25681,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="751" ht="17" spans="1:11">
+    <row r="751" spans="1:11">
       <c r="A751" s="7">
         <v>2025</v>
       </c>
@@ -26214,7 +25707,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="752" ht="17" spans="1:11">
+    <row r="752" spans="1:11">
       <c r="A752" s="7">
         <v>2025</v>
       </c>
@@ -26240,7 +25733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="753" ht="17" spans="1:16">
+    <row r="753" spans="1:16">
       <c r="A753" s="7">
         <v>2025</v>
       </c>
@@ -26266,7 +25759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="754" ht="17" spans="1:16">
+    <row r="754" spans="1:16">
       <c r="A754" s="7">
         <v>2025</v>
       </c>
@@ -26292,7 +25785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="755" ht="17" spans="1:16">
+    <row r="755" spans="1:16">
       <c r="A755" s="7">
         <v>2025</v>
       </c>
@@ -26318,7 +25811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="756" ht="17" spans="1:16">
+    <row r="756" spans="1:16">
       <c r="A756" s="7">
         <v>2025</v>
       </c>
@@ -26344,7 +25837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="757" ht="17" spans="1:16">
+    <row r="757" spans="1:16">
       <c r="A757" s="7">
         <v>2025</v>
       </c>
@@ -26370,7 +25863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="758" ht="17" spans="1:16">
+    <row r="758" spans="1:16">
       <c r="A758" s="7">
         <v>2025</v>
       </c>
@@ -26396,7 +25889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="759" ht="17" spans="1:16">
+    <row r="759" spans="1:16">
       <c r="A759" s="7">
         <v>2025</v>
       </c>
@@ -26422,7 +25915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="760" ht="17" spans="1:16">
+    <row r="760" spans="1:16">
       <c r="A760" s="7">
         <v>2025</v>
       </c>
@@ -26448,7 +25941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="761" ht="17" spans="1:16">
+    <row r="761" spans="1:16">
       <c r="A761" s="7">
         <v>2025</v>
       </c>
@@ -27489,7 +26982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="801" ht="17" spans="1:8">
+    <row r="801" spans="1:8">
       <c r="A801" s="2">
         <v>2025</v>
       </c>
@@ -37560,28 +37053,24 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H1201" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
+  <autoFilter ref="A1:H1201" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.71428571428571" customWidth="1"/>
-    <col min="2" max="2" width="15.4285714285714" customWidth="1"/>
-    <col min="3" max="3" width="9.42857142857143" customWidth="1"/>
-    <col min="4" max="4" width="42.5714285714286" customWidth="1"/>
-    <col min="5" max="5" width="11.7142857142857" customWidth="1"/>
-    <col min="6" max="6" width="4.57142857142857" customWidth="1"/>
-    <col min="7" max="7" width="6.71428571428571" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.42578125" customWidth="1"/>
+    <col min="3" max="3" width="9.42578125" customWidth="1"/>
+    <col min="4" max="4" width="42.5703125" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.5703125" customWidth="1"/>
+    <col min="7" max="7" width="6.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -37625,7 +37114,7 @@
         <v>58</v>
       </c>
       <c r="G2" s="2">
-        <v>5.278</v>
+        <v>5.2779999999999996</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -37646,7 +37135,7 @@
         <v>56</v>
       </c>
       <c r="G3" s="2">
-        <v>5.451</v>
+        <v>5.4509999999999996</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -37667,7 +37156,7 @@
         <v>53</v>
       </c>
       <c r="G4" s="2">
-        <v>5.807</v>
+        <v>5.8070000000000004</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -37688,7 +37177,7 @@
         <v>57</v>
       </c>
       <c r="G5" s="2">
-        <v>5.412</v>
+        <v>5.4119999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -37709,7 +37198,7 @@
         <v>50</v>
       </c>
       <c r="G6" s="2">
-        <v>5.174</v>
+        <v>5.1740000000000004</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -37732,7 +37221,7 @@
         <v>57</v>
       </c>
       <c r="G7" s="2">
-        <v>5.412</v>
+        <v>5.4119999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -37755,7 +37244,7 @@
         <v>63</v>
       </c>
       <c r="G8" s="2">
-        <v>4.909</v>
+        <v>4.9089999999999998</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -37776,7 +37265,7 @@
         <v>78</v>
       </c>
       <c r="G9" s="2">
-        <v>3.337</v>
+        <v>3.3370000000000002</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -37820,7 +37309,7 @@
         <v>70</v>
       </c>
       <c r="G11" s="2">
-        <v>4.361</v>
+        <v>4.3609999999999998</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -37841,7 +37330,7 @@
         <v>71</v>
       </c>
       <c r="G12" s="2">
-        <v>4.318</v>
+        <v>4.3179999999999996</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -37883,7 +37372,7 @@
         <v>44</v>
       </c>
       <c r="G14" s="2">
-        <v>7.004</v>
+        <v>7.0039999999999996</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -37904,7 +37393,7 @@
         <v>70</v>
       </c>
       <c r="G15" s="2">
-        <v>4.381</v>
+        <v>4.3810000000000002</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -37925,7 +37414,7 @@
         <v>72</v>
       </c>
       <c r="G16" s="2">
-        <v>4.259</v>
+        <v>4.2590000000000003</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -37948,7 +37437,7 @@
         <v>53</v>
       </c>
       <c r="G17" s="2">
-        <v>5.793</v>
+        <v>5.7930000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -37969,7 +37458,7 @@
         <v>51</v>
       </c>
       <c r="G18" s="2">
-        <v>6.003</v>
+        <v>6.0030000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -38013,7 +37502,7 @@
         <v>56</v>
       </c>
       <c r="G20" s="2">
-        <v>5.513</v>
+        <v>5.5129999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -38034,7 +37523,7 @@
         <v>71</v>
       </c>
       <c r="G21" s="2">
-        <v>4.304</v>
+        <v>4.3040000000000003</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -38055,7 +37544,7 @@
         <v>71</v>
       </c>
       <c r="G22" s="2">
-        <v>4.309</v>
+        <v>4.3090000000000002</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -38078,7 +37567,7 @@
         <v>50</v>
       </c>
       <c r="G23" s="2">
-        <v>6.201</v>
+        <v>6.2009999999999996</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -38099,7 +37588,7 @@
         <v>57</v>
       </c>
       <c r="G24" s="2">
-        <v>5.419</v>
+        <v>5.4189999999999996</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -38120,26 +37609,24 @@
         <v>58</v>
       </c>
       <c r="G25" s="2">
-        <v>5.281</v>
+        <v>5.2809999999999997</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:G22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="5.14285714285714" customWidth="1"/>
-    <col min="3" max="3" width="7.71428571428571" customWidth="1"/>
+    <col min="1" max="2" width="5.140625" customWidth="1"/>
+    <col min="3" max="3" width="7.7109375" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="5" max="5" width="14.7142857142857" customWidth="1"/>
-    <col min="6" max="6" width="15.4285714285714" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" customWidth="1"/>
+    <col min="6" max="6" width="15.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -38651,20 +38138,18 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:E32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="12.2857142857143" customWidth="1"/>
-    <col min="3" max="3" width="29.2857142857143" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" customWidth="1"/>
+    <col min="3" max="3" width="29.28515625" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="8.57142857142857" customWidth="1"/>
+    <col min="5" max="5" width="8.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -38684,7 +38169,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="2" ht="17" spans="1:5">
+    <row r="2" spans="1:5">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -38701,7 +38186,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="3" ht="17" spans="1:5">
+    <row r="3" spans="1:5">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -38718,7 +38203,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="4" ht="17" spans="1:5">
+    <row r="4" spans="1:5">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -38735,7 +38220,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="5" ht="17" spans="1:5">
+    <row r="5" spans="1:5">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -38752,7 +38237,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="6" ht="17" spans="1:5">
+    <row r="6" spans="1:5">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -38769,7 +38254,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="7" ht="17" spans="1:5">
+    <row r="7" spans="1:5">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -38786,7 +38271,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="8" ht="17" spans="1:5">
+    <row r="8" spans="1:5">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -38803,7 +38288,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="9" ht="17" spans="1:5">
+    <row r="9" spans="1:5">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -38820,7 +38305,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="10" ht="17" spans="1:5">
+    <row r="10" spans="1:5">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -38837,7 +38322,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="11" ht="17" spans="1:5">
+    <row r="11" spans="1:5">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -38962,6 +38447,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/public/docs/datas/f1.xlsx
+++ b/public/docs/datas/f1.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Docs\byMe\vue_platform\public\docs\datas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8103B34-C4FD-4DBF-A32F-56AFB3A23F17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11835" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="26420" windowHeight="15520" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="rounds" sheetId="1" r:id="rId1"/>
@@ -41,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4209" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4449" uniqueCount="247">
   <si>
     <t>year</t>
   </si>
@@ -499,10 +493,10 @@
     <t>shortName</t>
   </si>
   <si>
-    <t>isActive</t>
+    <t>NOR</t>
   </si>
   <si>
-    <t>NOR</t>
+    <t>Lando Norris</t>
   </si>
   <si>
     <t>Norris</t>
@@ -511,10 +505,16 @@
     <t>PIA</t>
   </si>
   <si>
+    <t>Oscar Piastri</t>
+  </si>
+  <si>
     <t>Piastri</t>
   </si>
   <si>
     <t>VER</t>
+  </si>
+  <si>
+    <t>Max Verstappen</t>
   </si>
   <si>
     <t>Verstappen</t>
@@ -523,10 +523,16 @@
     <t>TSU</t>
   </si>
   <si>
+    <t>Yuki Tsunoda</t>
+  </si>
+  <si>
     <t>Tsunoda</t>
   </si>
   <si>
     <t>RUS</t>
+  </si>
+  <si>
+    <t>George Russell</t>
   </si>
   <si>
     <t>Russell</t>
@@ -535,10 +541,16 @@
     <t>ANT</t>
   </si>
   <si>
+    <t>Kimi Antonelli</t>
+  </si>
+  <si>
     <t>Antonelli</t>
   </si>
   <si>
     <t>LEC</t>
+  </si>
+  <si>
+    <t>Charles Leclerc</t>
   </si>
   <si>
     <t>Leclerc</t>
@@ -547,10 +559,16 @@
     <t>HAM</t>
   </si>
   <si>
+    <t>Lewis Hamilton</t>
+  </si>
+  <si>
     <t>Hamilton</t>
   </si>
   <si>
     <t>LAW</t>
+  </si>
+  <si>
+    <t>Liam Lawson</t>
   </si>
   <si>
     <t>Lawson</t>
@@ -562,6 +580,9 @@
     <t>HAD</t>
   </si>
   <si>
+    <t>Isack Hadjar</t>
+  </si>
+  <si>
     <t>Hadjar</t>
   </si>
   <si>
@@ -569,6 +590,9 @@
   </si>
   <si>
     <t>ALB</t>
+  </si>
+  <si>
+    <t>Alexander Albon</t>
   </si>
   <si>
     <t>Albon</t>
@@ -580,10 +604,16 @@
     <t>SAI</t>
   </si>
   <si>
+    <t>Carlos Sainz</t>
+  </si>
+  <si>
     <t>Sainz</t>
   </si>
   <si>
     <t>GAS</t>
+  </si>
+  <si>
+    <t>Pierre Gasly</t>
   </si>
   <si>
     <t>Gasly</t>
@@ -601,10 +631,16 @@
     <t>DOO</t>
   </si>
   <si>
+    <t>Jack Doohan</t>
+  </si>
+  <si>
     <t>Doohan</t>
   </si>
   <si>
     <t>STR</t>
+  </si>
+  <si>
+    <t>Lance Stroll</t>
   </si>
   <si>
     <t>Stroll</t>
@@ -613,10 +649,16 @@
     <t>ALO</t>
   </si>
   <si>
+    <t>Fernando Alonso</t>
+  </si>
+  <si>
     <t>Alonso</t>
   </si>
   <si>
     <t>HUL</t>
+  </si>
+  <si>
+    <t>Nico Hulkenberg</t>
   </si>
   <si>
     <t>Hulkenberg</t>
@@ -628,10 +670,16 @@
     <t>BOR</t>
   </si>
   <si>
+    <t>Gabriel Bortoleto</t>
+  </si>
+  <si>
     <t>Bortoleto</t>
   </si>
   <si>
     <t>OCO</t>
+  </si>
+  <si>
+    <t>Esteban Ocon</t>
   </si>
   <si>
     <t>Ocon</t>
@@ -640,7 +688,40 @@
     <t>BEA</t>
   </si>
   <si>
+    <t>Oliver Bearman</t>
+  </si>
+  <si>
     <t>Bearman</t>
+  </si>
+  <si>
+    <t>LIN</t>
+  </si>
+  <si>
+    <t>Arvid Lindblad</t>
+  </si>
+  <si>
+    <t>Lindblad</t>
+  </si>
+  <si>
+    <t>PER</t>
+  </si>
+  <si>
+    <t>Sergio Perez</t>
+  </si>
+  <si>
+    <t>Perez</t>
+  </si>
+  <si>
+    <t>BOT</t>
+  </si>
+  <si>
+    <t>Valtteri Bottas</t>
+  </si>
+  <si>
+    <t>Bottas</t>
+  </si>
+  <si>
+    <t>Finland</t>
   </si>
   <si>
     <t>newName</t>
@@ -700,24 +781,174 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -736,8 +967,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -760,9 +1177,251 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -806,17 +1465,61 @@
     <xf numFmtId="20" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1074,23 +1777,23 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:J49"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="5.5703125" customWidth="1"/>
-    <col min="2" max="2" width="6.7109375" customWidth="1"/>
-    <col min="3" max="3" width="12.28515625" customWidth="1"/>
+    <col min="1" max="1" width="5.57142857142857" customWidth="1"/>
+    <col min="2" max="2" width="6.71428571428571" customWidth="1"/>
+    <col min="3" max="3" width="12.2857142857143" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" customWidth="1"/>
-    <col min="6" max="6" width="43.7109375" customWidth="1"/>
-    <col min="7" max="7" width="11.140625" customWidth="1"/>
-    <col min="8" max="8" width="4.85546875" customWidth="1"/>
+    <col min="5" max="5" width="14.2857142857143" customWidth="1"/>
+    <col min="6" max="6" width="43.7142857142857" customWidth="1"/>
+    <col min="7" max="7" width="11.1428571428571" customWidth="1"/>
+    <col min="8" max="8" width="4.85714285714286" customWidth="1"/>
     <col min="9" max="9" width="7" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1148,7 +1851,7 @@
         <v>58</v>
       </c>
       <c r="I2" s="2">
-        <v>5.2779999999999996</v>
+        <v>5.278</v>
       </c>
       <c r="J2" s="2">
         <v>1</v>
@@ -1176,7 +1879,7 @@
         <v>56</v>
       </c>
       <c r="I3" s="2">
-        <v>5.4509999999999996</v>
+        <v>5.451</v>
       </c>
       <c r="J3" s="2">
         <v>1</v>
@@ -1204,7 +1907,7 @@
         <v>53</v>
       </c>
       <c r="I4" s="2">
-        <v>5.8070000000000004</v>
+        <v>5.807</v>
       </c>
       <c r="J4" s="2">
         <v>1</v>
@@ -1232,7 +1935,7 @@
         <v>57</v>
       </c>
       <c r="I5" s="2">
-        <v>5.4119999999999999</v>
+        <v>5.412</v>
       </c>
       <c r="J5" s="2">
         <v>1</v>
@@ -1260,7 +1963,7 @@
         <v>50</v>
       </c>
       <c r="I6" s="2">
-        <v>5.1740000000000004</v>
+        <v>5.174</v>
       </c>
       <c r="J6" s="2">
         <v>1</v>
@@ -1290,7 +1993,7 @@
         <v>57</v>
       </c>
       <c r="I7" s="2">
-        <v>5.4119999999999999</v>
+        <v>5.412</v>
       </c>
       <c r="J7" s="2">
         <v>1</v>
@@ -1320,7 +2023,7 @@
         <v>63</v>
       </c>
       <c r="I8" s="2">
-        <v>4.9089999999999998</v>
+        <v>4.909</v>
       </c>
       <c r="J8" s="2">
         <v>1</v>
@@ -1348,7 +2051,7 @@
         <v>78</v>
       </c>
       <c r="I9" s="2">
-        <v>3.3370000000000002</v>
+        <v>3.337</v>
       </c>
       <c r="J9" s="2">
         <v>1</v>
@@ -1404,7 +2107,7 @@
         <v>70</v>
       </c>
       <c r="I11" s="2">
-        <v>4.3609999999999998</v>
+        <v>4.361</v>
       </c>
       <c r="J11" s="2">
         <v>1</v>
@@ -1432,7 +2135,7 @@
         <v>71</v>
       </c>
       <c r="I12" s="2">
-        <v>4.3179999999999996</v>
+        <v>4.318</v>
       </c>
       <c r="J12" s="2">
         <v>1</v>
@@ -1488,7 +2191,7 @@
         <v>44</v>
       </c>
       <c r="I14" s="2">
-        <v>7.0039999999999996</v>
+        <v>7.004</v>
       </c>
       <c r="J14" s="2">
         <v>1</v>
@@ -1516,7 +2219,7 @@
         <v>70</v>
       </c>
       <c r="I15" s="2">
-        <v>4.3810000000000002</v>
+        <v>4.381</v>
       </c>
       <c r="J15" s="2">
         <v>1</v>
@@ -1544,7 +2247,7 @@
         <v>72</v>
       </c>
       <c r="I16" s="2">
-        <v>4.2590000000000003</v>
+        <v>4.259</v>
       </c>
       <c r="J16" s="2">
         <v>1</v>
@@ -1574,7 +2277,7 @@
         <v>53</v>
       </c>
       <c r="I17" s="2">
-        <v>5.7930000000000001</v>
+        <v>5.793</v>
       </c>
       <c r="J17" s="2">
         <v>1</v>
@@ -1602,7 +2305,7 @@
         <v>51</v>
       </c>
       <c r="I18" s="2">
-        <v>6.0030000000000001</v>
+        <v>6.003</v>
       </c>
       <c r="J18" s="2">
         <v>1</v>
@@ -1660,7 +2363,7 @@
         <v>56</v>
       </c>
       <c r="I20" s="2">
-        <v>5.5129999999999999</v>
+        <v>5.513</v>
       </c>
       <c r="J20" s="2">
         <v>1</v>
@@ -1688,7 +2391,7 @@
         <v>71</v>
       </c>
       <c r="I21" s="2">
-        <v>4.3040000000000003</v>
+        <v>4.304</v>
       </c>
       <c r="J21" s="2">
         <v>1</v>
@@ -1716,7 +2419,7 @@
         <v>71</v>
       </c>
       <c r="I22" s="2">
-        <v>4.3090000000000002</v>
+        <v>4.309</v>
       </c>
       <c r="J22" s="2">
         <v>1</v>
@@ -1746,7 +2449,7 @@
         <v>50</v>
       </c>
       <c r="I23" s="2">
-        <v>6.2009999999999996</v>
+        <v>6.201</v>
       </c>
       <c r="J23" s="2">
         <v>1</v>
@@ -1774,7 +2477,7 @@
         <v>57</v>
       </c>
       <c r="I24" s="2">
-        <v>5.4189999999999996</v>
+        <v>5.419</v>
       </c>
       <c r="J24" s="2">
         <v>1</v>
@@ -1802,7 +2505,7 @@
         <v>58</v>
       </c>
       <c r="I25" s="2">
-        <v>5.2809999999999997</v>
+        <v>5.281</v>
       </c>
       <c r="J25" s="2">
         <v>1</v>
@@ -1815,6 +2518,7 @@
       <c r="B26" s="2">
         <v>1</v>
       </c>
+      <c r="C26" s="2"/>
       <c r="D26" s="2" t="s">
         <v>10</v>
       </c>
@@ -1829,7 +2533,7 @@
         <v>58</v>
       </c>
       <c r="I26" s="2">
-        <v>5.2779999999999996</v>
+        <v>5.278</v>
       </c>
       <c r="J26" s="2">
         <v>0</v>
@@ -1842,6 +2546,7 @@
       <c r="B27" s="2">
         <v>2</v>
       </c>
+      <c r="C27" s="2"/>
       <c r="D27" s="2" t="s">
         <v>13</v>
       </c>
@@ -1856,7 +2561,7 @@
         <v>56</v>
       </c>
       <c r="I27" s="2">
-        <v>5.4509999999999996</v>
+        <v>5.451</v>
       </c>
       <c r="J27" s="2">
         <v>0</v>
@@ -1869,6 +2574,7 @@
       <c r="B28" s="2">
         <v>3</v>
       </c>
+      <c r="C28" s="2"/>
       <c r="D28" s="2" t="s">
         <v>16</v>
       </c>
@@ -1883,7 +2589,7 @@
         <v>53</v>
       </c>
       <c r="I28" s="2">
-        <v>5.8070000000000004</v>
+        <v>5.807</v>
       </c>
       <c r="J28" s="2">
         <v>0</v>
@@ -1896,6 +2602,7 @@
       <c r="B29" s="2">
         <v>4</v>
       </c>
+      <c r="C29" s="2"/>
       <c r="D29" s="2" t="s">
         <v>19</v>
       </c>
@@ -1910,7 +2617,7 @@
         <v>57</v>
       </c>
       <c r="I29" s="2">
-        <v>5.4119999999999999</v>
+        <v>5.412</v>
       </c>
       <c r="J29" s="2">
         <v>0</v>
@@ -1923,6 +2630,7 @@
       <c r="B30" s="2">
         <v>5</v>
       </c>
+      <c r="C30" s="2"/>
       <c r="D30" s="2" t="s">
         <v>22</v>
       </c>
@@ -1937,7 +2645,7 @@
         <v>50</v>
       </c>
       <c r="I30" s="2">
-        <v>5.1740000000000004</v>
+        <v>5.174</v>
       </c>
       <c r="J30" s="2">
         <v>0</v>
@@ -1950,6 +2658,7 @@
       <c r="B31" s="2">
         <v>6</v>
       </c>
+      <c r="C31" s="2"/>
       <c r="D31" s="2" t="s">
         <v>25</v>
       </c>
@@ -1966,7 +2675,7 @@
         <v>57</v>
       </c>
       <c r="I31" s="2">
-        <v>5.4119999999999999</v>
+        <v>5.412</v>
       </c>
       <c r="J31" s="2">
         <v>0</v>
@@ -1979,6 +2688,7 @@
       <c r="B32" s="2">
         <v>7</v>
       </c>
+      <c r="C32" s="2"/>
       <c r="D32" s="2" t="s">
         <v>39</v>
       </c>
@@ -1993,7 +2703,7 @@
         <v>70</v>
       </c>
       <c r="I32" s="2">
-        <v>4.3609999999999998</v>
+        <v>4.361</v>
       </c>
       <c r="J32" s="2">
         <v>0</v>
@@ -2006,6 +2716,7 @@
       <c r="B33" s="2">
         <v>8</v>
       </c>
+      <c r="C33" s="2"/>
       <c r="D33" s="2" t="s">
         <v>33</v>
       </c>
@@ -2020,7 +2731,7 @@
         <v>78</v>
       </c>
       <c r="I33" s="2">
-        <v>3.3370000000000002</v>
+        <v>3.337</v>
       </c>
       <c r="J33" s="2">
         <v>0</v>
@@ -2033,6 +2744,7 @@
       <c r="B34" s="2">
         <v>9</v>
       </c>
+      <c r="C34" s="2"/>
       <c r="D34" s="2" t="s">
         <v>36</v>
       </c>
@@ -2062,6 +2774,7 @@
       <c r="B35" s="2">
         <v>10</v>
       </c>
+      <c r="C35" s="2"/>
       <c r="D35" s="2" t="s">
         <v>42</v>
       </c>
@@ -2076,7 +2789,7 @@
         <v>71</v>
       </c>
       <c r="I35" s="2">
-        <v>4.3179999999999996</v>
+        <v>4.318</v>
       </c>
       <c r="J35" s="2">
         <v>0</v>
@@ -2089,6 +2802,7 @@
       <c r="B36" s="2">
         <v>11</v>
       </c>
+      <c r="C36" s="2"/>
       <c r="D36" s="2" t="s">
         <v>45</v>
       </c>
@@ -2116,6 +2830,7 @@
       <c r="B37" s="2">
         <v>12</v>
       </c>
+      <c r="C37" s="2"/>
       <c r="D37" s="2" t="s">
         <v>48</v>
       </c>
@@ -2130,7 +2845,7 @@
         <v>44</v>
       </c>
       <c r="I37" s="2">
-        <v>7.0039999999999996</v>
+        <v>7.004</v>
       </c>
       <c r="J37" s="2">
         <v>0</v>
@@ -2143,6 +2858,7 @@
       <c r="B38" s="2">
         <v>13</v>
       </c>
+      <c r="C38" s="2"/>
       <c r="D38" s="2" t="s">
         <v>51</v>
       </c>
@@ -2157,7 +2873,7 @@
         <v>70</v>
       </c>
       <c r="I38" s="2">
-        <v>4.3810000000000002</v>
+        <v>4.381</v>
       </c>
       <c r="J38" s="2">
         <v>0</v>
@@ -2170,6 +2886,7 @@
       <c r="B39" s="2">
         <v>14</v>
       </c>
+      <c r="C39" s="2"/>
       <c r="D39" s="2" t="s">
         <v>54</v>
       </c>
@@ -2184,7 +2901,7 @@
         <v>72</v>
       </c>
       <c r="I39" s="2">
-        <v>4.2590000000000003</v>
+        <v>4.259</v>
       </c>
       <c r="J39" s="2">
         <v>0</v>
@@ -2197,6 +2914,7 @@
       <c r="B40" s="2">
         <v>15</v>
       </c>
+      <c r="C40" s="2"/>
       <c r="D40" s="2" t="s">
         <v>29</v>
       </c>
@@ -2213,7 +2931,7 @@
         <v>53</v>
       </c>
       <c r="I40" s="2">
-        <v>5.7930000000000001</v>
+        <v>5.793</v>
       </c>
       <c r="J40" s="2">
         <v>0</v>
@@ -2226,23 +2944,24 @@
       <c r="B41" s="2">
         <v>16</v>
       </c>
+      <c r="C41" s="2"/>
       <c r="D41" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E41" s="2" t="s">
+      <c r="E41" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="F41" s="2" t="s">
+      <c r="F41" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="G41" s="2" t="s">
+      <c r="G41" s="7" t="s">
         <v>85</v>
       </c>
       <c r="H41" s="2">
         <v>57</v>
       </c>
       <c r="I41" s="2">
-        <v>5.4160000000000004</v>
+        <v>5.416</v>
       </c>
       <c r="J41" s="2">
         <v>0</v>
@@ -2255,6 +2974,7 @@
       <c r="B42" s="2">
         <v>17</v>
       </c>
+      <c r="C42" s="2"/>
       <c r="D42" s="2" t="s">
         <v>60</v>
       </c>
@@ -2269,7 +2989,7 @@
         <v>51</v>
       </c>
       <c r="I42" s="2">
-        <v>6.0030000000000001</v>
+        <v>6.003</v>
       </c>
       <c r="J42" s="2">
         <v>0</v>
@@ -2282,6 +3002,7 @@
       <c r="B43" s="2">
         <v>18</v>
       </c>
+      <c r="C43" s="2"/>
       <c r="D43" s="2" t="s">
         <v>63</v>
       </c>
@@ -2309,6 +3030,7 @@
       <c r="B44" s="2">
         <v>19</v>
       </c>
+      <c r="C44" s="2"/>
       <c r="D44" s="2" t="s">
         <v>25</v>
       </c>
@@ -2325,7 +3047,7 @@
         <v>56</v>
       </c>
       <c r="I44" s="2">
-        <v>5.5129999999999999</v>
+        <v>5.513</v>
       </c>
       <c r="J44" s="2">
         <v>0</v>
@@ -2338,6 +3060,7 @@
       <c r="B45" s="2">
         <v>20</v>
       </c>
+      <c r="C45" s="2"/>
       <c r="D45" s="2" t="s">
         <v>69</v>
       </c>
@@ -2352,7 +3075,7 @@
         <v>71</v>
       </c>
       <c r="I45" s="2">
-        <v>4.3040000000000003</v>
+        <v>4.304</v>
       </c>
       <c r="J45" s="2">
         <v>0</v>
@@ -2365,6 +3088,7 @@
       <c r="B46" s="2">
         <v>21</v>
       </c>
+      <c r="C46" s="2"/>
       <c r="D46" s="2" t="s">
         <v>72</v>
       </c>
@@ -2379,7 +3103,7 @@
         <v>71</v>
       </c>
       <c r="I46" s="2">
-        <v>4.3090000000000002</v>
+        <v>4.309</v>
       </c>
       <c r="J46" s="2">
         <v>0</v>
@@ -2392,6 +3116,7 @@
       <c r="B47" s="2">
         <v>22</v>
       </c>
+      <c r="C47" s="2"/>
       <c r="D47" s="2" t="s">
         <v>25</v>
       </c>
@@ -2408,7 +3133,7 @@
         <v>50</v>
       </c>
       <c r="I47" s="2">
-        <v>6.2009999999999996</v>
+        <v>6.201</v>
       </c>
       <c r="J47" s="2">
         <v>0</v>
@@ -2421,6 +3146,7 @@
       <c r="B48" s="2">
         <v>23</v>
       </c>
+      <c r="C48" s="2"/>
       <c r="D48" s="2" t="s">
         <v>78</v>
       </c>
@@ -2435,7 +3161,7 @@
         <v>57</v>
       </c>
       <c r="I48" s="2">
-        <v>5.4189999999999996</v>
+        <v>5.419</v>
       </c>
       <c r="J48" s="2">
         <v>0</v>
@@ -2448,6 +3174,7 @@
       <c r="B49" s="2">
         <v>24</v>
       </c>
+      <c r="C49" s="2"/>
       <c r="D49" s="2" t="s">
         <v>81</v>
       </c>
@@ -2462,7 +3189,7 @@
         <v>58</v>
       </c>
       <c r="I49" s="2">
-        <v>5.2809999999999997</v>
+        <v>5.281</v>
       </c>
       <c r="J49" s="2">
         <v>0</v>
@@ -2471,20 +3198,22 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G126"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G241"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="5.5703125" customWidth="1"/>
-    <col min="2" max="2" width="6.7109375" customWidth="1"/>
-    <col min="3" max="3" width="19.7109375" customWidth="1"/>
-    <col min="4" max="4" width="11.28515625" customWidth="1"/>
-    <col min="5" max="6" width="9.42578125" customWidth="1"/>
-    <col min="7" max="7" width="7.42578125" customWidth="1"/>
+    <col min="1" max="1" width="5.57142857142857" customWidth="1"/>
+    <col min="2" max="2" width="6.71428571428571" customWidth="1"/>
+    <col min="3" max="3" width="19.7142857142857" customWidth="1"/>
+    <col min="4" max="4" width="11.2857142857143" customWidth="1"/>
+    <col min="5" max="6" width="9.42857142857143" customWidth="1"/>
+    <col min="7" max="7" width="7.42857142857143" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -2524,7 +3253,7 @@
         <v>45730</v>
       </c>
       <c r="E2" s="17">
-        <v>0.39583333333333298</v>
+        <v>0.395833333333333</v>
       </c>
       <c r="F2" s="17">
         <v>0.4375</v>
@@ -2547,10 +3276,10 @@
         <v>45730</v>
       </c>
       <c r="E3" s="17">
-        <v>0.54166666666666696</v>
+        <v>0.541666666666667</v>
       </c>
       <c r="F3" s="17">
-        <v>0.58333333333333304</v>
+        <v>0.583333333333333</v>
       </c>
       <c r="G3" s="2">
         <v>0</v>
@@ -2570,7 +3299,7 @@
         <v>45731</v>
       </c>
       <c r="E4" s="17">
-        <v>0.39583333333333298</v>
+        <v>0.395833333333333</v>
       </c>
       <c r="F4" s="17">
         <v>0.4375</v>
@@ -2593,10 +3322,10 @@
         <v>45731</v>
       </c>
       <c r="E5" s="17">
-        <v>0.54166666666666696</v>
+        <v>0.541666666666667</v>
       </c>
       <c r="F5" s="17">
-        <v>0.58333333333333304</v>
+        <v>0.583333333333333</v>
       </c>
       <c r="G5" s="2">
         <v>1</v>
@@ -2637,10 +3366,10 @@
         <v>45737</v>
       </c>
       <c r="E7" s="19">
-        <v>0.47916666666666702</v>
+        <v>0.479166666666667</v>
       </c>
       <c r="F7" s="19">
-        <v>0.52083333333333304</v>
+        <v>0.520833333333333</v>
       </c>
       <c r="G7" s="7">
         <v>0</v>
@@ -2660,10 +3389,10 @@
         <v>45737</v>
       </c>
       <c r="E8" s="19">
-        <v>0.64583333333333304</v>
+        <v>0.645833333333333</v>
       </c>
       <c r="F8" s="19">
-        <v>0.67638888888888904</v>
+        <v>0.676388888888889</v>
       </c>
       <c r="G8" s="7">
         <v>1</v>
@@ -2683,7 +3412,7 @@
         <v>45738</v>
       </c>
       <c r="E9" s="19">
-        <v>0.45833333333333298</v>
+        <v>0.458333333333333</v>
       </c>
       <c r="F9" s="19">
         <v>0.5</v>
@@ -2709,7 +3438,7 @@
         <v>0.625</v>
       </c>
       <c r="F10" s="19">
-        <v>0.66666666666666696</v>
+        <v>0.666666666666667</v>
       </c>
       <c r="G10" s="7">
         <v>1</v>
@@ -2753,7 +3482,7 @@
         <v>0.4375</v>
       </c>
       <c r="F12" s="17">
-        <v>0.47916666666666702</v>
+        <v>0.479166666666667</v>
       </c>
       <c r="G12" s="2">
         <v>0</v>
@@ -2773,7 +3502,7 @@
         <v>45751</v>
       </c>
       <c r="E13" s="17">
-        <v>0.58333333333333304</v>
+        <v>0.583333333333333</v>
       </c>
       <c r="F13" s="17">
         <v>0.625</v>
@@ -2799,7 +3528,7 @@
         <v>0.4375</v>
       </c>
       <c r="F14" s="17">
-        <v>0.47916666666666702</v>
+        <v>0.479166666666667</v>
       </c>
       <c r="G14" s="2">
         <v>0</v>
@@ -2819,7 +3548,7 @@
         <v>45752</v>
       </c>
       <c r="E15" s="17">
-        <v>0.58333333333333304</v>
+        <v>0.583333333333333</v>
       </c>
       <c r="F15" s="17">
         <v>0.625</v>
@@ -2842,7 +3571,7 @@
         <v>45753</v>
       </c>
       <c r="E16" s="17">
-        <v>0.54166666666666696</v>
+        <v>0.541666666666667</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2">
@@ -2866,7 +3595,7 @@
         <v>0.8125</v>
       </c>
       <c r="F17" s="19">
-        <v>0.85416666666666696</v>
+        <v>0.854166666666667</v>
       </c>
       <c r="G17" s="7">
         <v>0</v>
@@ -2886,7 +3615,7 @@
         <v>45758</v>
       </c>
       <c r="E18" s="19">
-        <v>0.95833333333333304</v>
+        <v>0.958333333333333</v>
       </c>
       <c r="F18" s="19">
         <v>0</v>
@@ -2909,10 +3638,10 @@
         <v>45759</v>
       </c>
       <c r="E19" s="19">
-        <v>0.85416666666666696</v>
+        <v>0.854166666666667</v>
       </c>
       <c r="F19" s="19">
-        <v>0.89583333333333304</v>
+        <v>0.895833333333333</v>
       </c>
       <c r="G19" s="7">
         <v>0</v>
@@ -2935,7 +3664,7 @@
         <v>0</v>
       </c>
       <c r="F20" s="19">
-        <v>4.1666666666666699E-2</v>
+        <v>0.0416666666666667</v>
       </c>
       <c r="G20" s="7">
         <v>1</v>
@@ -2955,7 +3684,7 @@
         <v>45760</v>
       </c>
       <c r="E21" s="19">
-        <v>0.95833333333333304</v>
+        <v>0.958333333333333</v>
       </c>
       <c r="F21" s="7"/>
       <c r="G21" s="7">
@@ -2976,7 +3705,7 @@
         <v>45765</v>
       </c>
       <c r="E22" s="17">
-        <v>0.89583333333333304</v>
+        <v>0.895833333333333</v>
       </c>
       <c r="F22" s="17">
         <v>0.9375</v>
@@ -2999,10 +3728,10 @@
         <v>45766</v>
       </c>
       <c r="E23" s="17">
-        <v>4.1666666666666699E-2</v>
+        <v>0.0416666666666667</v>
       </c>
       <c r="F23" s="17">
-        <v>8.3333333333333301E-2</v>
+        <v>0.0833333333333333</v>
       </c>
       <c r="G23" s="2">
         <v>0</v>
@@ -3022,7 +3751,7 @@
         <v>45766</v>
       </c>
       <c r="E24" s="17">
-        <v>0.89583333333333304</v>
+        <v>0.895833333333333</v>
       </c>
       <c r="F24" s="17">
         <v>0.9375</v>
@@ -3045,10 +3774,10 @@
         <v>45767</v>
       </c>
       <c r="E25" s="17">
-        <v>4.1666666666666699E-2</v>
+        <v>0.0416666666666667</v>
       </c>
       <c r="F25" s="17">
-        <v>8.3333333333333301E-2</v>
+        <v>0.0833333333333333</v>
       </c>
       <c r="G25" s="2">
         <v>1</v>
@@ -3068,7 +3797,7 @@
         <v>45767</v>
       </c>
       <c r="E26" s="17">
-        <v>4.1666666666666699E-2</v>
+        <v>0.0416666666666667</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2">
@@ -3089,10 +3818,10 @@
         <v>45780</v>
       </c>
       <c r="E27" s="19">
-        <v>2.0833333333333301E-2</v>
+        <v>0.0208333333333333</v>
       </c>
       <c r="F27" s="19">
-        <v>6.25E-2</v>
+        <v>0.0625</v>
       </c>
       <c r="G27" s="7">
         <v>0</v>
@@ -3138,7 +3867,7 @@
         <v>0</v>
       </c>
       <c r="F29" s="19">
-        <v>4.1666666666666699E-2</v>
+        <v>0.0416666666666667</v>
       </c>
       <c r="G29" s="7">
         <v>1</v>
@@ -3158,10 +3887,10 @@
         <v>45781</v>
       </c>
       <c r="E30" s="19">
-        <v>0.16666666666666699</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="F30" s="19">
-        <v>0.20833333333333301</v>
+        <v>0.208333333333333</v>
       </c>
       <c r="G30" s="7">
         <v>1</v>
@@ -3181,7 +3910,7 @@
         <v>45782</v>
       </c>
       <c r="E31" s="19">
-        <v>0.16666666666666699</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="F31" s="19"/>
       <c r="G31" s="7">
@@ -3205,7 +3934,7 @@
         <v>0.8125</v>
       </c>
       <c r="F32" s="17">
-        <v>0.85416666666666696</v>
+        <v>0.854166666666667</v>
       </c>
       <c r="G32" s="2">
         <v>0</v>
@@ -3225,7 +3954,7 @@
         <v>45793</v>
       </c>
       <c r="E33" s="17">
-        <v>0.95833333333333304</v>
+        <v>0.958333333333333</v>
       </c>
       <c r="F33" s="17">
         <v>0</v>
@@ -3248,7 +3977,7 @@
         <v>45794</v>
       </c>
       <c r="E34" s="17">
-        <v>0.77083333333333304</v>
+        <v>0.770833333333333</v>
       </c>
       <c r="F34" s="17">
         <v>0.8125</v>
@@ -3271,10 +4000,10 @@
         <v>45794</v>
       </c>
       <c r="E35" s="17">
-        <v>0.91666666666666696</v>
+        <v>0.916666666666667</v>
       </c>
       <c r="F35" s="17">
-        <v>0.95833333333333304</v>
+        <v>0.958333333333333</v>
       </c>
       <c r="G35" s="2">
         <v>1</v>
@@ -3318,7 +4047,7 @@
         <v>0.8125</v>
       </c>
       <c r="F37" s="19">
-        <v>0.85416666666666696</v>
+        <v>0.854166666666667</v>
       </c>
       <c r="G37" s="7">
         <v>0</v>
@@ -3338,7 +4067,7 @@
         <v>45800</v>
       </c>
       <c r="E38" s="19">
-        <v>0.95833333333333304</v>
+        <v>0.958333333333333</v>
       </c>
       <c r="F38" s="19">
         <v>0</v>
@@ -3361,7 +4090,7 @@
         <v>45801</v>
       </c>
       <c r="E39" s="19">
-        <v>0.77083333333333304</v>
+        <v>0.770833333333333</v>
       </c>
       <c r="F39" s="19">
         <v>0.8125</v>
@@ -3384,10 +4113,10 @@
         <v>45801</v>
       </c>
       <c r="E40" s="19">
-        <v>0.91666666666666696</v>
+        <v>0.916666666666667</v>
       </c>
       <c r="F40" s="19">
-        <v>0.95833333333333304</v>
+        <v>0.958333333333333</v>
       </c>
       <c r="G40" s="7">
         <v>1</v>
@@ -3431,7 +4160,7 @@
         <v>0.8125</v>
       </c>
       <c r="F42" s="17">
-        <v>0.85416666666666696</v>
+        <v>0.854166666666667</v>
       </c>
       <c r="G42" s="2">
         <v>0</v>
@@ -3451,7 +4180,7 @@
         <v>45807</v>
       </c>
       <c r="E43" s="17">
-        <v>0.95833333333333304</v>
+        <v>0.958333333333333</v>
       </c>
       <c r="F43" s="17">
         <v>0</v>
@@ -3474,7 +4203,7 @@
         <v>45808</v>
       </c>
       <c r="E44" s="17">
-        <v>0.77083333333333304</v>
+        <v>0.770833333333333</v>
       </c>
       <c r="F44" s="17">
         <v>0.8125</v>
@@ -3497,10 +4226,10 @@
         <v>45808</v>
       </c>
       <c r="E45" s="17">
-        <v>0.91666666666666696</v>
+        <v>0.916666666666667</v>
       </c>
       <c r="F45" s="17">
-        <v>0.95833333333333304</v>
+        <v>0.958333333333333</v>
       </c>
       <c r="G45" s="2">
         <v>1</v>
@@ -3541,7 +4270,7 @@
         <v>45822</v>
       </c>
       <c r="E47" s="19">
-        <v>6.25E-2</v>
+        <v>0.0625</v>
       </c>
       <c r="F47" s="19">
         <v>0.104166666666667</v>
@@ -3564,7 +4293,7 @@
         <v>45822</v>
       </c>
       <c r="E48" s="19">
-        <v>0.20833333333333301</v>
+        <v>0.208333333333333</v>
       </c>
       <c r="F48" s="19">
         <v>0.25</v>
@@ -3587,10 +4316,10 @@
         <v>45823</v>
       </c>
       <c r="E49" s="19">
-        <v>2.0833333333333301E-2</v>
+        <v>0.0208333333333333</v>
       </c>
       <c r="F49" s="19">
-        <v>6.25E-2</v>
+        <v>0.0625</v>
       </c>
       <c r="G49" s="7">
         <v>0</v>
@@ -3610,10 +4339,10 @@
         <v>45823</v>
       </c>
       <c r="E50" s="19">
-        <v>0.16666666666666699</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="F50" s="19">
-        <v>0.20833333333333301</v>
+        <v>0.208333333333333</v>
       </c>
       <c r="G50" s="7">
         <v>1</v>
@@ -3633,7 +4362,7 @@
         <v>45824</v>
       </c>
       <c r="E51" s="19">
-        <v>8.3333333333333301E-2</v>
+        <v>0.0833333333333333</v>
       </c>
       <c r="F51" s="7"/>
       <c r="G51" s="7">
@@ -3657,7 +4386,7 @@
         <v>0.8125</v>
       </c>
       <c r="F52" s="17">
-        <v>0.85416666666666696</v>
+        <v>0.854166666666667</v>
       </c>
       <c r="G52" s="2">
         <v>0</v>
@@ -3677,7 +4406,7 @@
         <v>45835</v>
       </c>
       <c r="E53" s="17">
-        <v>0.95833333333333304</v>
+        <v>0.958333333333333</v>
       </c>
       <c r="F53" s="17">
         <v>0</v>
@@ -3700,7 +4429,7 @@
         <v>45836</v>
       </c>
       <c r="E54" s="17">
-        <v>0.77083333333333304</v>
+        <v>0.770833333333333</v>
       </c>
       <c r="F54" s="17">
         <v>0.8125</v>
@@ -3723,10 +4452,10 @@
         <v>45836</v>
       </c>
       <c r="E55" s="17">
-        <v>0.91666666666666696</v>
+        <v>0.916666666666667</v>
       </c>
       <c r="F55" s="17">
-        <v>0.95833333333333304</v>
+        <v>0.958333333333333</v>
       </c>
       <c r="G55" s="2">
         <v>1</v>
@@ -3770,7 +4499,7 @@
         <v>0.8125</v>
       </c>
       <c r="F57" s="19">
-        <v>0.85416666666666696</v>
+        <v>0.854166666666667</v>
       </c>
       <c r="G57" s="7">
         <v>0</v>
@@ -3790,7 +4519,7 @@
         <v>45842</v>
       </c>
       <c r="E58" s="19">
-        <v>0.95833333333333304</v>
+        <v>0.958333333333333</v>
       </c>
       <c r="F58" s="19">
         <v>0</v>
@@ -3813,7 +4542,7 @@
         <v>45843</v>
       </c>
       <c r="E59" s="19">
-        <v>0.77083333333333304</v>
+        <v>0.770833333333333</v>
       </c>
       <c r="F59" s="19">
         <v>0.8125</v>
@@ -3836,10 +4565,10 @@
         <v>45843</v>
       </c>
       <c r="E60" s="19">
-        <v>0.91666666666666696</v>
+        <v>0.916666666666667</v>
       </c>
       <c r="F60" s="19">
-        <v>0.95833333333333304</v>
+        <v>0.958333333333333</v>
       </c>
       <c r="G60" s="7">
         <v>1</v>
@@ -3859,7 +4588,7 @@
         <v>45844</v>
       </c>
       <c r="E61" s="19">
-        <v>0.91666666666666696</v>
+        <v>0.916666666666667</v>
       </c>
       <c r="F61" s="7"/>
       <c r="G61" s="7">
@@ -3883,7 +4612,7 @@
         <v>0.8125</v>
       </c>
       <c r="F62" s="17">
-        <v>0.85416666666666696</v>
+        <v>0.854166666666667</v>
       </c>
       <c r="G62" s="2">
         <v>0</v>
@@ -3929,7 +4658,7 @@
         <v>0.75</v>
       </c>
       <c r="F64" s="17">
-        <v>0.79166666666666696</v>
+        <v>0.791666666666667</v>
       </c>
       <c r="G64" s="2">
         <v>1</v>
@@ -3949,10 +4678,10 @@
         <v>45864</v>
       </c>
       <c r="E65" s="17">
-        <v>0.91666666666666696</v>
+        <v>0.916666666666667</v>
       </c>
       <c r="F65" s="17">
-        <v>0.95833333333333304</v>
+        <v>0.958333333333333</v>
       </c>
       <c r="G65" s="2">
         <v>1</v>
@@ -3996,7 +4725,7 @@
         <v>0.8125</v>
       </c>
       <c r="F67" s="19">
-        <v>0.85416666666666696</v>
+        <v>0.854166666666667</v>
       </c>
       <c r="G67" s="7">
         <v>0</v>
@@ -4016,7 +4745,7 @@
         <v>45870</v>
       </c>
       <c r="E68" s="19">
-        <v>0.95833333333333304</v>
+        <v>0.958333333333333</v>
       </c>
       <c r="F68" s="19">
         <v>0</v>
@@ -4039,7 +4768,7 @@
         <v>45871</v>
       </c>
       <c r="E69" s="19">
-        <v>0.77083333333333304</v>
+        <v>0.770833333333333</v>
       </c>
       <c r="F69" s="19">
         <v>0.8125</v>
@@ -4062,10 +4791,10 @@
         <v>45871</v>
       </c>
       <c r="E70" s="19">
-        <v>0.91666666666666696</v>
+        <v>0.916666666666667</v>
       </c>
       <c r="F70" s="19">
-        <v>0.95833333333333304</v>
+        <v>0.958333333333333</v>
       </c>
       <c r="G70" s="7">
         <v>1</v>
@@ -4106,7 +4835,7 @@
         <v>45898</v>
       </c>
       <c r="E72" s="17">
-        <v>0.77083333333333304</v>
+        <v>0.770833333333333</v>
       </c>
       <c r="F72" s="17">
         <v>0.8125</v>
@@ -4129,10 +4858,10 @@
         <v>45898</v>
       </c>
       <c r="E73" s="17">
-        <v>0.91666666666666696</v>
+        <v>0.916666666666667</v>
       </c>
       <c r="F73" s="17">
-        <v>0.95833333333333304</v>
+        <v>0.958333333333333</v>
       </c>
       <c r="G73" s="2">
         <v>0</v>
@@ -4152,10 +4881,10 @@
         <v>45899</v>
       </c>
       <c r="E74" s="17">
-        <v>0.72916666666666696</v>
+        <v>0.729166666666667</v>
       </c>
       <c r="F74" s="17">
-        <v>0.77083333333333304</v>
+        <v>0.770833333333333</v>
       </c>
       <c r="G74" s="2">
         <v>0</v>
@@ -4178,7 +4907,7 @@
         <v>0.875</v>
       </c>
       <c r="F75" s="17">
-        <v>0.91666666666666696</v>
+        <v>0.916666666666667</v>
       </c>
       <c r="G75" s="2">
         <v>1</v>
@@ -4222,7 +4951,7 @@
         <v>0.8125</v>
       </c>
       <c r="F77" s="19">
-        <v>0.85416666666666696</v>
+        <v>0.854166666666667</v>
       </c>
       <c r="G77" s="7">
         <v>0</v>
@@ -4242,7 +4971,7 @@
         <v>45905</v>
       </c>
       <c r="E78" s="19">
-        <v>0.95833333333333304</v>
+        <v>0.958333333333333</v>
       </c>
       <c r="F78" s="19">
         <v>0</v>
@@ -4265,7 +4994,7 @@
         <v>45906</v>
       </c>
       <c r="E79" s="19">
-        <v>0.77083333333333304</v>
+        <v>0.770833333333333</v>
       </c>
       <c r="F79" s="19">
         <v>0.8125</v>
@@ -4288,10 +5017,10 @@
         <v>45906</v>
       </c>
       <c r="E80" s="19">
-        <v>0.91666666666666696</v>
+        <v>0.916666666666667</v>
       </c>
       <c r="F80" s="19">
-        <v>0.95833333333333304</v>
+        <v>0.958333333333333</v>
       </c>
       <c r="G80" s="7">
         <v>1</v>
@@ -4335,7 +5064,7 @@
         <v>0.6875</v>
       </c>
       <c r="F82" s="17">
-        <v>0.72916666666666696</v>
+        <v>0.729166666666667</v>
       </c>
       <c r="G82" s="2">
         <v>0</v>
@@ -4355,7 +5084,7 @@
         <v>45919</v>
       </c>
       <c r="E83" s="17">
-        <v>0.83333333333333304</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="F83" s="17">
         <v>0.875</v>
@@ -4381,7 +5110,7 @@
         <v>0.6875</v>
       </c>
       <c r="F84" s="17">
-        <v>0.72916666666666696</v>
+        <v>0.729166666666667</v>
       </c>
       <c r="G84" s="2">
         <v>0</v>
@@ -4401,7 +5130,7 @@
         <v>45920</v>
       </c>
       <c r="E85" s="17">
-        <v>0.83333333333333304</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="F85" s="17">
         <v>0.875</v>
@@ -4424,7 +5153,7 @@
         <v>45921</v>
       </c>
       <c r="E86" s="17">
-        <v>0.79166666666666696</v>
+        <v>0.791666666666667</v>
       </c>
       <c r="F86" s="2"/>
       <c r="G86" s="2">
@@ -4445,10 +5174,10 @@
         <v>45933</v>
       </c>
       <c r="E87" s="19">
-        <v>0.72916666666666696</v>
+        <v>0.729166666666667</v>
       </c>
       <c r="F87" s="19">
-        <v>0.77083333333333304</v>
+        <v>0.770833333333333</v>
       </c>
       <c r="G87" s="7">
         <v>0</v>
@@ -4471,7 +5200,7 @@
         <v>0.875</v>
       </c>
       <c r="F88" s="19">
-        <v>0.91666666666666696</v>
+        <v>0.916666666666667</v>
       </c>
       <c r="G88" s="7">
         <v>0</v>
@@ -4491,10 +5220,10 @@
         <v>45934</v>
       </c>
       <c r="E89" s="19">
-        <v>0.72916666666666696</v>
+        <v>0.729166666666667</v>
       </c>
       <c r="F89" s="19">
-        <v>0.77083333333333304</v>
+        <v>0.770833333333333</v>
       </c>
       <c r="G89" s="7">
         <v>0</v>
@@ -4517,7 +5246,7 @@
         <v>0.875</v>
       </c>
       <c r="F90" s="19">
-        <v>0.91666666666666696</v>
+        <v>0.916666666666667</v>
       </c>
       <c r="G90" s="7">
         <v>1</v>
@@ -4537,7 +5266,7 @@
         <v>45935</v>
       </c>
       <c r="E91" s="19">
-        <v>0.83333333333333304</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="F91" s="7"/>
       <c r="G91" s="7">
@@ -4558,7 +5287,7 @@
         <v>45948</v>
       </c>
       <c r="E92" s="17">
-        <v>6.25E-2</v>
+        <v>0.0625</v>
       </c>
       <c r="F92" s="17">
         <v>0.104166666666667</v>
@@ -4581,10 +5310,10 @@
         <v>45948</v>
       </c>
       <c r="E93" s="17">
-        <v>0.22916666666666699</v>
+        <v>0.229166666666667</v>
       </c>
       <c r="F93" s="17">
-        <v>0.25972222222222202</v>
+        <v>0.259722222222222</v>
       </c>
       <c r="G93" s="2">
         <v>1</v>
@@ -4604,10 +5333,10 @@
         <v>45949</v>
       </c>
       <c r="E94" s="17">
-        <v>4.1666666666666699E-2</v>
+        <v>0.0416666666666667</v>
       </c>
       <c r="F94" s="17">
-        <v>6.25E-2</v>
+        <v>0.0625</v>
       </c>
       <c r="G94" s="2">
         <v>1</v>
@@ -4627,7 +5356,7 @@
         <v>45949</v>
       </c>
       <c r="E95" s="17">
-        <v>0.20833333333333301</v>
+        <v>0.208333333333333</v>
       </c>
       <c r="F95" s="17">
         <v>0.25</v>
@@ -4674,7 +5403,7 @@
         <v>0.104166666666667</v>
       </c>
       <c r="F97" s="19">
-        <v>0.14583333333333301</v>
+        <v>0.145833333333333</v>
       </c>
       <c r="G97" s="7">
         <v>0</v>
@@ -4697,7 +5426,7 @@
         <v>0.25</v>
       </c>
       <c r="F98" s="19">
-        <v>0.29166666666666702</v>
+        <v>0.291666666666667</v>
       </c>
       <c r="G98" s="7">
         <v>0</v>
@@ -4717,7 +5446,7 @@
         <v>45956</v>
       </c>
       <c r="E99" s="19">
-        <v>6.25E-2</v>
+        <v>0.0625</v>
       </c>
       <c r="F99" s="19">
         <v>0.104166666666667</v>
@@ -4740,7 +5469,7 @@
         <v>45956</v>
       </c>
       <c r="E100" s="19">
-        <v>0.20833333333333301</v>
+        <v>0.208333333333333</v>
       </c>
       <c r="F100" s="19">
         <v>0.25</v>
@@ -4763,7 +5492,7 @@
         <v>45957</v>
       </c>
       <c r="E101" s="19">
-        <v>0.16666666666666699</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="F101" s="7"/>
       <c r="G101" s="7">
@@ -4787,7 +5516,7 @@
         <v>0.9375</v>
       </c>
       <c r="F102" s="17">
-        <v>0.97916666666666696</v>
+        <v>0.979166666666667</v>
       </c>
       <c r="G102" s="2">
         <v>0</v>
@@ -4810,7 +5539,7 @@
         <v>0.104166666666667</v>
       </c>
       <c r="F103" s="17">
-        <v>0.13472222222222199</v>
+        <v>0.134722222222222</v>
       </c>
       <c r="G103" s="2">
         <v>1</v>
@@ -4830,10 +5559,10 @@
         <v>45969</v>
       </c>
       <c r="E104" s="17">
-        <v>0.91666666666666696</v>
+        <v>0.916666666666667</v>
       </c>
       <c r="F104" s="17">
-        <v>0.95833333333333304</v>
+        <v>0.958333333333333</v>
       </c>
       <c r="G104" s="2">
         <v>1</v>
@@ -4853,7 +5582,7 @@
         <v>45970</v>
       </c>
       <c r="E105" s="17">
-        <v>8.3333333333333301E-2</v>
+        <v>0.0833333333333333</v>
       </c>
       <c r="F105" s="17">
         <v>0.125</v>
@@ -4876,7 +5605,7 @@
         <v>45971</v>
       </c>
       <c r="E106" s="17">
-        <v>4.1666666666666699E-2</v>
+        <v>0.0416666666666667</v>
       </c>
       <c r="F106" s="2"/>
       <c r="G106" s="2">
@@ -4897,10 +5626,10 @@
         <v>45982</v>
       </c>
       <c r="E107" s="19">
-        <v>0.35416666666666702</v>
+        <v>0.354166666666667</v>
       </c>
       <c r="F107" s="19">
-        <v>0.39583333333333298</v>
+        <v>0.395833333333333</v>
       </c>
       <c r="G107" s="7">
         <v>0</v>
@@ -4923,7 +5652,7 @@
         <v>0.5</v>
       </c>
       <c r="F108" s="19">
-        <v>0.54166666666666696</v>
+        <v>0.541666666666667</v>
       </c>
       <c r="G108" s="7">
         <v>0</v>
@@ -4943,10 +5672,10 @@
         <v>45983</v>
       </c>
       <c r="E109" s="20">
-        <v>0.35416666666666702</v>
+        <v>0.354166666666667</v>
       </c>
       <c r="F109" s="20">
-        <v>0.39583333333333298</v>
+        <v>0.395833333333333</v>
       </c>
       <c r="G109" s="7">
         <v>0</v>
@@ -4969,7 +5698,7 @@
         <v>0.5</v>
       </c>
       <c r="F110" s="20">
-        <v>0.54166666666666696</v>
+        <v>0.541666666666667</v>
       </c>
       <c r="G110" s="7">
         <v>1</v>
@@ -5010,7 +5739,7 @@
         <v>45989</v>
       </c>
       <c r="E112" s="21">
-        <v>0.89583333333333304</v>
+        <v>0.895833333333333</v>
       </c>
       <c r="F112" s="21">
         <v>0.9375</v>
@@ -5033,10 +5762,10 @@
         <v>45990</v>
       </c>
       <c r="E113" s="21">
-        <v>6.25E-2</v>
+        <v>0.0625</v>
       </c>
       <c r="F113" s="21">
-        <v>9.30555555555556E-2</v>
+        <v>0.0930555555555556</v>
       </c>
       <c r="G113" s="2">
         <v>1</v>
@@ -5056,10 +5785,10 @@
         <v>45990</v>
       </c>
       <c r="E114" s="21">
-        <v>0.91666666666666696</v>
+        <v>0.916666666666667</v>
       </c>
       <c r="F114" s="21">
-        <v>0.95833333333333304</v>
+        <v>0.958333333333333</v>
       </c>
       <c r="G114" s="2">
         <v>1</v>
@@ -5079,7 +5808,7 @@
         <v>45991</v>
       </c>
       <c r="E115" s="21">
-        <v>8.3333333333333301E-2</v>
+        <v>0.0833333333333333</v>
       </c>
       <c r="F115" s="21">
         <v>0.125</v>
@@ -5123,10 +5852,10 @@
         <v>45996</v>
       </c>
       <c r="E117" s="20">
-        <v>0.72916666666666696</v>
+        <v>0.729166666666667</v>
       </c>
       <c r="F117" s="20">
-        <v>0.77083333333333304</v>
+        <v>0.770833333333333</v>
       </c>
       <c r="G117" s="7">
         <v>0</v>
@@ -5149,7 +5878,7 @@
         <v>0.875</v>
       </c>
       <c r="F118" s="20">
-        <v>0.91666666666666696</v>
+        <v>0.916666666666667</v>
       </c>
       <c r="G118" s="7">
         <v>0</v>
@@ -5169,7 +5898,7 @@
         <v>45997</v>
       </c>
       <c r="E119" s="20">
-        <v>0.77083333333333304</v>
+        <v>0.770833333333333</v>
       </c>
       <c r="F119" s="20">
         <v>0.8125</v>
@@ -5192,10 +5921,10 @@
         <v>45997</v>
       </c>
       <c r="E120" s="20">
-        <v>0.91666666666666696</v>
+        <v>0.916666666666667</v>
       </c>
       <c r="F120" s="20">
-        <v>0.95833333333333304</v>
+        <v>0.958333333333333</v>
       </c>
       <c r="G120" s="7">
         <v>1</v>
@@ -5233,10 +5962,10 @@
         <v>91</v>
       </c>
       <c r="D122" s="16">
-        <v>46095</v>
+        <v>46087</v>
       </c>
       <c r="E122" s="17">
-        <v>0.39583333333333298</v>
+        <v>0.395833333333333</v>
       </c>
       <c r="F122" s="17">
         <v>0.4375</v>
@@ -5256,13 +5985,13 @@
         <v>92</v>
       </c>
       <c r="D123" s="16">
-        <v>46095</v>
+        <v>46087</v>
       </c>
       <c r="E123" s="17">
-        <v>0.54166666666666696</v>
+        <v>0.541666666666667</v>
       </c>
       <c r="F123" s="17">
-        <v>0.58333333333333304</v>
+        <v>0.583333333333333</v>
       </c>
       <c r="G123" s="2">
         <v>0</v>
@@ -5279,10 +6008,10 @@
         <v>93</v>
       </c>
       <c r="D124" s="16">
-        <v>46096</v>
+        <v>46088</v>
       </c>
       <c r="E124" s="17">
-        <v>0.39583333333333298</v>
+        <v>0.395833333333333</v>
       </c>
       <c r="F124" s="17">
         <v>0.4375</v>
@@ -5302,13 +6031,13 @@
         <v>94</v>
       </c>
       <c r="D125" s="16">
-        <v>46096</v>
+        <v>46088</v>
       </c>
       <c r="E125" s="17">
-        <v>0.54166666666666696</v>
+        <v>0.541666666666667</v>
       </c>
       <c r="F125" s="17">
-        <v>0.58333333333333304</v>
+        <v>0.583333333333333</v>
       </c>
       <c r="G125" s="2">
         <v>1</v>
@@ -5325,7 +6054,7 @@
         <v>95</v>
       </c>
       <c r="D126" s="16">
-        <v>46097</v>
+        <v>46089</v>
       </c>
       <c r="E126" s="17">
         <v>0.5</v>
@@ -5335,25 +6064,2626 @@
         <v>1</v>
       </c>
     </row>
+    <row r="127" spans="1:7">
+      <c r="A127" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B127" s="7">
+        <v>2</v>
+      </c>
+      <c r="C127" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="D127" s="18">
+        <v>45729</v>
+      </c>
+      <c r="E127" s="19">
+        <v>0.479166666666667</v>
+      </c>
+      <c r="F127" s="19">
+        <v>0.520833333333333</v>
+      </c>
+      <c r="G127" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7">
+      <c r="A128" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B128" s="7">
+        <v>2</v>
+      </c>
+      <c r="C128" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="D128" s="18">
+        <v>45729</v>
+      </c>
+      <c r="E128" s="19">
+        <v>0.645833333333333</v>
+      </c>
+      <c r="F128" s="19">
+        <v>0.676388888888889</v>
+      </c>
+      <c r="G128" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7">
+      <c r="A129" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B129" s="7">
+        <v>2</v>
+      </c>
+      <c r="C129" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="D129" s="18">
+        <v>45730</v>
+      </c>
+      <c r="E129" s="19">
+        <v>0.458333333333333</v>
+      </c>
+      <c r="F129" s="19">
+        <v>0.5</v>
+      </c>
+      <c r="G129" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7">
+      <c r="A130" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B130" s="7">
+        <v>2</v>
+      </c>
+      <c r="C130" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D130" s="18">
+        <v>45730</v>
+      </c>
+      <c r="E130" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="F130" s="19">
+        <v>0.666666666666667</v>
+      </c>
+      <c r="G130" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7">
+      <c r="A131" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B131" s="7">
+        <v>2</v>
+      </c>
+      <c r="C131" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="D131" s="18">
+        <v>45731</v>
+      </c>
+      <c r="E131" s="19">
+        <v>0.625</v>
+      </c>
+      <c r="F131" s="7"/>
+      <c r="G131" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7">
+      <c r="A132" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B132" s="2">
+        <v>3</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D132" s="16">
+        <v>45743</v>
+      </c>
+      <c r="E132" s="17">
+        <v>0.4375</v>
+      </c>
+      <c r="F132" s="17">
+        <v>0.479166666666667</v>
+      </c>
+      <c r="G132" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7">
+      <c r="A133" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B133" s="2">
+        <v>3</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D133" s="16">
+        <v>45743</v>
+      </c>
+      <c r="E133" s="17">
+        <v>0.583333333333333</v>
+      </c>
+      <c r="F133" s="17">
+        <v>0.625</v>
+      </c>
+      <c r="G133" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7">
+      <c r="A134" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B134" s="2">
+        <v>3</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D134" s="16">
+        <v>45744</v>
+      </c>
+      <c r="E134" s="17">
+        <v>0.4375</v>
+      </c>
+      <c r="F134" s="17">
+        <v>0.479166666666667</v>
+      </c>
+      <c r="G134" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7">
+      <c r="A135" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B135" s="2">
+        <v>3</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D135" s="16">
+        <v>45744</v>
+      </c>
+      <c r="E135" s="17">
+        <v>0.583333333333333</v>
+      </c>
+      <c r="F135" s="17">
+        <v>0.625</v>
+      </c>
+      <c r="G135" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7">
+      <c r="A136" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B136" s="2">
+        <v>3</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D136" s="16">
+        <v>45745</v>
+      </c>
+      <c r="E136" s="17">
+        <v>0.541666666666667</v>
+      </c>
+      <c r="F136" s="2"/>
+      <c r="G136" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7">
+      <c r="A137" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B137" s="7">
+        <v>4</v>
+      </c>
+      <c r="C137" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="D137" s="18">
+        <v>45757</v>
+      </c>
+      <c r="E137" s="19">
+        <v>0.8125</v>
+      </c>
+      <c r="F137" s="19">
+        <v>0.854166666666667</v>
+      </c>
+      <c r="G137" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7">
+      <c r="A138" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B138" s="7">
+        <v>4</v>
+      </c>
+      <c r="C138" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D138" s="18">
+        <v>45757</v>
+      </c>
+      <c r="E138" s="19">
+        <v>0.958333333333333</v>
+      </c>
+      <c r="F138" s="19">
+        <v>0</v>
+      </c>
+      <c r="G138" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7">
+      <c r="A139" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B139" s="7">
+        <v>4</v>
+      </c>
+      <c r="C139" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="D139" s="18">
+        <v>45758</v>
+      </c>
+      <c r="E139" s="19">
+        <v>0.854166666666667</v>
+      </c>
+      <c r="F139" s="19">
+        <v>0.895833333333333</v>
+      </c>
+      <c r="G139" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7">
+      <c r="A140" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B140" s="7">
+        <v>4</v>
+      </c>
+      <c r="C140" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D140" s="18">
+        <v>45758</v>
+      </c>
+      <c r="E140" s="19">
+        <v>0</v>
+      </c>
+      <c r="F140" s="19">
+        <v>0.0416666666666667</v>
+      </c>
+      <c r="G140" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7">
+      <c r="A141" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B141" s="7">
+        <v>4</v>
+      </c>
+      <c r="C141" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="D141" s="18">
+        <v>45759</v>
+      </c>
+      <c r="E141" s="19">
+        <v>0.958333333333333</v>
+      </c>
+      <c r="F141" s="7"/>
+      <c r="G141" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7">
+      <c r="A142" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B142" s="2">
+        <v>5</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D142" s="16">
+        <v>45764</v>
+      </c>
+      <c r="E142" s="17">
+        <v>0.895833333333333</v>
+      </c>
+      <c r="F142" s="17">
+        <v>0.9375</v>
+      </c>
+      <c r="G142" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7">
+      <c r="A143" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B143" s="2">
+        <v>5</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D143" s="16">
+        <v>45765</v>
+      </c>
+      <c r="E143" s="17">
+        <v>0.0416666666666667</v>
+      </c>
+      <c r="F143" s="17">
+        <v>0.0833333333333333</v>
+      </c>
+      <c r="G143" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7">
+      <c r="A144" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B144" s="2">
+        <v>5</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D144" s="16">
+        <v>45765</v>
+      </c>
+      <c r="E144" s="17">
+        <v>0.895833333333333</v>
+      </c>
+      <c r="F144" s="17">
+        <v>0.9375</v>
+      </c>
+      <c r="G144" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7">
+      <c r="A145" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B145" s="2">
+        <v>5</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D145" s="16">
+        <v>45766</v>
+      </c>
+      <c r="E145" s="17">
+        <v>0.0416666666666667</v>
+      </c>
+      <c r="F145" s="17">
+        <v>0.0833333333333333</v>
+      </c>
+      <c r="G145" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7">
+      <c r="A146" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B146" s="2">
+        <v>5</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D146" s="16">
+        <v>45767</v>
+      </c>
+      <c r="E146" s="17">
+        <v>0.0416666666666667</v>
+      </c>
+      <c r="F146" s="2"/>
+      <c r="G146" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7">
+      <c r="A147" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B147" s="7">
+        <v>6</v>
+      </c>
+      <c r="C147" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="D147" s="18">
+        <v>45779</v>
+      </c>
+      <c r="E147" s="19">
+        <v>0.0208333333333333</v>
+      </c>
+      <c r="F147" s="19">
+        <v>0.0625</v>
+      </c>
+      <c r="G147" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7">
+      <c r="A148" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B148" s="7">
+        <v>6</v>
+      </c>
+      <c r="C148" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="D148" s="18">
+        <v>45779</v>
+      </c>
+      <c r="E148" s="19">
+        <v>0.1875</v>
+      </c>
+      <c r="F148" s="19">
+        <v>0.218055555555556</v>
+      </c>
+      <c r="G148" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7">
+      <c r="A149" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B149" s="7">
+        <v>6</v>
+      </c>
+      <c r="C149" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="D149" s="18">
+        <v>45780</v>
+      </c>
+      <c r="E149" s="19">
+        <v>0</v>
+      </c>
+      <c r="F149" s="19">
+        <v>0.0416666666666667</v>
+      </c>
+      <c r="G149" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7">
+      <c r="A150" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B150" s="7">
+        <v>6</v>
+      </c>
+      <c r="C150" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D150" s="18">
+        <v>45780</v>
+      </c>
+      <c r="E150" s="19">
+        <v>0.166666666666667</v>
+      </c>
+      <c r="F150" s="19">
+        <v>0.208333333333333</v>
+      </c>
+      <c r="G150" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7">
+      <c r="A151" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B151" s="7">
+        <v>6</v>
+      </c>
+      <c r="C151" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="D151" s="18">
+        <v>45781</v>
+      </c>
+      <c r="E151" s="19">
+        <v>0.166666666666667</v>
+      </c>
+      <c r="F151" s="19"/>
+      <c r="G151" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7">
+      <c r="A152" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B152" s="2">
+        <v>7</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D152" s="16">
+        <v>45800</v>
+      </c>
+      <c r="E152" s="17">
+        <v>0.0208333333333333</v>
+      </c>
+      <c r="F152" s="17">
+        <v>0.0625</v>
+      </c>
+      <c r="G152" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7">
+      <c r="A153" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B153" s="2">
+        <v>7</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D153" s="16">
+        <v>45800</v>
+      </c>
+      <c r="E153" s="17">
+        <v>0.1875</v>
+      </c>
+      <c r="F153" s="17">
+        <v>0.218055555555556</v>
+      </c>
+      <c r="G153" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7">
+      <c r="A154" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B154" s="2">
+        <v>7</v>
+      </c>
+      <c r="C154" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D154" s="16">
+        <v>45801</v>
+      </c>
+      <c r="E154" s="17">
+        <v>0</v>
+      </c>
+      <c r="F154" s="17">
+        <v>0.0416666666666667</v>
+      </c>
+      <c r="G154" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7">
+      <c r="A155" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B155" s="2">
+        <v>7</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D155" s="16">
+        <v>45801</v>
+      </c>
+      <c r="E155" s="17">
+        <v>0.166666666666667</v>
+      </c>
+      <c r="F155" s="17">
+        <v>0.208333333333333</v>
+      </c>
+      <c r="G155" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7">
+      <c r="A156" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B156" s="2">
+        <v>7</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D156" s="16">
+        <v>45802</v>
+      </c>
+      <c r="E156" s="17">
+        <v>0.166666666666667</v>
+      </c>
+      <c r="F156" s="2"/>
+      <c r="G156" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7">
+      <c r="A157" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B157" s="7">
+        <v>8</v>
+      </c>
+      <c r="C157" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="D157" s="18">
+        <v>45813</v>
+      </c>
+      <c r="E157" s="19">
+        <v>0.8125</v>
+      </c>
+      <c r="F157" s="19">
+        <v>0.854166666666667</v>
+      </c>
+      <c r="G157" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7">
+      <c r="A158" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B158" s="7">
+        <v>8</v>
+      </c>
+      <c r="C158" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D158" s="18">
+        <v>45813</v>
+      </c>
+      <c r="E158" s="19">
+        <v>0.958333333333333</v>
+      </c>
+      <c r="F158" s="19">
+        <v>0</v>
+      </c>
+      <c r="G158" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7">
+      <c r="A159" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B159" s="7">
+        <v>8</v>
+      </c>
+      <c r="C159" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="D159" s="18">
+        <v>45814</v>
+      </c>
+      <c r="E159" s="19">
+        <v>0.770833333333333</v>
+      </c>
+      <c r="F159" s="19">
+        <v>0.8125</v>
+      </c>
+      <c r="G159" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7">
+      <c r="A160" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B160" s="7">
+        <v>8</v>
+      </c>
+      <c r="C160" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D160" s="18">
+        <v>45814</v>
+      </c>
+      <c r="E160" s="19">
+        <v>0.916666666666667</v>
+      </c>
+      <c r="F160" s="19">
+        <v>0.958333333333333</v>
+      </c>
+      <c r="G160" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7">
+      <c r="A161" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B161" s="7">
+        <v>8</v>
+      </c>
+      <c r="C161" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="D161" s="18">
+        <v>45815</v>
+      </c>
+      <c r="E161" s="19">
+        <v>0.875</v>
+      </c>
+      <c r="F161" s="7"/>
+      <c r="G161" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7">
+      <c r="A162" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B162" s="2">
+        <v>9</v>
+      </c>
+      <c r="C162" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D162" s="16">
+        <v>45820</v>
+      </c>
+      <c r="E162" s="17">
+        <v>0.8125</v>
+      </c>
+      <c r="F162" s="17">
+        <v>0.854166666666667</v>
+      </c>
+      <c r="G162" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7">
+      <c r="A163" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B163" s="2">
+        <v>9</v>
+      </c>
+      <c r="C163" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D163" s="16">
+        <v>45820</v>
+      </c>
+      <c r="E163" s="17">
+        <v>0.958333333333333</v>
+      </c>
+      <c r="F163" s="17">
+        <v>0</v>
+      </c>
+      <c r="G163" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7">
+      <c r="A164" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B164" s="2">
+        <v>9</v>
+      </c>
+      <c r="C164" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D164" s="16">
+        <v>45821</v>
+      </c>
+      <c r="E164" s="17">
+        <v>0.770833333333333</v>
+      </c>
+      <c r="F164" s="17">
+        <v>0.8125</v>
+      </c>
+      <c r="G164" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7">
+      <c r="A165" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B165" s="2">
+        <v>9</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D165" s="16">
+        <v>45821</v>
+      </c>
+      <c r="E165" s="17">
+        <v>0.916666666666667</v>
+      </c>
+      <c r="F165" s="17">
+        <v>0.958333333333333</v>
+      </c>
+      <c r="G165" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7">
+      <c r="A166" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B166" s="2">
+        <v>9</v>
+      </c>
+      <c r="C166" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D166" s="16">
+        <v>45822</v>
+      </c>
+      <c r="E166" s="17">
+        <v>0.875</v>
+      </c>
+      <c r="F166" s="2"/>
+      <c r="G166" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7">
+      <c r="A167" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B167" s="7">
+        <v>10</v>
+      </c>
+      <c r="C167" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="D167" s="18">
+        <v>45834</v>
+      </c>
+      <c r="E167" s="19">
+        <v>0.8125</v>
+      </c>
+      <c r="F167" s="19">
+        <v>0.854166666666667</v>
+      </c>
+      <c r="G167" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7">
+      <c r="A168" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B168" s="7">
+        <v>10</v>
+      </c>
+      <c r="C168" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D168" s="18">
+        <v>45834</v>
+      </c>
+      <c r="E168" s="19">
+        <v>0.958333333333333</v>
+      </c>
+      <c r="F168" s="19">
+        <v>0</v>
+      </c>
+      <c r="G168" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7">
+      <c r="A169" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B169" s="7">
+        <v>10</v>
+      </c>
+      <c r="C169" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="D169" s="18">
+        <v>45835</v>
+      </c>
+      <c r="E169" s="19">
+        <v>0.770833333333333</v>
+      </c>
+      <c r="F169" s="19">
+        <v>0.8125</v>
+      </c>
+      <c r="G169" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7">
+      <c r="A170" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B170" s="7">
+        <v>10</v>
+      </c>
+      <c r="C170" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D170" s="18">
+        <v>45835</v>
+      </c>
+      <c r="E170" s="19">
+        <v>0.916666666666667</v>
+      </c>
+      <c r="F170" s="19">
+        <v>0.958333333333333</v>
+      </c>
+      <c r="G170" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7">
+      <c r="A171" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B171" s="7">
+        <v>10</v>
+      </c>
+      <c r="C171" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="D171" s="18">
+        <v>45836</v>
+      </c>
+      <c r="E171" s="19">
+        <v>0.875</v>
+      </c>
+      <c r="F171" s="7"/>
+      <c r="G171" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7">
+      <c r="A172" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B172" s="2">
+        <v>11</v>
+      </c>
+      <c r="C172" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D172" s="16">
+        <v>45841</v>
+      </c>
+      <c r="E172" s="17">
+        <v>0.8125</v>
+      </c>
+      <c r="F172" s="17">
+        <v>0.854166666666667</v>
+      </c>
+      <c r="G172" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7">
+      <c r="A173" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B173" s="2">
+        <v>11</v>
+      </c>
+      <c r="C173" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D173" s="16">
+        <v>45841</v>
+      </c>
+      <c r="E173" s="17">
+        <v>0.979166666666667</v>
+      </c>
+      <c r="F173" s="17">
+        <v>0.00972222222222222</v>
+      </c>
+      <c r="G173" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7">
+      <c r="A174" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B174" s="2">
+        <v>11</v>
+      </c>
+      <c r="C174" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D174" s="16">
+        <v>45842</v>
+      </c>
+      <c r="E174" s="17">
+        <v>0.791666666666667</v>
+      </c>
+      <c r="F174" s="17">
+        <v>0.833333333333333</v>
+      </c>
+      <c r="G174" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7">
+      <c r="A175" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B175" s="2">
+        <v>11</v>
+      </c>
+      <c r="C175" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D175" s="16">
+        <v>45842</v>
+      </c>
+      <c r="E175" s="17">
+        <v>0.958333333333333</v>
+      </c>
+      <c r="F175" s="17">
+        <v>0</v>
+      </c>
+      <c r="G175" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7">
+      <c r="A176" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B176" s="2">
+        <v>11</v>
+      </c>
+      <c r="C176" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D176" s="16">
+        <v>45843</v>
+      </c>
+      <c r="E176" s="17">
+        <v>0.916666666666667</v>
+      </c>
+      <c r="F176" s="2"/>
+      <c r="G176" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7">
+      <c r="A177" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B177" s="7">
+        <v>12</v>
+      </c>
+      <c r="C177" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="D177" s="18">
+        <v>45855</v>
+      </c>
+      <c r="E177" s="19">
+        <v>0.8125</v>
+      </c>
+      <c r="F177" s="19">
+        <v>0.854166666666667</v>
+      </c>
+      <c r="G177" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7">
+      <c r="A178" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B178" s="7">
+        <v>12</v>
+      </c>
+      <c r="C178" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D178" s="18">
+        <v>45855</v>
+      </c>
+      <c r="E178" s="19">
+        <v>0.958333333333333</v>
+      </c>
+      <c r="F178" s="19">
+        <v>0</v>
+      </c>
+      <c r="G178" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7">
+      <c r="A179" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B179" s="7">
+        <v>12</v>
+      </c>
+      <c r="C179" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="D179" s="18">
+        <v>45856</v>
+      </c>
+      <c r="E179" s="19">
+        <v>0.770833333333333</v>
+      </c>
+      <c r="F179" s="19">
+        <v>0.8125</v>
+      </c>
+      <c r="G179" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7">
+      <c r="A180" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B180" s="7">
+        <v>12</v>
+      </c>
+      <c r="C180" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D180" s="18">
+        <v>45856</v>
+      </c>
+      <c r="E180" s="19">
+        <v>0.916666666666667</v>
+      </c>
+      <c r="F180" s="19">
+        <v>0.958333333333333</v>
+      </c>
+      <c r="G180" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7">
+      <c r="A181" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B181" s="7">
+        <v>12</v>
+      </c>
+      <c r="C181" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="D181" s="18">
+        <v>45857</v>
+      </c>
+      <c r="E181" s="19">
+        <v>0.875</v>
+      </c>
+      <c r="F181" s="7"/>
+      <c r="G181" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7">
+      <c r="A182" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B182" s="2">
+        <v>13</v>
+      </c>
+      <c r="C182" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D182" s="16">
+        <v>45862</v>
+      </c>
+      <c r="E182" s="17">
+        <v>0.8125</v>
+      </c>
+      <c r="F182" s="17">
+        <v>0.854166666666667</v>
+      </c>
+      <c r="G182" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7">
+      <c r="A183" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B183" s="2">
+        <v>13</v>
+      </c>
+      <c r="C183" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D183" s="16">
+        <v>45862</v>
+      </c>
+      <c r="E183" s="17">
+        <v>0.9375</v>
+      </c>
+      <c r="F183" s="17">
+        <v>0.968055555555556</v>
+      </c>
+      <c r="G183" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7">
+      <c r="A184" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B184" s="2">
+        <v>13</v>
+      </c>
+      <c r="C184" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D184" s="16">
+        <v>45863</v>
+      </c>
+      <c r="E184" s="17">
+        <v>0.75</v>
+      </c>
+      <c r="F184" s="17">
+        <v>0.791666666666667</v>
+      </c>
+      <c r="G184" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7">
+      <c r="A185" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B185" s="2">
+        <v>13</v>
+      </c>
+      <c r="C185" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D185" s="16">
+        <v>45863</v>
+      </c>
+      <c r="E185" s="17">
+        <v>0.916666666666667</v>
+      </c>
+      <c r="F185" s="17">
+        <v>0.958333333333333</v>
+      </c>
+      <c r="G185" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7">
+      <c r="A186" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B186" s="2">
+        <v>13</v>
+      </c>
+      <c r="C186" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D186" s="16">
+        <v>45864</v>
+      </c>
+      <c r="E186" s="17">
+        <v>0.875</v>
+      </c>
+      <c r="F186" s="2"/>
+      <c r="G186" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7">
+      <c r="A187" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B187" s="7">
+        <v>14</v>
+      </c>
+      <c r="C187" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="D187" s="18">
+        <v>45890</v>
+      </c>
+      <c r="E187" s="19">
+        <v>0.8125</v>
+      </c>
+      <c r="F187" s="19">
+        <v>0.854166666666667</v>
+      </c>
+      <c r="G187" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7">
+      <c r="A188" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B188" s="7">
+        <v>14</v>
+      </c>
+      <c r="C188" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="D188" s="18">
+        <v>45890</v>
+      </c>
+      <c r="E188" s="19">
+        <v>0.958333333333333</v>
+      </c>
+      <c r="F188" s="19">
+        <v>0</v>
+      </c>
+      <c r="G188" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7">
+      <c r="A189" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B189" s="7">
+        <v>14</v>
+      </c>
+      <c r="C189" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="D189" s="18">
+        <v>45891</v>
+      </c>
+      <c r="E189" s="19">
+        <v>0.770833333333333</v>
+      </c>
+      <c r="F189" s="19">
+        <v>0.8125</v>
+      </c>
+      <c r="G189" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7">
+      <c r="A190" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B190" s="7">
+        <v>14</v>
+      </c>
+      <c r="C190" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D190" s="18">
+        <v>45891</v>
+      </c>
+      <c r="E190" s="19">
+        <v>0.916666666666667</v>
+      </c>
+      <c r="F190" s="19">
+        <v>0.958333333333333</v>
+      </c>
+      <c r="G190" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7">
+      <c r="A191" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B191" s="7">
+        <v>14</v>
+      </c>
+      <c r="C191" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="D191" s="18">
+        <v>45892</v>
+      </c>
+      <c r="E191" s="19">
+        <v>0.875</v>
+      </c>
+      <c r="F191" s="7"/>
+      <c r="G191" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7">
+      <c r="A192" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B192" s="2">
+        <v>15</v>
+      </c>
+      <c r="C192" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D192" s="16">
+        <v>45904</v>
+      </c>
+      <c r="E192" s="17">
+        <v>0.770833333333333</v>
+      </c>
+      <c r="F192" s="17">
+        <v>0.8125</v>
+      </c>
+      <c r="G192" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7">
+      <c r="A193" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B193" s="2">
+        <v>15</v>
+      </c>
+      <c r="C193" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D193" s="16">
+        <v>45904</v>
+      </c>
+      <c r="E193" s="17">
+        <v>0.916666666666667</v>
+      </c>
+      <c r="F193" s="17">
+        <v>0.958333333333333</v>
+      </c>
+      <c r="G193" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7">
+      <c r="A194" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B194" s="2">
+        <v>15</v>
+      </c>
+      <c r="C194" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D194" s="16">
+        <v>45905</v>
+      </c>
+      <c r="E194" s="17">
+        <v>0.770833333333333</v>
+      </c>
+      <c r="F194" s="17">
+        <v>0.8125</v>
+      </c>
+      <c r="G194" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7">
+      <c r="A195" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B195" s="2">
+        <v>15</v>
+      </c>
+      <c r="C195" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D195" s="16">
+        <v>45905</v>
+      </c>
+      <c r="E195" s="17">
+        <v>0.916666666666667</v>
+      </c>
+      <c r="F195" s="17">
+        <v>0.958333333333333</v>
+      </c>
+      <c r="G195" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7">
+      <c r="A196" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B196" s="2">
+        <v>15</v>
+      </c>
+      <c r="C196" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D196" s="16">
+        <v>45906</v>
+      </c>
+      <c r="E196" s="17">
+        <v>0.875</v>
+      </c>
+      <c r="F196" s="17"/>
+      <c r="G196" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7">
+      <c r="A197" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B197" s="7">
+        <v>16</v>
+      </c>
+      <c r="C197" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="D197" s="18">
+        <v>45911</v>
+      </c>
+      <c r="E197" s="19">
+        <v>0.8125</v>
+      </c>
+      <c r="F197" s="19">
+        <v>0.854166666666667</v>
+      </c>
+      <c r="G197" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7">
+      <c r="A198" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B198" s="7">
+        <v>16</v>
+      </c>
+      <c r="C198" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D198" s="18">
+        <v>45911</v>
+      </c>
+      <c r="E198" s="19">
+        <v>0.958333333333333</v>
+      </c>
+      <c r="F198" s="19">
+        <v>0</v>
+      </c>
+      <c r="G198" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7">
+      <c r="A199" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B199" s="7">
+        <v>16</v>
+      </c>
+      <c r="C199" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="D199" s="18">
+        <v>45912</v>
+      </c>
+      <c r="E199" s="19">
+        <v>0.770833333333333</v>
+      </c>
+      <c r="F199" s="19">
+        <v>0.8125</v>
+      </c>
+      <c r="G199" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7">
+      <c r="A200" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B200" s="7">
+        <v>16</v>
+      </c>
+      <c r="C200" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D200" s="18">
+        <v>45912</v>
+      </c>
+      <c r="E200" s="19">
+        <v>0.916666666666667</v>
+      </c>
+      <c r="F200" s="19">
+        <v>0.958333333333333</v>
+      </c>
+      <c r="G200" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7">
+      <c r="A201" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B201" s="7">
+        <v>16</v>
+      </c>
+      <c r="C201" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="D201" s="18">
+        <v>45913</v>
+      </c>
+      <c r="E201" s="19">
+        <v>0.875</v>
+      </c>
+      <c r="F201" s="7"/>
+      <c r="G201" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7">
+      <c r="A202" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B202" s="2">
+        <v>17</v>
+      </c>
+      <c r="C202" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D202" s="16">
+        <v>45924</v>
+      </c>
+      <c r="E202" s="17">
+        <v>0.6875</v>
+      </c>
+      <c r="F202" s="17">
+        <v>0.729166666666667</v>
+      </c>
+      <c r="G202" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7">
+      <c r="A203" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B203" s="2">
+        <v>17</v>
+      </c>
+      <c r="C203" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D203" s="16">
+        <v>45924</v>
+      </c>
+      <c r="E203" s="17">
+        <v>0.833333333333333</v>
+      </c>
+      <c r="F203" s="17">
+        <v>0.875</v>
+      </c>
+      <c r="G203" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7">
+      <c r="A204" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B204" s="2">
+        <v>17</v>
+      </c>
+      <c r="C204" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D204" s="16">
+        <v>45925</v>
+      </c>
+      <c r="E204" s="17">
+        <v>0.6875</v>
+      </c>
+      <c r="F204" s="17">
+        <v>0.729166666666667</v>
+      </c>
+      <c r="G204" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7">
+      <c r="A205" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B205" s="2">
+        <v>17</v>
+      </c>
+      <c r="C205" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D205" s="16">
+        <v>45925</v>
+      </c>
+      <c r="E205" s="17">
+        <v>0.833333333333333</v>
+      </c>
+      <c r="F205" s="17">
+        <v>0.875</v>
+      </c>
+      <c r="G205" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7">
+      <c r="A206" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B206" s="2">
+        <v>17</v>
+      </c>
+      <c r="C206" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D206" s="16">
+        <v>45926</v>
+      </c>
+      <c r="E206" s="17">
+        <v>0.791666666666667</v>
+      </c>
+      <c r="F206" s="2"/>
+      <c r="G206" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7">
+      <c r="A207" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B207" s="7">
+        <v>18</v>
+      </c>
+      <c r="C207" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="D207" s="18">
+        <v>45939</v>
+      </c>
+      <c r="E207" s="19">
+        <v>0.6875</v>
+      </c>
+      <c r="F207" s="19">
+        <v>0.729166666666667</v>
+      </c>
+      <c r="G207" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7">
+      <c r="A208" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B208" s="7">
+        <v>18</v>
+      </c>
+      <c r="C208" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="D208" s="18">
+        <v>45939</v>
+      </c>
+      <c r="E208" s="19">
+        <v>0.895833333333333</v>
+      </c>
+      <c r="F208" s="19">
+        <v>0.926388888888889</v>
+      </c>
+      <c r="G208" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7">
+      <c r="A209" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B209" s="7">
+        <v>18</v>
+      </c>
+      <c r="C209" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="D209" s="18">
+        <v>45940</v>
+      </c>
+      <c r="E209" s="19">
+        <v>0.708333333333333</v>
+      </c>
+      <c r="F209" s="19">
+        <v>0.75</v>
+      </c>
+      <c r="G209" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7">
+      <c r="A210" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B210" s="7">
+        <v>18</v>
+      </c>
+      <c r="C210" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D210" s="18">
+        <v>45940</v>
+      </c>
+      <c r="E210" s="19">
+        <v>0.875</v>
+      </c>
+      <c r="F210" s="19">
+        <v>0.916666666666667</v>
+      </c>
+      <c r="G210" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7">
+      <c r="A211" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B211" s="7">
+        <v>18</v>
+      </c>
+      <c r="C211" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="D211" s="18">
+        <v>45941</v>
+      </c>
+      <c r="E211" s="19">
+        <v>0.833333333333333</v>
+      </c>
+      <c r="F211" s="7"/>
+      <c r="G211" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7">
+      <c r="A212" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B212" s="2">
+        <v>19</v>
+      </c>
+      <c r="C212" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D212" s="16">
+        <v>45954</v>
+      </c>
+      <c r="E212" s="17">
+        <v>0.0625</v>
+      </c>
+      <c r="F212" s="17">
+        <v>0.104166666666667</v>
+      </c>
+      <c r="G212" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7">
+      <c r="A213" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B213" s="2">
+        <v>19</v>
+      </c>
+      <c r="C213" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D213" s="16">
+        <v>45954</v>
+      </c>
+      <c r="E213" s="17">
+        <v>0.208333333333333</v>
+      </c>
+      <c r="F213" s="17">
+        <v>0.25</v>
+      </c>
+      <c r="G213" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7">
+      <c r="A214" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B214" s="2">
+        <v>19</v>
+      </c>
+      <c r="C214" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D214" s="16">
+        <v>45955</v>
+      </c>
+      <c r="E214" s="17">
+        <v>0.0625</v>
+      </c>
+      <c r="F214" s="17">
+        <v>0.104166666666667</v>
+      </c>
+      <c r="G214" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7">
+      <c r="A215" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B215" s="2">
+        <v>19</v>
+      </c>
+      <c r="C215" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D215" s="16">
+        <v>45955</v>
+      </c>
+      <c r="E215" s="17">
+        <v>0.208333333333333</v>
+      </c>
+      <c r="F215" s="17">
+        <v>0.25</v>
+      </c>
+      <c r="G215" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7">
+      <c r="A216" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B216" s="2">
+        <v>19</v>
+      </c>
+      <c r="C216" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D216" s="16">
+        <v>45956</v>
+      </c>
+      <c r="E216" s="17">
+        <v>0.125</v>
+      </c>
+      <c r="F216" s="2"/>
+      <c r="G216" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7">
+      <c r="A217" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B217" s="7">
+        <v>20</v>
+      </c>
+      <c r="C217" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="D217" s="18">
+        <v>45961</v>
+      </c>
+      <c r="E217" s="19">
+        <v>0.104166666666667</v>
+      </c>
+      <c r="F217" s="19">
+        <v>0.145833333333333</v>
+      </c>
+      <c r="G217" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7">
+      <c r="A218" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B218" s="7">
+        <v>20</v>
+      </c>
+      <c r="C218" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D218" s="18">
+        <v>45961</v>
+      </c>
+      <c r="E218" s="19">
+        <v>0.25</v>
+      </c>
+      <c r="F218" s="19">
+        <v>0.291666666666667</v>
+      </c>
+      <c r="G218" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7">
+      <c r="A219" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B219" s="7">
+        <v>20</v>
+      </c>
+      <c r="C219" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="D219" s="18">
+        <v>45962</v>
+      </c>
+      <c r="E219" s="19">
+        <v>0.0625</v>
+      </c>
+      <c r="F219" s="19">
+        <v>0.104166666666667</v>
+      </c>
+      <c r="G219" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7">
+      <c r="A220" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B220" s="7">
+        <v>20</v>
+      </c>
+      <c r="C220" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D220" s="18">
+        <v>45962</v>
+      </c>
+      <c r="E220" s="19">
+        <v>0.208333333333333</v>
+      </c>
+      <c r="F220" s="19">
+        <v>0.25</v>
+      </c>
+      <c r="G220" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7">
+      <c r="A221" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B221" s="7">
+        <v>20</v>
+      </c>
+      <c r="C221" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="D221" s="18">
+        <v>45963</v>
+      </c>
+      <c r="E221" s="19">
+        <v>0.166666666666667</v>
+      </c>
+      <c r="F221" s="7"/>
+      <c r="G221" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7">
+      <c r="A222" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B222" s="2">
+        <v>21</v>
+      </c>
+      <c r="C222" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D222" s="16">
+        <v>45967</v>
+      </c>
+      <c r="E222" s="17">
+        <v>0.979166666666667</v>
+      </c>
+      <c r="F222" s="17">
+        <v>0.0208333333333333</v>
+      </c>
+      <c r="G222" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7">
+      <c r="A223" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B223" s="2">
+        <v>21</v>
+      </c>
+      <c r="C223" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D223" s="16">
+        <v>45968</v>
+      </c>
+      <c r="E223" s="17">
+        <v>0.125</v>
+      </c>
+      <c r="F223" s="17">
+        <v>0.166666666666667</v>
+      </c>
+      <c r="G223" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7">
+      <c r="A224" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B224" s="2">
+        <v>21</v>
+      </c>
+      <c r="C224" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D224" s="16">
+        <v>45968</v>
+      </c>
+      <c r="E224" s="17">
+        <v>0.9375</v>
+      </c>
+      <c r="F224" s="17">
+        <v>0.979166666666667</v>
+      </c>
+      <c r="G224" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7">
+      <c r="A225" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B225" s="2">
+        <v>21</v>
+      </c>
+      <c r="C225" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D225" s="16">
+        <v>45969</v>
+      </c>
+      <c r="E225" s="17">
+        <v>0.0833333333333333</v>
+      </c>
+      <c r="F225" s="17">
+        <v>0.125</v>
+      </c>
+      <c r="G225" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7">
+      <c r="A226" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B226" s="2">
+        <v>21</v>
+      </c>
+      <c r="C226" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D226" s="16">
+        <v>45970</v>
+      </c>
+      <c r="E226" s="17">
+        <v>0.0416666666666667</v>
+      </c>
+      <c r="F226" s="2"/>
+      <c r="G226" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7">
+      <c r="A227" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B227" s="7">
+        <v>22</v>
+      </c>
+      <c r="C227" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="D227" s="18">
+        <v>45981</v>
+      </c>
+      <c r="E227" s="19">
+        <v>0.354166666666667</v>
+      </c>
+      <c r="F227" s="19">
+        <v>0.395833333333333</v>
+      </c>
+      <c r="G227" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7">
+      <c r="A228" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B228" s="7">
+        <v>22</v>
+      </c>
+      <c r="C228" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D228" s="18">
+        <v>45981</v>
+      </c>
+      <c r="E228" s="19">
+        <v>0.5</v>
+      </c>
+      <c r="F228" s="19">
+        <v>0.541666666666667</v>
+      </c>
+      <c r="G228" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7">
+      <c r="A229" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B229" s="7">
+        <v>22</v>
+      </c>
+      <c r="C229" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="D229" s="18">
+        <v>45982</v>
+      </c>
+      <c r="E229" s="20">
+        <v>0.354166666666667</v>
+      </c>
+      <c r="F229" s="20">
+        <v>0.395833333333333</v>
+      </c>
+      <c r="G229" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7">
+      <c r="A230" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B230" s="7">
+        <v>22</v>
+      </c>
+      <c r="C230" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D230" s="18">
+        <v>45982</v>
+      </c>
+      <c r="E230" s="20">
+        <v>0.5</v>
+      </c>
+      <c r="F230" s="20">
+        <v>0.541666666666667</v>
+      </c>
+      <c r="G230" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7">
+      <c r="A231" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B231" s="7">
+        <v>22</v>
+      </c>
+      <c r="C231" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="D231" s="18">
+        <v>45983</v>
+      </c>
+      <c r="E231" s="20">
+        <v>0.5</v>
+      </c>
+      <c r="F231" s="7"/>
+      <c r="G231" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7">
+      <c r="A232" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B232" s="2">
+        <v>23</v>
+      </c>
+      <c r="C232" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D232" s="16">
+        <v>45988</v>
+      </c>
+      <c r="E232" s="21">
+        <v>0.895833333333333</v>
+      </c>
+      <c r="F232" s="21">
+        <v>0.9375</v>
+      </c>
+      <c r="G232" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7">
+      <c r="A233" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B233" s="2">
+        <v>23</v>
+      </c>
+      <c r="C233" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D233" s="16">
+        <v>45989</v>
+      </c>
+      <c r="E233" s="21">
+        <v>0.0416666666666667</v>
+      </c>
+      <c r="F233" s="21">
+        <v>0.0833333333333333</v>
+      </c>
+      <c r="G233" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7">
+      <c r="A234" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B234" s="2">
+        <v>23</v>
+      </c>
+      <c r="C234" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D234" s="16">
+        <v>45989</v>
+      </c>
+      <c r="E234" s="17">
+        <v>0.9375</v>
+      </c>
+      <c r="F234" s="17">
+        <v>0.979166666666667</v>
+      </c>
+      <c r="G234" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7">
+      <c r="A235" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B235" s="2">
+        <v>23</v>
+      </c>
+      <c r="C235" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D235" s="16">
+        <v>45990</v>
+      </c>
+      <c r="E235" s="17">
+        <v>0.0833333333333333</v>
+      </c>
+      <c r="F235" s="17">
+        <v>0.125</v>
+      </c>
+      <c r="G235" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7">
+      <c r="A236" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B236" s="2">
+        <v>23</v>
+      </c>
+      <c r="C236" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D236" s="16">
+        <v>45991</v>
+      </c>
+      <c r="E236" s="17">
+        <v>0.0416666666666667</v>
+      </c>
+      <c r="F236" s="2"/>
+      <c r="G236" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7">
+      <c r="A237" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B237" s="7">
+        <v>24</v>
+      </c>
+      <c r="C237" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="D237" s="18">
+        <v>45995</v>
+      </c>
+      <c r="E237" s="20">
+        <v>0.729166666666667</v>
+      </c>
+      <c r="F237" s="20">
+        <v>0.770833333333333</v>
+      </c>
+      <c r="G237" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7">
+      <c r="A238" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B238" s="7">
+        <v>24</v>
+      </c>
+      <c r="C238" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D238" s="18">
+        <v>45995</v>
+      </c>
+      <c r="E238" s="20">
+        <v>0.875</v>
+      </c>
+      <c r="F238" s="20">
+        <v>0.916666666666667</v>
+      </c>
+      <c r="G238" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7">
+      <c r="A239" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B239" s="7">
+        <v>24</v>
+      </c>
+      <c r="C239" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="D239" s="18">
+        <v>45996</v>
+      </c>
+      <c r="E239" s="20">
+        <v>0.770833333333333</v>
+      </c>
+      <c r="F239" s="20">
+        <v>0.8125</v>
+      </c>
+      <c r="G239" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7">
+      <c r="A240" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B240" s="7">
+        <v>24</v>
+      </c>
+      <c r="C240" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D240" s="18">
+        <v>45996</v>
+      </c>
+      <c r="E240" s="20">
+        <v>0.916666666666667</v>
+      </c>
+      <c r="F240" s="20">
+        <v>0.958333333333333</v>
+      </c>
+      <c r="G240" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7">
+      <c r="A241" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B241" s="7">
+        <v>24</v>
+      </c>
+      <c r="C241" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="D241" s="18">
+        <v>45997</v>
+      </c>
+      <c r="E241" s="20">
+        <v>0.875</v>
+      </c>
+      <c r="F241" s="7"/>
+      <c r="G241" s="7">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:R1201"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
-    <col min="2" max="2" width="6.28515625" customWidth="1"/>
-    <col min="3" max="3" width="15.5703125" customWidth="1"/>
-    <col min="4" max="4" width="8.28515625" customWidth="1"/>
-    <col min="5" max="5" width="8.85546875" customWidth="1"/>
-    <col min="6" max="6" width="16.42578125" customWidth="1"/>
-    <col min="7" max="7" width="31.140625" customWidth="1"/>
-    <col min="8" max="10" width="12.7109375"/>
-    <col min="11" max="11" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="6.28571428571429" customWidth="1"/>
+    <col min="3" max="3" width="15.5714285714286" customWidth="1"/>
+    <col min="4" max="4" width="8.28571428571429" customWidth="1"/>
+    <col min="5" max="5" width="8.85714285714286" customWidth="1"/>
+    <col min="6" max="6" width="16.4285714285714" customWidth="1"/>
+    <col min="7" max="7" width="31.1428571428571" customWidth="1"/>
+    <col min="8" max="10" width="12.7142857142857"/>
+    <col min="11" max="11" width="18.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17">
@@ -16727,7 +20057,7 @@
       <c r="N421" s="6"/>
       <c r="O421" s="5"/>
     </row>
-    <row r="422" spans="1:15">
+    <row r="422" ht="17" spans="1:15">
       <c r="A422" s="7">
         <v>2025</v>
       </c>
@@ -16760,7 +20090,7 @@
       <c r="N422" s="5"/>
       <c r="O422" s="5"/>
     </row>
-    <row r="423" spans="1:15">
+    <row r="423" ht="17" spans="1:15">
       <c r="A423" s="7">
         <v>2025</v>
       </c>
@@ -16793,7 +20123,7 @@
       <c r="N423" s="5"/>
       <c r="O423" s="5"/>
     </row>
-    <row r="424" spans="1:15">
+    <row r="424" ht="17" spans="1:15">
       <c r="A424" s="7">
         <v>2025</v>
       </c>
@@ -16826,7 +20156,7 @@
       <c r="N424" s="5"/>
       <c r="O424" s="5"/>
     </row>
-    <row r="425" spans="1:15">
+    <row r="425" ht="17" spans="1:15">
       <c r="A425" s="7">
         <v>2025</v>
       </c>
@@ -16859,7 +20189,7 @@
       <c r="N425" s="5"/>
       <c r="O425" s="5"/>
     </row>
-    <row r="426" spans="1:15">
+    <row r="426" ht="17" spans="1:15">
       <c r="A426" s="7">
         <v>2025</v>
       </c>
@@ -16892,7 +20222,7 @@
       <c r="N426" s="5"/>
       <c r="O426" s="5"/>
     </row>
-    <row r="427" spans="1:15">
+    <row r="427" ht="17" spans="1:15">
       <c r="A427" s="7">
         <v>2025</v>
       </c>
@@ -16925,7 +20255,7 @@
       <c r="N427" s="5"/>
       <c r="O427" s="5"/>
     </row>
-    <row r="428" spans="1:15">
+    <row r="428" ht="17" spans="1:15">
       <c r="A428" s="7">
         <v>2025</v>
       </c>
@@ -16958,7 +20288,7 @@
       <c r="N428" s="5"/>
       <c r="O428" s="5"/>
     </row>
-    <row r="429" spans="1:15">
+    <row r="429" ht="17" spans="1:15">
       <c r="A429" s="7">
         <v>2025</v>
       </c>
@@ -16991,7 +20321,7 @@
       <c r="N429" s="5"/>
       <c r="O429" s="5"/>
     </row>
-    <row r="430" spans="1:15">
+    <row r="430" ht="17" spans="1:15">
       <c r="A430" s="7">
         <v>2025</v>
       </c>
@@ -17024,7 +20354,7 @@
       <c r="N430" s="5"/>
       <c r="O430" s="5"/>
     </row>
-    <row r="431" spans="1:15">
+    <row r="431" ht="17" spans="1:15">
       <c r="A431" s="7">
         <v>2025</v>
       </c>
@@ -17057,7 +20387,7 @@
       <c r="N431" s="5"/>
       <c r="O431" s="5"/>
     </row>
-    <row r="432" spans="1:15">
+    <row r="432" ht="17" spans="1:15">
       <c r="A432" s="7">
         <v>2025</v>
       </c>
@@ -17090,7 +20420,7 @@
       <c r="N432" s="5"/>
       <c r="O432" s="5"/>
     </row>
-    <row r="433" spans="1:15">
+    <row r="433" ht="17" spans="1:15">
       <c r="A433" s="7">
         <v>2025</v>
       </c>
@@ -17123,7 +20453,7 @@
       <c r="N433" s="5"/>
       <c r="O433" s="5"/>
     </row>
-    <row r="434" spans="1:15">
+    <row r="434" ht="17" spans="1:15">
       <c r="A434" s="7">
         <v>2025</v>
       </c>
@@ -17156,7 +20486,7 @@
       <c r="N434" s="5"/>
       <c r="O434" s="5"/>
     </row>
-    <row r="435" spans="1:15">
+    <row r="435" ht="17" spans="1:15">
       <c r="A435" s="7">
         <v>2025</v>
       </c>
@@ -17189,7 +20519,7 @@
       <c r="N435" s="5"/>
       <c r="O435" s="5"/>
     </row>
-    <row r="436" spans="1:15">
+    <row r="436" ht="17" spans="1:15">
       <c r="A436" s="7">
         <v>2025</v>
       </c>
@@ -17222,7 +20552,7 @@
       <c r="N436" s="5"/>
       <c r="O436" s="5"/>
     </row>
-    <row r="437" spans="1:15">
+    <row r="437" ht="17" spans="1:15">
       <c r="A437" s="7">
         <v>2025</v>
       </c>
@@ -17255,7 +20585,7 @@
       <c r="N437" s="5"/>
       <c r="O437" s="5"/>
     </row>
-    <row r="438" spans="1:15">
+    <row r="438" ht="17" spans="1:15">
       <c r="A438" s="7">
         <v>2025</v>
       </c>
@@ -17288,7 +20618,7 @@
       <c r="N438" s="5"/>
       <c r="O438" s="5"/>
     </row>
-    <row r="439" spans="1:15">
+    <row r="439" ht="17" spans="1:15">
       <c r="A439" s="7">
         <v>2025</v>
       </c>
@@ -17321,7 +20651,7 @@
       <c r="N439" s="5"/>
       <c r="O439" s="5"/>
     </row>
-    <row r="440" spans="1:15">
+    <row r="440" ht="17" spans="1:15">
       <c r="A440" s="7">
         <v>2025</v>
       </c>
@@ -17347,7 +20677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="441" spans="1:15">
+    <row r="441" ht="17" spans="1:15">
       <c r="A441" s="7">
         <v>2025</v>
       </c>
@@ -17371,7 +20701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="442" spans="1:15">
+    <row r="442" ht="17" spans="1:15">
       <c r="A442" s="2">
         <v>2025</v>
       </c>
@@ -17398,7 +20728,7 @@
       <c r="J442" s="6"/>
       <c r="K442" s="5"/>
     </row>
-    <row r="443" spans="1:15">
+    <row r="443" ht="17" spans="1:15">
       <c r="A443" s="2">
         <v>2025</v>
       </c>
@@ -17425,7 +20755,7 @@
       <c r="J443" s="6"/>
       <c r="K443" s="5"/>
     </row>
-    <row r="444" spans="1:15">
+    <row r="444" ht="17" spans="1:15">
       <c r="A444" s="2">
         <v>2025</v>
       </c>
@@ -17452,7 +20782,7 @@
       <c r="J444" s="6"/>
       <c r="K444" s="5"/>
     </row>
-    <row r="445" spans="1:15">
+    <row r="445" ht="17" spans="1:15">
       <c r="A445" s="2">
         <v>2025</v>
       </c>
@@ -17479,7 +20809,7 @@
       <c r="J445" s="6"/>
       <c r="K445" s="5"/>
     </row>
-    <row r="446" spans="1:15">
+    <row r="446" ht="17" spans="1:15">
       <c r="A446" s="2">
         <v>2025</v>
       </c>
@@ -17506,7 +20836,7 @@
       <c r="J446" s="6"/>
       <c r="K446" s="5"/>
     </row>
-    <row r="447" spans="1:15">
+    <row r="447" ht="17" spans="1:15">
       <c r="A447" s="2">
         <v>2025</v>
       </c>
@@ -17533,7 +20863,7 @@
       <c r="J447" s="6"/>
       <c r="K447" s="5"/>
     </row>
-    <row r="448" spans="1:15">
+    <row r="448" ht="17" spans="1:15">
       <c r="A448" s="2">
         <v>2025</v>
       </c>
@@ -17560,7 +20890,7 @@
       <c r="J448" s="6"/>
       <c r="K448" s="5"/>
     </row>
-    <row r="449" spans="1:11">
+    <row r="449" ht="17" spans="1:11">
       <c r="A449" s="2">
         <v>2025</v>
       </c>
@@ -17587,7 +20917,7 @@
       <c r="J449" s="6"/>
       <c r="K449" s="5"/>
     </row>
-    <row r="450" spans="1:11">
+    <row r="450" ht="17" spans="1:11">
       <c r="A450" s="2">
         <v>2025</v>
       </c>
@@ -17614,7 +20944,7 @@
       <c r="J450" s="6"/>
       <c r="K450" s="5"/>
     </row>
-    <row r="451" spans="1:11">
+    <row r="451" ht="17" spans="1:11">
       <c r="A451" s="2">
         <v>2025</v>
       </c>
@@ -17641,7 +20971,7 @@
       <c r="J451" s="6"/>
       <c r="K451" s="5"/>
     </row>
-    <row r="452" spans="1:11">
+    <row r="452" ht="17" spans="1:11">
       <c r="A452" s="2">
         <v>2025</v>
       </c>
@@ -17668,7 +20998,7 @@
       <c r="J452" s="5"/>
       <c r="K452" s="5"/>
     </row>
-    <row r="453" spans="1:11">
+    <row r="453" ht="17" spans="1:11">
       <c r="A453" s="2">
         <v>2025</v>
       </c>
@@ -17695,7 +21025,7 @@
       <c r="J453" s="5"/>
       <c r="K453" s="5"/>
     </row>
-    <row r="454" spans="1:11">
+    <row r="454" ht="17" spans="1:11">
       <c r="A454" s="2">
         <v>2025</v>
       </c>
@@ -17722,7 +21052,7 @@
       <c r="J454" s="5"/>
       <c r="K454" s="5"/>
     </row>
-    <row r="455" spans="1:11">
+    <row r="455" ht="17" spans="1:11">
       <c r="A455" s="2">
         <v>2025</v>
       </c>
@@ -17749,7 +21079,7 @@
       <c r="J455" s="5"/>
       <c r="K455" s="5"/>
     </row>
-    <row r="456" spans="1:11">
+    <row r="456" ht="17" spans="1:11">
       <c r="A456" s="2">
         <v>2025</v>
       </c>
@@ -17776,7 +21106,7 @@
       <c r="J456" s="5"/>
       <c r="K456" s="5"/>
     </row>
-    <row r="457" spans="1:11">
+    <row r="457" ht="17" spans="1:11">
       <c r="A457" s="2">
         <v>2025</v>
       </c>
@@ -17803,7 +21133,7 @@
       <c r="J457" s="5"/>
       <c r="K457" s="5"/>
     </row>
-    <row r="458" spans="1:11">
+    <row r="458" ht="17" spans="1:11">
       <c r="A458" s="2">
         <v>2025</v>
       </c>
@@ -17830,7 +21160,7 @@
       <c r="J458" s="5"/>
       <c r="K458" s="5"/>
     </row>
-    <row r="459" spans="1:11">
+    <row r="459" ht="17" spans="1:11">
       <c r="A459" s="2">
         <v>2025</v>
       </c>
@@ -17857,7 +21187,7 @@
       <c r="J459" s="5"/>
       <c r="K459" s="5"/>
     </row>
-    <row r="460" spans="1:11">
+    <row r="460" ht="17" spans="1:11">
       <c r="A460" s="2">
         <v>2025</v>
       </c>
@@ -17884,7 +21214,7 @@
       <c r="J460" s="5"/>
       <c r="K460" s="5"/>
     </row>
-    <row r="461" spans="1:11">
+    <row r="461" ht="17" spans="1:11">
       <c r="A461" s="2">
         <v>2025</v>
       </c>
@@ -17911,7 +21241,7 @@
       <c r="J461" s="5"/>
       <c r="K461" s="5"/>
     </row>
-    <row r="462" spans="1:11">
+    <row r="462" ht="17" spans="1:11">
       <c r="A462" s="7">
         <v>2025</v>
       </c>
@@ -17939,7 +21269,7 @@
       <c r="I462" s="6"/>
       <c r="J462" s="5"/>
     </row>
-    <row r="463" spans="1:11">
+    <row r="463" ht="17" spans="1:11">
       <c r="A463" s="7">
         <v>2025</v>
       </c>
@@ -17967,7 +21297,7 @@
       <c r="I463" s="5"/>
       <c r="J463" s="5"/>
     </row>
-    <row r="464" spans="1:11">
+    <row r="464" ht="17" spans="1:11">
       <c r="A464" s="7">
         <v>2025</v>
       </c>
@@ -17995,7 +21325,7 @@
       <c r="I464" s="5"/>
       <c r="J464" s="5"/>
     </row>
-    <row r="465" spans="1:10">
+    <row r="465" ht="17" spans="1:10">
       <c r="A465" s="7">
         <v>2025</v>
       </c>
@@ -18023,7 +21353,7 @@
       <c r="I465" s="5"/>
       <c r="J465" s="5"/>
     </row>
-    <row r="466" spans="1:10">
+    <row r="466" ht="17" spans="1:10">
       <c r="A466" s="7">
         <v>2025</v>
       </c>
@@ -18051,7 +21381,7 @@
       <c r="I466" s="5"/>
       <c r="J466" s="5"/>
     </row>
-    <row r="467" spans="1:10">
+    <row r="467" ht="17" spans="1:10">
       <c r="A467" s="7">
         <v>2025</v>
       </c>
@@ -18079,7 +21409,7 @@
       <c r="I467" s="5"/>
       <c r="J467" s="5"/>
     </row>
-    <row r="468" spans="1:10">
+    <row r="468" ht="17" spans="1:10">
       <c r="A468" s="7">
         <v>2025</v>
       </c>
@@ -18107,7 +21437,7 @@
       <c r="I468" s="5"/>
       <c r="J468" s="5"/>
     </row>
-    <row r="469" spans="1:10">
+    <row r="469" ht="17" spans="1:10">
       <c r="A469" s="7">
         <v>2025</v>
       </c>
@@ -18135,7 +21465,7 @@
       <c r="I469" s="5"/>
       <c r="J469" s="5"/>
     </row>
-    <row r="470" spans="1:10">
+    <row r="470" ht="17" spans="1:10">
       <c r="A470" s="7">
         <v>2025</v>
       </c>
@@ -18163,7 +21493,7 @@
       <c r="I470" s="5"/>
       <c r="J470" s="5"/>
     </row>
-    <row r="471" spans="1:10">
+    <row r="471" ht="17" spans="1:10">
       <c r="A471" s="7">
         <v>2025</v>
       </c>
@@ -18191,7 +21521,7 @@
       <c r="I471" s="5"/>
       <c r="J471" s="5"/>
     </row>
-    <row r="472" spans="1:10">
+    <row r="472" ht="17" spans="1:10">
       <c r="A472" s="7">
         <v>2025</v>
       </c>
@@ -18219,7 +21549,7 @@
       <c r="I472" s="5"/>
       <c r="J472" s="5"/>
     </row>
-    <row r="473" spans="1:10">
+    <row r="473" ht="17" spans="1:10">
       <c r="A473" s="7">
         <v>2025</v>
       </c>
@@ -18247,7 +21577,7 @@
       <c r="I473" s="5"/>
       <c r="J473" s="5"/>
     </row>
-    <row r="474" spans="1:10">
+    <row r="474" ht="17" spans="1:10">
       <c r="A474" s="7">
         <v>2025</v>
       </c>
@@ -18275,7 +21605,7 @@
       <c r="I474" s="5"/>
       <c r="J474" s="5"/>
     </row>
-    <row r="475" spans="1:10">
+    <row r="475" ht="17" spans="1:10">
       <c r="A475" s="7">
         <v>2025</v>
       </c>
@@ -18303,7 +21633,7 @@
       <c r="I475" s="5"/>
       <c r="J475" s="5"/>
     </row>
-    <row r="476" spans="1:10">
+    <row r="476" ht="17" spans="1:10">
       <c r="A476" s="7">
         <v>2025</v>
       </c>
@@ -18331,7 +21661,7 @@
       <c r="I476" s="5"/>
       <c r="J476" s="5"/>
     </row>
-    <row r="477" spans="1:10">
+    <row r="477" ht="17" spans="1:10">
       <c r="A477" s="7">
         <v>2025</v>
       </c>
@@ -18359,7 +21689,7 @@
       <c r="I477" s="5"/>
       <c r="J477" s="5"/>
     </row>
-    <row r="478" spans="1:10">
+    <row r="478" ht="17" spans="1:10">
       <c r="A478" s="7">
         <v>2025</v>
       </c>
@@ -18387,7 +21717,7 @@
       <c r="I478" s="5"/>
       <c r="J478" s="5"/>
     </row>
-    <row r="479" spans="1:10">
+    <row r="479" ht="17" spans="1:10">
       <c r="A479" s="7">
         <v>2025</v>
       </c>
@@ -18415,7 +21745,7 @@
       <c r="I479" s="5"/>
       <c r="J479" s="5"/>
     </row>
-    <row r="480" spans="1:10">
+    <row r="480" ht="17" spans="1:10">
       <c r="A480" s="7">
         <v>2025</v>
       </c>
@@ -18443,7 +21773,7 @@
       <c r="I480" s="5"/>
       <c r="J480" s="5"/>
     </row>
-    <row r="481" spans="1:11">
+    <row r="481" ht="17" spans="1:11">
       <c r="A481" s="7">
         <v>2025</v>
       </c>
@@ -18471,7 +21801,7 @@
       <c r="I481" s="5"/>
       <c r="J481" s="5"/>
     </row>
-    <row r="482" spans="1:11">
+    <row r="482" ht="17" spans="1:11">
       <c r="A482" s="2">
         <v>2025</v>
       </c>
@@ -18498,7 +21828,7 @@
       <c r="J482" s="6"/>
       <c r="K482" s="5"/>
     </row>
-    <row r="483" spans="1:11">
+    <row r="483" ht="17" spans="1:11">
       <c r="A483" s="2">
         <v>2025</v>
       </c>
@@ -18525,7 +21855,7 @@
       <c r="J483" s="6"/>
       <c r="K483" s="5"/>
     </row>
-    <row r="484" spans="1:11">
+    <row r="484" ht="17" spans="1:11">
       <c r="A484" s="2">
         <v>2025</v>
       </c>
@@ -18552,7 +21882,7 @@
       <c r="J484" s="6"/>
       <c r="K484" s="5"/>
     </row>
-    <row r="485" spans="1:11">
+    <row r="485" ht="17" spans="1:11">
       <c r="A485" s="2">
         <v>2025</v>
       </c>
@@ -18579,7 +21909,7 @@
       <c r="J485" s="6"/>
       <c r="K485" s="5"/>
     </row>
-    <row r="486" spans="1:11">
+    <row r="486" ht="17" spans="1:11">
       <c r="A486" s="2">
         <v>2025</v>
       </c>
@@ -18606,7 +21936,7 @@
       <c r="J486" s="6"/>
       <c r="K486" s="5"/>
     </row>
-    <row r="487" spans="1:11">
+    <row r="487" ht="17" spans="1:11">
       <c r="A487" s="2">
         <v>2025</v>
       </c>
@@ -18633,7 +21963,7 @@
       <c r="J487" s="6"/>
       <c r="K487" s="5"/>
     </row>
-    <row r="488" spans="1:11">
+    <row r="488" ht="17" spans="1:11">
       <c r="A488" s="2">
         <v>2025</v>
       </c>
@@ -18660,7 +21990,7 @@
       <c r="J488" s="6"/>
       <c r="K488" s="5"/>
     </row>
-    <row r="489" spans="1:11">
+    <row r="489" ht="17" spans="1:11">
       <c r="A489" s="2">
         <v>2025</v>
       </c>
@@ -18687,7 +22017,7 @@
       <c r="J489" s="6"/>
       <c r="K489" s="5"/>
     </row>
-    <row r="490" spans="1:11">
+    <row r="490" ht="17" spans="1:11">
       <c r="A490" s="2">
         <v>2025</v>
       </c>
@@ -18714,7 +22044,7 @@
       <c r="J490" s="6"/>
       <c r="K490" s="5"/>
     </row>
-    <row r="491" spans="1:11">
+    <row r="491" ht="17" spans="1:11">
       <c r="A491" s="2">
         <v>2025</v>
       </c>
@@ -18741,7 +22071,7 @@
       <c r="J491" s="6"/>
       <c r="K491" s="5"/>
     </row>
-    <row r="492" spans="1:11">
+    <row r="492" ht="17" spans="1:11">
       <c r="A492" s="2">
         <v>2025</v>
       </c>
@@ -18768,7 +22098,7 @@
       <c r="J492" s="5"/>
       <c r="K492" s="5"/>
     </row>
-    <row r="493" spans="1:11">
+    <row r="493" ht="17" spans="1:11">
       <c r="A493" s="2">
         <v>2025</v>
       </c>
@@ -18795,7 +22125,7 @@
       <c r="J493" s="5"/>
       <c r="K493" s="5"/>
     </row>
-    <row r="494" spans="1:11">
+    <row r="494" ht="17" spans="1:11">
       <c r="A494" s="2">
         <v>2025</v>
       </c>
@@ -18822,7 +22152,7 @@
       <c r="J494" s="5"/>
       <c r="K494" s="5"/>
     </row>
-    <row r="495" spans="1:11">
+    <row r="495" ht="17" spans="1:11">
       <c r="A495" s="2">
         <v>2025</v>
       </c>
@@ -18849,7 +22179,7 @@
       <c r="J495" s="5"/>
       <c r="K495" s="5"/>
     </row>
-    <row r="496" spans="1:11">
+    <row r="496" ht="17" spans="1:11">
       <c r="A496" s="2">
         <v>2025</v>
       </c>
@@ -18876,7 +22206,7 @@
       <c r="J496" s="5"/>
       <c r="K496" s="5"/>
     </row>
-    <row r="497" spans="1:11">
+    <row r="497" ht="17" spans="1:11">
       <c r="A497" s="2">
         <v>2025</v>
       </c>
@@ -18903,7 +22233,7 @@
       <c r="J497" s="5"/>
       <c r="K497" s="5"/>
     </row>
-    <row r="498" spans="1:11">
+    <row r="498" ht="17" spans="1:11">
       <c r="A498" s="2">
         <v>2025</v>
       </c>
@@ -18930,7 +22260,7 @@
       <c r="J498" s="5"/>
       <c r="K498" s="5"/>
     </row>
-    <row r="499" spans="1:11">
+    <row r="499" ht="17" spans="1:11">
       <c r="A499" s="2">
         <v>2025</v>
       </c>
@@ -18957,7 +22287,7 @@
       <c r="J499" s="5"/>
       <c r="K499" s="5"/>
     </row>
-    <row r="500" spans="1:11">
+    <row r="500" ht="17" spans="1:11">
       <c r="A500" s="2">
         <v>2025</v>
       </c>
@@ -18984,7 +22314,7 @@
       <c r="J500" s="5"/>
       <c r="K500" s="5"/>
     </row>
-    <row r="501" spans="1:11">
+    <row r="501" ht="17" spans="1:11">
       <c r="A501" s="2">
         <v>2025</v>
       </c>
@@ -19011,7 +22341,7 @@
       <c r="J501" s="5"/>
       <c r="K501" s="5"/>
     </row>
-    <row r="502" spans="1:11">
+    <row r="502" ht="17" spans="1:11">
       <c r="A502" s="7">
         <v>2025</v>
       </c>
@@ -19039,7 +22369,7 @@
       <c r="I502" s="6"/>
       <c r="J502" s="5"/>
     </row>
-    <row r="503" spans="1:11">
+    <row r="503" ht="17" spans="1:11">
       <c r="A503" s="7">
         <v>2025</v>
       </c>
@@ -19067,7 +22397,7 @@
       <c r="I503" s="5"/>
       <c r="J503" s="5"/>
     </row>
-    <row r="504" spans="1:11">
+    <row r="504" ht="17" spans="1:11">
       <c r="A504" s="7">
         <v>2025</v>
       </c>
@@ -19095,7 +22425,7 @@
       <c r="I504" s="5"/>
       <c r="J504" s="5"/>
     </row>
-    <row r="505" spans="1:11">
+    <row r="505" ht="17" spans="1:11">
       <c r="A505" s="7">
         <v>2025</v>
       </c>
@@ -19123,7 +22453,7 @@
       <c r="I505" s="5"/>
       <c r="J505" s="5"/>
     </row>
-    <row r="506" spans="1:11">
+    <row r="506" ht="17" spans="1:11">
       <c r="A506" s="7">
         <v>2025</v>
       </c>
@@ -19151,7 +22481,7 @@
       <c r="I506" s="5"/>
       <c r="J506" s="5"/>
     </row>
-    <row r="507" spans="1:11">
+    <row r="507" ht="17" spans="1:11">
       <c r="A507" s="7">
         <v>2025</v>
       </c>
@@ -19179,7 +22509,7 @@
       <c r="I507" s="5"/>
       <c r="J507" s="5"/>
     </row>
-    <row r="508" spans="1:11">
+    <row r="508" ht="17" spans="1:11">
       <c r="A508" s="7">
         <v>2025</v>
       </c>
@@ -19207,7 +22537,7 @@
       <c r="I508" s="5"/>
       <c r="J508" s="5"/>
     </row>
-    <row r="509" spans="1:11">
+    <row r="509" ht="17" spans="1:11">
       <c r="A509" s="7">
         <v>2025</v>
       </c>
@@ -19235,7 +22565,7 @@
       <c r="I509" s="5"/>
       <c r="J509" s="5"/>
     </row>
-    <row r="510" spans="1:11">
+    <row r="510" ht="17" spans="1:11">
       <c r="A510" s="7">
         <v>2025</v>
       </c>
@@ -19263,7 +22593,7 @@
       <c r="I510" s="5"/>
       <c r="J510" s="5"/>
     </row>
-    <row r="511" spans="1:11">
+    <row r="511" ht="17" spans="1:11">
       <c r="A511" s="7">
         <v>2025</v>
       </c>
@@ -19291,7 +22621,7 @@
       <c r="I511" s="5"/>
       <c r="J511" s="5"/>
     </row>
-    <row r="512" spans="1:11">
+    <row r="512" ht="17" spans="1:11">
       <c r="A512" s="7">
         <v>2025</v>
       </c>
@@ -19319,7 +22649,7 @@
       <c r="I512" s="5"/>
       <c r="J512" s="5"/>
     </row>
-    <row r="513" spans="1:11">
+    <row r="513" ht="17" spans="1:11">
       <c r="A513" s="7">
         <v>2025</v>
       </c>
@@ -19347,7 +22677,7 @@
       <c r="I513" s="5"/>
       <c r="J513" s="5"/>
     </row>
-    <row r="514" spans="1:11">
+    <row r="514" ht="17" spans="1:11">
       <c r="A514" s="7">
         <v>2025</v>
       </c>
@@ -19375,7 +22705,7 @@
       <c r="I514" s="5"/>
       <c r="J514" s="5"/>
     </row>
-    <row r="515" spans="1:11">
+    <row r="515" ht="17" spans="1:11">
       <c r="A515" s="7">
         <v>2025</v>
       </c>
@@ -19403,7 +22733,7 @@
       <c r="I515" s="5"/>
       <c r="J515" s="5"/>
     </row>
-    <row r="516" spans="1:11">
+    <row r="516" ht="17" spans="1:11">
       <c r="A516" s="7">
         <v>2025</v>
       </c>
@@ -19431,7 +22761,7 @@
       <c r="I516" s="5"/>
       <c r="J516" s="5"/>
     </row>
-    <row r="517" spans="1:11">
+    <row r="517" ht="17" spans="1:11">
       <c r="A517" s="7">
         <v>2025</v>
       </c>
@@ -19459,7 +22789,7 @@
       <c r="I517" s="5"/>
       <c r="J517" s="5"/>
     </row>
-    <row r="518" spans="1:11">
+    <row r="518" ht="17" spans="1:11">
       <c r="A518" s="7">
         <v>2025</v>
       </c>
@@ -19487,7 +22817,7 @@
       <c r="I518" s="5"/>
       <c r="J518" s="5"/>
     </row>
-    <row r="519" spans="1:11">
+    <row r="519" ht="17" spans="1:11">
       <c r="A519" s="7">
         <v>2025</v>
       </c>
@@ -19515,7 +22845,7 @@
       <c r="I519" s="5"/>
       <c r="J519" s="5"/>
     </row>
-    <row r="520" spans="1:11">
+    <row r="520" ht="17" spans="1:11">
       <c r="A520" s="7">
         <v>2025</v>
       </c>
@@ -19543,7 +22873,7 @@
       <c r="I520" s="5"/>
       <c r="J520" s="5"/>
     </row>
-    <row r="521" spans="1:11">
+    <row r="521" ht="17" spans="1:11">
       <c r="A521" s="7">
         <v>2025</v>
       </c>
@@ -19571,7 +22901,7 @@
       <c r="I521" s="5"/>
       <c r="J521" s="5"/>
     </row>
-    <row r="522" spans="1:11">
+    <row r="522" ht="17" spans="1:11">
       <c r="A522" s="2">
         <v>2025</v>
       </c>
@@ -19598,7 +22928,7 @@
       <c r="J522" s="6"/>
       <c r="K522" s="5"/>
     </row>
-    <row r="523" spans="1:11">
+    <row r="523" ht="17" spans="1:11">
       <c r="A523" s="2">
         <v>2025</v>
       </c>
@@ -19625,7 +22955,7 @@
       <c r="J523" s="6"/>
       <c r="K523" s="5"/>
     </row>
-    <row r="524" spans="1:11">
+    <row r="524" ht="17" spans="1:11">
       <c r="A524" s="2">
         <v>2025</v>
       </c>
@@ -19652,7 +22982,7 @@
       <c r="J524" s="6"/>
       <c r="K524" s="5"/>
     </row>
-    <row r="525" spans="1:11">
+    <row r="525" ht="17" spans="1:11">
       <c r="A525" s="2">
         <v>2025</v>
       </c>
@@ -19679,7 +23009,7 @@
       <c r="J525" s="6"/>
       <c r="K525" s="5"/>
     </row>
-    <row r="526" spans="1:11">
+    <row r="526" ht="17" spans="1:11">
       <c r="A526" s="2">
         <v>2025</v>
       </c>
@@ -19706,7 +23036,7 @@
       <c r="J526" s="6"/>
       <c r="K526" s="5"/>
     </row>
-    <row r="527" spans="1:11">
+    <row r="527" ht="17" spans="1:11">
       <c r="A527" s="2">
         <v>2025</v>
       </c>
@@ -19733,7 +23063,7 @@
       <c r="J527" s="6"/>
       <c r="K527" s="5"/>
     </row>
-    <row r="528" spans="1:11">
+    <row r="528" ht="17" spans="1:11">
       <c r="A528" s="2">
         <v>2025</v>
       </c>
@@ -19760,7 +23090,7 @@
       <c r="J528" s="6"/>
       <c r="K528" s="5"/>
     </row>
-    <row r="529" spans="1:11">
+    <row r="529" ht="17" spans="1:11">
       <c r="A529" s="2">
         <v>2025</v>
       </c>
@@ -19787,7 +23117,7 @@
       <c r="J529" s="6"/>
       <c r="K529" s="5"/>
     </row>
-    <row r="530" spans="1:11">
+    <row r="530" ht="17" spans="1:11">
       <c r="A530" s="2">
         <v>2025</v>
       </c>
@@ -19814,7 +23144,7 @@
       <c r="J530" s="6"/>
       <c r="K530" s="5"/>
     </row>
-    <row r="531" spans="1:11">
+    <row r="531" ht="17" spans="1:11">
       <c r="A531" s="2">
         <v>2025</v>
       </c>
@@ -19841,7 +23171,7 @@
       <c r="J531" s="6"/>
       <c r="K531" s="5"/>
     </row>
-    <row r="532" spans="1:11">
+    <row r="532" ht="17" spans="1:11">
       <c r="A532" s="2">
         <v>2025</v>
       </c>
@@ -19868,7 +23198,7 @@
       <c r="J532" s="5"/>
       <c r="K532" s="5"/>
     </row>
-    <row r="533" spans="1:11">
+    <row r="533" ht="17" spans="1:11">
       <c r="A533" s="2">
         <v>2025</v>
       </c>
@@ -19895,7 +23225,7 @@
       <c r="J533" s="5"/>
       <c r="K533" s="5"/>
     </row>
-    <row r="534" spans="1:11">
+    <row r="534" ht="17" spans="1:11">
       <c r="A534" s="2">
         <v>2025</v>
       </c>
@@ -19922,7 +23252,7 @@
       <c r="J534" s="5"/>
       <c r="K534" s="5"/>
     </row>
-    <row r="535" spans="1:11">
+    <row r="535" ht="17" spans="1:11">
       <c r="A535" s="2">
         <v>2025</v>
       </c>
@@ -19949,7 +23279,7 @@
       <c r="J535" s="5"/>
       <c r="K535" s="5"/>
     </row>
-    <row r="536" spans="1:11">
+    <row r="536" ht="17" spans="1:11">
       <c r="A536" s="2">
         <v>2025</v>
       </c>
@@ -19976,7 +23306,7 @@
       <c r="J536" s="5"/>
       <c r="K536" s="5"/>
     </row>
-    <row r="537" spans="1:11">
+    <row r="537" ht="17" spans="1:11">
       <c r="A537" s="2">
         <v>2025</v>
       </c>
@@ -20003,7 +23333,7 @@
       <c r="J537" s="5"/>
       <c r="K537" s="5"/>
     </row>
-    <row r="538" spans="1:11">
+    <row r="538" ht="17" spans="1:11">
       <c r="A538" s="2">
         <v>2025</v>
       </c>
@@ -20030,7 +23360,7 @@
       <c r="J538" s="5"/>
       <c r="K538" s="5"/>
     </row>
-    <row r="539" spans="1:11">
+    <row r="539" ht="17" spans="1:11">
       <c r="A539" s="2">
         <v>2025</v>
       </c>
@@ -20057,7 +23387,7 @@
       <c r="J539" s="5"/>
       <c r="K539" s="5"/>
     </row>
-    <row r="540" spans="1:11">
+    <row r="540" ht="17" spans="1:11">
       <c r="A540" s="2">
         <v>2025</v>
       </c>
@@ -20084,7 +23414,7 @@
       <c r="J540" s="5"/>
       <c r="K540" s="5"/>
     </row>
-    <row r="541" spans="1:11">
+    <row r="541" ht="17" spans="1:11">
       <c r="A541" s="2">
         <v>2025</v>
       </c>
@@ -20111,7 +23441,7 @@
       <c r="J541" s="5"/>
       <c r="K541" s="5"/>
     </row>
-    <row r="542" spans="1:11">
+    <row r="542" ht="17" spans="1:11">
       <c r="A542" s="7">
         <v>2025</v>
       </c>
@@ -20139,7 +23469,7 @@
       <c r="I542" s="6"/>
       <c r="J542" s="5"/>
     </row>
-    <row r="543" spans="1:11">
+    <row r="543" ht="17" spans="1:11">
       <c r="A543" s="7">
         <v>2025</v>
       </c>
@@ -20167,7 +23497,7 @@
       <c r="I543" s="5"/>
       <c r="J543" s="5"/>
     </row>
-    <row r="544" spans="1:11">
+    <row r="544" ht="17" spans="1:11">
       <c r="A544" s="7">
         <v>2025</v>
       </c>
@@ -20195,7 +23525,7 @@
       <c r="I544" s="5"/>
       <c r="J544" s="5"/>
     </row>
-    <row r="545" spans="1:10">
+    <row r="545" ht="17" spans="1:10">
       <c r="A545" s="7">
         <v>2025</v>
       </c>
@@ -20223,7 +23553,7 @@
       <c r="I545" s="5"/>
       <c r="J545" s="5"/>
     </row>
-    <row r="546" spans="1:10">
+    <row r="546" ht="17" spans="1:10">
       <c r="A546" s="7">
         <v>2025</v>
       </c>
@@ -20251,7 +23581,7 @@
       <c r="I546" s="5"/>
       <c r="J546" s="5"/>
     </row>
-    <row r="547" spans="1:10">
+    <row r="547" ht="17" spans="1:10">
       <c r="A547" s="7">
         <v>2025</v>
       </c>
@@ -20279,7 +23609,7 @@
       <c r="I547" s="5"/>
       <c r="J547" s="5"/>
     </row>
-    <row r="548" spans="1:10">
+    <row r="548" ht="17" spans="1:10">
       <c r="A548" s="7">
         <v>2025</v>
       </c>
@@ -20307,7 +23637,7 @@
       <c r="I548" s="5"/>
       <c r="J548" s="5"/>
     </row>
-    <row r="549" spans="1:10">
+    <row r="549" ht="17" spans="1:10">
       <c r="A549" s="7">
         <v>2025</v>
       </c>
@@ -20335,7 +23665,7 @@
       <c r="I549" s="5"/>
       <c r="J549" s="5"/>
     </row>
-    <row r="550" spans="1:10">
+    <row r="550" ht="17" spans="1:10">
       <c r="A550" s="7">
         <v>2025</v>
       </c>
@@ -20363,7 +23693,7 @@
       <c r="I550" s="5"/>
       <c r="J550" s="5"/>
     </row>
-    <row r="551" spans="1:10">
+    <row r="551" ht="17" spans="1:10">
       <c r="A551" s="7">
         <v>2025</v>
       </c>
@@ -20391,7 +23721,7 @@
       <c r="I551" s="5"/>
       <c r="J551" s="5"/>
     </row>
-    <row r="552" spans="1:10">
+    <row r="552" ht="17" spans="1:10">
       <c r="A552" s="7">
         <v>2025</v>
       </c>
@@ -20419,7 +23749,7 @@
       <c r="I552" s="5"/>
       <c r="J552" s="5"/>
     </row>
-    <row r="553" spans="1:10">
+    <row r="553" ht="17" spans="1:10">
       <c r="A553" s="7">
         <v>2025</v>
       </c>
@@ -20447,7 +23777,7 @@
       <c r="I553" s="5"/>
       <c r="J553" s="5"/>
     </row>
-    <row r="554" spans="1:10">
+    <row r="554" ht="17" spans="1:10">
       <c r="A554" s="7">
         <v>2025</v>
       </c>
@@ -20475,7 +23805,7 @@
       <c r="I554" s="5"/>
       <c r="J554" s="5"/>
     </row>
-    <row r="555" spans="1:10">
+    <row r="555" ht="17" spans="1:10">
       <c r="A555" s="7">
         <v>2025</v>
       </c>
@@ -20503,7 +23833,7 @@
       <c r="I555" s="5"/>
       <c r="J555" s="5"/>
     </row>
-    <row r="556" spans="1:10">
+    <row r="556" ht="17" spans="1:10">
       <c r="A556" s="7">
         <v>2025</v>
       </c>
@@ -20531,7 +23861,7 @@
       <c r="I556" s="5"/>
       <c r="J556" s="5"/>
     </row>
-    <row r="557" spans="1:10">
+    <row r="557" ht="17" spans="1:10">
       <c r="A557" s="7">
         <v>2025</v>
       </c>
@@ -20559,7 +23889,7 @@
       <c r="I557" s="5"/>
       <c r="J557" s="5"/>
     </row>
-    <row r="558" spans="1:10">
+    <row r="558" ht="17" spans="1:10">
       <c r="A558" s="7">
         <v>2025</v>
       </c>
@@ -20587,7 +23917,7 @@
       <c r="I558" s="5"/>
       <c r="J558" s="5"/>
     </row>
-    <row r="559" spans="1:10">
+    <row r="559" ht="17" spans="1:10">
       <c r="A559" s="7">
         <v>2025</v>
       </c>
@@ -20615,7 +23945,7 @@
       <c r="I559" s="5"/>
       <c r="J559" s="5"/>
     </row>
-    <row r="560" spans="1:10">
+    <row r="560" ht="17" spans="1:10">
       <c r="A560" s="7">
         <v>2025</v>
       </c>
@@ -20643,7 +23973,7 @@
       <c r="I560" s="5"/>
       <c r="J560" s="5"/>
     </row>
-    <row r="561" spans="1:16">
+    <row r="561" ht="17" spans="1:16">
       <c r="A561" s="7">
         <v>2025</v>
       </c>
@@ -21196,7 +24526,7 @@
       <c r="H581" s="2"/>
       <c r="N581" s="11"/>
     </row>
-    <row r="582" spans="1:14">
+    <row r="582" ht="17" spans="1:14">
       <c r="A582" s="7">
         <v>2025</v>
       </c>
@@ -21224,7 +24554,7 @@
       <c r="I582" s="6"/>
       <c r="J582" s="5"/>
     </row>
-    <row r="583" spans="1:14">
+    <row r="583" ht="17" spans="1:14">
       <c r="A583" s="7">
         <v>2025</v>
       </c>
@@ -21252,7 +24582,7 @@
       <c r="I583" s="5"/>
       <c r="J583" s="5"/>
     </row>
-    <row r="584" spans="1:14">
+    <row r="584" ht="17" spans="1:14">
       <c r="A584" s="7">
         <v>2025</v>
       </c>
@@ -21280,7 +24610,7 @@
       <c r="I584" s="5"/>
       <c r="J584" s="5"/>
     </row>
-    <row r="585" spans="1:14">
+    <row r="585" ht="17" spans="1:14">
       <c r="A585" s="7">
         <v>2025</v>
       </c>
@@ -21308,7 +24638,7 @@
       <c r="I585" s="5"/>
       <c r="J585" s="5"/>
     </row>
-    <row r="586" spans="1:14">
+    <row r="586" ht="17" spans="1:14">
       <c r="A586" s="7">
         <v>2025</v>
       </c>
@@ -21336,7 +24666,7 @@
       <c r="I586" s="5"/>
       <c r="J586" s="5"/>
     </row>
-    <row r="587" spans="1:14">
+    <row r="587" ht="17" spans="1:14">
       <c r="A587" s="7">
         <v>2025</v>
       </c>
@@ -21364,7 +24694,7 @@
       <c r="I587" s="5"/>
       <c r="J587" s="5"/>
     </row>
-    <row r="588" spans="1:14">
+    <row r="588" ht="17" spans="1:14">
       <c r="A588" s="7">
         <v>2025</v>
       </c>
@@ -21392,7 +24722,7 @@
       <c r="I588" s="5"/>
       <c r="J588" s="5"/>
     </row>
-    <row r="589" spans="1:14">
+    <row r="589" ht="17" spans="1:14">
       <c r="A589" s="7">
         <v>2025</v>
       </c>
@@ -21420,7 +24750,7 @@
       <c r="I589" s="5"/>
       <c r="J589" s="5"/>
     </row>
-    <row r="590" spans="1:14">
+    <row r="590" ht="17" spans="1:14">
       <c r="A590" s="7">
         <v>2025</v>
       </c>
@@ -21448,7 +24778,7 @@
       <c r="I590" s="5"/>
       <c r="J590" s="5"/>
     </row>
-    <row r="591" spans="1:14">
+    <row r="591" ht="17" spans="1:14">
       <c r="A591" s="7">
         <v>2025</v>
       </c>
@@ -21476,7 +24806,7 @@
       <c r="I591" s="5"/>
       <c r="J591" s="5"/>
     </row>
-    <row r="592" spans="1:14">
+    <row r="592" ht="17" spans="1:14">
       <c r="A592" s="7">
         <v>2025</v>
       </c>
@@ -21504,7 +24834,7 @@
       <c r="I592" s="5"/>
       <c r="J592" s="5"/>
     </row>
-    <row r="593" spans="1:10">
+    <row r="593" ht="17" spans="1:10">
       <c r="A593" s="7">
         <v>2025</v>
       </c>
@@ -21532,7 +24862,7 @@
       <c r="I593" s="5"/>
       <c r="J593" s="5"/>
     </row>
-    <row r="594" spans="1:10">
+    <row r="594" ht="17" spans="1:10">
       <c r="A594" s="7">
         <v>2025</v>
       </c>
@@ -21560,7 +24890,7 @@
       <c r="I594" s="5"/>
       <c r="J594" s="5"/>
     </row>
-    <row r="595" spans="1:10">
+    <row r="595" ht="17" spans="1:10">
       <c r="A595" s="7">
         <v>2025</v>
       </c>
@@ -21588,7 +24918,7 @@
       <c r="I595" s="5"/>
       <c r="J595" s="5"/>
     </row>
-    <row r="596" spans="1:10">
+    <row r="596" ht="17" spans="1:10">
       <c r="A596" s="7">
         <v>2025</v>
       </c>
@@ -21616,7 +24946,7 @@
       <c r="I596" s="5"/>
       <c r="J596" s="5"/>
     </row>
-    <row r="597" spans="1:10">
+    <row r="597" ht="17" spans="1:10">
       <c r="A597" s="7">
         <v>2025</v>
       </c>
@@ -21644,7 +24974,7 @@
       <c r="I597" s="5"/>
       <c r="J597" s="5"/>
     </row>
-    <row r="598" spans="1:10">
+    <row r="598" ht="17" spans="1:10">
       <c r="A598" s="7">
         <v>2025</v>
       </c>
@@ -21672,7 +25002,7 @@
       <c r="I598" s="5"/>
       <c r="J598" s="5"/>
     </row>
-    <row r="599" spans="1:10">
+    <row r="599" ht="17" spans="1:10">
       <c r="A599" s="7">
         <v>2025</v>
       </c>
@@ -21700,7 +25030,7 @@
       <c r="I599" s="5"/>
       <c r="J599" s="5"/>
     </row>
-    <row r="600" spans="1:10">
+    <row r="600" ht="17" spans="1:10">
       <c r="A600" s="7">
         <v>2025</v>
       </c>
@@ -21728,7 +25058,7 @@
       <c r="I600" s="5"/>
       <c r="J600" s="5"/>
     </row>
-    <row r="601" spans="1:10">
+    <row r="601" ht="17" spans="1:10">
       <c r="A601" s="7">
         <v>2025</v>
       </c>
@@ -23781,7 +27111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="681" spans="1:17">
+    <row r="681" ht="17" spans="1:17">
       <c r="A681" s="7">
         <v>2025</v>
       </c>
@@ -23807,7 +27137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="682" spans="1:17">
+    <row r="682" ht="17" spans="1:17">
       <c r="A682" s="2">
         <v>2025</v>
       </c>
@@ -23835,7 +27165,7 @@
       <c r="P682" s="6"/>
       <c r="Q682" s="5"/>
     </row>
-    <row r="683" spans="1:17">
+    <row r="683" ht="17" spans="1:17">
       <c r="A683" s="2">
         <v>2025</v>
       </c>
@@ -23863,7 +27193,7 @@
       <c r="P683" s="6"/>
       <c r="Q683" s="5"/>
     </row>
-    <row r="684" spans="1:17">
+    <row r="684" ht="17" spans="1:17">
       <c r="A684" s="2">
         <v>2025</v>
       </c>
@@ -23891,7 +27221,7 @@
       <c r="P684" s="6"/>
       <c r="Q684" s="5"/>
     </row>
-    <row r="685" spans="1:17">
+    <row r="685" ht="17" spans="1:17">
       <c r="A685" s="2">
         <v>2025</v>
       </c>
@@ -23919,7 +27249,7 @@
       <c r="P685" s="6"/>
       <c r="Q685" s="5"/>
     </row>
-    <row r="686" spans="1:17">
+    <row r="686" ht="17" spans="1:17">
       <c r="A686" s="2">
         <v>2025</v>
       </c>
@@ -23947,7 +27277,7 @@
       <c r="P686" s="6"/>
       <c r="Q686" s="5"/>
     </row>
-    <row r="687" spans="1:17">
+    <row r="687" ht="17" spans="1:17">
       <c r="A687" s="2">
         <v>2025</v>
       </c>
@@ -23975,7 +27305,7 @@
       <c r="P687" s="6"/>
       <c r="Q687" s="5"/>
     </row>
-    <row r="688" spans="1:17">
+    <row r="688" ht="17" spans="1:17">
       <c r="A688" s="2">
         <v>2025</v>
       </c>
@@ -24003,7 +27333,7 @@
       <c r="P688" s="6"/>
       <c r="Q688" s="5"/>
     </row>
-    <row r="689" spans="1:17">
+    <row r="689" ht="17" spans="1:17">
       <c r="A689" s="2">
         <v>2025</v>
       </c>
@@ -24031,7 +27361,7 @@
       <c r="P689" s="6"/>
       <c r="Q689" s="5"/>
     </row>
-    <row r="690" spans="1:17">
+    <row r="690" ht="17" spans="1:17">
       <c r="A690" s="2">
         <v>2025</v>
       </c>
@@ -24059,7 +27389,7 @@
       <c r="P690" s="6"/>
       <c r="Q690" s="5"/>
     </row>
-    <row r="691" spans="1:17">
+    <row r="691" ht="17" spans="1:17">
       <c r="A691" s="2">
         <v>2025</v>
       </c>
@@ -24087,7 +27417,7 @@
       <c r="P691" s="6"/>
       <c r="Q691" s="5"/>
     </row>
-    <row r="692" spans="1:17">
+    <row r="692" ht="17" spans="1:17">
       <c r="A692" s="2">
         <v>2025</v>
       </c>
@@ -24115,7 +27445,7 @@
       <c r="P692" s="5"/>
       <c r="Q692" s="5"/>
     </row>
-    <row r="693" spans="1:17">
+    <row r="693" ht="17" spans="1:17">
       <c r="A693" s="2">
         <v>2025</v>
       </c>
@@ -24143,7 +27473,7 @@
       <c r="P693" s="5"/>
       <c r="Q693" s="5"/>
     </row>
-    <row r="694" spans="1:17">
+    <row r="694" ht="17" spans="1:17">
       <c r="A694" s="2">
         <v>2025</v>
       </c>
@@ -24171,7 +27501,7 @@
       <c r="P694" s="5"/>
       <c r="Q694" s="5"/>
     </row>
-    <row r="695" spans="1:17">
+    <row r="695" ht="17" spans="1:17">
       <c r="A695" s="2">
         <v>2025</v>
       </c>
@@ -24199,7 +27529,7 @@
       <c r="P695" s="5"/>
       <c r="Q695" s="5"/>
     </row>
-    <row r="696" spans="1:17">
+    <row r="696" ht="17" spans="1:17">
       <c r="A696" s="2">
         <v>2025</v>
       </c>
@@ -24227,7 +27557,7 @@
       <c r="P696" s="5"/>
       <c r="Q696" s="5"/>
     </row>
-    <row r="697" spans="1:17">
+    <row r="697" ht="17" spans="1:17">
       <c r="A697" s="2">
         <v>2025</v>
       </c>
@@ -24255,7 +27585,7 @@
       <c r="P697" s="5"/>
       <c r="Q697" s="5"/>
     </row>
-    <row r="698" spans="1:17">
+    <row r="698" ht="17" spans="1:17">
       <c r="A698" s="2">
         <v>2025</v>
       </c>
@@ -24283,7 +27613,7 @@
       <c r="P698" s="5"/>
       <c r="Q698" s="5"/>
     </row>
-    <row r="699" spans="1:17">
+    <row r="699" ht="17" spans="1:17">
       <c r="A699" s="2">
         <v>2025</v>
       </c>
@@ -24311,7 +27641,7 @@
       <c r="P699" s="5"/>
       <c r="Q699" s="5"/>
     </row>
-    <row r="700" spans="1:17">
+    <row r="700" ht="17" spans="1:17">
       <c r="A700" s="2">
         <v>2025</v>
       </c>
@@ -24339,7 +27669,7 @@
       <c r="P700" s="5"/>
       <c r="Q700" s="5"/>
     </row>
-    <row r="701" spans="1:17">
+    <row r="701" ht="17" spans="1:17">
       <c r="A701" s="2">
         <v>2025</v>
       </c>
@@ -24367,7 +27697,7 @@
       <c r="P701" s="5"/>
       <c r="Q701" s="5"/>
     </row>
-    <row r="702" spans="1:17">
+    <row r="702" ht="17" spans="1:17">
       <c r="A702" s="7">
         <v>2025</v>
       </c>
@@ -24394,7 +27724,7 @@
       </c>
       <c r="I702" s="6"/>
     </row>
-    <row r="703" spans="1:17">
+    <row r="703" ht="17" spans="1:17">
       <c r="A703" s="7">
         <v>2025</v>
       </c>
@@ -24421,7 +27751,7 @@
       </c>
       <c r="I703" s="5"/>
     </row>
-    <row r="704" spans="1:17">
+    <row r="704" ht="17" spans="1:17">
       <c r="A704" s="7">
         <v>2025</v>
       </c>
@@ -24448,7 +27778,7 @@
       </c>
       <c r="I704" s="5"/>
     </row>
-    <row r="705" spans="1:9">
+    <row r="705" ht="17" spans="1:9">
       <c r="A705" s="7">
         <v>2025</v>
       </c>
@@ -24475,7 +27805,7 @@
       </c>
       <c r="I705" s="5"/>
     </row>
-    <row r="706" spans="1:9">
+    <row r="706" ht="17" spans="1:9">
       <c r="A706" s="7">
         <v>2025</v>
       </c>
@@ -24502,7 +27832,7 @@
       </c>
       <c r="I706" s="5"/>
     </row>
-    <row r="707" spans="1:9">
+    <row r="707" ht="17" spans="1:9">
       <c r="A707" s="7">
         <v>2025</v>
       </c>
@@ -24529,7 +27859,7 @@
       </c>
       <c r="I707" s="5"/>
     </row>
-    <row r="708" spans="1:9">
+    <row r="708" ht="17" spans="1:9">
       <c r="A708" s="7">
         <v>2025</v>
       </c>
@@ -24556,7 +27886,7 @@
       </c>
       <c r="I708" s="5"/>
     </row>
-    <row r="709" spans="1:9">
+    <row r="709" ht="17" spans="1:9">
       <c r="A709" s="7">
         <v>2025</v>
       </c>
@@ -24583,7 +27913,7 @@
       </c>
       <c r="I709" s="5"/>
     </row>
-    <row r="710" spans="1:9">
+    <row r="710" ht="17" spans="1:9">
       <c r="A710" s="7">
         <v>2025</v>
       </c>
@@ -24610,7 +27940,7 @@
       </c>
       <c r="I710" s="5"/>
     </row>
-    <row r="711" spans="1:9">
+    <row r="711" ht="17" spans="1:9">
       <c r="A711" s="7">
         <v>2025</v>
       </c>
@@ -24637,7 +27967,7 @@
       </c>
       <c r="I711" s="5"/>
     </row>
-    <row r="712" spans="1:9">
+    <row r="712" ht="17" spans="1:9">
       <c r="A712" s="7">
         <v>2025</v>
       </c>
@@ -24664,7 +27994,7 @@
       </c>
       <c r="I712" s="5"/>
     </row>
-    <row r="713" spans="1:9">
+    <row r="713" ht="17" spans="1:9">
       <c r="A713" s="7">
         <v>2025</v>
       </c>
@@ -24691,7 +28021,7 @@
       </c>
       <c r="I713" s="5"/>
     </row>
-    <row r="714" spans="1:9">
+    <row r="714" ht="17" spans="1:9">
       <c r="A714" s="7">
         <v>2025</v>
       </c>
@@ -24718,7 +28048,7 @@
       </c>
       <c r="I714" s="5"/>
     </row>
-    <row r="715" spans="1:9">
+    <row r="715" ht="17" spans="1:9">
       <c r="A715" s="7">
         <v>2025</v>
       </c>
@@ -24745,7 +28075,7 @@
       </c>
       <c r="I715" s="5"/>
     </row>
-    <row r="716" spans="1:9">
+    <row r="716" ht="17" spans="1:9">
       <c r="A716" s="7">
         <v>2025</v>
       </c>
@@ -24772,7 +28102,7 @@
       </c>
       <c r="I716" s="5"/>
     </row>
-    <row r="717" spans="1:9">
+    <row r="717" ht="17" spans="1:9">
       <c r="A717" s="7">
         <v>2025</v>
       </c>
@@ -24799,7 +28129,7 @@
       </c>
       <c r="I717" s="5"/>
     </row>
-    <row r="718" spans="1:9">
+    <row r="718" ht="17" spans="1:9">
       <c r="A718" s="7">
         <v>2025</v>
       </c>
@@ -24826,7 +28156,7 @@
       </c>
       <c r="I718" s="5"/>
     </row>
-    <row r="719" spans="1:9">
+    <row r="719" ht="17" spans="1:9">
       <c r="A719" s="7">
         <v>2025</v>
       </c>
@@ -24853,7 +28183,7 @@
       </c>
       <c r="I719" s="5"/>
     </row>
-    <row r="720" spans="1:9">
+    <row r="720" ht="17" spans="1:9">
       <c r="A720" s="7">
         <v>2025</v>
       </c>
@@ -24880,7 +28210,7 @@
       </c>
       <c r="I720" s="5"/>
     </row>
-    <row r="721" spans="1:11">
+    <row r="721" ht="17" spans="1:11">
       <c r="A721" s="7">
         <v>2025</v>
       </c>
@@ -24907,7 +28237,7 @@
       </c>
       <c r="I721" s="5"/>
     </row>
-    <row r="722" spans="1:11">
+    <row r="722" ht="17" spans="1:11">
       <c r="A722" s="2">
         <v>2025</v>
       </c>
@@ -24934,7 +28264,7 @@
       <c r="J722" s="6"/>
       <c r="K722" s="5"/>
     </row>
-    <row r="723" spans="1:11">
+    <row r="723" ht="17" spans="1:11">
       <c r="A723" s="2">
         <v>2025</v>
       </c>
@@ -24961,7 +28291,7 @@
       <c r="J723" s="6"/>
       <c r="K723" s="5"/>
     </row>
-    <row r="724" spans="1:11">
+    <row r="724" ht="17" spans="1:11">
       <c r="A724" s="2">
         <v>2025</v>
       </c>
@@ -24988,7 +28318,7 @@
       <c r="J724" s="6"/>
       <c r="K724" s="5"/>
     </row>
-    <row r="725" spans="1:11">
+    <row r="725" ht="17" spans="1:11">
       <c r="A725" s="2">
         <v>2025</v>
       </c>
@@ -25015,7 +28345,7 @@
       <c r="J725" s="6"/>
       <c r="K725" s="5"/>
     </row>
-    <row r="726" spans="1:11">
+    <row r="726" ht="17" spans="1:11">
       <c r="A726" s="2">
         <v>2025</v>
       </c>
@@ -25042,7 +28372,7 @@
       <c r="J726" s="6"/>
       <c r="K726" s="5"/>
     </row>
-    <row r="727" spans="1:11">
+    <row r="727" ht="17" spans="1:11">
       <c r="A727" s="2">
         <v>2025</v>
       </c>
@@ -25069,7 +28399,7 @@
       <c r="J727" s="6"/>
       <c r="K727" s="5"/>
     </row>
-    <row r="728" spans="1:11">
+    <row r="728" ht="17" spans="1:11">
       <c r="A728" s="2">
         <v>2025</v>
       </c>
@@ -25096,7 +28426,7 @@
       <c r="J728" s="6"/>
       <c r="K728" s="5"/>
     </row>
-    <row r="729" spans="1:11">
+    <row r="729" ht="17" spans="1:11">
       <c r="A729" s="2">
         <v>2025</v>
       </c>
@@ -25123,7 +28453,7 @@
       <c r="J729" s="6"/>
       <c r="K729" s="5"/>
     </row>
-    <row r="730" spans="1:11">
+    <row r="730" ht="17" spans="1:11">
       <c r="A730" s="2">
         <v>2025</v>
       </c>
@@ -25150,7 +28480,7 @@
       <c r="J730" s="6"/>
       <c r="K730" s="5"/>
     </row>
-    <row r="731" spans="1:11">
+    <row r="731" ht="17" spans="1:11">
       <c r="A731" s="2">
         <v>2025</v>
       </c>
@@ -25177,7 +28507,7 @@
       <c r="J731" s="6"/>
       <c r="K731" s="5"/>
     </row>
-    <row r="732" spans="1:11">
+    <row r="732" ht="17" spans="1:11">
       <c r="A732" s="2">
         <v>2025</v>
       </c>
@@ -25204,7 +28534,7 @@
       <c r="J732" s="5"/>
       <c r="K732" s="5"/>
     </row>
-    <row r="733" spans="1:11">
+    <row r="733" ht="17" spans="1:11">
       <c r="A733" s="2">
         <v>2025</v>
       </c>
@@ -25231,7 +28561,7 @@
       <c r="J733" s="5"/>
       <c r="K733" s="5"/>
     </row>
-    <row r="734" spans="1:11">
+    <row r="734" ht="17" spans="1:11">
       <c r="A734" s="2">
         <v>2025</v>
       </c>
@@ -25258,7 +28588,7 @@
       <c r="J734" s="5"/>
       <c r="K734" s="5"/>
     </row>
-    <row r="735" spans="1:11">
+    <row r="735" ht="17" spans="1:11">
       <c r="A735" s="2">
         <v>2025</v>
       </c>
@@ -25285,7 +28615,7 @@
       <c r="J735" s="5"/>
       <c r="K735" s="5"/>
     </row>
-    <row r="736" spans="1:11">
+    <row r="736" ht="17" spans="1:11">
       <c r="A736" s="2">
         <v>2025</v>
       </c>
@@ -25312,7 +28642,7 @@
       <c r="J736" s="5"/>
       <c r="K736" s="5"/>
     </row>
-    <row r="737" spans="1:11">
+    <row r="737" ht="17" spans="1:11">
       <c r="A737" s="2">
         <v>2025</v>
       </c>
@@ -25339,7 +28669,7 @@
       <c r="J737" s="5"/>
       <c r="K737" s="5"/>
     </row>
-    <row r="738" spans="1:11">
+    <row r="738" ht="17" spans="1:11">
       <c r="A738" s="2">
         <v>2025</v>
       </c>
@@ -25366,7 +28696,7 @@
       <c r="J738" s="5"/>
       <c r="K738" s="5"/>
     </row>
-    <row r="739" spans="1:11">
+    <row r="739" ht="17" spans="1:11">
       <c r="A739" s="2">
         <v>2025</v>
       </c>
@@ -25393,7 +28723,7 @@
       <c r="J739" s="5"/>
       <c r="K739" s="5"/>
     </row>
-    <row r="740" spans="1:11">
+    <row r="740" ht="17" spans="1:11">
       <c r="A740" s="2">
         <v>2025</v>
       </c>
@@ -25420,7 +28750,7 @@
       <c r="J740" s="5"/>
       <c r="K740" s="5"/>
     </row>
-    <row r="741" spans="1:11">
+    <row r="741" ht="17" spans="1:11">
       <c r="A741" s="2">
         <v>2025</v>
       </c>
@@ -25447,7 +28777,7 @@
       <c r="J741" s="5"/>
       <c r="K741" s="5"/>
     </row>
-    <row r="742" spans="1:11">
+    <row r="742" ht="17" spans="1:11">
       <c r="A742" s="7">
         <v>2025</v>
       </c>
@@ -25473,7 +28803,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="743" spans="1:11">
+    <row r="743" ht="17" spans="1:11">
       <c r="A743" s="7">
         <v>2025</v>
       </c>
@@ -25499,7 +28829,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="744" spans="1:11">
+    <row r="744" ht="17" spans="1:11">
       <c r="A744" s="7">
         <v>2025</v>
       </c>
@@ -25525,7 +28855,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="745" spans="1:11">
+    <row r="745" ht="17" spans="1:11">
       <c r="A745" s="7">
         <v>2025</v>
       </c>
@@ -25551,7 +28881,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="746" spans="1:11">
+    <row r="746" ht="17" spans="1:11">
       <c r="A746" s="7">
         <v>2025</v>
       </c>
@@ -25577,7 +28907,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="747" spans="1:11">
+    <row r="747" ht="17" spans="1:11">
       <c r="A747" s="7">
         <v>2025</v>
       </c>
@@ -25603,7 +28933,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="748" spans="1:11">
+    <row r="748" ht="17" spans="1:11">
       <c r="A748" s="7">
         <v>2025</v>
       </c>
@@ -25629,7 +28959,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="749" spans="1:11">
+    <row r="749" ht="17" spans="1:11">
       <c r="A749" s="7">
         <v>2025</v>
       </c>
@@ -25655,7 +28985,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="750" spans="1:11">
+    <row r="750" ht="17" spans="1:11">
       <c r="A750" s="7">
         <v>2025</v>
       </c>
@@ -25681,7 +29011,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="751" spans="1:11">
+    <row r="751" ht="17" spans="1:11">
       <c r="A751" s="7">
         <v>2025</v>
       </c>
@@ -25707,7 +29037,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="752" spans="1:11">
+    <row r="752" ht="17" spans="1:11">
       <c r="A752" s="7">
         <v>2025</v>
       </c>
@@ -25733,7 +29063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="753" spans="1:16">
+    <row r="753" ht="17" spans="1:16">
       <c r="A753" s="7">
         <v>2025</v>
       </c>
@@ -25759,7 +29089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="754" spans="1:16">
+    <row r="754" ht="17" spans="1:16">
       <c r="A754" s="7">
         <v>2025</v>
       </c>
@@ -25785,7 +29115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="755" spans="1:16">
+    <row r="755" ht="17" spans="1:16">
       <c r="A755" s="7">
         <v>2025</v>
       </c>
@@ -25811,7 +29141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="756" spans="1:16">
+    <row r="756" ht="17" spans="1:16">
       <c r="A756" s="7">
         <v>2025</v>
       </c>
@@ -25837,7 +29167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="757" spans="1:16">
+    <row r="757" ht="17" spans="1:16">
       <c r="A757" s="7">
         <v>2025</v>
       </c>
@@ -25863,7 +29193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="758" spans="1:16">
+    <row r="758" ht="17" spans="1:16">
       <c r="A758" s="7">
         <v>2025</v>
       </c>
@@ -25889,7 +29219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="759" spans="1:16">
+    <row r="759" ht="17" spans="1:16">
       <c r="A759" s="7">
         <v>2025</v>
       </c>
@@ -25915,7 +29245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="760" spans="1:16">
+    <row r="760" ht="17" spans="1:16">
       <c r="A760" s="7">
         <v>2025</v>
       </c>
@@ -25941,7 +29271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="761" spans="1:16">
+    <row r="761" ht="17" spans="1:16">
       <c r="A761" s="7">
         <v>2025</v>
       </c>
@@ -26982,7 +30312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="801" spans="1:8">
+    <row r="801" ht="17" spans="1:8">
       <c r="A801" s="2">
         <v>2025</v>
       </c>
@@ -37053,24 +40383,28 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1201" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H1201" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" customWidth="1"/>
-    <col min="2" max="2" width="15.42578125" customWidth="1"/>
-    <col min="3" max="3" width="9.42578125" customWidth="1"/>
-    <col min="4" max="4" width="42.5703125" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.5703125" customWidth="1"/>
-    <col min="7" max="7" width="6.7109375" customWidth="1"/>
+    <col min="1" max="1" width="9.71428571428571" customWidth="1"/>
+    <col min="2" max="2" width="15.4285714285714" customWidth="1"/>
+    <col min="3" max="3" width="9.42857142857143" customWidth="1"/>
+    <col min="4" max="4" width="42.5714285714286" customWidth="1"/>
+    <col min="5" max="5" width="11.7142857142857" customWidth="1"/>
+    <col min="6" max="6" width="4.57142857142857" customWidth="1"/>
+    <col min="7" max="7" width="6.71428571428571" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -37114,7 +40448,7 @@
         <v>58</v>
       </c>
       <c r="G2" s="2">
-        <v>5.2779999999999996</v>
+        <v>5.278</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -37135,7 +40469,7 @@
         <v>56</v>
       </c>
       <c r="G3" s="2">
-        <v>5.4509999999999996</v>
+        <v>5.451</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -37156,7 +40490,7 @@
         <v>53</v>
       </c>
       <c r="G4" s="2">
-        <v>5.8070000000000004</v>
+        <v>5.807</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -37177,7 +40511,7 @@
         <v>57</v>
       </c>
       <c r="G5" s="2">
-        <v>5.4119999999999999</v>
+        <v>5.412</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -37198,7 +40532,7 @@
         <v>50</v>
       </c>
       <c r="G6" s="2">
-        <v>5.1740000000000004</v>
+        <v>5.174</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -37221,7 +40555,7 @@
         <v>57</v>
       </c>
       <c r="G7" s="2">
-        <v>5.4119999999999999</v>
+        <v>5.412</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -37244,7 +40578,7 @@
         <v>63</v>
       </c>
       <c r="G8" s="2">
-        <v>4.9089999999999998</v>
+        <v>4.909</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -37265,7 +40599,7 @@
         <v>78</v>
       </c>
       <c r="G9" s="2">
-        <v>3.3370000000000002</v>
+        <v>3.337</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -37309,7 +40643,7 @@
         <v>70</v>
       </c>
       <c r="G11" s="2">
-        <v>4.3609999999999998</v>
+        <v>4.361</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -37330,7 +40664,7 @@
         <v>71</v>
       </c>
       <c r="G12" s="2">
-        <v>4.3179999999999996</v>
+        <v>4.318</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -37372,7 +40706,7 @@
         <v>44</v>
       </c>
       <c r="G14" s="2">
-        <v>7.0039999999999996</v>
+        <v>7.004</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -37393,7 +40727,7 @@
         <v>70</v>
       </c>
       <c r="G15" s="2">
-        <v>4.3810000000000002</v>
+        <v>4.381</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -37414,7 +40748,7 @@
         <v>72</v>
       </c>
       <c r="G16" s="2">
-        <v>4.2590000000000003</v>
+        <v>4.259</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -37437,7 +40771,7 @@
         <v>53</v>
       </c>
       <c r="G17" s="2">
-        <v>5.7930000000000001</v>
+        <v>5.793</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -37458,7 +40792,7 @@
         <v>51</v>
       </c>
       <c r="G18" s="2">
-        <v>6.0030000000000001</v>
+        <v>6.003</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -37502,7 +40836,7 @@
         <v>56</v>
       </c>
       <c r="G20" s="2">
-        <v>5.5129999999999999</v>
+        <v>5.513</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -37523,7 +40857,7 @@
         <v>71</v>
       </c>
       <c r="G21" s="2">
-        <v>4.3040000000000003</v>
+        <v>4.304</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -37544,7 +40878,7 @@
         <v>71</v>
       </c>
       <c r="G22" s="2">
-        <v>4.3090000000000002</v>
+        <v>4.309</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -37567,7 +40901,7 @@
         <v>50</v>
       </c>
       <c r="G23" s="2">
-        <v>6.2009999999999996</v>
+        <v>6.201</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -37588,7 +40922,7 @@
         <v>57</v>
       </c>
       <c r="G24" s="2">
-        <v>5.4189999999999996</v>
+        <v>5.419</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -37609,24 +40943,26 @@
         <v>58</v>
       </c>
       <c r="G25" s="2">
-        <v>5.2809999999999997</v>
+        <v>5.281</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:G22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G44"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="2" width="5.140625" customWidth="1"/>
-    <col min="3" max="3" width="7.7109375" customWidth="1"/>
-    <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" customWidth="1"/>
-    <col min="6" max="6" width="15.42578125" customWidth="1"/>
+    <col min="1" max="3" width="5.14285714285714" customWidth="1"/>
+    <col min="4" max="4" width="7.71428571428571" customWidth="1"/>
+    <col min="5" max="5" width="20" customWidth="1"/>
+    <col min="6" max="6" width="14.7142857142857" customWidth="1"/>
+    <col min="7" max="7" width="15.4285714285714" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -37634,818 +40970,1498 @@
         <v>148</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C2" s="4">
         <v>4</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="G2" s="2">
-        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C3" s="4">
         <v>81</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>156</v>
       </c>
       <c r="F3" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="G3" s="2">
-        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C4" s="4">
         <v>1</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>158</v>
       </c>
+      <c r="E4" s="3" t="s">
+        <v>159</v>
+      </c>
       <c r="F4" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="G4" s="2">
-        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C5" s="4">
         <v>22</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>160</v>
+      <c r="D5" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>162</v>
       </c>
       <c r="F5" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="G5" s="2">
-        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C6" s="4">
         <v>63</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>162</v>
+      <c r="D6" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>165</v>
       </c>
       <c r="F6" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="G6" s="2">
-        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C7" s="4">
         <v>12</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>164</v>
+      <c r="D7" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>168</v>
       </c>
       <c r="F7" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="G7" s="2">
-        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C8" s="4">
         <v>16</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>166</v>
+      <c r="D8" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>171</v>
       </c>
       <c r="F8" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="G8" s="2">
-        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C9" s="4">
         <v>44</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>168</v>
+      <c r="D9" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>174</v>
       </c>
       <c r="F9" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="G9" s="2">
-        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C10" s="4">
         <v>30</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>170</v>
+      <c r="D10" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>177</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="G10" s="2">
-        <v>1</v>
+        <v>178</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="2">
         <v>10</v>
       </c>
-      <c r="B11" s="4">
+      <c r="B11" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C11" s="4">
         <v>6</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>173</v>
+      <c r="D11" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>181</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="G11" s="2">
-        <v>1</v>
+        <v>182</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="2">
         <v>11</v>
       </c>
-      <c r="B12" s="4">
+      <c r="B12" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C12" s="4">
         <v>23</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>176</v>
+      <c r="D12" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>185</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="G12" s="2">
-        <v>1</v>
+        <v>186</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="2">
         <v>12</v>
       </c>
-      <c r="B13" s="4">
+      <c r="B13" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C13" s="4">
         <v>55</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>179</v>
+      <c r="D13" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>189</v>
       </c>
       <c r="F13" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="G13" s="2">
-        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="2">
         <v>13</v>
       </c>
-      <c r="B14" s="4">
+      <c r="B14" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C14" s="4">
         <v>10</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>181</v>
+      <c r="D14" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>192</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="G14" s="2">
-        <v>1</v>
+        <v>193</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="2">
         <v>21</v>
       </c>
-      <c r="B15" s="4">
+      <c r="B15" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C15" s="4">
         <v>43</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="E15" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>183</v>
-      </c>
       <c r="F15" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="G15" s="2">
-        <v>1</v>
+        <v>195</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="2">
         <v>14</v>
       </c>
-      <c r="B16" s="4">
+      <c r="B16" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C16" s="4">
         <v>7</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>124</v>
+      <c r="D16" s="2" t="s">
+        <v>197</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="F16" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="G16" s="2">
-        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="2">
         <v>15</v>
       </c>
-      <c r="B17" s="4">
+      <c r="B17" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C17" s="4">
         <v>18</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>188</v>
+      <c r="D17" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="F17" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="G17" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="G17" s="2">
-        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="2">
         <v>16</v>
       </c>
-      <c r="B18" s="4">
+      <c r="B18" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C18" s="4">
         <v>14</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>190</v>
+      <c r="D18" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>204</v>
       </c>
       <c r="F18" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="G18" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="G18" s="2">
-        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="2">
         <v>17</v>
       </c>
-      <c r="B19" s="4">
+      <c r="B19" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C19" s="4">
         <v>27</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>192</v>
+      <c r="D19" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>207</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="G19" s="2">
-        <v>1</v>
+        <v>208</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="2">
         <v>18</v>
       </c>
-      <c r="B20" s="4">
+      <c r="B20" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C20" s="4">
         <v>5</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>195</v>
+      <c r="D20" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>211</v>
       </c>
       <c r="F20" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="G20" s="2" t="s">
         <v>72</v>
-      </c>
-      <c r="G20" s="2">
-        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="2">
         <v>19</v>
       </c>
-      <c r="B21" s="4">
+      <c r="B21" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C21" s="4">
         <v>31</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>197</v>
+      <c r="D21" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>214</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="G21" s="2">
-        <v>1</v>
+        <v>215</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="2">
         <v>20</v>
       </c>
-      <c r="B22" s="4">
+      <c r="B22" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C22" s="4">
         <v>87</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>199</v>
+      <c r="D22" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>217</v>
       </c>
       <c r="F22" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="G22" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="G22" s="2">
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="2">
         <v>1</v>
+      </c>
+      <c r="B23" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C23" s="4">
+        <v>1</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="2">
+        <v>2</v>
+      </c>
+      <c r="B24" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C24" s="4">
+        <v>81</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="2">
+        <v>3</v>
+      </c>
+      <c r="B25" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C25" s="4">
+        <v>3</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="2">
+        <v>4</v>
+      </c>
+      <c r="B26" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C26" s="4">
+        <v>6</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="2">
+        <v>5</v>
+      </c>
+      <c r="B27" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C27" s="4">
+        <v>63</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="2">
+        <v>6</v>
+      </c>
+      <c r="B28" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C28" s="4">
+        <v>12</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="2">
+        <v>7</v>
+      </c>
+      <c r="B29" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C29" s="4">
+        <v>16</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="2">
+        <v>8</v>
+      </c>
+      <c r="B30" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C30" s="4">
+        <v>44</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="2">
+        <v>9</v>
+      </c>
+      <c r="B31" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C31" s="4">
+        <v>30</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="2">
+        <v>10</v>
+      </c>
+      <c r="B32" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C32" s="4">
+        <v>41</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="2">
+        <v>11</v>
+      </c>
+      <c r="B33" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C33" s="4">
+        <v>23</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" s="2">
+        <v>12</v>
+      </c>
+      <c r="B34" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C34" s="4">
+        <v>55</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" s="2">
+        <v>13</v>
+      </c>
+      <c r="B35" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C35" s="4">
+        <v>10</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" s="2">
+        <v>21</v>
+      </c>
+      <c r="B36" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C36" s="4">
+        <v>43</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" s="2">
+        <v>15</v>
+      </c>
+      <c r="B37" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C37" s="4">
+        <v>18</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" s="2">
+        <v>16</v>
+      </c>
+      <c r="B38" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C38" s="4">
+        <v>14</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" s="2">
+        <v>17</v>
+      </c>
+      <c r="B39" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C39" s="4">
+        <v>27</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="2">
+        <v>18</v>
+      </c>
+      <c r="B40" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C40" s="4">
+        <v>5</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="2">
+        <v>19</v>
+      </c>
+      <c r="B41" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C41" s="4">
+        <v>31</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="2">
+        <v>20</v>
+      </c>
+      <c r="B42" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C42" s="4">
+        <v>87</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="2">
+        <v>21</v>
+      </c>
+      <c r="B43" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C43" s="4">
+        <v>11</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="2">
+        <v>22</v>
+      </c>
+      <c r="B44" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C44" s="4">
+        <v>77</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>228</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:E32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F31"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="5"/>
   <cols>
-    <col min="2" max="2" width="12.28515625" customWidth="1"/>
-    <col min="3" max="3" width="29.28515625" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="8.5703125" customWidth="1"/>
+    <col min="3" max="3" width="12.2857142857143" customWidth="1"/>
+    <col min="4" max="4" width="29.2857142857143" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="8.57142857142857" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>148</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>200</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+        <v>229</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="2" ht="17" spans="1:6">
       <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="F2" s="2" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="3" ht="17" spans="1:6">
       <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="C3" s="3" t="s">
+      <c r="B3" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="F3" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="4" ht="17" spans="1:6">
       <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="F4" s="2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="5" ht="17" spans="1:6">
       <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="E5" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="F5" s="2" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="6" ht="17" spans="1:6">
       <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="C6" s="3" t="s">
+      <c r="B6" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+      <c r="F6" s="2" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="7" ht="17" spans="1:6">
       <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="E7" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+      <c r="F7" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="8" ht="17" spans="1:6">
       <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="E8" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+      <c r="F8" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="9" ht="17" spans="1:6">
       <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="C9" s="3" t="s">
+      <c r="B9" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="E9" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+      <c r="F9" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="10" ht="17" spans="1:6">
       <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="C10" s="3" t="s">
+      <c r="B10" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="E10" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+      <c r="F10" s="2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="11" ht="17" spans="1:6">
       <c r="A11" s="2">
         <v>10</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="E11" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+      <c r="F11" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="12" ht="17" spans="1:6">
       <c r="A12" s="2">
+        <v>1</v>
+      </c>
+      <c r="B12" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="13" ht="17" spans="1:6">
+      <c r="A13" s="2">
+        <v>2</v>
+      </c>
+      <c r="B13" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="14" ht="17" spans="1:6">
+      <c r="A14" s="2">
+        <v>3</v>
+      </c>
+      <c r="B14" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="15" ht="17" spans="1:6">
+      <c r="A15" s="2">
+        <v>4</v>
+      </c>
+      <c r="B15" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="16" ht="17" spans="1:6">
+      <c r="A16" s="2">
+        <v>5</v>
+      </c>
+      <c r="B16" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="17" ht="17" spans="1:6">
+      <c r="A17" s="2">
+        <v>6</v>
+      </c>
+      <c r="B17" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="18" ht="17" spans="1:6">
+      <c r="A18" s="2">
+        <v>7</v>
+      </c>
+      <c r="B18" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="19" ht="17" spans="1:6">
+      <c r="A19" s="2">
+        <v>8</v>
+      </c>
+      <c r="B19" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="20" ht="17" spans="1:6">
+      <c r="A20" s="2">
+        <v>10</v>
+      </c>
+      <c r="B20" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="2">
         <v>11</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="E12" s="2"/>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="2">
+      <c r="B21" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="F21" s="2"/>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="2">
         <v>12</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="E13" s="2"/>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-    </row>
-    <row r="17" spans="4:5">
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-    </row>
-    <row r="18" spans="4:5">
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-    </row>
-    <row r="19" spans="4:5">
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-    </row>
-    <row r="20" spans="4:5">
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-    </row>
-    <row r="21" spans="4:5">
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-    </row>
-    <row r="22" spans="4:5">
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-    </row>
-    <row r="23" spans="4:5">
-      <c r="D23" s="5"/>
+      <c r="B22" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="F22" s="2"/>
+    </row>
+    <row r="23" spans="1:6">
       <c r="E23" s="5"/>
-    </row>
-    <row r="24" spans="4:5">
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-    </row>
-    <row r="25" spans="4:5">
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-    </row>
-    <row r="26" spans="4:5">
-      <c r="D26" s="5"/>
+      <c r="F23" s="5"/>
+    </row>
+    <row r="26" spans="1:6">
       <c r="E26" s="5"/>
-    </row>
-    <row r="27" spans="4:5">
-      <c r="D27" s="5"/>
+      <c r="F26" s="5"/>
+    </row>
+    <row r="27" spans="1:6">
       <c r="E27" s="5"/>
-    </row>
-    <row r="28" spans="4:5">
-      <c r="D28" s="5"/>
+      <c r="F27" s="5"/>
+    </row>
+    <row r="28" spans="1:6">
       <c r="E28" s="5"/>
-    </row>
-    <row r="29" spans="4:5">
-      <c r="D29" s="5"/>
+      <c r="F28" s="5"/>
+    </row>
+    <row r="29" spans="1:6">
       <c r="E29" s="5"/>
-    </row>
-    <row r="30" spans="4:5">
-      <c r="D30" s="5"/>
+      <c r="F29" s="5"/>
+    </row>
+    <row r="30" spans="1:6">
       <c r="E30" s="5"/>
-    </row>
-    <row r="31" spans="4:5">
-      <c r="D31" s="5"/>
+      <c r="F30" s="5"/>
+    </row>
+    <row r="31" spans="1:6">
       <c r="E31" s="5"/>
-    </row>
-    <row r="32" spans="4:5">
-      <c r="D32" s="5"/>
-      <c r="E32" s="5"/>
+      <c r="F31" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/public/docs/datas/f1.xlsx
+++ b/public/docs/datas/f1.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Docs\byMe\vue_platform\public\docs\datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29CE998A-B2E4-4A00-A6B8-E38D27AD4A7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="26420" windowHeight="15520" firstSheet="1" activeTab="4"/>
+    <workbookView xWindow="660" yWindow="360" windowWidth="21285" windowHeight="15525" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="rounds" sheetId="7" r:id="rId1"/>
@@ -848,174 +854,24 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="21">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="35">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1034,194 +890,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1244,251 +914,9 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1535,61 +963,17 @@
     <xf numFmtId="20" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1847,16 +1231,16 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C49"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="9.57142857142857" customWidth="1"/>
+    <col min="1" max="2" width="9.5703125" customWidth="1"/>
     <col min="3" max="3" width="11" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2401,22 +1785,20 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G241"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="5.57142857142857" customWidth="1"/>
-    <col min="2" max="2" width="6.28571428571429" customWidth="1"/>
-    <col min="3" max="3" width="19.7142857142857" customWidth="1"/>
-    <col min="4" max="4" width="11.2857142857143" customWidth="1"/>
-    <col min="5" max="6" width="9.42857142857143" customWidth="1"/>
-    <col min="7" max="7" width="7.42857142857143" customWidth="1"/>
+    <col min="1" max="1" width="5.5703125" customWidth="1"/>
+    <col min="2" max="2" width="6.28515625" customWidth="1"/>
+    <col min="3" max="3" width="19.7109375" customWidth="1"/>
+    <col min="4" max="4" width="11.28515625" customWidth="1"/>
+    <col min="5" max="6" width="9.42578125" customWidth="1"/>
+    <col min="7" max="7" width="7.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -2456,7 +1838,7 @@
         <v>45730</v>
       </c>
       <c r="E2" s="20">
-        <v>0.395833333333333</v>
+        <v>0.39583333333333298</v>
       </c>
       <c r="F2" s="20">
         <v>0.4375</v>
@@ -2479,10 +1861,10 @@
         <v>45730</v>
       </c>
       <c r="E3" s="20">
-        <v>0.541666666666667</v>
+        <v>0.54166666666666696</v>
       </c>
       <c r="F3" s="20">
-        <v>0.583333333333333</v>
+        <v>0.58333333333333304</v>
       </c>
       <c r="G3" s="6">
         <v>0</v>
@@ -2502,7 +1884,7 @@
         <v>45731</v>
       </c>
       <c r="E4" s="20">
-        <v>0.395833333333333</v>
+        <v>0.39583333333333298</v>
       </c>
       <c r="F4" s="20">
         <v>0.4375</v>
@@ -2525,10 +1907,10 @@
         <v>45731</v>
       </c>
       <c r="E5" s="20">
-        <v>0.541666666666667</v>
+        <v>0.54166666666666696</v>
       </c>
       <c r="F5" s="20">
-        <v>0.583333333333333</v>
+        <v>0.58333333333333304</v>
       </c>
       <c r="G5" s="6">
         <v>1</v>
@@ -2569,10 +1951,10 @@
         <v>45737</v>
       </c>
       <c r="E7" s="22">
-        <v>0.479166666666667</v>
+        <v>0.47916666666666702</v>
       </c>
       <c r="F7" s="22">
-        <v>0.520833333333333</v>
+        <v>0.52083333333333304</v>
       </c>
       <c r="G7" s="12">
         <v>0</v>
@@ -2592,10 +1974,10 @@
         <v>45737</v>
       </c>
       <c r="E8" s="22">
-        <v>0.645833333333333</v>
+        <v>0.64583333333333304</v>
       </c>
       <c r="F8" s="22">
-        <v>0.676388888888889</v>
+        <v>0.67638888888888904</v>
       </c>
       <c r="G8" s="12">
         <v>1</v>
@@ -2615,7 +1997,7 @@
         <v>45738</v>
       </c>
       <c r="E9" s="22">
-        <v>0.458333333333333</v>
+        <v>0.45833333333333298</v>
       </c>
       <c r="F9" s="22">
         <v>0.5</v>
@@ -2641,7 +2023,7 @@
         <v>0.625</v>
       </c>
       <c r="F10" s="22">
-        <v>0.666666666666667</v>
+        <v>0.66666666666666696</v>
       </c>
       <c r="G10" s="12">
         <v>1</v>
@@ -2685,7 +2067,7 @@
         <v>0.4375</v>
       </c>
       <c r="F12" s="20">
-        <v>0.479166666666667</v>
+        <v>0.47916666666666702</v>
       </c>
       <c r="G12" s="6">
         <v>0</v>
@@ -2705,7 +2087,7 @@
         <v>45751</v>
       </c>
       <c r="E13" s="20">
-        <v>0.583333333333333</v>
+        <v>0.58333333333333304</v>
       </c>
       <c r="F13" s="20">
         <v>0.625</v>
@@ -2731,7 +2113,7 @@
         <v>0.4375</v>
       </c>
       <c r="F14" s="20">
-        <v>0.479166666666667</v>
+        <v>0.47916666666666702</v>
       </c>
       <c r="G14" s="6">
         <v>0</v>
@@ -2751,7 +2133,7 @@
         <v>45752</v>
       </c>
       <c r="E15" s="20">
-        <v>0.583333333333333</v>
+        <v>0.58333333333333304</v>
       </c>
       <c r="F15" s="20">
         <v>0.625</v>
@@ -2774,7 +2156,7 @@
         <v>45753</v>
       </c>
       <c r="E16" s="20">
-        <v>0.541666666666667</v>
+        <v>0.54166666666666696</v>
       </c>
       <c r="F16" s="6"/>
       <c r="G16" s="6">
@@ -2798,7 +2180,7 @@
         <v>0.8125</v>
       </c>
       <c r="F17" s="22">
-        <v>0.854166666666667</v>
+        <v>0.85416666666666696</v>
       </c>
       <c r="G17" s="12">
         <v>0</v>
@@ -2818,7 +2200,7 @@
         <v>45758</v>
       </c>
       <c r="E18" s="22">
-        <v>0.958333333333333</v>
+        <v>0.95833333333333304</v>
       </c>
       <c r="F18" s="22">
         <v>0</v>
@@ -2841,10 +2223,10 @@
         <v>45759</v>
       </c>
       <c r="E19" s="22">
-        <v>0.854166666666667</v>
+        <v>0.85416666666666696</v>
       </c>
       <c r="F19" s="22">
-        <v>0.895833333333333</v>
+        <v>0.89583333333333304</v>
       </c>
       <c r="G19" s="12">
         <v>0</v>
@@ -2867,7 +2249,7 @@
         <v>0</v>
       </c>
       <c r="F20" s="22">
-        <v>0.0416666666666667</v>
+        <v>4.1666666666666699E-2</v>
       </c>
       <c r="G20" s="12">
         <v>1</v>
@@ -2887,7 +2269,7 @@
         <v>45760</v>
       </c>
       <c r="E21" s="22">
-        <v>0.958333333333333</v>
+        <v>0.95833333333333304</v>
       </c>
       <c r="F21" s="12"/>
       <c r="G21" s="12">
@@ -2908,7 +2290,7 @@
         <v>45765</v>
       </c>
       <c r="E22" s="20">
-        <v>0.895833333333333</v>
+        <v>0.89583333333333304</v>
       </c>
       <c r="F22" s="20">
         <v>0.9375</v>
@@ -2931,10 +2313,10 @@
         <v>45766</v>
       </c>
       <c r="E23" s="20">
-        <v>0.0416666666666667</v>
+        <v>4.1666666666666699E-2</v>
       </c>
       <c r="F23" s="20">
-        <v>0.0833333333333333</v>
+        <v>8.3333333333333301E-2</v>
       </c>
       <c r="G23" s="6">
         <v>0</v>
@@ -2954,7 +2336,7 @@
         <v>45766</v>
       </c>
       <c r="E24" s="20">
-        <v>0.895833333333333</v>
+        <v>0.89583333333333304</v>
       </c>
       <c r="F24" s="20">
         <v>0.9375</v>
@@ -2977,10 +2359,10 @@
         <v>45767</v>
       </c>
       <c r="E25" s="20">
-        <v>0.0416666666666667</v>
+        <v>4.1666666666666699E-2</v>
       </c>
       <c r="F25" s="20">
-        <v>0.0833333333333333</v>
+        <v>8.3333333333333301E-2</v>
       </c>
       <c r="G25" s="6">
         <v>1</v>
@@ -3000,7 +2382,7 @@
         <v>45767</v>
       </c>
       <c r="E26" s="20">
-        <v>0.0416666666666667</v>
+        <v>4.1666666666666699E-2</v>
       </c>
       <c r="F26" s="6"/>
       <c r="G26" s="6">
@@ -3021,10 +2403,10 @@
         <v>45780</v>
       </c>
       <c r="E27" s="22">
-        <v>0.0208333333333333</v>
+        <v>2.0833333333333301E-2</v>
       </c>
       <c r="F27" s="22">
-        <v>0.0625</v>
+        <v>6.25E-2</v>
       </c>
       <c r="G27" s="12">
         <v>0</v>
@@ -3070,7 +2452,7 @@
         <v>0</v>
       </c>
       <c r="F29" s="22">
-        <v>0.0416666666666667</v>
+        <v>4.1666666666666699E-2</v>
       </c>
       <c r="G29" s="12">
         <v>1</v>
@@ -3090,10 +2472,10 @@
         <v>45781</v>
       </c>
       <c r="E30" s="22">
-        <v>0.166666666666667</v>
+        <v>0.16666666666666699</v>
       </c>
       <c r="F30" s="22">
-        <v>0.208333333333333</v>
+        <v>0.20833333333333301</v>
       </c>
       <c r="G30" s="12">
         <v>1</v>
@@ -3113,7 +2495,7 @@
         <v>45782</v>
       </c>
       <c r="E31" s="22">
-        <v>0.166666666666667</v>
+        <v>0.16666666666666699</v>
       </c>
       <c r="F31" s="22"/>
       <c r="G31" s="12">
@@ -3137,7 +2519,7 @@
         <v>0.8125</v>
       </c>
       <c r="F32" s="20">
-        <v>0.854166666666667</v>
+        <v>0.85416666666666696</v>
       </c>
       <c r="G32" s="6">
         <v>0</v>
@@ -3157,7 +2539,7 @@
         <v>45793</v>
       </c>
       <c r="E33" s="20">
-        <v>0.958333333333333</v>
+        <v>0.95833333333333304</v>
       </c>
       <c r="F33" s="20">
         <v>0</v>
@@ -3180,7 +2562,7 @@
         <v>45794</v>
       </c>
       <c r="E34" s="20">
-        <v>0.770833333333333</v>
+        <v>0.77083333333333304</v>
       </c>
       <c r="F34" s="20">
         <v>0.8125</v>
@@ -3203,10 +2585,10 @@
         <v>45794</v>
       </c>
       <c r="E35" s="20">
-        <v>0.916666666666667</v>
+        <v>0.91666666666666696</v>
       </c>
       <c r="F35" s="20">
-        <v>0.958333333333333</v>
+        <v>0.95833333333333304</v>
       </c>
       <c r="G35" s="6">
         <v>1</v>
@@ -3250,7 +2632,7 @@
         <v>0.8125</v>
       </c>
       <c r="F37" s="22">
-        <v>0.854166666666667</v>
+        <v>0.85416666666666696</v>
       </c>
       <c r="G37" s="12">
         <v>0</v>
@@ -3270,7 +2652,7 @@
         <v>45800</v>
       </c>
       <c r="E38" s="22">
-        <v>0.958333333333333</v>
+        <v>0.95833333333333304</v>
       </c>
       <c r="F38" s="22">
         <v>0</v>
@@ -3293,7 +2675,7 @@
         <v>45801</v>
       </c>
       <c r="E39" s="22">
-        <v>0.770833333333333</v>
+        <v>0.77083333333333304</v>
       </c>
       <c r="F39" s="22">
         <v>0.8125</v>
@@ -3316,10 +2698,10 @@
         <v>45801</v>
       </c>
       <c r="E40" s="22">
-        <v>0.916666666666667</v>
+        <v>0.91666666666666696</v>
       </c>
       <c r="F40" s="22">
-        <v>0.958333333333333</v>
+        <v>0.95833333333333304</v>
       </c>
       <c r="G40" s="12">
         <v>1</v>
@@ -3363,7 +2745,7 @@
         <v>0.8125</v>
       </c>
       <c r="F42" s="20">
-        <v>0.854166666666667</v>
+        <v>0.85416666666666696</v>
       </c>
       <c r="G42" s="6">
         <v>0</v>
@@ -3383,7 +2765,7 @@
         <v>45807</v>
       </c>
       <c r="E43" s="20">
-        <v>0.958333333333333</v>
+        <v>0.95833333333333304</v>
       </c>
       <c r="F43" s="20">
         <v>0</v>
@@ -3406,7 +2788,7 @@
         <v>45808</v>
       </c>
       <c r="E44" s="20">
-        <v>0.770833333333333</v>
+        <v>0.77083333333333304</v>
       </c>
       <c r="F44" s="20">
         <v>0.8125</v>
@@ -3429,10 +2811,10 @@
         <v>45808</v>
       </c>
       <c r="E45" s="20">
-        <v>0.916666666666667</v>
+        <v>0.91666666666666696</v>
       </c>
       <c r="F45" s="20">
-        <v>0.958333333333333</v>
+        <v>0.95833333333333304</v>
       </c>
       <c r="G45" s="6">
         <v>1</v>
@@ -3473,7 +2855,7 @@
         <v>45822</v>
       </c>
       <c r="E47" s="22">
-        <v>0.0625</v>
+        <v>6.25E-2</v>
       </c>
       <c r="F47" s="22">
         <v>0.104166666666667</v>
@@ -3496,7 +2878,7 @@
         <v>45822</v>
       </c>
       <c r="E48" s="22">
-        <v>0.208333333333333</v>
+        <v>0.20833333333333301</v>
       </c>
       <c r="F48" s="22">
         <v>0.25</v>
@@ -3519,10 +2901,10 @@
         <v>45823</v>
       </c>
       <c r="E49" s="22">
-        <v>0.0208333333333333</v>
+        <v>2.0833333333333301E-2</v>
       </c>
       <c r="F49" s="22">
-        <v>0.0625</v>
+        <v>6.25E-2</v>
       </c>
       <c r="G49" s="12">
         <v>0</v>
@@ -3542,10 +2924,10 @@
         <v>45823</v>
       </c>
       <c r="E50" s="22">
-        <v>0.166666666666667</v>
+        <v>0.16666666666666699</v>
       </c>
       <c r="F50" s="22">
-        <v>0.208333333333333</v>
+        <v>0.20833333333333301</v>
       </c>
       <c r="G50" s="12">
         <v>1</v>
@@ -3565,7 +2947,7 @@
         <v>45824</v>
       </c>
       <c r="E51" s="22">
-        <v>0.0833333333333333</v>
+        <v>8.3333333333333301E-2</v>
       </c>
       <c r="F51" s="12"/>
       <c r="G51" s="12">
@@ -3589,7 +2971,7 @@
         <v>0.8125</v>
       </c>
       <c r="F52" s="20">
-        <v>0.854166666666667</v>
+        <v>0.85416666666666696</v>
       </c>
       <c r="G52" s="6">
         <v>0</v>
@@ -3609,7 +2991,7 @@
         <v>45835</v>
       </c>
       <c r="E53" s="20">
-        <v>0.958333333333333</v>
+        <v>0.95833333333333304</v>
       </c>
       <c r="F53" s="20">
         <v>0</v>
@@ -3632,7 +3014,7 @@
         <v>45836</v>
       </c>
       <c r="E54" s="20">
-        <v>0.770833333333333</v>
+        <v>0.77083333333333304</v>
       </c>
       <c r="F54" s="20">
         <v>0.8125</v>
@@ -3655,10 +3037,10 @@
         <v>45836</v>
       </c>
       <c r="E55" s="20">
-        <v>0.916666666666667</v>
+        <v>0.91666666666666696</v>
       </c>
       <c r="F55" s="20">
-        <v>0.958333333333333</v>
+        <v>0.95833333333333304</v>
       </c>
       <c r="G55" s="6">
         <v>1</v>
@@ -3702,7 +3084,7 @@
         <v>0.8125</v>
       </c>
       <c r="F57" s="22">
-        <v>0.854166666666667</v>
+        <v>0.85416666666666696</v>
       </c>
       <c r="G57" s="12">
         <v>0</v>
@@ -3722,7 +3104,7 @@
         <v>45842</v>
       </c>
       <c r="E58" s="22">
-        <v>0.958333333333333</v>
+        <v>0.95833333333333304</v>
       </c>
       <c r="F58" s="22">
         <v>0</v>
@@ -3745,7 +3127,7 @@
         <v>45843</v>
       </c>
       <c r="E59" s="22">
-        <v>0.770833333333333</v>
+        <v>0.77083333333333304</v>
       </c>
       <c r="F59" s="22">
         <v>0.8125</v>
@@ -3768,10 +3150,10 @@
         <v>45843</v>
       </c>
       <c r="E60" s="22">
-        <v>0.916666666666667</v>
+        <v>0.91666666666666696</v>
       </c>
       <c r="F60" s="22">
-        <v>0.958333333333333</v>
+        <v>0.95833333333333304</v>
       </c>
       <c r="G60" s="12">
         <v>1</v>
@@ -3791,7 +3173,7 @@
         <v>45844</v>
       </c>
       <c r="E61" s="22">
-        <v>0.916666666666667</v>
+        <v>0.91666666666666696</v>
       </c>
       <c r="F61" s="12"/>
       <c r="G61" s="12">
@@ -3815,7 +3197,7 @@
         <v>0.8125</v>
       </c>
       <c r="F62" s="20">
-        <v>0.854166666666667</v>
+        <v>0.85416666666666696</v>
       </c>
       <c r="G62" s="6">
         <v>0</v>
@@ -3861,7 +3243,7 @@
         <v>0.75</v>
       </c>
       <c r="F64" s="20">
-        <v>0.791666666666667</v>
+        <v>0.79166666666666696</v>
       </c>
       <c r="G64" s="6">
         <v>1</v>
@@ -3881,10 +3263,10 @@
         <v>45864</v>
       </c>
       <c r="E65" s="20">
-        <v>0.916666666666667</v>
+        <v>0.91666666666666696</v>
       </c>
       <c r="F65" s="20">
-        <v>0.958333333333333</v>
+        <v>0.95833333333333304</v>
       </c>
       <c r="G65" s="6">
         <v>1</v>
@@ -3928,7 +3310,7 @@
         <v>0.8125</v>
       </c>
       <c r="F67" s="22">
-        <v>0.854166666666667</v>
+        <v>0.85416666666666696</v>
       </c>
       <c r="G67" s="12">
         <v>0</v>
@@ -3948,7 +3330,7 @@
         <v>45870</v>
       </c>
       <c r="E68" s="22">
-        <v>0.958333333333333</v>
+        <v>0.95833333333333304</v>
       </c>
       <c r="F68" s="22">
         <v>0</v>
@@ -3971,7 +3353,7 @@
         <v>45871</v>
       </c>
       <c r="E69" s="22">
-        <v>0.770833333333333</v>
+        <v>0.77083333333333304</v>
       </c>
       <c r="F69" s="22">
         <v>0.8125</v>
@@ -3994,10 +3376,10 @@
         <v>45871</v>
       </c>
       <c r="E70" s="22">
-        <v>0.916666666666667</v>
+        <v>0.91666666666666696</v>
       </c>
       <c r="F70" s="22">
-        <v>0.958333333333333</v>
+        <v>0.95833333333333304</v>
       </c>
       <c r="G70" s="12">
         <v>1</v>
@@ -4038,7 +3420,7 @@
         <v>45898</v>
       </c>
       <c r="E72" s="20">
-        <v>0.770833333333333</v>
+        <v>0.77083333333333304</v>
       </c>
       <c r="F72" s="20">
         <v>0.8125</v>
@@ -4061,10 +3443,10 @@
         <v>45898</v>
       </c>
       <c r="E73" s="20">
-        <v>0.916666666666667</v>
+        <v>0.91666666666666696</v>
       </c>
       <c r="F73" s="20">
-        <v>0.958333333333333</v>
+        <v>0.95833333333333304</v>
       </c>
       <c r="G73" s="6">
         <v>0</v>
@@ -4084,10 +3466,10 @@
         <v>45899</v>
       </c>
       <c r="E74" s="20">
-        <v>0.729166666666667</v>
+        <v>0.72916666666666696</v>
       </c>
       <c r="F74" s="20">
-        <v>0.770833333333333</v>
+        <v>0.77083333333333304</v>
       </c>
       <c r="G74" s="6">
         <v>0</v>
@@ -4110,7 +3492,7 @@
         <v>0.875</v>
       </c>
       <c r="F75" s="20">
-        <v>0.916666666666667</v>
+        <v>0.91666666666666696</v>
       </c>
       <c r="G75" s="6">
         <v>1</v>
@@ -4154,7 +3536,7 @@
         <v>0.8125</v>
       </c>
       <c r="F77" s="22">
-        <v>0.854166666666667</v>
+        <v>0.85416666666666696</v>
       </c>
       <c r="G77" s="12">
         <v>0</v>
@@ -4174,7 +3556,7 @@
         <v>45905</v>
       </c>
       <c r="E78" s="22">
-        <v>0.958333333333333</v>
+        <v>0.95833333333333304</v>
       </c>
       <c r="F78" s="22">
         <v>0</v>
@@ -4197,7 +3579,7 @@
         <v>45906</v>
       </c>
       <c r="E79" s="22">
-        <v>0.770833333333333</v>
+        <v>0.77083333333333304</v>
       </c>
       <c r="F79" s="22">
         <v>0.8125</v>
@@ -4220,10 +3602,10 @@
         <v>45906</v>
       </c>
       <c r="E80" s="22">
-        <v>0.916666666666667</v>
+        <v>0.91666666666666696</v>
       </c>
       <c r="F80" s="22">
-        <v>0.958333333333333</v>
+        <v>0.95833333333333304</v>
       </c>
       <c r="G80" s="12">
         <v>1</v>
@@ -4267,7 +3649,7 @@
         <v>0.6875</v>
       </c>
       <c r="F82" s="20">
-        <v>0.729166666666667</v>
+        <v>0.72916666666666696</v>
       </c>
       <c r="G82" s="6">
         <v>0</v>
@@ -4287,7 +3669,7 @@
         <v>45919</v>
       </c>
       <c r="E83" s="20">
-        <v>0.833333333333333</v>
+        <v>0.83333333333333304</v>
       </c>
       <c r="F83" s="20">
         <v>0.875</v>
@@ -4313,7 +3695,7 @@
         <v>0.6875</v>
       </c>
       <c r="F84" s="20">
-        <v>0.729166666666667</v>
+        <v>0.72916666666666696</v>
       </c>
       <c r="G84" s="6">
         <v>0</v>
@@ -4333,7 +3715,7 @@
         <v>45920</v>
       </c>
       <c r="E85" s="20">
-        <v>0.833333333333333</v>
+        <v>0.83333333333333304</v>
       </c>
       <c r="F85" s="20">
         <v>0.875</v>
@@ -4356,7 +3738,7 @@
         <v>45921</v>
       </c>
       <c r="E86" s="20">
-        <v>0.791666666666667</v>
+        <v>0.79166666666666696</v>
       </c>
       <c r="F86" s="6"/>
       <c r="G86" s="6">
@@ -4377,10 +3759,10 @@
         <v>45933</v>
       </c>
       <c r="E87" s="22">
-        <v>0.729166666666667</v>
+        <v>0.72916666666666696</v>
       </c>
       <c r="F87" s="22">
-        <v>0.770833333333333</v>
+        <v>0.77083333333333304</v>
       </c>
       <c r="G87" s="12">
         <v>0</v>
@@ -4403,7 +3785,7 @@
         <v>0.875</v>
       </c>
       <c r="F88" s="22">
-        <v>0.916666666666667</v>
+        <v>0.91666666666666696</v>
       </c>
       <c r="G88" s="12">
         <v>0</v>
@@ -4423,10 +3805,10 @@
         <v>45934</v>
       </c>
       <c r="E89" s="22">
-        <v>0.729166666666667</v>
+        <v>0.72916666666666696</v>
       </c>
       <c r="F89" s="22">
-        <v>0.770833333333333</v>
+        <v>0.77083333333333304</v>
       </c>
       <c r="G89" s="12">
         <v>0</v>
@@ -4449,7 +3831,7 @@
         <v>0.875</v>
       </c>
       <c r="F90" s="22">
-        <v>0.916666666666667</v>
+        <v>0.91666666666666696</v>
       </c>
       <c r="G90" s="12">
         <v>1</v>
@@ -4469,7 +3851,7 @@
         <v>45935</v>
       </c>
       <c r="E91" s="22">
-        <v>0.833333333333333</v>
+        <v>0.83333333333333304</v>
       </c>
       <c r="F91" s="12"/>
       <c r="G91" s="12">
@@ -4490,7 +3872,7 @@
         <v>45948</v>
       </c>
       <c r="E92" s="20">
-        <v>0.0625</v>
+        <v>6.25E-2</v>
       </c>
       <c r="F92" s="20">
         <v>0.104166666666667</v>
@@ -4513,10 +3895,10 @@
         <v>45948</v>
       </c>
       <c r="E93" s="20">
-        <v>0.229166666666667</v>
+        <v>0.22916666666666699</v>
       </c>
       <c r="F93" s="20">
-        <v>0.259722222222222</v>
+        <v>0.25972222222222202</v>
       </c>
       <c r="G93" s="6">
         <v>1</v>
@@ -4536,10 +3918,10 @@
         <v>45949</v>
       </c>
       <c r="E94" s="20">
-        <v>0.0416666666666667</v>
+        <v>4.1666666666666699E-2</v>
       </c>
       <c r="F94" s="20">
-        <v>0.0625</v>
+        <v>6.25E-2</v>
       </c>
       <c r="G94" s="6">
         <v>1</v>
@@ -4559,7 +3941,7 @@
         <v>45949</v>
       </c>
       <c r="E95" s="20">
-        <v>0.208333333333333</v>
+        <v>0.20833333333333301</v>
       </c>
       <c r="F95" s="20">
         <v>0.25</v>
@@ -4606,7 +3988,7 @@
         <v>0.104166666666667</v>
       </c>
       <c r="F97" s="22">
-        <v>0.145833333333333</v>
+        <v>0.14583333333333301</v>
       </c>
       <c r="G97" s="12">
         <v>0</v>
@@ -4629,7 +4011,7 @@
         <v>0.25</v>
       </c>
       <c r="F98" s="22">
-        <v>0.291666666666667</v>
+        <v>0.29166666666666702</v>
       </c>
       <c r="G98" s="12">
         <v>0</v>
@@ -4649,7 +4031,7 @@
         <v>45956</v>
       </c>
       <c r="E99" s="22">
-        <v>0.0625</v>
+        <v>6.25E-2</v>
       </c>
       <c r="F99" s="22">
         <v>0.104166666666667</v>
@@ -4672,7 +4054,7 @@
         <v>45956</v>
       </c>
       <c r="E100" s="22">
-        <v>0.208333333333333</v>
+        <v>0.20833333333333301</v>
       </c>
       <c r="F100" s="22">
         <v>0.25</v>
@@ -4695,7 +4077,7 @@
         <v>45957</v>
       </c>
       <c r="E101" s="22">
-        <v>0.166666666666667</v>
+        <v>0.16666666666666699</v>
       </c>
       <c r="F101" s="12"/>
       <c r="G101" s="12">
@@ -4719,7 +4101,7 @@
         <v>0.9375</v>
       </c>
       <c r="F102" s="20">
-        <v>0.979166666666667</v>
+        <v>0.97916666666666696</v>
       </c>
       <c r="G102" s="6">
         <v>0</v>
@@ -4742,7 +4124,7 @@
         <v>0.104166666666667</v>
       </c>
       <c r="F103" s="20">
-        <v>0.134722222222222</v>
+        <v>0.13472222222222199</v>
       </c>
       <c r="G103" s="6">
         <v>1</v>
@@ -4762,10 +4144,10 @@
         <v>45969</v>
       </c>
       <c r="E104" s="20">
-        <v>0.916666666666667</v>
+        <v>0.91666666666666696</v>
       </c>
       <c r="F104" s="20">
-        <v>0.958333333333333</v>
+        <v>0.95833333333333304</v>
       </c>
       <c r="G104" s="6">
         <v>1</v>
@@ -4785,7 +4167,7 @@
         <v>45970</v>
       </c>
       <c r="E105" s="20">
-        <v>0.0833333333333333</v>
+        <v>8.3333333333333301E-2</v>
       </c>
       <c r="F105" s="20">
         <v>0.125</v>
@@ -4808,7 +4190,7 @@
         <v>45971</v>
       </c>
       <c r="E106" s="20">
-        <v>0.0416666666666667</v>
+        <v>4.1666666666666699E-2</v>
       </c>
       <c r="F106" s="6"/>
       <c r="G106" s="6">
@@ -4829,10 +4211,10 @@
         <v>45982</v>
       </c>
       <c r="E107" s="22">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="F107" s="22">
-        <v>0.395833333333333</v>
+        <v>0.39583333333333298</v>
       </c>
       <c r="G107" s="12">
         <v>0</v>
@@ -4855,7 +4237,7 @@
         <v>0.5</v>
       </c>
       <c r="F108" s="22">
-        <v>0.541666666666667</v>
+        <v>0.54166666666666696</v>
       </c>
       <c r="G108" s="12">
         <v>0</v>
@@ -4875,10 +4257,10 @@
         <v>45983</v>
       </c>
       <c r="E109" s="23">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="F109" s="23">
-        <v>0.395833333333333</v>
+        <v>0.39583333333333298</v>
       </c>
       <c r="G109" s="12">
         <v>0</v>
@@ -4901,7 +4283,7 @@
         <v>0.5</v>
       </c>
       <c r="F110" s="23">
-        <v>0.541666666666667</v>
+        <v>0.54166666666666696</v>
       </c>
       <c r="G110" s="12">
         <v>1</v>
@@ -4942,7 +4324,7 @@
         <v>45989</v>
       </c>
       <c r="E112" s="24">
-        <v>0.895833333333333</v>
+        <v>0.89583333333333304</v>
       </c>
       <c r="F112" s="24">
         <v>0.9375</v>
@@ -4965,10 +4347,10 @@
         <v>45990</v>
       </c>
       <c r="E113" s="24">
-        <v>0.0625</v>
+        <v>6.25E-2</v>
       </c>
       <c r="F113" s="24">
-        <v>0.0930555555555556</v>
+        <v>9.30555555555556E-2</v>
       </c>
       <c r="G113" s="6">
         <v>1</v>
@@ -4988,10 +4370,10 @@
         <v>45990</v>
       </c>
       <c r="E114" s="24">
-        <v>0.916666666666667</v>
+        <v>0.91666666666666696</v>
       </c>
       <c r="F114" s="24">
-        <v>0.958333333333333</v>
+        <v>0.95833333333333304</v>
       </c>
       <c r="G114" s="6">
         <v>1</v>
@@ -5011,7 +4393,7 @@
         <v>45991</v>
       </c>
       <c r="E115" s="24">
-        <v>0.0833333333333333</v>
+        <v>8.3333333333333301E-2</v>
       </c>
       <c r="F115" s="24">
         <v>0.125</v>
@@ -5055,10 +4437,10 @@
         <v>45996</v>
       </c>
       <c r="E117" s="23">
-        <v>0.729166666666667</v>
+        <v>0.72916666666666696</v>
       </c>
       <c r="F117" s="23">
-        <v>0.770833333333333</v>
+        <v>0.77083333333333304</v>
       </c>
       <c r="G117" s="12">
         <v>0</v>
@@ -5081,7 +4463,7 @@
         <v>0.875</v>
       </c>
       <c r="F118" s="23">
-        <v>0.916666666666667</v>
+        <v>0.91666666666666696</v>
       </c>
       <c r="G118" s="12">
         <v>0</v>
@@ -5101,7 +4483,7 @@
         <v>45997</v>
       </c>
       <c r="E119" s="23">
-        <v>0.770833333333333</v>
+        <v>0.77083333333333304</v>
       </c>
       <c r="F119" s="23">
         <v>0.8125</v>
@@ -5124,10 +4506,10 @@
         <v>45997</v>
       </c>
       <c r="E120" s="23">
-        <v>0.916666666666667</v>
+        <v>0.91666666666666696</v>
       </c>
       <c r="F120" s="23">
-        <v>0.958333333333333</v>
+        <v>0.95833333333333304</v>
       </c>
       <c r="G120" s="12">
         <v>1</v>
@@ -5168,7 +4550,7 @@
         <v>46087</v>
       </c>
       <c r="E122" s="20">
-        <v>0.395833333333333</v>
+        <v>0.39583333333333298</v>
       </c>
       <c r="F122" s="20">
         <v>0.4375</v>
@@ -5191,10 +4573,10 @@
         <v>46087</v>
       </c>
       <c r="E123" s="20">
-        <v>0.541666666666667</v>
+        <v>0.54166666666666696</v>
       </c>
       <c r="F123" s="20">
-        <v>0.583333333333333</v>
+        <v>0.58333333333333304</v>
       </c>
       <c r="G123" s="6">
         <v>0</v>
@@ -5214,7 +4596,7 @@
         <v>46088</v>
       </c>
       <c r="E124" s="20">
-        <v>0.395833333333333</v>
+        <v>0.39583333333333298</v>
       </c>
       <c r="F124" s="20">
         <v>0.4375</v>
@@ -5237,10 +4619,10 @@
         <v>46088</v>
       </c>
       <c r="E125" s="20">
-        <v>0.541666666666667</v>
+        <v>0.54166666666666696</v>
       </c>
       <c r="F125" s="20">
-        <v>0.583333333333333</v>
+        <v>0.58333333333333304</v>
       </c>
       <c r="G125" s="6">
         <v>1</v>
@@ -5281,10 +4663,10 @@
         <v>45729</v>
       </c>
       <c r="E127" s="22">
-        <v>0.479166666666667</v>
+        <v>0.47916666666666702</v>
       </c>
       <c r="F127" s="22">
-        <v>0.520833333333333</v>
+        <v>0.52083333333333304</v>
       </c>
       <c r="G127" s="12">
         <v>0</v>
@@ -5304,10 +4686,10 @@
         <v>45729</v>
       </c>
       <c r="E128" s="22">
-        <v>0.645833333333333</v>
+        <v>0.64583333333333304</v>
       </c>
       <c r="F128" s="22">
-        <v>0.676388888888889</v>
+        <v>0.67638888888888904</v>
       </c>
       <c r="G128" s="12">
         <v>1</v>
@@ -5327,7 +4709,7 @@
         <v>45730</v>
       </c>
       <c r="E129" s="22">
-        <v>0.458333333333333</v>
+        <v>0.45833333333333298</v>
       </c>
       <c r="F129" s="22">
         <v>0.5</v>
@@ -5353,7 +4735,7 @@
         <v>0.625</v>
       </c>
       <c r="F130" s="22">
-        <v>0.666666666666667</v>
+        <v>0.66666666666666696</v>
       </c>
       <c r="G130" s="12">
         <v>1</v>
@@ -5397,7 +4779,7 @@
         <v>0.4375</v>
       </c>
       <c r="F132" s="20">
-        <v>0.479166666666667</v>
+        <v>0.47916666666666702</v>
       </c>
       <c r="G132" s="6">
         <v>0</v>
@@ -5417,7 +4799,7 @@
         <v>45743</v>
       </c>
       <c r="E133" s="20">
-        <v>0.583333333333333</v>
+        <v>0.58333333333333304</v>
       </c>
       <c r="F133" s="20">
         <v>0.625</v>
@@ -5443,7 +4825,7 @@
         <v>0.4375</v>
       </c>
       <c r="F134" s="20">
-        <v>0.479166666666667</v>
+        <v>0.47916666666666702</v>
       </c>
       <c r="G134" s="6">
         <v>0</v>
@@ -5463,7 +4845,7 @@
         <v>45744</v>
       </c>
       <c r="E135" s="20">
-        <v>0.583333333333333</v>
+        <v>0.58333333333333304</v>
       </c>
       <c r="F135" s="20">
         <v>0.625</v>
@@ -5486,7 +4868,7 @@
         <v>45745</v>
       </c>
       <c r="E136" s="20">
-        <v>0.541666666666667</v>
+        <v>0.54166666666666696</v>
       </c>
       <c r="F136" s="6"/>
       <c r="G136" s="6">
@@ -5510,7 +4892,7 @@
         <v>0.8125</v>
       </c>
       <c r="F137" s="22">
-        <v>0.854166666666667</v>
+        <v>0.85416666666666696</v>
       </c>
       <c r="G137" s="12">
         <v>0</v>
@@ -5530,7 +4912,7 @@
         <v>45757</v>
       </c>
       <c r="E138" s="22">
-        <v>0.958333333333333</v>
+        <v>0.95833333333333304</v>
       </c>
       <c r="F138" s="22">
         <v>0</v>
@@ -5553,10 +4935,10 @@
         <v>45758</v>
       </c>
       <c r="E139" s="22">
-        <v>0.854166666666667</v>
+        <v>0.85416666666666696</v>
       </c>
       <c r="F139" s="22">
-        <v>0.895833333333333</v>
+        <v>0.89583333333333304</v>
       </c>
       <c r="G139" s="12">
         <v>0</v>
@@ -5579,7 +4961,7 @@
         <v>0</v>
       </c>
       <c r="F140" s="22">
-        <v>0.0416666666666667</v>
+        <v>4.1666666666666699E-2</v>
       </c>
       <c r="G140" s="12">
         <v>1</v>
@@ -5599,7 +4981,7 @@
         <v>45759</v>
       </c>
       <c r="E141" s="22">
-        <v>0.958333333333333</v>
+        <v>0.95833333333333304</v>
       </c>
       <c r="F141" s="12"/>
       <c r="G141" s="12">
@@ -5620,7 +5002,7 @@
         <v>45764</v>
       </c>
       <c r="E142" s="20">
-        <v>0.895833333333333</v>
+        <v>0.89583333333333304</v>
       </c>
       <c r="F142" s="20">
         <v>0.9375</v>
@@ -5643,10 +5025,10 @@
         <v>45765</v>
       </c>
       <c r="E143" s="20">
-        <v>0.0416666666666667</v>
+        <v>4.1666666666666699E-2</v>
       </c>
       <c r="F143" s="20">
-        <v>0.0833333333333333</v>
+        <v>8.3333333333333301E-2</v>
       </c>
       <c r="G143" s="6">
         <v>0</v>
@@ -5666,7 +5048,7 @@
         <v>45765</v>
       </c>
       <c r="E144" s="20">
-        <v>0.895833333333333</v>
+        <v>0.89583333333333304</v>
       </c>
       <c r="F144" s="20">
         <v>0.9375</v>
@@ -5689,10 +5071,10 @@
         <v>45766</v>
       </c>
       <c r="E145" s="20">
-        <v>0.0416666666666667</v>
+        <v>4.1666666666666699E-2</v>
       </c>
       <c r="F145" s="20">
-        <v>0.0833333333333333</v>
+        <v>8.3333333333333301E-2</v>
       </c>
       <c r="G145" s="6">
         <v>1</v>
@@ -5712,7 +5094,7 @@
         <v>45767</v>
       </c>
       <c r="E146" s="20">
-        <v>0.0416666666666667</v>
+        <v>4.1666666666666699E-2</v>
       </c>
       <c r="F146" s="6"/>
       <c r="G146" s="6">
@@ -5733,10 +5115,10 @@
         <v>45779</v>
       </c>
       <c r="E147" s="22">
-        <v>0.0208333333333333</v>
+        <v>2.0833333333333301E-2</v>
       </c>
       <c r="F147" s="22">
-        <v>0.0625</v>
+        <v>6.25E-2</v>
       </c>
       <c r="G147" s="12">
         <v>0</v>
@@ -5782,7 +5164,7 @@
         <v>0</v>
       </c>
       <c r="F149" s="22">
-        <v>0.0416666666666667</v>
+        <v>4.1666666666666699E-2</v>
       </c>
       <c r="G149" s="12">
         <v>1</v>
@@ -5802,10 +5184,10 @@
         <v>45780</v>
       </c>
       <c r="E150" s="22">
-        <v>0.166666666666667</v>
+        <v>0.16666666666666699</v>
       </c>
       <c r="F150" s="22">
-        <v>0.208333333333333</v>
+        <v>0.20833333333333301</v>
       </c>
       <c r="G150" s="12">
         <v>1</v>
@@ -5825,7 +5207,7 @@
         <v>45781</v>
       </c>
       <c r="E151" s="22">
-        <v>0.166666666666667</v>
+        <v>0.16666666666666699</v>
       </c>
       <c r="F151" s="22"/>
       <c r="G151" s="12">
@@ -5846,10 +5228,10 @@
         <v>45800</v>
       </c>
       <c r="E152" s="20">
-        <v>0.0208333333333333</v>
+        <v>2.0833333333333301E-2</v>
       </c>
       <c r="F152" s="20">
-        <v>0.0625</v>
+        <v>6.25E-2</v>
       </c>
       <c r="G152" s="6">
         <v>0</v>
@@ -5895,7 +5277,7 @@
         <v>0</v>
       </c>
       <c r="F154" s="20">
-        <v>0.0416666666666667</v>
+        <v>4.1666666666666699E-2</v>
       </c>
       <c r="G154" s="6">
         <v>1</v>
@@ -5915,10 +5297,10 @@
         <v>45801</v>
       </c>
       <c r="E155" s="20">
-        <v>0.166666666666667</v>
+        <v>0.16666666666666699</v>
       </c>
       <c r="F155" s="20">
-        <v>0.208333333333333</v>
+        <v>0.20833333333333301</v>
       </c>
       <c r="G155" s="6">
         <v>1</v>
@@ -5938,7 +5320,7 @@
         <v>45802</v>
       </c>
       <c r="E156" s="20">
-        <v>0.166666666666667</v>
+        <v>0.16666666666666699</v>
       </c>
       <c r="F156" s="6"/>
       <c r="G156" s="6">
@@ -5962,7 +5344,7 @@
         <v>0.8125</v>
       </c>
       <c r="F157" s="22">
-        <v>0.854166666666667</v>
+        <v>0.85416666666666696</v>
       </c>
       <c r="G157" s="12">
         <v>0</v>
@@ -5982,7 +5364,7 @@
         <v>45813</v>
       </c>
       <c r="E158" s="22">
-        <v>0.958333333333333</v>
+        <v>0.95833333333333304</v>
       </c>
       <c r="F158" s="22">
         <v>0</v>
@@ -6005,7 +5387,7 @@
         <v>45814</v>
       </c>
       <c r="E159" s="22">
-        <v>0.770833333333333</v>
+        <v>0.77083333333333304</v>
       </c>
       <c r="F159" s="22">
         <v>0.8125</v>
@@ -6028,10 +5410,10 @@
         <v>45814</v>
       </c>
       <c r="E160" s="22">
-        <v>0.916666666666667</v>
+        <v>0.91666666666666696</v>
       </c>
       <c r="F160" s="22">
-        <v>0.958333333333333</v>
+        <v>0.95833333333333304</v>
       </c>
       <c r="G160" s="12">
         <v>1</v>
@@ -6075,7 +5457,7 @@
         <v>0.8125</v>
       </c>
       <c r="F162" s="20">
-        <v>0.854166666666667</v>
+        <v>0.85416666666666696</v>
       </c>
       <c r="G162" s="6">
         <v>0</v>
@@ -6095,7 +5477,7 @@
         <v>45820</v>
       </c>
       <c r="E163" s="20">
-        <v>0.958333333333333</v>
+        <v>0.95833333333333304</v>
       </c>
       <c r="F163" s="20">
         <v>0</v>
@@ -6118,7 +5500,7 @@
         <v>45821</v>
       </c>
       <c r="E164" s="20">
-        <v>0.770833333333333</v>
+        <v>0.77083333333333304</v>
       </c>
       <c r="F164" s="20">
         <v>0.8125</v>
@@ -6141,10 +5523,10 @@
         <v>45821</v>
       </c>
       <c r="E165" s="20">
-        <v>0.916666666666667</v>
+        <v>0.91666666666666696</v>
       </c>
       <c r="F165" s="20">
-        <v>0.958333333333333</v>
+        <v>0.95833333333333304</v>
       </c>
       <c r="G165" s="6">
         <v>1</v>
@@ -6188,7 +5570,7 @@
         <v>0.8125</v>
       </c>
       <c r="F167" s="22">
-        <v>0.854166666666667</v>
+        <v>0.85416666666666696</v>
       </c>
       <c r="G167" s="12">
         <v>0</v>
@@ -6208,7 +5590,7 @@
         <v>45834</v>
       </c>
       <c r="E168" s="22">
-        <v>0.958333333333333</v>
+        <v>0.95833333333333304</v>
       </c>
       <c r="F168" s="22">
         <v>0</v>
@@ -6231,7 +5613,7 @@
         <v>45835</v>
       </c>
       <c r="E169" s="22">
-        <v>0.770833333333333</v>
+        <v>0.77083333333333304</v>
       </c>
       <c r="F169" s="22">
         <v>0.8125</v>
@@ -6254,10 +5636,10 @@
         <v>45835</v>
       </c>
       <c r="E170" s="22">
-        <v>0.916666666666667</v>
+        <v>0.91666666666666696</v>
       </c>
       <c r="F170" s="22">
-        <v>0.958333333333333</v>
+        <v>0.95833333333333304</v>
       </c>
       <c r="G170" s="12">
         <v>1</v>
@@ -6301,7 +5683,7 @@
         <v>0.8125</v>
       </c>
       <c r="F172" s="20">
-        <v>0.854166666666667</v>
+        <v>0.85416666666666696</v>
       </c>
       <c r="G172" s="6">
         <v>0</v>
@@ -6321,10 +5703,10 @@
         <v>45841</v>
       </c>
       <c r="E173" s="20">
-        <v>0.979166666666667</v>
+        <v>0.97916666666666696</v>
       </c>
       <c r="F173" s="20">
-        <v>0.00972222222222222</v>
+        <v>9.7222222222222206E-3</v>
       </c>
       <c r="G173" s="6">
         <v>1</v>
@@ -6344,10 +5726,10 @@
         <v>45842</v>
       </c>
       <c r="E174" s="20">
-        <v>0.791666666666667</v>
+        <v>0.79166666666666696</v>
       </c>
       <c r="F174" s="20">
-        <v>0.833333333333333</v>
+        <v>0.83333333333333304</v>
       </c>
       <c r="G174" s="6">
         <v>1</v>
@@ -6367,7 +5749,7 @@
         <v>45842</v>
       </c>
       <c r="E175" s="20">
-        <v>0.958333333333333</v>
+        <v>0.95833333333333304</v>
       </c>
       <c r="F175" s="20">
         <v>0</v>
@@ -6390,7 +5772,7 @@
         <v>45843</v>
       </c>
       <c r="E176" s="20">
-        <v>0.916666666666667</v>
+        <v>0.91666666666666696</v>
       </c>
       <c r="F176" s="6"/>
       <c r="G176" s="6">
@@ -6414,7 +5796,7 @@
         <v>0.8125</v>
       </c>
       <c r="F177" s="22">
-        <v>0.854166666666667</v>
+        <v>0.85416666666666696</v>
       </c>
       <c r="G177" s="12">
         <v>0</v>
@@ -6434,7 +5816,7 @@
         <v>45855</v>
       </c>
       <c r="E178" s="22">
-        <v>0.958333333333333</v>
+        <v>0.95833333333333304</v>
       </c>
       <c r="F178" s="22">
         <v>0</v>
@@ -6457,7 +5839,7 @@
         <v>45856</v>
       </c>
       <c r="E179" s="22">
-        <v>0.770833333333333</v>
+        <v>0.77083333333333304</v>
       </c>
       <c r="F179" s="22">
         <v>0.8125</v>
@@ -6480,10 +5862,10 @@
         <v>45856</v>
       </c>
       <c r="E180" s="22">
-        <v>0.916666666666667</v>
+        <v>0.91666666666666696</v>
       </c>
       <c r="F180" s="22">
-        <v>0.958333333333333</v>
+        <v>0.95833333333333304</v>
       </c>
       <c r="G180" s="12">
         <v>1</v>
@@ -6527,7 +5909,7 @@
         <v>0.8125</v>
       </c>
       <c r="F182" s="20">
-        <v>0.854166666666667</v>
+        <v>0.85416666666666696</v>
       </c>
       <c r="G182" s="6">
         <v>0</v>
@@ -6573,7 +5955,7 @@
         <v>0.75</v>
       </c>
       <c r="F184" s="20">
-        <v>0.791666666666667</v>
+        <v>0.79166666666666696</v>
       </c>
       <c r="G184" s="6">
         <v>0</v>
@@ -6593,10 +5975,10 @@
         <v>45863</v>
       </c>
       <c r="E185" s="20">
-        <v>0.916666666666667</v>
+        <v>0.91666666666666696</v>
       </c>
       <c r="F185" s="20">
-        <v>0.958333333333333</v>
+        <v>0.95833333333333304</v>
       </c>
       <c r="G185" s="6">
         <v>1</v>
@@ -6637,7 +6019,7 @@
         <v>45890</v>
       </c>
       <c r="E187" s="22">
-        <v>0.770833333333333</v>
+        <v>0.77083333333333304</v>
       </c>
       <c r="F187" s="22">
         <v>0.8125</v>
@@ -6663,7 +6045,7 @@
         <v>0.9375</v>
       </c>
       <c r="F188" s="22">
-        <v>0.979166666666667</v>
+        <v>0.97916666666666696</v>
       </c>
       <c r="G188" s="12">
         <v>1</v>
@@ -6686,7 +6068,7 @@
         <v>0.75</v>
       </c>
       <c r="F189" s="22">
-        <v>0.791666666666667</v>
+        <v>0.79166666666666696</v>
       </c>
       <c r="G189" s="12">
         <v>1</v>
@@ -6706,10 +6088,10 @@
         <v>45891</v>
       </c>
       <c r="E190" s="22">
-        <v>0.916666666666667</v>
+        <v>0.91666666666666696</v>
       </c>
       <c r="F190" s="22">
-        <v>0.958333333333333</v>
+        <v>0.95833333333333304</v>
       </c>
       <c r="G190" s="12">
         <v>1</v>
@@ -6750,7 +6132,7 @@
         <v>45904</v>
       </c>
       <c r="E192" s="20">
-        <v>0.770833333333333</v>
+        <v>0.77083333333333304</v>
       </c>
       <c r="F192" s="20">
         <v>0.8125</v>
@@ -6773,10 +6155,10 @@
         <v>45904</v>
       </c>
       <c r="E193" s="20">
-        <v>0.916666666666667</v>
+        <v>0.91666666666666696</v>
       </c>
       <c r="F193" s="20">
-        <v>0.958333333333333</v>
+        <v>0.95833333333333304</v>
       </c>
       <c r="G193" s="6">
         <v>0</v>
@@ -6796,7 +6178,7 @@
         <v>45905</v>
       </c>
       <c r="E194" s="20">
-        <v>0.770833333333333</v>
+        <v>0.77083333333333304</v>
       </c>
       <c r="F194" s="20">
         <v>0.8125</v>
@@ -6819,10 +6201,10 @@
         <v>45905</v>
       </c>
       <c r="E195" s="20">
-        <v>0.916666666666667</v>
+        <v>0.91666666666666696</v>
       </c>
       <c r="F195" s="20">
-        <v>0.958333333333333</v>
+        <v>0.95833333333333304</v>
       </c>
       <c r="G195" s="6">
         <v>1</v>
@@ -6866,7 +6248,7 @@
         <v>0.8125</v>
       </c>
       <c r="F197" s="22">
-        <v>0.854166666666667</v>
+        <v>0.85416666666666696</v>
       </c>
       <c r="G197" s="12">
         <v>0</v>
@@ -6886,7 +6268,7 @@
         <v>45911</v>
       </c>
       <c r="E198" s="22">
-        <v>0.958333333333333</v>
+        <v>0.95833333333333304</v>
       </c>
       <c r="F198" s="22">
         <v>0</v>
@@ -6909,7 +6291,7 @@
         <v>45912</v>
       </c>
       <c r="E199" s="22">
-        <v>0.770833333333333</v>
+        <v>0.77083333333333304</v>
       </c>
       <c r="F199" s="22">
         <v>0.8125</v>
@@ -6932,10 +6314,10 @@
         <v>45912</v>
       </c>
       <c r="E200" s="22">
-        <v>0.916666666666667</v>
+        <v>0.91666666666666696</v>
       </c>
       <c r="F200" s="22">
-        <v>0.958333333333333</v>
+        <v>0.95833333333333304</v>
       </c>
       <c r="G200" s="12">
         <v>1</v>
@@ -6979,7 +6361,7 @@
         <v>0.6875</v>
       </c>
       <c r="F202" s="20">
-        <v>0.729166666666667</v>
+        <v>0.72916666666666696</v>
       </c>
       <c r="G202" s="6">
         <v>0</v>
@@ -6999,7 +6381,7 @@
         <v>45924</v>
       </c>
       <c r="E203" s="20">
-        <v>0.833333333333333</v>
+        <v>0.83333333333333304</v>
       </c>
       <c r="F203" s="20">
         <v>0.875</v>
@@ -7025,7 +6407,7 @@
         <v>0.6875</v>
       </c>
       <c r="F204" s="20">
-        <v>0.729166666666667</v>
+        <v>0.72916666666666696</v>
       </c>
       <c r="G204" s="6">
         <v>0</v>
@@ -7045,7 +6427,7 @@
         <v>45925</v>
       </c>
       <c r="E205" s="20">
-        <v>0.833333333333333</v>
+        <v>0.83333333333333304</v>
       </c>
       <c r="F205" s="20">
         <v>0.875</v>
@@ -7068,7 +6450,7 @@
         <v>45926</v>
       </c>
       <c r="E206" s="20">
-        <v>0.791666666666667</v>
+        <v>0.79166666666666696</v>
       </c>
       <c r="F206" s="6"/>
       <c r="G206" s="6">
@@ -7092,7 +6474,7 @@
         <v>0.6875</v>
       </c>
       <c r="F207" s="22">
-        <v>0.729166666666667</v>
+        <v>0.72916666666666696</v>
       </c>
       <c r="G207" s="12">
         <v>0</v>
@@ -7112,10 +6494,10 @@
         <v>45939</v>
       </c>
       <c r="E208" s="22">
-        <v>0.854166666666667</v>
+        <v>0.85416666666666696</v>
       </c>
       <c r="F208" s="22">
-        <v>0.884722222222222</v>
+        <v>0.88472222222222197</v>
       </c>
       <c r="G208" s="12">
         <v>1</v>
@@ -7135,7 +6517,7 @@
         <v>45940</v>
       </c>
       <c r="E209" s="22">
-        <v>0.708333333333333</v>
+        <v>0.70833333333333304</v>
       </c>
       <c r="F209" s="22">
         <v>0.75</v>
@@ -7161,7 +6543,7 @@
         <v>0.875</v>
       </c>
       <c r="F210" s="22">
-        <v>0.916666666666667</v>
+        <v>0.91666666666666696</v>
       </c>
       <c r="G210" s="12">
         <v>1</v>
@@ -7181,7 +6563,7 @@
         <v>45941</v>
       </c>
       <c r="E211" s="22">
-        <v>0.833333333333333</v>
+        <v>0.83333333333333304</v>
       </c>
       <c r="F211" s="12"/>
       <c r="G211" s="12">
@@ -7202,7 +6584,7 @@
         <v>45954</v>
       </c>
       <c r="E212" s="20">
-        <v>0.0625</v>
+        <v>6.25E-2</v>
       </c>
       <c r="F212" s="20">
         <v>0.104166666666667</v>
@@ -7225,7 +6607,7 @@
         <v>45954</v>
       </c>
       <c r="E213" s="20">
-        <v>0.208333333333333</v>
+        <v>0.20833333333333301</v>
       </c>
       <c r="F213" s="20">
         <v>0.25</v>
@@ -7248,7 +6630,7 @@
         <v>45955</v>
       </c>
       <c r="E214" s="20">
-        <v>0.0625</v>
+        <v>6.25E-2</v>
       </c>
       <c r="F214" s="20">
         <v>0.104166666666667</v>
@@ -7271,7 +6653,7 @@
         <v>45955</v>
       </c>
       <c r="E215" s="20">
-        <v>0.208333333333333</v>
+        <v>0.20833333333333301</v>
       </c>
       <c r="F215" s="20">
         <v>0.25</v>
@@ -7294,7 +6676,7 @@
         <v>45956</v>
       </c>
       <c r="E216" s="20">
-        <v>0.166666666666667</v>
+        <v>0.16666666666666699</v>
       </c>
       <c r="F216" s="6"/>
       <c r="G216" s="6">
@@ -7318,7 +6700,7 @@
         <v>0.104166666666667</v>
       </c>
       <c r="F217" s="22">
-        <v>0.145833333333333</v>
+        <v>0.14583333333333301</v>
       </c>
       <c r="G217" s="12">
         <v>0</v>
@@ -7341,7 +6723,7 @@
         <v>0.25</v>
       </c>
       <c r="F218" s="22">
-        <v>0.291666666666667</v>
+        <v>0.29166666666666702</v>
       </c>
       <c r="G218" s="12">
         <v>0</v>
@@ -7361,7 +6743,7 @@
         <v>45962</v>
       </c>
       <c r="E219" s="22">
-        <v>0.0625</v>
+        <v>6.25E-2</v>
       </c>
       <c r="F219" s="22">
         <v>0.104166666666667</v>
@@ -7384,7 +6766,7 @@
         <v>45962</v>
       </c>
       <c r="E220" s="22">
-        <v>0.208333333333333</v>
+        <v>0.20833333333333301</v>
       </c>
       <c r="F220" s="22">
         <v>0.25</v>
@@ -7407,7 +6789,7 @@
         <v>45963</v>
       </c>
       <c r="E221" s="22">
-        <v>0.166666666666667</v>
+        <v>0.16666666666666699</v>
       </c>
       <c r="F221" s="12"/>
       <c r="G221" s="12">
@@ -7428,10 +6810,10 @@
         <v>45967</v>
       </c>
       <c r="E222" s="20">
-        <v>0.979166666666667</v>
+        <v>0.97916666666666696</v>
       </c>
       <c r="F222" s="20">
-        <v>0.0208333333333333</v>
+        <v>2.0833333333333301E-2</v>
       </c>
       <c r="G222" s="6">
         <v>0</v>
@@ -7454,7 +6836,7 @@
         <v>0.125</v>
       </c>
       <c r="F223" s="20">
-        <v>0.166666666666667</v>
+        <v>0.16666666666666699</v>
       </c>
       <c r="G223" s="6">
         <v>0</v>
@@ -7477,7 +6859,7 @@
         <v>0.9375</v>
       </c>
       <c r="F224" s="20">
-        <v>0.979166666666667</v>
+        <v>0.97916666666666696</v>
       </c>
       <c r="G224" s="6">
         <v>0</v>
@@ -7497,7 +6879,7 @@
         <v>45969</v>
       </c>
       <c r="E225" s="20">
-        <v>0.0833333333333333</v>
+        <v>8.3333333333333301E-2</v>
       </c>
       <c r="F225" s="20">
         <v>0.125</v>
@@ -7520,7 +6902,7 @@
         <v>45970</v>
       </c>
       <c r="E226" s="20">
-        <v>0.0416666666666667</v>
+        <v>4.1666666666666699E-2</v>
       </c>
       <c r="F226" s="6"/>
       <c r="G226" s="6">
@@ -7541,10 +6923,10 @@
         <v>45981</v>
       </c>
       <c r="E227" s="22">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="F227" s="22">
-        <v>0.395833333333333</v>
+        <v>0.39583333333333298</v>
       </c>
       <c r="G227" s="12">
         <v>0</v>
@@ -7567,7 +6949,7 @@
         <v>0.5</v>
       </c>
       <c r="F228" s="22">
-        <v>0.541666666666667</v>
+        <v>0.54166666666666696</v>
       </c>
       <c r="G228" s="12">
         <v>0</v>
@@ -7587,10 +6969,10 @@
         <v>45982</v>
       </c>
       <c r="E229" s="23">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="F229" s="23">
-        <v>0.395833333333333</v>
+        <v>0.39583333333333298</v>
       </c>
       <c r="G229" s="12">
         <v>0</v>
@@ -7613,7 +6995,7 @@
         <v>0.5</v>
       </c>
       <c r="F230" s="23">
-        <v>0.541666666666667</v>
+        <v>0.54166666666666696</v>
       </c>
       <c r="G230" s="12">
         <v>1</v>
@@ -7654,7 +7036,7 @@
         <v>45988</v>
       </c>
       <c r="E232" s="24">
-        <v>0.895833333333333</v>
+        <v>0.89583333333333304</v>
       </c>
       <c r="F232" s="24">
         <v>0.9375</v>
@@ -7677,10 +7059,10 @@
         <v>45989</v>
       </c>
       <c r="E233" s="24">
-        <v>0.0416666666666667</v>
+        <v>4.1666666666666699E-2</v>
       </c>
       <c r="F233" s="24">
-        <v>0.0833333333333333</v>
+        <v>8.3333333333333301E-2</v>
       </c>
       <c r="G233" s="6">
         <v>0</v>
@@ -7703,7 +7085,7 @@
         <v>0.9375</v>
       </c>
       <c r="F234" s="20">
-        <v>0.979166666666667</v>
+        <v>0.97916666666666696</v>
       </c>
       <c r="G234" s="6">
         <v>0</v>
@@ -7723,7 +7105,7 @@
         <v>45990</v>
       </c>
       <c r="E235" s="20">
-        <v>0.0833333333333333</v>
+        <v>8.3333333333333301E-2</v>
       </c>
       <c r="F235" s="20">
         <v>0.125</v>
@@ -7767,10 +7149,10 @@
         <v>45995</v>
       </c>
       <c r="E237" s="23">
-        <v>0.729166666666667</v>
+        <v>0.72916666666666696</v>
       </c>
       <c r="F237" s="23">
-        <v>0.770833333333333</v>
+        <v>0.77083333333333304</v>
       </c>
       <c r="G237" s="12">
         <v>0</v>
@@ -7793,7 +7175,7 @@
         <v>0.875</v>
       </c>
       <c r="F238" s="23">
-        <v>0.916666666666667</v>
+        <v>0.91666666666666696</v>
       </c>
       <c r="G238" s="12">
         <v>0</v>
@@ -7813,7 +7195,7 @@
         <v>45996</v>
       </c>
       <c r="E239" s="23">
-        <v>0.770833333333333</v>
+        <v>0.77083333333333304</v>
       </c>
       <c r="F239" s="23">
         <v>0.8125</v>
@@ -7836,10 +7218,10 @@
         <v>45996</v>
       </c>
       <c r="E240" s="23">
-        <v>0.916666666666667</v>
+        <v>0.91666666666666696</v>
       </c>
       <c r="F240" s="23">
-        <v>0.958333333333333</v>
+        <v>0.95833333333333304</v>
       </c>
       <c r="G240" s="12">
         <v>1</v>
@@ -7868,24 +7250,22 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:R1201"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
-    <col min="2" max="2" width="6.28571428571429" customWidth="1"/>
-    <col min="3" max="3" width="15.5714285714286" customWidth="1"/>
-    <col min="4" max="4" width="8.28571428571429" customWidth="1"/>
-    <col min="5" max="5" width="8.85714285714286" customWidth="1"/>
+    <col min="2" max="2" width="6.28515625" customWidth="1"/>
+    <col min="3" max="3" width="15.5703125" customWidth="1"/>
+    <col min="4" max="4" width="8.28515625" customWidth="1"/>
+    <col min="5" max="5" width="8.85546875" customWidth="1"/>
     <col min="6" max="6" width="17" customWidth="1"/>
-    <col min="7" max="7" width="29.2857142857143" customWidth="1"/>
-    <col min="8" max="10" width="12.7142857142857"/>
+    <col min="7" max="7" width="29.28515625" customWidth="1"/>
+    <col min="8" max="10" width="12.7109375"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17">
@@ -19238,7 +18618,7 @@
       <c r="N421" s="10"/>
       <c r="O421" s="11"/>
     </row>
-    <row r="422" ht="17" spans="1:15">
+    <row r="422" spans="1:15">
       <c r="A422" s="12">
         <v>2025</v>
       </c>
@@ -19270,7 +18650,7 @@
       <c r="N422" s="11"/>
       <c r="O422" s="11"/>
     </row>
-    <row r="423" ht="17" spans="1:15">
+    <row r="423" spans="1:15">
       <c r="A423" s="12">
         <v>2025</v>
       </c>
@@ -19302,7 +18682,7 @@
       <c r="N423" s="11"/>
       <c r="O423" s="11"/>
     </row>
-    <row r="424" ht="17" spans="1:15">
+    <row r="424" spans="1:15">
       <c r="A424" s="12">
         <v>2025</v>
       </c>
@@ -19334,7 +18714,7 @@
       <c r="N424" s="11"/>
       <c r="O424" s="11"/>
     </row>
-    <row r="425" ht="17" spans="1:15">
+    <row r="425" spans="1:15">
       <c r="A425" s="12">
         <v>2025</v>
       </c>
@@ -19366,7 +18746,7 @@
       <c r="N425" s="11"/>
       <c r="O425" s="11"/>
     </row>
-    <row r="426" ht="17" spans="1:15">
+    <row r="426" spans="1:15">
       <c r="A426" s="12">
         <v>2025</v>
       </c>
@@ -19398,7 +18778,7 @@
       <c r="N426" s="11"/>
       <c r="O426" s="11"/>
     </row>
-    <row r="427" ht="17" spans="1:15">
+    <row r="427" spans="1:15">
       <c r="A427" s="12">
         <v>2025</v>
       </c>
@@ -19430,7 +18810,7 @@
       <c r="N427" s="11"/>
       <c r="O427" s="11"/>
     </row>
-    <row r="428" ht="17" spans="1:15">
+    <row r="428" spans="1:15">
       <c r="A428" s="12">
         <v>2025</v>
       </c>
@@ -19462,7 +18842,7 @@
       <c r="N428" s="11"/>
       <c r="O428" s="11"/>
     </row>
-    <row r="429" ht="17" spans="1:15">
+    <row r="429" spans="1:15">
       <c r="A429" s="12">
         <v>2025</v>
       </c>
@@ -19494,7 +18874,7 @@
       <c r="N429" s="11"/>
       <c r="O429" s="11"/>
     </row>
-    <row r="430" ht="17" spans="1:15">
+    <row r="430" spans="1:15">
       <c r="A430" s="12">
         <v>2025</v>
       </c>
@@ -19526,7 +18906,7 @@
       <c r="N430" s="11"/>
       <c r="O430" s="11"/>
     </row>
-    <row r="431" ht="17" spans="1:15">
+    <row r="431" spans="1:15">
       <c r="A431" s="12">
         <v>2025</v>
       </c>
@@ -19558,7 +18938,7 @@
       <c r="N431" s="11"/>
       <c r="O431" s="11"/>
     </row>
-    <row r="432" ht="17" spans="1:15">
+    <row r="432" spans="1:15">
       <c r="A432" s="12">
         <v>2025</v>
       </c>
@@ -19590,7 +18970,7 @@
       <c r="N432" s="11"/>
       <c r="O432" s="11"/>
     </row>
-    <row r="433" ht="17" spans="1:15">
+    <row r="433" spans="1:15">
       <c r="A433" s="12">
         <v>2025</v>
       </c>
@@ -19622,7 +19002,7 @@
       <c r="N433" s="11"/>
       <c r="O433" s="11"/>
     </row>
-    <row r="434" ht="17" spans="1:15">
+    <row r="434" spans="1:15">
       <c r="A434" s="12">
         <v>2025</v>
       </c>
@@ -19654,7 +19034,7 @@
       <c r="N434" s="11"/>
       <c r="O434" s="11"/>
     </row>
-    <row r="435" ht="17" spans="1:15">
+    <row r="435" spans="1:15">
       <c r="A435" s="12">
         <v>2025</v>
       </c>
@@ -19686,7 +19066,7 @@
       <c r="N435" s="11"/>
       <c r="O435" s="11"/>
     </row>
-    <row r="436" ht="17" spans="1:15">
+    <row r="436" spans="1:15">
       <c r="A436" s="12">
         <v>2025</v>
       </c>
@@ -19718,7 +19098,7 @@
       <c r="N436" s="11"/>
       <c r="O436" s="11"/>
     </row>
-    <row r="437" ht="17" spans="1:15">
+    <row r="437" spans="1:15">
       <c r="A437" s="12">
         <v>2025</v>
       </c>
@@ -19750,7 +19130,7 @@
       <c r="N437" s="11"/>
       <c r="O437" s="11"/>
     </row>
-    <row r="438" ht="17" spans="1:15">
+    <row r="438" spans="1:15">
       <c r="A438" s="12">
         <v>2025</v>
       </c>
@@ -19782,7 +19162,7 @@
       <c r="N438" s="11"/>
       <c r="O438" s="11"/>
     </row>
-    <row r="439" ht="17" spans="1:15">
+    <row r="439" spans="1:15">
       <c r="A439" s="12">
         <v>2025</v>
       </c>
@@ -19814,7 +19194,7 @@
       <c r="N439" s="11"/>
       <c r="O439" s="11"/>
     </row>
-    <row r="440" ht="17" spans="1:15">
+    <row r="440" spans="1:15">
       <c r="A440" s="12">
         <v>2025</v>
       </c>
@@ -19840,7 +19220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="441" ht="17" spans="1:15">
+    <row r="441" spans="1:15">
       <c r="A441" s="12">
         <v>2025</v>
       </c>
@@ -19864,7 +19244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="442" ht="17" spans="1:15">
+    <row r="442" spans="1:15">
       <c r="A442" s="6">
         <v>2025</v>
       </c>
@@ -19890,7 +19270,7 @@
       <c r="I442" s="10"/>
       <c r="J442" s="10"/>
     </row>
-    <row r="443" ht="17" spans="1:15">
+    <row r="443" spans="1:15">
       <c r="A443" s="6">
         <v>2025</v>
       </c>
@@ -19916,7 +19296,7 @@
       <c r="I443" s="10"/>
       <c r="J443" s="10"/>
     </row>
-    <row r="444" ht="17" spans="1:15">
+    <row r="444" spans="1:15">
       <c r="A444" s="6">
         <v>2025</v>
       </c>
@@ -19942,7 +19322,7 @@
       <c r="I444" s="10"/>
       <c r="J444" s="10"/>
     </row>
-    <row r="445" ht="17" spans="1:15">
+    <row r="445" spans="1:15">
       <c r="A445" s="6">
         <v>2025</v>
       </c>
@@ -19968,7 +19348,7 @@
       <c r="I445" s="10"/>
       <c r="J445" s="10"/>
     </row>
-    <row r="446" ht="17" spans="1:15">
+    <row r="446" spans="1:15">
       <c r="A446" s="6">
         <v>2025</v>
       </c>
@@ -19994,7 +19374,7 @@
       <c r="I446" s="10"/>
       <c r="J446" s="10"/>
     </row>
-    <row r="447" ht="17" spans="1:15">
+    <row r="447" spans="1:15">
       <c r="A447" s="6">
         <v>2025</v>
       </c>
@@ -20020,7 +19400,7 @@
       <c r="I447" s="10"/>
       <c r="J447" s="10"/>
     </row>
-    <row r="448" ht="17" spans="1:15">
+    <row r="448" spans="1:15">
       <c r="A448" s="6">
         <v>2025</v>
       </c>
@@ -20046,7 +19426,7 @@
       <c r="I448" s="10"/>
       <c r="J448" s="10"/>
     </row>
-    <row r="449" ht="17" spans="1:10">
+    <row r="449" spans="1:10">
       <c r="A449" s="6">
         <v>2025</v>
       </c>
@@ -20072,7 +19452,7 @@
       <c r="I449" s="10"/>
       <c r="J449" s="10"/>
     </row>
-    <row r="450" ht="17" spans="1:10">
+    <row r="450" spans="1:10">
       <c r="A450" s="6">
         <v>2025</v>
       </c>
@@ -20098,7 +19478,7 @@
       <c r="I450" s="10"/>
       <c r="J450" s="10"/>
     </row>
-    <row r="451" ht="17" spans="1:10">
+    <row r="451" spans="1:10">
       <c r="A451" s="6">
         <v>2025</v>
       </c>
@@ -20124,7 +19504,7 @@
       <c r="I451" s="10"/>
       <c r="J451" s="10"/>
     </row>
-    <row r="452" ht="17" spans="1:10">
+    <row r="452" spans="1:10">
       <c r="A452" s="6">
         <v>2025</v>
       </c>
@@ -20150,7 +19530,7 @@
       <c r="I452" s="10"/>
       <c r="J452" s="11"/>
     </row>
-    <row r="453" ht="17" spans="1:10">
+    <row r="453" spans="1:10">
       <c r="A453" s="6">
         <v>2025</v>
       </c>
@@ -20176,7 +19556,7 @@
       <c r="I453" s="10"/>
       <c r="J453" s="11"/>
     </row>
-    <row r="454" ht="17" spans="1:10">
+    <row r="454" spans="1:10">
       <c r="A454" s="6">
         <v>2025</v>
       </c>
@@ -20202,7 +19582,7 @@
       <c r="I454" s="10"/>
       <c r="J454" s="11"/>
     </row>
-    <row r="455" ht="17" spans="1:10">
+    <row r="455" spans="1:10">
       <c r="A455" s="6">
         <v>2025</v>
       </c>
@@ -20228,7 +19608,7 @@
       <c r="I455" s="10"/>
       <c r="J455" s="11"/>
     </row>
-    <row r="456" ht="17" spans="1:10">
+    <row r="456" spans="1:10">
       <c r="A456" s="6">
         <v>2025</v>
       </c>
@@ -20254,7 +19634,7 @@
       <c r="I456" s="10"/>
       <c r="J456" s="11"/>
     </row>
-    <row r="457" ht="17" spans="1:10">
+    <row r="457" spans="1:10">
       <c r="A457" s="6">
         <v>2025</v>
       </c>
@@ -20280,7 +19660,7 @@
       <c r="I457" s="11"/>
       <c r="J457" s="11"/>
     </row>
-    <row r="458" ht="17" spans="1:10">
+    <row r="458" spans="1:10">
       <c r="A458" s="6">
         <v>2025</v>
       </c>
@@ -20306,7 +19686,7 @@
       <c r="I458" s="11"/>
       <c r="J458" s="11"/>
     </row>
-    <row r="459" ht="17" spans="1:10">
+    <row r="459" spans="1:10">
       <c r="A459" s="6">
         <v>2025</v>
       </c>
@@ -20332,7 +19712,7 @@
       <c r="I459" s="11"/>
       <c r="J459" s="11"/>
     </row>
-    <row r="460" ht="17" spans="1:10">
+    <row r="460" spans="1:10">
       <c r="A460" s="6">
         <v>2025</v>
       </c>
@@ -20358,7 +19738,7 @@
       <c r="I460" s="11"/>
       <c r="J460" s="11"/>
     </row>
-    <row r="461" ht="17" spans="1:10">
+    <row r="461" spans="1:10">
       <c r="A461" s="6">
         <v>2025</v>
       </c>
@@ -20384,7 +19764,7 @@
       <c r="I461" s="11"/>
       <c r="J461" s="11"/>
     </row>
-    <row r="462" ht="17" spans="1:10">
+    <row r="462" spans="1:10">
       <c r="A462" s="12">
         <v>2025</v>
       </c>
@@ -20412,7 +19792,7 @@
       <c r="I462" s="10"/>
       <c r="J462" s="11"/>
     </row>
-    <row r="463" ht="17" spans="1:10">
+    <row r="463" spans="1:10">
       <c r="A463" s="12">
         <v>2025</v>
       </c>
@@ -20440,7 +19820,7 @@
       <c r="I463" s="11"/>
       <c r="J463" s="11"/>
     </row>
-    <row r="464" ht="17" spans="1:10">
+    <row r="464" spans="1:10">
       <c r="A464" s="12">
         <v>2025</v>
       </c>
@@ -20468,7 +19848,7 @@
       <c r="I464" s="11"/>
       <c r="J464" s="11"/>
     </row>
-    <row r="465" ht="17" spans="1:10">
+    <row r="465" spans="1:10">
       <c r="A465" s="12">
         <v>2025</v>
       </c>
@@ -20496,7 +19876,7 @@
       <c r="I465" s="11"/>
       <c r="J465" s="11"/>
     </row>
-    <row r="466" ht="17" spans="1:10">
+    <row r="466" spans="1:10">
       <c r="A466" s="12">
         <v>2025</v>
       </c>
@@ -20524,7 +19904,7 @@
       <c r="I466" s="11"/>
       <c r="J466" s="11"/>
     </row>
-    <row r="467" ht="17" spans="1:10">
+    <row r="467" spans="1:10">
       <c r="A467" s="12">
         <v>2025</v>
       </c>
@@ -20552,7 +19932,7 @@
       <c r="I467" s="11"/>
       <c r="J467" s="11"/>
     </row>
-    <row r="468" ht="17" spans="1:10">
+    <row r="468" spans="1:10">
       <c r="A468" s="12">
         <v>2025</v>
       </c>
@@ -20580,7 +19960,7 @@
       <c r="I468" s="11"/>
       <c r="J468" s="11"/>
     </row>
-    <row r="469" ht="17" spans="1:10">
+    <row r="469" spans="1:10">
       <c r="A469" s="12">
         <v>2025</v>
       </c>
@@ -20608,7 +19988,7 @@
       <c r="I469" s="11"/>
       <c r="J469" s="11"/>
     </row>
-    <row r="470" ht="17" spans="1:10">
+    <row r="470" spans="1:10">
       <c r="A470" s="12">
         <v>2025</v>
       </c>
@@ -20636,7 +20016,7 @@
       <c r="I470" s="11"/>
       <c r="J470" s="11"/>
     </row>
-    <row r="471" ht="17" spans="1:10">
+    <row r="471" spans="1:10">
       <c r="A471" s="12">
         <v>2025</v>
       </c>
@@ -20664,7 +20044,7 @@
       <c r="I471" s="11"/>
       <c r="J471" s="11"/>
     </row>
-    <row r="472" ht="17" spans="1:10">
+    <row r="472" spans="1:10">
       <c r="A472" s="12">
         <v>2025</v>
       </c>
@@ -20692,7 +20072,7 @@
       <c r="I472" s="11"/>
       <c r="J472" s="11"/>
     </row>
-    <row r="473" ht="17" spans="1:10">
+    <row r="473" spans="1:10">
       <c r="A473" s="12">
         <v>2025</v>
       </c>
@@ -20720,7 +20100,7 @@
       <c r="I473" s="11"/>
       <c r="J473" s="11"/>
     </row>
-    <row r="474" ht="17" spans="1:10">
+    <row r="474" spans="1:10">
       <c r="A474" s="12">
         <v>2025</v>
       </c>
@@ -20748,7 +20128,7 @@
       <c r="I474" s="11"/>
       <c r="J474" s="11"/>
     </row>
-    <row r="475" ht="17" spans="1:10">
+    <row r="475" spans="1:10">
       <c r="A475" s="12">
         <v>2025</v>
       </c>
@@ -20776,7 +20156,7 @@
       <c r="I475" s="11"/>
       <c r="J475" s="11"/>
     </row>
-    <row r="476" ht="17" spans="1:10">
+    <row r="476" spans="1:10">
       <c r="A476" s="12">
         <v>2025</v>
       </c>
@@ -20804,7 +20184,7 @@
       <c r="I476" s="11"/>
       <c r="J476" s="11"/>
     </row>
-    <row r="477" ht="17" spans="1:10">
+    <row r="477" spans="1:10">
       <c r="A477" s="12">
         <v>2025</v>
       </c>
@@ -20832,7 +20212,7 @@
       <c r="I477" s="11"/>
       <c r="J477" s="11"/>
     </row>
-    <row r="478" ht="17" spans="1:10">
+    <row r="478" spans="1:10">
       <c r="A478" s="12">
         <v>2025</v>
       </c>
@@ -20860,7 +20240,7 @@
       <c r="I478" s="11"/>
       <c r="J478" s="11"/>
     </row>
-    <row r="479" ht="17" spans="1:10">
+    <row r="479" spans="1:10">
       <c r="A479" s="12">
         <v>2025</v>
       </c>
@@ -20888,7 +20268,7 @@
       <c r="I479" s="11"/>
       <c r="J479" s="11"/>
     </row>
-    <row r="480" ht="17" spans="1:10">
+    <row r="480" spans="1:10">
       <c r="A480" s="12">
         <v>2025</v>
       </c>
@@ -20916,7 +20296,7 @@
       <c r="I480" s="11"/>
       <c r="J480" s="11"/>
     </row>
-    <row r="481" ht="17" spans="1:10">
+    <row r="481" spans="1:10">
       <c r="A481" s="12">
         <v>2025</v>
       </c>
@@ -20944,7 +20324,7 @@
       <c r="I481" s="11"/>
       <c r="J481" s="11"/>
     </row>
-    <row r="482" ht="17" spans="1:10">
+    <row r="482" spans="1:10">
       <c r="A482" s="6">
         <v>2025</v>
       </c>
@@ -20970,7 +20350,7 @@
       <c r="I482" s="10"/>
       <c r="J482" s="10"/>
     </row>
-    <row r="483" ht="17" spans="1:10">
+    <row r="483" spans="1:10">
       <c r="A483" s="6">
         <v>2025</v>
       </c>
@@ -20996,7 +20376,7 @@
       <c r="I483" s="10"/>
       <c r="J483" s="10"/>
     </row>
-    <row r="484" ht="17" spans="1:10">
+    <row r="484" spans="1:10">
       <c r="A484" s="6">
         <v>2025</v>
       </c>
@@ -21022,7 +20402,7 @@
       <c r="I484" s="10"/>
       <c r="J484" s="10"/>
     </row>
-    <row r="485" ht="17" spans="1:10">
+    <row r="485" spans="1:10">
       <c r="A485" s="6">
         <v>2025</v>
       </c>
@@ -21048,7 +20428,7 @@
       <c r="I485" s="10"/>
       <c r="J485" s="10"/>
     </row>
-    <row r="486" ht="17" spans="1:10">
+    <row r="486" spans="1:10">
       <c r="A486" s="6">
         <v>2025</v>
       </c>
@@ -21074,7 +20454,7 @@
       <c r="I486" s="10"/>
       <c r="J486" s="10"/>
     </row>
-    <row r="487" ht="17" spans="1:10">
+    <row r="487" spans="1:10">
       <c r="A487" s="6">
         <v>2025</v>
       </c>
@@ -21100,7 +20480,7 @@
       <c r="I487" s="10"/>
       <c r="J487" s="10"/>
     </row>
-    <row r="488" ht="17" spans="1:10">
+    <row r="488" spans="1:10">
       <c r="A488" s="6">
         <v>2025</v>
       </c>
@@ -21126,7 +20506,7 @@
       <c r="I488" s="10"/>
       <c r="J488" s="10"/>
     </row>
-    <row r="489" ht="17" spans="1:10">
+    <row r="489" spans="1:10">
       <c r="A489" s="6">
         <v>2025</v>
       </c>
@@ -21152,7 +20532,7 @@
       <c r="I489" s="10"/>
       <c r="J489" s="10"/>
     </row>
-    <row r="490" ht="17" spans="1:10">
+    <row r="490" spans="1:10">
       <c r="A490" s="6">
         <v>2025</v>
       </c>
@@ -21178,7 +20558,7 @@
       <c r="I490" s="10"/>
       <c r="J490" s="10"/>
     </row>
-    <row r="491" ht="17" spans="1:10">
+    <row r="491" spans="1:10">
       <c r="A491" s="6">
         <v>2025</v>
       </c>
@@ -21204,7 +20584,7 @@
       <c r="I491" s="10"/>
       <c r="J491" s="10"/>
     </row>
-    <row r="492" ht="17" spans="1:10">
+    <row r="492" spans="1:10">
       <c r="A492" s="6">
         <v>2025</v>
       </c>
@@ -21230,7 +20610,7 @@
       <c r="I492" s="10"/>
       <c r="J492" s="11"/>
     </row>
-    <row r="493" ht="17" spans="1:10">
+    <row r="493" spans="1:10">
       <c r="A493" s="6">
         <v>2025</v>
       </c>
@@ -21256,7 +20636,7 @@
       <c r="I493" s="10"/>
       <c r="J493" s="11"/>
     </row>
-    <row r="494" ht="17" spans="1:10">
+    <row r="494" spans="1:10">
       <c r="A494" s="6">
         <v>2025</v>
       </c>
@@ -21282,7 +20662,7 @@
       <c r="I494" s="10"/>
       <c r="J494" s="11"/>
     </row>
-    <row r="495" ht="17" spans="1:10">
+    <row r="495" spans="1:10">
       <c r="A495" s="6">
         <v>2025</v>
       </c>
@@ -21308,7 +20688,7 @@
       <c r="I495" s="10"/>
       <c r="J495" s="11"/>
     </row>
-    <row r="496" ht="17" spans="1:10">
+    <row r="496" spans="1:10">
       <c r="A496" s="6">
         <v>2025</v>
       </c>
@@ -21334,7 +20714,7 @@
       <c r="I496" s="10"/>
       <c r="J496" s="11"/>
     </row>
-    <row r="497" ht="17" spans="1:10">
+    <row r="497" spans="1:10">
       <c r="A497" s="6">
         <v>2025</v>
       </c>
@@ -21360,7 +20740,7 @@
       <c r="I497" s="11"/>
       <c r="J497" s="11"/>
     </row>
-    <row r="498" ht="17" spans="1:10">
+    <row r="498" spans="1:10">
       <c r="A498" s="6">
         <v>2025</v>
       </c>
@@ -21386,7 +20766,7 @@
       <c r="I498" s="11"/>
       <c r="J498" s="11"/>
     </row>
-    <row r="499" ht="17" spans="1:10">
+    <row r="499" spans="1:10">
       <c r="A499" s="6">
         <v>2025</v>
       </c>
@@ -21412,7 +20792,7 @@
       <c r="I499" s="11"/>
       <c r="J499" s="11"/>
     </row>
-    <row r="500" ht="17" spans="1:10">
+    <row r="500" spans="1:10">
       <c r="A500" s="6">
         <v>2025</v>
       </c>
@@ -21438,7 +20818,7 @@
       <c r="I500" s="11"/>
       <c r="J500" s="11"/>
     </row>
-    <row r="501" ht="17" spans="1:10">
+    <row r="501" spans="1:10">
       <c r="A501" s="6">
         <v>2025</v>
       </c>
@@ -21464,7 +20844,7 @@
       <c r="I501" s="11"/>
       <c r="J501" s="11"/>
     </row>
-    <row r="502" ht="17" spans="1:10">
+    <row r="502" spans="1:10">
       <c r="A502" s="12">
         <v>2025</v>
       </c>
@@ -21492,7 +20872,7 @@
       <c r="I502" s="10"/>
       <c r="J502" s="11"/>
     </row>
-    <row r="503" ht="17" spans="1:10">
+    <row r="503" spans="1:10">
       <c r="A503" s="12">
         <v>2025</v>
       </c>
@@ -21520,7 +20900,7 @@
       <c r="I503" s="11"/>
       <c r="J503" s="11"/>
     </row>
-    <row r="504" ht="17" spans="1:10">
+    <row r="504" spans="1:10">
       <c r="A504" s="12">
         <v>2025</v>
       </c>
@@ -21548,7 +20928,7 @@
       <c r="I504" s="11"/>
       <c r="J504" s="11"/>
     </row>
-    <row r="505" ht="17" spans="1:10">
+    <row r="505" spans="1:10">
       <c r="A505" s="12">
         <v>2025</v>
       </c>
@@ -21576,7 +20956,7 @@
       <c r="I505" s="11"/>
       <c r="J505" s="11"/>
     </row>
-    <row r="506" ht="17" spans="1:10">
+    <row r="506" spans="1:10">
       <c r="A506" s="12">
         <v>2025</v>
       </c>
@@ -21604,7 +20984,7 @@
       <c r="I506" s="11"/>
       <c r="J506" s="11"/>
     </row>
-    <row r="507" ht="17" spans="1:10">
+    <row r="507" spans="1:10">
       <c r="A507" s="12">
         <v>2025</v>
       </c>
@@ -21632,7 +21012,7 @@
       <c r="I507" s="11"/>
       <c r="J507" s="11"/>
     </row>
-    <row r="508" ht="17" spans="1:10">
+    <row r="508" spans="1:10">
       <c r="A508" s="12">
         <v>2025</v>
       </c>
@@ -21660,7 +21040,7 @@
       <c r="I508" s="11"/>
       <c r="J508" s="11"/>
     </row>
-    <row r="509" ht="17" spans="1:10">
+    <row r="509" spans="1:10">
       <c r="A509" s="12">
         <v>2025</v>
       </c>
@@ -21688,7 +21068,7 @@
       <c r="I509" s="11"/>
       <c r="J509" s="11"/>
     </row>
-    <row r="510" ht="17" spans="1:10">
+    <row r="510" spans="1:10">
       <c r="A510" s="12">
         <v>2025</v>
       </c>
@@ -21716,7 +21096,7 @@
       <c r="I510" s="11"/>
       <c r="J510" s="11"/>
     </row>
-    <row r="511" ht="17" spans="1:10">
+    <row r="511" spans="1:10">
       <c r="A511" s="12">
         <v>2025</v>
       </c>
@@ -21744,7 +21124,7 @@
       <c r="I511" s="11"/>
       <c r="J511" s="11"/>
     </row>
-    <row r="512" ht="17" spans="1:10">
+    <row r="512" spans="1:10">
       <c r="A512" s="12">
         <v>2025</v>
       </c>
@@ -21772,7 +21152,7 @@
       <c r="I512" s="11"/>
       <c r="J512" s="11"/>
     </row>
-    <row r="513" ht="17" spans="1:10">
+    <row r="513" spans="1:10">
       <c r="A513" s="12">
         <v>2025</v>
       </c>
@@ -21800,7 +21180,7 @@
       <c r="I513" s="11"/>
       <c r="J513" s="11"/>
     </row>
-    <row r="514" ht="17" spans="1:10">
+    <row r="514" spans="1:10">
       <c r="A514" s="12">
         <v>2025</v>
       </c>
@@ -21828,7 +21208,7 @@
       <c r="I514" s="11"/>
       <c r="J514" s="11"/>
     </row>
-    <row r="515" ht="17" spans="1:10">
+    <row r="515" spans="1:10">
       <c r="A515" s="12">
         <v>2025</v>
       </c>
@@ -21856,7 +21236,7 @@
       <c r="I515" s="11"/>
       <c r="J515" s="11"/>
     </row>
-    <row r="516" ht="17" spans="1:10">
+    <row r="516" spans="1:10">
       <c r="A516" s="12">
         <v>2025</v>
       </c>
@@ -21884,7 +21264,7 @@
       <c r="I516" s="11"/>
       <c r="J516" s="11"/>
     </row>
-    <row r="517" ht="17" spans="1:10">
+    <row r="517" spans="1:10">
       <c r="A517" s="12">
         <v>2025</v>
       </c>
@@ -21912,7 +21292,7 @@
       <c r="I517" s="11"/>
       <c r="J517" s="11"/>
     </row>
-    <row r="518" ht="17" spans="1:10">
+    <row r="518" spans="1:10">
       <c r="A518" s="12">
         <v>2025</v>
       </c>
@@ -21940,7 +21320,7 @@
       <c r="I518" s="11"/>
       <c r="J518" s="11"/>
     </row>
-    <row r="519" ht="17" spans="1:10">
+    <row r="519" spans="1:10">
       <c r="A519" s="12">
         <v>2025</v>
       </c>
@@ -21968,7 +21348,7 @@
       <c r="I519" s="11"/>
       <c r="J519" s="11"/>
     </row>
-    <row r="520" ht="17" spans="1:10">
+    <row r="520" spans="1:10">
       <c r="A520" s="12">
         <v>2025</v>
       </c>
@@ -21996,7 +21376,7 @@
       <c r="I520" s="11"/>
       <c r="J520" s="11"/>
     </row>
-    <row r="521" ht="17" spans="1:10">
+    <row r="521" spans="1:10">
       <c r="A521" s="12">
         <v>2025</v>
       </c>
@@ -22024,7 +21404,7 @@
       <c r="I521" s="11"/>
       <c r="J521" s="11"/>
     </row>
-    <row r="522" ht="17" spans="1:10">
+    <row r="522" spans="1:10">
       <c r="A522" s="6">
         <v>2025</v>
       </c>
@@ -22050,7 +21430,7 @@
       <c r="I522" s="10"/>
       <c r="J522" s="10"/>
     </row>
-    <row r="523" ht="17" spans="1:10">
+    <row r="523" spans="1:10">
       <c r="A523" s="6">
         <v>2025</v>
       </c>
@@ -22076,7 +21456,7 @@
       <c r="I523" s="10"/>
       <c r="J523" s="10"/>
     </row>
-    <row r="524" ht="17" spans="1:10">
+    <row r="524" spans="1:10">
       <c r="A524" s="6">
         <v>2025</v>
       </c>
@@ -22102,7 +21482,7 @@
       <c r="I524" s="10"/>
       <c r="J524" s="10"/>
     </row>
-    <row r="525" ht="17" spans="1:10">
+    <row r="525" spans="1:10">
       <c r="A525" s="6">
         <v>2025</v>
       </c>
@@ -22128,7 +21508,7 @@
       <c r="I525" s="10"/>
       <c r="J525" s="10"/>
     </row>
-    <row r="526" ht="17" spans="1:10">
+    <row r="526" spans="1:10">
       <c r="A526" s="6">
         <v>2025</v>
       </c>
@@ -22154,7 +21534,7 @@
       <c r="I526" s="10"/>
       <c r="J526" s="10"/>
     </row>
-    <row r="527" ht="17" spans="1:10">
+    <row r="527" spans="1:10">
       <c r="A527" s="6">
         <v>2025</v>
       </c>
@@ -22180,7 +21560,7 @@
       <c r="I527" s="10"/>
       <c r="J527" s="10"/>
     </row>
-    <row r="528" ht="17" spans="1:10">
+    <row r="528" spans="1:10">
       <c r="A528" s="6">
         <v>2025</v>
       </c>
@@ -22206,7 +21586,7 @@
       <c r="I528" s="10"/>
       <c r="J528" s="10"/>
     </row>
-    <row r="529" ht="17" spans="1:10">
+    <row r="529" spans="1:10">
       <c r="A529" s="6">
         <v>2025</v>
       </c>
@@ -22232,7 +21612,7 @@
       <c r="I529" s="10"/>
       <c r="J529" s="10"/>
     </row>
-    <row r="530" ht="17" spans="1:10">
+    <row r="530" spans="1:10">
       <c r="A530" s="6">
         <v>2025</v>
       </c>
@@ -22258,7 +21638,7 @@
       <c r="I530" s="10"/>
       <c r="J530" s="10"/>
     </row>
-    <row r="531" ht="17" spans="1:10">
+    <row r="531" spans="1:10">
       <c r="A531" s="6">
         <v>2025</v>
       </c>
@@ -22284,7 +21664,7 @@
       <c r="I531" s="10"/>
       <c r="J531" s="10"/>
     </row>
-    <row r="532" ht="17" spans="1:10">
+    <row r="532" spans="1:10">
       <c r="A532" s="6">
         <v>2025</v>
       </c>
@@ -22310,7 +21690,7 @@
       <c r="I532" s="10"/>
       <c r="J532" s="11"/>
     </row>
-    <row r="533" ht="17" spans="1:10">
+    <row r="533" spans="1:10">
       <c r="A533" s="6">
         <v>2025</v>
       </c>
@@ -22336,7 +21716,7 @@
       <c r="I533" s="10"/>
       <c r="J533" s="11"/>
     </row>
-    <row r="534" ht="17" spans="1:10">
+    <row r="534" spans="1:10">
       <c r="A534" s="6">
         <v>2025</v>
       </c>
@@ -22362,7 +21742,7 @@
       <c r="I534" s="10"/>
       <c r="J534" s="11"/>
     </row>
-    <row r="535" ht="17" spans="1:10">
+    <row r="535" spans="1:10">
       <c r="A535" s="6">
         <v>2025</v>
       </c>
@@ -22388,7 +21768,7 @@
       <c r="I535" s="10"/>
       <c r="J535" s="11"/>
     </row>
-    <row r="536" ht="17" spans="1:10">
+    <row r="536" spans="1:10">
       <c r="A536" s="6">
         <v>2025</v>
       </c>
@@ -22414,7 +21794,7 @@
       <c r="I536" s="10"/>
       <c r="J536" s="11"/>
     </row>
-    <row r="537" ht="17" spans="1:10">
+    <row r="537" spans="1:10">
       <c r="A537" s="6">
         <v>2025</v>
       </c>
@@ -22440,7 +21820,7 @@
       <c r="I537" s="11"/>
       <c r="J537" s="11"/>
     </row>
-    <row r="538" ht="17" spans="1:10">
+    <row r="538" spans="1:10">
       <c r="A538" s="6">
         <v>2025</v>
       </c>
@@ -22466,7 +21846,7 @@
       <c r="I538" s="11"/>
       <c r="J538" s="11"/>
     </row>
-    <row r="539" ht="17" spans="1:10">
+    <row r="539" spans="1:10">
       <c r="A539" s="6">
         <v>2025</v>
       </c>
@@ -22492,7 +21872,7 @@
       <c r="I539" s="11"/>
       <c r="J539" s="11"/>
     </row>
-    <row r="540" ht="17" spans="1:10">
+    <row r="540" spans="1:10">
       <c r="A540" s="6">
         <v>2025</v>
       </c>
@@ -22518,7 +21898,7 @@
       <c r="I540" s="11"/>
       <c r="J540" s="11"/>
     </row>
-    <row r="541" ht="17" spans="1:10">
+    <row r="541" spans="1:10">
       <c r="A541" s="6">
         <v>2025</v>
       </c>
@@ -22544,7 +21924,7 @@
       <c r="I541" s="11"/>
       <c r="J541" s="11"/>
     </row>
-    <row r="542" ht="17" spans="1:10">
+    <row r="542" spans="1:10">
       <c r="A542" s="12">
         <v>2025</v>
       </c>
@@ -22572,7 +21952,7 @@
       <c r="I542" s="10"/>
       <c r="J542" s="11"/>
     </row>
-    <row r="543" ht="17" spans="1:10">
+    <row r="543" spans="1:10">
       <c r="A543" s="12">
         <v>2025</v>
       </c>
@@ -22600,7 +21980,7 @@
       <c r="I543" s="11"/>
       <c r="J543" s="11"/>
     </row>
-    <row r="544" ht="17" spans="1:10">
+    <row r="544" spans="1:10">
       <c r="A544" s="12">
         <v>2025</v>
       </c>
@@ -22628,7 +22008,7 @@
       <c r="I544" s="11"/>
       <c r="J544" s="11"/>
     </row>
-    <row r="545" ht="17" spans="1:10">
+    <row r="545" spans="1:10">
       <c r="A545" s="12">
         <v>2025</v>
       </c>
@@ -22656,7 +22036,7 @@
       <c r="I545" s="11"/>
       <c r="J545" s="11"/>
     </row>
-    <row r="546" ht="17" spans="1:10">
+    <row r="546" spans="1:10">
       <c r="A546" s="12">
         <v>2025</v>
       </c>
@@ -22684,7 +22064,7 @@
       <c r="I546" s="11"/>
       <c r="J546" s="11"/>
     </row>
-    <row r="547" ht="17" spans="1:10">
+    <row r="547" spans="1:10">
       <c r="A547" s="12">
         <v>2025</v>
       </c>
@@ -22712,7 +22092,7 @@
       <c r="I547" s="11"/>
       <c r="J547" s="11"/>
     </row>
-    <row r="548" ht="17" spans="1:10">
+    <row r="548" spans="1:10">
       <c r="A548" s="12">
         <v>2025</v>
       </c>
@@ -22740,7 +22120,7 @@
       <c r="I548" s="11"/>
       <c r="J548" s="11"/>
     </row>
-    <row r="549" ht="17" spans="1:10">
+    <row r="549" spans="1:10">
       <c r="A549" s="12">
         <v>2025</v>
       </c>
@@ -22768,7 +22148,7 @@
       <c r="I549" s="11"/>
       <c r="J549" s="11"/>
     </row>
-    <row r="550" ht="17" spans="1:10">
+    <row r="550" spans="1:10">
       <c r="A550" s="12">
         <v>2025</v>
       </c>
@@ -22796,7 +22176,7 @@
       <c r="I550" s="11"/>
       <c r="J550" s="11"/>
     </row>
-    <row r="551" ht="17" spans="1:10">
+    <row r="551" spans="1:10">
       <c r="A551" s="12">
         <v>2025</v>
       </c>
@@ -22824,7 +22204,7 @@
       <c r="I551" s="11"/>
       <c r="J551" s="11"/>
     </row>
-    <row r="552" ht="17" spans="1:10">
+    <row r="552" spans="1:10">
       <c r="A552" s="12">
         <v>2025</v>
       </c>
@@ -22852,7 +22232,7 @@
       <c r="I552" s="11"/>
       <c r="J552" s="11"/>
     </row>
-    <row r="553" ht="17" spans="1:10">
+    <row r="553" spans="1:10">
       <c r="A553" s="12">
         <v>2025</v>
       </c>
@@ -22880,7 +22260,7 @@
       <c r="I553" s="11"/>
       <c r="J553" s="11"/>
     </row>
-    <row r="554" ht="17" spans="1:10">
+    <row r="554" spans="1:10">
       <c r="A554" s="12">
         <v>2025</v>
       </c>
@@ -22908,7 +22288,7 @@
       <c r="I554" s="11"/>
       <c r="J554" s="11"/>
     </row>
-    <row r="555" ht="17" spans="1:10">
+    <row r="555" spans="1:10">
       <c r="A555" s="12">
         <v>2025</v>
       </c>
@@ -22936,7 +22316,7 @@
       <c r="I555" s="11"/>
       <c r="J555" s="11"/>
     </row>
-    <row r="556" ht="17" spans="1:10">
+    <row r="556" spans="1:10">
       <c r="A556" s="12">
         <v>2025</v>
       </c>
@@ -22964,7 +22344,7 @@
       <c r="I556" s="11"/>
       <c r="J556" s="11"/>
     </row>
-    <row r="557" ht="17" spans="1:10">
+    <row r="557" spans="1:10">
       <c r="A557" s="12">
         <v>2025</v>
       </c>
@@ -22992,7 +22372,7 @@
       <c r="I557" s="11"/>
       <c r="J557" s="11"/>
     </row>
-    <row r="558" ht="17" spans="1:10">
+    <row r="558" spans="1:10">
       <c r="A558" s="12">
         <v>2025</v>
       </c>
@@ -23020,7 +22400,7 @@
       <c r="I558" s="11"/>
       <c r="J558" s="11"/>
     </row>
-    <row r="559" ht="17" spans="1:10">
+    <row r="559" spans="1:10">
       <c r="A559" s="12">
         <v>2025</v>
       </c>
@@ -23048,7 +22428,7 @@
       <c r="I559" s="11"/>
       <c r="J559" s="11"/>
     </row>
-    <row r="560" ht="17" spans="1:10">
+    <row r="560" spans="1:10">
       <c r="A560" s="12">
         <v>2025</v>
       </c>
@@ -23076,7 +22456,7 @@
       <c r="I560" s="11"/>
       <c r="J560" s="11"/>
     </row>
-    <row r="561" ht="17" spans="1:16">
+    <row r="561" spans="1:16">
       <c r="A561" s="12">
         <v>2025</v>
       </c>
@@ -23629,7 +23009,7 @@
       <c r="H581" s="6"/>
       <c r="N581" s="16"/>
     </row>
-    <row r="582" ht="17" spans="1:14">
+    <row r="582" spans="1:14">
       <c r="A582" s="12">
         <v>2025</v>
       </c>
@@ -23657,7 +23037,7 @@
       <c r="I582" s="10"/>
       <c r="J582" s="11"/>
     </row>
-    <row r="583" ht="17" spans="1:14">
+    <row r="583" spans="1:14">
       <c r="A583" s="12">
         <v>2025</v>
       </c>
@@ -23685,7 +23065,7 @@
       <c r="I583" s="11"/>
       <c r="J583" s="11"/>
     </row>
-    <row r="584" ht="17" spans="1:14">
+    <row r="584" spans="1:14">
       <c r="A584" s="12">
         <v>2025</v>
       </c>
@@ -23713,7 +23093,7 @@
       <c r="I584" s="11"/>
       <c r="J584" s="11"/>
     </row>
-    <row r="585" ht="17" spans="1:14">
+    <row r="585" spans="1:14">
       <c r="A585" s="12">
         <v>2025</v>
       </c>
@@ -23741,7 +23121,7 @@
       <c r="I585" s="11"/>
       <c r="J585" s="11"/>
     </row>
-    <row r="586" ht="17" spans="1:14">
+    <row r="586" spans="1:14">
       <c r="A586" s="12">
         <v>2025</v>
       </c>
@@ -23769,7 +23149,7 @@
       <c r="I586" s="11"/>
       <c r="J586" s="11"/>
     </row>
-    <row r="587" ht="17" spans="1:14">
+    <row r="587" spans="1:14">
       <c r="A587" s="12">
         <v>2025</v>
       </c>
@@ -23797,7 +23177,7 @@
       <c r="I587" s="11"/>
       <c r="J587" s="11"/>
     </row>
-    <row r="588" ht="17" spans="1:14">
+    <row r="588" spans="1:14">
       <c r="A588" s="12">
         <v>2025</v>
       </c>
@@ -23825,7 +23205,7 @@
       <c r="I588" s="11"/>
       <c r="J588" s="11"/>
     </row>
-    <row r="589" ht="17" spans="1:14">
+    <row r="589" spans="1:14">
       <c r="A589" s="12">
         <v>2025</v>
       </c>
@@ -23853,7 +23233,7 @@
       <c r="I589" s="11"/>
       <c r="J589" s="11"/>
     </row>
-    <row r="590" ht="17" spans="1:14">
+    <row r="590" spans="1:14">
       <c r="A590" s="12">
         <v>2025</v>
       </c>
@@ -23881,7 +23261,7 @@
       <c r="I590" s="11"/>
       <c r="J590" s="11"/>
     </row>
-    <row r="591" ht="17" spans="1:14">
+    <row r="591" spans="1:14">
       <c r="A591" s="12">
         <v>2025</v>
       </c>
@@ -23909,7 +23289,7 @@
       <c r="I591" s="11"/>
       <c r="J591" s="11"/>
     </row>
-    <row r="592" ht="17" spans="1:14">
+    <row r="592" spans="1:14">
       <c r="A592" s="12">
         <v>2025</v>
       </c>
@@ -23937,7 +23317,7 @@
       <c r="I592" s="11"/>
       <c r="J592" s="11"/>
     </row>
-    <row r="593" ht="17" spans="1:10">
+    <row r="593" spans="1:10">
       <c r="A593" s="12">
         <v>2025</v>
       </c>
@@ -23965,7 +23345,7 @@
       <c r="I593" s="11"/>
       <c r="J593" s="11"/>
     </row>
-    <row r="594" ht="17" spans="1:10">
+    <row r="594" spans="1:10">
       <c r="A594" s="12">
         <v>2025</v>
       </c>
@@ -23993,7 +23373,7 @@
       <c r="I594" s="11"/>
       <c r="J594" s="11"/>
     </row>
-    <row r="595" ht="17" spans="1:10">
+    <row r="595" spans="1:10">
       <c r="A595" s="12">
         <v>2025</v>
       </c>
@@ -24021,7 +23401,7 @@
       <c r="I595" s="11"/>
       <c r="J595" s="11"/>
     </row>
-    <row r="596" ht="17" spans="1:10">
+    <row r="596" spans="1:10">
       <c r="A596" s="12">
         <v>2025</v>
       </c>
@@ -24049,7 +23429,7 @@
       <c r="I596" s="11"/>
       <c r="J596" s="11"/>
     </row>
-    <row r="597" ht="17" spans="1:10">
+    <row r="597" spans="1:10">
       <c r="A597" s="12">
         <v>2025</v>
       </c>
@@ -24077,7 +23457,7 @@
       <c r="I597" s="11"/>
       <c r="J597" s="11"/>
     </row>
-    <row r="598" ht="17" spans="1:10">
+    <row r="598" spans="1:10">
       <c r="A598" s="12">
         <v>2025</v>
       </c>
@@ -24105,7 +23485,7 @@
       <c r="I598" s="11"/>
       <c r="J598" s="11"/>
     </row>
-    <row r="599" ht="17" spans="1:10">
+    <row r="599" spans="1:10">
       <c r="A599" s="12">
         <v>2025</v>
       </c>
@@ -24133,7 +23513,7 @@
       <c r="I599" s="11"/>
       <c r="J599" s="11"/>
     </row>
-    <row r="600" ht="17" spans="1:10">
+    <row r="600" spans="1:10">
       <c r="A600" s="12">
         <v>2025</v>
       </c>
@@ -24161,7 +23541,7 @@
       <c r="I600" s="11"/>
       <c r="J600" s="11"/>
     </row>
-    <row r="601" ht="17" spans="1:10">
+    <row r="601" spans="1:10">
       <c r="A601" s="12">
         <v>2025</v>
       </c>
@@ -26214,7 +25594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="681" ht="17" spans="1:17">
+    <row r="681" spans="1:17">
       <c r="A681" s="12">
         <v>2025</v>
       </c>
@@ -26240,7 +25620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="682" ht="17" spans="1:17">
+    <row r="682" spans="1:17">
       <c r="A682" s="6">
         <v>2025</v>
       </c>
@@ -26268,7 +25648,7 @@
       <c r="P682" s="10"/>
       <c r="Q682" s="11"/>
     </row>
-    <row r="683" ht="17" spans="1:17">
+    <row r="683" spans="1:17">
       <c r="A683" s="6">
         <v>2025</v>
       </c>
@@ -26296,7 +25676,7 @@
       <c r="P683" s="10"/>
       <c r="Q683" s="11"/>
     </row>
-    <row r="684" ht="17" spans="1:17">
+    <row r="684" spans="1:17">
       <c r="A684" s="6">
         <v>2025</v>
       </c>
@@ -26324,7 +25704,7 @@
       <c r="P684" s="10"/>
       <c r="Q684" s="11"/>
     </row>
-    <row r="685" ht="17" spans="1:17">
+    <row r="685" spans="1:17">
       <c r="A685" s="6">
         <v>2025</v>
       </c>
@@ -26352,7 +25732,7 @@
       <c r="P685" s="10"/>
       <c r="Q685" s="11"/>
     </row>
-    <row r="686" ht="17" spans="1:17">
+    <row r="686" spans="1:17">
       <c r="A686" s="6">
         <v>2025</v>
       </c>
@@ -26380,7 +25760,7 @@
       <c r="P686" s="10"/>
       <c r="Q686" s="11"/>
     </row>
-    <row r="687" ht="17" spans="1:17">
+    <row r="687" spans="1:17">
       <c r="A687" s="6">
         <v>2025</v>
       </c>
@@ -26408,7 +25788,7 @@
       <c r="P687" s="10"/>
       <c r="Q687" s="11"/>
     </row>
-    <row r="688" ht="17" spans="1:17">
+    <row r="688" spans="1:17">
       <c r="A688" s="6">
         <v>2025</v>
       </c>
@@ -26436,7 +25816,7 @@
       <c r="P688" s="10"/>
       <c r="Q688" s="11"/>
     </row>
-    <row r="689" ht="17" spans="1:17">
+    <row r="689" spans="1:17">
       <c r="A689" s="6">
         <v>2025</v>
       </c>
@@ -26464,7 +25844,7 @@
       <c r="P689" s="10"/>
       <c r="Q689" s="11"/>
     </row>
-    <row r="690" ht="17" spans="1:17">
+    <row r="690" spans="1:17">
       <c r="A690" s="6">
         <v>2025</v>
       </c>
@@ -26492,7 +25872,7 @@
       <c r="P690" s="10"/>
       <c r="Q690" s="11"/>
     </row>
-    <row r="691" ht="17" spans="1:17">
+    <row r="691" spans="1:17">
       <c r="A691" s="6">
         <v>2025</v>
       </c>
@@ -26520,7 +25900,7 @@
       <c r="P691" s="10"/>
       <c r="Q691" s="11"/>
     </row>
-    <row r="692" ht="17" spans="1:17">
+    <row r="692" spans="1:17">
       <c r="A692" s="6">
         <v>2025</v>
       </c>
@@ -26548,7 +25928,7 @@
       <c r="P692" s="11"/>
       <c r="Q692" s="11"/>
     </row>
-    <row r="693" ht="17" spans="1:17">
+    <row r="693" spans="1:17">
       <c r="A693" s="6">
         <v>2025</v>
       </c>
@@ -26576,7 +25956,7 @@
       <c r="P693" s="11"/>
       <c r="Q693" s="11"/>
     </row>
-    <row r="694" ht="17" spans="1:17">
+    <row r="694" spans="1:17">
       <c r="A694" s="6">
         <v>2025</v>
       </c>
@@ -26604,7 +25984,7 @@
       <c r="P694" s="11"/>
       <c r="Q694" s="11"/>
     </row>
-    <row r="695" ht="17" spans="1:17">
+    <row r="695" spans="1:17">
       <c r="A695" s="6">
         <v>2025</v>
       </c>
@@ -26632,7 +26012,7 @@
       <c r="P695" s="11"/>
       <c r="Q695" s="11"/>
     </row>
-    <row r="696" ht="17" spans="1:17">
+    <row r="696" spans="1:17">
       <c r="A696" s="6">
         <v>2025</v>
       </c>
@@ -26660,7 +26040,7 @@
       <c r="P696" s="11"/>
       <c r="Q696" s="11"/>
     </row>
-    <row r="697" ht="17" spans="1:17">
+    <row r="697" spans="1:17">
       <c r="A697" s="6">
         <v>2025</v>
       </c>
@@ -26688,7 +26068,7 @@
       <c r="P697" s="11"/>
       <c r="Q697" s="11"/>
     </row>
-    <row r="698" ht="17" spans="1:17">
+    <row r="698" spans="1:17">
       <c r="A698" s="6">
         <v>2025</v>
       </c>
@@ -26716,7 +26096,7 @@
       <c r="P698" s="11"/>
       <c r="Q698" s="11"/>
     </row>
-    <row r="699" ht="17" spans="1:17">
+    <row r="699" spans="1:17">
       <c r="A699" s="6">
         <v>2025</v>
       </c>
@@ -26744,7 +26124,7 @@
       <c r="P699" s="11"/>
       <c r="Q699" s="11"/>
     </row>
-    <row r="700" ht="17" spans="1:17">
+    <row r="700" spans="1:17">
       <c r="A700" s="6">
         <v>2025</v>
       </c>
@@ -26772,7 +26152,7 @@
       <c r="P700" s="11"/>
       <c r="Q700" s="11"/>
     </row>
-    <row r="701" ht="17" spans="1:17">
+    <row r="701" spans="1:17">
       <c r="A701" s="6">
         <v>2025</v>
       </c>
@@ -26800,7 +26180,7 @@
       <c r="P701" s="11"/>
       <c r="Q701" s="11"/>
     </row>
-    <row r="702" ht="17" spans="1:17">
+    <row r="702" spans="1:17">
       <c r="A702" s="12">
         <v>2025</v>
       </c>
@@ -26827,7 +26207,7 @@
       </c>
       <c r="I702" s="10"/>
     </row>
-    <row r="703" ht="17" spans="1:17">
+    <row r="703" spans="1:17">
       <c r="A703" s="12">
         <v>2025</v>
       </c>
@@ -26854,7 +26234,7 @@
       </c>
       <c r="I703" s="11"/>
     </row>
-    <row r="704" ht="17" spans="1:17">
+    <row r="704" spans="1:17">
       <c r="A704" s="12">
         <v>2025</v>
       </c>
@@ -26881,7 +26261,7 @@
       </c>
       <c r="I704" s="11"/>
     </row>
-    <row r="705" ht="17" spans="1:9">
+    <row r="705" spans="1:9">
       <c r="A705" s="12">
         <v>2025</v>
       </c>
@@ -26908,7 +26288,7 @@
       </c>
       <c r="I705" s="11"/>
     </row>
-    <row r="706" ht="17" spans="1:9">
+    <row r="706" spans="1:9">
       <c r="A706" s="12">
         <v>2025</v>
       </c>
@@ -26935,7 +26315,7 @@
       </c>
       <c r="I706" s="11"/>
     </row>
-    <row r="707" ht="17" spans="1:9">
+    <row r="707" spans="1:9">
       <c r="A707" s="12">
         <v>2025</v>
       </c>
@@ -26962,7 +26342,7 @@
       </c>
       <c r="I707" s="11"/>
     </row>
-    <row r="708" ht="17" spans="1:9">
+    <row r="708" spans="1:9">
       <c r="A708" s="12">
         <v>2025</v>
       </c>
@@ -26989,7 +26369,7 @@
       </c>
       <c r="I708" s="11"/>
     </row>
-    <row r="709" ht="17" spans="1:9">
+    <row r="709" spans="1:9">
       <c r="A709" s="12">
         <v>2025</v>
       </c>
@@ -27016,7 +26396,7 @@
       </c>
       <c r="I709" s="11"/>
     </row>
-    <row r="710" ht="17" spans="1:9">
+    <row r="710" spans="1:9">
       <c r="A710" s="12">
         <v>2025</v>
       </c>
@@ -27043,7 +26423,7 @@
       </c>
       <c r="I710" s="11"/>
     </row>
-    <row r="711" ht="17" spans="1:9">
+    <row r="711" spans="1:9">
       <c r="A711" s="12">
         <v>2025</v>
       </c>
@@ -27070,7 +26450,7 @@
       </c>
       <c r="I711" s="11"/>
     </row>
-    <row r="712" ht="17" spans="1:9">
+    <row r="712" spans="1:9">
       <c r="A712" s="12">
         <v>2025</v>
       </c>
@@ -27097,7 +26477,7 @@
       </c>
       <c r="I712" s="11"/>
     </row>
-    <row r="713" ht="17" spans="1:9">
+    <row r="713" spans="1:9">
       <c r="A713" s="12">
         <v>2025</v>
       </c>
@@ -27124,7 +26504,7 @@
       </c>
       <c r="I713" s="11"/>
     </row>
-    <row r="714" ht="17" spans="1:9">
+    <row r="714" spans="1:9">
       <c r="A714" s="12">
         <v>2025</v>
       </c>
@@ -27151,7 +26531,7 @@
       </c>
       <c r="I714" s="11"/>
     </row>
-    <row r="715" ht="17" spans="1:9">
+    <row r="715" spans="1:9">
       <c r="A715" s="12">
         <v>2025</v>
       </c>
@@ -27178,7 +26558,7 @@
       </c>
       <c r="I715" s="11"/>
     </row>
-    <row r="716" ht="17" spans="1:9">
+    <row r="716" spans="1:9">
       <c r="A716" s="12">
         <v>2025</v>
       </c>
@@ -27205,7 +26585,7 @@
       </c>
       <c r="I716" s="11"/>
     </row>
-    <row r="717" ht="17" spans="1:9">
+    <row r="717" spans="1:9">
       <c r="A717" s="12">
         <v>2025</v>
       </c>
@@ -27232,7 +26612,7 @@
       </c>
       <c r="I717" s="11"/>
     </row>
-    <row r="718" ht="17" spans="1:9">
+    <row r="718" spans="1:9">
       <c r="A718" s="12">
         <v>2025</v>
       </c>
@@ -27259,7 +26639,7 @@
       </c>
       <c r="I718" s="11"/>
     </row>
-    <row r="719" ht="17" spans="1:9">
+    <row r="719" spans="1:9">
       <c r="A719" s="12">
         <v>2025</v>
       </c>
@@ -27286,7 +26666,7 @@
       </c>
       <c r="I719" s="11"/>
     </row>
-    <row r="720" ht="17" spans="1:9">
+    <row r="720" spans="1:9">
       <c r="A720" s="12">
         <v>2025</v>
       </c>
@@ -27313,7 +26693,7 @@
       </c>
       <c r="I720" s="11"/>
     </row>
-    <row r="721" ht="17" spans="1:10">
+    <row r="721" spans="1:10">
       <c r="A721" s="12">
         <v>2025</v>
       </c>
@@ -27340,7 +26720,7 @@
       </c>
       <c r="I721" s="11"/>
     </row>
-    <row r="722" ht="17" spans="1:10">
+    <row r="722" spans="1:10">
       <c r="A722" s="6">
         <v>2025</v>
       </c>
@@ -27366,7 +26746,7 @@
       <c r="I722" s="10"/>
       <c r="J722" s="10"/>
     </row>
-    <row r="723" ht="17" spans="1:10">
+    <row r="723" spans="1:10">
       <c r="A723" s="6">
         <v>2025</v>
       </c>
@@ -27392,7 +26772,7 @@
       <c r="I723" s="10"/>
       <c r="J723" s="10"/>
     </row>
-    <row r="724" ht="17" spans="1:10">
+    <row r="724" spans="1:10">
       <c r="A724" s="6">
         <v>2025</v>
       </c>
@@ -27418,7 +26798,7 @@
       <c r="I724" s="10"/>
       <c r="J724" s="10"/>
     </row>
-    <row r="725" ht="17" spans="1:10">
+    <row r="725" spans="1:10">
       <c r="A725" s="6">
         <v>2025</v>
       </c>
@@ -27444,7 +26824,7 @@
       <c r="I725" s="10"/>
       <c r="J725" s="10"/>
     </row>
-    <row r="726" ht="17" spans="1:10">
+    <row r="726" spans="1:10">
       <c r="A726" s="6">
         <v>2025</v>
       </c>
@@ -27470,7 +26850,7 @@
       <c r="I726" s="10"/>
       <c r="J726" s="10"/>
     </row>
-    <row r="727" ht="17" spans="1:10">
+    <row r="727" spans="1:10">
       <c r="A727" s="6">
         <v>2025</v>
       </c>
@@ -27496,7 +26876,7 @@
       <c r="I727" s="10"/>
       <c r="J727" s="10"/>
     </row>
-    <row r="728" ht="17" spans="1:10">
+    <row r="728" spans="1:10">
       <c r="A728" s="6">
         <v>2025</v>
       </c>
@@ -27522,7 +26902,7 @@
       <c r="I728" s="10"/>
       <c r="J728" s="10"/>
     </row>
-    <row r="729" ht="17" spans="1:10">
+    <row r="729" spans="1:10">
       <c r="A729" s="6">
         <v>2025</v>
       </c>
@@ -27548,7 +26928,7 @@
       <c r="I729" s="10"/>
       <c r="J729" s="10"/>
     </row>
-    <row r="730" ht="17" spans="1:10">
+    <row r="730" spans="1:10">
       <c r="A730" s="6">
         <v>2025</v>
       </c>
@@ -27574,7 +26954,7 @@
       <c r="I730" s="10"/>
       <c r="J730" s="10"/>
     </row>
-    <row r="731" ht="17" spans="1:10">
+    <row r="731" spans="1:10">
       <c r="A731" s="6">
         <v>2025</v>
       </c>
@@ -27600,7 +26980,7 @@
       <c r="I731" s="10"/>
       <c r="J731" s="10"/>
     </row>
-    <row r="732" ht="17" spans="1:10">
+    <row r="732" spans="1:10">
       <c r="A732" s="6">
         <v>2025</v>
       </c>
@@ -27626,7 +27006,7 @@
       <c r="I732" s="10"/>
       <c r="J732" s="11"/>
     </row>
-    <row r="733" ht="17" spans="1:10">
+    <row r="733" spans="1:10">
       <c r="A733" s="6">
         <v>2025</v>
       </c>
@@ -27652,7 +27032,7 @@
       <c r="I733" s="10"/>
       <c r="J733" s="11"/>
     </row>
-    <row r="734" ht="17" spans="1:10">
+    <row r="734" spans="1:10">
       <c r="A734" s="6">
         <v>2025</v>
       </c>
@@ -27678,7 +27058,7 @@
       <c r="I734" s="10"/>
       <c r="J734" s="11"/>
     </row>
-    <row r="735" ht="17" spans="1:10">
+    <row r="735" spans="1:10">
       <c r="A735" s="6">
         <v>2025</v>
       </c>
@@ -27704,7 +27084,7 @@
       <c r="I735" s="10"/>
       <c r="J735" s="11"/>
     </row>
-    <row r="736" ht="17" spans="1:10">
+    <row r="736" spans="1:10">
       <c r="A736" s="6">
         <v>2025</v>
       </c>
@@ -27730,7 +27110,7 @@
       <c r="I736" s="10"/>
       <c r="J736" s="11"/>
     </row>
-    <row r="737" ht="17" spans="1:10">
+    <row r="737" spans="1:10">
       <c r="A737" s="6">
         <v>2025</v>
       </c>
@@ -27756,7 +27136,7 @@
       <c r="I737" s="11"/>
       <c r="J737" s="11"/>
     </row>
-    <row r="738" ht="17" spans="1:10">
+    <row r="738" spans="1:10">
       <c r="A738" s="6">
         <v>2025</v>
       </c>
@@ -27782,7 +27162,7 @@
       <c r="I738" s="11"/>
       <c r="J738" s="11"/>
     </row>
-    <row r="739" ht="17" spans="1:10">
+    <row r="739" spans="1:10">
       <c r="A739" s="6">
         <v>2025</v>
       </c>
@@ -27808,7 +27188,7 @@
       <c r="I739" s="11"/>
       <c r="J739" s="11"/>
     </row>
-    <row r="740" ht="17" spans="1:10">
+    <row r="740" spans="1:10">
       <c r="A740" s="6">
         <v>2025</v>
       </c>
@@ -27834,7 +27214,7 @@
       <c r="I740" s="11"/>
       <c r="J740" s="11"/>
     </row>
-    <row r="741" ht="17" spans="1:10">
+    <row r="741" spans="1:10">
       <c r="A741" s="6">
         <v>2025</v>
       </c>
@@ -27860,7 +27240,7 @@
       <c r="I741" s="11"/>
       <c r="J741" s="11"/>
     </row>
-    <row r="742" ht="17" spans="1:10">
+    <row r="742" spans="1:10">
       <c r="A742" s="12">
         <v>2025</v>
       </c>
@@ -27886,7 +27266,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="743" ht="17" spans="1:10">
+    <row r="743" spans="1:10">
       <c r="A743" s="12">
         <v>2025</v>
       </c>
@@ -27912,7 +27292,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="744" ht="17" spans="1:10">
+    <row r="744" spans="1:10">
       <c r="A744" s="12">
         <v>2025</v>
       </c>
@@ -27938,7 +27318,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="745" ht="17" spans="1:10">
+    <row r="745" spans="1:10">
       <c r="A745" s="12">
         <v>2025</v>
       </c>
@@ -27964,7 +27344,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="746" ht="17" spans="1:10">
+    <row r="746" spans="1:10">
       <c r="A746" s="12">
         <v>2025</v>
       </c>
@@ -27990,7 +27370,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="747" ht="17" spans="1:10">
+    <row r="747" spans="1:10">
       <c r="A747" s="12">
         <v>2025</v>
       </c>
@@ -28016,7 +27396,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="748" ht="17" spans="1:10">
+    <row r="748" spans="1:10">
       <c r="A748" s="12">
         <v>2025</v>
       </c>
@@ -28042,7 +27422,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="749" ht="17" spans="1:10">
+    <row r="749" spans="1:10">
       <c r="A749" s="12">
         <v>2025</v>
       </c>
@@ -28068,7 +27448,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="750" ht="17" spans="1:10">
+    <row r="750" spans="1:10">
       <c r="A750" s="12">
         <v>2025</v>
       </c>
@@ -28094,7 +27474,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="751" ht="17" spans="1:10">
+    <row r="751" spans="1:10">
       <c r="A751" s="12">
         <v>2025</v>
       </c>
@@ -28120,7 +27500,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="752" ht="17" spans="1:10">
+    <row r="752" spans="1:10">
       <c r="A752" s="12">
         <v>2025</v>
       </c>
@@ -28146,7 +27526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="753" ht="17" spans="1:16">
+    <row r="753" spans="1:16">
       <c r="A753" s="12">
         <v>2025</v>
       </c>
@@ -28172,7 +27552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="754" ht="17" spans="1:16">
+    <row r="754" spans="1:16">
       <c r="A754" s="12">
         <v>2025</v>
       </c>
@@ -28198,7 +27578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="755" ht="17" spans="1:16">
+    <row r="755" spans="1:16">
       <c r="A755" s="12">
         <v>2025</v>
       </c>
@@ -28224,7 +27604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="756" ht="17" spans="1:16">
+    <row r="756" spans="1:16">
       <c r="A756" s="12">
         <v>2025</v>
       </c>
@@ -28250,7 +27630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="757" ht="17" spans="1:16">
+    <row r="757" spans="1:16">
       <c r="A757" s="12">
         <v>2025</v>
       </c>
@@ -28276,7 +27656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="758" ht="17" spans="1:16">
+    <row r="758" spans="1:16">
       <c r="A758" s="12">
         <v>2025</v>
       </c>
@@ -28302,7 +27682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="759" ht="17" spans="1:16">
+    <row r="759" spans="1:16">
       <c r="A759" s="12">
         <v>2025</v>
       </c>
@@ -28328,7 +27708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="760" ht="17" spans="1:16">
+    <row r="760" spans="1:16">
       <c r="A760" s="12">
         <v>2025</v>
       </c>
@@ -28354,7 +27734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="761" ht="17" spans="1:16">
+    <row r="761" spans="1:16">
       <c r="A761" s="12">
         <v>2025</v>
       </c>
@@ -29395,7 +28775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="801" ht="17" spans="1:8">
+    <row r="801" spans="1:8">
       <c r="A801" s="6">
         <v>2025</v>
       </c>
@@ -39466,22 +38846,18 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H1201" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
+  <autoFilter ref="A1:H1201" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="29.2857142857143" customWidth="1"/>
+    <col min="1" max="1" width="29.28515625" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -39501,7 +38877,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="3" ht="17" spans="1:2">
+    <row r="3" spans="1:2">
       <c r="A3" s="9" t="s">
         <v>79</v>
       </c>
@@ -39517,7 +38893,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="5" ht="17" spans="1:2">
+    <row r="5" spans="1:2">
       <c r="A5" s="9" t="s">
         <v>84</v>
       </c>
@@ -39549,7 +38925,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="9" ht="17" spans="1:2">
+    <row r="9" spans="1:2">
       <c r="A9" s="9" t="s">
         <v>81</v>
       </c>
@@ -39565,7 +38941,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="11" ht="17" spans="1:2">
+    <row r="11" spans="1:2">
       <c r="A11" s="9" t="s">
         <v>85</v>
       </c>
@@ -39581,7 +38957,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="13" ht="17" spans="1:2">
+    <row r="13" spans="1:2">
       <c r="A13" s="9" t="s">
         <v>82</v>
       </c>
@@ -39597,7 +38973,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="15" ht="17" spans="1:2">
+    <row r="15" spans="1:2">
       <c r="A15" s="9" t="s">
         <v>83</v>
       </c>
@@ -39613,7 +38989,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="17" ht="17" spans="1:2">
+    <row r="17" spans="1:2">
       <c r="A17" s="9" t="s">
         <v>80</v>
       </c>
@@ -39629,7 +39005,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="19" ht="17" spans="1:2">
+    <row r="19" spans="1:2">
       <c r="A19" s="9" t="s">
         <v>86</v>
       </c>
@@ -39647,24 +39023,22 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.57142857142857" customWidth="1"/>
-    <col min="2" max="2" width="15.4285714285714" customWidth="1"/>
-    <col min="3" max="3" width="9.42857142857143" customWidth="1"/>
-    <col min="4" max="4" width="42.5714285714286" customWidth="1"/>
-    <col min="5" max="5" width="32.8571428571429" customWidth="1"/>
-    <col min="6" max="6" width="11.7142857142857" customWidth="1"/>
-    <col min="7" max="7" width="4.57142857142857" customWidth="1"/>
-    <col min="8" max="8" width="6.71428571428571" customWidth="1"/>
+    <col min="1" max="1" width="7.5703125" customWidth="1"/>
+    <col min="2" max="2" width="15.42578125" customWidth="1"/>
+    <col min="3" max="3" width="9.42578125" customWidth="1"/>
+    <col min="4" max="4" width="42.5703125" customWidth="1"/>
+    <col min="5" max="5" width="32.85546875" customWidth="1"/>
+    <col min="6" max="6" width="11.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.5703125" customWidth="1"/>
+    <col min="8" max="8" width="6.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -39714,7 +39088,7 @@
         <v>58</v>
       </c>
       <c r="H2" s="6">
-        <v>5.278</v>
+        <v>5.2779999999999996</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -39738,7 +39112,7 @@
         <v>56</v>
       </c>
       <c r="H3" s="6">
-        <v>5.451</v>
+        <v>5.4509999999999996</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -39762,7 +39136,7 @@
         <v>53</v>
       </c>
       <c r="H4" s="6">
-        <v>5.807</v>
+        <v>5.8070000000000004</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -39786,7 +39160,7 @@
         <v>57</v>
       </c>
       <c r="H5" s="6">
-        <v>5.412</v>
+        <v>5.4119999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -39810,7 +39184,7 @@
         <v>50</v>
       </c>
       <c r="H6" s="6">
-        <v>5.174</v>
+        <v>5.1740000000000004</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -39836,7 +39210,7 @@
         <v>57</v>
       </c>
       <c r="H7" s="6">
-        <v>5.412</v>
+        <v>5.4119999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -39862,7 +39236,7 @@
         <v>63</v>
       </c>
       <c r="H8" s="6">
-        <v>4.909</v>
+        <v>4.9089999999999998</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -39886,7 +39260,7 @@
         <v>78</v>
       </c>
       <c r="H9" s="6">
-        <v>3.337</v>
+        <v>3.3370000000000002</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -39936,7 +39310,7 @@
         <v>70</v>
       </c>
       <c r="H11" s="6">
-        <v>4.361</v>
+        <v>4.3609999999999998</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -39960,7 +39334,7 @@
         <v>71</v>
       </c>
       <c r="H12" s="6">
-        <v>4.318</v>
+        <v>4.3179999999999996</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -40008,7 +39382,7 @@
         <v>44</v>
       </c>
       <c r="H14" s="6">
-        <v>7.004</v>
+        <v>7.0039999999999996</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -40032,7 +39406,7 @@
         <v>70</v>
       </c>
       <c r="H15" s="6">
-        <v>4.381</v>
+        <v>4.3810000000000002</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -40056,7 +39430,7 @@
         <v>72</v>
       </c>
       <c r="H16" s="6">
-        <v>4.259</v>
+        <v>4.2590000000000003</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -40082,7 +39456,7 @@
         <v>53</v>
       </c>
       <c r="H17" s="6">
-        <v>5.793</v>
+        <v>5.7930000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -40106,7 +39480,7 @@
         <v>51</v>
       </c>
       <c r="H18" s="6">
-        <v>6.003</v>
+        <v>6.0030000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -40156,7 +39530,7 @@
         <v>56</v>
       </c>
       <c r="H20" s="6">
-        <v>5.513</v>
+        <v>5.5129999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -40180,7 +39554,7 @@
         <v>71</v>
       </c>
       <c r="H21" s="6">
-        <v>4.304</v>
+        <v>4.3040000000000003</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -40204,7 +39578,7 @@
         <v>71</v>
       </c>
       <c r="H22" s="6">
-        <v>4.309</v>
+        <v>4.3090000000000002</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -40230,7 +39604,7 @@
         <v>50</v>
       </c>
       <c r="H23" s="6">
-        <v>6.201</v>
+        <v>6.2009999999999996</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -40254,7 +39628,7 @@
         <v>57</v>
       </c>
       <c r="H24" s="6">
-        <v>5.419</v>
+        <v>5.4189999999999996</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -40278,7 +39652,7 @@
         <v>58</v>
       </c>
       <c r="H25" s="6">
-        <v>5.281</v>
+        <v>5.2809999999999997</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -40304,27 +39678,25 @@
         <v>57</v>
       </c>
       <c r="H26" s="6">
-        <v>5.416</v>
+        <v>5.4160000000000004</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:G44"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.71428571428571" customWidth="1"/>
-    <col min="2" max="2" width="6.57142857142857" customWidth="1"/>
-    <col min="3" max="3" width="17.8571428571429" customWidth="1"/>
-    <col min="4" max="4" width="5.28571428571429" customWidth="1"/>
-    <col min="5" max="5" width="5.14285714285714" customWidth="1"/>
-    <col min="6" max="6" width="16.1428571428571" customWidth="1"/>
+    <col min="1" max="1" width="4.7109375" customWidth="1"/>
+    <col min="2" max="2" width="6.5703125" customWidth="1"/>
+    <col min="3" max="3" width="17.85546875" customWidth="1"/>
+    <col min="4" max="4" width="5.28515625" customWidth="1"/>
+    <col min="5" max="5" width="5.140625" customWidth="1"/>
+    <col min="6" max="6" width="16.140625" customWidth="1"/>
     <col min="7" max="7" width="12" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -41343,21 +40715,19 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:E22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4" style="1" customWidth="1"/>
-    <col min="2" max="2" width="4.85714285714286" style="1" customWidth="1"/>
+    <col min="2" max="2" width="4.85546875" style="1" customWidth="1"/>
     <col min="3" max="3" width="12" style="1" customWidth="1"/>
-    <col min="4" max="4" width="29.2857142857143" style="1" customWidth="1"/>
-    <col min="5" max="5" width="8.57142857142857" style="1" customWidth="1"/>
+    <col min="4" max="4" width="29.28515625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="8.5703125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -41736,6 +41106,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/public/docs/datas/f1.xlsx
+++ b/public/docs/datas/f1.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Docs\byMe\vue_platform\public\docs\datas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29CE998A-B2E4-4A00-A6B8-E38D27AD4A7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="660" yWindow="360" windowWidth="21285" windowHeight="15525" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="26420" windowHeight="21900" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="rounds" sheetId="7" r:id="rId1"/>
@@ -854,24 +848,174 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -890,8 +1034,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -914,9 +1244,251 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -963,17 +1535,61 @@
     <xf numFmtId="20" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1231,16 +1847,16 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:C49"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="2" width="9.5703125" customWidth="1"/>
+    <col min="1" max="2" width="9.57142857142857" customWidth="1"/>
     <col min="3" max="3" width="11" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1785,20 +2401,22 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:G241"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="5.5703125" customWidth="1"/>
-    <col min="2" max="2" width="6.28515625" customWidth="1"/>
-    <col min="3" max="3" width="19.7109375" customWidth="1"/>
-    <col min="4" max="4" width="11.28515625" customWidth="1"/>
-    <col min="5" max="6" width="9.42578125" customWidth="1"/>
-    <col min="7" max="7" width="7.42578125" customWidth="1"/>
+    <col min="1" max="1" width="5.57142857142857" customWidth="1"/>
+    <col min="2" max="2" width="6.28571428571429" customWidth="1"/>
+    <col min="3" max="3" width="19.7142857142857" customWidth="1"/>
+    <col min="4" max="4" width="11.2857142857143" customWidth="1"/>
+    <col min="5" max="6" width="9.42857142857143" customWidth="1"/>
+    <col min="7" max="7" width="7.42857142857143" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1838,7 +2456,7 @@
         <v>45730</v>
       </c>
       <c r="E2" s="20">
-        <v>0.39583333333333298</v>
+        <v>0.395833333333333</v>
       </c>
       <c r="F2" s="20">
         <v>0.4375</v>
@@ -1861,10 +2479,10 @@
         <v>45730</v>
       </c>
       <c r="E3" s="20">
-        <v>0.54166666666666696</v>
+        <v>0.541666666666667</v>
       </c>
       <c r="F3" s="20">
-        <v>0.58333333333333304</v>
+        <v>0.583333333333333</v>
       </c>
       <c r="G3" s="6">
         <v>0</v>
@@ -1884,7 +2502,7 @@
         <v>45731</v>
       </c>
       <c r="E4" s="20">
-        <v>0.39583333333333298</v>
+        <v>0.395833333333333</v>
       </c>
       <c r="F4" s="20">
         <v>0.4375</v>
@@ -1907,10 +2525,10 @@
         <v>45731</v>
       </c>
       <c r="E5" s="20">
-        <v>0.54166666666666696</v>
+        <v>0.541666666666667</v>
       </c>
       <c r="F5" s="20">
-        <v>0.58333333333333304</v>
+        <v>0.583333333333333</v>
       </c>
       <c r="G5" s="6">
         <v>1</v>
@@ -1951,10 +2569,10 @@
         <v>45737</v>
       </c>
       <c r="E7" s="22">
-        <v>0.47916666666666702</v>
+        <v>0.479166666666667</v>
       </c>
       <c r="F7" s="22">
-        <v>0.52083333333333304</v>
+        <v>0.520833333333333</v>
       </c>
       <c r="G7" s="12">
         <v>0</v>
@@ -1974,10 +2592,10 @@
         <v>45737</v>
       </c>
       <c r="E8" s="22">
-        <v>0.64583333333333304</v>
+        <v>0.645833333333333</v>
       </c>
       <c r="F8" s="22">
-        <v>0.67638888888888904</v>
+        <v>0.676388888888889</v>
       </c>
       <c r="G8" s="12">
         <v>1</v>
@@ -1997,7 +2615,7 @@
         <v>45738</v>
       </c>
       <c r="E9" s="22">
-        <v>0.45833333333333298</v>
+        <v>0.458333333333333</v>
       </c>
       <c r="F9" s="22">
         <v>0.5</v>
@@ -2023,7 +2641,7 @@
         <v>0.625</v>
       </c>
       <c r="F10" s="22">
-        <v>0.66666666666666696</v>
+        <v>0.666666666666667</v>
       </c>
       <c r="G10" s="12">
         <v>1</v>
@@ -2067,7 +2685,7 @@
         <v>0.4375</v>
       </c>
       <c r="F12" s="20">
-        <v>0.47916666666666702</v>
+        <v>0.479166666666667</v>
       </c>
       <c r="G12" s="6">
         <v>0</v>
@@ -2087,7 +2705,7 @@
         <v>45751</v>
       </c>
       <c r="E13" s="20">
-        <v>0.58333333333333304</v>
+        <v>0.583333333333333</v>
       </c>
       <c r="F13" s="20">
         <v>0.625</v>
@@ -2113,7 +2731,7 @@
         <v>0.4375</v>
       </c>
       <c r="F14" s="20">
-        <v>0.47916666666666702</v>
+        <v>0.479166666666667</v>
       </c>
       <c r="G14" s="6">
         <v>0</v>
@@ -2133,7 +2751,7 @@
         <v>45752</v>
       </c>
       <c r="E15" s="20">
-        <v>0.58333333333333304</v>
+        <v>0.583333333333333</v>
       </c>
       <c r="F15" s="20">
         <v>0.625</v>
@@ -2156,7 +2774,7 @@
         <v>45753</v>
       </c>
       <c r="E16" s="20">
-        <v>0.54166666666666696</v>
+        <v>0.541666666666667</v>
       </c>
       <c r="F16" s="6"/>
       <c r="G16" s="6">
@@ -2180,7 +2798,7 @@
         <v>0.8125</v>
       </c>
       <c r="F17" s="22">
-        <v>0.85416666666666696</v>
+        <v>0.854166666666667</v>
       </c>
       <c r="G17" s="12">
         <v>0</v>
@@ -2200,7 +2818,7 @@
         <v>45758</v>
       </c>
       <c r="E18" s="22">
-        <v>0.95833333333333304</v>
+        <v>0.958333333333333</v>
       </c>
       <c r="F18" s="22">
         <v>0</v>
@@ -2223,10 +2841,10 @@
         <v>45759</v>
       </c>
       <c r="E19" s="22">
-        <v>0.85416666666666696</v>
+        <v>0.854166666666667</v>
       </c>
       <c r="F19" s="22">
-        <v>0.89583333333333304</v>
+        <v>0.895833333333333</v>
       </c>
       <c r="G19" s="12">
         <v>0</v>
@@ -2249,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="F20" s="22">
-        <v>4.1666666666666699E-2</v>
+        <v>0.0416666666666667</v>
       </c>
       <c r="G20" s="12">
         <v>1</v>
@@ -2269,7 +2887,7 @@
         <v>45760</v>
       </c>
       <c r="E21" s="22">
-        <v>0.95833333333333304</v>
+        <v>0.958333333333333</v>
       </c>
       <c r="F21" s="12"/>
       <c r="G21" s="12">
@@ -2290,7 +2908,7 @@
         <v>45765</v>
       </c>
       <c r="E22" s="20">
-        <v>0.89583333333333304</v>
+        <v>0.895833333333333</v>
       </c>
       <c r="F22" s="20">
         <v>0.9375</v>
@@ -2313,10 +2931,10 @@
         <v>45766</v>
       </c>
       <c r="E23" s="20">
-        <v>4.1666666666666699E-2</v>
+        <v>0.0416666666666667</v>
       </c>
       <c r="F23" s="20">
-        <v>8.3333333333333301E-2</v>
+        <v>0.0833333333333333</v>
       </c>
       <c r="G23" s="6">
         <v>0</v>
@@ -2336,7 +2954,7 @@
         <v>45766</v>
       </c>
       <c r="E24" s="20">
-        <v>0.89583333333333304</v>
+        <v>0.895833333333333</v>
       </c>
       <c r="F24" s="20">
         <v>0.9375</v>
@@ -2359,10 +2977,10 @@
         <v>45767</v>
       </c>
       <c r="E25" s="20">
-        <v>4.1666666666666699E-2</v>
+        <v>0.0416666666666667</v>
       </c>
       <c r="F25" s="20">
-        <v>8.3333333333333301E-2</v>
+        <v>0.0833333333333333</v>
       </c>
       <c r="G25" s="6">
         <v>1</v>
@@ -2382,7 +3000,7 @@
         <v>45767</v>
       </c>
       <c r="E26" s="20">
-        <v>4.1666666666666699E-2</v>
+        <v>0.0416666666666667</v>
       </c>
       <c r="F26" s="6"/>
       <c r="G26" s="6">
@@ -2403,10 +3021,10 @@
         <v>45780</v>
       </c>
       <c r="E27" s="22">
-        <v>2.0833333333333301E-2</v>
+        <v>0.0208333333333333</v>
       </c>
       <c r="F27" s="22">
-        <v>6.25E-2</v>
+        <v>0.0625</v>
       </c>
       <c r="G27" s="12">
         <v>0</v>
@@ -2452,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="F29" s="22">
-        <v>4.1666666666666699E-2</v>
+        <v>0.0416666666666667</v>
       </c>
       <c r="G29" s="12">
         <v>1</v>
@@ -2472,10 +3090,10 @@
         <v>45781</v>
       </c>
       <c r="E30" s="22">
-        <v>0.16666666666666699</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="F30" s="22">
-        <v>0.20833333333333301</v>
+        <v>0.208333333333333</v>
       </c>
       <c r="G30" s="12">
         <v>1</v>
@@ -2495,7 +3113,7 @@
         <v>45782</v>
       </c>
       <c r="E31" s="22">
-        <v>0.16666666666666699</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="F31" s="22"/>
       <c r="G31" s="12">
@@ -2519,7 +3137,7 @@
         <v>0.8125</v>
       </c>
       <c r="F32" s="20">
-        <v>0.85416666666666696</v>
+        <v>0.854166666666667</v>
       </c>
       <c r="G32" s="6">
         <v>0</v>
@@ -2539,7 +3157,7 @@
         <v>45793</v>
       </c>
       <c r="E33" s="20">
-        <v>0.95833333333333304</v>
+        <v>0.958333333333333</v>
       </c>
       <c r="F33" s="20">
         <v>0</v>
@@ -2562,7 +3180,7 @@
         <v>45794</v>
       </c>
       <c r="E34" s="20">
-        <v>0.77083333333333304</v>
+        <v>0.770833333333333</v>
       </c>
       <c r="F34" s="20">
         <v>0.8125</v>
@@ -2585,10 +3203,10 @@
         <v>45794</v>
       </c>
       <c r="E35" s="20">
-        <v>0.91666666666666696</v>
+        <v>0.916666666666667</v>
       </c>
       <c r="F35" s="20">
-        <v>0.95833333333333304</v>
+        <v>0.958333333333333</v>
       </c>
       <c r="G35" s="6">
         <v>1</v>
@@ -2632,7 +3250,7 @@
         <v>0.8125</v>
       </c>
       <c r="F37" s="22">
-        <v>0.85416666666666696</v>
+        <v>0.854166666666667</v>
       </c>
       <c r="G37" s="12">
         <v>0</v>
@@ -2652,7 +3270,7 @@
         <v>45800</v>
       </c>
       <c r="E38" s="22">
-        <v>0.95833333333333304</v>
+        <v>0.958333333333333</v>
       </c>
       <c r="F38" s="22">
         <v>0</v>
@@ -2675,7 +3293,7 @@
         <v>45801</v>
       </c>
       <c r="E39" s="22">
-        <v>0.77083333333333304</v>
+        <v>0.770833333333333</v>
       </c>
       <c r="F39" s="22">
         <v>0.8125</v>
@@ -2698,10 +3316,10 @@
         <v>45801</v>
       </c>
       <c r="E40" s="22">
-        <v>0.91666666666666696</v>
+        <v>0.916666666666667</v>
       </c>
       <c r="F40" s="22">
-        <v>0.95833333333333304</v>
+        <v>0.958333333333333</v>
       </c>
       <c r="G40" s="12">
         <v>1</v>
@@ -2745,7 +3363,7 @@
         <v>0.8125</v>
       </c>
       <c r="F42" s="20">
-        <v>0.85416666666666696</v>
+        <v>0.854166666666667</v>
       </c>
       <c r="G42" s="6">
         <v>0</v>
@@ -2765,7 +3383,7 @@
         <v>45807</v>
       </c>
       <c r="E43" s="20">
-        <v>0.95833333333333304</v>
+        <v>0.958333333333333</v>
       </c>
       <c r="F43" s="20">
         <v>0</v>
@@ -2788,7 +3406,7 @@
         <v>45808</v>
       </c>
       <c r="E44" s="20">
-        <v>0.77083333333333304</v>
+        <v>0.770833333333333</v>
       </c>
       <c r="F44" s="20">
         <v>0.8125</v>
@@ -2811,10 +3429,10 @@
         <v>45808</v>
       </c>
       <c r="E45" s="20">
-        <v>0.91666666666666696</v>
+        <v>0.916666666666667</v>
       </c>
       <c r="F45" s="20">
-        <v>0.95833333333333304</v>
+        <v>0.958333333333333</v>
       </c>
       <c r="G45" s="6">
         <v>1</v>
@@ -2855,7 +3473,7 @@
         <v>45822</v>
       </c>
       <c r="E47" s="22">
-        <v>6.25E-2</v>
+        <v>0.0625</v>
       </c>
       <c r="F47" s="22">
         <v>0.104166666666667</v>
@@ -2878,7 +3496,7 @@
         <v>45822</v>
       </c>
       <c r="E48" s="22">
-        <v>0.20833333333333301</v>
+        <v>0.208333333333333</v>
       </c>
       <c r="F48" s="22">
         <v>0.25</v>
@@ -2901,10 +3519,10 @@
         <v>45823</v>
       </c>
       <c r="E49" s="22">
-        <v>2.0833333333333301E-2</v>
+        <v>0.0208333333333333</v>
       </c>
       <c r="F49" s="22">
-        <v>6.25E-2</v>
+        <v>0.0625</v>
       </c>
       <c r="G49" s="12">
         <v>0</v>
@@ -2924,10 +3542,10 @@
         <v>45823</v>
       </c>
       <c r="E50" s="22">
-        <v>0.16666666666666699</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="F50" s="22">
-        <v>0.20833333333333301</v>
+        <v>0.208333333333333</v>
       </c>
       <c r="G50" s="12">
         <v>1</v>
@@ -2947,7 +3565,7 @@
         <v>45824</v>
       </c>
       <c r="E51" s="22">
-        <v>8.3333333333333301E-2</v>
+        <v>0.0833333333333333</v>
       </c>
       <c r="F51" s="12"/>
       <c r="G51" s="12">
@@ -2971,7 +3589,7 @@
         <v>0.8125</v>
       </c>
       <c r="F52" s="20">
-        <v>0.85416666666666696</v>
+        <v>0.854166666666667</v>
       </c>
       <c r="G52" s="6">
         <v>0</v>
@@ -2991,7 +3609,7 @@
         <v>45835</v>
       </c>
       <c r="E53" s="20">
-        <v>0.95833333333333304</v>
+        <v>0.958333333333333</v>
       </c>
       <c r="F53" s="20">
         <v>0</v>
@@ -3014,7 +3632,7 @@
         <v>45836</v>
       </c>
       <c r="E54" s="20">
-        <v>0.77083333333333304</v>
+        <v>0.770833333333333</v>
       </c>
       <c r="F54" s="20">
         <v>0.8125</v>
@@ -3037,10 +3655,10 @@
         <v>45836</v>
       </c>
       <c r="E55" s="20">
-        <v>0.91666666666666696</v>
+        <v>0.916666666666667</v>
       </c>
       <c r="F55" s="20">
-        <v>0.95833333333333304</v>
+        <v>0.958333333333333</v>
       </c>
       <c r="G55" s="6">
         <v>1</v>
@@ -3084,7 +3702,7 @@
         <v>0.8125</v>
       </c>
       <c r="F57" s="22">
-        <v>0.85416666666666696</v>
+        <v>0.854166666666667</v>
       </c>
       <c r="G57" s="12">
         <v>0</v>
@@ -3104,7 +3722,7 @@
         <v>45842</v>
       </c>
       <c r="E58" s="22">
-        <v>0.95833333333333304</v>
+        <v>0.958333333333333</v>
       </c>
       <c r="F58" s="22">
         <v>0</v>
@@ -3127,7 +3745,7 @@
         <v>45843</v>
       </c>
       <c r="E59" s="22">
-        <v>0.77083333333333304</v>
+        <v>0.770833333333333</v>
       </c>
       <c r="F59" s="22">
         <v>0.8125</v>
@@ -3150,10 +3768,10 @@
         <v>45843</v>
       </c>
       <c r="E60" s="22">
-        <v>0.91666666666666696</v>
+        <v>0.916666666666667</v>
       </c>
       <c r="F60" s="22">
-        <v>0.95833333333333304</v>
+        <v>0.958333333333333</v>
       </c>
       <c r="G60" s="12">
         <v>1</v>
@@ -3173,7 +3791,7 @@
         <v>45844</v>
       </c>
       <c r="E61" s="22">
-        <v>0.91666666666666696</v>
+        <v>0.916666666666667</v>
       </c>
       <c r="F61" s="12"/>
       <c r="G61" s="12">
@@ -3197,7 +3815,7 @@
         <v>0.8125</v>
       </c>
       <c r="F62" s="20">
-        <v>0.85416666666666696</v>
+        <v>0.854166666666667</v>
       </c>
       <c r="G62" s="6">
         <v>0</v>
@@ -3243,7 +3861,7 @@
         <v>0.75</v>
       </c>
       <c r="F64" s="20">
-        <v>0.79166666666666696</v>
+        <v>0.791666666666667</v>
       </c>
       <c r="G64" s="6">
         <v>1</v>
@@ -3263,10 +3881,10 @@
         <v>45864</v>
       </c>
       <c r="E65" s="20">
-        <v>0.91666666666666696</v>
+        <v>0.916666666666667</v>
       </c>
       <c r="F65" s="20">
-        <v>0.95833333333333304</v>
+        <v>0.958333333333333</v>
       </c>
       <c r="G65" s="6">
         <v>1</v>
@@ -3310,7 +3928,7 @@
         <v>0.8125</v>
       </c>
       <c r="F67" s="22">
-        <v>0.85416666666666696</v>
+        <v>0.854166666666667</v>
       </c>
       <c r="G67" s="12">
         <v>0</v>
@@ -3330,7 +3948,7 @@
         <v>45870</v>
       </c>
       <c r="E68" s="22">
-        <v>0.95833333333333304</v>
+        <v>0.958333333333333</v>
       </c>
       <c r="F68" s="22">
         <v>0</v>
@@ -3353,7 +3971,7 @@
         <v>45871</v>
       </c>
       <c r="E69" s="22">
-        <v>0.77083333333333304</v>
+        <v>0.770833333333333</v>
       </c>
       <c r="F69" s="22">
         <v>0.8125</v>
@@ -3376,10 +3994,10 @@
         <v>45871</v>
       </c>
       <c r="E70" s="22">
-        <v>0.91666666666666696</v>
+        <v>0.916666666666667</v>
       </c>
       <c r="F70" s="22">
-        <v>0.95833333333333304</v>
+        <v>0.958333333333333</v>
       </c>
       <c r="G70" s="12">
         <v>1</v>
@@ -3420,7 +4038,7 @@
         <v>45898</v>
       </c>
       <c r="E72" s="20">
-        <v>0.77083333333333304</v>
+        <v>0.770833333333333</v>
       </c>
       <c r="F72" s="20">
         <v>0.8125</v>
@@ -3443,10 +4061,10 @@
         <v>45898</v>
       </c>
       <c r="E73" s="20">
-        <v>0.91666666666666696</v>
+        <v>0.916666666666667</v>
       </c>
       <c r="F73" s="20">
-        <v>0.95833333333333304</v>
+        <v>0.958333333333333</v>
       </c>
       <c r="G73" s="6">
         <v>0</v>
@@ -3466,10 +4084,10 @@
         <v>45899</v>
       </c>
       <c r="E74" s="20">
-        <v>0.72916666666666696</v>
+        <v>0.729166666666667</v>
       </c>
       <c r="F74" s="20">
-        <v>0.77083333333333304</v>
+        <v>0.770833333333333</v>
       </c>
       <c r="G74" s="6">
         <v>0</v>
@@ -3492,7 +4110,7 @@
         <v>0.875</v>
       </c>
       <c r="F75" s="20">
-        <v>0.91666666666666696</v>
+        <v>0.916666666666667</v>
       </c>
       <c r="G75" s="6">
         <v>1</v>
@@ -3536,7 +4154,7 @@
         <v>0.8125</v>
       </c>
       <c r="F77" s="22">
-        <v>0.85416666666666696</v>
+        <v>0.854166666666667</v>
       </c>
       <c r="G77" s="12">
         <v>0</v>
@@ -3556,7 +4174,7 @@
         <v>45905</v>
       </c>
       <c r="E78" s="22">
-        <v>0.95833333333333304</v>
+        <v>0.958333333333333</v>
       </c>
       <c r="F78" s="22">
         <v>0</v>
@@ -3579,7 +4197,7 @@
         <v>45906</v>
       </c>
       <c r="E79" s="22">
-        <v>0.77083333333333304</v>
+        <v>0.770833333333333</v>
       </c>
       <c r="F79" s="22">
         <v>0.8125</v>
@@ -3602,10 +4220,10 @@
         <v>45906</v>
       </c>
       <c r="E80" s="22">
-        <v>0.91666666666666696</v>
+        <v>0.916666666666667</v>
       </c>
       <c r="F80" s="22">
-        <v>0.95833333333333304</v>
+        <v>0.958333333333333</v>
       </c>
       <c r="G80" s="12">
         <v>1</v>
@@ -3649,7 +4267,7 @@
         <v>0.6875</v>
       </c>
       <c r="F82" s="20">
-        <v>0.72916666666666696</v>
+        <v>0.729166666666667</v>
       </c>
       <c r="G82" s="6">
         <v>0</v>
@@ -3669,7 +4287,7 @@
         <v>45919</v>
       </c>
       <c r="E83" s="20">
-        <v>0.83333333333333304</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="F83" s="20">
         <v>0.875</v>
@@ -3695,7 +4313,7 @@
         <v>0.6875</v>
       </c>
       <c r="F84" s="20">
-        <v>0.72916666666666696</v>
+        <v>0.729166666666667</v>
       </c>
       <c r="G84" s="6">
         <v>0</v>
@@ -3715,7 +4333,7 @@
         <v>45920</v>
       </c>
       <c r="E85" s="20">
-        <v>0.83333333333333304</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="F85" s="20">
         <v>0.875</v>
@@ -3738,7 +4356,7 @@
         <v>45921</v>
       </c>
       <c r="E86" s="20">
-        <v>0.79166666666666696</v>
+        <v>0.791666666666667</v>
       </c>
       <c r="F86" s="6"/>
       <c r="G86" s="6">
@@ -3759,10 +4377,10 @@
         <v>45933</v>
       </c>
       <c r="E87" s="22">
-        <v>0.72916666666666696</v>
+        <v>0.729166666666667</v>
       </c>
       <c r="F87" s="22">
-        <v>0.77083333333333304</v>
+        <v>0.770833333333333</v>
       </c>
       <c r="G87" s="12">
         <v>0</v>
@@ -3785,7 +4403,7 @@
         <v>0.875</v>
       </c>
       <c r="F88" s="22">
-        <v>0.91666666666666696</v>
+        <v>0.916666666666667</v>
       </c>
       <c r="G88" s="12">
         <v>0</v>
@@ -3805,10 +4423,10 @@
         <v>45934</v>
       </c>
       <c r="E89" s="22">
-        <v>0.72916666666666696</v>
+        <v>0.729166666666667</v>
       </c>
       <c r="F89" s="22">
-        <v>0.77083333333333304</v>
+        <v>0.770833333333333</v>
       </c>
       <c r="G89" s="12">
         <v>0</v>
@@ -3831,7 +4449,7 @@
         <v>0.875</v>
       </c>
       <c r="F90" s="22">
-        <v>0.91666666666666696</v>
+        <v>0.916666666666667</v>
       </c>
       <c r="G90" s="12">
         <v>1</v>
@@ -3851,7 +4469,7 @@
         <v>45935</v>
       </c>
       <c r="E91" s="22">
-        <v>0.83333333333333304</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="F91" s="12"/>
       <c r="G91" s="12">
@@ -3872,7 +4490,7 @@
         <v>45948</v>
       </c>
       <c r="E92" s="20">
-        <v>6.25E-2</v>
+        <v>0.0625</v>
       </c>
       <c r="F92" s="20">
         <v>0.104166666666667</v>
@@ -3895,10 +4513,10 @@
         <v>45948</v>
       </c>
       <c r="E93" s="20">
-        <v>0.22916666666666699</v>
+        <v>0.229166666666667</v>
       </c>
       <c r="F93" s="20">
-        <v>0.25972222222222202</v>
+        <v>0.259722222222222</v>
       </c>
       <c r="G93" s="6">
         <v>1</v>
@@ -3918,10 +4536,10 @@
         <v>45949</v>
       </c>
       <c r="E94" s="20">
-        <v>4.1666666666666699E-2</v>
+        <v>0.0416666666666667</v>
       </c>
       <c r="F94" s="20">
-        <v>6.25E-2</v>
+        <v>0.0625</v>
       </c>
       <c r="G94" s="6">
         <v>1</v>
@@ -3941,7 +4559,7 @@
         <v>45949</v>
       </c>
       <c r="E95" s="20">
-        <v>0.20833333333333301</v>
+        <v>0.208333333333333</v>
       </c>
       <c r="F95" s="20">
         <v>0.25</v>
@@ -3988,7 +4606,7 @@
         <v>0.104166666666667</v>
       </c>
       <c r="F97" s="22">
-        <v>0.14583333333333301</v>
+        <v>0.145833333333333</v>
       </c>
       <c r="G97" s="12">
         <v>0</v>
@@ -4011,7 +4629,7 @@
         <v>0.25</v>
       </c>
       <c r="F98" s="22">
-        <v>0.29166666666666702</v>
+        <v>0.291666666666667</v>
       </c>
       <c r="G98" s="12">
         <v>0</v>
@@ -4031,7 +4649,7 @@
         <v>45956</v>
       </c>
       <c r="E99" s="22">
-        <v>6.25E-2</v>
+        <v>0.0625</v>
       </c>
       <c r="F99" s="22">
         <v>0.104166666666667</v>
@@ -4054,7 +4672,7 @@
         <v>45956</v>
       </c>
       <c r="E100" s="22">
-        <v>0.20833333333333301</v>
+        <v>0.208333333333333</v>
       </c>
       <c r="F100" s="22">
         <v>0.25</v>
@@ -4077,7 +4695,7 @@
         <v>45957</v>
       </c>
       <c r="E101" s="22">
-        <v>0.16666666666666699</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="F101" s="12"/>
       <c r="G101" s="12">
@@ -4101,7 +4719,7 @@
         <v>0.9375</v>
       </c>
       <c r="F102" s="20">
-        <v>0.97916666666666696</v>
+        <v>0.979166666666667</v>
       </c>
       <c r="G102" s="6">
         <v>0</v>
@@ -4124,7 +4742,7 @@
         <v>0.104166666666667</v>
       </c>
       <c r="F103" s="20">
-        <v>0.13472222222222199</v>
+        <v>0.134722222222222</v>
       </c>
       <c r="G103" s="6">
         <v>1</v>
@@ -4144,10 +4762,10 @@
         <v>45969</v>
       </c>
       <c r="E104" s="20">
-        <v>0.91666666666666696</v>
+        <v>0.916666666666667</v>
       </c>
       <c r="F104" s="20">
-        <v>0.95833333333333304</v>
+        <v>0.958333333333333</v>
       </c>
       <c r="G104" s="6">
         <v>1</v>
@@ -4167,7 +4785,7 @@
         <v>45970</v>
       </c>
       <c r="E105" s="20">
-        <v>8.3333333333333301E-2</v>
+        <v>0.0833333333333333</v>
       </c>
       <c r="F105" s="20">
         <v>0.125</v>
@@ -4190,7 +4808,7 @@
         <v>45971</v>
       </c>
       <c r="E106" s="20">
-        <v>4.1666666666666699E-2</v>
+        <v>0.0416666666666667</v>
       </c>
       <c r="F106" s="6"/>
       <c r="G106" s="6">
@@ -4211,10 +4829,10 @@
         <v>45982</v>
       </c>
       <c r="E107" s="22">
-        <v>0.35416666666666702</v>
+        <v>0.354166666666667</v>
       </c>
       <c r="F107" s="22">
-        <v>0.39583333333333298</v>
+        <v>0.395833333333333</v>
       </c>
       <c r="G107" s="12">
         <v>0</v>
@@ -4237,7 +4855,7 @@
         <v>0.5</v>
       </c>
       <c r="F108" s="22">
-        <v>0.54166666666666696</v>
+        <v>0.541666666666667</v>
       </c>
       <c r="G108" s="12">
         <v>0</v>
@@ -4257,10 +4875,10 @@
         <v>45983</v>
       </c>
       <c r="E109" s="23">
-        <v>0.35416666666666702</v>
+        <v>0.354166666666667</v>
       </c>
       <c r="F109" s="23">
-        <v>0.39583333333333298</v>
+        <v>0.395833333333333</v>
       </c>
       <c r="G109" s="12">
         <v>0</v>
@@ -4283,7 +4901,7 @@
         <v>0.5</v>
       </c>
       <c r="F110" s="23">
-        <v>0.54166666666666696</v>
+        <v>0.541666666666667</v>
       </c>
       <c r="G110" s="12">
         <v>1</v>
@@ -4324,7 +4942,7 @@
         <v>45989</v>
       </c>
       <c r="E112" s="24">
-        <v>0.89583333333333304</v>
+        <v>0.895833333333333</v>
       </c>
       <c r="F112" s="24">
         <v>0.9375</v>
@@ -4347,10 +4965,10 @@
         <v>45990</v>
       </c>
       <c r="E113" s="24">
-        <v>6.25E-2</v>
+        <v>0.0625</v>
       </c>
       <c r="F113" s="24">
-        <v>9.30555555555556E-2</v>
+        <v>0.0930555555555556</v>
       </c>
       <c r="G113" s="6">
         <v>1</v>
@@ -4370,10 +4988,10 @@
         <v>45990</v>
       </c>
       <c r="E114" s="24">
-        <v>0.91666666666666696</v>
+        <v>0.916666666666667</v>
       </c>
       <c r="F114" s="24">
-        <v>0.95833333333333304</v>
+        <v>0.958333333333333</v>
       </c>
       <c r="G114" s="6">
         <v>1</v>
@@ -4393,7 +5011,7 @@
         <v>45991</v>
       </c>
       <c r="E115" s="24">
-        <v>8.3333333333333301E-2</v>
+        <v>0.0833333333333333</v>
       </c>
       <c r="F115" s="24">
         <v>0.125</v>
@@ -4437,10 +5055,10 @@
         <v>45996</v>
       </c>
       <c r="E117" s="23">
-        <v>0.72916666666666696</v>
+        <v>0.729166666666667</v>
       </c>
       <c r="F117" s="23">
-        <v>0.77083333333333304</v>
+        <v>0.770833333333333</v>
       </c>
       <c r="G117" s="12">
         <v>0</v>
@@ -4463,7 +5081,7 @@
         <v>0.875</v>
       </c>
       <c r="F118" s="23">
-        <v>0.91666666666666696</v>
+        <v>0.916666666666667</v>
       </c>
       <c r="G118" s="12">
         <v>0</v>
@@ -4483,7 +5101,7 @@
         <v>45997</v>
       </c>
       <c r="E119" s="23">
-        <v>0.77083333333333304</v>
+        <v>0.770833333333333</v>
       </c>
       <c r="F119" s="23">
         <v>0.8125</v>
@@ -4506,10 +5124,10 @@
         <v>45997</v>
       </c>
       <c r="E120" s="23">
-        <v>0.91666666666666696</v>
+        <v>0.916666666666667</v>
       </c>
       <c r="F120" s="23">
-        <v>0.95833333333333304</v>
+        <v>0.958333333333333</v>
       </c>
       <c r="G120" s="12">
         <v>1</v>
@@ -4550,7 +5168,7 @@
         <v>46087</v>
       </c>
       <c r="E122" s="20">
-        <v>0.39583333333333298</v>
+        <v>0.395833333333333</v>
       </c>
       <c r="F122" s="20">
         <v>0.4375</v>
@@ -4573,10 +5191,10 @@
         <v>46087</v>
       </c>
       <c r="E123" s="20">
-        <v>0.54166666666666696</v>
+        <v>0.541666666666667</v>
       </c>
       <c r="F123" s="20">
-        <v>0.58333333333333304</v>
+        <v>0.583333333333333</v>
       </c>
       <c r="G123" s="6">
         <v>0</v>
@@ -4596,7 +5214,7 @@
         <v>46088</v>
       </c>
       <c r="E124" s="20">
-        <v>0.39583333333333298</v>
+        <v>0.395833333333333</v>
       </c>
       <c r="F124" s="20">
         <v>0.4375</v>
@@ -4619,10 +5237,10 @@
         <v>46088</v>
       </c>
       <c r="E125" s="20">
-        <v>0.54166666666666696</v>
+        <v>0.541666666666667</v>
       </c>
       <c r="F125" s="20">
-        <v>0.58333333333333304</v>
+        <v>0.583333333333333</v>
       </c>
       <c r="G125" s="6">
         <v>1</v>
@@ -4663,10 +5281,10 @@
         <v>45729</v>
       </c>
       <c r="E127" s="22">
-        <v>0.47916666666666702</v>
+        <v>0.479166666666667</v>
       </c>
       <c r="F127" s="22">
-        <v>0.52083333333333304</v>
+        <v>0.520833333333333</v>
       </c>
       <c r="G127" s="12">
         <v>0</v>
@@ -4686,10 +5304,10 @@
         <v>45729</v>
       </c>
       <c r="E128" s="22">
-        <v>0.64583333333333304</v>
+        <v>0.645833333333333</v>
       </c>
       <c r="F128" s="22">
-        <v>0.67638888888888904</v>
+        <v>0.676388888888889</v>
       </c>
       <c r="G128" s="12">
         <v>1</v>
@@ -4709,7 +5327,7 @@
         <v>45730</v>
       </c>
       <c r="E129" s="22">
-        <v>0.45833333333333298</v>
+        <v>0.458333333333333</v>
       </c>
       <c r="F129" s="22">
         <v>0.5</v>
@@ -4735,7 +5353,7 @@
         <v>0.625</v>
       </c>
       <c r="F130" s="22">
-        <v>0.66666666666666696</v>
+        <v>0.666666666666667</v>
       </c>
       <c r="G130" s="12">
         <v>1</v>
@@ -4779,7 +5397,7 @@
         <v>0.4375</v>
       </c>
       <c r="F132" s="20">
-        <v>0.47916666666666702</v>
+        <v>0.479166666666667</v>
       </c>
       <c r="G132" s="6">
         <v>0</v>
@@ -4799,7 +5417,7 @@
         <v>45743</v>
       </c>
       <c r="E133" s="20">
-        <v>0.58333333333333304</v>
+        <v>0.583333333333333</v>
       </c>
       <c r="F133" s="20">
         <v>0.625</v>
@@ -4825,7 +5443,7 @@
         <v>0.4375</v>
       </c>
       <c r="F134" s="20">
-        <v>0.47916666666666702</v>
+        <v>0.479166666666667</v>
       </c>
       <c r="G134" s="6">
         <v>0</v>
@@ -4845,7 +5463,7 @@
         <v>45744</v>
       </c>
       <c r="E135" s="20">
-        <v>0.58333333333333304</v>
+        <v>0.583333333333333</v>
       </c>
       <c r="F135" s="20">
         <v>0.625</v>
@@ -4868,7 +5486,7 @@
         <v>45745</v>
       </c>
       <c r="E136" s="20">
-        <v>0.54166666666666696</v>
+        <v>0.541666666666667</v>
       </c>
       <c r="F136" s="6"/>
       <c r="G136" s="6">
@@ -4892,7 +5510,7 @@
         <v>0.8125</v>
       </c>
       <c r="F137" s="22">
-        <v>0.85416666666666696</v>
+        <v>0.854166666666667</v>
       </c>
       <c r="G137" s="12">
         <v>0</v>
@@ -4912,7 +5530,7 @@
         <v>45757</v>
       </c>
       <c r="E138" s="22">
-        <v>0.95833333333333304</v>
+        <v>0.958333333333333</v>
       </c>
       <c r="F138" s="22">
         <v>0</v>
@@ -4935,10 +5553,10 @@
         <v>45758</v>
       </c>
       <c r="E139" s="22">
-        <v>0.85416666666666696</v>
+        <v>0.854166666666667</v>
       </c>
       <c r="F139" s="22">
-        <v>0.89583333333333304</v>
+        <v>0.895833333333333</v>
       </c>
       <c r="G139" s="12">
         <v>0</v>
@@ -4961,7 +5579,7 @@
         <v>0</v>
       </c>
       <c r="F140" s="22">
-        <v>4.1666666666666699E-2</v>
+        <v>0.0416666666666667</v>
       </c>
       <c r="G140" s="12">
         <v>1</v>
@@ -4981,7 +5599,7 @@
         <v>45759</v>
       </c>
       <c r="E141" s="22">
-        <v>0.95833333333333304</v>
+        <v>0.958333333333333</v>
       </c>
       <c r="F141" s="12"/>
       <c r="G141" s="12">
@@ -5002,7 +5620,7 @@
         <v>45764</v>
       </c>
       <c r="E142" s="20">
-        <v>0.89583333333333304</v>
+        <v>0.895833333333333</v>
       </c>
       <c r="F142" s="20">
         <v>0.9375</v>
@@ -5025,10 +5643,10 @@
         <v>45765</v>
       </c>
       <c r="E143" s="20">
-        <v>4.1666666666666699E-2</v>
+        <v>0.0416666666666667</v>
       </c>
       <c r="F143" s="20">
-        <v>8.3333333333333301E-2</v>
+        <v>0.0833333333333333</v>
       </c>
       <c r="G143" s="6">
         <v>0</v>
@@ -5048,7 +5666,7 @@
         <v>45765</v>
       </c>
       <c r="E144" s="20">
-        <v>0.89583333333333304</v>
+        <v>0.895833333333333</v>
       </c>
       <c r="F144" s="20">
         <v>0.9375</v>
@@ -5071,10 +5689,10 @@
         <v>45766</v>
       </c>
       <c r="E145" s="20">
-        <v>4.1666666666666699E-2</v>
+        <v>0.0416666666666667</v>
       </c>
       <c r="F145" s="20">
-        <v>8.3333333333333301E-2</v>
+        <v>0.0833333333333333</v>
       </c>
       <c r="G145" s="6">
         <v>1</v>
@@ -5094,7 +5712,7 @@
         <v>45767</v>
       </c>
       <c r="E146" s="20">
-        <v>4.1666666666666699E-2</v>
+        <v>0.0416666666666667</v>
       </c>
       <c r="F146" s="6"/>
       <c r="G146" s="6">
@@ -5115,10 +5733,10 @@
         <v>45779</v>
       </c>
       <c r="E147" s="22">
-        <v>2.0833333333333301E-2</v>
+        <v>0.0208333333333333</v>
       </c>
       <c r="F147" s="22">
-        <v>6.25E-2</v>
+        <v>0.0625</v>
       </c>
       <c r="G147" s="12">
         <v>0</v>
@@ -5164,7 +5782,7 @@
         <v>0</v>
       </c>
       <c r="F149" s="22">
-        <v>4.1666666666666699E-2</v>
+        <v>0.0416666666666667</v>
       </c>
       <c r="G149" s="12">
         <v>1</v>
@@ -5184,10 +5802,10 @@
         <v>45780</v>
       </c>
       <c r="E150" s="22">
-        <v>0.16666666666666699</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="F150" s="22">
-        <v>0.20833333333333301</v>
+        <v>0.208333333333333</v>
       </c>
       <c r="G150" s="12">
         <v>1</v>
@@ -5207,7 +5825,7 @@
         <v>45781</v>
       </c>
       <c r="E151" s="22">
-        <v>0.16666666666666699</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="F151" s="22"/>
       <c r="G151" s="12">
@@ -5228,10 +5846,10 @@
         <v>45800</v>
       </c>
       <c r="E152" s="20">
-        <v>2.0833333333333301E-2</v>
+        <v>0.0208333333333333</v>
       </c>
       <c r="F152" s="20">
-        <v>6.25E-2</v>
+        <v>0.0625</v>
       </c>
       <c r="G152" s="6">
         <v>0</v>
@@ -5277,7 +5895,7 @@
         <v>0</v>
       </c>
       <c r="F154" s="20">
-        <v>4.1666666666666699E-2</v>
+        <v>0.0416666666666667</v>
       </c>
       <c r="G154" s="6">
         <v>1</v>
@@ -5297,10 +5915,10 @@
         <v>45801</v>
       </c>
       <c r="E155" s="20">
-        <v>0.16666666666666699</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="F155" s="20">
-        <v>0.20833333333333301</v>
+        <v>0.208333333333333</v>
       </c>
       <c r="G155" s="6">
         <v>1</v>
@@ -5320,7 +5938,7 @@
         <v>45802</v>
       </c>
       <c r="E156" s="20">
-        <v>0.16666666666666699</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="F156" s="6"/>
       <c r="G156" s="6">
@@ -5344,7 +5962,7 @@
         <v>0.8125</v>
       </c>
       <c r="F157" s="22">
-        <v>0.85416666666666696</v>
+        <v>0.854166666666667</v>
       </c>
       <c r="G157" s="12">
         <v>0</v>
@@ -5364,7 +5982,7 @@
         <v>45813</v>
       </c>
       <c r="E158" s="22">
-        <v>0.95833333333333304</v>
+        <v>0.958333333333333</v>
       </c>
       <c r="F158" s="22">
         <v>0</v>
@@ -5387,7 +6005,7 @@
         <v>45814</v>
       </c>
       <c r="E159" s="22">
-        <v>0.77083333333333304</v>
+        <v>0.770833333333333</v>
       </c>
       <c r="F159" s="22">
         <v>0.8125</v>
@@ -5410,10 +6028,10 @@
         <v>45814</v>
       </c>
       <c r="E160" s="22">
-        <v>0.91666666666666696</v>
+        <v>0.916666666666667</v>
       </c>
       <c r="F160" s="22">
-        <v>0.95833333333333304</v>
+        <v>0.958333333333333</v>
       </c>
       <c r="G160" s="12">
         <v>1</v>
@@ -5457,7 +6075,7 @@
         <v>0.8125</v>
       </c>
       <c r="F162" s="20">
-        <v>0.85416666666666696</v>
+        <v>0.854166666666667</v>
       </c>
       <c r="G162" s="6">
         <v>0</v>
@@ -5477,7 +6095,7 @@
         <v>45820</v>
       </c>
       <c r="E163" s="20">
-        <v>0.95833333333333304</v>
+        <v>0.958333333333333</v>
       </c>
       <c r="F163" s="20">
         <v>0</v>
@@ -5500,7 +6118,7 @@
         <v>45821</v>
       </c>
       <c r="E164" s="20">
-        <v>0.77083333333333304</v>
+        <v>0.770833333333333</v>
       </c>
       <c r="F164" s="20">
         <v>0.8125</v>
@@ -5523,10 +6141,10 @@
         <v>45821</v>
       </c>
       <c r="E165" s="20">
-        <v>0.91666666666666696</v>
+        <v>0.916666666666667</v>
       </c>
       <c r="F165" s="20">
-        <v>0.95833333333333304</v>
+        <v>0.958333333333333</v>
       </c>
       <c r="G165" s="6">
         <v>1</v>
@@ -5570,7 +6188,7 @@
         <v>0.8125</v>
       </c>
       <c r="F167" s="22">
-        <v>0.85416666666666696</v>
+        <v>0.854166666666667</v>
       </c>
       <c r="G167" s="12">
         <v>0</v>
@@ -5590,7 +6208,7 @@
         <v>45834</v>
       </c>
       <c r="E168" s="22">
-        <v>0.95833333333333304</v>
+        <v>0.958333333333333</v>
       </c>
       <c r="F168" s="22">
         <v>0</v>
@@ -5613,7 +6231,7 @@
         <v>45835</v>
       </c>
       <c r="E169" s="22">
-        <v>0.77083333333333304</v>
+        <v>0.770833333333333</v>
       </c>
       <c r="F169" s="22">
         <v>0.8125</v>
@@ -5636,10 +6254,10 @@
         <v>45835</v>
       </c>
       <c r="E170" s="22">
-        <v>0.91666666666666696</v>
+        <v>0.916666666666667</v>
       </c>
       <c r="F170" s="22">
-        <v>0.95833333333333304</v>
+        <v>0.958333333333333</v>
       </c>
       <c r="G170" s="12">
         <v>1</v>
@@ -5683,7 +6301,7 @@
         <v>0.8125</v>
       </c>
       <c r="F172" s="20">
-        <v>0.85416666666666696</v>
+        <v>0.854166666666667</v>
       </c>
       <c r="G172" s="6">
         <v>0</v>
@@ -5703,10 +6321,10 @@
         <v>45841</v>
       </c>
       <c r="E173" s="20">
-        <v>0.97916666666666696</v>
+        <v>0.979166666666667</v>
       </c>
       <c r="F173" s="20">
-        <v>9.7222222222222206E-3</v>
+        <v>0.00972222222222222</v>
       </c>
       <c r="G173" s="6">
         <v>1</v>
@@ -5726,10 +6344,10 @@
         <v>45842</v>
       </c>
       <c r="E174" s="20">
-        <v>0.79166666666666696</v>
+        <v>0.791666666666667</v>
       </c>
       <c r="F174" s="20">
-        <v>0.83333333333333304</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="G174" s="6">
         <v>1</v>
@@ -5749,7 +6367,7 @@
         <v>45842</v>
       </c>
       <c r="E175" s="20">
-        <v>0.95833333333333304</v>
+        <v>0.958333333333333</v>
       </c>
       <c r="F175" s="20">
         <v>0</v>
@@ -5772,7 +6390,7 @@
         <v>45843</v>
       </c>
       <c r="E176" s="20">
-        <v>0.91666666666666696</v>
+        <v>0.916666666666667</v>
       </c>
       <c r="F176" s="6"/>
       <c r="G176" s="6">
@@ -5796,7 +6414,7 @@
         <v>0.8125</v>
       </c>
       <c r="F177" s="22">
-        <v>0.85416666666666696</v>
+        <v>0.854166666666667</v>
       </c>
       <c r="G177" s="12">
         <v>0</v>
@@ -5816,7 +6434,7 @@
         <v>45855</v>
       </c>
       <c r="E178" s="22">
-        <v>0.95833333333333304</v>
+        <v>0.958333333333333</v>
       </c>
       <c r="F178" s="22">
         <v>0</v>
@@ -5839,7 +6457,7 @@
         <v>45856</v>
       </c>
       <c r="E179" s="22">
-        <v>0.77083333333333304</v>
+        <v>0.770833333333333</v>
       </c>
       <c r="F179" s="22">
         <v>0.8125</v>
@@ -5862,10 +6480,10 @@
         <v>45856</v>
       </c>
       <c r="E180" s="22">
-        <v>0.91666666666666696</v>
+        <v>0.916666666666667</v>
       </c>
       <c r="F180" s="22">
-        <v>0.95833333333333304</v>
+        <v>0.958333333333333</v>
       </c>
       <c r="G180" s="12">
         <v>1</v>
@@ -5909,7 +6527,7 @@
         <v>0.8125</v>
       </c>
       <c r="F182" s="20">
-        <v>0.85416666666666696</v>
+        <v>0.854166666666667</v>
       </c>
       <c r="G182" s="6">
         <v>0</v>
@@ -5955,7 +6573,7 @@
         <v>0.75</v>
       </c>
       <c r="F184" s="20">
-        <v>0.79166666666666696</v>
+        <v>0.791666666666667</v>
       </c>
       <c r="G184" s="6">
         <v>0</v>
@@ -5975,10 +6593,10 @@
         <v>45863</v>
       </c>
       <c r="E185" s="20">
-        <v>0.91666666666666696</v>
+        <v>0.916666666666667</v>
       </c>
       <c r="F185" s="20">
-        <v>0.95833333333333304</v>
+        <v>0.958333333333333</v>
       </c>
       <c r="G185" s="6">
         <v>1</v>
@@ -6019,7 +6637,7 @@
         <v>45890</v>
       </c>
       <c r="E187" s="22">
-        <v>0.77083333333333304</v>
+        <v>0.770833333333333</v>
       </c>
       <c r="F187" s="22">
         <v>0.8125</v>
@@ -6045,7 +6663,7 @@
         <v>0.9375</v>
       </c>
       <c r="F188" s="22">
-        <v>0.97916666666666696</v>
+        <v>0.979166666666667</v>
       </c>
       <c r="G188" s="12">
         <v>1</v>
@@ -6068,7 +6686,7 @@
         <v>0.75</v>
       </c>
       <c r="F189" s="22">
-        <v>0.79166666666666696</v>
+        <v>0.791666666666667</v>
       </c>
       <c r="G189" s="12">
         <v>1</v>
@@ -6088,10 +6706,10 @@
         <v>45891</v>
       </c>
       <c r="E190" s="22">
-        <v>0.91666666666666696</v>
+        <v>0.916666666666667</v>
       </c>
       <c r="F190" s="22">
-        <v>0.95833333333333304</v>
+        <v>0.958333333333333</v>
       </c>
       <c r="G190" s="12">
         <v>1</v>
@@ -6132,7 +6750,7 @@
         <v>45904</v>
       </c>
       <c r="E192" s="20">
-        <v>0.77083333333333304</v>
+        <v>0.770833333333333</v>
       </c>
       <c r="F192" s="20">
         <v>0.8125</v>
@@ -6155,10 +6773,10 @@
         <v>45904</v>
       </c>
       <c r="E193" s="20">
-        <v>0.91666666666666696</v>
+        <v>0.916666666666667</v>
       </c>
       <c r="F193" s="20">
-        <v>0.95833333333333304</v>
+        <v>0.958333333333333</v>
       </c>
       <c r="G193" s="6">
         <v>0</v>
@@ -6178,7 +6796,7 @@
         <v>45905</v>
       </c>
       <c r="E194" s="20">
-        <v>0.77083333333333304</v>
+        <v>0.770833333333333</v>
       </c>
       <c r="F194" s="20">
         <v>0.8125</v>
@@ -6201,10 +6819,10 @@
         <v>45905</v>
       </c>
       <c r="E195" s="20">
-        <v>0.91666666666666696</v>
+        <v>0.916666666666667</v>
       </c>
       <c r="F195" s="20">
-        <v>0.95833333333333304</v>
+        <v>0.958333333333333</v>
       </c>
       <c r="G195" s="6">
         <v>1</v>
@@ -6248,7 +6866,7 @@
         <v>0.8125</v>
       </c>
       <c r="F197" s="22">
-        <v>0.85416666666666696</v>
+        <v>0.854166666666667</v>
       </c>
       <c r="G197" s="12">
         <v>0</v>
@@ -6268,7 +6886,7 @@
         <v>45911</v>
       </c>
       <c r="E198" s="22">
-        <v>0.95833333333333304</v>
+        <v>0.958333333333333</v>
       </c>
       <c r="F198" s="22">
         <v>0</v>
@@ -6291,7 +6909,7 @@
         <v>45912</v>
       </c>
       <c r="E199" s="22">
-        <v>0.77083333333333304</v>
+        <v>0.770833333333333</v>
       </c>
       <c r="F199" s="22">
         <v>0.8125</v>
@@ -6314,10 +6932,10 @@
         <v>45912</v>
       </c>
       <c r="E200" s="22">
-        <v>0.91666666666666696</v>
+        <v>0.916666666666667</v>
       </c>
       <c r="F200" s="22">
-        <v>0.95833333333333304</v>
+        <v>0.958333333333333</v>
       </c>
       <c r="G200" s="12">
         <v>1</v>
@@ -6361,7 +6979,7 @@
         <v>0.6875</v>
       </c>
       <c r="F202" s="20">
-        <v>0.72916666666666696</v>
+        <v>0.729166666666667</v>
       </c>
       <c r="G202" s="6">
         <v>0</v>
@@ -6381,7 +6999,7 @@
         <v>45924</v>
       </c>
       <c r="E203" s="20">
-        <v>0.83333333333333304</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="F203" s="20">
         <v>0.875</v>
@@ -6407,7 +7025,7 @@
         <v>0.6875</v>
       </c>
       <c r="F204" s="20">
-        <v>0.72916666666666696</v>
+        <v>0.729166666666667</v>
       </c>
       <c r="G204" s="6">
         <v>0</v>
@@ -6427,7 +7045,7 @@
         <v>45925</v>
       </c>
       <c r="E205" s="20">
-        <v>0.83333333333333304</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="F205" s="20">
         <v>0.875</v>
@@ -6450,7 +7068,7 @@
         <v>45926</v>
       </c>
       <c r="E206" s="20">
-        <v>0.79166666666666696</v>
+        <v>0.791666666666667</v>
       </c>
       <c r="F206" s="6"/>
       <c r="G206" s="6">
@@ -6474,7 +7092,7 @@
         <v>0.6875</v>
       </c>
       <c r="F207" s="22">
-        <v>0.72916666666666696</v>
+        <v>0.729166666666667</v>
       </c>
       <c r="G207" s="12">
         <v>0</v>
@@ -6494,10 +7112,10 @@
         <v>45939</v>
       </c>
       <c r="E208" s="22">
-        <v>0.85416666666666696</v>
+        <v>0.854166666666667</v>
       </c>
       <c r="F208" s="22">
-        <v>0.88472222222222197</v>
+        <v>0.884722222222222</v>
       </c>
       <c r="G208" s="12">
         <v>1</v>
@@ -6517,7 +7135,7 @@
         <v>45940</v>
       </c>
       <c r="E209" s="22">
-        <v>0.70833333333333304</v>
+        <v>0.708333333333333</v>
       </c>
       <c r="F209" s="22">
         <v>0.75</v>
@@ -6543,7 +7161,7 @@
         <v>0.875</v>
       </c>
       <c r="F210" s="22">
-        <v>0.91666666666666696</v>
+        <v>0.916666666666667</v>
       </c>
       <c r="G210" s="12">
         <v>1</v>
@@ -6563,7 +7181,7 @@
         <v>45941</v>
       </c>
       <c r="E211" s="22">
-        <v>0.83333333333333304</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="F211" s="12"/>
       <c r="G211" s="12">
@@ -6584,7 +7202,7 @@
         <v>45954</v>
       </c>
       <c r="E212" s="20">
-        <v>6.25E-2</v>
+        <v>0.0625</v>
       </c>
       <c r="F212" s="20">
         <v>0.104166666666667</v>
@@ -6607,7 +7225,7 @@
         <v>45954</v>
       </c>
       <c r="E213" s="20">
-        <v>0.20833333333333301</v>
+        <v>0.208333333333333</v>
       </c>
       <c r="F213" s="20">
         <v>0.25</v>
@@ -6630,7 +7248,7 @@
         <v>45955</v>
       </c>
       <c r="E214" s="20">
-        <v>6.25E-2</v>
+        <v>0.0625</v>
       </c>
       <c r="F214" s="20">
         <v>0.104166666666667</v>
@@ -6653,7 +7271,7 @@
         <v>45955</v>
       </c>
       <c r="E215" s="20">
-        <v>0.20833333333333301</v>
+        <v>0.208333333333333</v>
       </c>
       <c r="F215" s="20">
         <v>0.25</v>
@@ -6676,7 +7294,7 @@
         <v>45956</v>
       </c>
       <c r="E216" s="20">
-        <v>0.16666666666666699</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="F216" s="6"/>
       <c r="G216" s="6">
@@ -6700,7 +7318,7 @@
         <v>0.104166666666667</v>
       </c>
       <c r="F217" s="22">
-        <v>0.14583333333333301</v>
+        <v>0.145833333333333</v>
       </c>
       <c r="G217" s="12">
         <v>0</v>
@@ -6723,7 +7341,7 @@
         <v>0.25</v>
       </c>
       <c r="F218" s="22">
-        <v>0.29166666666666702</v>
+        <v>0.291666666666667</v>
       </c>
       <c r="G218" s="12">
         <v>0</v>
@@ -6743,7 +7361,7 @@
         <v>45962</v>
       </c>
       <c r="E219" s="22">
-        <v>6.25E-2</v>
+        <v>0.0625</v>
       </c>
       <c r="F219" s="22">
         <v>0.104166666666667</v>
@@ -6766,7 +7384,7 @@
         <v>45962</v>
       </c>
       <c r="E220" s="22">
-        <v>0.20833333333333301</v>
+        <v>0.208333333333333</v>
       </c>
       <c r="F220" s="22">
         <v>0.25</v>
@@ -6789,7 +7407,7 @@
         <v>45963</v>
       </c>
       <c r="E221" s="22">
-        <v>0.16666666666666699</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="F221" s="12"/>
       <c r="G221" s="12">
@@ -6810,10 +7428,10 @@
         <v>45967</v>
       </c>
       <c r="E222" s="20">
-        <v>0.97916666666666696</v>
+        <v>0.979166666666667</v>
       </c>
       <c r="F222" s="20">
-        <v>2.0833333333333301E-2</v>
+        <v>0.0208333333333333</v>
       </c>
       <c r="G222" s="6">
         <v>0</v>
@@ -6836,7 +7454,7 @@
         <v>0.125</v>
       </c>
       <c r="F223" s="20">
-        <v>0.16666666666666699</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="G223" s="6">
         <v>0</v>
@@ -6859,7 +7477,7 @@
         <v>0.9375</v>
       </c>
       <c r="F224" s="20">
-        <v>0.97916666666666696</v>
+        <v>0.979166666666667</v>
       </c>
       <c r="G224" s="6">
         <v>0</v>
@@ -6879,7 +7497,7 @@
         <v>45969</v>
       </c>
       <c r="E225" s="20">
-        <v>8.3333333333333301E-2</v>
+        <v>0.0833333333333333</v>
       </c>
       <c r="F225" s="20">
         <v>0.125</v>
@@ -6902,7 +7520,7 @@
         <v>45970</v>
       </c>
       <c r="E226" s="20">
-        <v>4.1666666666666699E-2</v>
+        <v>0.0416666666666667</v>
       </c>
       <c r="F226" s="6"/>
       <c r="G226" s="6">
@@ -6923,10 +7541,10 @@
         <v>45981</v>
       </c>
       <c r="E227" s="22">
-        <v>0.35416666666666702</v>
+        <v>0.354166666666667</v>
       </c>
       <c r="F227" s="22">
-        <v>0.39583333333333298</v>
+        <v>0.395833333333333</v>
       </c>
       <c r="G227" s="12">
         <v>0</v>
@@ -6949,7 +7567,7 @@
         <v>0.5</v>
       </c>
       <c r="F228" s="22">
-        <v>0.54166666666666696</v>
+        <v>0.541666666666667</v>
       </c>
       <c r="G228" s="12">
         <v>0</v>
@@ -6969,10 +7587,10 @@
         <v>45982</v>
       </c>
       <c r="E229" s="23">
-        <v>0.35416666666666702</v>
+        <v>0.354166666666667</v>
       </c>
       <c r="F229" s="23">
-        <v>0.39583333333333298</v>
+        <v>0.395833333333333</v>
       </c>
       <c r="G229" s="12">
         <v>0</v>
@@ -6995,7 +7613,7 @@
         <v>0.5</v>
       </c>
       <c r="F230" s="23">
-        <v>0.54166666666666696</v>
+        <v>0.541666666666667</v>
       </c>
       <c r="G230" s="12">
         <v>1</v>
@@ -7036,7 +7654,7 @@
         <v>45988</v>
       </c>
       <c r="E232" s="24">
-        <v>0.89583333333333304</v>
+        <v>0.895833333333333</v>
       </c>
       <c r="F232" s="24">
         <v>0.9375</v>
@@ -7059,10 +7677,10 @@
         <v>45989</v>
       </c>
       <c r="E233" s="24">
-        <v>4.1666666666666699E-2</v>
+        <v>0.0416666666666667</v>
       </c>
       <c r="F233" s="24">
-        <v>8.3333333333333301E-2</v>
+        <v>0.0833333333333333</v>
       </c>
       <c r="G233" s="6">
         <v>0</v>
@@ -7085,7 +7703,7 @@
         <v>0.9375</v>
       </c>
       <c r="F234" s="20">
-        <v>0.97916666666666696</v>
+        <v>0.979166666666667</v>
       </c>
       <c r="G234" s="6">
         <v>0</v>
@@ -7105,7 +7723,7 @@
         <v>45990</v>
       </c>
       <c r="E235" s="20">
-        <v>8.3333333333333301E-2</v>
+        <v>0.0833333333333333</v>
       </c>
       <c r="F235" s="20">
         <v>0.125</v>
@@ -7149,10 +7767,10 @@
         <v>45995</v>
       </c>
       <c r="E237" s="23">
-        <v>0.72916666666666696</v>
+        <v>0.729166666666667</v>
       </c>
       <c r="F237" s="23">
-        <v>0.77083333333333304</v>
+        <v>0.770833333333333</v>
       </c>
       <c r="G237" s="12">
         <v>0</v>
@@ -7175,7 +7793,7 @@
         <v>0.875</v>
       </c>
       <c r="F238" s="23">
-        <v>0.91666666666666696</v>
+        <v>0.916666666666667</v>
       </c>
       <c r="G238" s="12">
         <v>0</v>
@@ -7195,7 +7813,7 @@
         <v>45996</v>
       </c>
       <c r="E239" s="23">
-        <v>0.77083333333333304</v>
+        <v>0.770833333333333</v>
       </c>
       <c r="F239" s="23">
         <v>0.8125</v>
@@ -7218,10 +7836,10 @@
         <v>45996</v>
       </c>
       <c r="E240" s="23">
-        <v>0.91666666666666696</v>
+        <v>0.916666666666667</v>
       </c>
       <c r="F240" s="23">
-        <v>0.95833333333333304</v>
+        <v>0.958333333333333</v>
       </c>
       <c r="G240" s="12">
         <v>1</v>
@@ -7250,22 +7868,24 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:R1201"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
-    <col min="2" max="2" width="6.28515625" customWidth="1"/>
-    <col min="3" max="3" width="15.5703125" customWidth="1"/>
-    <col min="4" max="4" width="8.28515625" customWidth="1"/>
-    <col min="5" max="5" width="8.85546875" customWidth="1"/>
+    <col min="2" max="2" width="6.28571428571429" customWidth="1"/>
+    <col min="3" max="3" width="15.5714285714286" customWidth="1"/>
+    <col min="4" max="4" width="8.28571428571429" customWidth="1"/>
+    <col min="5" max="5" width="8.85714285714286" customWidth="1"/>
     <col min="6" max="6" width="17" customWidth="1"/>
-    <col min="7" max="7" width="29.28515625" customWidth="1"/>
-    <col min="8" max="10" width="12.7109375"/>
+    <col min="7" max="7" width="29.2857142857143" customWidth="1"/>
+    <col min="8" max="10" width="12.7142857142857"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17">
@@ -18618,7 +19238,7 @@
       <c r="N421" s="10"/>
       <c r="O421" s="11"/>
     </row>
-    <row r="422" spans="1:15">
+    <row r="422" ht="17" spans="1:15">
       <c r="A422" s="12">
         <v>2025</v>
       </c>
@@ -18650,7 +19270,7 @@
       <c r="N422" s="11"/>
       <c r="O422" s="11"/>
     </row>
-    <row r="423" spans="1:15">
+    <row r="423" ht="17" spans="1:15">
       <c r="A423" s="12">
         <v>2025</v>
       </c>
@@ -18682,7 +19302,7 @@
       <c r="N423" s="11"/>
       <c r="O423" s="11"/>
     </row>
-    <row r="424" spans="1:15">
+    <row r="424" ht="17" spans="1:15">
       <c r="A424" s="12">
         <v>2025</v>
       </c>
@@ -18714,7 +19334,7 @@
       <c r="N424" s="11"/>
       <c r="O424" s="11"/>
     </row>
-    <row r="425" spans="1:15">
+    <row r="425" ht="17" spans="1:15">
       <c r="A425" s="12">
         <v>2025</v>
       </c>
@@ -18746,7 +19366,7 @@
       <c r="N425" s="11"/>
       <c r="O425" s="11"/>
     </row>
-    <row r="426" spans="1:15">
+    <row r="426" ht="17" spans="1:15">
       <c r="A426" s="12">
         <v>2025</v>
       </c>
@@ -18778,7 +19398,7 @@
       <c r="N426" s="11"/>
       <c r="O426" s="11"/>
     </row>
-    <row r="427" spans="1:15">
+    <row r="427" ht="17" spans="1:15">
       <c r="A427" s="12">
         <v>2025</v>
       </c>
@@ -18810,7 +19430,7 @@
       <c r="N427" s="11"/>
       <c r="O427" s="11"/>
     </row>
-    <row r="428" spans="1:15">
+    <row r="428" ht="17" spans="1:15">
       <c r="A428" s="12">
         <v>2025</v>
       </c>
@@ -18842,7 +19462,7 @@
       <c r="N428" s="11"/>
       <c r="O428" s="11"/>
     </row>
-    <row r="429" spans="1:15">
+    <row r="429" ht="17" spans="1:15">
       <c r="A429" s="12">
         <v>2025</v>
       </c>
@@ -18874,7 +19494,7 @@
       <c r="N429" s="11"/>
       <c r="O429" s="11"/>
     </row>
-    <row r="430" spans="1:15">
+    <row r="430" ht="17" spans="1:15">
       <c r="A430" s="12">
         <v>2025</v>
       </c>
@@ -18906,7 +19526,7 @@
       <c r="N430" s="11"/>
       <c r="O430" s="11"/>
     </row>
-    <row r="431" spans="1:15">
+    <row r="431" ht="17" spans="1:15">
       <c r="A431" s="12">
         <v>2025</v>
       </c>
@@ -18938,7 +19558,7 @@
       <c r="N431" s="11"/>
       <c r="O431" s="11"/>
     </row>
-    <row r="432" spans="1:15">
+    <row r="432" ht="17" spans="1:15">
       <c r="A432" s="12">
         <v>2025</v>
       </c>
@@ -18970,7 +19590,7 @@
       <c r="N432" s="11"/>
       <c r="O432" s="11"/>
     </row>
-    <row r="433" spans="1:15">
+    <row r="433" ht="17" spans="1:15">
       <c r="A433" s="12">
         <v>2025</v>
       </c>
@@ -19002,7 +19622,7 @@
       <c r="N433" s="11"/>
       <c r="O433" s="11"/>
     </row>
-    <row r="434" spans="1:15">
+    <row r="434" ht="17" spans="1:15">
       <c r="A434" s="12">
         <v>2025</v>
       </c>
@@ -19034,7 +19654,7 @@
       <c r="N434" s="11"/>
       <c r="O434" s="11"/>
     </row>
-    <row r="435" spans="1:15">
+    <row r="435" ht="17" spans="1:15">
       <c r="A435" s="12">
         <v>2025</v>
       </c>
@@ -19066,7 +19686,7 @@
       <c r="N435" s="11"/>
       <c r="O435" s="11"/>
     </row>
-    <row r="436" spans="1:15">
+    <row r="436" ht="17" spans="1:15">
       <c r="A436" s="12">
         <v>2025</v>
       </c>
@@ -19098,7 +19718,7 @@
       <c r="N436" s="11"/>
       <c r="O436" s="11"/>
     </row>
-    <row r="437" spans="1:15">
+    <row r="437" ht="17" spans="1:15">
       <c r="A437" s="12">
         <v>2025</v>
       </c>
@@ -19130,7 +19750,7 @@
       <c r="N437" s="11"/>
       <c r="O437" s="11"/>
     </row>
-    <row r="438" spans="1:15">
+    <row r="438" ht="17" spans="1:15">
       <c r="A438" s="12">
         <v>2025</v>
       </c>
@@ -19162,7 +19782,7 @@
       <c r="N438" s="11"/>
       <c r="O438" s="11"/>
     </row>
-    <row r="439" spans="1:15">
+    <row r="439" ht="17" spans="1:15">
       <c r="A439" s="12">
         <v>2025</v>
       </c>
@@ -19194,7 +19814,7 @@
       <c r="N439" s="11"/>
       <c r="O439" s="11"/>
     </row>
-    <row r="440" spans="1:15">
+    <row r="440" ht="17" spans="1:15">
       <c r="A440" s="12">
         <v>2025</v>
       </c>
@@ -19220,7 +19840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="441" spans="1:15">
+    <row r="441" ht="17" spans="1:15">
       <c r="A441" s="12">
         <v>2025</v>
       </c>
@@ -19244,7 +19864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="442" spans="1:15">
+    <row r="442" ht="17" spans="1:15">
       <c r="A442" s="6">
         <v>2025</v>
       </c>
@@ -19270,7 +19890,7 @@
       <c r="I442" s="10"/>
       <c r="J442" s="10"/>
     </row>
-    <row r="443" spans="1:15">
+    <row r="443" ht="17" spans="1:15">
       <c r="A443" s="6">
         <v>2025</v>
       </c>
@@ -19296,7 +19916,7 @@
       <c r="I443" s="10"/>
       <c r="J443" s="10"/>
     </row>
-    <row r="444" spans="1:15">
+    <row r="444" ht="17" spans="1:15">
       <c r="A444" s="6">
         <v>2025</v>
       </c>
@@ -19322,7 +19942,7 @@
       <c r="I444" s="10"/>
       <c r="J444" s="10"/>
     </row>
-    <row r="445" spans="1:15">
+    <row r="445" ht="17" spans="1:15">
       <c r="A445" s="6">
         <v>2025</v>
       </c>
@@ -19348,7 +19968,7 @@
       <c r="I445" s="10"/>
       <c r="J445" s="10"/>
     </row>
-    <row r="446" spans="1:15">
+    <row r="446" ht="17" spans="1:15">
       <c r="A446" s="6">
         <v>2025</v>
       </c>
@@ -19374,7 +19994,7 @@
       <c r="I446" s="10"/>
       <c r="J446" s="10"/>
     </row>
-    <row r="447" spans="1:15">
+    <row r="447" ht="17" spans="1:15">
       <c r="A447" s="6">
         <v>2025</v>
       </c>
@@ -19400,7 +20020,7 @@
       <c r="I447" s="10"/>
       <c r="J447" s="10"/>
     </row>
-    <row r="448" spans="1:15">
+    <row r="448" ht="17" spans="1:15">
       <c r="A448" s="6">
         <v>2025</v>
       </c>
@@ -19426,7 +20046,7 @@
       <c r="I448" s="10"/>
       <c r="J448" s="10"/>
     </row>
-    <row r="449" spans="1:10">
+    <row r="449" ht="17" spans="1:10">
       <c r="A449" s="6">
         <v>2025</v>
       </c>
@@ -19452,7 +20072,7 @@
       <c r="I449" s="10"/>
       <c r="J449" s="10"/>
     </row>
-    <row r="450" spans="1:10">
+    <row r="450" ht="17" spans="1:10">
       <c r="A450" s="6">
         <v>2025</v>
       </c>
@@ -19478,7 +20098,7 @@
       <c r="I450" s="10"/>
       <c r="J450" s="10"/>
     </row>
-    <row r="451" spans="1:10">
+    <row r="451" ht="17" spans="1:10">
       <c r="A451" s="6">
         <v>2025</v>
       </c>
@@ -19504,7 +20124,7 @@
       <c r="I451" s="10"/>
       <c r="J451" s="10"/>
     </row>
-    <row r="452" spans="1:10">
+    <row r="452" ht="17" spans="1:10">
       <c r="A452" s="6">
         <v>2025</v>
       </c>
@@ -19530,7 +20150,7 @@
       <c r="I452" s="10"/>
       <c r="J452" s="11"/>
     </row>
-    <row r="453" spans="1:10">
+    <row r="453" ht="17" spans="1:10">
       <c r="A453" s="6">
         <v>2025</v>
       </c>
@@ -19556,7 +20176,7 @@
       <c r="I453" s="10"/>
       <c r="J453" s="11"/>
     </row>
-    <row r="454" spans="1:10">
+    <row r="454" ht="17" spans="1:10">
       <c r="A454" s="6">
         <v>2025</v>
       </c>
@@ -19582,7 +20202,7 @@
       <c r="I454" s="10"/>
       <c r="J454" s="11"/>
     </row>
-    <row r="455" spans="1:10">
+    <row r="455" ht="17" spans="1:10">
       <c r="A455" s="6">
         <v>2025</v>
       </c>
@@ -19608,7 +20228,7 @@
       <c r="I455" s="10"/>
       <c r="J455" s="11"/>
     </row>
-    <row r="456" spans="1:10">
+    <row r="456" ht="17" spans="1:10">
       <c r="A456" s="6">
         <v>2025</v>
       </c>
@@ -19634,7 +20254,7 @@
       <c r="I456" s="10"/>
       <c r="J456" s="11"/>
     </row>
-    <row r="457" spans="1:10">
+    <row r="457" ht="17" spans="1:10">
       <c r="A457" s="6">
         <v>2025</v>
       </c>
@@ -19660,7 +20280,7 @@
       <c r="I457" s="11"/>
       <c r="J457" s="11"/>
     </row>
-    <row r="458" spans="1:10">
+    <row r="458" ht="17" spans="1:10">
       <c r="A458" s="6">
         <v>2025</v>
       </c>
@@ -19686,7 +20306,7 @@
       <c r="I458" s="11"/>
       <c r="J458" s="11"/>
     </row>
-    <row r="459" spans="1:10">
+    <row r="459" ht="17" spans="1:10">
       <c r="A459" s="6">
         <v>2025</v>
       </c>
@@ -19712,7 +20332,7 @@
       <c r="I459" s="11"/>
       <c r="J459" s="11"/>
     </row>
-    <row r="460" spans="1:10">
+    <row r="460" ht="17" spans="1:10">
       <c r="A460" s="6">
         <v>2025</v>
       </c>
@@ -19738,7 +20358,7 @@
       <c r="I460" s="11"/>
       <c r="J460" s="11"/>
     </row>
-    <row r="461" spans="1:10">
+    <row r="461" ht="17" spans="1:10">
       <c r="A461" s="6">
         <v>2025</v>
       </c>
@@ -19764,7 +20384,7 @@
       <c r="I461" s="11"/>
       <c r="J461" s="11"/>
     </row>
-    <row r="462" spans="1:10">
+    <row r="462" ht="17" spans="1:10">
       <c r="A462" s="12">
         <v>2025</v>
       </c>
@@ -19792,7 +20412,7 @@
       <c r="I462" s="10"/>
       <c r="J462" s="11"/>
     </row>
-    <row r="463" spans="1:10">
+    <row r="463" ht="17" spans="1:10">
       <c r="A463" s="12">
         <v>2025</v>
       </c>
@@ -19820,7 +20440,7 @@
       <c r="I463" s="11"/>
       <c r="J463" s="11"/>
     </row>
-    <row r="464" spans="1:10">
+    <row r="464" ht="17" spans="1:10">
       <c r="A464" s="12">
         <v>2025</v>
       </c>
@@ -19848,7 +20468,7 @@
       <c r="I464" s="11"/>
       <c r="J464" s="11"/>
     </row>
-    <row r="465" spans="1:10">
+    <row r="465" ht="17" spans="1:10">
       <c r="A465" s="12">
         <v>2025</v>
       </c>
@@ -19876,7 +20496,7 @@
       <c r="I465" s="11"/>
       <c r="J465" s="11"/>
     </row>
-    <row r="466" spans="1:10">
+    <row r="466" ht="17" spans="1:10">
       <c r="A466" s="12">
         <v>2025</v>
       </c>
@@ -19904,7 +20524,7 @@
       <c r="I466" s="11"/>
       <c r="J466" s="11"/>
     </row>
-    <row r="467" spans="1:10">
+    <row r="467" ht="17" spans="1:10">
       <c r="A467" s="12">
         <v>2025</v>
       </c>
@@ -19932,7 +20552,7 @@
       <c r="I467" s="11"/>
       <c r="J467" s="11"/>
     </row>
-    <row r="468" spans="1:10">
+    <row r="468" ht="17" spans="1:10">
       <c r="A468" s="12">
         <v>2025</v>
       </c>
@@ -19960,7 +20580,7 @@
       <c r="I468" s="11"/>
       <c r="J468" s="11"/>
     </row>
-    <row r="469" spans="1:10">
+    <row r="469" ht="17" spans="1:10">
       <c r="A469" s="12">
         <v>2025</v>
       </c>
@@ -19988,7 +20608,7 @@
       <c r="I469" s="11"/>
       <c r="J469" s="11"/>
     </row>
-    <row r="470" spans="1:10">
+    <row r="470" ht="17" spans="1:10">
       <c r="A470" s="12">
         <v>2025</v>
       </c>
@@ -20016,7 +20636,7 @@
       <c r="I470" s="11"/>
       <c r="J470" s="11"/>
     </row>
-    <row r="471" spans="1:10">
+    <row r="471" ht="17" spans="1:10">
       <c r="A471" s="12">
         <v>2025</v>
       </c>
@@ -20044,7 +20664,7 @@
       <c r="I471" s="11"/>
       <c r="J471" s="11"/>
     </row>
-    <row r="472" spans="1:10">
+    <row r="472" ht="17" spans="1:10">
       <c r="A472" s="12">
         <v>2025</v>
       </c>
@@ -20072,7 +20692,7 @@
       <c r="I472" s="11"/>
       <c r="J472" s="11"/>
     </row>
-    <row r="473" spans="1:10">
+    <row r="473" ht="17" spans="1:10">
       <c r="A473" s="12">
         <v>2025</v>
       </c>
@@ -20100,7 +20720,7 @@
       <c r="I473" s="11"/>
       <c r="J473" s="11"/>
     </row>
-    <row r="474" spans="1:10">
+    <row r="474" ht="17" spans="1:10">
       <c r="A474" s="12">
         <v>2025</v>
       </c>
@@ -20128,7 +20748,7 @@
       <c r="I474" s="11"/>
       <c r="J474" s="11"/>
     </row>
-    <row r="475" spans="1:10">
+    <row r="475" ht="17" spans="1:10">
       <c r="A475" s="12">
         <v>2025</v>
       </c>
@@ -20156,7 +20776,7 @@
       <c r="I475" s="11"/>
       <c r="J475" s="11"/>
     </row>
-    <row r="476" spans="1:10">
+    <row r="476" ht="17" spans="1:10">
       <c r="A476" s="12">
         <v>2025</v>
       </c>
@@ -20184,7 +20804,7 @@
       <c r="I476" s="11"/>
       <c r="J476" s="11"/>
     </row>
-    <row r="477" spans="1:10">
+    <row r="477" ht="17" spans="1:10">
       <c r="A477" s="12">
         <v>2025</v>
       </c>
@@ -20212,7 +20832,7 @@
       <c r="I477" s="11"/>
       <c r="J477" s="11"/>
     </row>
-    <row r="478" spans="1:10">
+    <row r="478" ht="17" spans="1:10">
       <c r="A478" s="12">
         <v>2025</v>
       </c>
@@ -20240,7 +20860,7 @@
       <c r="I478" s="11"/>
       <c r="J478" s="11"/>
     </row>
-    <row r="479" spans="1:10">
+    <row r="479" ht="17" spans="1:10">
       <c r="A479" s="12">
         <v>2025</v>
       </c>
@@ -20268,7 +20888,7 @@
       <c r="I479" s="11"/>
       <c r="J479" s="11"/>
     </row>
-    <row r="480" spans="1:10">
+    <row r="480" ht="17" spans="1:10">
       <c r="A480" s="12">
         <v>2025</v>
       </c>
@@ -20296,7 +20916,7 @@
       <c r="I480" s="11"/>
       <c r="J480" s="11"/>
     </row>
-    <row r="481" spans="1:10">
+    <row r="481" ht="17" spans="1:10">
       <c r="A481" s="12">
         <v>2025</v>
       </c>
@@ -20324,7 +20944,7 @@
       <c r="I481" s="11"/>
       <c r="J481" s="11"/>
     </row>
-    <row r="482" spans="1:10">
+    <row r="482" ht="17" spans="1:10">
       <c r="A482" s="6">
         <v>2025</v>
       </c>
@@ -20350,7 +20970,7 @@
       <c r="I482" s="10"/>
       <c r="J482" s="10"/>
     </row>
-    <row r="483" spans="1:10">
+    <row r="483" ht="17" spans="1:10">
       <c r="A483" s="6">
         <v>2025</v>
       </c>
@@ -20376,7 +20996,7 @@
       <c r="I483" s="10"/>
       <c r="J483" s="10"/>
     </row>
-    <row r="484" spans="1:10">
+    <row r="484" ht="17" spans="1:10">
       <c r="A484" s="6">
         <v>2025</v>
       </c>
@@ -20402,7 +21022,7 @@
       <c r="I484" s="10"/>
       <c r="J484" s="10"/>
     </row>
-    <row r="485" spans="1:10">
+    <row r="485" ht="17" spans="1:10">
       <c r="A485" s="6">
         <v>2025</v>
       </c>
@@ -20428,7 +21048,7 @@
       <c r="I485" s="10"/>
       <c r="J485" s="10"/>
     </row>
-    <row r="486" spans="1:10">
+    <row r="486" ht="17" spans="1:10">
       <c r="A486" s="6">
         <v>2025</v>
       </c>
@@ -20454,7 +21074,7 @@
       <c r="I486" s="10"/>
       <c r="J486" s="10"/>
     </row>
-    <row r="487" spans="1:10">
+    <row r="487" ht="17" spans="1:10">
       <c r="A487" s="6">
         <v>2025</v>
       </c>
@@ -20480,7 +21100,7 @@
       <c r="I487" s="10"/>
       <c r="J487" s="10"/>
     </row>
-    <row r="488" spans="1:10">
+    <row r="488" ht="17" spans="1:10">
       <c r="A488" s="6">
         <v>2025</v>
       </c>
@@ -20506,7 +21126,7 @@
       <c r="I488" s="10"/>
       <c r="J488" s="10"/>
     </row>
-    <row r="489" spans="1:10">
+    <row r="489" ht="17" spans="1:10">
       <c r="A489" s="6">
         <v>2025</v>
       </c>
@@ -20532,7 +21152,7 @@
       <c r="I489" s="10"/>
       <c r="J489" s="10"/>
     </row>
-    <row r="490" spans="1:10">
+    <row r="490" ht="17" spans="1:10">
       <c r="A490" s="6">
         <v>2025</v>
       </c>
@@ -20558,7 +21178,7 @@
       <c r="I490" s="10"/>
       <c r="J490" s="10"/>
     </row>
-    <row r="491" spans="1:10">
+    <row r="491" ht="17" spans="1:10">
       <c r="A491" s="6">
         <v>2025</v>
       </c>
@@ -20584,7 +21204,7 @@
       <c r="I491" s="10"/>
       <c r="J491" s="10"/>
     </row>
-    <row r="492" spans="1:10">
+    <row r="492" ht="17" spans="1:10">
       <c r="A492" s="6">
         <v>2025</v>
       </c>
@@ -20610,7 +21230,7 @@
       <c r="I492" s="10"/>
       <c r="J492" s="11"/>
     </row>
-    <row r="493" spans="1:10">
+    <row r="493" ht="17" spans="1:10">
       <c r="A493" s="6">
         <v>2025</v>
       </c>
@@ -20636,7 +21256,7 @@
       <c r="I493" s="10"/>
       <c r="J493" s="11"/>
     </row>
-    <row r="494" spans="1:10">
+    <row r="494" ht="17" spans="1:10">
       <c r="A494" s="6">
         <v>2025</v>
       </c>
@@ -20662,7 +21282,7 @@
       <c r="I494" s="10"/>
       <c r="J494" s="11"/>
     </row>
-    <row r="495" spans="1:10">
+    <row r="495" ht="17" spans="1:10">
       <c r="A495" s="6">
         <v>2025</v>
       </c>
@@ -20688,7 +21308,7 @@
       <c r="I495" s="10"/>
       <c r="J495" s="11"/>
     </row>
-    <row r="496" spans="1:10">
+    <row r="496" ht="17" spans="1:10">
       <c r="A496" s="6">
         <v>2025</v>
       </c>
@@ -20714,7 +21334,7 @@
       <c r="I496" s="10"/>
       <c r="J496" s="11"/>
     </row>
-    <row r="497" spans="1:10">
+    <row r="497" ht="17" spans="1:10">
       <c r="A497" s="6">
         <v>2025</v>
       </c>
@@ -20740,7 +21360,7 @@
       <c r="I497" s="11"/>
       <c r="J497" s="11"/>
     </row>
-    <row r="498" spans="1:10">
+    <row r="498" ht="17" spans="1:10">
       <c r="A498" s="6">
         <v>2025</v>
       </c>
@@ -20766,7 +21386,7 @@
       <c r="I498" s="11"/>
       <c r="J498" s="11"/>
     </row>
-    <row r="499" spans="1:10">
+    <row r="499" ht="17" spans="1:10">
       <c r="A499" s="6">
         <v>2025</v>
       </c>
@@ -20792,7 +21412,7 @@
       <c r="I499" s="11"/>
       <c r="J499" s="11"/>
     </row>
-    <row r="500" spans="1:10">
+    <row r="500" ht="17" spans="1:10">
       <c r="A500" s="6">
         <v>2025</v>
       </c>
@@ -20818,7 +21438,7 @@
       <c r="I500" s="11"/>
       <c r="J500" s="11"/>
     </row>
-    <row r="501" spans="1:10">
+    <row r="501" ht="17" spans="1:10">
       <c r="A501" s="6">
         <v>2025</v>
       </c>
@@ -20844,7 +21464,7 @@
       <c r="I501" s="11"/>
       <c r="J501" s="11"/>
     </row>
-    <row r="502" spans="1:10">
+    <row r="502" ht="17" spans="1:10">
       <c r="A502" s="12">
         <v>2025</v>
       </c>
@@ -20872,7 +21492,7 @@
       <c r="I502" s="10"/>
       <c r="J502" s="11"/>
     </row>
-    <row r="503" spans="1:10">
+    <row r="503" ht="17" spans="1:10">
       <c r="A503" s="12">
         <v>2025</v>
       </c>
@@ -20900,7 +21520,7 @@
       <c r="I503" s="11"/>
       <c r="J503" s="11"/>
     </row>
-    <row r="504" spans="1:10">
+    <row r="504" ht="17" spans="1:10">
       <c r="A504" s="12">
         <v>2025</v>
       </c>
@@ -20928,7 +21548,7 @@
       <c r="I504" s="11"/>
       <c r="J504" s="11"/>
     </row>
-    <row r="505" spans="1:10">
+    <row r="505" ht="17" spans="1:10">
       <c r="A505" s="12">
         <v>2025</v>
       </c>
@@ -20956,7 +21576,7 @@
       <c r="I505" s="11"/>
       <c r="J505" s="11"/>
     </row>
-    <row r="506" spans="1:10">
+    <row r="506" ht="17" spans="1:10">
       <c r="A506" s="12">
         <v>2025</v>
       </c>
@@ -20984,7 +21604,7 @@
       <c r="I506" s="11"/>
       <c r="J506" s="11"/>
     </row>
-    <row r="507" spans="1:10">
+    <row r="507" ht="17" spans="1:10">
       <c r="A507" s="12">
         <v>2025</v>
       </c>
@@ -21012,7 +21632,7 @@
       <c r="I507" s="11"/>
       <c r="J507" s="11"/>
     </row>
-    <row r="508" spans="1:10">
+    <row r="508" ht="17" spans="1:10">
       <c r="A508" s="12">
         <v>2025</v>
       </c>
@@ -21040,7 +21660,7 @@
       <c r="I508" s="11"/>
       <c r="J508" s="11"/>
     </row>
-    <row r="509" spans="1:10">
+    <row r="509" ht="17" spans="1:10">
       <c r="A509" s="12">
         <v>2025</v>
       </c>
@@ -21068,7 +21688,7 @@
       <c r="I509" s="11"/>
       <c r="J509" s="11"/>
     </row>
-    <row r="510" spans="1:10">
+    <row r="510" ht="17" spans="1:10">
       <c r="A510" s="12">
         <v>2025</v>
       </c>
@@ -21096,7 +21716,7 @@
       <c r="I510" s="11"/>
       <c r="J510" s="11"/>
     </row>
-    <row r="511" spans="1:10">
+    <row r="511" ht="17" spans="1:10">
       <c r="A511" s="12">
         <v>2025</v>
       </c>
@@ -21124,7 +21744,7 @@
       <c r="I511" s="11"/>
       <c r="J511" s="11"/>
     </row>
-    <row r="512" spans="1:10">
+    <row r="512" ht="17" spans="1:10">
       <c r="A512" s="12">
         <v>2025</v>
       </c>
@@ -21152,7 +21772,7 @@
       <c r="I512" s="11"/>
       <c r="J512" s="11"/>
     </row>
-    <row r="513" spans="1:10">
+    <row r="513" ht="17" spans="1:10">
       <c r="A513" s="12">
         <v>2025</v>
       </c>
@@ -21180,7 +21800,7 @@
       <c r="I513" s="11"/>
       <c r="J513" s="11"/>
     </row>
-    <row r="514" spans="1:10">
+    <row r="514" ht="17" spans="1:10">
       <c r="A514" s="12">
         <v>2025</v>
       </c>
@@ -21208,7 +21828,7 @@
       <c r="I514" s="11"/>
       <c r="J514" s="11"/>
     </row>
-    <row r="515" spans="1:10">
+    <row r="515" ht="17" spans="1:10">
       <c r="A515" s="12">
         <v>2025</v>
       </c>
@@ -21236,7 +21856,7 @@
       <c r="I515" s="11"/>
       <c r="J515" s="11"/>
     </row>
-    <row r="516" spans="1:10">
+    <row r="516" ht="17" spans="1:10">
       <c r="A516" s="12">
         <v>2025</v>
       </c>
@@ -21264,7 +21884,7 @@
       <c r="I516" s="11"/>
       <c r="J516" s="11"/>
     </row>
-    <row r="517" spans="1:10">
+    <row r="517" ht="17" spans="1:10">
       <c r="A517" s="12">
         <v>2025</v>
       </c>
@@ -21292,7 +21912,7 @@
       <c r="I517" s="11"/>
       <c r="J517" s="11"/>
     </row>
-    <row r="518" spans="1:10">
+    <row r="518" ht="17" spans="1:10">
       <c r="A518" s="12">
         <v>2025</v>
       </c>
@@ -21320,7 +21940,7 @@
       <c r="I518" s="11"/>
       <c r="J518" s="11"/>
     </row>
-    <row r="519" spans="1:10">
+    <row r="519" ht="17" spans="1:10">
       <c r="A519" s="12">
         <v>2025</v>
       </c>
@@ -21348,7 +21968,7 @@
       <c r="I519" s="11"/>
       <c r="J519" s="11"/>
     </row>
-    <row r="520" spans="1:10">
+    <row r="520" ht="17" spans="1:10">
       <c r="A520" s="12">
         <v>2025</v>
       </c>
@@ -21376,7 +21996,7 @@
       <c r="I520" s="11"/>
       <c r="J520" s="11"/>
     </row>
-    <row r="521" spans="1:10">
+    <row r="521" ht="17" spans="1:10">
       <c r="A521" s="12">
         <v>2025</v>
       </c>
@@ -21404,7 +22024,7 @@
       <c r="I521" s="11"/>
       <c r="J521" s="11"/>
     </row>
-    <row r="522" spans="1:10">
+    <row r="522" ht="17" spans="1:10">
       <c r="A522" s="6">
         <v>2025</v>
       </c>
@@ -21430,7 +22050,7 @@
       <c r="I522" s="10"/>
       <c r="J522" s="10"/>
     </row>
-    <row r="523" spans="1:10">
+    <row r="523" ht="17" spans="1:10">
       <c r="A523" s="6">
         <v>2025</v>
       </c>
@@ -21456,7 +22076,7 @@
       <c r="I523" s="10"/>
       <c r="J523" s="10"/>
     </row>
-    <row r="524" spans="1:10">
+    <row r="524" ht="17" spans="1:10">
       <c r="A524" s="6">
         <v>2025</v>
       </c>
@@ -21482,7 +22102,7 @@
       <c r="I524" s="10"/>
       <c r="J524" s="10"/>
     </row>
-    <row r="525" spans="1:10">
+    <row r="525" ht="17" spans="1:10">
       <c r="A525" s="6">
         <v>2025</v>
       </c>
@@ -21508,7 +22128,7 @@
       <c r="I525" s="10"/>
       <c r="J525" s="10"/>
     </row>
-    <row r="526" spans="1:10">
+    <row r="526" ht="17" spans="1:10">
       <c r="A526" s="6">
         <v>2025</v>
       </c>
@@ -21534,7 +22154,7 @@
       <c r="I526" s="10"/>
       <c r="J526" s="10"/>
     </row>
-    <row r="527" spans="1:10">
+    <row r="527" ht="17" spans="1:10">
       <c r="A527" s="6">
         <v>2025</v>
       </c>
@@ -21560,7 +22180,7 @@
       <c r="I527" s="10"/>
       <c r="J527" s="10"/>
     </row>
-    <row r="528" spans="1:10">
+    <row r="528" ht="17" spans="1:10">
       <c r="A528" s="6">
         <v>2025</v>
       </c>
@@ -21586,7 +22206,7 @@
       <c r="I528" s="10"/>
       <c r="J528" s="10"/>
     </row>
-    <row r="529" spans="1:10">
+    <row r="529" ht="17" spans="1:10">
       <c r="A529" s="6">
         <v>2025</v>
       </c>
@@ -21612,7 +22232,7 @@
       <c r="I529" s="10"/>
       <c r="J529" s="10"/>
     </row>
-    <row r="530" spans="1:10">
+    <row r="530" ht="17" spans="1:10">
       <c r="A530" s="6">
         <v>2025</v>
       </c>
@@ -21638,7 +22258,7 @@
       <c r="I530" s="10"/>
       <c r="J530" s="10"/>
     </row>
-    <row r="531" spans="1:10">
+    <row r="531" ht="17" spans="1:10">
       <c r="A531" s="6">
         <v>2025</v>
       </c>
@@ -21664,7 +22284,7 @@
       <c r="I531" s="10"/>
       <c r="J531" s="10"/>
     </row>
-    <row r="532" spans="1:10">
+    <row r="532" ht="17" spans="1:10">
       <c r="A532" s="6">
         <v>2025</v>
       </c>
@@ -21690,7 +22310,7 @@
       <c r="I532" s="10"/>
       <c r="J532" s="11"/>
     </row>
-    <row r="533" spans="1:10">
+    <row r="533" ht="17" spans="1:10">
       <c r="A533" s="6">
         <v>2025</v>
       </c>
@@ -21716,7 +22336,7 @@
       <c r="I533" s="10"/>
       <c r="J533" s="11"/>
     </row>
-    <row r="534" spans="1:10">
+    <row r="534" ht="17" spans="1:10">
       <c r="A534" s="6">
         <v>2025</v>
       </c>
@@ -21742,7 +22362,7 @@
       <c r="I534" s="10"/>
       <c r="J534" s="11"/>
     </row>
-    <row r="535" spans="1:10">
+    <row r="535" ht="17" spans="1:10">
       <c r="A535" s="6">
         <v>2025</v>
       </c>
@@ -21768,7 +22388,7 @@
       <c r="I535" s="10"/>
       <c r="J535" s="11"/>
     </row>
-    <row r="536" spans="1:10">
+    <row r="536" ht="17" spans="1:10">
       <c r="A536" s="6">
         <v>2025</v>
       </c>
@@ -21794,7 +22414,7 @@
       <c r="I536" s="10"/>
       <c r="J536" s="11"/>
     </row>
-    <row r="537" spans="1:10">
+    <row r="537" ht="17" spans="1:10">
       <c r="A537" s="6">
         <v>2025</v>
       </c>
@@ -21820,7 +22440,7 @@
       <c r="I537" s="11"/>
       <c r="J537" s="11"/>
     </row>
-    <row r="538" spans="1:10">
+    <row r="538" ht="17" spans="1:10">
       <c r="A538" s="6">
         <v>2025</v>
       </c>
@@ -21846,7 +22466,7 @@
       <c r="I538" s="11"/>
       <c r="J538" s="11"/>
     </row>
-    <row r="539" spans="1:10">
+    <row r="539" ht="17" spans="1:10">
       <c r="A539" s="6">
         <v>2025</v>
       </c>
@@ -21872,7 +22492,7 @@
       <c r="I539" s="11"/>
       <c r="J539" s="11"/>
     </row>
-    <row r="540" spans="1:10">
+    <row r="540" ht="17" spans="1:10">
       <c r="A540" s="6">
         <v>2025</v>
       </c>
@@ -21898,7 +22518,7 @@
       <c r="I540" s="11"/>
       <c r="J540" s="11"/>
     </row>
-    <row r="541" spans="1:10">
+    <row r="541" ht="17" spans="1:10">
       <c r="A541" s="6">
         <v>2025</v>
       </c>
@@ -21924,7 +22544,7 @@
       <c r="I541" s="11"/>
       <c r="J541" s="11"/>
     </row>
-    <row r="542" spans="1:10">
+    <row r="542" ht="17" spans="1:10">
       <c r="A542" s="12">
         <v>2025</v>
       </c>
@@ -21952,7 +22572,7 @@
       <c r="I542" s="10"/>
       <c r="J542" s="11"/>
     </row>
-    <row r="543" spans="1:10">
+    <row r="543" ht="17" spans="1:10">
       <c r="A543" s="12">
         <v>2025</v>
       </c>
@@ -21980,7 +22600,7 @@
       <c r="I543" s="11"/>
       <c r="J543" s="11"/>
     </row>
-    <row r="544" spans="1:10">
+    <row r="544" ht="17" spans="1:10">
       <c r="A544" s="12">
         <v>2025</v>
       </c>
@@ -22008,7 +22628,7 @@
       <c r="I544" s="11"/>
       <c r="J544" s="11"/>
     </row>
-    <row r="545" spans="1:10">
+    <row r="545" ht="17" spans="1:10">
       <c r="A545" s="12">
         <v>2025</v>
       </c>
@@ -22036,7 +22656,7 @@
       <c r="I545" s="11"/>
       <c r="J545" s="11"/>
     </row>
-    <row r="546" spans="1:10">
+    <row r="546" ht="17" spans="1:10">
       <c r="A546" s="12">
         <v>2025</v>
       </c>
@@ -22064,7 +22684,7 @@
       <c r="I546" s="11"/>
       <c r="J546" s="11"/>
     </row>
-    <row r="547" spans="1:10">
+    <row r="547" ht="17" spans="1:10">
       <c r="A547" s="12">
         <v>2025</v>
       </c>
@@ -22092,7 +22712,7 @@
       <c r="I547" s="11"/>
       <c r="J547" s="11"/>
     </row>
-    <row r="548" spans="1:10">
+    <row r="548" ht="17" spans="1:10">
       <c r="A548" s="12">
         <v>2025</v>
       </c>
@@ -22120,7 +22740,7 @@
       <c r="I548" s="11"/>
       <c r="J548" s="11"/>
     </row>
-    <row r="549" spans="1:10">
+    <row r="549" ht="17" spans="1:10">
       <c r="A549" s="12">
         <v>2025</v>
       </c>
@@ -22148,7 +22768,7 @@
       <c r="I549" s="11"/>
       <c r="J549" s="11"/>
     </row>
-    <row r="550" spans="1:10">
+    <row r="550" ht="17" spans="1:10">
       <c r="A550" s="12">
         <v>2025</v>
       </c>
@@ -22176,7 +22796,7 @@
       <c r="I550" s="11"/>
       <c r="J550" s="11"/>
     </row>
-    <row r="551" spans="1:10">
+    <row r="551" ht="17" spans="1:10">
       <c r="A551" s="12">
         <v>2025</v>
       </c>
@@ -22204,7 +22824,7 @@
       <c r="I551" s="11"/>
       <c r="J551" s="11"/>
     </row>
-    <row r="552" spans="1:10">
+    <row r="552" ht="17" spans="1:10">
       <c r="A552" s="12">
         <v>2025</v>
       </c>
@@ -22232,7 +22852,7 @@
       <c r="I552" s="11"/>
       <c r="J552" s="11"/>
     </row>
-    <row r="553" spans="1:10">
+    <row r="553" ht="17" spans="1:10">
       <c r="A553" s="12">
         <v>2025</v>
       </c>
@@ -22260,7 +22880,7 @@
       <c r="I553" s="11"/>
       <c r="J553" s="11"/>
     </row>
-    <row r="554" spans="1:10">
+    <row r="554" ht="17" spans="1:10">
       <c r="A554" s="12">
         <v>2025</v>
       </c>
@@ -22288,7 +22908,7 @@
       <c r="I554" s="11"/>
       <c r="J554" s="11"/>
     </row>
-    <row r="555" spans="1:10">
+    <row r="555" ht="17" spans="1:10">
       <c r="A555" s="12">
         <v>2025</v>
       </c>
@@ -22316,7 +22936,7 @@
       <c r="I555" s="11"/>
       <c r="J555" s="11"/>
     </row>
-    <row r="556" spans="1:10">
+    <row r="556" ht="17" spans="1:10">
       <c r="A556" s="12">
         <v>2025</v>
       </c>
@@ -22344,7 +22964,7 @@
       <c r="I556" s="11"/>
       <c r="J556" s="11"/>
     </row>
-    <row r="557" spans="1:10">
+    <row r="557" ht="17" spans="1:10">
       <c r="A557" s="12">
         <v>2025</v>
       </c>
@@ -22372,7 +22992,7 @@
       <c r="I557" s="11"/>
       <c r="J557" s="11"/>
     </row>
-    <row r="558" spans="1:10">
+    <row r="558" ht="17" spans="1:10">
       <c r="A558" s="12">
         <v>2025</v>
       </c>
@@ -22400,7 +23020,7 @@
       <c r="I558" s="11"/>
       <c r="J558" s="11"/>
     </row>
-    <row r="559" spans="1:10">
+    <row r="559" ht="17" spans="1:10">
       <c r="A559" s="12">
         <v>2025</v>
       </c>
@@ -22428,7 +23048,7 @@
       <c r="I559" s="11"/>
       <c r="J559" s="11"/>
     </row>
-    <row r="560" spans="1:10">
+    <row r="560" ht="17" spans="1:10">
       <c r="A560" s="12">
         <v>2025</v>
       </c>
@@ -22456,7 +23076,7 @@
       <c r="I560" s="11"/>
       <c r="J560" s="11"/>
     </row>
-    <row r="561" spans="1:16">
+    <row r="561" ht="17" spans="1:16">
       <c r="A561" s="12">
         <v>2025</v>
       </c>
@@ -23009,7 +23629,7 @@
       <c r="H581" s="6"/>
       <c r="N581" s="16"/>
     </row>
-    <row r="582" spans="1:14">
+    <row r="582" ht="17" spans="1:14">
       <c r="A582" s="12">
         <v>2025</v>
       </c>
@@ -23037,7 +23657,7 @@
       <c r="I582" s="10"/>
       <c r="J582" s="11"/>
     </row>
-    <row r="583" spans="1:14">
+    <row r="583" ht="17" spans="1:14">
       <c r="A583" s="12">
         <v>2025</v>
       </c>
@@ -23065,7 +23685,7 @@
       <c r="I583" s="11"/>
       <c r="J583" s="11"/>
     </row>
-    <row r="584" spans="1:14">
+    <row r="584" ht="17" spans="1:14">
       <c r="A584" s="12">
         <v>2025</v>
       </c>
@@ -23093,7 +23713,7 @@
       <c r="I584" s="11"/>
       <c r="J584" s="11"/>
     </row>
-    <row r="585" spans="1:14">
+    <row r="585" ht="17" spans="1:14">
       <c r="A585" s="12">
         <v>2025</v>
       </c>
@@ -23121,7 +23741,7 @@
       <c r="I585" s="11"/>
       <c r="J585" s="11"/>
     </row>
-    <row r="586" spans="1:14">
+    <row r="586" ht="17" spans="1:14">
       <c r="A586" s="12">
         <v>2025</v>
       </c>
@@ -23149,7 +23769,7 @@
       <c r="I586" s="11"/>
       <c r="J586" s="11"/>
     </row>
-    <row r="587" spans="1:14">
+    <row r="587" ht="17" spans="1:14">
       <c r="A587" s="12">
         <v>2025</v>
       </c>
@@ -23177,7 +23797,7 @@
       <c r="I587" s="11"/>
       <c r="J587" s="11"/>
     </row>
-    <row r="588" spans="1:14">
+    <row r="588" ht="17" spans="1:14">
       <c r="A588" s="12">
         <v>2025</v>
       </c>
@@ -23205,7 +23825,7 @@
       <c r="I588" s="11"/>
       <c r="J588" s="11"/>
     </row>
-    <row r="589" spans="1:14">
+    <row r="589" ht="17" spans="1:14">
       <c r="A589" s="12">
         <v>2025</v>
       </c>
@@ -23233,7 +23853,7 @@
       <c r="I589" s="11"/>
       <c r="J589" s="11"/>
     </row>
-    <row r="590" spans="1:14">
+    <row r="590" ht="17" spans="1:14">
       <c r="A590" s="12">
         <v>2025</v>
       </c>
@@ -23261,7 +23881,7 @@
       <c r="I590" s="11"/>
       <c r="J590" s="11"/>
     </row>
-    <row r="591" spans="1:14">
+    <row r="591" ht="17" spans="1:14">
       <c r="A591" s="12">
         <v>2025</v>
       </c>
@@ -23289,7 +23909,7 @@
       <c r="I591" s="11"/>
       <c r="J591" s="11"/>
     </row>
-    <row r="592" spans="1:14">
+    <row r="592" ht="17" spans="1:14">
       <c r="A592" s="12">
         <v>2025</v>
       </c>
@@ -23317,7 +23937,7 @@
       <c r="I592" s="11"/>
       <c r="J592" s="11"/>
     </row>
-    <row r="593" spans="1:10">
+    <row r="593" ht="17" spans="1:10">
       <c r="A593" s="12">
         <v>2025</v>
       </c>
@@ -23345,7 +23965,7 @@
       <c r="I593" s="11"/>
       <c r="J593" s="11"/>
     </row>
-    <row r="594" spans="1:10">
+    <row r="594" ht="17" spans="1:10">
       <c r="A594" s="12">
         <v>2025</v>
       </c>
@@ -23373,7 +23993,7 @@
       <c r="I594" s="11"/>
       <c r="J594" s="11"/>
     </row>
-    <row r="595" spans="1:10">
+    <row r="595" ht="17" spans="1:10">
       <c r="A595" s="12">
         <v>2025</v>
       </c>
@@ -23401,7 +24021,7 @@
       <c r="I595" s="11"/>
       <c r="J595" s="11"/>
     </row>
-    <row r="596" spans="1:10">
+    <row r="596" ht="17" spans="1:10">
       <c r="A596" s="12">
         <v>2025</v>
       </c>
@@ -23429,7 +24049,7 @@
       <c r="I596" s="11"/>
       <c r="J596" s="11"/>
     </row>
-    <row r="597" spans="1:10">
+    <row r="597" ht="17" spans="1:10">
       <c r="A597" s="12">
         <v>2025</v>
       </c>
@@ -23457,7 +24077,7 @@
       <c r="I597" s="11"/>
       <c r="J597" s="11"/>
     </row>
-    <row r="598" spans="1:10">
+    <row r="598" ht="17" spans="1:10">
       <c r="A598" s="12">
         <v>2025</v>
       </c>
@@ -23485,7 +24105,7 @@
       <c r="I598" s="11"/>
       <c r="J598" s="11"/>
     </row>
-    <row r="599" spans="1:10">
+    <row r="599" ht="17" spans="1:10">
       <c r="A599" s="12">
         <v>2025</v>
       </c>
@@ -23513,7 +24133,7 @@
       <c r="I599" s="11"/>
       <c r="J599" s="11"/>
     </row>
-    <row r="600" spans="1:10">
+    <row r="600" ht="17" spans="1:10">
       <c r="A600" s="12">
         <v>2025</v>
       </c>
@@ -23541,7 +24161,7 @@
       <c r="I600" s="11"/>
       <c r="J600" s="11"/>
     </row>
-    <row r="601" spans="1:10">
+    <row r="601" ht="17" spans="1:10">
       <c r="A601" s="12">
         <v>2025</v>
       </c>
@@ -25594,7 +26214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="681" spans="1:17">
+    <row r="681" ht="17" spans="1:17">
       <c r="A681" s="12">
         <v>2025</v>
       </c>
@@ -25620,7 +26240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="682" spans="1:17">
+    <row r="682" ht="17" spans="1:17">
       <c r="A682" s="6">
         <v>2025</v>
       </c>
@@ -25648,7 +26268,7 @@
       <c r="P682" s="10"/>
       <c r="Q682" s="11"/>
     </row>
-    <row r="683" spans="1:17">
+    <row r="683" ht="17" spans="1:17">
       <c r="A683" s="6">
         <v>2025</v>
       </c>
@@ -25676,7 +26296,7 @@
       <c r="P683" s="10"/>
       <c r="Q683" s="11"/>
     </row>
-    <row r="684" spans="1:17">
+    <row r="684" ht="17" spans="1:17">
       <c r="A684" s="6">
         <v>2025</v>
       </c>
@@ -25704,7 +26324,7 @@
       <c r="P684" s="10"/>
       <c r="Q684" s="11"/>
     </row>
-    <row r="685" spans="1:17">
+    <row r="685" ht="17" spans="1:17">
       <c r="A685" s="6">
         <v>2025</v>
       </c>
@@ -25732,7 +26352,7 @@
       <c r="P685" s="10"/>
       <c r="Q685" s="11"/>
     </row>
-    <row r="686" spans="1:17">
+    <row r="686" ht="17" spans="1:17">
       <c r="A686" s="6">
         <v>2025</v>
       </c>
@@ -25760,7 +26380,7 @@
       <c r="P686" s="10"/>
       <c r="Q686" s="11"/>
     </row>
-    <row r="687" spans="1:17">
+    <row r="687" ht="17" spans="1:17">
       <c r="A687" s="6">
         <v>2025</v>
       </c>
@@ -25788,7 +26408,7 @@
       <c r="P687" s="10"/>
       <c r="Q687" s="11"/>
     </row>
-    <row r="688" spans="1:17">
+    <row r="688" ht="17" spans="1:17">
       <c r="A688" s="6">
         <v>2025</v>
       </c>
@@ -25816,7 +26436,7 @@
       <c r="P688" s="10"/>
       <c r="Q688" s="11"/>
     </row>
-    <row r="689" spans="1:17">
+    <row r="689" ht="17" spans="1:17">
       <c r="A689" s="6">
         <v>2025</v>
       </c>
@@ -25844,7 +26464,7 @@
       <c r="P689" s="10"/>
       <c r="Q689" s="11"/>
     </row>
-    <row r="690" spans="1:17">
+    <row r="690" ht="17" spans="1:17">
       <c r="A690" s="6">
         <v>2025</v>
       </c>
@@ -25872,7 +26492,7 @@
       <c r="P690" s="10"/>
       <c r="Q690" s="11"/>
     </row>
-    <row r="691" spans="1:17">
+    <row r="691" ht="17" spans="1:17">
       <c r="A691" s="6">
         <v>2025</v>
       </c>
@@ -25900,7 +26520,7 @@
       <c r="P691" s="10"/>
       <c r="Q691" s="11"/>
     </row>
-    <row r="692" spans="1:17">
+    <row r="692" ht="17" spans="1:17">
       <c r="A692" s="6">
         <v>2025</v>
       </c>
@@ -25928,7 +26548,7 @@
       <c r="P692" s="11"/>
       <c r="Q692" s="11"/>
     </row>
-    <row r="693" spans="1:17">
+    <row r="693" ht="17" spans="1:17">
       <c r="A693" s="6">
         <v>2025</v>
       </c>
@@ -25956,7 +26576,7 @@
       <c r="P693" s="11"/>
       <c r="Q693" s="11"/>
     </row>
-    <row r="694" spans="1:17">
+    <row r="694" ht="17" spans="1:17">
       <c r="A694" s="6">
         <v>2025</v>
       </c>
@@ -25984,7 +26604,7 @@
       <c r="P694" s="11"/>
       <c r="Q694" s="11"/>
     </row>
-    <row r="695" spans="1:17">
+    <row r="695" ht="17" spans="1:17">
       <c r="A695" s="6">
         <v>2025</v>
       </c>
@@ -26012,7 +26632,7 @@
       <c r="P695" s="11"/>
       <c r="Q695" s="11"/>
     </row>
-    <row r="696" spans="1:17">
+    <row r="696" ht="17" spans="1:17">
       <c r="A696" s="6">
         <v>2025</v>
       </c>
@@ -26040,7 +26660,7 @@
       <c r="P696" s="11"/>
       <c r="Q696" s="11"/>
     </row>
-    <row r="697" spans="1:17">
+    <row r="697" ht="17" spans="1:17">
       <c r="A697" s="6">
         <v>2025</v>
       </c>
@@ -26068,7 +26688,7 @@
       <c r="P697" s="11"/>
       <c r="Q697" s="11"/>
     </row>
-    <row r="698" spans="1:17">
+    <row r="698" ht="17" spans="1:17">
       <c r="A698" s="6">
         <v>2025</v>
       </c>
@@ -26096,7 +26716,7 @@
       <c r="P698" s="11"/>
       <c r="Q698" s="11"/>
     </row>
-    <row r="699" spans="1:17">
+    <row r="699" ht="17" spans="1:17">
       <c r="A699" s="6">
         <v>2025</v>
       </c>
@@ -26124,7 +26744,7 @@
       <c r="P699" s="11"/>
       <c r="Q699" s="11"/>
     </row>
-    <row r="700" spans="1:17">
+    <row r="700" ht="17" spans="1:17">
       <c r="A700" s="6">
         <v>2025</v>
       </c>
@@ -26152,7 +26772,7 @@
       <c r="P700" s="11"/>
       <c r="Q700" s="11"/>
     </row>
-    <row r="701" spans="1:17">
+    <row r="701" ht="17" spans="1:17">
       <c r="A701" s="6">
         <v>2025</v>
       </c>
@@ -26180,7 +26800,7 @@
       <c r="P701" s="11"/>
       <c r="Q701" s="11"/>
     </row>
-    <row r="702" spans="1:17">
+    <row r="702" ht="17" spans="1:17">
       <c r="A702" s="12">
         <v>2025</v>
       </c>
@@ -26207,7 +26827,7 @@
       </c>
       <c r="I702" s="10"/>
     </row>
-    <row r="703" spans="1:17">
+    <row r="703" ht="17" spans="1:17">
       <c r="A703" s="12">
         <v>2025</v>
       </c>
@@ -26234,7 +26854,7 @@
       </c>
       <c r="I703" s="11"/>
     </row>
-    <row r="704" spans="1:17">
+    <row r="704" ht="17" spans="1:17">
       <c r="A704" s="12">
         <v>2025</v>
       </c>
@@ -26261,7 +26881,7 @@
       </c>
       <c r="I704" s="11"/>
     </row>
-    <row r="705" spans="1:9">
+    <row r="705" ht="17" spans="1:9">
       <c r="A705" s="12">
         <v>2025</v>
       </c>
@@ -26288,7 +26908,7 @@
       </c>
       <c r="I705" s="11"/>
     </row>
-    <row r="706" spans="1:9">
+    <row r="706" ht="17" spans="1:9">
       <c r="A706" s="12">
         <v>2025</v>
       </c>
@@ -26315,7 +26935,7 @@
       </c>
       <c r="I706" s="11"/>
     </row>
-    <row r="707" spans="1:9">
+    <row r="707" ht="17" spans="1:9">
       <c r="A707" s="12">
         <v>2025</v>
       </c>
@@ -26342,7 +26962,7 @@
       </c>
       <c r="I707" s="11"/>
     </row>
-    <row r="708" spans="1:9">
+    <row r="708" ht="17" spans="1:9">
       <c r="A708" s="12">
         <v>2025</v>
       </c>
@@ -26369,7 +26989,7 @@
       </c>
       <c r="I708" s="11"/>
     </row>
-    <row r="709" spans="1:9">
+    <row r="709" ht="17" spans="1:9">
       <c r="A709" s="12">
         <v>2025</v>
       </c>
@@ -26396,7 +27016,7 @@
       </c>
       <c r="I709" s="11"/>
     </row>
-    <row r="710" spans="1:9">
+    <row r="710" ht="17" spans="1:9">
       <c r="A710" s="12">
         <v>2025</v>
       </c>
@@ -26423,7 +27043,7 @@
       </c>
       <c r="I710" s="11"/>
     </row>
-    <row r="711" spans="1:9">
+    <row r="711" ht="17" spans="1:9">
       <c r="A711" s="12">
         <v>2025</v>
       </c>
@@ -26450,7 +27070,7 @@
       </c>
       <c r="I711" s="11"/>
     </row>
-    <row r="712" spans="1:9">
+    <row r="712" ht="17" spans="1:9">
       <c r="A712" s="12">
         <v>2025</v>
       </c>
@@ -26477,7 +27097,7 @@
       </c>
       <c r="I712" s="11"/>
     </row>
-    <row r="713" spans="1:9">
+    <row r="713" ht="17" spans="1:9">
       <c r="A713" s="12">
         <v>2025</v>
       </c>
@@ -26504,7 +27124,7 @@
       </c>
       <c r="I713" s="11"/>
     </row>
-    <row r="714" spans="1:9">
+    <row r="714" ht="17" spans="1:9">
       <c r="A714" s="12">
         <v>2025</v>
       </c>
@@ -26531,7 +27151,7 @@
       </c>
       <c r="I714" s="11"/>
     </row>
-    <row r="715" spans="1:9">
+    <row r="715" ht="17" spans="1:9">
       <c r="A715" s="12">
         <v>2025</v>
       </c>
@@ -26558,7 +27178,7 @@
       </c>
       <c r="I715" s="11"/>
     </row>
-    <row r="716" spans="1:9">
+    <row r="716" ht="17" spans="1:9">
       <c r="A716" s="12">
         <v>2025</v>
       </c>
@@ -26585,7 +27205,7 @@
       </c>
       <c r="I716" s="11"/>
     </row>
-    <row r="717" spans="1:9">
+    <row r="717" ht="17" spans="1:9">
       <c r="A717" s="12">
         <v>2025</v>
       </c>
@@ -26612,7 +27232,7 @@
       </c>
       <c r="I717" s="11"/>
     </row>
-    <row r="718" spans="1:9">
+    <row r="718" ht="17" spans="1:9">
       <c r="A718" s="12">
         <v>2025</v>
       </c>
@@ -26639,7 +27259,7 @@
       </c>
       <c r="I718" s="11"/>
     </row>
-    <row r="719" spans="1:9">
+    <row r="719" ht="17" spans="1:9">
       <c r="A719" s="12">
         <v>2025</v>
       </c>
@@ -26666,7 +27286,7 @@
       </c>
       <c r="I719" s="11"/>
     </row>
-    <row r="720" spans="1:9">
+    <row r="720" ht="17" spans="1:9">
       <c r="A720" s="12">
         <v>2025</v>
       </c>
@@ -26693,7 +27313,7 @@
       </c>
       <c r="I720" s="11"/>
     </row>
-    <row r="721" spans="1:10">
+    <row r="721" ht="17" spans="1:10">
       <c r="A721" s="12">
         <v>2025</v>
       </c>
@@ -26720,7 +27340,7 @@
       </c>
       <c r="I721" s="11"/>
     </row>
-    <row r="722" spans="1:10">
+    <row r="722" ht="17" spans="1:10">
       <c r="A722" s="6">
         <v>2025</v>
       </c>
@@ -26746,7 +27366,7 @@
       <c r="I722" s="10"/>
       <c r="J722" s="10"/>
     </row>
-    <row r="723" spans="1:10">
+    <row r="723" ht="17" spans="1:10">
       <c r="A723" s="6">
         <v>2025</v>
       </c>
@@ -26772,7 +27392,7 @@
       <c r="I723" s="10"/>
       <c r="J723" s="10"/>
     </row>
-    <row r="724" spans="1:10">
+    <row r="724" ht="17" spans="1:10">
       <c r="A724" s="6">
         <v>2025</v>
       </c>
@@ -26798,7 +27418,7 @@
       <c r="I724" s="10"/>
       <c r="J724" s="10"/>
     </row>
-    <row r="725" spans="1:10">
+    <row r="725" ht="17" spans="1:10">
       <c r="A725" s="6">
         <v>2025</v>
       </c>
@@ -26824,7 +27444,7 @@
       <c r="I725" s="10"/>
       <c r="J725" s="10"/>
     </row>
-    <row r="726" spans="1:10">
+    <row r="726" ht="17" spans="1:10">
       <c r="A726" s="6">
         <v>2025</v>
       </c>
@@ -26850,7 +27470,7 @@
       <c r="I726" s="10"/>
       <c r="J726" s="10"/>
     </row>
-    <row r="727" spans="1:10">
+    <row r="727" ht="17" spans="1:10">
       <c r="A727" s="6">
         <v>2025</v>
       </c>
@@ -26876,7 +27496,7 @@
       <c r="I727" s="10"/>
       <c r="J727" s="10"/>
     </row>
-    <row r="728" spans="1:10">
+    <row r="728" ht="17" spans="1:10">
       <c r="A728" s="6">
         <v>2025</v>
       </c>
@@ -26902,7 +27522,7 @@
       <c r="I728" s="10"/>
       <c r="J728" s="10"/>
     </row>
-    <row r="729" spans="1:10">
+    <row r="729" ht="17" spans="1:10">
       <c r="A729" s="6">
         <v>2025</v>
       </c>
@@ -26928,7 +27548,7 @@
       <c r="I729" s="10"/>
       <c r="J729" s="10"/>
     </row>
-    <row r="730" spans="1:10">
+    <row r="730" ht="17" spans="1:10">
       <c r="A730" s="6">
         <v>2025</v>
       </c>
@@ -26954,7 +27574,7 @@
       <c r="I730" s="10"/>
       <c r="J730" s="10"/>
     </row>
-    <row r="731" spans="1:10">
+    <row r="731" ht="17" spans="1:10">
       <c r="A731" s="6">
         <v>2025</v>
       </c>
@@ -26980,7 +27600,7 @@
       <c r="I731" s="10"/>
       <c r="J731" s="10"/>
     </row>
-    <row r="732" spans="1:10">
+    <row r="732" ht="17" spans="1:10">
       <c r="A732" s="6">
         <v>2025</v>
       </c>
@@ -27006,7 +27626,7 @@
       <c r="I732" s="10"/>
       <c r="J732" s="11"/>
     </row>
-    <row r="733" spans="1:10">
+    <row r="733" ht="17" spans="1:10">
       <c r="A733" s="6">
         <v>2025</v>
       </c>
@@ -27032,7 +27652,7 @@
       <c r="I733" s="10"/>
       <c r="J733" s="11"/>
     </row>
-    <row r="734" spans="1:10">
+    <row r="734" ht="17" spans="1:10">
       <c r="A734" s="6">
         <v>2025</v>
       </c>
@@ -27058,7 +27678,7 @@
       <c r="I734" s="10"/>
       <c r="J734" s="11"/>
     </row>
-    <row r="735" spans="1:10">
+    <row r="735" ht="17" spans="1:10">
       <c r="A735" s="6">
         <v>2025</v>
       </c>
@@ -27084,7 +27704,7 @@
       <c r="I735" s="10"/>
       <c r="J735" s="11"/>
     </row>
-    <row r="736" spans="1:10">
+    <row r="736" ht="17" spans="1:10">
       <c r="A736" s="6">
         <v>2025</v>
       </c>
@@ -27110,7 +27730,7 @@
       <c r="I736" s="10"/>
       <c r="J736" s="11"/>
     </row>
-    <row r="737" spans="1:10">
+    <row r="737" ht="17" spans="1:10">
       <c r="A737" s="6">
         <v>2025</v>
       </c>
@@ -27136,7 +27756,7 @@
       <c r="I737" s="11"/>
       <c r="J737" s="11"/>
     </row>
-    <row r="738" spans="1:10">
+    <row r="738" ht="17" spans="1:10">
       <c r="A738" s="6">
         <v>2025</v>
       </c>
@@ -27162,7 +27782,7 @@
       <c r="I738" s="11"/>
       <c r="J738" s="11"/>
     </row>
-    <row r="739" spans="1:10">
+    <row r="739" ht="17" spans="1:10">
       <c r="A739" s="6">
         <v>2025</v>
       </c>
@@ -27188,7 +27808,7 @@
       <c r="I739" s="11"/>
       <c r="J739" s="11"/>
     </row>
-    <row r="740" spans="1:10">
+    <row r="740" ht="17" spans="1:10">
       <c r="A740" s="6">
         <v>2025</v>
       </c>
@@ -27214,7 +27834,7 @@
       <c r="I740" s="11"/>
       <c r="J740" s="11"/>
     </row>
-    <row r="741" spans="1:10">
+    <row r="741" ht="17" spans="1:10">
       <c r="A741" s="6">
         <v>2025</v>
       </c>
@@ -27240,7 +27860,7 @@
       <c r="I741" s="11"/>
       <c r="J741" s="11"/>
     </row>
-    <row r="742" spans="1:10">
+    <row r="742" ht="17" spans="1:10">
       <c r="A742" s="12">
         <v>2025</v>
       </c>
@@ -27266,7 +27886,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="743" spans="1:10">
+    <row r="743" ht="17" spans="1:10">
       <c r="A743" s="12">
         <v>2025</v>
       </c>
@@ -27292,7 +27912,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="744" spans="1:10">
+    <row r="744" ht="17" spans="1:10">
       <c r="A744" s="12">
         <v>2025</v>
       </c>
@@ -27318,7 +27938,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="745" spans="1:10">
+    <row r="745" ht="17" spans="1:10">
       <c r="A745" s="12">
         <v>2025</v>
       </c>
@@ -27344,7 +27964,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="746" spans="1:10">
+    <row r="746" ht="17" spans="1:10">
       <c r="A746" s="12">
         <v>2025</v>
       </c>
@@ -27370,7 +27990,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="747" spans="1:10">
+    <row r="747" ht="17" spans="1:10">
       <c r="A747" s="12">
         <v>2025</v>
       </c>
@@ -27396,7 +28016,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="748" spans="1:10">
+    <row r="748" ht="17" spans="1:10">
       <c r="A748" s="12">
         <v>2025</v>
       </c>
@@ -27422,7 +28042,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="749" spans="1:10">
+    <row r="749" ht="17" spans="1:10">
       <c r="A749" s="12">
         <v>2025</v>
       </c>
@@ -27448,7 +28068,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="750" spans="1:10">
+    <row r="750" ht="17" spans="1:10">
       <c r="A750" s="12">
         <v>2025</v>
       </c>
@@ -27474,7 +28094,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="751" spans="1:10">
+    <row r="751" ht="17" spans="1:10">
       <c r="A751" s="12">
         <v>2025</v>
       </c>
@@ -27500,7 +28120,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="752" spans="1:10">
+    <row r="752" ht="17" spans="1:10">
       <c r="A752" s="12">
         <v>2025</v>
       </c>
@@ -27526,7 +28146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="753" spans="1:16">
+    <row r="753" ht="17" spans="1:16">
       <c r="A753" s="12">
         <v>2025</v>
       </c>
@@ -27552,7 +28172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="754" spans="1:16">
+    <row r="754" ht="17" spans="1:16">
       <c r="A754" s="12">
         <v>2025</v>
       </c>
@@ -27578,7 +28198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="755" spans="1:16">
+    <row r="755" ht="17" spans="1:16">
       <c r="A755" s="12">
         <v>2025</v>
       </c>
@@ -27604,7 +28224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="756" spans="1:16">
+    <row r="756" ht="17" spans="1:16">
       <c r="A756" s="12">
         <v>2025</v>
       </c>
@@ -27630,7 +28250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="757" spans="1:16">
+    <row r="757" ht="17" spans="1:16">
       <c r="A757" s="12">
         <v>2025</v>
       </c>
@@ -27656,7 +28276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="758" spans="1:16">
+    <row r="758" ht="17" spans="1:16">
       <c r="A758" s="12">
         <v>2025</v>
       </c>
@@ -27682,7 +28302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="759" spans="1:16">
+    <row r="759" ht="17" spans="1:16">
       <c r="A759" s="12">
         <v>2025</v>
       </c>
@@ -27708,7 +28328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="760" spans="1:16">
+    <row r="760" ht="17" spans="1:16">
       <c r="A760" s="12">
         <v>2025</v>
       </c>
@@ -27734,7 +28354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="761" spans="1:16">
+    <row r="761" ht="17" spans="1:16">
       <c r="A761" s="12">
         <v>2025</v>
       </c>
@@ -28282,7 +28902,7 @@
       <c r="H781" s="6"/>
     </row>
     <row r="782" spans="1:16">
-      <c r="A782" s="6">
+      <c r="A782" s="12">
         <v>2025</v>
       </c>
       <c r="B782" s="12">
@@ -28308,7 +28928,7 @@
       </c>
     </row>
     <row r="783" spans="1:16">
-      <c r="A783" s="6">
+      <c r="A783" s="12">
         <v>2025</v>
       </c>
       <c r="B783" s="12">
@@ -28334,7 +28954,7 @@
       </c>
     </row>
     <row r="784" spans="1:16">
-      <c r="A784" s="6">
+      <c r="A784" s="12">
         <v>2025</v>
       </c>
       <c r="B784" s="12">
@@ -28360,7 +28980,7 @@
       </c>
     </row>
     <row r="785" spans="1:8">
-      <c r="A785" s="6">
+      <c r="A785" s="12">
         <v>2025</v>
       </c>
       <c r="B785" s="12">
@@ -28386,7 +29006,7 @@
       </c>
     </row>
     <row r="786" spans="1:8">
-      <c r="A786" s="6">
+      <c r="A786" s="12">
         <v>2025</v>
       </c>
       <c r="B786" s="12">
@@ -28412,7 +29032,7 @@
       </c>
     </row>
     <row r="787" spans="1:8">
-      <c r="A787" s="6">
+      <c r="A787" s="12">
         <v>2025</v>
       </c>
       <c r="B787" s="12">
@@ -28438,7 +29058,7 @@
       </c>
     </row>
     <row r="788" spans="1:8">
-      <c r="A788" s="6">
+      <c r="A788" s="12">
         <v>2025</v>
       </c>
       <c r="B788" s="12">
@@ -28464,7 +29084,7 @@
       </c>
     </row>
     <row r="789" spans="1:8">
-      <c r="A789" s="6">
+      <c r="A789" s="12">
         <v>2025</v>
       </c>
       <c r="B789" s="12">
@@ -28490,7 +29110,7 @@
       </c>
     </row>
     <row r="790" spans="1:8">
-      <c r="A790" s="6">
+      <c r="A790" s="12">
         <v>2025</v>
       </c>
       <c r="B790" s="12">
@@ -28516,7 +29136,7 @@
       </c>
     </row>
     <row r="791" spans="1:8">
-      <c r="A791" s="6">
+      <c r="A791" s="12">
         <v>2025</v>
       </c>
       <c r="B791" s="12">
@@ -28542,7 +29162,7 @@
       </c>
     </row>
     <row r="792" spans="1:8">
-      <c r="A792" s="6">
+      <c r="A792" s="12">
         <v>2025</v>
       </c>
       <c r="B792" s="12">
@@ -28568,7 +29188,7 @@
       </c>
     </row>
     <row r="793" spans="1:8">
-      <c r="A793" s="6">
+      <c r="A793" s="12">
         <v>2025</v>
       </c>
       <c r="B793" s="12">
@@ -28594,7 +29214,7 @@
       </c>
     </row>
     <row r="794" spans="1:8">
-      <c r="A794" s="6">
+      <c r="A794" s="12">
         <v>2025</v>
       </c>
       <c r="B794" s="12">
@@ -28620,7 +29240,7 @@
       </c>
     </row>
     <row r="795" spans="1:8">
-      <c r="A795" s="6">
+      <c r="A795" s="12">
         <v>2025</v>
       </c>
       <c r="B795" s="12">
@@ -28646,7 +29266,7 @@
       </c>
     </row>
     <row r="796" spans="1:8">
-      <c r="A796" s="6">
+      <c r="A796" s="12">
         <v>2025</v>
       </c>
       <c r="B796" s="12">
@@ -28672,7 +29292,7 @@
       </c>
     </row>
     <row r="797" spans="1:8">
-      <c r="A797" s="6">
+      <c r="A797" s="12">
         <v>2025</v>
       </c>
       <c r="B797" s="12">
@@ -28698,7 +29318,7 @@
       </c>
     </row>
     <row r="798" spans="1:8">
-      <c r="A798" s="6">
+      <c r="A798" s="12">
         <v>2025</v>
       </c>
       <c r="B798" s="12">
@@ -28724,7 +29344,7 @@
       </c>
     </row>
     <row r="799" spans="1:8">
-      <c r="A799" s="6">
+      <c r="A799" s="12">
         <v>2025</v>
       </c>
       <c r="B799" s="12">
@@ -28750,7 +29370,7 @@
       </c>
     </row>
     <row r="800" spans="1:8">
-      <c r="A800" s="6">
+      <c r="A800" s="12">
         <v>2025</v>
       </c>
       <c r="B800" s="12">
@@ -28775,8 +29395,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="801" spans="1:8">
-      <c r="A801" s="6">
+    <row r="801" ht="17" spans="1:8">
+      <c r="A801" s="12">
         <v>2025</v>
       </c>
       <c r="B801" s="12">
@@ -29451,13 +30071,13 @@
         <v>7</v>
       </c>
       <c r="E828" s="12">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="F828" s="12" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G828" s="12" t="s">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="H828" s="9">
         <v>6</v>
@@ -29477,13 +30097,13 @@
         <v>8</v>
       </c>
       <c r="E829" s="12">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="F829" s="12" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="G829" s="12" t="s">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="H829" s="9">
         <v>4</v>
@@ -38846,18 +39466,22 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1201" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H1201" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="29.28515625" customWidth="1"/>
+    <col min="1" max="1" width="29.2857142857143" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -38877,7 +39501,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" ht="17" spans="1:2">
       <c r="A3" s="9" t="s">
         <v>79</v>
       </c>
@@ -38893,7 +39517,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" ht="17" spans="1:2">
       <c r="A5" s="9" t="s">
         <v>84</v>
       </c>
@@ -38925,7 +39549,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" ht="17" spans="1:2">
       <c r="A9" s="9" t="s">
         <v>81</v>
       </c>
@@ -38941,7 +39565,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" ht="17" spans="1:2">
       <c r="A11" s="9" t="s">
         <v>85</v>
       </c>
@@ -38957,7 +39581,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" ht="17" spans="1:2">
       <c r="A13" s="9" t="s">
         <v>82</v>
       </c>
@@ -38973,7 +39597,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" ht="17" spans="1:2">
       <c r="A15" s="9" t="s">
         <v>83</v>
       </c>
@@ -38989,7 +39613,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" ht="17" spans="1:2">
       <c r="A17" s="9" t="s">
         <v>80</v>
       </c>
@@ -39005,7 +39629,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" ht="17" spans="1:2">
       <c r="A19" s="9" t="s">
         <v>86</v>
       </c>
@@ -39023,22 +39647,24 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="7.5703125" customWidth="1"/>
-    <col min="2" max="2" width="15.42578125" customWidth="1"/>
-    <col min="3" max="3" width="9.42578125" customWidth="1"/>
-    <col min="4" max="4" width="42.5703125" customWidth="1"/>
-    <col min="5" max="5" width="32.85546875" customWidth="1"/>
-    <col min="6" max="6" width="11.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.5703125" customWidth="1"/>
-    <col min="8" max="8" width="6.7109375" customWidth="1"/>
+    <col min="1" max="1" width="7.57142857142857" customWidth="1"/>
+    <col min="2" max="2" width="15.4285714285714" customWidth="1"/>
+    <col min="3" max="3" width="9.42857142857143" customWidth="1"/>
+    <col min="4" max="4" width="42.5714285714286" customWidth="1"/>
+    <col min="5" max="5" width="32.8571428571429" customWidth="1"/>
+    <col min="6" max="6" width="11.7142857142857" customWidth="1"/>
+    <col min="7" max="7" width="4.57142857142857" customWidth="1"/>
+    <col min="8" max="8" width="6.71428571428571" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -39088,7 +39714,7 @@
         <v>58</v>
       </c>
       <c r="H2" s="6">
-        <v>5.2779999999999996</v>
+        <v>5.278</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -39112,7 +39738,7 @@
         <v>56</v>
       </c>
       <c r="H3" s="6">
-        <v>5.4509999999999996</v>
+        <v>5.451</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -39136,7 +39762,7 @@
         <v>53</v>
       </c>
       <c r="H4" s="6">
-        <v>5.8070000000000004</v>
+        <v>5.807</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -39160,7 +39786,7 @@
         <v>57</v>
       </c>
       <c r="H5" s="6">
-        <v>5.4119999999999999</v>
+        <v>5.412</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -39184,7 +39810,7 @@
         <v>50</v>
       </c>
       <c r="H6" s="6">
-        <v>5.1740000000000004</v>
+        <v>5.174</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -39210,7 +39836,7 @@
         <v>57</v>
       </c>
       <c r="H7" s="6">
-        <v>5.4119999999999999</v>
+        <v>5.412</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -39236,7 +39862,7 @@
         <v>63</v>
       </c>
       <c r="H8" s="6">
-        <v>4.9089999999999998</v>
+        <v>4.909</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -39260,7 +39886,7 @@
         <v>78</v>
       </c>
       <c r="H9" s="6">
-        <v>3.3370000000000002</v>
+        <v>3.337</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -39310,7 +39936,7 @@
         <v>70</v>
       </c>
       <c r="H11" s="6">
-        <v>4.3609999999999998</v>
+        <v>4.361</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -39334,7 +39960,7 @@
         <v>71</v>
       </c>
       <c r="H12" s="6">
-        <v>4.3179999999999996</v>
+        <v>4.318</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -39382,7 +40008,7 @@
         <v>44</v>
       </c>
       <c r="H14" s="6">
-        <v>7.0039999999999996</v>
+        <v>7.004</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -39406,7 +40032,7 @@
         <v>70</v>
       </c>
       <c r="H15" s="6">
-        <v>4.3810000000000002</v>
+        <v>4.381</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -39430,7 +40056,7 @@
         <v>72</v>
       </c>
       <c r="H16" s="6">
-        <v>4.2590000000000003</v>
+        <v>4.259</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -39456,7 +40082,7 @@
         <v>53</v>
       </c>
       <c r="H17" s="6">
-        <v>5.7930000000000001</v>
+        <v>5.793</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -39480,7 +40106,7 @@
         <v>51</v>
       </c>
       <c r="H18" s="6">
-        <v>6.0030000000000001</v>
+        <v>6.003</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -39530,7 +40156,7 @@
         <v>56</v>
       </c>
       <c r="H20" s="6">
-        <v>5.5129999999999999</v>
+        <v>5.513</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -39554,7 +40180,7 @@
         <v>71</v>
       </c>
       <c r="H21" s="6">
-        <v>4.3040000000000003</v>
+        <v>4.304</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -39578,7 +40204,7 @@
         <v>71</v>
       </c>
       <c r="H22" s="6">
-        <v>4.3090000000000002</v>
+        <v>4.309</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -39604,7 +40230,7 @@
         <v>50</v>
       </c>
       <c r="H23" s="6">
-        <v>6.2009999999999996</v>
+        <v>6.201</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -39628,7 +40254,7 @@
         <v>57</v>
       </c>
       <c r="H24" s="6">
-        <v>5.4189999999999996</v>
+        <v>5.419</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -39652,7 +40278,7 @@
         <v>58</v>
       </c>
       <c r="H25" s="6">
-        <v>5.2809999999999997</v>
+        <v>5.281</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -39678,25 +40304,27 @@
         <v>57</v>
       </c>
       <c r="H26" s="6">
-        <v>5.4160000000000004</v>
+        <v>5.416</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:G44"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="4.7109375" customWidth="1"/>
-    <col min="2" max="2" width="6.5703125" customWidth="1"/>
-    <col min="3" max="3" width="17.85546875" customWidth="1"/>
-    <col min="4" max="4" width="5.28515625" customWidth="1"/>
-    <col min="5" max="5" width="5.140625" customWidth="1"/>
-    <col min="6" max="6" width="16.140625" customWidth="1"/>
+    <col min="1" max="1" width="4.71428571428571" customWidth="1"/>
+    <col min="2" max="2" width="6.57142857142857" customWidth="1"/>
+    <col min="3" max="3" width="17.8571428571429" customWidth="1"/>
+    <col min="4" max="4" width="5.28571428571429" customWidth="1"/>
+    <col min="5" max="5" width="5.14285714285714" customWidth="1"/>
+    <col min="6" max="6" width="16.1428571428571" customWidth="1"/>
     <col min="7" max="7" width="12" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -40715,19 +41343,21 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:E22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="4" style="1" customWidth="1"/>
-    <col min="2" max="2" width="4.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="4.85714285714286" style="1" customWidth="1"/>
     <col min="3" max="3" width="12" style="1" customWidth="1"/>
-    <col min="4" max="4" width="29.28515625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="8.5703125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="29.2857142857143" style="1" customWidth="1"/>
+    <col min="5" max="5" width="8.57142857142857" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -41106,5 +41736,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/public/docs/datas/f1.xlsx
+++ b/public/docs/datas/f1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28260" windowHeight="15240" activeTab="1"/>
+    <workbookView windowHeight="24020" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="rounds" sheetId="7" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4611" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4883" uniqueCount="270">
   <si>
     <t>year</t>
   </si>
@@ -1565,7 +1565,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
@@ -1640,6 +1640,7 @@
     <xf numFmtId="0" fontId="1" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -2580,13 +2581,13 @@
       <c r="C2" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="40">
+      <c r="D2" s="41">
         <v>45730</v>
       </c>
-      <c r="E2" s="41">
+      <c r="E2" s="42">
         <v>0.395833333333333</v>
       </c>
-      <c r="F2" s="41">
+      <c r="F2" s="42">
         <v>0.4375</v>
       </c>
       <c r="G2" s="6">
@@ -2603,13 +2604,13 @@
       <c r="C3" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="40">
+      <c r="D3" s="41">
         <v>45730</v>
       </c>
-      <c r="E3" s="41">
+      <c r="E3" s="42">
         <v>0.541666666666667</v>
       </c>
-      <c r="F3" s="41">
+      <c r="F3" s="42">
         <v>0.583333333333333</v>
       </c>
       <c r="G3" s="6">
@@ -2626,13 +2627,13 @@
       <c r="C4" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D4" s="40">
+      <c r="D4" s="41">
         <v>45731</v>
       </c>
-      <c r="E4" s="41">
+      <c r="E4" s="42">
         <v>0.395833333333333</v>
       </c>
-      <c r="F4" s="41">
+      <c r="F4" s="42">
         <v>0.4375</v>
       </c>
       <c r="G4" s="6">
@@ -2649,13 +2650,13 @@
       <c r="C5" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="40">
+      <c r="D5" s="41">
         <v>45731</v>
       </c>
-      <c r="E5" s="41">
+      <c r="E5" s="42">
         <v>0.541666666666667</v>
       </c>
-      <c r="F5" s="41">
+      <c r="F5" s="42">
         <v>0.583333333333333</v>
       </c>
       <c r="G5" s="6">
@@ -2672,13 +2673,13 @@
       <c r="C6" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="40">
+      <c r="D6" s="41">
         <v>45732</v>
       </c>
-      <c r="E6" s="41">
+      <c r="E6" s="42">
         <v>0.5</v>
       </c>
-      <c r="F6" s="41"/>
+      <c r="F6" s="42"/>
       <c r="G6" s="6">
         <v>1</v>
       </c>
@@ -2693,13 +2694,13 @@
       <c r="C7" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D7" s="42">
+      <c r="D7" s="43">
         <v>45737</v>
       </c>
-      <c r="E7" s="43">
+      <c r="E7" s="44">
         <v>0.479166666666667</v>
       </c>
-      <c r="F7" s="43">
+      <c r="F7" s="44">
         <v>0.520833333333333</v>
       </c>
       <c r="G7" s="18">
@@ -2716,13 +2717,13 @@
       <c r="C8" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="42">
+      <c r="D8" s="43">
         <v>45737</v>
       </c>
-      <c r="E8" s="43">
+      <c r="E8" s="44">
         <v>0.645833333333333</v>
       </c>
-      <c r="F8" s="43">
+      <c r="F8" s="44">
         <v>0.676388888888889</v>
       </c>
       <c r="G8" s="18">
@@ -2739,13 +2740,13 @@
       <c r="C9" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="D9" s="42">
+      <c r="D9" s="43">
         <v>45738</v>
       </c>
-      <c r="E9" s="43">
+      <c r="E9" s="44">
         <v>0.458333333333333</v>
       </c>
-      <c r="F9" s="43">
+      <c r="F9" s="44">
         <v>0.5</v>
       </c>
       <c r="G9" s="18">
@@ -2762,13 +2763,13 @@
       <c r="C10" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="42">
+      <c r="D10" s="43">
         <v>45738</v>
       </c>
-      <c r="E10" s="43">
+      <c r="E10" s="44">
         <v>0.625</v>
       </c>
-      <c r="F10" s="43">
+      <c r="F10" s="44">
         <v>0.666666666666667</v>
       </c>
       <c r="G10" s="18">
@@ -2785,10 +2786,10 @@
       <c r="C11" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D11" s="42">
+      <c r="D11" s="43">
         <v>45739</v>
       </c>
-      <c r="E11" s="43">
+      <c r="E11" s="44">
         <v>0.625</v>
       </c>
       <c r="F11" s="18"/>
@@ -2806,13 +2807,13 @@
       <c r="C12" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D12" s="40">
+      <c r="D12" s="41">
         <v>45751</v>
       </c>
-      <c r="E12" s="41">
+      <c r="E12" s="42">
         <v>0.4375</v>
       </c>
-      <c r="F12" s="41">
+      <c r="F12" s="42">
         <v>0.479166666666667</v>
       </c>
       <c r="G12" s="6">
@@ -2829,13 +2830,13 @@
       <c r="C13" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="40">
+      <c r="D13" s="41">
         <v>45751</v>
       </c>
-      <c r="E13" s="41">
+      <c r="E13" s="42">
         <v>0.583333333333333</v>
       </c>
-      <c r="F13" s="41">
+      <c r="F13" s="42">
         <v>0.625</v>
       </c>
       <c r="G13" s="6">
@@ -2852,13 +2853,13 @@
       <c r="C14" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D14" s="40">
+      <c r="D14" s="41">
         <v>45752</v>
       </c>
-      <c r="E14" s="41">
+      <c r="E14" s="42">
         <v>0.4375</v>
       </c>
-      <c r="F14" s="41">
+      <c r="F14" s="42">
         <v>0.479166666666667</v>
       </c>
       <c r="G14" s="6">
@@ -2875,13 +2876,13 @@
       <c r="C15" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="40">
+      <c r="D15" s="41">
         <v>45752</v>
       </c>
-      <c r="E15" s="41">
+      <c r="E15" s="42">
         <v>0.583333333333333</v>
       </c>
-      <c r="F15" s="41">
+      <c r="F15" s="42">
         <v>0.625</v>
       </c>
       <c r="G15" s="6">
@@ -2898,10 +2899,10 @@
       <c r="C16" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D16" s="40">
+      <c r="D16" s="41">
         <v>45753</v>
       </c>
-      <c r="E16" s="41">
+      <c r="E16" s="42">
         <v>0.541666666666667</v>
       </c>
       <c r="F16" s="6"/>
@@ -2919,13 +2920,13 @@
       <c r="C17" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D17" s="42">
+      <c r="D17" s="43">
         <v>45758</v>
       </c>
-      <c r="E17" s="43">
+      <c r="E17" s="44">
         <v>0.8125</v>
       </c>
-      <c r="F17" s="43">
+      <c r="F17" s="44">
         <v>0.854166666666667</v>
       </c>
       <c r="G17" s="18">
@@ -2942,13 +2943,13 @@
       <c r="C18" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="D18" s="42">
+      <c r="D18" s="43">
         <v>45758</v>
       </c>
-      <c r="E18" s="43">
+      <c r="E18" s="44">
         <v>0.958333333333333</v>
       </c>
-      <c r="F18" s="43">
+      <c r="F18" s="44">
         <v>0</v>
       </c>
       <c r="G18" s="18">
@@ -2965,13 +2966,13 @@
       <c r="C19" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="D19" s="42">
+      <c r="D19" s="43">
         <v>45759</v>
       </c>
-      <c r="E19" s="43">
+      <c r="E19" s="44">
         <v>0.854166666666667</v>
       </c>
-      <c r="F19" s="43">
+      <c r="F19" s="44">
         <v>0.895833333333333</v>
       </c>
       <c r="G19" s="18">
@@ -2988,13 +2989,13 @@
       <c r="C20" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D20" s="42">
+      <c r="D20" s="43">
         <v>45760</v>
       </c>
-      <c r="E20" s="43">
-        <v>0</v>
-      </c>
-      <c r="F20" s="43">
+      <c r="E20" s="44">
+        <v>0</v>
+      </c>
+      <c r="F20" s="44">
         <v>0.0416666666666667</v>
       </c>
       <c r="G20" s="18">
@@ -3011,10 +3012,10 @@
       <c r="C21" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D21" s="42">
+      <c r="D21" s="43">
         <v>45760</v>
       </c>
-      <c r="E21" s="43">
+      <c r="E21" s="44">
         <v>0.958333333333333</v>
       </c>
       <c r="F21" s="18"/>
@@ -3032,13 +3033,13 @@
       <c r="C22" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D22" s="40">
+      <c r="D22" s="41">
         <v>45765</v>
       </c>
-      <c r="E22" s="41">
+      <c r="E22" s="42">
         <v>0.895833333333333</v>
       </c>
-      <c r="F22" s="41">
+      <c r="F22" s="42">
         <v>0.9375</v>
       </c>
       <c r="G22" s="6">
@@ -3055,13 +3056,13 @@
       <c r="C23" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D23" s="40">
+      <c r="D23" s="41">
         <v>45766</v>
       </c>
-      <c r="E23" s="41">
+      <c r="E23" s="42">
         <v>0.0416666666666667</v>
       </c>
-      <c r="F23" s="41">
+      <c r="F23" s="42">
         <v>0.0833333333333333</v>
       </c>
       <c r="G23" s="6">
@@ -3078,13 +3079,13 @@
       <c r="C24" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="40">
+      <c r="D24" s="41">
         <v>45766</v>
       </c>
-      <c r="E24" s="41">
+      <c r="E24" s="42">
         <v>0.895833333333333</v>
       </c>
-      <c r="F24" s="41">
+      <c r="F24" s="42">
         <v>0.9375</v>
       </c>
       <c r="G24" s="6">
@@ -3101,13 +3102,13 @@
       <c r="C25" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="40">
+      <c r="D25" s="41">
         <v>45767</v>
       </c>
-      <c r="E25" s="41">
+      <c r="E25" s="42">
         <v>0.0416666666666667</v>
       </c>
-      <c r="F25" s="41">
+      <c r="F25" s="42">
         <v>0.0833333333333333</v>
       </c>
       <c r="G25" s="6">
@@ -3124,10 +3125,10 @@
       <c r="C26" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D26" s="40">
+      <c r="D26" s="41">
         <v>45767</v>
       </c>
-      <c r="E26" s="41">
+      <c r="E26" s="42">
         <v>0.0416666666666667</v>
       </c>
       <c r="F26" s="6"/>
@@ -3145,13 +3146,13 @@
       <c r="C27" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D27" s="42">
+      <c r="D27" s="43">
         <v>45780</v>
       </c>
-      <c r="E27" s="43">
+      <c r="E27" s="44">
         <v>0.0208333333333333</v>
       </c>
-      <c r="F27" s="43">
+      <c r="F27" s="44">
         <v>0.0625</v>
       </c>
       <c r="G27" s="18">
@@ -3168,13 +3169,13 @@
       <c r="C28" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="D28" s="42">
+      <c r="D28" s="43">
         <v>45780</v>
       </c>
-      <c r="E28" s="43">
+      <c r="E28" s="44">
         <v>0.1875</v>
       </c>
-      <c r="F28" s="43">
+      <c r="F28" s="44">
         <v>0.218055555555556</v>
       </c>
       <c r="G28" s="18">
@@ -3191,13 +3192,13 @@
       <c r="C29" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="D29" s="42">
+      <c r="D29" s="43">
         <v>45781</v>
       </c>
-      <c r="E29" s="43">
-        <v>0</v>
-      </c>
-      <c r="F29" s="43">
+      <c r="E29" s="44">
+        <v>0</v>
+      </c>
+      <c r="F29" s="44">
         <v>0.0416666666666667</v>
       </c>
       <c r="G29" s="18">
@@ -3214,13 +3215,13 @@
       <c r="C30" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D30" s="42">
+      <c r="D30" s="43">
         <v>45781</v>
       </c>
-      <c r="E30" s="43">
+      <c r="E30" s="44">
         <v>0.166666666666667</v>
       </c>
-      <c r="F30" s="43">
+      <c r="F30" s="44">
         <v>0.208333333333333</v>
       </c>
       <c r="G30" s="18">
@@ -3237,13 +3238,13 @@
       <c r="C31" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D31" s="42">
+      <c r="D31" s="43">
         <v>45782</v>
       </c>
-      <c r="E31" s="43">
+      <c r="E31" s="44">
         <v>0.166666666666667</v>
       </c>
-      <c r="F31" s="43"/>
+      <c r="F31" s="44"/>
       <c r="G31" s="18">
         <v>1</v>
       </c>
@@ -3258,13 +3259,13 @@
       <c r="C32" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D32" s="40">
+      <c r="D32" s="41">
         <v>45793</v>
       </c>
-      <c r="E32" s="41">
+      <c r="E32" s="42">
         <v>0.8125</v>
       </c>
-      <c r="F32" s="41">
+      <c r="F32" s="42">
         <v>0.854166666666667</v>
       </c>
       <c r="G32" s="6">
@@ -3281,13 +3282,13 @@
       <c r="C33" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D33" s="40">
+      <c r="D33" s="41">
         <v>45793</v>
       </c>
-      <c r="E33" s="41">
+      <c r="E33" s="42">
         <v>0.958333333333333</v>
       </c>
-      <c r="F33" s="41">
+      <c r="F33" s="42">
         <v>0</v>
       </c>
       <c r="G33" s="6">
@@ -3304,13 +3305,13 @@
       <c r="C34" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D34" s="40">
+      <c r="D34" s="41">
         <v>45794</v>
       </c>
-      <c r="E34" s="41">
+      <c r="E34" s="42">
         <v>0.770833333333333</v>
       </c>
-      <c r="F34" s="41">
+      <c r="F34" s="42">
         <v>0.8125</v>
       </c>
       <c r="G34" s="6">
@@ -3327,13 +3328,13 @@
       <c r="C35" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D35" s="40">
+      <c r="D35" s="41">
         <v>45794</v>
       </c>
-      <c r="E35" s="41">
+      <c r="E35" s="42">
         <v>0.916666666666667</v>
       </c>
-      <c r="F35" s="41">
+      <c r="F35" s="42">
         <v>0.958333333333333</v>
       </c>
       <c r="G35" s="6">
@@ -3350,10 +3351,10 @@
       <c r="C36" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D36" s="40">
+      <c r="D36" s="41">
         <v>45795</v>
       </c>
-      <c r="E36" s="41">
+      <c r="E36" s="42">
         <v>0.875</v>
       </c>
       <c r="F36" s="6"/>
@@ -3371,13 +3372,13 @@
       <c r="C37" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D37" s="42">
+      <c r="D37" s="43">
         <v>45800</v>
       </c>
-      <c r="E37" s="43">
+      <c r="E37" s="44">
         <v>0.8125</v>
       </c>
-      <c r="F37" s="43">
+      <c r="F37" s="44">
         <v>0.854166666666667</v>
       </c>
       <c r="G37" s="18">
@@ -3394,13 +3395,13 @@
       <c r="C38" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="D38" s="42">
+      <c r="D38" s="43">
         <v>45800</v>
       </c>
-      <c r="E38" s="43">
+      <c r="E38" s="44">
         <v>0.958333333333333</v>
       </c>
-      <c r="F38" s="43">
+      <c r="F38" s="44">
         <v>0</v>
       </c>
       <c r="G38" s="18">
@@ -3417,13 +3418,13 @@
       <c r="C39" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="D39" s="42">
+      <c r="D39" s="43">
         <v>45801</v>
       </c>
-      <c r="E39" s="43">
+      <c r="E39" s="44">
         <v>0.770833333333333</v>
       </c>
-      <c r="F39" s="43">
+      <c r="F39" s="44">
         <v>0.8125</v>
       </c>
       <c r="G39" s="18">
@@ -3440,13 +3441,13 @@
       <c r="C40" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D40" s="42">
+      <c r="D40" s="43">
         <v>45801</v>
       </c>
-      <c r="E40" s="43">
+      <c r="E40" s="44">
         <v>0.916666666666667</v>
       </c>
-      <c r="F40" s="43">
+      <c r="F40" s="44">
         <v>0.958333333333333</v>
       </c>
       <c r="G40" s="18">
@@ -3463,10 +3464,10 @@
       <c r="C41" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D41" s="42">
+      <c r="D41" s="43">
         <v>45802</v>
       </c>
-      <c r="E41" s="43">
+      <c r="E41" s="44">
         <v>0.875</v>
       </c>
       <c r="F41" s="18"/>
@@ -3484,13 +3485,13 @@
       <c r="C42" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D42" s="40">
+      <c r="D42" s="41">
         <v>45807</v>
       </c>
-      <c r="E42" s="41">
+      <c r="E42" s="42">
         <v>0.8125</v>
       </c>
-      <c r="F42" s="41">
+      <c r="F42" s="42">
         <v>0.854166666666667</v>
       </c>
       <c r="G42" s="6">
@@ -3507,13 +3508,13 @@
       <c r="C43" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D43" s="40">
+      <c r="D43" s="41">
         <v>45807</v>
       </c>
-      <c r="E43" s="41">
+      <c r="E43" s="42">
         <v>0.958333333333333</v>
       </c>
-      <c r="F43" s="41">
+      <c r="F43" s="42">
         <v>0</v>
       </c>
       <c r="G43" s="6">
@@ -3530,13 +3531,13 @@
       <c r="C44" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D44" s="40">
+      <c r="D44" s="41">
         <v>45808</v>
       </c>
-      <c r="E44" s="41">
+      <c r="E44" s="42">
         <v>0.770833333333333</v>
       </c>
-      <c r="F44" s="41">
+      <c r="F44" s="42">
         <v>0.8125</v>
       </c>
       <c r="G44" s="6">
@@ -3553,13 +3554,13 @@
       <c r="C45" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D45" s="40">
+      <c r="D45" s="41">
         <v>45808</v>
       </c>
-      <c r="E45" s="41">
+      <c r="E45" s="42">
         <v>0.916666666666667</v>
       </c>
-      <c r="F45" s="41">
+      <c r="F45" s="42">
         <v>0.958333333333333</v>
       </c>
       <c r="G45" s="6">
@@ -3576,10 +3577,10 @@
       <c r="C46" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D46" s="40">
+      <c r="D46" s="41">
         <v>45809</v>
       </c>
-      <c r="E46" s="41">
+      <c r="E46" s="42">
         <v>0.875</v>
       </c>
       <c r="F46" s="6"/>
@@ -3597,13 +3598,13 @@
       <c r="C47" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D47" s="42">
+      <c r="D47" s="43">
         <v>45822</v>
       </c>
-      <c r="E47" s="43">
+      <c r="E47" s="44">
         <v>0.0625</v>
       </c>
-      <c r="F47" s="43">
+      <c r="F47" s="44">
         <v>0.104166666666667</v>
       </c>
       <c r="G47" s="18">
@@ -3620,13 +3621,13 @@
       <c r="C48" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="D48" s="42">
+      <c r="D48" s="43">
         <v>45822</v>
       </c>
-      <c r="E48" s="43">
+      <c r="E48" s="44">
         <v>0.208333333333333</v>
       </c>
-      <c r="F48" s="43">
+      <c r="F48" s="44">
         <v>0.25</v>
       </c>
       <c r="G48" s="18">
@@ -3643,13 +3644,13 @@
       <c r="C49" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="D49" s="42">
+      <c r="D49" s="43">
         <v>45823</v>
       </c>
-      <c r="E49" s="43">
+      <c r="E49" s="44">
         <v>0.0208333333333333</v>
       </c>
-      <c r="F49" s="43">
+      <c r="F49" s="44">
         <v>0.0625</v>
       </c>
       <c r="G49" s="18">
@@ -3666,13 +3667,13 @@
       <c r="C50" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D50" s="42">
+      <c r="D50" s="43">
         <v>45823</v>
       </c>
-      <c r="E50" s="43">
+      <c r="E50" s="44">
         <v>0.166666666666667</v>
       </c>
-      <c r="F50" s="43">
+      <c r="F50" s="44">
         <v>0.208333333333333</v>
       </c>
       <c r="G50" s="18">
@@ -3689,10 +3690,10 @@
       <c r="C51" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D51" s="42">
+      <c r="D51" s="43">
         <v>45824</v>
       </c>
-      <c r="E51" s="43">
+      <c r="E51" s="44">
         <v>0.0833333333333333</v>
       </c>
       <c r="F51" s="18"/>
@@ -3710,13 +3711,13 @@
       <c r="C52" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D52" s="40">
+      <c r="D52" s="41">
         <v>45835</v>
       </c>
-      <c r="E52" s="41">
+      <c r="E52" s="42">
         <v>0.8125</v>
       </c>
-      <c r="F52" s="41">
+      <c r="F52" s="42">
         <v>0.854166666666667</v>
       </c>
       <c r="G52" s="6">
@@ -3733,13 +3734,13 @@
       <c r="C53" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D53" s="40">
+      <c r="D53" s="41">
         <v>45835</v>
       </c>
-      <c r="E53" s="41">
+      <c r="E53" s="42">
         <v>0.958333333333333</v>
       </c>
-      <c r="F53" s="41">
+      <c r="F53" s="42">
         <v>0</v>
       </c>
       <c r="G53" s="6">
@@ -3756,13 +3757,13 @@
       <c r="C54" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D54" s="40">
+      <c r="D54" s="41">
         <v>45836</v>
       </c>
-      <c r="E54" s="41">
+      <c r="E54" s="42">
         <v>0.770833333333333</v>
       </c>
-      <c r="F54" s="41">
+      <c r="F54" s="42">
         <v>0.8125</v>
       </c>
       <c r="G54" s="6">
@@ -3779,13 +3780,13 @@
       <c r="C55" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D55" s="40">
+      <c r="D55" s="41">
         <v>45836</v>
       </c>
-      <c r="E55" s="41">
+      <c r="E55" s="42">
         <v>0.916666666666667</v>
       </c>
-      <c r="F55" s="41">
+      <c r="F55" s="42">
         <v>0.958333333333333</v>
       </c>
       <c r="G55" s="6">
@@ -3802,10 +3803,10 @@
       <c r="C56" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D56" s="40">
+      <c r="D56" s="41">
         <v>45837</v>
       </c>
-      <c r="E56" s="41">
+      <c r="E56" s="42">
         <v>0.875</v>
       </c>
       <c r="F56" s="6"/>
@@ -3823,13 +3824,13 @@
       <c r="C57" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D57" s="42">
+      <c r="D57" s="43">
         <v>45842</v>
       </c>
-      <c r="E57" s="43">
+      <c r="E57" s="44">
         <v>0.8125</v>
       </c>
-      <c r="F57" s="43">
+      <c r="F57" s="44">
         <v>0.854166666666667</v>
       </c>
       <c r="G57" s="18">
@@ -3846,13 +3847,13 @@
       <c r="C58" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="D58" s="42">
+      <c r="D58" s="43">
         <v>45842</v>
       </c>
-      <c r="E58" s="43">
+      <c r="E58" s="44">
         <v>0.958333333333333</v>
       </c>
-      <c r="F58" s="43">
+      <c r="F58" s="44">
         <v>0</v>
       </c>
       <c r="G58" s="18">
@@ -3869,13 +3870,13 @@
       <c r="C59" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="D59" s="42">
+      <c r="D59" s="43">
         <v>45843</v>
       </c>
-      <c r="E59" s="43">
+      <c r="E59" s="44">
         <v>0.770833333333333</v>
       </c>
-      <c r="F59" s="43">
+      <c r="F59" s="44">
         <v>0.8125</v>
       </c>
       <c r="G59" s="18">
@@ -3892,13 +3893,13 @@
       <c r="C60" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D60" s="42">
+      <c r="D60" s="43">
         <v>45843</v>
       </c>
-      <c r="E60" s="43">
+      <c r="E60" s="44">
         <v>0.916666666666667</v>
       </c>
-      <c r="F60" s="43">
+      <c r="F60" s="44">
         <v>0.958333333333333</v>
       </c>
       <c r="G60" s="18">
@@ -3915,10 +3916,10 @@
       <c r="C61" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D61" s="42">
+      <c r="D61" s="43">
         <v>45844</v>
       </c>
-      <c r="E61" s="43">
+      <c r="E61" s="44">
         <v>0.916666666666667</v>
       </c>
       <c r="F61" s="18"/>
@@ -3936,13 +3937,13 @@
       <c r="C62" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D62" s="40">
+      <c r="D62" s="41">
         <v>45863</v>
       </c>
-      <c r="E62" s="41">
+      <c r="E62" s="42">
         <v>0.8125</v>
       </c>
-      <c r="F62" s="41">
+      <c r="F62" s="42">
         <v>0.854166666666667</v>
       </c>
       <c r="G62" s="6">
@@ -3959,13 +3960,13 @@
       <c r="C63" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="D63" s="40">
+      <c r="D63" s="41">
         <v>45863</v>
       </c>
-      <c r="E63" s="41">
+      <c r="E63" s="42">
         <v>0.9375</v>
       </c>
-      <c r="F63" s="41">
+      <c r="F63" s="42">
         <v>0.968055555555556</v>
       </c>
       <c r="G63" s="6">
@@ -3982,13 +3983,13 @@
       <c r="C64" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D64" s="40">
+      <c r="D64" s="41">
         <v>45864</v>
       </c>
-      <c r="E64" s="41">
+      <c r="E64" s="42">
         <v>0.75</v>
       </c>
-      <c r="F64" s="41">
+      <c r="F64" s="42">
         <v>0.791666666666667</v>
       </c>
       <c r="G64" s="6">
@@ -4005,13 +4006,13 @@
       <c r="C65" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D65" s="40">
+      <c r="D65" s="41">
         <v>45864</v>
       </c>
-      <c r="E65" s="41">
+      <c r="E65" s="42">
         <v>0.916666666666667</v>
       </c>
-      <c r="F65" s="41">
+      <c r="F65" s="42">
         <v>0.958333333333333</v>
       </c>
       <c r="G65" s="6">
@@ -4028,10 +4029,10 @@
       <c r="C66" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D66" s="40">
+      <c r="D66" s="41">
         <v>45865</v>
       </c>
-      <c r="E66" s="41">
+      <c r="E66" s="42">
         <v>0.875</v>
       </c>
       <c r="F66" s="6"/>
@@ -4049,13 +4050,13 @@
       <c r="C67" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D67" s="42">
+      <c r="D67" s="43">
         <v>45870</v>
       </c>
-      <c r="E67" s="43">
+      <c r="E67" s="44">
         <v>0.8125</v>
       </c>
-      <c r="F67" s="43">
+      <c r="F67" s="44">
         <v>0.854166666666667</v>
       </c>
       <c r="G67" s="18">
@@ -4072,13 +4073,13 @@
       <c r="C68" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="D68" s="42">
+      <c r="D68" s="43">
         <v>45870</v>
       </c>
-      <c r="E68" s="43">
+      <c r="E68" s="44">
         <v>0.958333333333333</v>
       </c>
-      <c r="F68" s="43">
+      <c r="F68" s="44">
         <v>0</v>
       </c>
       <c r="G68" s="18">
@@ -4095,13 +4096,13 @@
       <c r="C69" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="D69" s="42">
+      <c r="D69" s="43">
         <v>45871</v>
       </c>
-      <c r="E69" s="43">
+      <c r="E69" s="44">
         <v>0.770833333333333</v>
       </c>
-      <c r="F69" s="43">
+      <c r="F69" s="44">
         <v>0.8125</v>
       </c>
       <c r="G69" s="18">
@@ -4118,13 +4119,13 @@
       <c r="C70" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D70" s="42">
+      <c r="D70" s="43">
         <v>45871</v>
       </c>
-      <c r="E70" s="43">
+      <c r="E70" s="44">
         <v>0.916666666666667</v>
       </c>
-      <c r="F70" s="43">
+      <c r="F70" s="44">
         <v>0.958333333333333</v>
       </c>
       <c r="G70" s="18">
@@ -4141,10 +4142,10 @@
       <c r="C71" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D71" s="42">
+      <c r="D71" s="43">
         <v>45872</v>
       </c>
-      <c r="E71" s="43">
+      <c r="E71" s="44">
         <v>0.875</v>
       </c>
       <c r="F71" s="18"/>
@@ -4162,13 +4163,13 @@
       <c r="C72" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D72" s="40">
+      <c r="D72" s="41">
         <v>45898</v>
       </c>
-      <c r="E72" s="41">
+      <c r="E72" s="42">
         <v>0.770833333333333</v>
       </c>
-      <c r="F72" s="41">
+      <c r="F72" s="42">
         <v>0.8125</v>
       </c>
       <c r="G72" s="6">
@@ -4185,13 +4186,13 @@
       <c r="C73" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D73" s="40">
+      <c r="D73" s="41">
         <v>45898</v>
       </c>
-      <c r="E73" s="41">
+      <c r="E73" s="42">
         <v>0.916666666666667</v>
       </c>
-      <c r="F73" s="41">
+      <c r="F73" s="42">
         <v>0.958333333333333</v>
       </c>
       <c r="G73" s="6">
@@ -4208,13 +4209,13 @@
       <c r="C74" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D74" s="40">
+      <c r="D74" s="41">
         <v>45899</v>
       </c>
-      <c r="E74" s="41">
+      <c r="E74" s="42">
         <v>0.729166666666667</v>
       </c>
-      <c r="F74" s="41">
+      <c r="F74" s="42">
         <v>0.770833333333333</v>
       </c>
       <c r="G74" s="6">
@@ -4231,13 +4232,13 @@
       <c r="C75" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D75" s="40">
+      <c r="D75" s="41">
         <v>45899</v>
       </c>
-      <c r="E75" s="41">
+      <c r="E75" s="42">
         <v>0.875</v>
       </c>
-      <c r="F75" s="41">
+      <c r="F75" s="42">
         <v>0.916666666666667</v>
       </c>
       <c r="G75" s="6">
@@ -4254,13 +4255,13 @@
       <c r="C76" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D76" s="40">
+      <c r="D76" s="41">
         <v>45900</v>
       </c>
-      <c r="E76" s="41">
+      <c r="E76" s="42">
         <v>0.875</v>
       </c>
-      <c r="F76" s="41"/>
+      <c r="F76" s="42"/>
       <c r="G76" s="6">
         <v>1</v>
       </c>
@@ -4275,13 +4276,13 @@
       <c r="C77" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D77" s="42">
+      <c r="D77" s="43">
         <v>45905</v>
       </c>
-      <c r="E77" s="43">
+      <c r="E77" s="44">
         <v>0.8125</v>
       </c>
-      <c r="F77" s="43">
+      <c r="F77" s="44">
         <v>0.854166666666667</v>
       </c>
       <c r="G77" s="18">
@@ -4298,13 +4299,13 @@
       <c r="C78" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="D78" s="42">
+      <c r="D78" s="43">
         <v>45905</v>
       </c>
-      <c r="E78" s="43">
+      <c r="E78" s="44">
         <v>0.958333333333333</v>
       </c>
-      <c r="F78" s="43">
+      <c r="F78" s="44">
         <v>0</v>
       </c>
       <c r="G78" s="18">
@@ -4321,13 +4322,13 @@
       <c r="C79" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="D79" s="42">
+      <c r="D79" s="43">
         <v>45906</v>
       </c>
-      <c r="E79" s="43">
+      <c r="E79" s="44">
         <v>0.770833333333333</v>
       </c>
-      <c r="F79" s="43">
+      <c r="F79" s="44">
         <v>0.8125</v>
       </c>
       <c r="G79" s="18">
@@ -4344,13 +4345,13 @@
       <c r="C80" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D80" s="42">
+      <c r="D80" s="43">
         <v>45906</v>
       </c>
-      <c r="E80" s="43">
+      <c r="E80" s="44">
         <v>0.916666666666667</v>
       </c>
-      <c r="F80" s="43">
+      <c r="F80" s="44">
         <v>0.958333333333333</v>
       </c>
       <c r="G80" s="18">
@@ -4367,10 +4368,10 @@
       <c r="C81" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D81" s="42">
+      <c r="D81" s="43">
         <v>45907</v>
       </c>
-      <c r="E81" s="43">
+      <c r="E81" s="44">
         <v>0.875</v>
       </c>
       <c r="F81" s="18"/>
@@ -4388,13 +4389,13 @@
       <c r="C82" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D82" s="40">
+      <c r="D82" s="41">
         <v>45919</v>
       </c>
-      <c r="E82" s="41">
+      <c r="E82" s="42">
         <v>0.6875</v>
       </c>
-      <c r="F82" s="41">
+      <c r="F82" s="42">
         <v>0.729166666666667</v>
       </c>
       <c r="G82" s="6">
@@ -4411,13 +4412,13 @@
       <c r="C83" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D83" s="40">
+      <c r="D83" s="41">
         <v>45919</v>
       </c>
-      <c r="E83" s="41">
+      <c r="E83" s="42">
         <v>0.833333333333333</v>
       </c>
-      <c r="F83" s="41">
+      <c r="F83" s="42">
         <v>0.875</v>
       </c>
       <c r="G83" s="6">
@@ -4434,13 +4435,13 @@
       <c r="C84" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D84" s="40">
+      <c r="D84" s="41">
         <v>45920</v>
       </c>
-      <c r="E84" s="41">
+      <c r="E84" s="42">
         <v>0.6875</v>
       </c>
-      <c r="F84" s="41">
+      <c r="F84" s="42">
         <v>0.729166666666667</v>
       </c>
       <c r="G84" s="6">
@@ -4457,13 +4458,13 @@
       <c r="C85" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D85" s="40">
+      <c r="D85" s="41">
         <v>45920</v>
       </c>
-      <c r="E85" s="41">
+      <c r="E85" s="42">
         <v>0.833333333333333</v>
       </c>
-      <c r="F85" s="41">
+      <c r="F85" s="42">
         <v>0.875</v>
       </c>
       <c r="G85" s="6">
@@ -4480,10 +4481,10 @@
       <c r="C86" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D86" s="40">
+      <c r="D86" s="41">
         <v>45921</v>
       </c>
-      <c r="E86" s="41">
+      <c r="E86" s="42">
         <v>0.791666666666667</v>
       </c>
       <c r="F86" s="6"/>
@@ -4501,13 +4502,13 @@
       <c r="C87" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D87" s="42">
+      <c r="D87" s="43">
         <v>45933</v>
       </c>
-      <c r="E87" s="43">
+      <c r="E87" s="44">
         <v>0.729166666666667</v>
       </c>
-      <c r="F87" s="43">
+      <c r="F87" s="44">
         <v>0.770833333333333</v>
       </c>
       <c r="G87" s="18">
@@ -4524,13 +4525,13 @@
       <c r="C88" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="D88" s="42">
+      <c r="D88" s="43">
         <v>45933</v>
       </c>
-      <c r="E88" s="43">
+      <c r="E88" s="44">
         <v>0.875</v>
       </c>
-      <c r="F88" s="43">
+      <c r="F88" s="44">
         <v>0.916666666666667</v>
       </c>
       <c r="G88" s="18">
@@ -4547,13 +4548,13 @@
       <c r="C89" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="D89" s="42">
+      <c r="D89" s="43">
         <v>45934</v>
       </c>
-      <c r="E89" s="43">
+      <c r="E89" s="44">
         <v>0.729166666666667</v>
       </c>
-      <c r="F89" s="43">
+      <c r="F89" s="44">
         <v>0.770833333333333</v>
       </c>
       <c r="G89" s="18">
@@ -4570,13 +4571,13 @@
       <c r="C90" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D90" s="42">
+      <c r="D90" s="43">
         <v>45934</v>
       </c>
-      <c r="E90" s="43">
+      <c r="E90" s="44">
         <v>0.875</v>
       </c>
-      <c r="F90" s="43">
+      <c r="F90" s="44">
         <v>0.916666666666667</v>
       </c>
       <c r="G90" s="18">
@@ -4593,10 +4594,10 @@
       <c r="C91" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D91" s="42">
+      <c r="D91" s="43">
         <v>45935</v>
       </c>
-      <c r="E91" s="43">
+      <c r="E91" s="44">
         <v>0.833333333333333</v>
       </c>
       <c r="F91" s="18"/>
@@ -4614,13 +4615,13 @@
       <c r="C92" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D92" s="40">
+      <c r="D92" s="41">
         <v>45948</v>
       </c>
-      <c r="E92" s="41">
+      <c r="E92" s="42">
         <v>0.0625</v>
       </c>
-      <c r="F92" s="41">
+      <c r="F92" s="42">
         <v>0.104166666666667</v>
       </c>
       <c r="G92" s="6">
@@ -4637,13 +4638,13 @@
       <c r="C93" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="D93" s="40">
+      <c r="D93" s="41">
         <v>45948</v>
       </c>
-      <c r="E93" s="41">
+      <c r="E93" s="42">
         <v>0.229166666666667</v>
       </c>
-      <c r="F93" s="41">
+      <c r="F93" s="42">
         <v>0.259722222222222</v>
       </c>
       <c r="G93" s="6">
@@ -4660,13 +4661,13 @@
       <c r="C94" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D94" s="40">
+      <c r="D94" s="41">
         <v>45949</v>
       </c>
-      <c r="E94" s="41">
+      <c r="E94" s="42">
         <v>0.0416666666666667</v>
       </c>
-      <c r="F94" s="41">
+      <c r="F94" s="42">
         <v>0.0625</v>
       </c>
       <c r="G94" s="6">
@@ -4683,13 +4684,13 @@
       <c r="C95" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D95" s="40">
+      <c r="D95" s="41">
         <v>45949</v>
       </c>
-      <c r="E95" s="41">
+      <c r="E95" s="42">
         <v>0.208333333333333</v>
       </c>
-      <c r="F95" s="41">
+      <c r="F95" s="42">
         <v>0.25</v>
       </c>
       <c r="G95" s="6">
@@ -4706,10 +4707,10 @@
       <c r="C96" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D96" s="40">
+      <c r="D96" s="41">
         <v>45950</v>
       </c>
-      <c r="E96" s="41">
+      <c r="E96" s="42">
         <v>0.125</v>
       </c>
       <c r="F96" s="6"/>
@@ -4727,13 +4728,13 @@
       <c r="C97" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D97" s="42">
+      <c r="D97" s="43">
         <v>45955</v>
       </c>
-      <c r="E97" s="43">
+      <c r="E97" s="44">
         <v>0.104166666666667</v>
       </c>
-      <c r="F97" s="43">
+      <c r="F97" s="44">
         <v>0.145833333333333</v>
       </c>
       <c r="G97" s="18">
@@ -4750,13 +4751,13 @@
       <c r="C98" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="D98" s="42">
+      <c r="D98" s="43">
         <v>45955</v>
       </c>
-      <c r="E98" s="43">
+      <c r="E98" s="44">
         <v>0.25</v>
       </c>
-      <c r="F98" s="43">
+      <c r="F98" s="44">
         <v>0.291666666666667</v>
       </c>
       <c r="G98" s="18">
@@ -4773,13 +4774,13 @@
       <c r="C99" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="D99" s="42">
+      <c r="D99" s="43">
         <v>45956</v>
       </c>
-      <c r="E99" s="43">
+      <c r="E99" s="44">
         <v>0.0625</v>
       </c>
-      <c r="F99" s="43">
+      <c r="F99" s="44">
         <v>0.104166666666667</v>
       </c>
       <c r="G99" s="18">
@@ -4796,13 +4797,13 @@
       <c r="C100" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D100" s="42">
+      <c r="D100" s="43">
         <v>45956</v>
       </c>
-      <c r="E100" s="43">
+      <c r="E100" s="44">
         <v>0.208333333333333</v>
       </c>
-      <c r="F100" s="43">
+      <c r="F100" s="44">
         <v>0.25</v>
       </c>
       <c r="G100" s="18">
@@ -4819,10 +4820,10 @@
       <c r="C101" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D101" s="42">
+      <c r="D101" s="43">
         <v>45957</v>
       </c>
-      <c r="E101" s="43">
+      <c r="E101" s="44">
         <v>0.166666666666667</v>
       </c>
       <c r="F101" s="18"/>
@@ -4840,13 +4841,13 @@
       <c r="C102" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D102" s="40">
+      <c r="D102" s="41">
         <v>45968</v>
       </c>
-      <c r="E102" s="41">
+      <c r="E102" s="42">
         <v>0.9375</v>
       </c>
-      <c r="F102" s="41">
+      <c r="F102" s="42">
         <v>0.979166666666667</v>
       </c>
       <c r="G102" s="6">
@@ -4863,13 +4864,13 @@
       <c r="C103" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="D103" s="40">
+      <c r="D103" s="41">
         <v>45969</v>
       </c>
-      <c r="E103" s="41">
+      <c r="E103" s="42">
         <v>0.104166666666667</v>
       </c>
-      <c r="F103" s="41">
+      <c r="F103" s="42">
         <v>0.134722222222222</v>
       </c>
       <c r="G103" s="6">
@@ -4886,13 +4887,13 @@
       <c r="C104" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D104" s="40">
+      <c r="D104" s="41">
         <v>45969</v>
       </c>
-      <c r="E104" s="41">
+      <c r="E104" s="42">
         <v>0.916666666666667</v>
       </c>
-      <c r="F104" s="41">
+      <c r="F104" s="42">
         <v>0.958333333333333</v>
       </c>
       <c r="G104" s="6">
@@ -4909,13 +4910,13 @@
       <c r="C105" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D105" s="40">
+      <c r="D105" s="41">
         <v>45970</v>
       </c>
-      <c r="E105" s="41">
+      <c r="E105" s="42">
         <v>0.0833333333333333</v>
       </c>
-      <c r="F105" s="41">
+      <c r="F105" s="42">
         <v>0.125</v>
       </c>
       <c r="G105" s="6">
@@ -4932,10 +4933,10 @@
       <c r="C106" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D106" s="40">
+      <c r="D106" s="41">
         <v>45971</v>
       </c>
-      <c r="E106" s="41">
+      <c r="E106" s="42">
         <v>0.0416666666666667</v>
       </c>
       <c r="F106" s="6"/>
@@ -4953,13 +4954,13 @@
       <c r="C107" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D107" s="42">
+      <c r="D107" s="43">
         <v>45982</v>
       </c>
-      <c r="E107" s="43">
+      <c r="E107" s="44">
         <v>0.354166666666667</v>
       </c>
-      <c r="F107" s="43">
+      <c r="F107" s="44">
         <v>0.395833333333333</v>
       </c>
       <c r="G107" s="18">
@@ -4976,13 +4977,13 @@
       <c r="C108" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="D108" s="42">
+      <c r="D108" s="43">
         <v>45982</v>
       </c>
-      <c r="E108" s="43">
+      <c r="E108" s="44">
         <v>0.5</v>
       </c>
-      <c r="F108" s="43">
+      <c r="F108" s="44">
         <v>0.541666666666667</v>
       </c>
       <c r="G108" s="18">
@@ -4999,13 +5000,13 @@
       <c r="C109" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="D109" s="42">
+      <c r="D109" s="43">
         <v>45983</v>
       </c>
-      <c r="E109" s="44">
+      <c r="E109" s="45">
         <v>0.354166666666667</v>
       </c>
-      <c r="F109" s="44">
+      <c r="F109" s="45">
         <v>0.395833333333333</v>
       </c>
       <c r="G109" s="18">
@@ -5022,13 +5023,13 @@
       <c r="C110" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D110" s="42">
+      <c r="D110" s="43">
         <v>45983</v>
       </c>
-      <c r="E110" s="44">
+      <c r="E110" s="45">
         <v>0.5</v>
       </c>
-      <c r="F110" s="44">
+      <c r="F110" s="45">
         <v>0.541666666666667</v>
       </c>
       <c r="G110" s="18">
@@ -5045,10 +5046,10 @@
       <c r="C111" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D111" s="42">
+      <c r="D111" s="43">
         <v>45984</v>
       </c>
-      <c r="E111" s="44">
+      <c r="E111" s="45">
         <v>0.5</v>
       </c>
       <c r="F111" s="18"/>
@@ -5066,13 +5067,13 @@
       <c r="C112" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D112" s="40">
+      <c r="D112" s="41">
         <v>45989</v>
       </c>
-      <c r="E112" s="45">
+      <c r="E112" s="46">
         <v>0.895833333333333</v>
       </c>
-      <c r="F112" s="45">
+      <c r="F112" s="46">
         <v>0.9375</v>
       </c>
       <c r="G112" s="6">
@@ -5089,13 +5090,13 @@
       <c r="C113" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="D113" s="40">
+      <c r="D113" s="41">
         <v>45990</v>
       </c>
-      <c r="E113" s="45">
+      <c r="E113" s="46">
         <v>0.0625</v>
       </c>
-      <c r="F113" s="45">
+      <c r="F113" s="46">
         <v>0.0930555555555556</v>
       </c>
       <c r="G113" s="6">
@@ -5112,13 +5113,13 @@
       <c r="C114" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D114" s="40">
+      <c r="D114" s="41">
         <v>45990</v>
       </c>
-      <c r="E114" s="45">
+      <c r="E114" s="46">
         <v>0.916666666666667</v>
       </c>
-      <c r="F114" s="45">
+      <c r="F114" s="46">
         <v>0.958333333333333</v>
       </c>
       <c r="G114" s="6">
@@ -5135,13 +5136,13 @@
       <c r="C115" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D115" s="40">
+      <c r="D115" s="41">
         <v>45991</v>
       </c>
-      <c r="E115" s="45">
+      <c r="E115" s="46">
         <v>0.0833333333333333</v>
       </c>
-      <c r="F115" s="45">
+      <c r="F115" s="46">
         <v>0.125</v>
       </c>
       <c r="G115" s="6">
@@ -5158,10 +5159,10 @@
       <c r="C116" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D116" s="40">
+      <c r="D116" s="41">
         <v>45992</v>
       </c>
-      <c r="E116" s="45">
+      <c r="E116" s="46">
         <v>0</v>
       </c>
       <c r="F116" s="6"/>
@@ -5179,13 +5180,13 @@
       <c r="C117" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D117" s="42">
+      <c r="D117" s="43">
         <v>45996</v>
       </c>
-      <c r="E117" s="44">
+      <c r="E117" s="45">
         <v>0.729166666666667</v>
       </c>
-      <c r="F117" s="44">
+      <c r="F117" s="45">
         <v>0.770833333333333</v>
       </c>
       <c r="G117" s="18">
@@ -5202,13 +5203,13 @@
       <c r="C118" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="D118" s="42">
+      <c r="D118" s="43">
         <v>45996</v>
       </c>
-      <c r="E118" s="44">
+      <c r="E118" s="45">
         <v>0.875</v>
       </c>
-      <c r="F118" s="44">
+      <c r="F118" s="45">
         <v>0.916666666666667</v>
       </c>
       <c r="G118" s="18">
@@ -5225,13 +5226,13 @@
       <c r="C119" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="D119" s="42">
+      <c r="D119" s="43">
         <v>45997</v>
       </c>
-      <c r="E119" s="44">
+      <c r="E119" s="45">
         <v>0.770833333333333</v>
       </c>
-      <c r="F119" s="44">
+      <c r="F119" s="45">
         <v>0.8125</v>
       </c>
       <c r="G119" s="18">
@@ -5248,13 +5249,13 @@
       <c r="C120" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D120" s="42">
+      <c r="D120" s="43">
         <v>45997</v>
       </c>
-      <c r="E120" s="44">
+      <c r="E120" s="45">
         <v>0.916666666666667</v>
       </c>
-      <c r="F120" s="44">
+      <c r="F120" s="45">
         <v>0.958333333333333</v>
       </c>
       <c r="G120" s="18">
@@ -5271,10 +5272,10 @@
       <c r="C121" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D121" s="42">
+      <c r="D121" s="43">
         <v>45998</v>
       </c>
-      <c r="E121" s="44">
+      <c r="E121" s="45">
         <v>0.875</v>
       </c>
       <c r="F121" s="18"/>
@@ -5292,13 +5293,13 @@
       <c r="C122" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D122" s="40">
+      <c r="D122" s="41">
         <v>46087</v>
       </c>
-      <c r="E122" s="41">
+      <c r="E122" s="42">
         <v>0.395833333333333</v>
       </c>
-      <c r="F122" s="41">
+      <c r="F122" s="42">
         <v>0.4375</v>
       </c>
       <c r="G122" s="6">
@@ -5315,13 +5316,13 @@
       <c r="C123" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D123" s="40">
+      <c r="D123" s="41">
         <v>46087</v>
       </c>
-      <c r="E123" s="41">
+      <c r="E123" s="42">
         <v>0.541666666666667</v>
       </c>
-      <c r="F123" s="41">
+      <c r="F123" s="42">
         <v>0.583333333333333</v>
       </c>
       <c r="G123" s="6">
@@ -5338,13 +5339,13 @@
       <c r="C124" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D124" s="40">
+      <c r="D124" s="41">
         <v>46088</v>
       </c>
-      <c r="E124" s="41">
+      <c r="E124" s="42">
         <v>0.395833333333333</v>
       </c>
-      <c r="F124" s="41">
+      <c r="F124" s="42">
         <v>0.4375</v>
       </c>
       <c r="G124" s="6">
@@ -5361,13 +5362,13 @@
       <c r="C125" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D125" s="40">
+      <c r="D125" s="41">
         <v>46088</v>
       </c>
-      <c r="E125" s="41">
+      <c r="E125" s="42">
         <v>0.541666666666667</v>
       </c>
-      <c r="F125" s="41">
+      <c r="F125" s="42">
         <v>0.583333333333333</v>
       </c>
       <c r="G125" s="6">
@@ -5384,13 +5385,13 @@
       <c r="C126" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D126" s="40">
+      <c r="D126" s="41">
         <v>46089</v>
       </c>
-      <c r="E126" s="41">
+      <c r="E126" s="42">
         <v>0.5</v>
       </c>
-      <c r="F126" s="41"/>
+      <c r="F126" s="42"/>
       <c r="G126" s="6">
         <v>1</v>
       </c>
@@ -5405,13 +5406,13 @@
       <c r="C127" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D127" s="42">
+      <c r="D127" s="43">
         <v>46094</v>
       </c>
-      <c r="E127" s="43">
+      <c r="E127" s="44">
         <v>0.479166666666667</v>
       </c>
-      <c r="F127" s="43">
+      <c r="F127" s="44">
         <v>0.520833333333333</v>
       </c>
       <c r="G127" s="18">
@@ -5428,13 +5429,13 @@
       <c r="C128" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="D128" s="42">
+      <c r="D128" s="43">
         <v>46094</v>
       </c>
-      <c r="E128" s="43">
+      <c r="E128" s="44">
         <v>0.645833333333333</v>
       </c>
-      <c r="F128" s="43">
+      <c r="F128" s="44">
         <v>0.676388888888889</v>
       </c>
       <c r="G128" s="18">
@@ -5451,13 +5452,13 @@
       <c r="C129" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="D129" s="42">
+      <c r="D129" s="43">
         <v>46095</v>
       </c>
-      <c r="E129" s="43">
+      <c r="E129" s="44">
         <v>0.458333333333333</v>
       </c>
-      <c r="F129" s="43">
+      <c r="F129" s="44">
         <v>0.5</v>
       </c>
       <c r="G129" s="18">
@@ -5474,13 +5475,13 @@
       <c r="C130" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D130" s="42">
+      <c r="D130" s="43">
         <v>46095</v>
       </c>
-      <c r="E130" s="43">
+      <c r="E130" s="44">
         <v>0.625</v>
       </c>
-      <c r="F130" s="43">
+      <c r="F130" s="44">
         <v>0.666666666666667</v>
       </c>
       <c r="G130" s="18">
@@ -5497,10 +5498,10 @@
       <c r="C131" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D131" s="42">
+      <c r="D131" s="43">
         <v>46096</v>
       </c>
-      <c r="E131" s="43">
+      <c r="E131" s="44">
         <v>0.625</v>
       </c>
       <c r="F131" s="18"/>
@@ -5518,13 +5519,13 @@
       <c r="C132" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D132" s="40">
+      <c r="D132" s="41">
         <v>46108</v>
       </c>
-      <c r="E132" s="41">
+      <c r="E132" s="42">
         <v>0.4375</v>
       </c>
-      <c r="F132" s="41">
+      <c r="F132" s="42">
         <v>0.479166666666667</v>
       </c>
       <c r="G132" s="6">
@@ -5541,13 +5542,13 @@
       <c r="C133" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D133" s="40">
+      <c r="D133" s="41">
         <v>46108</v>
       </c>
-      <c r="E133" s="41">
+      <c r="E133" s="42">
         <v>0.583333333333333</v>
       </c>
-      <c r="F133" s="41">
+      <c r="F133" s="42">
         <v>0.625</v>
       </c>
       <c r="G133" s="6">
@@ -5564,13 +5565,13 @@
       <c r="C134" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D134" s="40">
+      <c r="D134" s="41">
         <v>46109</v>
       </c>
-      <c r="E134" s="41">
+      <c r="E134" s="42">
         <v>0.4375</v>
       </c>
-      <c r="F134" s="41">
+      <c r="F134" s="42">
         <v>0.479166666666667</v>
       </c>
       <c r="G134" s="6">
@@ -5587,13 +5588,13 @@
       <c r="C135" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D135" s="40">
+      <c r="D135" s="41">
         <v>46109</v>
       </c>
-      <c r="E135" s="41">
+      <c r="E135" s="42">
         <v>0.583333333333333</v>
       </c>
-      <c r="F135" s="41">
+      <c r="F135" s="42">
         <v>0.625</v>
       </c>
       <c r="G135" s="6">
@@ -5610,10 +5611,10 @@
       <c r="C136" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D136" s="40">
+      <c r="D136" s="41">
         <v>46110</v>
       </c>
-      <c r="E136" s="41">
+      <c r="E136" s="42">
         <v>0.541666666666667</v>
       </c>
       <c r="F136" s="6"/>
@@ -5631,13 +5632,13 @@
       <c r="C137" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D137" s="42">
+      <c r="D137" s="43">
         <v>46122</v>
       </c>
-      <c r="E137" s="43">
+      <c r="E137" s="44">
         <v>0.8125</v>
       </c>
-      <c r="F137" s="43">
+      <c r="F137" s="44">
         <v>0.854166666666667</v>
       </c>
       <c r="G137" s="18">
@@ -5654,13 +5655,13 @@
       <c r="C138" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="D138" s="42">
+      <c r="D138" s="43">
         <v>46122</v>
       </c>
-      <c r="E138" s="43">
+      <c r="E138" s="44">
         <v>0.958333333333333</v>
       </c>
-      <c r="F138" s="43">
+      <c r="F138" s="44">
         <v>0</v>
       </c>
       <c r="G138" s="18">
@@ -5677,13 +5678,13 @@
       <c r="C139" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="D139" s="42">
+      <c r="D139" s="43">
         <v>46123</v>
       </c>
-      <c r="E139" s="43">
+      <c r="E139" s="44">
         <v>0.854166666666667</v>
       </c>
-      <c r="F139" s="43">
+      <c r="F139" s="44">
         <v>0.895833333333333</v>
       </c>
       <c r="G139" s="18">
@@ -5700,13 +5701,13 @@
       <c r="C140" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D140" s="42">
+      <c r="D140" s="43">
         <v>46123</v>
       </c>
-      <c r="E140" s="43">
-        <v>0</v>
-      </c>
-      <c r="F140" s="43">
+      <c r="E140" s="44">
+        <v>0</v>
+      </c>
+      <c r="F140" s="44">
         <v>0.0416666666666667</v>
       </c>
       <c r="G140" s="18">
@@ -5723,10 +5724,10 @@
       <c r="C141" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D141" s="42">
+      <c r="D141" s="43">
         <v>46124</v>
       </c>
-      <c r="E141" s="43">
+      <c r="E141" s="44">
         <v>0.958333333333333</v>
       </c>
       <c r="F141" s="18"/>
@@ -5744,13 +5745,13 @@
       <c r="C142" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D142" s="40">
+      <c r="D142" s="41">
         <v>46129</v>
       </c>
-      <c r="E142" s="41">
+      <c r="E142" s="42">
         <v>0.895833333333333</v>
       </c>
-      <c r="F142" s="41">
+      <c r="F142" s="42">
         <v>0.9375</v>
       </c>
       <c r="G142" s="6">
@@ -5767,13 +5768,13 @@
       <c r="C143" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D143" s="40">
+      <c r="D143" s="41">
         <v>46130</v>
       </c>
-      <c r="E143" s="41">
+      <c r="E143" s="42">
         <v>0.0416666666666667</v>
       </c>
-      <c r="F143" s="41">
+      <c r="F143" s="42">
         <v>0.0833333333333333</v>
       </c>
       <c r="G143" s="6">
@@ -5790,13 +5791,13 @@
       <c r="C144" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D144" s="40">
+      <c r="D144" s="41">
         <v>46130</v>
       </c>
-      <c r="E144" s="41">
+      <c r="E144" s="42">
         <v>0.895833333333333</v>
       </c>
-      <c r="F144" s="41">
+      <c r="F144" s="42">
         <v>0.9375</v>
       </c>
       <c r="G144" s="6">
@@ -5813,13 +5814,13 @@
       <c r="C145" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D145" s="40">
+      <c r="D145" s="41">
         <v>46131</v>
       </c>
-      <c r="E145" s="41">
+      <c r="E145" s="42">
         <v>0.0416666666666667</v>
       </c>
-      <c r="F145" s="41">
+      <c r="F145" s="42">
         <v>0.0833333333333333</v>
       </c>
       <c r="G145" s="6">
@@ -5836,10 +5837,10 @@
       <c r="C146" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D146" s="40">
+      <c r="D146" s="41">
         <v>46132</v>
       </c>
-      <c r="E146" s="41">
+      <c r="E146" s="42">
         <v>0.0416666666666667</v>
       </c>
       <c r="F146" s="6"/>
@@ -5857,13 +5858,13 @@
       <c r="C147" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D147" s="42">
+      <c r="D147" s="43">
         <v>46144</v>
       </c>
-      <c r="E147" s="43">
+      <c r="E147" s="44">
         <v>0.0208333333333333</v>
       </c>
-      <c r="F147" s="43">
+      <c r="F147" s="44">
         <v>0.0625</v>
       </c>
       <c r="G147" s="18">
@@ -5880,13 +5881,13 @@
       <c r="C148" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="D148" s="42">
+      <c r="D148" s="43">
         <v>46144</v>
       </c>
-      <c r="E148" s="43">
+      <c r="E148" s="44">
         <v>0.1875</v>
       </c>
-      <c r="F148" s="43">
+      <c r="F148" s="44">
         <v>0.218055555555556</v>
       </c>
       <c r="G148" s="18">
@@ -5903,13 +5904,13 @@
       <c r="C149" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="D149" s="42">
+      <c r="D149" s="43">
         <v>46145</v>
       </c>
-      <c r="E149" s="43">
-        <v>0</v>
-      </c>
-      <c r="F149" s="43">
+      <c r="E149" s="44">
+        <v>0</v>
+      </c>
+      <c r="F149" s="44">
         <v>0.0416666666666667</v>
       </c>
       <c r="G149" s="18">
@@ -5926,13 +5927,13 @@
       <c r="C150" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D150" s="42">
+      <c r="D150" s="43">
         <v>46145</v>
       </c>
-      <c r="E150" s="43">
+      <c r="E150" s="44">
         <v>0.166666666666667</v>
       </c>
-      <c r="F150" s="43">
+      <c r="F150" s="44">
         <v>0.208333333333333</v>
       </c>
       <c r="G150" s="18">
@@ -5949,13 +5950,13 @@
       <c r="C151" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D151" s="42">
+      <c r="D151" s="43">
         <v>46146</v>
       </c>
-      <c r="E151" s="43">
+      <c r="E151" s="44">
         <v>0.166666666666667</v>
       </c>
-      <c r="F151" s="43"/>
+      <c r="F151" s="44"/>
       <c r="G151" s="18">
         <v>1</v>
       </c>
@@ -5970,13 +5971,13 @@
       <c r="C152" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D152" s="40">
+      <c r="D152" s="41">
         <v>46165</v>
       </c>
-      <c r="E152" s="41">
+      <c r="E152" s="42">
         <v>0.0208333333333333</v>
       </c>
-      <c r="F152" s="41">
+      <c r="F152" s="42">
         <v>0.0625</v>
       </c>
       <c r="G152" s="6">
@@ -5993,13 +5994,13 @@
       <c r="C153" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="D153" s="40">
+      <c r="D153" s="41">
         <v>46165</v>
       </c>
-      <c r="E153" s="41">
+      <c r="E153" s="42">
         <v>0.1875</v>
       </c>
-      <c r="F153" s="41">
+      <c r="F153" s="42">
         <v>0.218055555555556</v>
       </c>
       <c r="G153" s="6">
@@ -6016,13 +6017,13 @@
       <c r="C154" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D154" s="40">
+      <c r="D154" s="41">
         <v>46166</v>
       </c>
-      <c r="E154" s="41">
-        <v>0</v>
-      </c>
-      <c r="F154" s="41">
+      <c r="E154" s="42">
+        <v>0</v>
+      </c>
+      <c r="F154" s="42">
         <v>0.0416666666666667</v>
       </c>
       <c r="G154" s="6">
@@ -6039,13 +6040,13 @@
       <c r="C155" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D155" s="40">
+      <c r="D155" s="41">
         <v>46166</v>
       </c>
-      <c r="E155" s="41">
+      <c r="E155" s="42">
         <v>0.166666666666667</v>
       </c>
-      <c r="F155" s="41">
+      <c r="F155" s="42">
         <v>0.208333333333333</v>
       </c>
       <c r="G155" s="6">
@@ -6062,10 +6063,10 @@
       <c r="C156" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D156" s="40">
+      <c r="D156" s="41">
         <v>46167</v>
       </c>
-      <c r="E156" s="41">
+      <c r="E156" s="42">
         <v>0.166666666666667</v>
       </c>
       <c r="F156" s="6"/>
@@ -6083,13 +6084,13 @@
       <c r="C157" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D157" s="42">
+      <c r="D157" s="43">
         <v>46178</v>
       </c>
-      <c r="E157" s="43">
+      <c r="E157" s="44">
         <v>0.8125</v>
       </c>
-      <c r="F157" s="43">
+      <c r="F157" s="44">
         <v>0.854166666666667</v>
       </c>
       <c r="G157" s="18">
@@ -6106,13 +6107,13 @@
       <c r="C158" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="D158" s="42">
+      <c r="D158" s="43">
         <v>46178</v>
       </c>
-      <c r="E158" s="43">
+      <c r="E158" s="44">
         <v>0.958333333333333</v>
       </c>
-      <c r="F158" s="43">
+      <c r="F158" s="44">
         <v>0</v>
       </c>
       <c r="G158" s="18">
@@ -6129,13 +6130,13 @@
       <c r="C159" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="D159" s="42">
+      <c r="D159" s="43">
         <v>46179</v>
       </c>
-      <c r="E159" s="43">
+      <c r="E159" s="44">
         <v>0.770833333333333</v>
       </c>
-      <c r="F159" s="43">
+      <c r="F159" s="44">
         <v>0.8125</v>
       </c>
       <c r="G159" s="18">
@@ -6152,13 +6153,13 @@
       <c r="C160" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D160" s="42">
+      <c r="D160" s="43">
         <v>46179</v>
       </c>
-      <c r="E160" s="43">
+      <c r="E160" s="44">
         <v>0.916666666666667</v>
       </c>
-      <c r="F160" s="43">
+      <c r="F160" s="44">
         <v>0.958333333333333</v>
       </c>
       <c r="G160" s="18">
@@ -6175,10 +6176,10 @@
       <c r="C161" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D161" s="42">
+      <c r="D161" s="43">
         <v>46180</v>
       </c>
-      <c r="E161" s="43">
+      <c r="E161" s="44">
         <v>0.875</v>
       </c>
       <c r="F161" s="18"/>
@@ -6196,13 +6197,13 @@
       <c r="C162" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D162" s="40">
+      <c r="D162" s="41">
         <v>46185</v>
       </c>
-      <c r="E162" s="41">
+      <c r="E162" s="42">
         <v>0.8125</v>
       </c>
-      <c r="F162" s="41">
+      <c r="F162" s="42">
         <v>0.854166666666667</v>
       </c>
       <c r="G162" s="6">
@@ -6219,13 +6220,13 @@
       <c r="C163" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D163" s="40">
+      <c r="D163" s="41">
         <v>46185</v>
       </c>
-      <c r="E163" s="41">
+      <c r="E163" s="42">
         <v>0.958333333333333</v>
       </c>
-      <c r="F163" s="41">
+      <c r="F163" s="42">
         <v>0</v>
       </c>
       <c r="G163" s="6">
@@ -6242,13 +6243,13 @@
       <c r="C164" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D164" s="40">
+      <c r="D164" s="41">
         <v>46186</v>
       </c>
-      <c r="E164" s="41">
+      <c r="E164" s="42">
         <v>0.770833333333333</v>
       </c>
-      <c r="F164" s="41">
+      <c r="F164" s="42">
         <v>0.8125</v>
       </c>
       <c r="G164" s="6">
@@ -6265,13 +6266,13 @@
       <c r="C165" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D165" s="40">
+      <c r="D165" s="41">
         <v>46186</v>
       </c>
-      <c r="E165" s="41">
+      <c r="E165" s="42">
         <v>0.916666666666667</v>
       </c>
-      <c r="F165" s="41">
+      <c r="F165" s="42">
         <v>0.958333333333333</v>
       </c>
       <c r="G165" s="6">
@@ -6288,10 +6289,10 @@
       <c r="C166" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D166" s="40">
+      <c r="D166" s="41">
         <v>46187</v>
       </c>
-      <c r="E166" s="41">
+      <c r="E166" s="42">
         <v>0.875</v>
       </c>
       <c r="F166" s="6"/>
@@ -6309,13 +6310,13 @@
       <c r="C167" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D167" s="42">
+      <c r="D167" s="43">
         <v>46199</v>
       </c>
-      <c r="E167" s="43">
+      <c r="E167" s="44">
         <v>0.8125</v>
       </c>
-      <c r="F167" s="43">
+      <c r="F167" s="44">
         <v>0.854166666666667</v>
       </c>
       <c r="G167" s="18">
@@ -6332,13 +6333,13 @@
       <c r="C168" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="D168" s="42">
+      <c r="D168" s="43">
         <v>46199</v>
       </c>
-      <c r="E168" s="43">
+      <c r="E168" s="44">
         <v>0.958333333333333</v>
       </c>
-      <c r="F168" s="43">
+      <c r="F168" s="44">
         <v>0</v>
       </c>
       <c r="G168" s="18">
@@ -6355,13 +6356,13 @@
       <c r="C169" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="D169" s="42">
+      <c r="D169" s="43">
         <v>46200</v>
       </c>
-      <c r="E169" s="43">
+      <c r="E169" s="44">
         <v>0.770833333333333</v>
       </c>
-      <c r="F169" s="43">
+      <c r="F169" s="44">
         <v>0.8125</v>
       </c>
       <c r="G169" s="18">
@@ -6378,13 +6379,13 @@
       <c r="C170" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D170" s="42">
+      <c r="D170" s="43">
         <v>46200</v>
       </c>
-      <c r="E170" s="43">
+      <c r="E170" s="44">
         <v>0.916666666666667</v>
       </c>
-      <c r="F170" s="43">
+      <c r="F170" s="44">
         <v>0.958333333333333</v>
       </c>
       <c r="G170" s="18">
@@ -6401,10 +6402,10 @@
       <c r="C171" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D171" s="42">
+      <c r="D171" s="43">
         <v>46201</v>
       </c>
-      <c r="E171" s="43">
+      <c r="E171" s="44">
         <v>0.875</v>
       </c>
       <c r="F171" s="18"/>
@@ -6422,13 +6423,13 @@
       <c r="C172" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D172" s="40">
+      <c r="D172" s="41">
         <v>46206</v>
       </c>
-      <c r="E172" s="41">
+      <c r="E172" s="42">
         <v>0.8125</v>
       </c>
-      <c r="F172" s="41">
+      <c r="F172" s="42">
         <v>0.854166666666667</v>
       </c>
       <c r="G172" s="6">
@@ -6445,13 +6446,13 @@
       <c r="C173" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="D173" s="40">
+      <c r="D173" s="41">
         <v>46206</v>
       </c>
-      <c r="E173" s="41">
+      <c r="E173" s="42">
         <v>0.979166666666667</v>
       </c>
-      <c r="F173" s="41">
+      <c r="F173" s="42">
         <v>0.00972222222222222</v>
       </c>
       <c r="G173" s="6">
@@ -6468,13 +6469,13 @@
       <c r="C174" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D174" s="40">
+      <c r="D174" s="41">
         <v>46207</v>
       </c>
-      <c r="E174" s="41">
+      <c r="E174" s="42">
         <v>0.791666666666667</v>
       </c>
-      <c r="F174" s="41">
+      <c r="F174" s="42">
         <v>0.833333333333333</v>
       </c>
       <c r="G174" s="6">
@@ -6491,13 +6492,13 @@
       <c r="C175" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D175" s="40">
+      <c r="D175" s="41">
         <v>46207</v>
       </c>
-      <c r="E175" s="41">
+      <c r="E175" s="42">
         <v>0.958333333333333</v>
       </c>
-      <c r="F175" s="41">
+      <c r="F175" s="42">
         <v>0</v>
       </c>
       <c r="G175" s="6">
@@ -6514,10 +6515,10 @@
       <c r="C176" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D176" s="40">
+      <c r="D176" s="41">
         <v>46208</v>
       </c>
-      <c r="E176" s="41">
+      <c r="E176" s="42">
         <v>0.916666666666667</v>
       </c>
       <c r="F176" s="6"/>
@@ -6535,13 +6536,13 @@
       <c r="C177" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D177" s="42">
+      <c r="D177" s="43">
         <v>46220</v>
       </c>
-      <c r="E177" s="43">
+      <c r="E177" s="44">
         <v>0.8125</v>
       </c>
-      <c r="F177" s="43">
+      <c r="F177" s="44">
         <v>0.854166666666667</v>
       </c>
       <c r="G177" s="18">
@@ -6558,13 +6559,13 @@
       <c r="C178" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="D178" s="42">
+      <c r="D178" s="43">
         <v>46220</v>
       </c>
-      <c r="E178" s="43">
+      <c r="E178" s="44">
         <v>0.958333333333333</v>
       </c>
-      <c r="F178" s="43">
+      <c r="F178" s="44">
         <v>0</v>
       </c>
       <c r="G178" s="18">
@@ -6581,13 +6582,13 @@
       <c r="C179" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="D179" s="42">
+      <c r="D179" s="43">
         <v>46221</v>
       </c>
-      <c r="E179" s="43">
+      <c r="E179" s="44">
         <v>0.770833333333333</v>
       </c>
-      <c r="F179" s="43">
+      <c r="F179" s="44">
         <v>0.8125</v>
       </c>
       <c r="G179" s="18">
@@ -6604,13 +6605,13 @@
       <c r="C180" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D180" s="42">
+      <c r="D180" s="43">
         <v>46221</v>
       </c>
-      <c r="E180" s="43">
+      <c r="E180" s="44">
         <v>0.916666666666667</v>
       </c>
-      <c r="F180" s="43">
+      <c r="F180" s="44">
         <v>0.958333333333333</v>
       </c>
       <c r="G180" s="18">
@@ -6627,10 +6628,10 @@
       <c r="C181" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D181" s="42">
+      <c r="D181" s="43">
         <v>46222</v>
       </c>
-      <c r="E181" s="43">
+      <c r="E181" s="44">
         <v>0.875</v>
       </c>
       <c r="F181" s="18"/>
@@ -6648,13 +6649,13 @@
       <c r="C182" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D182" s="40">
+      <c r="D182" s="41">
         <v>46227</v>
       </c>
-      <c r="E182" s="41">
+      <c r="E182" s="42">
         <v>0.8125</v>
       </c>
-      <c r="F182" s="41">
+      <c r="F182" s="42">
         <v>0.854166666666667</v>
       </c>
       <c r="G182" s="6">
@@ -6671,13 +6672,13 @@
       <c r="C183" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D183" s="40">
+      <c r="D183" s="41">
         <v>46227</v>
       </c>
-      <c r="E183" s="41">
+      <c r="E183" s="42">
         <v>0.9375</v>
       </c>
-      <c r="F183" s="41">
+      <c r="F183" s="42">
         <v>0.968055555555556</v>
       </c>
       <c r="G183" s="6">
@@ -6694,13 +6695,13 @@
       <c r="C184" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D184" s="40">
+      <c r="D184" s="41">
         <v>46228</v>
       </c>
-      <c r="E184" s="41">
+      <c r="E184" s="42">
         <v>0.75</v>
       </c>
-      <c r="F184" s="41">
+      <c r="F184" s="42">
         <v>0.791666666666667</v>
       </c>
       <c r="G184" s="6">
@@ -6717,13 +6718,13 @@
       <c r="C185" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D185" s="40">
+      <c r="D185" s="41">
         <v>46228</v>
       </c>
-      <c r="E185" s="41">
+      <c r="E185" s="42">
         <v>0.916666666666667</v>
       </c>
-      <c r="F185" s="41">
+      <c r="F185" s="42">
         <v>0.958333333333333</v>
       </c>
       <c r="G185" s="6">
@@ -6740,10 +6741,10 @@
       <c r="C186" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D186" s="40">
+      <c r="D186" s="41">
         <v>46229</v>
       </c>
-      <c r="E186" s="41">
+      <c r="E186" s="42">
         <v>0.875</v>
       </c>
       <c r="F186" s="6"/>
@@ -6761,13 +6762,13 @@
       <c r="C187" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D187" s="42">
+      <c r="D187" s="43">
         <v>46255</v>
       </c>
-      <c r="E187" s="43">
+      <c r="E187" s="44">
         <v>0.770833333333333</v>
       </c>
-      <c r="F187" s="43">
+      <c r="F187" s="44">
         <v>0.8125</v>
       </c>
       <c r="G187" s="18">
@@ -6784,13 +6785,13 @@
       <c r="C188" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="D188" s="42">
+      <c r="D188" s="43">
         <v>46255</v>
       </c>
-      <c r="E188" s="43">
+      <c r="E188" s="44">
         <v>0.9375</v>
       </c>
-      <c r="F188" s="43">
+      <c r="F188" s="44">
         <v>0.979166666666667</v>
       </c>
       <c r="G188" s="18">
@@ -6807,13 +6808,13 @@
       <c r="C189" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="D189" s="42">
+      <c r="D189" s="43">
         <v>46256</v>
       </c>
-      <c r="E189" s="43">
+      <c r="E189" s="44">
         <v>0.75</v>
       </c>
-      <c r="F189" s="43">
+      <c r="F189" s="44">
         <v>0.791666666666667</v>
       </c>
       <c r="G189" s="18">
@@ -6830,13 +6831,13 @@
       <c r="C190" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D190" s="42">
+      <c r="D190" s="43">
         <v>46256</v>
       </c>
-      <c r="E190" s="43">
+      <c r="E190" s="44">
         <v>0.916666666666667</v>
       </c>
-      <c r="F190" s="43">
+      <c r="F190" s="44">
         <v>0.958333333333333</v>
       </c>
       <c r="G190" s="18">
@@ -6853,10 +6854,10 @@
       <c r="C191" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D191" s="42">
+      <c r="D191" s="43">
         <v>46257</v>
       </c>
-      <c r="E191" s="43">
+      <c r="E191" s="44">
         <v>0.875</v>
       </c>
       <c r="F191" s="18"/>
@@ -6874,13 +6875,13 @@
       <c r="C192" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D192" s="40">
+      <c r="D192" s="41">
         <v>46269</v>
       </c>
-      <c r="E192" s="41">
+      <c r="E192" s="42">
         <v>0.770833333333333</v>
       </c>
-      <c r="F192" s="41">
+      <c r="F192" s="42">
         <v>0.8125</v>
       </c>
       <c r="G192" s="6">
@@ -6897,13 +6898,13 @@
       <c r="C193" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D193" s="40">
+      <c r="D193" s="41">
         <v>46269</v>
       </c>
-      <c r="E193" s="41">
+      <c r="E193" s="42">
         <v>0.916666666666667</v>
       </c>
-      <c r="F193" s="41">
+      <c r="F193" s="42">
         <v>0.958333333333333</v>
       </c>
       <c r="G193" s="6">
@@ -6920,13 +6921,13 @@
       <c r="C194" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D194" s="40">
+      <c r="D194" s="41">
         <v>46270</v>
       </c>
-      <c r="E194" s="41">
+      <c r="E194" s="42">
         <v>0.770833333333333</v>
       </c>
-      <c r="F194" s="41">
+      <c r="F194" s="42">
         <v>0.8125</v>
       </c>
       <c r="G194" s="6">
@@ -6943,13 +6944,13 @@
       <c r="C195" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D195" s="40">
+      <c r="D195" s="41">
         <v>46270</v>
       </c>
-      <c r="E195" s="41">
+      <c r="E195" s="42">
         <v>0.916666666666667</v>
       </c>
-      <c r="F195" s="41">
+      <c r="F195" s="42">
         <v>0.958333333333333</v>
       </c>
       <c r="G195" s="6">
@@ -6966,13 +6967,13 @@
       <c r="C196" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D196" s="40">
+      <c r="D196" s="41">
         <v>46271</v>
       </c>
-      <c r="E196" s="41">
+      <c r="E196" s="42">
         <v>0.875</v>
       </c>
-      <c r="F196" s="41"/>
+      <c r="F196" s="42"/>
       <c r="G196" s="6">
         <v>1</v>
       </c>
@@ -6987,13 +6988,13 @@
       <c r="C197" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D197" s="42">
+      <c r="D197" s="43">
         <v>46276</v>
       </c>
-      <c r="E197" s="43">
+      <c r="E197" s="44">
         <v>0.8125</v>
       </c>
-      <c r="F197" s="43">
+      <c r="F197" s="44">
         <v>0.854166666666667</v>
       </c>
       <c r="G197" s="18">
@@ -7010,13 +7011,13 @@
       <c r="C198" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="D198" s="42">
+      <c r="D198" s="43">
         <v>46276</v>
       </c>
-      <c r="E198" s="43">
+      <c r="E198" s="44">
         <v>0.958333333333333</v>
       </c>
-      <c r="F198" s="43">
+      <c r="F198" s="44">
         <v>0</v>
       </c>
       <c r="G198" s="18">
@@ -7033,13 +7034,13 @@
       <c r="C199" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="D199" s="42">
+      <c r="D199" s="43">
         <v>46277</v>
       </c>
-      <c r="E199" s="43">
+      <c r="E199" s="44">
         <v>0.770833333333333</v>
       </c>
-      <c r="F199" s="43">
+      <c r="F199" s="44">
         <v>0.8125</v>
       </c>
       <c r="G199" s="18">
@@ -7056,13 +7057,13 @@
       <c r="C200" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D200" s="42">
+      <c r="D200" s="43">
         <v>46277</v>
       </c>
-      <c r="E200" s="43">
+      <c r="E200" s="44">
         <v>0.916666666666667</v>
       </c>
-      <c r="F200" s="43">
+      <c r="F200" s="44">
         <v>0.958333333333333</v>
       </c>
       <c r="G200" s="18">
@@ -7079,10 +7080,10 @@
       <c r="C201" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D201" s="42">
+      <c r="D201" s="43">
         <v>46278</v>
       </c>
-      <c r="E201" s="43">
+      <c r="E201" s="44">
         <v>0.875</v>
       </c>
       <c r="F201" s="18"/>
@@ -7100,13 +7101,13 @@
       <c r="C202" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D202" s="40">
+      <c r="D202" s="41">
         <v>46289</v>
       </c>
-      <c r="E202" s="41">
+      <c r="E202" s="42">
         <v>0.6875</v>
       </c>
-      <c r="F202" s="41">
+      <c r="F202" s="42">
         <v>0.729166666666667</v>
       </c>
       <c r="G202" s="6">
@@ -7123,13 +7124,13 @@
       <c r="C203" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D203" s="40">
+      <c r="D203" s="41">
         <v>46289</v>
       </c>
-      <c r="E203" s="41">
+      <c r="E203" s="42">
         <v>0.833333333333333</v>
       </c>
-      <c r="F203" s="41">
+      <c r="F203" s="42">
         <v>0.875</v>
       </c>
       <c r="G203" s="6">
@@ -7146,13 +7147,13 @@
       <c r="C204" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D204" s="40">
+      <c r="D204" s="41">
         <v>46290</v>
       </c>
-      <c r="E204" s="41">
+      <c r="E204" s="42">
         <v>0.6875</v>
       </c>
-      <c r="F204" s="41">
+      <c r="F204" s="42">
         <v>0.729166666666667</v>
       </c>
       <c r="G204" s="6">
@@ -7169,13 +7170,13 @@
       <c r="C205" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D205" s="40">
+      <c r="D205" s="41">
         <v>46290</v>
       </c>
-      <c r="E205" s="41">
+      <c r="E205" s="42">
         <v>0.833333333333333</v>
       </c>
-      <c r="F205" s="41">
+      <c r="F205" s="42">
         <v>0.875</v>
       </c>
       <c r="G205" s="6">
@@ -7192,10 +7193,10 @@
       <c r="C206" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D206" s="40">
+      <c r="D206" s="41">
         <v>46291</v>
       </c>
-      <c r="E206" s="41">
+      <c r="E206" s="42">
         <v>0.791666666666667</v>
       </c>
       <c r="F206" s="6"/>
@@ -7213,13 +7214,13 @@
       <c r="C207" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D207" s="42">
+      <c r="D207" s="43">
         <v>46304</v>
       </c>
-      <c r="E207" s="43">
+      <c r="E207" s="44">
         <v>0.6875</v>
       </c>
-      <c r="F207" s="43">
+      <c r="F207" s="44">
         <v>0.729166666666667</v>
       </c>
       <c r="G207" s="18">
@@ -7236,13 +7237,13 @@
       <c r="C208" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="D208" s="42">
+      <c r="D208" s="43">
         <v>46304</v>
       </c>
-      <c r="E208" s="43">
+      <c r="E208" s="44">
         <v>0.854166666666667</v>
       </c>
-      <c r="F208" s="43">
+      <c r="F208" s="44">
         <v>0.884722222222222</v>
       </c>
       <c r="G208" s="18">
@@ -7259,13 +7260,13 @@
       <c r="C209" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="D209" s="42">
+      <c r="D209" s="43">
         <v>46305</v>
       </c>
-      <c r="E209" s="43">
+      <c r="E209" s="44">
         <v>0.708333333333333</v>
       </c>
-      <c r="F209" s="43">
+      <c r="F209" s="44">
         <v>0.75</v>
       </c>
       <c r="G209" s="18">
@@ -7282,13 +7283,13 @@
       <c r="C210" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D210" s="42">
+      <c r="D210" s="43">
         <v>46305</v>
       </c>
-      <c r="E210" s="43">
+      <c r="E210" s="44">
         <v>0.875</v>
       </c>
-      <c r="F210" s="43">
+      <c r="F210" s="44">
         <v>0.916666666666667</v>
       </c>
       <c r="G210" s="18">
@@ -7305,10 +7306,10 @@
       <c r="C211" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D211" s="42">
+      <c r="D211" s="43">
         <v>46306</v>
       </c>
-      <c r="E211" s="43">
+      <c r="E211" s="44">
         <v>0.833333333333333</v>
       </c>
       <c r="F211" s="18"/>
@@ -7326,13 +7327,13 @@
       <c r="C212" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D212" s="40">
+      <c r="D212" s="41">
         <v>46319</v>
       </c>
-      <c r="E212" s="41">
+      <c r="E212" s="42">
         <v>0.0625</v>
       </c>
-      <c r="F212" s="41">
+      <c r="F212" s="42">
         <v>0.104166666666667</v>
       </c>
       <c r="G212" s="6">
@@ -7349,13 +7350,13 @@
       <c r="C213" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D213" s="40">
+      <c r="D213" s="41">
         <v>46319</v>
       </c>
-      <c r="E213" s="41">
+      <c r="E213" s="42">
         <v>0.208333333333333</v>
       </c>
-      <c r="F213" s="41">
+      <c r="F213" s="42">
         <v>0.25</v>
       </c>
       <c r="G213" s="6">
@@ -7372,13 +7373,13 @@
       <c r="C214" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D214" s="40">
+      <c r="D214" s="41">
         <v>46320</v>
       </c>
-      <c r="E214" s="41">
+      <c r="E214" s="42">
         <v>0.0625</v>
       </c>
-      <c r="F214" s="41">
+      <c r="F214" s="42">
         <v>0.104166666666667</v>
       </c>
       <c r="G214" s="6">
@@ -7395,13 +7396,13 @@
       <c r="C215" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D215" s="40">
+      <c r="D215" s="41">
         <v>46320</v>
       </c>
-      <c r="E215" s="41">
+      <c r="E215" s="42">
         <v>0.208333333333333</v>
       </c>
-      <c r="F215" s="41">
+      <c r="F215" s="42">
         <v>0.25</v>
       </c>
       <c r="G215" s="6">
@@ -7418,10 +7419,10 @@
       <c r="C216" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D216" s="40">
+      <c r="D216" s="41">
         <v>46321</v>
       </c>
-      <c r="E216" s="41">
+      <c r="E216" s="42">
         <v>0.166666666666667</v>
       </c>
       <c r="F216" s="6"/>
@@ -7439,13 +7440,13 @@
       <c r="C217" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D217" s="42">
+      <c r="D217" s="43">
         <v>46326</v>
       </c>
-      <c r="E217" s="43">
+      <c r="E217" s="44">
         <v>0.104166666666667</v>
       </c>
-      <c r="F217" s="43">
+      <c r="F217" s="44">
         <v>0.145833333333333</v>
       </c>
       <c r="G217" s="18">
@@ -7462,13 +7463,13 @@
       <c r="C218" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="D218" s="42">
+      <c r="D218" s="43">
         <v>46326</v>
       </c>
-      <c r="E218" s="43">
+      <c r="E218" s="44">
         <v>0.25</v>
       </c>
-      <c r="F218" s="43">
+      <c r="F218" s="44">
         <v>0.291666666666667</v>
       </c>
       <c r="G218" s="18">
@@ -7485,13 +7486,13 @@
       <c r="C219" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="D219" s="42">
+      <c r="D219" s="43">
         <v>46327</v>
       </c>
-      <c r="E219" s="43">
+      <c r="E219" s="44">
         <v>0.0625</v>
       </c>
-      <c r="F219" s="43">
+      <c r="F219" s="44">
         <v>0.104166666666667</v>
       </c>
       <c r="G219" s="18">
@@ -7508,13 +7509,13 @@
       <c r="C220" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D220" s="42">
+      <c r="D220" s="43">
         <v>46327</v>
       </c>
-      <c r="E220" s="43">
+      <c r="E220" s="44">
         <v>0.208333333333333</v>
       </c>
-      <c r="F220" s="43">
+      <c r="F220" s="44">
         <v>0.25</v>
       </c>
       <c r="G220" s="18">
@@ -7531,10 +7532,10 @@
       <c r="C221" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D221" s="42">
+      <c r="D221" s="43">
         <v>46328</v>
       </c>
-      <c r="E221" s="43">
+      <c r="E221" s="44">
         <v>0.166666666666667</v>
       </c>
       <c r="F221" s="18"/>
@@ -7552,13 +7553,13 @@
       <c r="C222" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D222" s="40">
+      <c r="D222" s="41">
         <v>46332</v>
       </c>
-      <c r="E222" s="41">
+      <c r="E222" s="42">
         <v>0.979166666666667</v>
       </c>
-      <c r="F222" s="41">
+      <c r="F222" s="42">
         <v>0.0208333333333333</v>
       </c>
       <c r="G222" s="6">
@@ -7575,13 +7576,13 @@
       <c r="C223" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D223" s="40">
+      <c r="D223" s="41">
         <v>46333</v>
       </c>
-      <c r="E223" s="41">
+      <c r="E223" s="42">
         <v>0.125</v>
       </c>
-      <c r="F223" s="41">
+      <c r="F223" s="42">
         <v>0.166666666666667</v>
       </c>
       <c r="G223" s="6">
@@ -7598,13 +7599,13 @@
       <c r="C224" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D224" s="40">
+      <c r="D224" s="41">
         <v>46333</v>
       </c>
-      <c r="E224" s="41">
+      <c r="E224" s="42">
         <v>0.9375</v>
       </c>
-      <c r="F224" s="41">
+      <c r="F224" s="42">
         <v>0.979166666666667</v>
       </c>
       <c r="G224" s="6">
@@ -7621,13 +7622,13 @@
       <c r="C225" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D225" s="40">
+      <c r="D225" s="41">
         <v>46334</v>
       </c>
-      <c r="E225" s="41">
+      <c r="E225" s="42">
         <v>0.0833333333333333</v>
       </c>
-      <c r="F225" s="41">
+      <c r="F225" s="42">
         <v>0.125</v>
       </c>
       <c r="G225" s="6">
@@ -7644,10 +7645,10 @@
       <c r="C226" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D226" s="40">
+      <c r="D226" s="41">
         <v>46335</v>
       </c>
-      <c r="E226" s="41">
+      <c r="E226" s="42">
         <v>0.0416666666666667</v>
       </c>
       <c r="F226" s="6"/>
@@ -7665,13 +7666,13 @@
       <c r="C227" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D227" s="42">
+      <c r="D227" s="43">
         <v>46346</v>
       </c>
-      <c r="E227" s="43">
+      <c r="E227" s="44">
         <v>0.354166666666667</v>
       </c>
-      <c r="F227" s="43">
+      <c r="F227" s="44">
         <v>0.395833333333333</v>
       </c>
       <c r="G227" s="18">
@@ -7688,13 +7689,13 @@
       <c r="C228" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="D228" s="42">
+      <c r="D228" s="43">
         <v>46346</v>
       </c>
-      <c r="E228" s="43">
+      <c r="E228" s="44">
         <v>0.5</v>
       </c>
-      <c r="F228" s="43">
+      <c r="F228" s="44">
         <v>0.541666666666667</v>
       </c>
       <c r="G228" s="18">
@@ -7711,13 +7712,13 @@
       <c r="C229" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="D229" s="42">
+      <c r="D229" s="43">
         <v>46347</v>
       </c>
-      <c r="E229" s="44">
+      <c r="E229" s="45">
         <v>0.354166666666667</v>
       </c>
-      <c r="F229" s="44">
+      <c r="F229" s="45">
         <v>0.395833333333333</v>
       </c>
       <c r="G229" s="18">
@@ -7734,13 +7735,13 @@
       <c r="C230" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D230" s="42">
+      <c r="D230" s="43">
         <v>46347</v>
       </c>
-      <c r="E230" s="44">
+      <c r="E230" s="45">
         <v>0.5</v>
       </c>
-      <c r="F230" s="44">
+      <c r="F230" s="45">
         <v>0.541666666666667</v>
       </c>
       <c r="G230" s="18">
@@ -7757,10 +7758,10 @@
       <c r="C231" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D231" s="42">
+      <c r="D231" s="43">
         <v>46348</v>
       </c>
-      <c r="E231" s="44">
+      <c r="E231" s="45">
         <v>0.5</v>
       </c>
       <c r="F231" s="18"/>
@@ -7778,13 +7779,13 @@
       <c r="C232" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D232" s="40">
+      <c r="D232" s="41">
         <v>46353</v>
       </c>
-      <c r="E232" s="45">
+      <c r="E232" s="46">
         <v>0.895833333333333</v>
       </c>
-      <c r="F232" s="45">
+      <c r="F232" s="46">
         <v>0.9375</v>
       </c>
       <c r="G232" s="6">
@@ -7801,13 +7802,13 @@
       <c r="C233" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D233" s="40">
+      <c r="D233" s="41">
         <v>46354</v>
       </c>
-      <c r="E233" s="45">
+      <c r="E233" s="46">
         <v>0.0416666666666667</v>
       </c>
-      <c r="F233" s="45">
+      <c r="F233" s="46">
         <v>0.0833333333333333</v>
       </c>
       <c r="G233" s="6">
@@ -7824,13 +7825,13 @@
       <c r="C234" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D234" s="40">
+      <c r="D234" s="41">
         <v>46354</v>
       </c>
-      <c r="E234" s="41">
+      <c r="E234" s="42">
         <v>0.9375</v>
       </c>
-      <c r="F234" s="41">
+      <c r="F234" s="42">
         <v>0.979166666666667</v>
       </c>
       <c r="G234" s="6">
@@ -7847,13 +7848,13 @@
       <c r="C235" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D235" s="40">
+      <c r="D235" s="41">
         <v>46355</v>
       </c>
-      <c r="E235" s="41">
+      <c r="E235" s="42">
         <v>0.0833333333333333</v>
       </c>
-      <c r="F235" s="41">
+      <c r="F235" s="42">
         <v>0.125</v>
       </c>
       <c r="G235" s="6">
@@ -7870,10 +7871,10 @@
       <c r="C236" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D236" s="40">
+      <c r="D236" s="41">
         <v>46356</v>
       </c>
-      <c r="E236" s="41">
+      <c r="E236" s="42">
         <v>0</v>
       </c>
       <c r="F236" s="6"/>
@@ -7891,13 +7892,13 @@
       <c r="C237" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D237" s="42">
+      <c r="D237" s="43">
         <v>46360</v>
       </c>
-      <c r="E237" s="44">
+      <c r="E237" s="45">
         <v>0.729166666666667</v>
       </c>
-      <c r="F237" s="44">
+      <c r="F237" s="45">
         <v>0.770833333333333</v>
       </c>
       <c r="G237" s="18">
@@ -7914,13 +7915,13 @@
       <c r="C238" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="D238" s="42">
+      <c r="D238" s="43">
         <v>46360</v>
       </c>
-      <c r="E238" s="44">
+      <c r="E238" s="45">
         <v>0.875</v>
       </c>
-      <c r="F238" s="44">
+      <c r="F238" s="45">
         <v>0.916666666666667</v>
       </c>
       <c r="G238" s="18">
@@ -7937,13 +7938,13 @@
       <c r="C239" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="D239" s="42">
+      <c r="D239" s="43">
         <v>46361</v>
       </c>
-      <c r="E239" s="44">
+      <c r="E239" s="45">
         <v>0.770833333333333</v>
       </c>
-      <c r="F239" s="44">
+      <c r="F239" s="45">
         <v>0.8125</v>
       </c>
       <c r="G239" s="18">
@@ -7960,13 +7961,13 @@
       <c r="C240" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D240" s="42">
+      <c r="D240" s="43">
         <v>46361</v>
       </c>
-      <c r="E240" s="44">
+      <c r="E240" s="45">
         <v>0.916666666666667</v>
       </c>
-      <c r="F240" s="44">
+      <c r="F240" s="45">
         <v>0.958333333333333</v>
       </c>
       <c r="G240" s="18">
@@ -7983,10 +7984,10 @@
       <c r="C241" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D241" s="42">
+      <c r="D241" s="43">
         <v>46362</v>
       </c>
-      <c r="E241" s="44">
+      <c r="E241" s="45">
         <v>0.875</v>
       </c>
       <c r="F241" s="18"/>
@@ -8003,7 +8004,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R1245"/>
+  <dimension ref="A1:R1333"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="5.57142857142857" customWidth="1"/>
@@ -8018,6 +8019,9 @@
     <col min="10" max="10" width="3.57142857142857" customWidth="1"/>
     <col min="11" max="11" width="15.7857142857143" customWidth="1"/>
     <col min="12" max="12" width="15.1428571428571" customWidth="1"/>
+    <col min="14" max="14" width="3.57142857142857" customWidth="1"/>
+    <col min="15" max="15" width="14.7142857142857" customWidth="1"/>
+    <col min="16" max="16" width="13.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17">
@@ -29996,7 +30000,7 @@
         <v>36</v>
       </c>
       <c r="D820" s="6" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="E820" s="6">
         <v>23</v>
@@ -30020,7 +30024,7 @@
         <v>36</v>
       </c>
       <c r="D821" s="6" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="E821" s="6">
         <v>55</v>
@@ -40577,8 +40581,8 @@
       <c r="C1241" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="D1241" s="6">
-        <v>18</v>
+      <c r="D1241" s="6" t="s">
+        <v>76</v>
       </c>
       <c r="E1241" s="14">
         <v>14</v>
@@ -40603,8 +40607,8 @@
       <c r="C1242" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="D1242" s="6">
-        <v>19</v>
+      <c r="D1242" s="6" t="s">
+        <v>76</v>
       </c>
       <c r="E1242" s="38">
         <v>77</v>
@@ -40629,8 +40633,8 @@
       <c r="C1243" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="D1243" s="6">
-        <v>20</v>
+      <c r="D1243" s="6" t="s">
+        <v>76</v>
       </c>
       <c r="E1243" s="8">
         <v>6</v>
@@ -40655,8 +40659,8 @@
       <c r="C1244" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="D1244" s="6">
-        <v>21</v>
+      <c r="D1244" s="6" t="s">
+        <v>74</v>
       </c>
       <c r="E1244" s="7">
         <v>81</v>
@@ -40681,8 +40685,8 @@
       <c r="C1245" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="D1245" s="6">
-        <v>22</v>
+      <c r="D1245" s="6" t="s">
+        <v>74</v>
       </c>
       <c r="E1245" s="19">
         <v>27</v>
@@ -40694,6 +40698,2206 @@
         <v>90</v>
       </c>
       <c r="H1245" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1246" spans="1:8">
+      <c r="A1246" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1246" s="18">
+        <v>2</v>
+      </c>
+      <c r="C1246" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1246" s="18">
+        <v>1</v>
+      </c>
+      <c r="E1246" s="9">
+        <v>63</v>
+      </c>
+      <c r="F1246" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1246" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1246" s="21"/>
+    </row>
+    <row r="1247" spans="1:8">
+      <c r="A1247" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1247" s="18">
+        <v>2</v>
+      </c>
+      <c r="C1247" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1247" s="18">
+        <v>2</v>
+      </c>
+      <c r="E1247" s="9">
+        <v>12</v>
+      </c>
+      <c r="F1247" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1247" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1247" s="21"/>
+    </row>
+    <row r="1248" spans="1:8">
+      <c r="A1248" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1248" s="18">
+        <v>2</v>
+      </c>
+      <c r="C1248" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1248" s="18">
+        <v>3</v>
+      </c>
+      <c r="E1248" s="7">
+        <v>1</v>
+      </c>
+      <c r="F1248" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G1248" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="H1248" s="21"/>
+    </row>
+    <row r="1249" spans="1:8">
+      <c r="A1249" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1249" s="18">
+        <v>2</v>
+      </c>
+      <c r="C1249" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1249" s="18">
+        <v>4</v>
+      </c>
+      <c r="E1249" s="10">
+        <v>44</v>
+      </c>
+      <c r="F1249" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1249" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1249" s="21"/>
+    </row>
+    <row r="1250" spans="1:8">
+      <c r="A1250" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1250" s="18">
+        <v>2</v>
+      </c>
+      <c r="C1250" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1250" s="18">
+        <v>5</v>
+      </c>
+      <c r="E1250" s="7">
+        <v>81</v>
+      </c>
+      <c r="F1250" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G1250" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="H1250" s="21"/>
+    </row>
+    <row r="1251" spans="1:8">
+      <c r="A1251" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1251" s="18">
+        <v>2</v>
+      </c>
+      <c r="C1251" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1251" s="18">
+        <v>6</v>
+      </c>
+      <c r="E1251" s="10">
+        <v>16</v>
+      </c>
+      <c r="F1251" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G1251" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1251" s="21"/>
+    </row>
+    <row r="1252" spans="1:8">
+      <c r="A1252" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1252" s="18">
+        <v>2</v>
+      </c>
+      <c r="C1252" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1252" s="18">
+        <v>7</v>
+      </c>
+      <c r="E1252" s="13">
+        <v>10</v>
+      </c>
+      <c r="F1252" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1252" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="H1252" s="21"/>
+    </row>
+    <row r="1253" spans="1:8">
+      <c r="A1253" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1253" s="18">
+        <v>2</v>
+      </c>
+      <c r="C1253" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1253" s="18">
+        <v>8</v>
+      </c>
+      <c r="E1253" s="8">
+        <v>3</v>
+      </c>
+      <c r="F1253" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1253" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H1253" s="21"/>
+    </row>
+    <row r="1254" spans="1:8">
+      <c r="A1254" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1254" s="18">
+        <v>2</v>
+      </c>
+      <c r="C1254" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1254" s="18">
+        <v>9</v>
+      </c>
+      <c r="E1254" s="17">
+        <v>87</v>
+      </c>
+      <c r="F1254" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1254" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="H1254" s="21"/>
+    </row>
+    <row r="1255" spans="1:8">
+      <c r="A1255" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1255" s="18">
+        <v>2</v>
+      </c>
+      <c r="C1255" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1255" s="18">
+        <v>10</v>
+      </c>
+      <c r="E1255" s="8">
+        <v>6</v>
+      </c>
+      <c r="F1255" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G1255" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H1255" s="21"/>
+    </row>
+    <row r="1256" spans="1:8">
+      <c r="A1256" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1256" s="18">
+        <v>2</v>
+      </c>
+      <c r="C1256" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1256" s="18">
+        <v>11</v>
+      </c>
+      <c r="E1256" s="19">
+        <v>27</v>
+      </c>
+      <c r="F1256" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G1256" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="H1256" s="21"/>
+    </row>
+    <row r="1257" spans="1:8">
+      <c r="A1257" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1257" s="18">
+        <v>2</v>
+      </c>
+      <c r="C1257" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1257" s="18">
+        <v>12</v>
+      </c>
+      <c r="E1257" s="17">
+        <v>31</v>
+      </c>
+      <c r="F1257" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="G1257" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="H1257" s="21"/>
+    </row>
+    <row r="1258" spans="1:8">
+      <c r="A1258" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1258" s="18">
+        <v>2</v>
+      </c>
+      <c r="C1258" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1258" s="18">
+        <v>13</v>
+      </c>
+      <c r="E1258" s="11">
+        <v>30</v>
+      </c>
+      <c r="F1258" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1258" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="H1258" s="21"/>
+    </row>
+    <row r="1259" spans="1:8">
+      <c r="A1259" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1259" s="18">
+        <v>2</v>
+      </c>
+      <c r="C1259" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1259" s="18">
+        <v>14</v>
+      </c>
+      <c r="E1259" s="19">
+        <v>5</v>
+      </c>
+      <c r="F1259" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1259" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="H1259" s="21"/>
+    </row>
+    <row r="1260" spans="1:8">
+      <c r="A1260" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1260" s="18">
+        <v>2</v>
+      </c>
+      <c r="C1260" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1260" s="18">
+        <v>15</v>
+      </c>
+      <c r="E1260" s="11">
+        <v>41</v>
+      </c>
+      <c r="F1260" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="G1260" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="H1260" s="21"/>
+    </row>
+    <row r="1261" spans="1:8">
+      <c r="A1261" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1261" s="18">
+        <v>2</v>
+      </c>
+      <c r="C1261" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1261" s="18">
+        <v>16</v>
+      </c>
+      <c r="E1261" s="13">
+        <v>43</v>
+      </c>
+      <c r="F1261" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="G1261" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="H1261" s="21"/>
+    </row>
+    <row r="1262" spans="1:8">
+      <c r="A1262" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1262" s="18">
+        <v>2</v>
+      </c>
+      <c r="C1262" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1262" s="18">
+        <v>17</v>
+      </c>
+      <c r="E1262" s="12">
+        <v>55</v>
+      </c>
+      <c r="F1262" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="G1262" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="H1262" s="21"/>
+    </row>
+    <row r="1263" spans="1:8">
+      <c r="A1263" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1263" s="18">
+        <v>2</v>
+      </c>
+      <c r="C1263" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1263" s="18">
+        <v>18</v>
+      </c>
+      <c r="E1263" s="12">
+        <v>23</v>
+      </c>
+      <c r="F1263" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1263" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="H1263" s="21"/>
+    </row>
+    <row r="1264" spans="1:8">
+      <c r="A1264" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1264" s="18">
+        <v>2</v>
+      </c>
+      <c r="C1264" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1264" s="18">
+        <v>19</v>
+      </c>
+      <c r="E1264" s="14">
+        <v>14</v>
+      </c>
+      <c r="F1264" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="G1264" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="H1264" s="21"/>
+    </row>
+    <row r="1265" spans="1:8">
+      <c r="A1265" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1265" s="18">
+        <v>2</v>
+      </c>
+      <c r="C1265" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1265" s="18">
+        <v>20</v>
+      </c>
+      <c r="E1265" s="14">
+        <v>18</v>
+      </c>
+      <c r="F1265" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1265" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="H1265" s="21"/>
+    </row>
+    <row r="1266" spans="1:8">
+      <c r="A1266" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1266" s="18">
+        <v>2</v>
+      </c>
+      <c r="C1266" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1266" s="18">
+        <v>21</v>
+      </c>
+      <c r="E1266" s="20">
+        <v>77</v>
+      </c>
+      <c r="F1266" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1266" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="H1266" s="21"/>
+    </row>
+    <row r="1267" spans="1:8">
+      <c r="A1267" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1267" s="18">
+        <v>2</v>
+      </c>
+      <c r="C1267" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1267" s="18">
+        <v>22</v>
+      </c>
+      <c r="E1267" s="20">
+        <v>11</v>
+      </c>
+      <c r="F1267" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="G1267" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="H1267" s="21"/>
+    </row>
+    <row r="1268" spans="1:8">
+      <c r="A1268" s="21">
+        <v>2026</v>
+      </c>
+      <c r="B1268" s="21">
+        <v>2</v>
+      </c>
+      <c r="C1268" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1268" s="6">
+        <v>1</v>
+      </c>
+      <c r="E1268" s="9">
+        <v>63</v>
+      </c>
+      <c r="F1268" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1268" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1268" s="40">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1269" spans="1:8">
+      <c r="A1269" s="21">
+        <v>2026</v>
+      </c>
+      <c r="B1269" s="21">
+        <v>2</v>
+      </c>
+      <c r="C1269" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1269" s="6">
+        <v>2</v>
+      </c>
+      <c r="E1269" s="10">
+        <v>16</v>
+      </c>
+      <c r="F1269" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G1269" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1269" s="40">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1270" spans="1:8">
+      <c r="A1270" s="21">
+        <v>2026</v>
+      </c>
+      <c r="B1270" s="21">
+        <v>2</v>
+      </c>
+      <c r="C1270" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1270" s="6">
+        <v>3</v>
+      </c>
+      <c r="E1270" s="10">
+        <v>44</v>
+      </c>
+      <c r="F1270" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1270" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1270" s="40">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1271" spans="1:8">
+      <c r="A1271" s="21">
+        <v>2026</v>
+      </c>
+      <c r="B1271" s="21">
+        <v>2</v>
+      </c>
+      <c r="C1271" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1271" s="6">
+        <v>4</v>
+      </c>
+      <c r="E1271" s="7">
+        <v>1</v>
+      </c>
+      <c r="F1271" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G1271" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="H1271" s="40">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1272" spans="1:8">
+      <c r="A1272" s="21">
+        <v>2026</v>
+      </c>
+      <c r="B1272" s="21">
+        <v>2</v>
+      </c>
+      <c r="C1272" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1272" s="6">
+        <v>5</v>
+      </c>
+      <c r="E1272" s="9">
+        <v>12</v>
+      </c>
+      <c r="F1272" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1272" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1272" s="40">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1273" spans="1:8">
+      <c r="A1273" s="21">
+        <v>2026</v>
+      </c>
+      <c r="B1273" s="21">
+        <v>2</v>
+      </c>
+      <c r="C1273" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1273" s="6">
+        <v>6</v>
+      </c>
+      <c r="E1273" s="7">
+        <v>81</v>
+      </c>
+      <c r="F1273" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G1273" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="H1273" s="40">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1274" spans="1:8">
+      <c r="A1274" s="21">
+        <v>2026</v>
+      </c>
+      <c r="B1274" s="21">
+        <v>2</v>
+      </c>
+      <c r="C1274" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1274" s="6">
+        <v>7</v>
+      </c>
+      <c r="E1274" s="11">
+        <v>30</v>
+      </c>
+      <c r="F1274" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1274" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="H1274" s="40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1275" spans="1:8">
+      <c r="A1275" s="21">
+        <v>2026</v>
+      </c>
+      <c r="B1275" s="21">
+        <v>2</v>
+      </c>
+      <c r="C1275" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1275" s="6">
+        <v>8</v>
+      </c>
+      <c r="E1275" s="17">
+        <v>87</v>
+      </c>
+      <c r="F1275" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1275" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="H1275" s="40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1276" spans="1:8">
+      <c r="A1276" s="21">
+        <v>2026</v>
+      </c>
+      <c r="B1276" s="21">
+        <v>2</v>
+      </c>
+      <c r="C1276" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1276" s="6">
+        <v>9</v>
+      </c>
+      <c r="E1276" s="8">
+        <v>3</v>
+      </c>
+      <c r="F1276" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1276" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H1276" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1277" spans="1:8">
+      <c r="A1277" s="21">
+        <v>2026</v>
+      </c>
+      <c r="B1277" s="21">
+        <v>2</v>
+      </c>
+      <c r="C1277" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1277" s="6">
+        <v>10</v>
+      </c>
+      <c r="E1277" s="17">
+        <v>31</v>
+      </c>
+      <c r="F1277" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="G1277" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="H1277" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1278" spans="1:8">
+      <c r="A1278" s="21">
+        <v>2026</v>
+      </c>
+      <c r="B1278" s="21">
+        <v>2</v>
+      </c>
+      <c r="C1278" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1278" s="6">
+        <v>11</v>
+      </c>
+      <c r="E1278" s="13">
+        <v>10</v>
+      </c>
+      <c r="F1278" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1278" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="H1278" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1279" spans="1:8">
+      <c r="A1279" s="21">
+        <v>2026</v>
+      </c>
+      <c r="B1279" s="21">
+        <v>2</v>
+      </c>
+      <c r="C1279" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1279" s="6">
+        <v>12</v>
+      </c>
+      <c r="E1279" s="12">
+        <v>55</v>
+      </c>
+      <c r="F1279" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="G1279" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="H1279" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1280" spans="1:8">
+      <c r="A1280" s="21">
+        <v>2026</v>
+      </c>
+      <c r="B1280" s="21">
+        <v>2</v>
+      </c>
+      <c r="C1280" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1280" s="6">
+        <v>13</v>
+      </c>
+      <c r="E1280" s="19">
+        <v>5</v>
+      </c>
+      <c r="F1280" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1280" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="H1280" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1281" spans="1:8">
+      <c r="A1281" s="21">
+        <v>2026</v>
+      </c>
+      <c r="B1281" s="21">
+        <v>2</v>
+      </c>
+      <c r="C1281" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1281" s="6">
+        <v>14</v>
+      </c>
+      <c r="E1281" s="13">
+        <v>43</v>
+      </c>
+      <c r="F1281" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="G1281" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="H1281" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1282" spans="1:8">
+      <c r="A1282" s="21">
+        <v>2026</v>
+      </c>
+      <c r="B1282" s="21">
+        <v>2</v>
+      </c>
+      <c r="C1282" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1282" s="6">
+        <v>15</v>
+      </c>
+      <c r="E1282" s="8">
+        <v>6</v>
+      </c>
+      <c r="F1282" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G1282" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H1282" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1283" spans="1:8">
+      <c r="A1283" s="21">
+        <v>2026</v>
+      </c>
+      <c r="B1283" s="21">
+        <v>2</v>
+      </c>
+      <c r="C1283" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1283" s="6">
+        <v>16</v>
+      </c>
+      <c r="E1283" s="12">
+        <v>23</v>
+      </c>
+      <c r="F1283" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1283" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="H1283" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1284" spans="1:8">
+      <c r="A1284" s="21">
+        <v>2026</v>
+      </c>
+      <c r="B1284" s="21">
+        <v>2</v>
+      </c>
+      <c r="C1284" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1284" s="6">
+        <v>17</v>
+      </c>
+      <c r="E1284" s="14">
+        <v>14</v>
+      </c>
+      <c r="F1284" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="G1284" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="H1284" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1285" spans="1:8">
+      <c r="A1285" s="21">
+        <v>2026</v>
+      </c>
+      <c r="B1285" s="21">
+        <v>2</v>
+      </c>
+      <c r="C1285" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1285" s="6">
+        <v>18</v>
+      </c>
+      <c r="E1285" s="14">
+        <v>18</v>
+      </c>
+      <c r="F1285" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1285" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="H1285" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1286" spans="1:8">
+      <c r="A1286" s="21">
+        <v>2026</v>
+      </c>
+      <c r="B1286" s="21">
+        <v>2</v>
+      </c>
+      <c r="C1286" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1286" s="6">
+        <v>19</v>
+      </c>
+      <c r="E1286" s="20">
+        <v>11</v>
+      </c>
+      <c r="F1286" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="G1286" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="H1286" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1287" spans="1:8">
+      <c r="A1287" s="21">
+        <v>2026</v>
+      </c>
+      <c r="B1287" s="21">
+        <v>2</v>
+      </c>
+      <c r="C1287" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1287" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1287" s="19">
+        <v>27</v>
+      </c>
+      <c r="F1287" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G1287" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="H1287" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1288" spans="1:8">
+      <c r="A1288" s="21">
+        <v>2026</v>
+      </c>
+      <c r="B1288" s="21">
+        <v>2</v>
+      </c>
+      <c r="C1288" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1288" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1288" s="20">
+        <v>77</v>
+      </c>
+      <c r="F1288" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1288" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="H1288" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1289" spans="1:8">
+      <c r="A1289" s="21">
+        <v>2026</v>
+      </c>
+      <c r="B1289" s="21">
+        <v>2</v>
+      </c>
+      <c r="C1289" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1289" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1289" s="11">
+        <v>41</v>
+      </c>
+      <c r="F1289" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="G1289" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="H1289" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1290" spans="1:8">
+      <c r="A1290" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1290" s="18">
+        <v>2</v>
+      </c>
+      <c r="C1290" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1290" s="18">
+        <v>1</v>
+      </c>
+      <c r="E1290" s="9">
+        <v>12</v>
+      </c>
+      <c r="F1290" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1290" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1290" s="21"/>
+    </row>
+    <row r="1291" spans="1:8">
+      <c r="A1291" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1291" s="18">
+        <v>2</v>
+      </c>
+      <c r="C1291" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1291" s="18">
+        <v>2</v>
+      </c>
+      <c r="E1291" s="9">
+        <v>63</v>
+      </c>
+      <c r="F1291" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1291" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1291" s="21"/>
+    </row>
+    <row r="1292" spans="1:8">
+      <c r="A1292" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1292" s="18">
+        <v>2</v>
+      </c>
+      <c r="C1292" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1292" s="18">
+        <v>3</v>
+      </c>
+      <c r="E1292" s="10">
+        <v>44</v>
+      </c>
+      <c r="F1292" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1292" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1292" s="21"/>
+    </row>
+    <row r="1293" spans="1:8">
+      <c r="A1293" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1293" s="18">
+        <v>2</v>
+      </c>
+      <c r="C1293" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1293" s="18">
+        <v>4</v>
+      </c>
+      <c r="E1293" s="10">
+        <v>16</v>
+      </c>
+      <c r="F1293" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G1293" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1293" s="21"/>
+    </row>
+    <row r="1294" spans="1:8">
+      <c r="A1294" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1294" s="18">
+        <v>2</v>
+      </c>
+      <c r="C1294" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1294" s="18">
+        <v>5</v>
+      </c>
+      <c r="E1294" s="7">
+        <v>81</v>
+      </c>
+      <c r="F1294" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G1294" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="H1294" s="21"/>
+    </row>
+    <row r="1295" spans="1:8">
+      <c r="A1295" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1295" s="18">
+        <v>2</v>
+      </c>
+      <c r="C1295" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1295" s="18">
+        <v>6</v>
+      </c>
+      <c r="E1295" s="7">
+        <v>1</v>
+      </c>
+      <c r="F1295" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G1295" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="H1295" s="21"/>
+    </row>
+    <row r="1296" spans="1:8">
+      <c r="A1296" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1296" s="18">
+        <v>2</v>
+      </c>
+      <c r="C1296" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1296" s="18">
+        <v>7</v>
+      </c>
+      <c r="E1296" s="13">
+        <v>10</v>
+      </c>
+      <c r="F1296" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1296" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="H1296" s="21"/>
+    </row>
+    <row r="1297" spans="1:8">
+      <c r="A1297" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1297" s="18">
+        <v>2</v>
+      </c>
+      <c r="C1297" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1297" s="18">
+        <v>8</v>
+      </c>
+      <c r="E1297" s="8">
+        <v>3</v>
+      </c>
+      <c r="F1297" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1297" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H1297" s="21"/>
+    </row>
+    <row r="1298" spans="1:8">
+      <c r="A1298" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1298" s="18">
+        <v>2</v>
+      </c>
+      <c r="C1298" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1298" s="18">
+        <v>9</v>
+      </c>
+      <c r="E1298" s="8">
+        <v>6</v>
+      </c>
+      <c r="F1298" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G1298" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H1298" s="21"/>
+    </row>
+    <row r="1299" spans="1:8">
+      <c r="A1299" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1299" s="18">
+        <v>2</v>
+      </c>
+      <c r="C1299" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1299" s="18">
+        <v>10</v>
+      </c>
+      <c r="E1299" s="17">
+        <v>87</v>
+      </c>
+      <c r="F1299" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1299" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="H1299" s="21"/>
+    </row>
+    <row r="1300" spans="1:8">
+      <c r="A1300" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1300" s="18">
+        <v>2</v>
+      </c>
+      <c r="C1300" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1300" s="18">
+        <v>11</v>
+      </c>
+      <c r="E1300" s="19">
+        <v>27</v>
+      </c>
+      <c r="F1300" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G1300" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="H1300" s="21"/>
+    </row>
+    <row r="1301" spans="1:8">
+      <c r="A1301" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1301" s="18">
+        <v>2</v>
+      </c>
+      <c r="C1301" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1301" s="18">
+        <v>12</v>
+      </c>
+      <c r="E1301" s="13">
+        <v>43</v>
+      </c>
+      <c r="F1301" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="G1301" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="H1301" s="21"/>
+    </row>
+    <row r="1302" spans="1:8">
+      <c r="A1302" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1302" s="18">
+        <v>2</v>
+      </c>
+      <c r="C1302" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1302" s="18">
+        <v>13</v>
+      </c>
+      <c r="E1302" s="17">
+        <v>31</v>
+      </c>
+      <c r="F1302" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="G1302" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="H1302" s="21"/>
+    </row>
+    <row r="1303" spans="1:8">
+      <c r="A1303" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1303" s="18">
+        <v>2</v>
+      </c>
+      <c r="C1303" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1303" s="18">
+        <v>14</v>
+      </c>
+      <c r="E1303" s="11">
+        <v>30</v>
+      </c>
+      <c r="F1303" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1303" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="H1303" s="21"/>
+    </row>
+    <row r="1304" spans="1:8">
+      <c r="A1304" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1304" s="18">
+        <v>2</v>
+      </c>
+      <c r="C1304" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1304" s="18">
+        <v>15</v>
+      </c>
+      <c r="E1304" s="11">
+        <v>41</v>
+      </c>
+      <c r="F1304" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="G1304" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="H1304" s="21"/>
+    </row>
+    <row r="1305" spans="1:8">
+      <c r="A1305" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1305" s="18">
+        <v>2</v>
+      </c>
+      <c r="C1305" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1305" s="18">
+        <v>16</v>
+      </c>
+      <c r="E1305" s="19">
+        <v>5</v>
+      </c>
+      <c r="F1305" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1305" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="H1305" s="21"/>
+    </row>
+    <row r="1306" spans="1:8">
+      <c r="A1306" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1306" s="18">
+        <v>2</v>
+      </c>
+      <c r="C1306" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1306" s="18">
+        <v>17</v>
+      </c>
+      <c r="E1306" s="12">
+        <v>55</v>
+      </c>
+      <c r="F1306" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="G1306" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="H1306" s="21"/>
+    </row>
+    <row r="1307" spans="1:8">
+      <c r="A1307" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1307" s="18">
+        <v>2</v>
+      </c>
+      <c r="C1307" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1307" s="18">
+        <v>18</v>
+      </c>
+      <c r="E1307" s="12">
+        <v>23</v>
+      </c>
+      <c r="F1307" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1307" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="H1307" s="21"/>
+    </row>
+    <row r="1308" spans="1:8">
+      <c r="A1308" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1308" s="18">
+        <v>2</v>
+      </c>
+      <c r="C1308" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1308" s="18">
+        <v>19</v>
+      </c>
+      <c r="E1308" s="14">
+        <v>14</v>
+      </c>
+      <c r="F1308" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="G1308" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="H1308" s="21"/>
+    </row>
+    <row r="1309" spans="1:8">
+      <c r="A1309" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1309" s="18">
+        <v>2</v>
+      </c>
+      <c r="C1309" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1309" s="18">
+        <v>20</v>
+      </c>
+      <c r="E1309" s="20">
+        <v>77</v>
+      </c>
+      <c r="F1309" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1309" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="H1309" s="21"/>
+    </row>
+    <row r="1310" spans="1:8">
+      <c r="A1310" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1310" s="18">
+        <v>2</v>
+      </c>
+      <c r="C1310" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1310" s="18">
+        <v>21</v>
+      </c>
+      <c r="E1310" s="14">
+        <v>18</v>
+      </c>
+      <c r="F1310" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1310" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="H1310" s="21"/>
+    </row>
+    <row r="1311" spans="1:8">
+      <c r="A1311" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1311" s="18">
+        <v>2</v>
+      </c>
+      <c r="C1311" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1311" s="18">
+        <v>22</v>
+      </c>
+      <c r="E1311" s="20">
+        <v>11</v>
+      </c>
+      <c r="F1311" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="G1311" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="H1311" s="21"/>
+    </row>
+    <row r="1312" spans="1:8">
+      <c r="A1312" s="21">
+        <v>2026</v>
+      </c>
+      <c r="B1312" s="21">
+        <v>2</v>
+      </c>
+      <c r="C1312" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1312" s="6">
+        <v>1</v>
+      </c>
+      <c r="E1312" s="9">
+        <v>12</v>
+      </c>
+      <c r="F1312" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1312" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1312" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1313" spans="1:8">
+      <c r="A1313" s="21">
+        <v>2026</v>
+      </c>
+      <c r="B1313" s="21">
+        <v>2</v>
+      </c>
+      <c r="C1313" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1313" s="6">
+        <v>2</v>
+      </c>
+      <c r="E1313" s="9">
+        <v>63</v>
+      </c>
+      <c r="F1313" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1313" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1313" s="6">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1314" spans="1:8">
+      <c r="A1314" s="21">
+        <v>2026</v>
+      </c>
+      <c r="B1314" s="21">
+        <v>2</v>
+      </c>
+      <c r="C1314" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1314" s="6">
+        <v>3</v>
+      </c>
+      <c r="E1314" s="10">
+        <v>44</v>
+      </c>
+      <c r="F1314" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1314" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1314" s="6">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1315" spans="1:8">
+      <c r="A1315" s="21">
+        <v>2026</v>
+      </c>
+      <c r="B1315" s="21">
+        <v>2</v>
+      </c>
+      <c r="C1315" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1315" s="6">
+        <v>4</v>
+      </c>
+      <c r="E1315" s="10">
+        <v>16</v>
+      </c>
+      <c r="F1315" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G1315" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1315" s="6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1316" spans="1:8">
+      <c r="A1316" s="21">
+        <v>2026</v>
+      </c>
+      <c r="B1316" s="21">
+        <v>2</v>
+      </c>
+      <c r="C1316" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1316" s="6">
+        <v>5</v>
+      </c>
+      <c r="E1316" s="17">
+        <v>87</v>
+      </c>
+      <c r="F1316" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1316" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="H1316" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1317" spans="1:8">
+      <c r="A1317" s="21">
+        <v>2026</v>
+      </c>
+      <c r="B1317" s="21">
+        <v>2</v>
+      </c>
+      <c r="C1317" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1317" s="6">
+        <v>6</v>
+      </c>
+      <c r="E1317" s="13">
+        <v>10</v>
+      </c>
+      <c r="F1317" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1317" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="H1317" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1318" spans="1:8">
+      <c r="A1318" s="21">
+        <v>2026</v>
+      </c>
+      <c r="B1318" s="21">
+        <v>2</v>
+      </c>
+      <c r="C1318" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1318" s="6">
+        <v>7</v>
+      </c>
+      <c r="E1318" s="11">
+        <v>30</v>
+      </c>
+      <c r="F1318" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1318" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="H1318" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1319" spans="1:8">
+      <c r="A1319" s="21">
+        <v>2026</v>
+      </c>
+      <c r="B1319" s="21">
+        <v>2</v>
+      </c>
+      <c r="C1319" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1319" s="6">
+        <v>8</v>
+      </c>
+      <c r="E1319" s="8">
+        <v>6</v>
+      </c>
+      <c r="F1319" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G1319" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H1319" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1320" spans="1:8">
+      <c r="A1320" s="21">
+        <v>2026</v>
+      </c>
+      <c r="B1320" s="21">
+        <v>2</v>
+      </c>
+      <c r="C1320" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1320" s="6">
+        <v>9</v>
+      </c>
+      <c r="E1320" s="12">
+        <v>55</v>
+      </c>
+      <c r="F1320" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="G1320" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="H1320" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1321" spans="1:8">
+      <c r="A1321" s="21">
+        <v>2026</v>
+      </c>
+      <c r="B1321" s="21">
+        <v>2</v>
+      </c>
+      <c r="C1321" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1321" s="6">
+        <v>10</v>
+      </c>
+      <c r="E1321" s="13">
+        <v>43</v>
+      </c>
+      <c r="F1321" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="G1321" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="H1321" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1322" spans="1:8">
+      <c r="A1322" s="21">
+        <v>2026</v>
+      </c>
+      <c r="B1322" s="21">
+        <v>2</v>
+      </c>
+      <c r="C1322" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1322" s="6">
+        <v>11</v>
+      </c>
+      <c r="E1322" s="19">
+        <v>27</v>
+      </c>
+      <c r="F1322" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G1322" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="H1322" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1323" spans="1:8">
+      <c r="A1323" s="21">
+        <v>2026</v>
+      </c>
+      <c r="B1323" s="21">
+        <v>2</v>
+      </c>
+      <c r="C1323" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1323" s="6">
+        <v>12</v>
+      </c>
+      <c r="E1323" s="11">
+        <v>41</v>
+      </c>
+      <c r="F1323" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="G1323" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="H1323" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1324" spans="1:8">
+      <c r="A1324" s="21">
+        <v>2026</v>
+      </c>
+      <c r="B1324" s="21">
+        <v>2</v>
+      </c>
+      <c r="C1324" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1324" s="6">
+        <v>13</v>
+      </c>
+      <c r="E1324" s="20">
+        <v>77</v>
+      </c>
+      <c r="F1324" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1324" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="H1324" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1325" spans="1:8">
+      <c r="A1325" s="21">
+        <v>2026</v>
+      </c>
+      <c r="B1325" s="21">
+        <v>2</v>
+      </c>
+      <c r="C1325" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1325" s="6">
+        <v>14</v>
+      </c>
+      <c r="E1325" s="17">
+        <v>31</v>
+      </c>
+      <c r="F1325" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="G1325" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="H1325" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1326" spans="1:8">
+      <c r="A1326" s="21">
+        <v>2026</v>
+      </c>
+      <c r="B1326" s="21">
+        <v>2</v>
+      </c>
+      <c r="C1326" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1326" s="6">
+        <v>15</v>
+      </c>
+      <c r="E1326" s="20">
+        <v>11</v>
+      </c>
+      <c r="F1326" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="G1326" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="H1326" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1327" spans="1:8">
+      <c r="A1327" s="21">
+        <v>2026</v>
+      </c>
+      <c r="B1327" s="21">
+        <v>2</v>
+      </c>
+      <c r="C1327" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1327" s="6">
+        <v>16</v>
+      </c>
+      <c r="E1327" s="8">
+        <v>3</v>
+      </c>
+      <c r="F1327" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1327" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H1327" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1328" spans="1:8">
+      <c r="A1328" s="21">
+        <v>2026</v>
+      </c>
+      <c r="B1328" s="21">
+        <v>2</v>
+      </c>
+      <c r="C1328" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1328" s="6">
+        <v>17</v>
+      </c>
+      <c r="E1328" s="14">
+        <v>14</v>
+      </c>
+      <c r="F1328" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="G1328" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="H1328" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1329" spans="1:8">
+      <c r="A1329" s="21">
+        <v>2026</v>
+      </c>
+      <c r="B1329" s="21">
+        <v>2</v>
+      </c>
+      <c r="C1329" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1329" s="6">
+        <v>18</v>
+      </c>
+      <c r="E1329" s="14">
+        <v>18</v>
+      </c>
+      <c r="F1329" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1329" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="H1329" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1330" spans="1:8">
+      <c r="A1330" s="21">
+        <v>2026</v>
+      </c>
+      <c r="B1330" s="21">
+        <v>2</v>
+      </c>
+      <c r="C1330" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1330" s="6">
+        <v>19</v>
+      </c>
+      <c r="E1330" s="7">
+        <v>1</v>
+      </c>
+      <c r="F1330" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G1330" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="H1330" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1331" spans="1:8">
+      <c r="A1331" s="21">
+        <v>2026</v>
+      </c>
+      <c r="B1331" s="21">
+        <v>2</v>
+      </c>
+      <c r="C1331" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1331" s="6">
+        <v>20</v>
+      </c>
+      <c r="E1331" s="7">
+        <v>81</v>
+      </c>
+      <c r="F1331" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G1331" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="H1331" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1332" spans="1:8">
+      <c r="A1332" s="21">
+        <v>2026</v>
+      </c>
+      <c r="B1332" s="21">
+        <v>2</v>
+      </c>
+      <c r="C1332" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1332" s="6">
+        <v>21</v>
+      </c>
+      <c r="E1332" s="19">
+        <v>5</v>
+      </c>
+      <c r="F1332" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1332" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="H1332" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1333" spans="1:8">
+      <c r="A1333" s="21">
+        <v>2026</v>
+      </c>
+      <c r="B1333" s="21">
+        <v>2</v>
+      </c>
+      <c r="C1333" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1333" s="6">
+        <v>22</v>
+      </c>
+      <c r="E1333" s="12">
+        <v>23</v>
+      </c>
+      <c r="F1333" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1333" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="H1333" s="6">
         <v>0</v>
       </c>
     </row>
@@ -42151,210 +44355,210 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="18">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B23" s="18">
         <v>2026</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>214</v>
-      </c>
-      <c r="D23" s="7">
-        <v>1</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>79</v>
+        <v>218</v>
+      </c>
+      <c r="D23" s="9">
+        <v>63</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>51</v>
       </c>
       <c r="G23" s="6" t="s">
         <v>154</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="18">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B24" s="18">
         <v>2026</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>215</v>
-      </c>
-      <c r="D24" s="7">
-        <v>81</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>79</v>
+        <v>219</v>
+      </c>
+      <c r="D24" s="9">
+        <v>12</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>51</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="18">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B25" s="18">
         <v>2026</v>
       </c>
       <c r="C25" s="18" t="s">
-        <v>216</v>
-      </c>
-      <c r="D25" s="8">
-        <v>3</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>84</v>
+        <v>220</v>
+      </c>
+      <c r="D25" s="10">
+        <v>16</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F25" s="10" t="s">
+        <v>57</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>166</v>
+        <v>137</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>95</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="18">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B26" s="18">
         <v>2026</v>
       </c>
       <c r="C26" s="18" t="s">
-        <v>224</v>
-      </c>
-      <c r="D26" s="8">
-        <v>6</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>84</v>
+        <v>221</v>
+      </c>
+      <c r="D26" s="10">
+        <v>44</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>57</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>225</v>
+        <v>154</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>95</v>
+        <v>57</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="18">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B27" s="18">
         <v>2026</v>
       </c>
       <c r="C27" s="18" t="s">
-        <v>218</v>
-      </c>
-      <c r="D27" s="9">
-        <v>63</v>
-      </c>
-      <c r="E27" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="F27" s="9" t="s">
-        <v>51</v>
+        <v>214</v>
+      </c>
+      <c r="D27" s="7">
+        <v>1</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>79</v>
       </c>
       <c r="G27" s="6" t="s">
         <v>154</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="18">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B28" s="18">
         <v>2026</v>
       </c>
       <c r="C28" s="18" t="s">
-        <v>219</v>
-      </c>
-      <c r="D28" s="9">
-        <v>12</v>
-      </c>
-      <c r="E28" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="F28" s="9" t="s">
-        <v>51</v>
+        <v>215</v>
+      </c>
+      <c r="D28" s="7">
+        <v>81</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>79</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>132</v>
+        <v>107</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="18">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B29" s="18">
         <v>2026</v>
       </c>
       <c r="C29" s="18" t="s">
-        <v>220</v>
-      </c>
-      <c r="D29" s="10">
-        <v>16</v>
-      </c>
-      <c r="E29" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="F29" s="10" t="s">
-        <v>57</v>
+        <v>216</v>
+      </c>
+      <c r="D29" s="8">
+        <v>3</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>84</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>137</v>
+        <v>166</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>57</v>
+        <v>95</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="18">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B30" s="18">
         <v>2026</v>
       </c>
       <c r="C30" s="18" t="s">
-        <v>221</v>
-      </c>
-      <c r="D30" s="10">
-        <v>44</v>
-      </c>
-      <c r="E30" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="F30" s="10" t="s">
-        <v>57</v>
+        <v>224</v>
+      </c>
+      <c r="D30" s="8">
+        <v>6</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>84</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>154</v>
+        <v>225</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>57</v>
+        <v>95</v>
       </c>
     </row>
     <row r="31" spans="1:8">

--- a/public/docs/datas/f1.xlsx
+++ b/public/docs/datas/f1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="24020" activeTab="2"/>
+    <workbookView windowWidth="25340" windowHeight="23580" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="rounds" sheetId="7" r:id="rId1"/>
@@ -16,7 +16,7 @@
     <sheet name="teams" sheetId="5" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">result!$A$1:$H$1245</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">result!$A$1:$H$1333</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4883" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5012" uniqueCount="270">
   <si>
     <t>year</t>
   </si>
@@ -1565,7 +1565,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
@@ -1640,7 +1640,6 @@
     <xf numFmtId="0" fontId="1" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -1980,7 +1979,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C49"/>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="5.57142857142857" customWidth="1"/>
@@ -2304,7 +2303,7 @@
         <v>4</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -2315,7 +2314,7 @@
         <v>5</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -2326,7 +2325,7 @@
         <v>6</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -2337,7 +2336,7 @@
         <v>7</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -2348,7 +2347,7 @@
         <v>8</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -2359,7 +2358,7 @@
         <v>9</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -2370,7 +2369,7 @@
         <v>10</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -2381,7 +2380,7 @@
         <v>11</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -2392,7 +2391,7 @@
         <v>12</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -2403,7 +2402,7 @@
         <v>13</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -2414,7 +2413,7 @@
         <v>14</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -2425,7 +2424,7 @@
         <v>15</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -2436,7 +2435,7 @@
         <v>16</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -2447,7 +2446,7 @@
         <v>17</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -2458,7 +2457,7 @@
         <v>18</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -2469,7 +2468,7 @@
         <v>19</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -2480,7 +2479,7 @@
         <v>20</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -2491,7 +2490,7 @@
         <v>21</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -2502,28 +2501,6 @@
         <v>22</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="6">
-        <v>2026</v>
-      </c>
-      <c r="B48" s="6">
-        <v>23</v>
-      </c>
-      <c r="C48" s="6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="6">
-        <v>2026</v>
-      </c>
-      <c r="B49" s="6">
-        <v>24</v>
-      </c>
-      <c r="C49" s="6" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2536,7 +2513,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G241"/>
+  <dimension ref="A1:G231"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="5.57142857142857" customWidth="1"/>
@@ -2581,13 +2558,13 @@
       <c r="C2" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="41">
+      <c r="D2" s="40">
         <v>45730</v>
       </c>
-      <c r="E2" s="42">
+      <c r="E2" s="41">
         <v>0.395833333333333</v>
       </c>
-      <c r="F2" s="42">
+      <c r="F2" s="41">
         <v>0.4375</v>
       </c>
       <c r="G2" s="6">
@@ -2604,13 +2581,13 @@
       <c r="C3" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="41">
+      <c r="D3" s="40">
         <v>45730</v>
       </c>
-      <c r="E3" s="42">
+      <c r="E3" s="41">
         <v>0.541666666666667</v>
       </c>
-      <c r="F3" s="42">
+      <c r="F3" s="41">
         <v>0.583333333333333</v>
       </c>
       <c r="G3" s="6">
@@ -2627,13 +2604,13 @@
       <c r="C4" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D4" s="41">
+      <c r="D4" s="40">
         <v>45731</v>
       </c>
-      <c r="E4" s="42">
+      <c r="E4" s="41">
         <v>0.395833333333333</v>
       </c>
-      <c r="F4" s="42">
+      <c r="F4" s="41">
         <v>0.4375</v>
       </c>
       <c r="G4" s="6">
@@ -2650,13 +2627,13 @@
       <c r="C5" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="41">
+      <c r="D5" s="40">
         <v>45731</v>
       </c>
-      <c r="E5" s="42">
+      <c r="E5" s="41">
         <v>0.541666666666667</v>
       </c>
-      <c r="F5" s="42">
+      <c r="F5" s="41">
         <v>0.583333333333333</v>
       </c>
       <c r="G5" s="6">
@@ -2673,13 +2650,13 @@
       <c r="C6" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="41">
+      <c r="D6" s="40">
         <v>45732</v>
       </c>
-      <c r="E6" s="42">
+      <c r="E6" s="41">
         <v>0.5</v>
       </c>
-      <c r="F6" s="42"/>
+      <c r="F6" s="41"/>
       <c r="G6" s="6">
         <v>1</v>
       </c>
@@ -2694,13 +2671,13 @@
       <c r="C7" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D7" s="43">
+      <c r="D7" s="42">
         <v>45737</v>
       </c>
-      <c r="E7" s="44">
+      <c r="E7" s="43">
         <v>0.479166666666667</v>
       </c>
-      <c r="F7" s="44">
+      <c r="F7" s="43">
         <v>0.520833333333333</v>
       </c>
       <c r="G7" s="18">
@@ -2717,13 +2694,13 @@
       <c r="C8" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="43">
+      <c r="D8" s="42">
         <v>45737</v>
       </c>
-      <c r="E8" s="44">
+      <c r="E8" s="43">
         <v>0.645833333333333</v>
       </c>
-      <c r="F8" s="44">
+      <c r="F8" s="43">
         <v>0.676388888888889</v>
       </c>
       <c r="G8" s="18">
@@ -2740,13 +2717,13 @@
       <c r="C9" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="D9" s="43">
+      <c r="D9" s="42">
         <v>45738</v>
       </c>
-      <c r="E9" s="44">
+      <c r="E9" s="43">
         <v>0.458333333333333</v>
       </c>
-      <c r="F9" s="44">
+      <c r="F9" s="43">
         <v>0.5</v>
       </c>
       <c r="G9" s="18">
@@ -2763,13 +2740,13 @@
       <c r="C10" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="43">
+      <c r="D10" s="42">
         <v>45738</v>
       </c>
-      <c r="E10" s="44">
+      <c r="E10" s="43">
         <v>0.625</v>
       </c>
-      <c r="F10" s="44">
+      <c r="F10" s="43">
         <v>0.666666666666667</v>
       </c>
       <c r="G10" s="18">
@@ -2786,10 +2763,10 @@
       <c r="C11" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D11" s="43">
+      <c r="D11" s="42">
         <v>45739</v>
       </c>
-      <c r="E11" s="44">
+      <c r="E11" s="43">
         <v>0.625</v>
       </c>
       <c r="F11" s="18"/>
@@ -2807,13 +2784,13 @@
       <c r="C12" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D12" s="41">
+      <c r="D12" s="40">
         <v>45751</v>
       </c>
-      <c r="E12" s="42">
+      <c r="E12" s="41">
         <v>0.4375</v>
       </c>
-      <c r="F12" s="42">
+      <c r="F12" s="41">
         <v>0.479166666666667</v>
       </c>
       <c r="G12" s="6">
@@ -2830,13 +2807,13 @@
       <c r="C13" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="41">
+      <c r="D13" s="40">
         <v>45751</v>
       </c>
-      <c r="E13" s="42">
+      <c r="E13" s="41">
         <v>0.583333333333333</v>
       </c>
-      <c r="F13" s="42">
+      <c r="F13" s="41">
         <v>0.625</v>
       </c>
       <c r="G13" s="6">
@@ -2853,13 +2830,13 @@
       <c r="C14" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D14" s="41">
+      <c r="D14" s="40">
         <v>45752</v>
       </c>
-      <c r="E14" s="42">
+      <c r="E14" s="41">
         <v>0.4375</v>
       </c>
-      <c r="F14" s="42">
+      <c r="F14" s="41">
         <v>0.479166666666667</v>
       </c>
       <c r="G14" s="6">
@@ -2876,13 +2853,13 @@
       <c r="C15" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="41">
+      <c r="D15" s="40">
         <v>45752</v>
       </c>
-      <c r="E15" s="42">
+      <c r="E15" s="41">
         <v>0.583333333333333</v>
       </c>
-      <c r="F15" s="42">
+      <c r="F15" s="41">
         <v>0.625</v>
       </c>
       <c r="G15" s="6">
@@ -2899,10 +2876,10 @@
       <c r="C16" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D16" s="41">
+      <c r="D16" s="40">
         <v>45753</v>
       </c>
-      <c r="E16" s="42">
+      <c r="E16" s="41">
         <v>0.541666666666667</v>
       </c>
       <c r="F16" s="6"/>
@@ -2920,13 +2897,13 @@
       <c r="C17" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D17" s="43">
+      <c r="D17" s="42">
         <v>45758</v>
       </c>
-      <c r="E17" s="44">
+      <c r="E17" s="43">
         <v>0.8125</v>
       </c>
-      <c r="F17" s="44">
+      <c r="F17" s="43">
         <v>0.854166666666667</v>
       </c>
       <c r="G17" s="18">
@@ -2943,13 +2920,13 @@
       <c r="C18" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="D18" s="43">
+      <c r="D18" s="42">
         <v>45758</v>
       </c>
-      <c r="E18" s="44">
+      <c r="E18" s="43">
         <v>0.958333333333333</v>
       </c>
-      <c r="F18" s="44">
+      <c r="F18" s="43">
         <v>0</v>
       </c>
       <c r="G18" s="18">
@@ -2966,13 +2943,13 @@
       <c r="C19" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="D19" s="43">
+      <c r="D19" s="42">
         <v>45759</v>
       </c>
-      <c r="E19" s="44">
+      <c r="E19" s="43">
         <v>0.854166666666667</v>
       </c>
-      <c r="F19" s="44">
+      <c r="F19" s="43">
         <v>0.895833333333333</v>
       </c>
       <c r="G19" s="18">
@@ -2989,13 +2966,13 @@
       <c r="C20" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D20" s="43">
+      <c r="D20" s="42">
         <v>45760</v>
       </c>
-      <c r="E20" s="44">
-        <v>0</v>
-      </c>
-      <c r="F20" s="44">
+      <c r="E20" s="43">
+        <v>0</v>
+      </c>
+      <c r="F20" s="43">
         <v>0.0416666666666667</v>
       </c>
       <c r="G20" s="18">
@@ -3012,10 +2989,10 @@
       <c r="C21" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D21" s="43">
+      <c r="D21" s="42">
         <v>45760</v>
       </c>
-      <c r="E21" s="44">
+      <c r="E21" s="43">
         <v>0.958333333333333</v>
       </c>
       <c r="F21" s="18"/>
@@ -3033,13 +3010,13 @@
       <c r="C22" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D22" s="41">
+      <c r="D22" s="40">
         <v>45765</v>
       </c>
-      <c r="E22" s="42">
+      <c r="E22" s="41">
         <v>0.895833333333333</v>
       </c>
-      <c r="F22" s="42">
+      <c r="F22" s="41">
         <v>0.9375</v>
       </c>
       <c r="G22" s="6">
@@ -3056,13 +3033,13 @@
       <c r="C23" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D23" s="41">
+      <c r="D23" s="40">
         <v>45766</v>
       </c>
-      <c r="E23" s="42">
+      <c r="E23" s="41">
         <v>0.0416666666666667</v>
       </c>
-      <c r="F23" s="42">
+      <c r="F23" s="41">
         <v>0.0833333333333333</v>
       </c>
       <c r="G23" s="6">
@@ -3079,13 +3056,13 @@
       <c r="C24" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="41">
+      <c r="D24" s="40">
         <v>45766</v>
       </c>
-      <c r="E24" s="42">
+      <c r="E24" s="41">
         <v>0.895833333333333</v>
       </c>
-      <c r="F24" s="42">
+      <c r="F24" s="41">
         <v>0.9375</v>
       </c>
       <c r="G24" s="6">
@@ -3102,13 +3079,13 @@
       <c r="C25" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="41">
+      <c r="D25" s="40">
         <v>45767</v>
       </c>
-      <c r="E25" s="42">
+      <c r="E25" s="41">
         <v>0.0416666666666667</v>
       </c>
-      <c r="F25" s="42">
+      <c r="F25" s="41">
         <v>0.0833333333333333</v>
       </c>
       <c r="G25" s="6">
@@ -3125,10 +3102,10 @@
       <c r="C26" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D26" s="41">
+      <c r="D26" s="40">
         <v>45767</v>
       </c>
-      <c r="E26" s="42">
+      <c r="E26" s="41">
         <v>0.0416666666666667</v>
       </c>
       <c r="F26" s="6"/>
@@ -3146,13 +3123,13 @@
       <c r="C27" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D27" s="43">
+      <c r="D27" s="42">
         <v>45780</v>
       </c>
-      <c r="E27" s="44">
+      <c r="E27" s="43">
         <v>0.0208333333333333</v>
       </c>
-      <c r="F27" s="44">
+      <c r="F27" s="43">
         <v>0.0625</v>
       </c>
       <c r="G27" s="18">
@@ -3169,13 +3146,13 @@
       <c r="C28" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="D28" s="43">
+      <c r="D28" s="42">
         <v>45780</v>
       </c>
-      <c r="E28" s="44">
+      <c r="E28" s="43">
         <v>0.1875</v>
       </c>
-      <c r="F28" s="44">
+      <c r="F28" s="43">
         <v>0.218055555555556</v>
       </c>
       <c r="G28" s="18">
@@ -3192,13 +3169,13 @@
       <c r="C29" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="D29" s="43">
+      <c r="D29" s="42">
         <v>45781</v>
       </c>
-      <c r="E29" s="44">
-        <v>0</v>
-      </c>
-      <c r="F29" s="44">
+      <c r="E29" s="43">
+        <v>0</v>
+      </c>
+      <c r="F29" s="43">
         <v>0.0416666666666667</v>
       </c>
       <c r="G29" s="18">
@@ -3215,13 +3192,13 @@
       <c r="C30" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D30" s="43">
+      <c r="D30" s="42">
         <v>45781</v>
       </c>
-      <c r="E30" s="44">
+      <c r="E30" s="43">
         <v>0.166666666666667</v>
       </c>
-      <c r="F30" s="44">
+      <c r="F30" s="43">
         <v>0.208333333333333</v>
       </c>
       <c r="G30" s="18">
@@ -3238,13 +3215,13 @@
       <c r="C31" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D31" s="43">
+      <c r="D31" s="42">
         <v>45782</v>
       </c>
-      <c r="E31" s="44">
+      <c r="E31" s="43">
         <v>0.166666666666667</v>
       </c>
-      <c r="F31" s="44"/>
+      <c r="F31" s="43"/>
       <c r="G31" s="18">
         <v>1</v>
       </c>
@@ -3259,13 +3236,13 @@
       <c r="C32" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D32" s="41">
+      <c r="D32" s="40">
         <v>45793</v>
       </c>
-      <c r="E32" s="42">
+      <c r="E32" s="41">
         <v>0.8125</v>
       </c>
-      <c r="F32" s="42">
+      <c r="F32" s="41">
         <v>0.854166666666667</v>
       </c>
       <c r="G32" s="6">
@@ -3282,13 +3259,13 @@
       <c r="C33" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D33" s="41">
+      <c r="D33" s="40">
         <v>45793</v>
       </c>
-      <c r="E33" s="42">
+      <c r="E33" s="41">
         <v>0.958333333333333</v>
       </c>
-      <c r="F33" s="42">
+      <c r="F33" s="41">
         <v>0</v>
       </c>
       <c r="G33" s="6">
@@ -3305,13 +3282,13 @@
       <c r="C34" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D34" s="41">
+      <c r="D34" s="40">
         <v>45794</v>
       </c>
-      <c r="E34" s="42">
+      <c r="E34" s="41">
         <v>0.770833333333333</v>
       </c>
-      <c r="F34" s="42">
+      <c r="F34" s="41">
         <v>0.8125</v>
       </c>
       <c r="G34" s="6">
@@ -3328,13 +3305,13 @@
       <c r="C35" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D35" s="41">
+      <c r="D35" s="40">
         <v>45794</v>
       </c>
-      <c r="E35" s="42">
+      <c r="E35" s="41">
         <v>0.916666666666667</v>
       </c>
-      <c r="F35" s="42">
+      <c r="F35" s="41">
         <v>0.958333333333333</v>
       </c>
       <c r="G35" s="6">
@@ -3351,10 +3328,10 @@
       <c r="C36" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D36" s="41">
+      <c r="D36" s="40">
         <v>45795</v>
       </c>
-      <c r="E36" s="42">
+      <c r="E36" s="41">
         <v>0.875</v>
       </c>
       <c r="F36" s="6"/>
@@ -3372,13 +3349,13 @@
       <c r="C37" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D37" s="43">
+      <c r="D37" s="42">
         <v>45800</v>
       </c>
-      <c r="E37" s="44">
+      <c r="E37" s="43">
         <v>0.8125</v>
       </c>
-      <c r="F37" s="44">
+      <c r="F37" s="43">
         <v>0.854166666666667</v>
       </c>
       <c r="G37" s="18">
@@ -3395,13 +3372,13 @@
       <c r="C38" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="D38" s="43">
+      <c r="D38" s="42">
         <v>45800</v>
       </c>
-      <c r="E38" s="44">
+      <c r="E38" s="43">
         <v>0.958333333333333</v>
       </c>
-      <c r="F38" s="44">
+      <c r="F38" s="43">
         <v>0</v>
       </c>
       <c r="G38" s="18">
@@ -3418,13 +3395,13 @@
       <c r="C39" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="D39" s="43">
+      <c r="D39" s="42">
         <v>45801</v>
       </c>
-      <c r="E39" s="44">
+      <c r="E39" s="43">
         <v>0.770833333333333</v>
       </c>
-      <c r="F39" s="44">
+      <c r="F39" s="43">
         <v>0.8125</v>
       </c>
       <c r="G39" s="18">
@@ -3441,13 +3418,13 @@
       <c r="C40" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D40" s="43">
+      <c r="D40" s="42">
         <v>45801</v>
       </c>
-      <c r="E40" s="44">
+      <c r="E40" s="43">
         <v>0.916666666666667</v>
       </c>
-      <c r="F40" s="44">
+      <c r="F40" s="43">
         <v>0.958333333333333</v>
       </c>
       <c r="G40" s="18">
@@ -3464,10 +3441,10 @@
       <c r="C41" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D41" s="43">
+      <c r="D41" s="42">
         <v>45802</v>
       </c>
-      <c r="E41" s="44">
+      <c r="E41" s="43">
         <v>0.875</v>
       </c>
       <c r="F41" s="18"/>
@@ -3485,13 +3462,13 @@
       <c r="C42" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D42" s="41">
+      <c r="D42" s="40">
         <v>45807</v>
       </c>
-      <c r="E42" s="42">
+      <c r="E42" s="41">
         <v>0.8125</v>
       </c>
-      <c r="F42" s="42">
+      <c r="F42" s="41">
         <v>0.854166666666667</v>
       </c>
       <c r="G42" s="6">
@@ -3508,13 +3485,13 @@
       <c r="C43" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D43" s="41">
+      <c r="D43" s="40">
         <v>45807</v>
       </c>
-      <c r="E43" s="42">
+      <c r="E43" s="41">
         <v>0.958333333333333</v>
       </c>
-      <c r="F43" s="42">
+      <c r="F43" s="41">
         <v>0</v>
       </c>
       <c r="G43" s="6">
@@ -3531,13 +3508,13 @@
       <c r="C44" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D44" s="41">
+      <c r="D44" s="40">
         <v>45808</v>
       </c>
-      <c r="E44" s="42">
+      <c r="E44" s="41">
         <v>0.770833333333333</v>
       </c>
-      <c r="F44" s="42">
+      <c r="F44" s="41">
         <v>0.8125</v>
       </c>
       <c r="G44" s="6">
@@ -3554,13 +3531,13 @@
       <c r="C45" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D45" s="41">
+      <c r="D45" s="40">
         <v>45808</v>
       </c>
-      <c r="E45" s="42">
+      <c r="E45" s="41">
         <v>0.916666666666667</v>
       </c>
-      <c r="F45" s="42">
+      <c r="F45" s="41">
         <v>0.958333333333333</v>
       </c>
       <c r="G45" s="6">
@@ -3577,10 +3554,10 @@
       <c r="C46" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D46" s="41">
+      <c r="D46" s="40">
         <v>45809</v>
       </c>
-      <c r="E46" s="42">
+      <c r="E46" s="41">
         <v>0.875</v>
       </c>
       <c r="F46" s="6"/>
@@ -3598,13 +3575,13 @@
       <c r="C47" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D47" s="43">
+      <c r="D47" s="42">
         <v>45822</v>
       </c>
-      <c r="E47" s="44">
+      <c r="E47" s="43">
         <v>0.0625</v>
       </c>
-      <c r="F47" s="44">
+      <c r="F47" s="43">
         <v>0.104166666666667</v>
       </c>
       <c r="G47" s="18">
@@ -3621,13 +3598,13 @@
       <c r="C48" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="D48" s="43">
+      <c r="D48" s="42">
         <v>45822</v>
       </c>
-      <c r="E48" s="44">
+      <c r="E48" s="43">
         <v>0.208333333333333</v>
       </c>
-      <c r="F48" s="44">
+      <c r="F48" s="43">
         <v>0.25</v>
       </c>
       <c r="G48" s="18">
@@ -3644,13 +3621,13 @@
       <c r="C49" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="D49" s="43">
+      <c r="D49" s="42">
         <v>45823</v>
       </c>
-      <c r="E49" s="44">
+      <c r="E49" s="43">
         <v>0.0208333333333333</v>
       </c>
-      <c r="F49" s="44">
+      <c r="F49" s="43">
         <v>0.0625</v>
       </c>
       <c r="G49" s="18">
@@ -3667,13 +3644,13 @@
       <c r="C50" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D50" s="43">
+      <c r="D50" s="42">
         <v>45823</v>
       </c>
-      <c r="E50" s="44">
+      <c r="E50" s="43">
         <v>0.166666666666667</v>
       </c>
-      <c r="F50" s="44">
+      <c r="F50" s="43">
         <v>0.208333333333333</v>
       </c>
       <c r="G50" s="18">
@@ -3690,10 +3667,10 @@
       <c r="C51" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D51" s="43">
+      <c r="D51" s="42">
         <v>45824</v>
       </c>
-      <c r="E51" s="44">
+      <c r="E51" s="43">
         <v>0.0833333333333333</v>
       </c>
       <c r="F51" s="18"/>
@@ -3711,13 +3688,13 @@
       <c r="C52" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D52" s="41">
+      <c r="D52" s="40">
         <v>45835</v>
       </c>
-      <c r="E52" s="42">
+      <c r="E52" s="41">
         <v>0.8125</v>
       </c>
-      <c r="F52" s="42">
+      <c r="F52" s="41">
         <v>0.854166666666667</v>
       </c>
       <c r="G52" s="6">
@@ -3734,13 +3711,13 @@
       <c r="C53" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D53" s="41">
+      <c r="D53" s="40">
         <v>45835</v>
       </c>
-      <c r="E53" s="42">
+      <c r="E53" s="41">
         <v>0.958333333333333</v>
       </c>
-      <c r="F53" s="42">
+      <c r="F53" s="41">
         <v>0</v>
       </c>
       <c r="G53" s="6">
@@ -3757,13 +3734,13 @@
       <c r="C54" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D54" s="41">
+      <c r="D54" s="40">
         <v>45836</v>
       </c>
-      <c r="E54" s="42">
+      <c r="E54" s="41">
         <v>0.770833333333333</v>
       </c>
-      <c r="F54" s="42">
+      <c r="F54" s="41">
         <v>0.8125</v>
       </c>
       <c r="G54" s="6">
@@ -3780,13 +3757,13 @@
       <c r="C55" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D55" s="41">
+      <c r="D55" s="40">
         <v>45836</v>
       </c>
-      <c r="E55" s="42">
+      <c r="E55" s="41">
         <v>0.916666666666667</v>
       </c>
-      <c r="F55" s="42">
+      <c r="F55" s="41">
         <v>0.958333333333333</v>
       </c>
       <c r="G55" s="6">
@@ -3803,10 +3780,10 @@
       <c r="C56" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D56" s="41">
+      <c r="D56" s="40">
         <v>45837</v>
       </c>
-      <c r="E56" s="42">
+      <c r="E56" s="41">
         <v>0.875</v>
       </c>
       <c r="F56" s="6"/>
@@ -3824,13 +3801,13 @@
       <c r="C57" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D57" s="43">
+      <c r="D57" s="42">
         <v>45842</v>
       </c>
-      <c r="E57" s="44">
+      <c r="E57" s="43">
         <v>0.8125</v>
       </c>
-      <c r="F57" s="44">
+      <c r="F57" s="43">
         <v>0.854166666666667</v>
       </c>
       <c r="G57" s="18">
@@ -3847,13 +3824,13 @@
       <c r="C58" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="D58" s="43">
+      <c r="D58" s="42">
         <v>45842</v>
       </c>
-      <c r="E58" s="44">
+      <c r="E58" s="43">
         <v>0.958333333333333</v>
       </c>
-      <c r="F58" s="44">
+      <c r="F58" s="43">
         <v>0</v>
       </c>
       <c r="G58" s="18">
@@ -3870,13 +3847,13 @@
       <c r="C59" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="D59" s="43">
+      <c r="D59" s="42">
         <v>45843</v>
       </c>
-      <c r="E59" s="44">
+      <c r="E59" s="43">
         <v>0.770833333333333</v>
       </c>
-      <c r="F59" s="44">
+      <c r="F59" s="43">
         <v>0.8125</v>
       </c>
       <c r="G59" s="18">
@@ -3893,13 +3870,13 @@
       <c r="C60" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D60" s="43">
+      <c r="D60" s="42">
         <v>45843</v>
       </c>
-      <c r="E60" s="44">
+      <c r="E60" s="43">
         <v>0.916666666666667</v>
       </c>
-      <c r="F60" s="44">
+      <c r="F60" s="43">
         <v>0.958333333333333</v>
       </c>
       <c r="G60" s="18">
@@ -3916,10 +3893,10 @@
       <c r="C61" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D61" s="43">
+      <c r="D61" s="42">
         <v>45844</v>
       </c>
-      <c r="E61" s="44">
+      <c r="E61" s="43">
         <v>0.916666666666667</v>
       </c>
       <c r="F61" s="18"/>
@@ -3937,13 +3914,13 @@
       <c r="C62" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D62" s="41">
+      <c r="D62" s="40">
         <v>45863</v>
       </c>
-      <c r="E62" s="42">
+      <c r="E62" s="41">
         <v>0.8125</v>
       </c>
-      <c r="F62" s="42">
+      <c r="F62" s="41">
         <v>0.854166666666667</v>
       </c>
       <c r="G62" s="6">
@@ -3960,13 +3937,13 @@
       <c r="C63" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="D63" s="41">
+      <c r="D63" s="40">
         <v>45863</v>
       </c>
-      <c r="E63" s="42">
+      <c r="E63" s="41">
         <v>0.9375</v>
       </c>
-      <c r="F63" s="42">
+      <c r="F63" s="41">
         <v>0.968055555555556</v>
       </c>
       <c r="G63" s="6">
@@ -3983,13 +3960,13 @@
       <c r="C64" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D64" s="41">
+      <c r="D64" s="40">
         <v>45864</v>
       </c>
-      <c r="E64" s="42">
+      <c r="E64" s="41">
         <v>0.75</v>
       </c>
-      <c r="F64" s="42">
+      <c r="F64" s="41">
         <v>0.791666666666667</v>
       </c>
       <c r="G64" s="6">
@@ -4006,13 +3983,13 @@
       <c r="C65" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D65" s="41">
+      <c r="D65" s="40">
         <v>45864</v>
       </c>
-      <c r="E65" s="42">
+      <c r="E65" s="41">
         <v>0.916666666666667</v>
       </c>
-      <c r="F65" s="42">
+      <c r="F65" s="41">
         <v>0.958333333333333</v>
       </c>
       <c r="G65" s="6">
@@ -4029,10 +4006,10 @@
       <c r="C66" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D66" s="41">
+      <c r="D66" s="40">
         <v>45865</v>
       </c>
-      <c r="E66" s="42">
+      <c r="E66" s="41">
         <v>0.875</v>
       </c>
       <c r="F66" s="6"/>
@@ -4050,13 +4027,13 @@
       <c r="C67" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D67" s="43">
+      <c r="D67" s="42">
         <v>45870</v>
       </c>
-      <c r="E67" s="44">
+      <c r="E67" s="43">
         <v>0.8125</v>
       </c>
-      <c r="F67" s="44">
+      <c r="F67" s="43">
         <v>0.854166666666667</v>
       </c>
       <c r="G67" s="18">
@@ -4073,13 +4050,13 @@
       <c r="C68" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="D68" s="43">
+      <c r="D68" s="42">
         <v>45870</v>
       </c>
-      <c r="E68" s="44">
+      <c r="E68" s="43">
         <v>0.958333333333333</v>
       </c>
-      <c r="F68" s="44">
+      <c r="F68" s="43">
         <v>0</v>
       </c>
       <c r="G68" s="18">
@@ -4096,13 +4073,13 @@
       <c r="C69" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="D69" s="43">
+      <c r="D69" s="42">
         <v>45871</v>
       </c>
-      <c r="E69" s="44">
+      <c r="E69" s="43">
         <v>0.770833333333333</v>
       </c>
-      <c r="F69" s="44">
+      <c r="F69" s="43">
         <v>0.8125</v>
       </c>
       <c r="G69" s="18">
@@ -4119,13 +4096,13 @@
       <c r="C70" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D70" s="43">
+      <c r="D70" s="42">
         <v>45871</v>
       </c>
-      <c r="E70" s="44">
+      <c r="E70" s="43">
         <v>0.916666666666667</v>
       </c>
-      <c r="F70" s="44">
+      <c r="F70" s="43">
         <v>0.958333333333333</v>
       </c>
       <c r="G70" s="18">
@@ -4142,10 +4119,10 @@
       <c r="C71" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D71" s="43">
+      <c r="D71" s="42">
         <v>45872</v>
       </c>
-      <c r="E71" s="44">
+      <c r="E71" s="43">
         <v>0.875</v>
       </c>
       <c r="F71" s="18"/>
@@ -4163,13 +4140,13 @@
       <c r="C72" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D72" s="41">
+      <c r="D72" s="40">
         <v>45898</v>
       </c>
-      <c r="E72" s="42">
+      <c r="E72" s="41">
         <v>0.770833333333333</v>
       </c>
-      <c r="F72" s="42">
+      <c r="F72" s="41">
         <v>0.8125</v>
       </c>
       <c r="G72" s="6">
@@ -4186,13 +4163,13 @@
       <c r="C73" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D73" s="41">
+      <c r="D73" s="40">
         <v>45898</v>
       </c>
-      <c r="E73" s="42">
+      <c r="E73" s="41">
         <v>0.916666666666667</v>
       </c>
-      <c r="F73" s="42">
+      <c r="F73" s="41">
         <v>0.958333333333333</v>
       </c>
       <c r="G73" s="6">
@@ -4209,13 +4186,13 @@
       <c r="C74" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D74" s="41">
+      <c r="D74" s="40">
         <v>45899</v>
       </c>
-      <c r="E74" s="42">
+      <c r="E74" s="41">
         <v>0.729166666666667</v>
       </c>
-      <c r="F74" s="42">
+      <c r="F74" s="41">
         <v>0.770833333333333</v>
       </c>
       <c r="G74" s="6">
@@ -4232,13 +4209,13 @@
       <c r="C75" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D75" s="41">
+      <c r="D75" s="40">
         <v>45899</v>
       </c>
-      <c r="E75" s="42">
+      <c r="E75" s="41">
         <v>0.875</v>
       </c>
-      <c r="F75" s="42">
+      <c r="F75" s="41">
         <v>0.916666666666667</v>
       </c>
       <c r="G75" s="6">
@@ -4255,13 +4232,13 @@
       <c r="C76" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D76" s="41">
+      <c r="D76" s="40">
         <v>45900</v>
       </c>
-      <c r="E76" s="42">
+      <c r="E76" s="41">
         <v>0.875</v>
       </c>
-      <c r="F76" s="42"/>
+      <c r="F76" s="41"/>
       <c r="G76" s="6">
         <v>1</v>
       </c>
@@ -4276,13 +4253,13 @@
       <c r="C77" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D77" s="43">
+      <c r="D77" s="42">
         <v>45905</v>
       </c>
-      <c r="E77" s="44">
+      <c r="E77" s="43">
         <v>0.8125</v>
       </c>
-      <c r="F77" s="44">
+      <c r="F77" s="43">
         <v>0.854166666666667</v>
       </c>
       <c r="G77" s="18">
@@ -4299,13 +4276,13 @@
       <c r="C78" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="D78" s="43">
+      <c r="D78" s="42">
         <v>45905</v>
       </c>
-      <c r="E78" s="44">
+      <c r="E78" s="43">
         <v>0.958333333333333</v>
       </c>
-      <c r="F78" s="44">
+      <c r="F78" s="43">
         <v>0</v>
       </c>
       <c r="G78" s="18">
@@ -4322,13 +4299,13 @@
       <c r="C79" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="D79" s="43">
+      <c r="D79" s="42">
         <v>45906</v>
       </c>
-      <c r="E79" s="44">
+      <c r="E79" s="43">
         <v>0.770833333333333</v>
       </c>
-      <c r="F79" s="44">
+      <c r="F79" s="43">
         <v>0.8125</v>
       </c>
       <c r="G79" s="18">
@@ -4345,13 +4322,13 @@
       <c r="C80" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D80" s="43">
+      <c r="D80" s="42">
         <v>45906</v>
       </c>
-      <c r="E80" s="44">
+      <c r="E80" s="43">
         <v>0.916666666666667</v>
       </c>
-      <c r="F80" s="44">
+      <c r="F80" s="43">
         <v>0.958333333333333</v>
       </c>
       <c r="G80" s="18">
@@ -4368,10 +4345,10 @@
       <c r="C81" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D81" s="43">
+      <c r="D81" s="42">
         <v>45907</v>
       </c>
-      <c r="E81" s="44">
+      <c r="E81" s="43">
         <v>0.875</v>
       </c>
       <c r="F81" s="18"/>
@@ -4389,13 +4366,13 @@
       <c r="C82" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D82" s="41">
+      <c r="D82" s="40">
         <v>45919</v>
       </c>
-      <c r="E82" s="42">
+      <c r="E82" s="41">
         <v>0.6875</v>
       </c>
-      <c r="F82" s="42">
+      <c r="F82" s="41">
         <v>0.729166666666667</v>
       </c>
       <c r="G82" s="6">
@@ -4412,13 +4389,13 @@
       <c r="C83" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D83" s="41">
+      <c r="D83" s="40">
         <v>45919</v>
       </c>
-      <c r="E83" s="42">
+      <c r="E83" s="41">
         <v>0.833333333333333</v>
       </c>
-      <c r="F83" s="42">
+      <c r="F83" s="41">
         <v>0.875</v>
       </c>
       <c r="G83" s="6">
@@ -4435,13 +4412,13 @@
       <c r="C84" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D84" s="41">
+      <c r="D84" s="40">
         <v>45920</v>
       </c>
-      <c r="E84" s="42">
+      <c r="E84" s="41">
         <v>0.6875</v>
       </c>
-      <c r="F84" s="42">
+      <c r="F84" s="41">
         <v>0.729166666666667</v>
       </c>
       <c r="G84" s="6">
@@ -4458,13 +4435,13 @@
       <c r="C85" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D85" s="41">
+      <c r="D85" s="40">
         <v>45920</v>
       </c>
-      <c r="E85" s="42">
+      <c r="E85" s="41">
         <v>0.833333333333333</v>
       </c>
-      <c r="F85" s="42">
+      <c r="F85" s="41">
         <v>0.875</v>
       </c>
       <c r="G85" s="6">
@@ -4481,10 +4458,10 @@
       <c r="C86" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D86" s="41">
+      <c r="D86" s="40">
         <v>45921</v>
       </c>
-      <c r="E86" s="42">
+      <c r="E86" s="41">
         <v>0.791666666666667</v>
       </c>
       <c r="F86" s="6"/>
@@ -4502,13 +4479,13 @@
       <c r="C87" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D87" s="43">
+      <c r="D87" s="42">
         <v>45933</v>
       </c>
-      <c r="E87" s="44">
+      <c r="E87" s="43">
         <v>0.729166666666667</v>
       </c>
-      <c r="F87" s="44">
+      <c r="F87" s="43">
         <v>0.770833333333333</v>
       </c>
       <c r="G87" s="18">
@@ -4525,13 +4502,13 @@
       <c r="C88" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="D88" s="43">
+      <c r="D88" s="42">
         <v>45933</v>
       </c>
-      <c r="E88" s="44">
+      <c r="E88" s="43">
         <v>0.875</v>
       </c>
-      <c r="F88" s="44">
+      <c r="F88" s="43">
         <v>0.916666666666667</v>
       </c>
       <c r="G88" s="18">
@@ -4548,13 +4525,13 @@
       <c r="C89" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="D89" s="43">
+      <c r="D89" s="42">
         <v>45934</v>
       </c>
-      <c r="E89" s="44">
+      <c r="E89" s="43">
         <v>0.729166666666667</v>
       </c>
-      <c r="F89" s="44">
+      <c r="F89" s="43">
         <v>0.770833333333333</v>
       </c>
       <c r="G89" s="18">
@@ -4571,13 +4548,13 @@
       <c r="C90" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D90" s="43">
+      <c r="D90" s="42">
         <v>45934</v>
       </c>
-      <c r="E90" s="44">
+      <c r="E90" s="43">
         <v>0.875</v>
       </c>
-      <c r="F90" s="44">
+      <c r="F90" s="43">
         <v>0.916666666666667</v>
       </c>
       <c r="G90" s="18">
@@ -4594,10 +4571,10 @@
       <c r="C91" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D91" s="43">
+      <c r="D91" s="42">
         <v>45935</v>
       </c>
-      <c r="E91" s="44">
+      <c r="E91" s="43">
         <v>0.833333333333333</v>
       </c>
       <c r="F91" s="18"/>
@@ -4615,13 +4592,13 @@
       <c r="C92" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D92" s="41">
+      <c r="D92" s="40">
         <v>45948</v>
       </c>
-      <c r="E92" s="42">
+      <c r="E92" s="41">
         <v>0.0625</v>
       </c>
-      <c r="F92" s="42">
+      <c r="F92" s="41">
         <v>0.104166666666667</v>
       </c>
       <c r="G92" s="6">
@@ -4638,13 +4615,13 @@
       <c r="C93" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="D93" s="41">
+      <c r="D93" s="40">
         <v>45948</v>
       </c>
-      <c r="E93" s="42">
+      <c r="E93" s="41">
         <v>0.229166666666667</v>
       </c>
-      <c r="F93" s="42">
+      <c r="F93" s="41">
         <v>0.259722222222222</v>
       </c>
       <c r="G93" s="6">
@@ -4661,13 +4638,13 @@
       <c r="C94" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D94" s="41">
+      <c r="D94" s="40">
         <v>45949</v>
       </c>
-      <c r="E94" s="42">
+      <c r="E94" s="41">
         <v>0.0416666666666667</v>
       </c>
-      <c r="F94" s="42">
+      <c r="F94" s="41">
         <v>0.0625</v>
       </c>
       <c r="G94" s="6">
@@ -4684,13 +4661,13 @@
       <c r="C95" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D95" s="41">
+      <c r="D95" s="40">
         <v>45949</v>
       </c>
-      <c r="E95" s="42">
+      <c r="E95" s="41">
         <v>0.208333333333333</v>
       </c>
-      <c r="F95" s="42">
+      <c r="F95" s="41">
         <v>0.25</v>
       </c>
       <c r="G95" s="6">
@@ -4707,10 +4684,10 @@
       <c r="C96" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D96" s="41">
+      <c r="D96" s="40">
         <v>45950</v>
       </c>
-      <c r="E96" s="42">
+      <c r="E96" s="41">
         <v>0.125</v>
       </c>
       <c r="F96" s="6"/>
@@ -4728,13 +4705,13 @@
       <c r="C97" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D97" s="43">
+      <c r="D97" s="42">
         <v>45955</v>
       </c>
-      <c r="E97" s="44">
+      <c r="E97" s="43">
         <v>0.104166666666667</v>
       </c>
-      <c r="F97" s="44">
+      <c r="F97" s="43">
         <v>0.145833333333333</v>
       </c>
       <c r="G97" s="18">
@@ -4751,13 +4728,13 @@
       <c r="C98" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="D98" s="43">
+      <c r="D98" s="42">
         <v>45955</v>
       </c>
-      <c r="E98" s="44">
+      <c r="E98" s="43">
         <v>0.25</v>
       </c>
-      <c r="F98" s="44">
+      <c r="F98" s="43">
         <v>0.291666666666667</v>
       </c>
       <c r="G98" s="18">
@@ -4774,13 +4751,13 @@
       <c r="C99" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="D99" s="43">
+      <c r="D99" s="42">
         <v>45956</v>
       </c>
-      <c r="E99" s="44">
+      <c r="E99" s="43">
         <v>0.0625</v>
       </c>
-      <c r="F99" s="44">
+      <c r="F99" s="43">
         <v>0.104166666666667</v>
       </c>
       <c r="G99" s="18">
@@ -4797,13 +4774,13 @@
       <c r="C100" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D100" s="43">
+      <c r="D100" s="42">
         <v>45956</v>
       </c>
-      <c r="E100" s="44">
+      <c r="E100" s="43">
         <v>0.208333333333333</v>
       </c>
-      <c r="F100" s="44">
+      <c r="F100" s="43">
         <v>0.25</v>
       </c>
       <c r="G100" s="18">
@@ -4820,10 +4797,10 @@
       <c r="C101" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D101" s="43">
+      <c r="D101" s="42">
         <v>45957</v>
       </c>
-      <c r="E101" s="44">
+      <c r="E101" s="43">
         <v>0.166666666666667</v>
       </c>
       <c r="F101" s="18"/>
@@ -4841,13 +4818,13 @@
       <c r="C102" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D102" s="41">
+      <c r="D102" s="40">
         <v>45968</v>
       </c>
-      <c r="E102" s="42">
+      <c r="E102" s="41">
         <v>0.9375</v>
       </c>
-      <c r="F102" s="42">
+      <c r="F102" s="41">
         <v>0.979166666666667</v>
       </c>
       <c r="G102" s="6">
@@ -4864,13 +4841,13 @@
       <c r="C103" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="D103" s="41">
+      <c r="D103" s="40">
         <v>45969</v>
       </c>
-      <c r="E103" s="42">
+      <c r="E103" s="41">
         <v>0.104166666666667</v>
       </c>
-      <c r="F103" s="42">
+      <c r="F103" s="41">
         <v>0.134722222222222</v>
       </c>
       <c r="G103" s="6">
@@ -4887,13 +4864,13 @@
       <c r="C104" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D104" s="41">
+      <c r="D104" s="40">
         <v>45969</v>
       </c>
-      <c r="E104" s="42">
+      <c r="E104" s="41">
         <v>0.916666666666667</v>
       </c>
-      <c r="F104" s="42">
+      <c r="F104" s="41">
         <v>0.958333333333333</v>
       </c>
       <c r="G104" s="6">
@@ -4910,13 +4887,13 @@
       <c r="C105" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D105" s="41">
+      <c r="D105" s="40">
         <v>45970</v>
       </c>
-      <c r="E105" s="42">
+      <c r="E105" s="41">
         <v>0.0833333333333333</v>
       </c>
-      <c r="F105" s="42">
+      <c r="F105" s="41">
         <v>0.125</v>
       </c>
       <c r="G105" s="6">
@@ -4933,10 +4910,10 @@
       <c r="C106" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D106" s="41">
+      <c r="D106" s="40">
         <v>45971</v>
       </c>
-      <c r="E106" s="42">
+      <c r="E106" s="41">
         <v>0.0416666666666667</v>
       </c>
       <c r="F106" s="6"/>
@@ -4954,13 +4931,13 @@
       <c r="C107" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D107" s="43">
+      <c r="D107" s="42">
         <v>45982</v>
       </c>
-      <c r="E107" s="44">
+      <c r="E107" s="43">
         <v>0.354166666666667</v>
       </c>
-      <c r="F107" s="44">
+      <c r="F107" s="43">
         <v>0.395833333333333</v>
       </c>
       <c r="G107" s="18">
@@ -4977,13 +4954,13 @@
       <c r="C108" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="D108" s="43">
+      <c r="D108" s="42">
         <v>45982</v>
       </c>
-      <c r="E108" s="44">
+      <c r="E108" s="43">
         <v>0.5</v>
       </c>
-      <c r="F108" s="44">
+      <c r="F108" s="43">
         <v>0.541666666666667</v>
       </c>
       <c r="G108" s="18">
@@ -5000,13 +4977,13 @@
       <c r="C109" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="D109" s="43">
+      <c r="D109" s="42">
         <v>45983</v>
       </c>
-      <c r="E109" s="45">
+      <c r="E109" s="44">
         <v>0.354166666666667</v>
       </c>
-      <c r="F109" s="45">
+      <c r="F109" s="44">
         <v>0.395833333333333</v>
       </c>
       <c r="G109" s="18">
@@ -5023,13 +5000,13 @@
       <c r="C110" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D110" s="43">
+      <c r="D110" s="42">
         <v>45983</v>
       </c>
-      <c r="E110" s="45">
+      <c r="E110" s="44">
         <v>0.5</v>
       </c>
-      <c r="F110" s="45">
+      <c r="F110" s="44">
         <v>0.541666666666667</v>
       </c>
       <c r="G110" s="18">
@@ -5046,10 +5023,10 @@
       <c r="C111" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D111" s="43">
+      <c r="D111" s="42">
         <v>45984</v>
       </c>
-      <c r="E111" s="45">
+      <c r="E111" s="44">
         <v>0.5</v>
       </c>
       <c r="F111" s="18"/>
@@ -5067,13 +5044,13 @@
       <c r="C112" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D112" s="41">
+      <c r="D112" s="40">
         <v>45989</v>
       </c>
-      <c r="E112" s="46">
+      <c r="E112" s="45">
         <v>0.895833333333333</v>
       </c>
-      <c r="F112" s="46">
+      <c r="F112" s="45">
         <v>0.9375</v>
       </c>
       <c r="G112" s="6">
@@ -5090,13 +5067,13 @@
       <c r="C113" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="D113" s="41">
+      <c r="D113" s="40">
         <v>45990</v>
       </c>
-      <c r="E113" s="46">
+      <c r="E113" s="45">
         <v>0.0625</v>
       </c>
-      <c r="F113" s="46">
+      <c r="F113" s="45">
         <v>0.0930555555555556</v>
       </c>
       <c r="G113" s="6">
@@ -5113,13 +5090,13 @@
       <c r="C114" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D114" s="41">
+      <c r="D114" s="40">
         <v>45990</v>
       </c>
-      <c r="E114" s="46">
+      <c r="E114" s="45">
         <v>0.916666666666667</v>
       </c>
-      <c r="F114" s="46">
+      <c r="F114" s="45">
         <v>0.958333333333333</v>
       </c>
       <c r="G114" s="6">
@@ -5136,13 +5113,13 @@
       <c r="C115" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D115" s="41">
+      <c r="D115" s="40">
         <v>45991</v>
       </c>
-      <c r="E115" s="46">
+      <c r="E115" s="45">
         <v>0.0833333333333333</v>
       </c>
-      <c r="F115" s="46">
+      <c r="F115" s="45">
         <v>0.125</v>
       </c>
       <c r="G115" s="6">
@@ -5159,10 +5136,10 @@
       <c r="C116" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D116" s="41">
+      <c r="D116" s="40">
         <v>45992</v>
       </c>
-      <c r="E116" s="46">
+      <c r="E116" s="45">
         <v>0</v>
       </c>
       <c r="F116" s="6"/>
@@ -5180,13 +5157,13 @@
       <c r="C117" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D117" s="43">
+      <c r="D117" s="42">
         <v>45996</v>
       </c>
-      <c r="E117" s="45">
+      <c r="E117" s="44">
         <v>0.729166666666667</v>
       </c>
-      <c r="F117" s="45">
+      <c r="F117" s="44">
         <v>0.770833333333333</v>
       </c>
       <c r="G117" s="18">
@@ -5203,13 +5180,13 @@
       <c r="C118" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="D118" s="43">
+      <c r="D118" s="42">
         <v>45996</v>
       </c>
-      <c r="E118" s="45">
+      <c r="E118" s="44">
         <v>0.875</v>
       </c>
-      <c r="F118" s="45">
+      <c r="F118" s="44">
         <v>0.916666666666667</v>
       </c>
       <c r="G118" s="18">
@@ -5226,13 +5203,13 @@
       <c r="C119" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="D119" s="43">
+      <c r="D119" s="42">
         <v>45997</v>
       </c>
-      <c r="E119" s="45">
+      <c r="E119" s="44">
         <v>0.770833333333333</v>
       </c>
-      <c r="F119" s="45">
+      <c r="F119" s="44">
         <v>0.8125</v>
       </c>
       <c r="G119" s="18">
@@ -5249,13 +5226,13 @@
       <c r="C120" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D120" s="43">
+      <c r="D120" s="42">
         <v>45997</v>
       </c>
-      <c r="E120" s="45">
+      <c r="E120" s="44">
         <v>0.916666666666667</v>
       </c>
-      <c r="F120" s="45">
+      <c r="F120" s="44">
         <v>0.958333333333333</v>
       </c>
       <c r="G120" s="18">
@@ -5272,10 +5249,10 @@
       <c r="C121" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D121" s="43">
+      <c r="D121" s="42">
         <v>45998</v>
       </c>
-      <c r="E121" s="45">
+      <c r="E121" s="44">
         <v>0.875</v>
       </c>
       <c r="F121" s="18"/>
@@ -5293,13 +5270,13 @@
       <c r="C122" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D122" s="41">
+      <c r="D122" s="40">
         <v>46087</v>
       </c>
-      <c r="E122" s="42">
+      <c r="E122" s="41">
         <v>0.395833333333333</v>
       </c>
-      <c r="F122" s="42">
+      <c r="F122" s="41">
         <v>0.4375</v>
       </c>
       <c r="G122" s="6">
@@ -5316,13 +5293,13 @@
       <c r="C123" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D123" s="41">
+      <c r="D123" s="40">
         <v>46087</v>
       </c>
-      <c r="E123" s="42">
+      <c r="E123" s="41">
         <v>0.541666666666667</v>
       </c>
-      <c r="F123" s="42">
+      <c r="F123" s="41">
         <v>0.583333333333333</v>
       </c>
       <c r="G123" s="6">
@@ -5339,13 +5316,13 @@
       <c r="C124" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D124" s="41">
+      <c r="D124" s="40">
         <v>46088</v>
       </c>
-      <c r="E124" s="42">
+      <c r="E124" s="41">
         <v>0.395833333333333</v>
       </c>
-      <c r="F124" s="42">
+      <c r="F124" s="41">
         <v>0.4375</v>
       </c>
       <c r="G124" s="6">
@@ -5362,13 +5339,13 @@
       <c r="C125" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D125" s="41">
+      <c r="D125" s="40">
         <v>46088</v>
       </c>
-      <c r="E125" s="42">
+      <c r="E125" s="41">
         <v>0.541666666666667</v>
       </c>
-      <c r="F125" s="42">
+      <c r="F125" s="41">
         <v>0.583333333333333</v>
       </c>
       <c r="G125" s="6">
@@ -5385,13 +5362,13 @@
       <c r="C126" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D126" s="41">
+      <c r="D126" s="40">
         <v>46089</v>
       </c>
-      <c r="E126" s="42">
+      <c r="E126" s="41">
         <v>0.5</v>
       </c>
-      <c r="F126" s="42"/>
+      <c r="F126" s="41"/>
       <c r="G126" s="6">
         <v>1</v>
       </c>
@@ -5406,13 +5383,13 @@
       <c r="C127" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D127" s="43">
+      <c r="D127" s="42">
         <v>46094</v>
       </c>
-      <c r="E127" s="44">
+      <c r="E127" s="43">
         <v>0.479166666666667</v>
       </c>
-      <c r="F127" s="44">
+      <c r="F127" s="43">
         <v>0.520833333333333</v>
       </c>
       <c r="G127" s="18">
@@ -5429,13 +5406,13 @@
       <c r="C128" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="D128" s="43">
+      <c r="D128" s="42">
         <v>46094</v>
       </c>
-      <c r="E128" s="44">
+      <c r="E128" s="43">
         <v>0.645833333333333</v>
       </c>
-      <c r="F128" s="44">
+      <c r="F128" s="43">
         <v>0.676388888888889</v>
       </c>
       <c r="G128" s="18">
@@ -5452,13 +5429,13 @@
       <c r="C129" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="D129" s="43">
+      <c r="D129" s="42">
         <v>46095</v>
       </c>
-      <c r="E129" s="44">
+      <c r="E129" s="43">
         <v>0.458333333333333</v>
       </c>
-      <c r="F129" s="44">
+      <c r="F129" s="43">
         <v>0.5</v>
       </c>
       <c r="G129" s="18">
@@ -5475,13 +5452,13 @@
       <c r="C130" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D130" s="43">
+      <c r="D130" s="42">
         <v>46095</v>
       </c>
-      <c r="E130" s="44">
+      <c r="E130" s="43">
         <v>0.625</v>
       </c>
-      <c r="F130" s="44">
+      <c r="F130" s="43">
         <v>0.666666666666667</v>
       </c>
       <c r="G130" s="18">
@@ -5498,10 +5475,10 @@
       <c r="C131" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D131" s="43">
+      <c r="D131" s="42">
         <v>46096</v>
       </c>
-      <c r="E131" s="44">
+      <c r="E131" s="43">
         <v>0.625</v>
       </c>
       <c r="F131" s="18"/>
@@ -5519,13 +5496,13 @@
       <c r="C132" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D132" s="41">
+      <c r="D132" s="40">
         <v>46108</v>
       </c>
-      <c r="E132" s="42">
+      <c r="E132" s="41">
         <v>0.4375</v>
       </c>
-      <c r="F132" s="42">
+      <c r="F132" s="41">
         <v>0.479166666666667</v>
       </c>
       <c r="G132" s="6">
@@ -5542,13 +5519,13 @@
       <c r="C133" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D133" s="41">
+      <c r="D133" s="40">
         <v>46108</v>
       </c>
-      <c r="E133" s="42">
+      <c r="E133" s="41">
         <v>0.583333333333333</v>
       </c>
-      <c r="F133" s="42">
+      <c r="F133" s="41">
         <v>0.625</v>
       </c>
       <c r="G133" s="6">
@@ -5565,13 +5542,13 @@
       <c r="C134" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D134" s="41">
+      <c r="D134" s="40">
         <v>46109</v>
       </c>
-      <c r="E134" s="42">
+      <c r="E134" s="41">
         <v>0.4375</v>
       </c>
-      <c r="F134" s="42">
+      <c r="F134" s="41">
         <v>0.479166666666667</v>
       </c>
       <c r="G134" s="6">
@@ -5588,13 +5565,13 @@
       <c r="C135" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D135" s="41">
+      <c r="D135" s="40">
         <v>46109</v>
       </c>
-      <c r="E135" s="42">
+      <c r="E135" s="41">
         <v>0.583333333333333</v>
       </c>
-      <c r="F135" s="42">
+      <c r="F135" s="41">
         <v>0.625</v>
       </c>
       <c r="G135" s="6">
@@ -5611,10 +5588,10 @@
       <c r="C136" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D136" s="41">
+      <c r="D136" s="40">
         <v>46110</v>
       </c>
-      <c r="E136" s="42">
+      <c r="E136" s="41">
         <v>0.541666666666667</v>
       </c>
       <c r="F136" s="6"/>
@@ -5632,14 +5609,14 @@
       <c r="C137" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D137" s="43">
-        <v>46122</v>
-      </c>
-      <c r="E137" s="44">
-        <v>0.8125</v>
-      </c>
-      <c r="F137" s="44">
-        <v>0.854166666666667</v>
+      <c r="D137" s="42">
+        <v>46144</v>
+      </c>
+      <c r="E137" s="43">
+        <v>0.0208333333333333</v>
+      </c>
+      <c r="F137" s="43">
+        <v>0.0625</v>
       </c>
       <c r="G137" s="18">
         <v>0</v>
@@ -5653,19 +5630,19 @@
         <v>4</v>
       </c>
       <c r="C138" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="D138" s="43">
-        <v>46122</v>
-      </c>
-      <c r="E138" s="44">
-        <v>0.958333333333333</v>
-      </c>
-      <c r="F138" s="44">
-        <v>0</v>
+        <v>38</v>
+      </c>
+      <c r="D138" s="42">
+        <v>46144</v>
+      </c>
+      <c r="E138" s="43">
+        <v>0.1875</v>
+      </c>
+      <c r="F138" s="43">
+        <v>0.218055555555556</v>
       </c>
       <c r="G138" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -5676,19 +5653,19 @@
         <v>4</v>
       </c>
       <c r="C139" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="D139" s="43">
-        <v>46123</v>
-      </c>
-      <c r="E139" s="44">
-        <v>0.854166666666667</v>
-      </c>
-      <c r="F139" s="44">
-        <v>0.895833333333333</v>
+        <v>39</v>
+      </c>
+      <c r="D139" s="42">
+        <v>46145</v>
+      </c>
+      <c r="E139" s="43">
+        <v>0</v>
+      </c>
+      <c r="F139" s="43">
+        <v>0.0416666666666667</v>
       </c>
       <c r="G139" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -5701,14 +5678,14 @@
       <c r="C140" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D140" s="43">
-        <v>46123</v>
-      </c>
-      <c r="E140" s="44">
-        <v>0</v>
-      </c>
-      <c r="F140" s="44">
-        <v>0.0416666666666667</v>
+      <c r="D140" s="42">
+        <v>46145</v>
+      </c>
+      <c r="E140" s="43">
+        <v>0.166666666666667</v>
+      </c>
+      <c r="F140" s="43">
+        <v>0.208333333333333</v>
       </c>
       <c r="G140" s="18">
         <v>1</v>
@@ -5724,13 +5701,13 @@
       <c r="C141" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D141" s="43">
-        <v>46124</v>
-      </c>
-      <c r="E141" s="44">
-        <v>0.958333333333333</v>
-      </c>
-      <c r="F141" s="18"/>
+      <c r="D141" s="42">
+        <v>46146</v>
+      </c>
+      <c r="E141" s="43">
+        <v>0.166666666666667</v>
+      </c>
+      <c r="F141" s="43"/>
       <c r="G141" s="18">
         <v>1</v>
       </c>
@@ -5745,14 +5722,14 @@
       <c r="C142" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D142" s="41">
-        <v>46129</v>
-      </c>
-      <c r="E142" s="42">
-        <v>0.895833333333333</v>
-      </c>
-      <c r="F142" s="42">
-        <v>0.9375</v>
+      <c r="D142" s="40">
+        <v>46165</v>
+      </c>
+      <c r="E142" s="41">
+        <v>0.0208333333333333</v>
+      </c>
+      <c r="F142" s="41">
+        <v>0.0625</v>
       </c>
       <c r="G142" s="6">
         <v>0</v>
@@ -5766,19 +5743,19 @@
         <v>5</v>
       </c>
       <c r="C143" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="D143" s="41">
-        <v>46130</v>
-      </c>
-      <c r="E143" s="42">
-        <v>0.0416666666666667</v>
-      </c>
-      <c r="F143" s="42">
-        <v>0.0833333333333333</v>
+        <v>38</v>
+      </c>
+      <c r="D143" s="40">
+        <v>46165</v>
+      </c>
+      <c r="E143" s="41">
+        <v>0.1875</v>
+      </c>
+      <c r="F143" s="41">
+        <v>0.218055555555556</v>
       </c>
       <c r="G143" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -5789,19 +5766,19 @@
         <v>5</v>
       </c>
       <c r="C144" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D144" s="41">
-        <v>46130</v>
-      </c>
-      <c r="E144" s="42">
-        <v>0.895833333333333</v>
-      </c>
-      <c r="F144" s="42">
-        <v>0.9375</v>
+        <v>39</v>
+      </c>
+      <c r="D144" s="40">
+        <v>46166</v>
+      </c>
+      <c r="E144" s="41">
+        <v>0</v>
+      </c>
+      <c r="F144" s="41">
+        <v>0.0416666666666667</v>
       </c>
       <c r="G144" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -5814,14 +5791,14 @@
       <c r="C145" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D145" s="41">
-        <v>46131</v>
-      </c>
-      <c r="E145" s="42">
-        <v>0.0416666666666667</v>
-      </c>
-      <c r="F145" s="42">
-        <v>0.0833333333333333</v>
+      <c r="D145" s="40">
+        <v>46166</v>
+      </c>
+      <c r="E145" s="41">
+        <v>0.166666666666667</v>
+      </c>
+      <c r="F145" s="41">
+        <v>0.208333333333333</v>
       </c>
       <c r="G145" s="6">
         <v>1</v>
@@ -5837,11 +5814,11 @@
       <c r="C146" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D146" s="41">
-        <v>46132</v>
-      </c>
-      <c r="E146" s="42">
-        <v>0.0416666666666667</v>
+      <c r="D146" s="40">
+        <v>46167</v>
+      </c>
+      <c r="E146" s="41">
+        <v>0.166666666666667</v>
       </c>
       <c r="F146" s="6"/>
       <c r="G146" s="6">
@@ -5858,14 +5835,14 @@
       <c r="C147" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D147" s="43">
-        <v>46144</v>
-      </c>
-      <c r="E147" s="44">
-        <v>0.0208333333333333</v>
-      </c>
-      <c r="F147" s="44">
-        <v>0.0625</v>
+      <c r="D147" s="42">
+        <v>46178</v>
+      </c>
+      <c r="E147" s="43">
+        <v>0.8125</v>
+      </c>
+      <c r="F147" s="43">
+        <v>0.854166666666667</v>
       </c>
       <c r="G147" s="18">
         <v>0</v>
@@ -5879,19 +5856,19 @@
         <v>6</v>
       </c>
       <c r="C148" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="D148" s="43">
-        <v>46144</v>
-      </c>
-      <c r="E148" s="44">
-        <v>0.1875</v>
-      </c>
-      <c r="F148" s="44">
-        <v>0.218055555555556</v>
+        <v>34</v>
+      </c>
+      <c r="D148" s="42">
+        <v>46178</v>
+      </c>
+      <c r="E148" s="43">
+        <v>0.958333333333333</v>
+      </c>
+      <c r="F148" s="43">
+        <v>0</v>
       </c>
       <c r="G148" s="18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5902,19 +5879,19 @@
         <v>6</v>
       </c>
       <c r="C149" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="D149" s="43">
-        <v>46145</v>
-      </c>
-      <c r="E149" s="44">
-        <v>0</v>
-      </c>
-      <c r="F149" s="44">
-        <v>0.0416666666666667</v>
+        <v>35</v>
+      </c>
+      <c r="D149" s="42">
+        <v>46179</v>
+      </c>
+      <c r="E149" s="43">
+        <v>0.770833333333333</v>
+      </c>
+      <c r="F149" s="43">
+        <v>0.8125</v>
       </c>
       <c r="G149" s="18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5927,14 +5904,14 @@
       <c r="C150" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D150" s="43">
-        <v>46145</v>
-      </c>
-      <c r="E150" s="44">
-        <v>0.166666666666667</v>
-      </c>
-      <c r="F150" s="44">
-        <v>0.208333333333333</v>
+      <c r="D150" s="42">
+        <v>46179</v>
+      </c>
+      <c r="E150" s="43">
+        <v>0.916666666666667</v>
+      </c>
+      <c r="F150" s="43">
+        <v>0.958333333333333</v>
       </c>
       <c r="G150" s="18">
         <v>1</v>
@@ -5950,13 +5927,13 @@
       <c r="C151" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D151" s="43">
-        <v>46146</v>
-      </c>
-      <c r="E151" s="44">
-        <v>0.166666666666667</v>
-      </c>
-      <c r="F151" s="44"/>
+      <c r="D151" s="42">
+        <v>46180</v>
+      </c>
+      <c r="E151" s="43">
+        <v>0.875</v>
+      </c>
+      <c r="F151" s="18"/>
       <c r="G151" s="18">
         <v>1</v>
       </c>
@@ -5971,14 +5948,14 @@
       <c r="C152" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D152" s="41">
-        <v>46165</v>
-      </c>
-      <c r="E152" s="42">
-        <v>0.0208333333333333</v>
-      </c>
-      <c r="F152" s="42">
-        <v>0.0625</v>
+      <c r="D152" s="40">
+        <v>46185</v>
+      </c>
+      <c r="E152" s="41">
+        <v>0.8125</v>
+      </c>
+      <c r="F152" s="41">
+        <v>0.854166666666667</v>
       </c>
       <c r="G152" s="6">
         <v>0</v>
@@ -5992,19 +5969,19 @@
         <v>7</v>
       </c>
       <c r="C153" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="D153" s="41">
-        <v>46165</v>
-      </c>
-      <c r="E153" s="42">
-        <v>0.1875</v>
-      </c>
-      <c r="F153" s="42">
-        <v>0.218055555555556</v>
+        <v>34</v>
+      </c>
+      <c r="D153" s="40">
+        <v>46185</v>
+      </c>
+      <c r="E153" s="41">
+        <v>0.958333333333333</v>
+      </c>
+      <c r="F153" s="41">
+        <v>0</v>
       </c>
       <c r="G153" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -6015,19 +5992,19 @@
         <v>7</v>
       </c>
       <c r="C154" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D154" s="41">
-        <v>46166</v>
-      </c>
-      <c r="E154" s="42">
-        <v>0</v>
-      </c>
-      <c r="F154" s="42">
-        <v>0.0416666666666667</v>
+        <v>35</v>
+      </c>
+      <c r="D154" s="40">
+        <v>46186</v>
+      </c>
+      <c r="E154" s="41">
+        <v>0.770833333333333</v>
+      </c>
+      <c r="F154" s="41">
+        <v>0.8125</v>
       </c>
       <c r="G154" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -6040,14 +6017,14 @@
       <c r="C155" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D155" s="41">
-        <v>46166</v>
-      </c>
-      <c r="E155" s="42">
-        <v>0.166666666666667</v>
-      </c>
-      <c r="F155" s="42">
-        <v>0.208333333333333</v>
+      <c r="D155" s="40">
+        <v>46186</v>
+      </c>
+      <c r="E155" s="41">
+        <v>0.916666666666667</v>
+      </c>
+      <c r="F155" s="41">
+        <v>0.958333333333333</v>
       </c>
       <c r="G155" s="6">
         <v>1</v>
@@ -6063,11 +6040,11 @@
       <c r="C156" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D156" s="41">
-        <v>46167</v>
-      </c>
-      <c r="E156" s="42">
-        <v>0.166666666666667</v>
+      <c r="D156" s="40">
+        <v>46187</v>
+      </c>
+      <c r="E156" s="41">
+        <v>0.875</v>
       </c>
       <c r="F156" s="6"/>
       <c r="G156" s="6">
@@ -6084,13 +6061,13 @@
       <c r="C157" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D157" s="43">
-        <v>46178</v>
-      </c>
-      <c r="E157" s="44">
+      <c r="D157" s="42">
+        <v>46199</v>
+      </c>
+      <c r="E157" s="43">
         <v>0.8125</v>
       </c>
-      <c r="F157" s="44">
+      <c r="F157" s="43">
         <v>0.854166666666667</v>
       </c>
       <c r="G157" s="18">
@@ -6107,13 +6084,13 @@
       <c r="C158" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="D158" s="43">
-        <v>46178</v>
-      </c>
-      <c r="E158" s="44">
+      <c r="D158" s="42">
+        <v>46199</v>
+      </c>
+      <c r="E158" s="43">
         <v>0.958333333333333</v>
       </c>
-      <c r="F158" s="44">
+      <c r="F158" s="43">
         <v>0</v>
       </c>
       <c r="G158" s="18">
@@ -6130,13 +6107,13 @@
       <c r="C159" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="D159" s="43">
-        <v>46179</v>
-      </c>
-      <c r="E159" s="44">
+      <c r="D159" s="42">
+        <v>46200</v>
+      </c>
+      <c r="E159" s="43">
         <v>0.770833333333333</v>
       </c>
-      <c r="F159" s="44">
+      <c r="F159" s="43">
         <v>0.8125</v>
       </c>
       <c r="G159" s="18">
@@ -6153,13 +6130,13 @@
       <c r="C160" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D160" s="43">
-        <v>46179</v>
-      </c>
-      <c r="E160" s="44">
+      <c r="D160" s="42">
+        <v>46200</v>
+      </c>
+      <c r="E160" s="43">
         <v>0.916666666666667</v>
       </c>
-      <c r="F160" s="44">
+      <c r="F160" s="43">
         <v>0.958333333333333</v>
       </c>
       <c r="G160" s="18">
@@ -6176,10 +6153,10 @@
       <c r="C161" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D161" s="43">
-        <v>46180</v>
-      </c>
-      <c r="E161" s="44">
+      <c r="D161" s="42">
+        <v>46201</v>
+      </c>
+      <c r="E161" s="43">
         <v>0.875</v>
       </c>
       <c r="F161" s="18"/>
@@ -6197,13 +6174,13 @@
       <c r="C162" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D162" s="41">
-        <v>46185</v>
-      </c>
-      <c r="E162" s="42">
+      <c r="D162" s="40">
+        <v>46206</v>
+      </c>
+      <c r="E162" s="41">
         <v>0.8125</v>
       </c>
-      <c r="F162" s="42">
+      <c r="F162" s="41">
         <v>0.854166666666667</v>
       </c>
       <c r="G162" s="6">
@@ -6218,19 +6195,19 @@
         <v>9</v>
       </c>
       <c r="C163" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="D163" s="41">
-        <v>46185</v>
-      </c>
-      <c r="E163" s="42">
-        <v>0.958333333333333</v>
-      </c>
-      <c r="F163" s="42">
-        <v>0</v>
+        <v>38</v>
+      </c>
+      <c r="D163" s="40">
+        <v>46206</v>
+      </c>
+      <c r="E163" s="41">
+        <v>0.979166666666667</v>
+      </c>
+      <c r="F163" s="41">
+        <v>0.00972222222222222</v>
       </c>
       <c r="G163" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -6241,19 +6218,19 @@
         <v>9</v>
       </c>
       <c r="C164" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D164" s="41">
-        <v>46186</v>
-      </c>
-      <c r="E164" s="42">
-        <v>0.770833333333333</v>
-      </c>
-      <c r="F164" s="42">
-        <v>0.8125</v>
+        <v>39</v>
+      </c>
+      <c r="D164" s="40">
+        <v>46207</v>
+      </c>
+      <c r="E164" s="41">
+        <v>0.791666666666667</v>
+      </c>
+      <c r="F164" s="41">
+        <v>0.833333333333333</v>
       </c>
       <c r="G164" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -6266,14 +6243,14 @@
       <c r="C165" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D165" s="41">
-        <v>46186</v>
-      </c>
-      <c r="E165" s="42">
-        <v>0.916666666666667</v>
-      </c>
-      <c r="F165" s="42">
+      <c r="D165" s="40">
+        <v>46207</v>
+      </c>
+      <c r="E165" s="41">
         <v>0.958333333333333</v>
+      </c>
+      <c r="F165" s="41">
+        <v>0</v>
       </c>
       <c r="G165" s="6">
         <v>1</v>
@@ -6289,11 +6266,11 @@
       <c r="C166" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D166" s="41">
-        <v>46187</v>
-      </c>
-      <c r="E166" s="42">
-        <v>0.875</v>
+      <c r="D166" s="40">
+        <v>46208</v>
+      </c>
+      <c r="E166" s="41">
+        <v>0.916666666666667</v>
       </c>
       <c r="F166" s="6"/>
       <c r="G166" s="6">
@@ -6310,13 +6287,13 @@
       <c r="C167" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D167" s="43">
-        <v>46199</v>
-      </c>
-      <c r="E167" s="44">
+      <c r="D167" s="42">
+        <v>46220</v>
+      </c>
+      <c r="E167" s="43">
         <v>0.8125</v>
       </c>
-      <c r="F167" s="44">
+      <c r="F167" s="43">
         <v>0.854166666666667</v>
       </c>
       <c r="G167" s="18">
@@ -6333,13 +6310,13 @@
       <c r="C168" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="D168" s="43">
-        <v>46199</v>
-      </c>
-      <c r="E168" s="44">
+      <c r="D168" s="42">
+        <v>46220</v>
+      </c>
+      <c r="E168" s="43">
         <v>0.958333333333333</v>
       </c>
-      <c r="F168" s="44">
+      <c r="F168" s="43">
         <v>0</v>
       </c>
       <c r="G168" s="18">
@@ -6356,13 +6333,13 @@
       <c r="C169" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="D169" s="43">
-        <v>46200</v>
-      </c>
-      <c r="E169" s="44">
+      <c r="D169" s="42">
+        <v>46221</v>
+      </c>
+      <c r="E169" s="43">
         <v>0.770833333333333</v>
       </c>
-      <c r="F169" s="44">
+      <c r="F169" s="43">
         <v>0.8125</v>
       </c>
       <c r="G169" s="18">
@@ -6379,13 +6356,13 @@
       <c r="C170" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D170" s="43">
-        <v>46200</v>
-      </c>
-      <c r="E170" s="44">
+      <c r="D170" s="42">
+        <v>46221</v>
+      </c>
+      <c r="E170" s="43">
         <v>0.916666666666667</v>
       </c>
-      <c r="F170" s="44">
+      <c r="F170" s="43">
         <v>0.958333333333333</v>
       </c>
       <c r="G170" s="18">
@@ -6402,10 +6379,10 @@
       <c r="C171" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D171" s="43">
-        <v>46201</v>
-      </c>
-      <c r="E171" s="44">
+      <c r="D171" s="42">
+        <v>46222</v>
+      </c>
+      <c r="E171" s="43">
         <v>0.875</v>
       </c>
       <c r="F171" s="18"/>
@@ -6423,13 +6400,13 @@
       <c r="C172" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D172" s="41">
-        <v>46206</v>
-      </c>
-      <c r="E172" s="42">
+      <c r="D172" s="40">
+        <v>46227</v>
+      </c>
+      <c r="E172" s="41">
         <v>0.8125</v>
       </c>
-      <c r="F172" s="42">
+      <c r="F172" s="41">
         <v>0.854166666666667</v>
       </c>
       <c r="G172" s="6">
@@ -6444,19 +6421,19 @@
         <v>11</v>
       </c>
       <c r="C173" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="D173" s="41">
-        <v>46206</v>
-      </c>
-      <c r="E173" s="42">
-        <v>0.979166666666667</v>
-      </c>
-      <c r="F173" s="42">
-        <v>0.00972222222222222</v>
+        <v>34</v>
+      </c>
+      <c r="D173" s="40">
+        <v>46227</v>
+      </c>
+      <c r="E173" s="41">
+        <v>0.9375</v>
+      </c>
+      <c r="F173" s="41">
+        <v>0.968055555555556</v>
       </c>
       <c r="G173" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -6467,19 +6444,19 @@
         <v>11</v>
       </c>
       <c r="C174" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D174" s="41">
-        <v>46207</v>
-      </c>
-      <c r="E174" s="42">
+        <v>35</v>
+      </c>
+      <c r="D174" s="40">
+        <v>46228</v>
+      </c>
+      <c r="E174" s="41">
+        <v>0.75</v>
+      </c>
+      <c r="F174" s="41">
         <v>0.791666666666667</v>
       </c>
-      <c r="F174" s="42">
-        <v>0.833333333333333</v>
-      </c>
       <c r="G174" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -6492,14 +6469,14 @@
       <c r="C175" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D175" s="41">
-        <v>46207</v>
-      </c>
-      <c r="E175" s="42">
+      <c r="D175" s="40">
+        <v>46228</v>
+      </c>
+      <c r="E175" s="41">
+        <v>0.916666666666667</v>
+      </c>
+      <c r="F175" s="41">
         <v>0.958333333333333</v>
-      </c>
-      <c r="F175" s="42">
-        <v>0</v>
       </c>
       <c r="G175" s="6">
         <v>1</v>
@@ -6515,11 +6492,11 @@
       <c r="C176" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D176" s="41">
-        <v>46208</v>
-      </c>
-      <c r="E176" s="42">
-        <v>0.916666666666667</v>
+      <c r="D176" s="40">
+        <v>46229</v>
+      </c>
+      <c r="E176" s="41">
+        <v>0.875</v>
       </c>
       <c r="F176" s="6"/>
       <c r="G176" s="6">
@@ -6536,14 +6513,14 @@
       <c r="C177" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D177" s="43">
-        <v>46220</v>
-      </c>
-      <c r="E177" s="44">
+      <c r="D177" s="42">
+        <v>46255</v>
+      </c>
+      <c r="E177" s="43">
+        <v>0.770833333333333</v>
+      </c>
+      <c r="F177" s="43">
         <v>0.8125</v>
-      </c>
-      <c r="F177" s="44">
-        <v>0.854166666666667</v>
       </c>
       <c r="G177" s="18">
         <v>0</v>
@@ -6557,19 +6534,19 @@
         <v>12</v>
       </c>
       <c r="C178" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="D178" s="43">
-        <v>46220</v>
-      </c>
-      <c r="E178" s="44">
-        <v>0.958333333333333</v>
-      </c>
-      <c r="F178" s="44">
-        <v>0</v>
+        <v>38</v>
+      </c>
+      <c r="D178" s="42">
+        <v>46255</v>
+      </c>
+      <c r="E178" s="43">
+        <v>0.9375</v>
+      </c>
+      <c r="F178" s="43">
+        <v>0.979166666666667</v>
       </c>
       <c r="G178" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -6580,19 +6557,19 @@
         <v>12</v>
       </c>
       <c r="C179" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="D179" s="43">
-        <v>46221</v>
-      </c>
-      <c r="E179" s="44">
-        <v>0.770833333333333</v>
-      </c>
-      <c r="F179" s="44">
-        <v>0.8125</v>
+        <v>39</v>
+      </c>
+      <c r="D179" s="42">
+        <v>46256</v>
+      </c>
+      <c r="E179" s="43">
+        <v>0.75</v>
+      </c>
+      <c r="F179" s="43">
+        <v>0.791666666666667</v>
       </c>
       <c r="G179" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -6605,13 +6582,13 @@
       <c r="C180" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D180" s="43">
-        <v>46221</v>
-      </c>
-      <c r="E180" s="44">
+      <c r="D180" s="42">
+        <v>46256</v>
+      </c>
+      <c r="E180" s="43">
         <v>0.916666666666667</v>
       </c>
-      <c r="F180" s="44">
+      <c r="F180" s="43">
         <v>0.958333333333333</v>
       </c>
       <c r="G180" s="18">
@@ -6628,10 +6605,10 @@
       <c r="C181" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D181" s="43">
-        <v>46222</v>
-      </c>
-      <c r="E181" s="44">
+      <c r="D181" s="42">
+        <v>46257</v>
+      </c>
+      <c r="E181" s="43">
         <v>0.875</v>
       </c>
       <c r="F181" s="18"/>
@@ -6649,14 +6626,14 @@
       <c r="C182" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D182" s="41">
-        <v>46227</v>
-      </c>
-      <c r="E182" s="42">
+      <c r="D182" s="40">
+        <v>46269</v>
+      </c>
+      <c r="E182" s="41">
+        <v>0.770833333333333</v>
+      </c>
+      <c r="F182" s="41">
         <v>0.8125</v>
-      </c>
-      <c r="F182" s="42">
-        <v>0.854166666666667</v>
       </c>
       <c r="G182" s="6">
         <v>0</v>
@@ -6672,14 +6649,14 @@
       <c r="C183" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D183" s="41">
-        <v>46227</v>
-      </c>
-      <c r="E183" s="42">
-        <v>0.9375</v>
-      </c>
-      <c r="F183" s="42">
-        <v>0.968055555555556</v>
+      <c r="D183" s="40">
+        <v>46269</v>
+      </c>
+      <c r="E183" s="41">
+        <v>0.916666666666667</v>
+      </c>
+      <c r="F183" s="41">
+        <v>0.958333333333333</v>
       </c>
       <c r="G183" s="6">
         <v>0</v>
@@ -6695,14 +6672,14 @@
       <c r="C184" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D184" s="41">
-        <v>46228</v>
-      </c>
-      <c r="E184" s="42">
-        <v>0.75</v>
-      </c>
-      <c r="F184" s="42">
-        <v>0.791666666666667</v>
+      <c r="D184" s="40">
+        <v>46270</v>
+      </c>
+      <c r="E184" s="41">
+        <v>0.770833333333333</v>
+      </c>
+      <c r="F184" s="41">
+        <v>0.8125</v>
       </c>
       <c r="G184" s="6">
         <v>0</v>
@@ -6718,13 +6695,13 @@
       <c r="C185" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D185" s="41">
-        <v>46228</v>
-      </c>
-      <c r="E185" s="42">
+      <c r="D185" s="40">
+        <v>46270</v>
+      </c>
+      <c r="E185" s="41">
         <v>0.916666666666667</v>
       </c>
-      <c r="F185" s="42">
+      <c r="F185" s="41">
         <v>0.958333333333333</v>
       </c>
       <c r="G185" s="6">
@@ -6741,13 +6718,13 @@
       <c r="C186" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D186" s="41">
-        <v>46229</v>
-      </c>
-      <c r="E186" s="42">
+      <c r="D186" s="40">
+        <v>46271</v>
+      </c>
+      <c r="E186" s="41">
         <v>0.875</v>
       </c>
-      <c r="F186" s="6"/>
+      <c r="F186" s="41"/>
       <c r="G186" s="6">
         <v>1</v>
       </c>
@@ -6762,14 +6739,14 @@
       <c r="C187" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D187" s="43">
-        <v>46255</v>
-      </c>
-      <c r="E187" s="44">
-        <v>0.770833333333333</v>
-      </c>
-      <c r="F187" s="44">
+      <c r="D187" s="42">
+        <v>46276</v>
+      </c>
+      <c r="E187" s="43">
         <v>0.8125</v>
+      </c>
+      <c r="F187" s="43">
+        <v>0.854166666666667</v>
       </c>
       <c r="G187" s="18">
         <v>0</v>
@@ -6783,19 +6760,19 @@
         <v>14</v>
       </c>
       <c r="C188" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="D188" s="43">
-        <v>46255</v>
-      </c>
-      <c r="E188" s="44">
-        <v>0.9375</v>
-      </c>
-      <c r="F188" s="44">
-        <v>0.979166666666667</v>
+        <v>34</v>
+      </c>
+      <c r="D188" s="42">
+        <v>46276</v>
+      </c>
+      <c r="E188" s="43">
+        <v>0.958333333333333</v>
+      </c>
+      <c r="F188" s="43">
+        <v>0</v>
       </c>
       <c r="G188" s="18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -6806,19 +6783,19 @@
         <v>14</v>
       </c>
       <c r="C189" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="D189" s="43">
-        <v>46256</v>
-      </c>
-      <c r="E189" s="44">
-        <v>0.75</v>
-      </c>
-      <c r="F189" s="44">
-        <v>0.791666666666667</v>
+        <v>35</v>
+      </c>
+      <c r="D189" s="42">
+        <v>46277</v>
+      </c>
+      <c r="E189" s="43">
+        <v>0.770833333333333</v>
+      </c>
+      <c r="F189" s="43">
+        <v>0.8125</v>
       </c>
       <c r="G189" s="18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -6831,13 +6808,13 @@
       <c r="C190" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D190" s="43">
-        <v>46256</v>
-      </c>
-      <c r="E190" s="44">
+      <c r="D190" s="42">
+        <v>46277</v>
+      </c>
+      <c r="E190" s="43">
         <v>0.916666666666667</v>
       </c>
-      <c r="F190" s="44">
+      <c r="F190" s="43">
         <v>0.958333333333333</v>
       </c>
       <c r="G190" s="18">
@@ -6854,10 +6831,10 @@
       <c r="C191" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D191" s="43">
-        <v>46257</v>
-      </c>
-      <c r="E191" s="44">
+      <c r="D191" s="42">
+        <v>46278</v>
+      </c>
+      <c r="E191" s="43">
         <v>0.875</v>
       </c>
       <c r="F191" s="18"/>
@@ -6875,14 +6852,14 @@
       <c r="C192" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D192" s="41">
-        <v>46269</v>
-      </c>
-      <c r="E192" s="42">
-        <v>0.770833333333333</v>
-      </c>
-      <c r="F192" s="42">
-        <v>0.8125</v>
+      <c r="D192" s="40">
+        <v>46289</v>
+      </c>
+      <c r="E192" s="41">
+        <v>0.6875</v>
+      </c>
+      <c r="F192" s="41">
+        <v>0.729166666666667</v>
       </c>
       <c r="G192" s="6">
         <v>0</v>
@@ -6898,14 +6875,14 @@
       <c r="C193" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D193" s="41">
-        <v>46269</v>
-      </c>
-      <c r="E193" s="42">
-        <v>0.916666666666667</v>
-      </c>
-      <c r="F193" s="42">
-        <v>0.958333333333333</v>
+      <c r="D193" s="40">
+        <v>46289</v>
+      </c>
+      <c r="E193" s="41">
+        <v>0.833333333333333</v>
+      </c>
+      <c r="F193" s="41">
+        <v>0.875</v>
       </c>
       <c r="G193" s="6">
         <v>0</v>
@@ -6921,14 +6898,14 @@
       <c r="C194" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D194" s="41">
-        <v>46270</v>
-      </c>
-      <c r="E194" s="42">
-        <v>0.770833333333333</v>
-      </c>
-      <c r="F194" s="42">
-        <v>0.8125</v>
+      <c r="D194" s="40">
+        <v>46290</v>
+      </c>
+      <c r="E194" s="41">
+        <v>0.6875</v>
+      </c>
+      <c r="F194" s="41">
+        <v>0.729166666666667</v>
       </c>
       <c r="G194" s="6">
         <v>0</v>
@@ -6944,14 +6921,14 @@
       <c r="C195" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D195" s="41">
-        <v>46270</v>
-      </c>
-      <c r="E195" s="42">
-        <v>0.916666666666667</v>
-      </c>
-      <c r="F195" s="42">
-        <v>0.958333333333333</v>
+      <c r="D195" s="40">
+        <v>46290</v>
+      </c>
+      <c r="E195" s="41">
+        <v>0.833333333333333</v>
+      </c>
+      <c r="F195" s="41">
+        <v>0.875</v>
       </c>
       <c r="G195" s="6">
         <v>1</v>
@@ -6967,13 +6944,13 @@
       <c r="C196" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D196" s="41">
-        <v>46271</v>
-      </c>
-      <c r="E196" s="42">
-        <v>0.875</v>
-      </c>
-      <c r="F196" s="42"/>
+      <c r="D196" s="40">
+        <v>46291</v>
+      </c>
+      <c r="E196" s="41">
+        <v>0.791666666666667</v>
+      </c>
+      <c r="F196" s="6"/>
       <c r="G196" s="6">
         <v>1</v>
       </c>
@@ -6988,14 +6965,14 @@
       <c r="C197" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D197" s="43">
-        <v>46276</v>
-      </c>
-      <c r="E197" s="44">
-        <v>0.8125</v>
-      </c>
-      <c r="F197" s="44">
-        <v>0.854166666666667</v>
+      <c r="D197" s="42">
+        <v>46304</v>
+      </c>
+      <c r="E197" s="43">
+        <v>0.6875</v>
+      </c>
+      <c r="F197" s="43">
+        <v>0.729166666666667</v>
       </c>
       <c r="G197" s="18">
         <v>0</v>
@@ -7009,19 +6986,19 @@
         <v>16</v>
       </c>
       <c r="C198" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="D198" s="43">
-        <v>46276</v>
-      </c>
-      <c r="E198" s="44">
-        <v>0.958333333333333</v>
-      </c>
-      <c r="F198" s="44">
-        <v>0</v>
+        <v>38</v>
+      </c>
+      <c r="D198" s="42">
+        <v>46304</v>
+      </c>
+      <c r="E198" s="43">
+        <v>0.854166666666667</v>
+      </c>
+      <c r="F198" s="43">
+        <v>0.884722222222222</v>
       </c>
       <c r="G198" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -7032,19 +7009,19 @@
         <v>16</v>
       </c>
       <c r="C199" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="D199" s="43">
-        <v>46277</v>
-      </c>
-      <c r="E199" s="44">
-        <v>0.770833333333333</v>
-      </c>
-      <c r="F199" s="44">
-        <v>0.8125</v>
+        <v>39</v>
+      </c>
+      <c r="D199" s="42">
+        <v>46305</v>
+      </c>
+      <c r="E199" s="43">
+        <v>0.708333333333333</v>
+      </c>
+      <c r="F199" s="43">
+        <v>0.75</v>
       </c>
       <c r="G199" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -7057,14 +7034,14 @@
       <c r="C200" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D200" s="43">
-        <v>46277</v>
-      </c>
-      <c r="E200" s="44">
+      <c r="D200" s="42">
+        <v>46305</v>
+      </c>
+      <c r="E200" s="43">
+        <v>0.875</v>
+      </c>
+      <c r="F200" s="43">
         <v>0.916666666666667</v>
-      </c>
-      <c r="F200" s="44">
-        <v>0.958333333333333</v>
       </c>
       <c r="G200" s="18">
         <v>1</v>
@@ -7080,11 +7057,11 @@
       <c r="C201" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D201" s="43">
-        <v>46278</v>
-      </c>
-      <c r="E201" s="44">
-        <v>0.875</v>
+      <c r="D201" s="42">
+        <v>46306</v>
+      </c>
+      <c r="E201" s="43">
+        <v>0.833333333333333</v>
       </c>
       <c r="F201" s="18"/>
       <c r="G201" s="18">
@@ -7101,14 +7078,14 @@
       <c r="C202" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D202" s="41">
-        <v>46289</v>
-      </c>
-      <c r="E202" s="42">
-        <v>0.6875</v>
-      </c>
-      <c r="F202" s="42">
-        <v>0.729166666666667</v>
+      <c r="D202" s="40">
+        <v>46319</v>
+      </c>
+      <c r="E202" s="41">
+        <v>0.0625</v>
+      </c>
+      <c r="F202" s="41">
+        <v>0.104166666666667</v>
       </c>
       <c r="G202" s="6">
         <v>0</v>
@@ -7124,14 +7101,14 @@
       <c r="C203" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D203" s="41">
-        <v>46289</v>
-      </c>
-      <c r="E203" s="42">
-        <v>0.833333333333333</v>
-      </c>
-      <c r="F203" s="42">
-        <v>0.875</v>
+      <c r="D203" s="40">
+        <v>46319</v>
+      </c>
+      <c r="E203" s="41">
+        <v>0.208333333333333</v>
+      </c>
+      <c r="F203" s="41">
+        <v>0.25</v>
       </c>
       <c r="G203" s="6">
         <v>0</v>
@@ -7147,14 +7124,14 @@
       <c r="C204" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D204" s="41">
-        <v>46290</v>
-      </c>
-      <c r="E204" s="42">
-        <v>0.6875</v>
-      </c>
-      <c r="F204" s="42">
-        <v>0.729166666666667</v>
+      <c r="D204" s="40">
+        <v>46320</v>
+      </c>
+      <c r="E204" s="41">
+        <v>0.0625</v>
+      </c>
+      <c r="F204" s="41">
+        <v>0.104166666666667</v>
       </c>
       <c r="G204" s="6">
         <v>0</v>
@@ -7170,14 +7147,14 @@
       <c r="C205" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D205" s="41">
-        <v>46290</v>
-      </c>
-      <c r="E205" s="42">
-        <v>0.833333333333333</v>
-      </c>
-      <c r="F205" s="42">
-        <v>0.875</v>
+      <c r="D205" s="40">
+        <v>46320</v>
+      </c>
+      <c r="E205" s="41">
+        <v>0.208333333333333</v>
+      </c>
+      <c r="F205" s="41">
+        <v>0.25</v>
       </c>
       <c r="G205" s="6">
         <v>1</v>
@@ -7193,11 +7170,11 @@
       <c r="C206" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D206" s="41">
-        <v>46291</v>
-      </c>
-      <c r="E206" s="42">
-        <v>0.791666666666667</v>
+      <c r="D206" s="40">
+        <v>46321</v>
+      </c>
+      <c r="E206" s="41">
+        <v>0.166666666666667</v>
       </c>
       <c r="F206" s="6"/>
       <c r="G206" s="6">
@@ -7214,14 +7191,14 @@
       <c r="C207" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D207" s="43">
-        <v>46304</v>
-      </c>
-      <c r="E207" s="44">
-        <v>0.6875</v>
-      </c>
-      <c r="F207" s="44">
-        <v>0.729166666666667</v>
+      <c r="D207" s="42">
+        <v>46326</v>
+      </c>
+      <c r="E207" s="43">
+        <v>0.104166666666667</v>
+      </c>
+      <c r="F207" s="43">
+        <v>0.145833333333333</v>
       </c>
       <c r="G207" s="18">
         <v>0</v>
@@ -7235,19 +7212,19 @@
         <v>18</v>
       </c>
       <c r="C208" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="D208" s="43">
-        <v>46304</v>
-      </c>
-      <c r="E208" s="44">
-        <v>0.854166666666667</v>
-      </c>
-      <c r="F208" s="44">
-        <v>0.884722222222222</v>
+        <v>34</v>
+      </c>
+      <c r="D208" s="42">
+        <v>46326</v>
+      </c>
+      <c r="E208" s="43">
+        <v>0.25</v>
+      </c>
+      <c r="F208" s="43">
+        <v>0.291666666666667</v>
       </c>
       <c r="G208" s="18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -7258,19 +7235,19 @@
         <v>18</v>
       </c>
       <c r="C209" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="D209" s="43">
-        <v>46305</v>
-      </c>
-      <c r="E209" s="44">
-        <v>0.708333333333333</v>
-      </c>
-      <c r="F209" s="44">
-        <v>0.75</v>
+        <v>35</v>
+      </c>
+      <c r="D209" s="42">
+        <v>46327</v>
+      </c>
+      <c r="E209" s="43">
+        <v>0.0625</v>
+      </c>
+      <c r="F209" s="43">
+        <v>0.104166666666667</v>
       </c>
       <c r="G209" s="18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -7283,14 +7260,14 @@
       <c r="C210" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D210" s="43">
-        <v>46305</v>
-      </c>
-      <c r="E210" s="44">
-        <v>0.875</v>
-      </c>
-      <c r="F210" s="44">
-        <v>0.916666666666667</v>
+      <c r="D210" s="42">
+        <v>46327</v>
+      </c>
+      <c r="E210" s="43">
+        <v>0.208333333333333</v>
+      </c>
+      <c r="F210" s="43">
+        <v>0.25</v>
       </c>
       <c r="G210" s="18">
         <v>1</v>
@@ -7306,11 +7283,11 @@
       <c r="C211" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D211" s="43">
-        <v>46306</v>
-      </c>
-      <c r="E211" s="44">
-        <v>0.833333333333333</v>
+      <c r="D211" s="42">
+        <v>46328</v>
+      </c>
+      <c r="E211" s="43">
+        <v>0.166666666666667</v>
       </c>
       <c r="F211" s="18"/>
       <c r="G211" s="18">
@@ -7327,14 +7304,14 @@
       <c r="C212" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D212" s="41">
-        <v>46319</v>
-      </c>
-      <c r="E212" s="42">
-        <v>0.0625</v>
-      </c>
-      <c r="F212" s="42">
-        <v>0.104166666666667</v>
+      <c r="D212" s="40">
+        <v>46332</v>
+      </c>
+      <c r="E212" s="41">
+        <v>0.979166666666667</v>
+      </c>
+      <c r="F212" s="41">
+        <v>0.0208333333333333</v>
       </c>
       <c r="G212" s="6">
         <v>0</v>
@@ -7350,14 +7327,14 @@
       <c r="C213" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D213" s="41">
-        <v>46319</v>
-      </c>
-      <c r="E213" s="42">
-        <v>0.208333333333333</v>
-      </c>
-      <c r="F213" s="42">
-        <v>0.25</v>
+      <c r="D213" s="40">
+        <v>46333</v>
+      </c>
+      <c r="E213" s="41">
+        <v>0.125</v>
+      </c>
+      <c r="F213" s="41">
+        <v>0.166666666666667</v>
       </c>
       <c r="G213" s="6">
         <v>0</v>
@@ -7373,14 +7350,14 @@
       <c r="C214" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D214" s="41">
-        <v>46320</v>
-      </c>
-      <c r="E214" s="42">
-        <v>0.0625</v>
-      </c>
-      <c r="F214" s="42">
-        <v>0.104166666666667</v>
+      <c r="D214" s="40">
+        <v>46333</v>
+      </c>
+      <c r="E214" s="41">
+        <v>0.9375</v>
+      </c>
+      <c r="F214" s="41">
+        <v>0.979166666666667</v>
       </c>
       <c r="G214" s="6">
         <v>0</v>
@@ -7396,14 +7373,14 @@
       <c r="C215" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D215" s="41">
-        <v>46320</v>
-      </c>
-      <c r="E215" s="42">
-        <v>0.208333333333333</v>
-      </c>
-      <c r="F215" s="42">
-        <v>0.25</v>
+      <c r="D215" s="40">
+        <v>46334</v>
+      </c>
+      <c r="E215" s="41">
+        <v>0.0833333333333333</v>
+      </c>
+      <c r="F215" s="41">
+        <v>0.125</v>
       </c>
       <c r="G215" s="6">
         <v>1</v>
@@ -7419,11 +7396,11 @@
       <c r="C216" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D216" s="41">
-        <v>46321</v>
-      </c>
-      <c r="E216" s="42">
-        <v>0.166666666666667</v>
+      <c r="D216" s="40">
+        <v>46335</v>
+      </c>
+      <c r="E216" s="41">
+        <v>0.0416666666666667</v>
       </c>
       <c r="F216" s="6"/>
       <c r="G216" s="6">
@@ -7440,14 +7417,14 @@
       <c r="C217" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D217" s="43">
-        <v>46326</v>
-      </c>
-      <c r="E217" s="44">
-        <v>0.104166666666667</v>
-      </c>
-      <c r="F217" s="44">
-        <v>0.145833333333333</v>
+      <c r="D217" s="42">
+        <v>46346</v>
+      </c>
+      <c r="E217" s="43">
+        <v>0.354166666666667</v>
+      </c>
+      <c r="F217" s="43">
+        <v>0.395833333333333</v>
       </c>
       <c r="G217" s="18">
         <v>0</v>
@@ -7463,14 +7440,14 @@
       <c r="C218" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="D218" s="43">
-        <v>46326</v>
-      </c>
-      <c r="E218" s="44">
-        <v>0.25</v>
-      </c>
-      <c r="F218" s="44">
-        <v>0.291666666666667</v>
+      <c r="D218" s="42">
+        <v>46346</v>
+      </c>
+      <c r="E218" s="43">
+        <v>0.5</v>
+      </c>
+      <c r="F218" s="43">
+        <v>0.541666666666667</v>
       </c>
       <c r="G218" s="18">
         <v>0</v>
@@ -7486,14 +7463,14 @@
       <c r="C219" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="D219" s="43">
-        <v>46327</v>
+      <c r="D219" s="42">
+        <v>46347</v>
       </c>
       <c r="E219" s="44">
-        <v>0.0625</v>
+        <v>0.354166666666667</v>
       </c>
       <c r="F219" s="44">
-        <v>0.104166666666667</v>
+        <v>0.395833333333333</v>
       </c>
       <c r="G219" s="18">
         <v>0</v>
@@ -7509,14 +7486,14 @@
       <c r="C220" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D220" s="43">
-        <v>46327</v>
+      <c r="D220" s="42">
+        <v>46347</v>
       </c>
       <c r="E220" s="44">
-        <v>0.208333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="F220" s="44">
-        <v>0.25</v>
+        <v>0.541666666666667</v>
       </c>
       <c r="G220" s="18">
         <v>1</v>
@@ -7532,11 +7509,11 @@
       <c r="C221" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D221" s="43">
-        <v>46328</v>
+      <c r="D221" s="42">
+        <v>46348</v>
       </c>
       <c r="E221" s="44">
-        <v>0.166666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="F221" s="18"/>
       <c r="G221" s="18">
@@ -7553,14 +7530,14 @@
       <c r="C222" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D222" s="41">
-        <v>46332</v>
-      </c>
-      <c r="E222" s="42">
-        <v>0.979166666666667</v>
-      </c>
-      <c r="F222" s="42">
-        <v>0.0208333333333333</v>
+      <c r="D222" s="40">
+        <v>46353</v>
+      </c>
+      <c r="E222" s="45">
+        <v>0.895833333333333</v>
+      </c>
+      <c r="F222" s="45">
+        <v>0.9375</v>
       </c>
       <c r="G222" s="6">
         <v>0</v>
@@ -7576,14 +7553,14 @@
       <c r="C223" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D223" s="41">
-        <v>46333</v>
-      </c>
-      <c r="E223" s="42">
-        <v>0.125</v>
-      </c>
-      <c r="F223" s="42">
-        <v>0.166666666666667</v>
+      <c r="D223" s="40">
+        <v>46354</v>
+      </c>
+      <c r="E223" s="45">
+        <v>0.0416666666666667</v>
+      </c>
+      <c r="F223" s="45">
+        <v>0.0833333333333333</v>
       </c>
       <c r="G223" s="6">
         <v>0</v>
@@ -7599,13 +7576,13 @@
       <c r="C224" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D224" s="41">
-        <v>46333</v>
-      </c>
-      <c r="E224" s="42">
+      <c r="D224" s="40">
+        <v>46354</v>
+      </c>
+      <c r="E224" s="41">
         <v>0.9375</v>
       </c>
-      <c r="F224" s="42">
+      <c r="F224" s="41">
         <v>0.979166666666667</v>
       </c>
       <c r="G224" s="6">
@@ -7622,13 +7599,13 @@
       <c r="C225" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D225" s="41">
-        <v>46334</v>
-      </c>
-      <c r="E225" s="42">
+      <c r="D225" s="40">
+        <v>46355</v>
+      </c>
+      <c r="E225" s="41">
         <v>0.0833333333333333</v>
       </c>
-      <c r="F225" s="42">
+      <c r="F225" s="41">
         <v>0.125</v>
       </c>
       <c r="G225" s="6">
@@ -7645,11 +7622,11 @@
       <c r="C226" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D226" s="41">
-        <v>46335</v>
-      </c>
-      <c r="E226" s="42">
-        <v>0.0416666666666667</v>
+      <c r="D226" s="40">
+        <v>46356</v>
+      </c>
+      <c r="E226" s="41">
+        <v>0</v>
       </c>
       <c r="F226" s="6"/>
       <c r="G226" s="6">
@@ -7666,14 +7643,14 @@
       <c r="C227" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D227" s="43">
-        <v>46346</v>
+      <c r="D227" s="42">
+        <v>46360</v>
       </c>
       <c r="E227" s="44">
-        <v>0.354166666666667</v>
+        <v>0.729166666666667</v>
       </c>
       <c r="F227" s="44">
-        <v>0.395833333333333</v>
+        <v>0.770833333333333</v>
       </c>
       <c r="G227" s="18">
         <v>0</v>
@@ -7689,14 +7666,14 @@
       <c r="C228" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="D228" s="43">
-        <v>46346</v>
+      <c r="D228" s="42">
+        <v>46360</v>
       </c>
       <c r="E228" s="44">
-        <v>0.5</v>
+        <v>0.875</v>
       </c>
       <c r="F228" s="44">
-        <v>0.541666666666667</v>
+        <v>0.916666666666667</v>
       </c>
       <c r="G228" s="18">
         <v>0</v>
@@ -7712,14 +7689,14 @@
       <c r="C229" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="D229" s="43">
-        <v>46347</v>
-      </c>
-      <c r="E229" s="45">
-        <v>0.354166666666667</v>
-      </c>
-      <c r="F229" s="45">
-        <v>0.395833333333333</v>
+      <c r="D229" s="42">
+        <v>46361</v>
+      </c>
+      <c r="E229" s="44">
+        <v>0.770833333333333</v>
+      </c>
+      <c r="F229" s="44">
+        <v>0.8125</v>
       </c>
       <c r="G229" s="18">
         <v>0</v>
@@ -7735,14 +7712,14 @@
       <c r="C230" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D230" s="43">
-        <v>46347</v>
-      </c>
-      <c r="E230" s="45">
-        <v>0.5</v>
-      </c>
-      <c r="F230" s="45">
-        <v>0.541666666666667</v>
+      <c r="D230" s="42">
+        <v>46361</v>
+      </c>
+      <c r="E230" s="44">
+        <v>0.916666666666667</v>
+      </c>
+      <c r="F230" s="44">
+        <v>0.958333333333333</v>
       </c>
       <c r="G230" s="18">
         <v>1</v>
@@ -7758,240 +7735,14 @@
       <c r="C231" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D231" s="43">
-        <v>46348</v>
-      </c>
-      <c r="E231" s="45">
-        <v>0.5</v>
+      <c r="D231" s="42">
+        <v>46362</v>
+      </c>
+      <c r="E231" s="44">
+        <v>0.875</v>
       </c>
       <c r="F231" s="18"/>
       <c r="G231" s="18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="232" spans="1:7">
-      <c r="A232" s="6">
-        <v>2026</v>
-      </c>
-      <c r="B232" s="6">
-        <v>23</v>
-      </c>
-      <c r="C232" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D232" s="41">
-        <v>46353</v>
-      </c>
-      <c r="E232" s="46">
-        <v>0.895833333333333</v>
-      </c>
-      <c r="F232" s="46">
-        <v>0.9375</v>
-      </c>
-      <c r="G232" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="233" spans="1:7">
-      <c r="A233" s="6">
-        <v>2026</v>
-      </c>
-      <c r="B233" s="6">
-        <v>23</v>
-      </c>
-      <c r="C233" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="D233" s="41">
-        <v>46354</v>
-      </c>
-      <c r="E233" s="46">
-        <v>0.0416666666666667</v>
-      </c>
-      <c r="F233" s="46">
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="G233" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="234" spans="1:7">
-      <c r="A234" s="6">
-        <v>2026</v>
-      </c>
-      <c r="B234" s="6">
-        <v>23</v>
-      </c>
-      <c r="C234" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D234" s="41">
-        <v>46354</v>
-      </c>
-      <c r="E234" s="42">
-        <v>0.9375</v>
-      </c>
-      <c r="F234" s="42">
-        <v>0.979166666666667</v>
-      </c>
-      <c r="G234" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="235" spans="1:7">
-      <c r="A235" s="6">
-        <v>2026</v>
-      </c>
-      <c r="B235" s="6">
-        <v>23</v>
-      </c>
-      <c r="C235" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D235" s="41">
-        <v>46355</v>
-      </c>
-      <c r="E235" s="42">
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="F235" s="42">
-        <v>0.125</v>
-      </c>
-      <c r="G235" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="236" spans="1:7">
-      <c r="A236" s="6">
-        <v>2026</v>
-      </c>
-      <c r="B236" s="6">
-        <v>23</v>
-      </c>
-      <c r="C236" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D236" s="41">
-        <v>46356</v>
-      </c>
-      <c r="E236" s="42">
-        <v>0</v>
-      </c>
-      <c r="F236" s="6"/>
-      <c r="G236" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="237" spans="1:7">
-      <c r="A237" s="18">
-        <v>2026</v>
-      </c>
-      <c r="B237" s="18">
-        <v>24</v>
-      </c>
-      <c r="C237" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="D237" s="43">
-        <v>46360</v>
-      </c>
-      <c r="E237" s="45">
-        <v>0.729166666666667</v>
-      </c>
-      <c r="F237" s="45">
-        <v>0.770833333333333</v>
-      </c>
-      <c r="G237" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="238" spans="1:7">
-      <c r="A238" s="18">
-        <v>2026</v>
-      </c>
-      <c r="B238" s="18">
-        <v>24</v>
-      </c>
-      <c r="C238" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="D238" s="43">
-        <v>46360</v>
-      </c>
-      <c r="E238" s="45">
-        <v>0.875</v>
-      </c>
-      <c r="F238" s="45">
-        <v>0.916666666666667</v>
-      </c>
-      <c r="G238" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="239" spans="1:7">
-      <c r="A239" s="18">
-        <v>2026</v>
-      </c>
-      <c r="B239" s="18">
-        <v>24</v>
-      </c>
-      <c r="C239" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="D239" s="43">
-        <v>46361</v>
-      </c>
-      <c r="E239" s="45">
-        <v>0.770833333333333</v>
-      </c>
-      <c r="F239" s="45">
-        <v>0.8125</v>
-      </c>
-      <c r="G239" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="240" spans="1:7">
-      <c r="A240" s="18">
-        <v>2026</v>
-      </c>
-      <c r="B240" s="18">
-        <v>24</v>
-      </c>
-      <c r="C240" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="D240" s="43">
-        <v>46361</v>
-      </c>
-      <c r="E240" s="45">
-        <v>0.916666666666667</v>
-      </c>
-      <c r="F240" s="45">
-        <v>0.958333333333333</v>
-      </c>
-      <c r="G240" s="18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="241" spans="1:7">
-      <c r="A241" s="18">
-        <v>2026</v>
-      </c>
-      <c r="B241" s="18">
-        <v>24</v>
-      </c>
-      <c r="C241" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="D241" s="43">
-        <v>46362</v>
-      </c>
-      <c r="E241" s="45">
-        <v>0.875</v>
-      </c>
-      <c r="F241" s="18"/>
-      <c r="G241" s="18">
         <v>1</v>
       </c>
     </row>
@@ -8004,7 +7755,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R1333"/>
+  <dimension ref="A1:R1377"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="5.57142857142857" customWidth="1"/>
@@ -41251,7 +41002,7 @@
       <c r="G1268" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="H1268" s="40">
+      <c r="H1268" s="6">
         <v>8</v>
       </c>
     </row>
@@ -41277,7 +41028,7 @@
       <c r="G1269" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="H1269" s="40">
+      <c r="H1269" s="6">
         <v>7</v>
       </c>
     </row>
@@ -41303,7 +41054,7 @@
       <c r="G1270" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="H1270" s="40">
+      <c r="H1270" s="6">
         <v>6</v>
       </c>
     </row>
@@ -41329,7 +41080,7 @@
       <c r="G1271" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="H1271" s="40">
+      <c r="H1271" s="6">
         <v>5</v>
       </c>
     </row>
@@ -41355,7 +41106,7 @@
       <c r="G1272" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="H1272" s="40">
+      <c r="H1272" s="6">
         <v>4</v>
       </c>
     </row>
@@ -41381,7 +41132,7 @@
       <c r="G1273" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="H1273" s="40">
+      <c r="H1273" s="6">
         <v>3</v>
       </c>
     </row>
@@ -41407,7 +41158,7 @@
       <c r="G1274" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="H1274" s="40">
+      <c r="H1274" s="6">
         <v>2</v>
       </c>
     </row>
@@ -41433,7 +41184,7 @@
       <c r="G1275" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="H1275" s="40">
+      <c r="H1275" s="6">
         <v>1</v>
       </c>
     </row>
@@ -41459,7 +41210,7 @@
       <c r="G1276" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="H1276" s="40">
+      <c r="H1276" s="6">
         <v>0</v>
       </c>
     </row>
@@ -41485,7 +41236,7 @@
       <c r="G1277" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="H1277" s="40">
+      <c r="H1277" s="6">
         <v>0</v>
       </c>
     </row>
@@ -41511,7 +41262,7 @@
       <c r="G1278" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="H1278" s="40">
+      <c r="H1278" s="6">
         <v>0</v>
       </c>
     </row>
@@ -41537,7 +41288,7 @@
       <c r="G1279" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="H1279" s="40">
+      <c r="H1279" s="6">
         <v>0</v>
       </c>
     </row>
@@ -41563,7 +41314,7 @@
       <c r="G1280" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="H1280" s="40">
+      <c r="H1280" s="6">
         <v>0</v>
       </c>
     </row>
@@ -41589,7 +41340,7 @@
       <c r="G1281" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="H1281" s="40">
+      <c r="H1281" s="6">
         <v>0</v>
       </c>
     </row>
@@ -41615,7 +41366,7 @@
       <c r="G1282" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="H1282" s="40">
+      <c r="H1282" s="6">
         <v>0</v>
       </c>
     </row>
@@ -41641,7 +41392,7 @@
       <c r="G1283" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="H1283" s="40">
+      <c r="H1283" s="6">
         <v>0</v>
       </c>
     </row>
@@ -41667,7 +41418,7 @@
       <c r="G1284" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="H1284" s="40">
+      <c r="H1284" s="6">
         <v>0</v>
       </c>
     </row>
@@ -41693,7 +41444,7 @@
       <c r="G1285" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="H1285" s="40">
+      <c r="H1285" s="6">
         <v>0</v>
       </c>
     </row>
@@ -41719,7 +41470,7 @@
       <c r="G1286" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="H1286" s="40">
+      <c r="H1286" s="6">
         <v>0</v>
       </c>
     </row>
@@ -41745,7 +41496,7 @@
       <c r="G1287" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="H1287" s="40">
+      <c r="H1287" s="6">
         <v>0</v>
       </c>
     </row>
@@ -41771,7 +41522,7 @@
       <c r="G1288" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="H1288" s="40">
+      <c r="H1288" s="6">
         <v>0</v>
       </c>
     </row>
@@ -41797,7 +41548,7 @@
       <c r="G1289" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="H1289" s="40">
+      <c r="H1289" s="6">
         <v>0</v>
       </c>
     </row>
@@ -42729,8 +42480,8 @@
       <c r="C1327" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="D1327" s="6">
-        <v>16</v>
+      <c r="D1327" s="6" t="s">
+        <v>76</v>
       </c>
       <c r="E1327" s="8">
         <v>3</v>
@@ -42755,8 +42506,8 @@
       <c r="C1328" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="D1328" s="6">
-        <v>17</v>
+      <c r="D1328" s="6" t="s">
+        <v>76</v>
       </c>
       <c r="E1328" s="14">
         <v>14</v>
@@ -42781,8 +42532,8 @@
       <c r="C1329" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="D1329" s="6">
-        <v>18</v>
+      <c r="D1329" s="6" t="s">
+        <v>76</v>
       </c>
       <c r="E1329" s="14">
         <v>18</v>
@@ -42807,8 +42558,8 @@
       <c r="C1330" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="D1330" s="6">
-        <v>19</v>
+      <c r="D1330" s="6" t="s">
+        <v>74</v>
       </c>
       <c r="E1330" s="7">
         <v>1</v>
@@ -42833,8 +42584,8 @@
       <c r="C1331" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="D1331" s="6">
-        <v>20</v>
+      <c r="D1331" s="6" t="s">
+        <v>74</v>
       </c>
       <c r="E1331" s="7">
         <v>81</v>
@@ -42859,8 +42610,8 @@
       <c r="C1332" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="D1332" s="6">
-        <v>21</v>
+      <c r="D1332" s="6" t="s">
+        <v>74</v>
       </c>
       <c r="E1332" s="19">
         <v>5</v>
@@ -42885,8 +42636,8 @@
       <c r="C1333" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="D1333" s="6">
-        <v>22</v>
+      <c r="D1333" s="6" t="s">
+        <v>74</v>
       </c>
       <c r="E1333" s="12">
         <v>23</v>
@@ -42901,8 +42652,1108 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1334" spans="1:8">
+      <c r="A1334" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1334" s="18">
+        <v>3</v>
+      </c>
+      <c r="C1334" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1334" s="18">
+        <v>1</v>
+      </c>
+      <c r="E1334" s="9">
+        <v>12</v>
+      </c>
+      <c r="F1334" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1334" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1334" s="21"/>
+    </row>
+    <row r="1335" spans="1:8">
+      <c r="A1335" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1335" s="18">
+        <v>3</v>
+      </c>
+      <c r="C1335" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1335" s="18">
+        <v>2</v>
+      </c>
+      <c r="E1335" s="9">
+        <v>63</v>
+      </c>
+      <c r="F1335" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1335" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1335" s="21"/>
+    </row>
+    <row r="1336" spans="1:8">
+      <c r="A1336" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1336" s="18">
+        <v>3</v>
+      </c>
+      <c r="C1336" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1336" s="18">
+        <v>3</v>
+      </c>
+      <c r="E1336" s="7">
+        <v>81</v>
+      </c>
+      <c r="F1336" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G1336" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="H1336" s="21"/>
+    </row>
+    <row r="1337" spans="1:8">
+      <c r="A1337" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1337" s="18">
+        <v>3</v>
+      </c>
+      <c r="C1337" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1337" s="18">
+        <v>4</v>
+      </c>
+      <c r="E1337" s="10">
+        <v>16</v>
+      </c>
+      <c r="F1337" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G1337" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1337" s="21"/>
+    </row>
+    <row r="1338" spans="1:8">
+      <c r="A1338" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1338" s="18">
+        <v>3</v>
+      </c>
+      <c r="C1338" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1338" s="18">
+        <v>5</v>
+      </c>
+      <c r="E1338" s="7">
+        <v>1</v>
+      </c>
+      <c r="F1338" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G1338" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="H1338" s="21"/>
+    </row>
+    <row r="1339" spans="1:8">
+      <c r="A1339" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1339" s="18">
+        <v>3</v>
+      </c>
+      <c r="C1339" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1339" s="18">
+        <v>6</v>
+      </c>
+      <c r="E1339" s="10">
+        <v>44</v>
+      </c>
+      <c r="F1339" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1339" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1339" s="21"/>
+    </row>
+    <row r="1340" spans="1:8">
+      <c r="A1340" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1340" s="18">
+        <v>3</v>
+      </c>
+      <c r="C1340" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1340" s="18">
+        <v>7</v>
+      </c>
+      <c r="E1340" s="13">
+        <v>10</v>
+      </c>
+      <c r="F1340" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1340" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="H1340" s="21"/>
+    </row>
+    <row r="1341" spans="1:8">
+      <c r="A1341" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1341" s="18">
+        <v>3</v>
+      </c>
+      <c r="C1341" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1341" s="18">
+        <v>8</v>
+      </c>
+      <c r="E1341" s="8">
+        <v>6</v>
+      </c>
+      <c r="F1341" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G1341" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H1341" s="21"/>
+    </row>
+    <row r="1342" spans="1:8">
+      <c r="A1342" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1342" s="18">
+        <v>3</v>
+      </c>
+      <c r="C1342" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1342" s="18">
+        <v>9</v>
+      </c>
+      <c r="E1342" s="19">
+        <v>5</v>
+      </c>
+      <c r="F1342" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1342" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="H1342" s="21"/>
+    </row>
+    <row r="1343" spans="1:8">
+      <c r="A1343" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1343" s="18">
+        <v>3</v>
+      </c>
+      <c r="C1343" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1343" s="18">
+        <v>10</v>
+      </c>
+      <c r="E1343" s="11">
+        <v>41</v>
+      </c>
+      <c r="F1343" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="G1343" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="H1343" s="21"/>
+    </row>
+    <row r="1344" spans="1:8">
+      <c r="A1344" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1344" s="18">
+        <v>3</v>
+      </c>
+      <c r="C1344" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1344" s="18">
+        <v>11</v>
+      </c>
+      <c r="E1344" s="8">
+        <v>3</v>
+      </c>
+      <c r="F1344" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1344" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H1344" s="21"/>
+    </row>
+    <row r="1345" spans="1:8">
+      <c r="A1345" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1345" s="18">
+        <v>3</v>
+      </c>
+      <c r="C1345" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1345" s="18">
+        <v>12</v>
+      </c>
+      <c r="E1345" s="17">
+        <v>31</v>
+      </c>
+      <c r="F1345" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="G1345" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="H1345" s="21"/>
+    </row>
+    <row r="1346" spans="1:8">
+      <c r="A1346" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1346" s="18">
+        <v>3</v>
+      </c>
+      <c r="C1346" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1346" s="18">
+        <v>13</v>
+      </c>
+      <c r="E1346" s="19">
+        <v>27</v>
+      </c>
+      <c r="F1346" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G1346" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="H1346" s="21"/>
+    </row>
+    <row r="1347" spans="1:8">
+      <c r="A1347" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1347" s="18">
+        <v>3</v>
+      </c>
+      <c r="C1347" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1347" s="18">
+        <v>14</v>
+      </c>
+      <c r="E1347" s="11">
+        <v>30</v>
+      </c>
+      <c r="F1347" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1347" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="H1347" s="21"/>
+    </row>
+    <row r="1348" spans="1:8">
+      <c r="A1348" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1348" s="18">
+        <v>3</v>
+      </c>
+      <c r="C1348" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1348" s="18">
+        <v>15</v>
+      </c>
+      <c r="E1348" s="13">
+        <v>43</v>
+      </c>
+      <c r="F1348" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="G1348" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="H1348" s="21"/>
+    </row>
+    <row r="1349" spans="1:8">
+      <c r="A1349" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1349" s="18">
+        <v>3</v>
+      </c>
+      <c r="C1349" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1349" s="18">
+        <v>16</v>
+      </c>
+      <c r="E1349" s="12">
+        <v>55</v>
+      </c>
+      <c r="F1349" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="G1349" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="H1349" s="21"/>
+    </row>
+    <row r="1350" spans="1:8">
+      <c r="A1350" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1350" s="18">
+        <v>3</v>
+      </c>
+      <c r="C1350" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1350" s="18">
+        <v>17</v>
+      </c>
+      <c r="E1350" s="12">
+        <v>23</v>
+      </c>
+      <c r="F1350" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1350" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="H1350" s="21"/>
+    </row>
+    <row r="1351" spans="1:8">
+      <c r="A1351" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1351" s="18">
+        <v>3</v>
+      </c>
+      <c r="C1351" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1351" s="18">
+        <v>18</v>
+      </c>
+      <c r="E1351" s="17">
+        <v>87</v>
+      </c>
+      <c r="F1351" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1351" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="H1351" s="21"/>
+    </row>
+    <row r="1352" spans="1:8">
+      <c r="A1352" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1352" s="18">
+        <v>3</v>
+      </c>
+      <c r="C1352" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1352" s="18">
+        <v>19</v>
+      </c>
+      <c r="E1352" s="20">
+        <v>11</v>
+      </c>
+      <c r="F1352" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="G1352" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="H1352" s="21"/>
+    </row>
+    <row r="1353" spans="1:8">
+      <c r="A1353" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1353" s="18">
+        <v>3</v>
+      </c>
+      <c r="C1353" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1353" s="18">
+        <v>20</v>
+      </c>
+      <c r="E1353" s="20">
+        <v>77</v>
+      </c>
+      <c r="F1353" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1353" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="H1353" s="21"/>
+    </row>
+    <row r="1354" spans="1:8">
+      <c r="A1354" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1354" s="18">
+        <v>3</v>
+      </c>
+      <c r="C1354" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1354" s="18">
+        <v>21</v>
+      </c>
+      <c r="E1354" s="14">
+        <v>14</v>
+      </c>
+      <c r="F1354" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="G1354" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="H1354" s="21"/>
+    </row>
+    <row r="1355" spans="1:8">
+      <c r="A1355" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1355" s="18">
+        <v>3</v>
+      </c>
+      <c r="C1355" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1355" s="18">
+        <v>22</v>
+      </c>
+      <c r="E1355" s="14">
+        <v>18</v>
+      </c>
+      <c r="F1355" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1355" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="H1355" s="21"/>
+    </row>
+    <row r="1356" spans="1:8">
+      <c r="A1356" s="21">
+        <v>2026</v>
+      </c>
+      <c r="B1356" s="21">
+        <v>3</v>
+      </c>
+      <c r="C1356" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1356" s="6">
+        <v>1</v>
+      </c>
+      <c r="E1356" s="9">
+        <v>12</v>
+      </c>
+      <c r="F1356" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1356" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1356" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1357" spans="1:8">
+      <c r="A1357" s="21">
+        <v>2026</v>
+      </c>
+      <c r="B1357" s="21">
+        <v>3</v>
+      </c>
+      <c r="C1357" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1357" s="6">
+        <v>2</v>
+      </c>
+      <c r="E1357" s="7">
+        <v>81</v>
+      </c>
+      <c r="F1357" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G1357" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="H1357" s="6">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1358" spans="1:8">
+      <c r="A1358" s="21">
+        <v>2026</v>
+      </c>
+      <c r="B1358" s="21">
+        <v>3</v>
+      </c>
+      <c r="C1358" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1358" s="6">
+        <v>3</v>
+      </c>
+      <c r="E1358" s="10">
+        <v>16</v>
+      </c>
+      <c r="F1358" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G1358" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1358" s="6">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1359" spans="1:8">
+      <c r="A1359" s="21">
+        <v>2026</v>
+      </c>
+      <c r="B1359" s="21">
+        <v>3</v>
+      </c>
+      <c r="C1359" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1359" s="6">
+        <v>4</v>
+      </c>
+      <c r="E1359" s="9">
+        <v>63</v>
+      </c>
+      <c r="F1359" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1359" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1359" s="6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1360" spans="1:8">
+      <c r="A1360" s="21">
+        <v>2026</v>
+      </c>
+      <c r="B1360" s="21">
+        <v>3</v>
+      </c>
+      <c r="C1360" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1360" s="6">
+        <v>5</v>
+      </c>
+      <c r="E1360" s="7">
+        <v>1</v>
+      </c>
+      <c r="F1360" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G1360" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="H1360" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1361" spans="1:8">
+      <c r="A1361" s="21">
+        <v>2026</v>
+      </c>
+      <c r="B1361" s="21">
+        <v>3</v>
+      </c>
+      <c r="C1361" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1361" s="6">
+        <v>6</v>
+      </c>
+      <c r="E1361" s="10">
+        <v>44</v>
+      </c>
+      <c r="F1361" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1361" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1361" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1362" spans="1:8">
+      <c r="A1362" s="21">
+        <v>2026</v>
+      </c>
+      <c r="B1362" s="21">
+        <v>3</v>
+      </c>
+      <c r="C1362" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1362" s="6">
+        <v>7</v>
+      </c>
+      <c r="E1362" s="13">
+        <v>10</v>
+      </c>
+      <c r="F1362" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1362" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="H1362" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1363" spans="1:8">
+      <c r="A1363" s="21">
+        <v>2026</v>
+      </c>
+      <c r="B1363" s="21">
+        <v>3</v>
+      </c>
+      <c r="C1363" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1363" s="6">
+        <v>8</v>
+      </c>
+      <c r="E1363" s="8">
+        <v>3</v>
+      </c>
+      <c r="F1363" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1363" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H1363" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1364" spans="1:8">
+      <c r="A1364" s="21">
+        <v>2026</v>
+      </c>
+      <c r="B1364" s="21">
+        <v>3</v>
+      </c>
+      <c r="C1364" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1364" s="6">
+        <v>9</v>
+      </c>
+      <c r="E1364" s="11">
+        <v>30</v>
+      </c>
+      <c r="F1364" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1364" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="H1364" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1365" spans="1:8">
+      <c r="A1365" s="21">
+        <v>2026</v>
+      </c>
+      <c r="B1365" s="21">
+        <v>3</v>
+      </c>
+      <c r="C1365" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1365" s="6">
+        <v>10</v>
+      </c>
+      <c r="E1365" s="17">
+        <v>31</v>
+      </c>
+      <c r="F1365" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="G1365" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="H1365" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1366" spans="1:8">
+      <c r="A1366" s="21">
+        <v>2026</v>
+      </c>
+      <c r="B1366" s="21">
+        <v>3</v>
+      </c>
+      <c r="C1366" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1366" s="6">
+        <v>11</v>
+      </c>
+      <c r="E1366" s="19">
+        <v>27</v>
+      </c>
+      <c r="F1366" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G1366" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="H1366" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1367" spans="1:8">
+      <c r="A1367" s="21">
+        <v>2026</v>
+      </c>
+      <c r="B1367" s="21">
+        <v>3</v>
+      </c>
+      <c r="C1367" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1367" s="6">
+        <v>12</v>
+      </c>
+      <c r="E1367" s="8">
+        <v>6</v>
+      </c>
+      <c r="F1367" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G1367" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H1367" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1368" spans="1:8">
+      <c r="A1368" s="21">
+        <v>2026</v>
+      </c>
+      <c r="B1368" s="21">
+        <v>3</v>
+      </c>
+      <c r="C1368" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1368" s="6">
+        <v>13</v>
+      </c>
+      <c r="E1368" s="19">
+        <v>5</v>
+      </c>
+      <c r="F1368" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1368" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="H1368" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1369" spans="1:8">
+      <c r="A1369" s="21">
+        <v>2026</v>
+      </c>
+      <c r="B1369" s="21">
+        <v>3</v>
+      </c>
+      <c r="C1369" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1369" s="6">
+        <v>14</v>
+      </c>
+      <c r="E1369" s="11">
+        <v>41</v>
+      </c>
+      <c r="F1369" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="G1369" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="H1369" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1370" spans="1:8">
+      <c r="A1370" s="21">
+        <v>2026</v>
+      </c>
+      <c r="B1370" s="21">
+        <v>3</v>
+      </c>
+      <c r="C1370" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1370" s="6">
+        <v>15</v>
+      </c>
+      <c r="E1370" s="12">
+        <v>55</v>
+      </c>
+      <c r="F1370" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="G1370" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="H1370" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1371" spans="1:8">
+      <c r="A1371" s="21">
+        <v>2026</v>
+      </c>
+      <c r="B1371" s="21">
+        <v>3</v>
+      </c>
+      <c r="C1371" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1371" s="6">
+        <v>16</v>
+      </c>
+      <c r="E1371" s="13">
+        <v>43</v>
+      </c>
+      <c r="F1371" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="G1371" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="H1371" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1372" spans="1:8">
+      <c r="A1372" s="21">
+        <v>2026</v>
+      </c>
+      <c r="B1372" s="21">
+        <v>3</v>
+      </c>
+      <c r="C1372" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1372" s="6">
+        <v>17</v>
+      </c>
+      <c r="E1372" s="20">
+        <v>11</v>
+      </c>
+      <c r="F1372" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="G1372" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="H1372" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1373" spans="1:8">
+      <c r="A1373" s="21">
+        <v>2026</v>
+      </c>
+      <c r="B1373" s="21">
+        <v>3</v>
+      </c>
+      <c r="C1373" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1373" s="6">
+        <v>18</v>
+      </c>
+      <c r="E1373" s="14">
+        <v>14</v>
+      </c>
+      <c r="F1373" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="G1373" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="H1373" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1374" spans="1:8">
+      <c r="A1374" s="21">
+        <v>2026</v>
+      </c>
+      <c r="B1374" s="21">
+        <v>3</v>
+      </c>
+      <c r="C1374" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1374" s="6">
+        <v>19</v>
+      </c>
+      <c r="E1374" s="20">
+        <v>77</v>
+      </c>
+      <c r="F1374" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1374" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="H1374" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1375" spans="1:8">
+      <c r="A1375" s="21">
+        <v>2026</v>
+      </c>
+      <c r="B1375" s="21">
+        <v>3</v>
+      </c>
+      <c r="C1375" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1375" s="6">
+        <v>20</v>
+      </c>
+      <c r="E1375" s="12">
+        <v>23</v>
+      </c>
+      <c r="F1375" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1375" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="H1375" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1376" spans="1:8">
+      <c r="A1376" s="21">
+        <v>2026</v>
+      </c>
+      <c r="B1376" s="21">
+        <v>3</v>
+      </c>
+      <c r="C1376" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1376" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1376" s="14">
+        <v>18</v>
+      </c>
+      <c r="F1376" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1376" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="H1376" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1377" spans="1:8">
+      <c r="A1377" s="21">
+        <v>2026</v>
+      </c>
+      <c r="B1377" s="21">
+        <v>3</v>
+      </c>
+      <c r="C1377" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1377" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1377" s="17">
+        <v>87</v>
+      </c>
+      <c r="F1377" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1377" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="H1377" s="6">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H1245" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H1333" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/docs/datas/f1.xlsx
+++ b/public/docs/datas/f1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25340" windowHeight="17260" activeTab="6"/>
+    <workbookView windowWidth="31560" windowHeight="17260" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="rounds" sheetId="7" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5034" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5100" uniqueCount="283">
   <si>
     <t>year</t>
   </si>
@@ -8456,7 +8456,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R1377"/>
+  <dimension ref="A1:R1399"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="5.57142857142857" customWidth="1"/>
@@ -44452,6 +44452,534 @@
       <c r="H1377" s="6">
         <v>0</v>
       </c>
+    </row>
+    <row r="1378" spans="1:8">
+      <c r="A1378" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1378" s="18">
+        <v>4</v>
+      </c>
+      <c r="C1378" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1378" s="18">
+        <v>1</v>
+      </c>
+      <c r="E1378" s="7">
+        <v>1</v>
+      </c>
+      <c r="F1378" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="G1378" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="H1378" s="24"/>
+    </row>
+    <row r="1379" spans="1:8">
+      <c r="A1379" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1379" s="18">
+        <v>4</v>
+      </c>
+      <c r="C1379" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1379" s="18">
+        <v>2</v>
+      </c>
+      <c r="E1379" s="9">
+        <v>12</v>
+      </c>
+      <c r="F1379" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="G1379" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="H1379" s="24"/>
+    </row>
+    <row r="1380" spans="1:8">
+      <c r="A1380" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1380" s="18">
+        <v>4</v>
+      </c>
+      <c r="C1380" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1380" s="18">
+        <v>3</v>
+      </c>
+      <c r="E1380" s="7">
+        <v>81</v>
+      </c>
+      <c r="F1380" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="G1380" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="H1380" s="24"/>
+    </row>
+    <row r="1381" spans="1:8">
+      <c r="A1381" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1381" s="18">
+        <v>4</v>
+      </c>
+      <c r="C1381" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1381" s="18">
+        <v>4</v>
+      </c>
+      <c r="E1381" s="10">
+        <v>16</v>
+      </c>
+      <c r="F1381" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="G1381" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="H1381" s="24"/>
+    </row>
+    <row r="1382" spans="1:8">
+      <c r="A1382" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1382" s="18">
+        <v>4</v>
+      </c>
+      <c r="C1382" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1382" s="18">
+        <v>5</v>
+      </c>
+      <c r="E1382" s="8">
+        <v>3</v>
+      </c>
+      <c r="F1382" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="G1382" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="H1382" s="24"/>
+    </row>
+    <row r="1383" spans="1:8">
+      <c r="A1383" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1383" s="18">
+        <v>4</v>
+      </c>
+      <c r="C1383" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1383" s="18">
+        <v>6</v>
+      </c>
+      <c r="E1383" s="9">
+        <v>63</v>
+      </c>
+      <c r="F1383" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="G1383" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="H1383" s="24"/>
+    </row>
+    <row r="1384" spans="1:8">
+      <c r="A1384" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1384" s="18">
+        <v>4</v>
+      </c>
+      <c r="C1384" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1384" s="18">
+        <v>7</v>
+      </c>
+      <c r="E1384" s="10">
+        <v>44</v>
+      </c>
+      <c r="F1384" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="G1384" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="H1384" s="24"/>
+    </row>
+    <row r="1385" spans="1:8">
+      <c r="A1385" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1385" s="18">
+        <v>4</v>
+      </c>
+      <c r="C1385" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1385" s="18">
+        <v>8</v>
+      </c>
+      <c r="E1385" s="13">
+        <v>43</v>
+      </c>
+      <c r="F1385" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="G1385" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="H1385" s="24"/>
+    </row>
+    <row r="1386" spans="1:8">
+      <c r="A1386" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1386" s="18">
+        <v>4</v>
+      </c>
+      <c r="C1386" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1386" s="18">
+        <v>9</v>
+      </c>
+      <c r="E1386" s="8">
+        <v>6</v>
+      </c>
+      <c r="F1386" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="G1386" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="H1386" s="24"/>
+    </row>
+    <row r="1387" spans="1:8">
+      <c r="A1387" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1387" s="18">
+        <v>4</v>
+      </c>
+      <c r="C1387" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1387" s="18">
+        <v>10</v>
+      </c>
+      <c r="E1387" s="13">
+        <v>10</v>
+      </c>
+      <c r="F1387" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="G1387" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="H1387" s="24"/>
+    </row>
+    <row r="1388" spans="1:8">
+      <c r="A1388" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1388" s="18">
+        <v>4</v>
+      </c>
+      <c r="C1388" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1388" s="18">
+        <v>11</v>
+      </c>
+      <c r="E1388" s="19">
+        <v>5</v>
+      </c>
+      <c r="F1388" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="G1388" s="19" t="s">
+        <v>201</v>
+      </c>
+      <c r="H1388" s="24"/>
+    </row>
+    <row r="1389" spans="1:8">
+      <c r="A1389" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1389" s="18">
+        <v>4</v>
+      </c>
+      <c r="C1389" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1389" s="18">
+        <v>12</v>
+      </c>
+      <c r="E1389" s="19">
+        <v>27</v>
+      </c>
+      <c r="F1389" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="G1389" s="19" t="s">
+        <v>201</v>
+      </c>
+      <c r="H1389" s="24"/>
+    </row>
+    <row r="1390" spans="1:8">
+      <c r="A1390" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1390" s="18">
+        <v>4</v>
+      </c>
+      <c r="C1390" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1390" s="18">
+        <v>13</v>
+      </c>
+      <c r="E1390" s="17">
+        <v>87</v>
+      </c>
+      <c r="F1390" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="G1390" s="17" t="s">
+        <v>199</v>
+      </c>
+      <c r="H1390" s="24"/>
+    </row>
+    <row r="1391" spans="1:8">
+      <c r="A1391" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1391" s="18">
+        <v>4</v>
+      </c>
+      <c r="C1391" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1391" s="18">
+        <v>14</v>
+      </c>
+      <c r="E1391" s="12">
+        <v>55</v>
+      </c>
+      <c r="F1391" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="G1391" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="H1391" s="24"/>
+    </row>
+    <row r="1392" spans="1:8">
+      <c r="A1392" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1392" s="18">
+        <v>4</v>
+      </c>
+      <c r="C1392" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1392" s="18">
+        <v>15</v>
+      </c>
+      <c r="E1392" s="11">
+        <v>41</v>
+      </c>
+      <c r="F1392" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="G1392" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="H1392" s="24"/>
+    </row>
+    <row r="1393" spans="1:8">
+      <c r="A1393" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1393" s="18">
+        <v>4</v>
+      </c>
+      <c r="C1393" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1393" s="18">
+        <v>16</v>
+      </c>
+      <c r="E1393" s="11">
+        <v>30</v>
+      </c>
+      <c r="F1393" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="G1393" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="H1393" s="24"/>
+    </row>
+    <row r="1394" spans="1:8">
+      <c r="A1394" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1394" s="18">
+        <v>4</v>
+      </c>
+      <c r="C1394" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1394" s="18">
+        <v>17</v>
+      </c>
+      <c r="E1394" s="17">
+        <v>31</v>
+      </c>
+      <c r="F1394" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="G1394" s="17" t="s">
+        <v>199</v>
+      </c>
+      <c r="H1394" s="24"/>
+    </row>
+    <row r="1395" spans="1:8">
+      <c r="A1395" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1395" s="18">
+        <v>4</v>
+      </c>
+      <c r="C1395" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1395" s="18">
+        <v>18</v>
+      </c>
+      <c r="E1395" s="20">
+        <v>11</v>
+      </c>
+      <c r="F1395" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="G1395" s="20" t="s">
+        <v>203</v>
+      </c>
+      <c r="H1395" s="24"/>
+    </row>
+    <row r="1396" spans="1:8">
+      <c r="A1396" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1396" s="18">
+        <v>4</v>
+      </c>
+      <c r="C1396" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1396" s="18">
+        <v>19</v>
+      </c>
+      <c r="E1396" s="12">
+        <v>23</v>
+      </c>
+      <c r="F1396" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1396" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="H1396" s="24"/>
+    </row>
+    <row r="1397" spans="1:8">
+      <c r="A1397" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1397" s="18">
+        <v>4</v>
+      </c>
+      <c r="C1397" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1397" s="18">
+        <v>20</v>
+      </c>
+      <c r="E1397" s="20">
+        <v>77</v>
+      </c>
+      <c r="F1397" s="20" t="s">
+        <v>204</v>
+      </c>
+      <c r="G1397" s="20" t="s">
+        <v>203</v>
+      </c>
+      <c r="H1397" s="24"/>
+    </row>
+    <row r="1398" spans="1:8">
+      <c r="A1398" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1398" s="18">
+        <v>4</v>
+      </c>
+      <c r="C1398" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1398" s="18">
+        <v>21</v>
+      </c>
+      <c r="E1398" s="14">
+        <v>14</v>
+      </c>
+      <c r="F1398" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="G1398" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="H1398" s="24"/>
+    </row>
+    <row r="1399" spans="1:8">
+      <c r="A1399" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1399" s="18">
+        <v>4</v>
+      </c>
+      <c r="C1399" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1399" s="18">
+        <v>22</v>
+      </c>
+      <c r="E1399" s="14">
+        <v>18</v>
+      </c>
+      <c r="F1399" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="G1399" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="H1399" s="24"/>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H1377" etc:filterBottomFollowUsedRange="0">

--- a/public/docs/datas/f1.xlsx
+++ b/public/docs/datas/f1.xlsx
@@ -16,7 +16,7 @@
     <sheet name="teams" sheetId="5" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">result!$A$1:$H$1377</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">result!$A$1:$H$1465</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5100" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5313" uniqueCount="282">
   <si>
     <t>year</t>
   </si>
@@ -630,9 +630,6 @@
   </si>
   <si>
     <t>Haas</t>
-  </si>
-  <si>
-    <t>DQ</t>
   </si>
   <si>
     <t>Haas F1 Team</t>
@@ -6406,7 +6403,7 @@
         <v>46146</v>
       </c>
       <c r="E141" s="43">
-        <v>0.166666666666667</v>
+        <v>0.0416666666666667</v>
       </c>
       <c r="F141" s="43"/>
       <c r="G141" s="18">
@@ -8456,7 +8453,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R1399"/>
+  <dimension ref="A1:R1465"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="5.57142857142857" customWidth="1"/>
@@ -9567,7 +9564,7 @@
         <v>148</v>
       </c>
       <c r="D41" s="28" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E41" s="28">
         <v>6</v>
@@ -9928,8 +9925,8 @@
       <c r="C56" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="D56" s="4">
-        <v>15</v>
+      <c r="D56" s="4" t="s">
+        <v>187</v>
       </c>
       <c r="E56" s="4">
         <v>6</v>
@@ -13200,8 +13197,8 @@
       <c r="C175" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="D175" s="4">
-        <v>14</v>
+      <c r="D175" s="4" t="s">
+        <v>187</v>
       </c>
       <c r="E175" s="4">
         <v>31</v>
@@ -14155,8 +14152,8 @@
       <c r="C211" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="D211" s="4">
-        <v>10</v>
+      <c r="D211" s="4" t="s">
+        <v>187</v>
       </c>
       <c r="E211" s="4">
         <v>4</v>
@@ -15992,7 +15989,7 @@
         <v>150</v>
       </c>
       <c r="D281" s="18" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E281" s="18">
         <v>16</v>
@@ -18610,8 +18607,8 @@
       <c r="C375" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="D375" s="6">
-        <v>14</v>
+      <c r="D375" s="6" t="s">
+        <v>187</v>
       </c>
       <c r="E375" s="6">
         <v>63</v>
@@ -20438,7 +20435,9 @@
       <c r="C441" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="D441" s="32"/>
+      <c r="D441" s="32" t="s">
+        <v>185</v>
+      </c>
       <c r="E441" s="32">
         <v>18</v>
       </c>
@@ -28953,7 +28952,7 @@
         <v>148</v>
       </c>
       <c r="D761" s="32" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E761" s="32">
         <v>27</v>
@@ -29350,8 +29349,8 @@
       <c r="C776" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="D776" s="6">
-        <v>15</v>
+      <c r="D776" s="6" t="s">
+        <v>187</v>
       </c>
       <c r="E776" s="6">
         <v>87</v>
@@ -29476,7 +29475,7 @@
         <v>147</v>
       </c>
       <c r="D781" s="6" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="E781" s="6">
         <v>31</v>
@@ -29994,7 +29993,7 @@
         <v>148</v>
       </c>
       <c r="D801" s="32" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E801" s="18">
         <v>81</v>
@@ -31413,7 +31412,7 @@
         <v>186</v>
       </c>
       <c r="G857" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H857" s="34"/>
     </row>
@@ -31485,7 +31484,7 @@
         <v>183</v>
       </c>
       <c r="G860" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H860" s="34"/>
     </row>
@@ -31898,7 +31897,7 @@
         <v>186</v>
       </c>
       <c r="G876" s="18" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H876" s="18">
         <v>0</v>
@@ -31924,7 +31923,7 @@
         <v>183</v>
       </c>
       <c r="G877" s="18" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H877" s="18">
         <v>0</v>
@@ -32236,7 +32235,7 @@
         <v>186</v>
       </c>
       <c r="G889" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H889" s="34"/>
       <c r="I889" s="31"/>
@@ -32463,7 +32462,7 @@
         <v>183</v>
       </c>
       <c r="G898" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H898" s="34"/>
     </row>
@@ -32767,7 +32766,7 @@
         <v>186</v>
       </c>
       <c r="G910" s="18" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H910" s="32">
         <v>2</v>
@@ -32923,7 +32922,7 @@
         <v>183</v>
       </c>
       <c r="G916" s="18" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H916" s="32">
         <v>0</v>
@@ -33295,7 +33294,7 @@
         <v>186</v>
       </c>
       <c r="G931" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H931" s="6"/>
     </row>
@@ -33343,7 +33342,7 @@
         <v>183</v>
       </c>
       <c r="G933" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H933" s="6"/>
     </row>
@@ -33637,7 +33636,7 @@
         <v>186</v>
       </c>
       <c r="G945" s="18" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H945" s="18">
         <v>12</v>
@@ -33767,7 +33766,7 @@
         <v>183</v>
       </c>
       <c r="G950" s="18" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H950" s="18">
         <v>2</v>
@@ -33965,8 +33964,8 @@
       <c r="C958" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="D958" s="18">
-        <v>17</v>
+      <c r="D958" s="18" t="s">
+        <v>187</v>
       </c>
       <c r="E958" s="18">
         <v>55</v>
@@ -34415,7 +34414,7 @@
         <v>186</v>
       </c>
       <c r="G976" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H976" s="6"/>
     </row>
@@ -34511,7 +34510,7 @@
         <v>183</v>
       </c>
       <c r="G980" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H980" s="6"/>
     </row>
@@ -34819,7 +34818,7 @@
         <v>183</v>
       </c>
       <c r="G992" s="18" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H992" s="18">
         <v>0</v>
@@ -34845,7 +34844,7 @@
         <v>186</v>
       </c>
       <c r="G993" s="18" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H993" s="18">
         <v>0</v>
@@ -35247,7 +35246,7 @@
         <v>186</v>
       </c>
       <c r="G1009" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H1009" s="6"/>
     </row>
@@ -35463,7 +35462,7 @@
         <v>183</v>
       </c>
       <c r="G1018" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H1018" s="6"/>
     </row>
@@ -35683,7 +35682,7 @@
         <v>186</v>
       </c>
       <c r="G1027" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H1027" s="6">
         <v>8</v>
@@ -35839,7 +35838,7 @@
         <v>183</v>
       </c>
       <c r="G1033" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H1033" s="6">
         <v>0</v>
@@ -36361,7 +36360,7 @@
         <v>183</v>
       </c>
       <c r="G1054" s="18" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H1054" s="18"/>
     </row>
@@ -36385,7 +36384,7 @@
         <v>186</v>
       </c>
       <c r="G1055" s="18" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H1055" s="18"/>
     </row>
@@ -36761,7 +36760,7 @@
         <v>183</v>
       </c>
       <c r="G1070" s="24" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H1070" s="24">
         <v>2</v>
@@ -36787,7 +36786,7 @@
         <v>186</v>
       </c>
       <c r="G1071" s="24" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H1071" s="24">
         <v>1</v>
@@ -36934,16 +36933,16 @@
         <v>148</v>
       </c>
       <c r="D1077" s="24" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E1077" s="24">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F1077" s="24" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="G1077" s="24" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="H1077" s="24">
         <v>0</v>
@@ -36960,16 +36959,16 @@
         <v>148</v>
       </c>
       <c r="D1078" s="24" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E1078" s="24">
-        <v>81</v>
+        <v>5</v>
       </c>
       <c r="F1078" s="24" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="G1078" s="24" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H1078" s="24">
         <v>0</v>
@@ -36989,13 +36988,13 @@
         <v>187</v>
       </c>
       <c r="E1079" s="24">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F1079" s="24" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="G1079" s="24" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H1079" s="24">
         <v>0</v>
@@ -37012,16 +37011,16 @@
         <v>148</v>
       </c>
       <c r="D1080" s="24" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E1080" s="24">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F1080" s="24" t="s">
-        <v>178</v>
+        <v>156</v>
       </c>
       <c r="G1080" s="24" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H1080" s="24">
         <v>0</v>
@@ -37038,16 +37037,16 @@
         <v>148</v>
       </c>
       <c r="D1081" s="24" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E1081" s="24">
-        <v>18</v>
+        <v>81</v>
       </c>
       <c r="F1081" s="24" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="G1081" s="24" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="H1081" s="24">
         <v>0</v>
@@ -37337,7 +37336,7 @@
         <v>186</v>
       </c>
       <c r="G1093" s="18" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H1093" s="18"/>
     </row>
@@ -37409,7 +37408,7 @@
         <v>183</v>
       </c>
       <c r="G1096" s="18" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H1096" s="18"/>
     </row>
@@ -37839,7 +37838,7 @@
         <v>186</v>
       </c>
       <c r="G1113" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H1113" s="6">
         <v>0</v>
@@ -37917,7 +37916,7 @@
         <v>183</v>
       </c>
       <c r="G1116" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H1116" s="6">
         <v>0</v>
@@ -38361,7 +38360,7 @@
         <v>186</v>
       </c>
       <c r="G1134" s="18" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H1134" s="18"/>
     </row>
@@ -38457,7 +38456,7 @@
         <v>183</v>
       </c>
       <c r="G1138" s="18" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H1138" s="18"/>
     </row>
@@ -38917,7 +38916,7 @@
         <v>183</v>
       </c>
       <c r="G1156" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H1156" s="6">
         <v>0</v>
@@ -39021,7 +39020,7 @@
         <v>186</v>
       </c>
       <c r="G1160" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H1160" s="6">
         <v>0</v>
@@ -39241,7 +39240,7 @@
         <v>183</v>
       </c>
       <c r="G1169" s="18" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H1169" s="18"/>
     </row>
@@ -39279,8 +39278,8 @@
       <c r="C1171" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="D1171" s="18">
-        <v>10</v>
+      <c r="D1171" s="18" t="s">
+        <v>187</v>
       </c>
       <c r="E1171" s="18">
         <v>22</v>
@@ -39313,7 +39312,7 @@
         <v>186</v>
       </c>
       <c r="G1172" s="18" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H1172" s="18"/>
     </row>
@@ -39709,7 +39708,7 @@
         <v>183</v>
       </c>
       <c r="G1188" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H1188" s="6">
         <v>6</v>
@@ -39839,7 +39838,7 @@
         <v>186</v>
       </c>
       <c r="G1193" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H1193" s="6">
         <v>0</v>
@@ -40262,7 +40261,7 @@
         <v>41</v>
       </c>
       <c r="F1210" s="36" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G1210" s="11" t="s">
         <v>192</v>
@@ -40289,7 +40288,7 @@
         <v>178</v>
       </c>
       <c r="G1211" s="19" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H1211" s="24"/>
     </row>
@@ -40313,7 +40312,7 @@
         <v>181</v>
       </c>
       <c r="G1212" s="19" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H1212" s="24"/>
     </row>
@@ -40337,7 +40336,7 @@
         <v>186</v>
       </c>
       <c r="G1213" s="17" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H1213" s="24"/>
     </row>
@@ -40361,7 +40360,7 @@
         <v>183</v>
       </c>
       <c r="G1214" s="17" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H1214" s="24"/>
     </row>
@@ -40478,10 +40477,10 @@
         <v>11</v>
       </c>
       <c r="F1219" s="39" t="s">
+        <v>201</v>
+      </c>
+      <c r="G1219" s="20" t="s">
         <v>202</v>
-      </c>
-      <c r="G1219" s="20" t="s">
-        <v>203</v>
       </c>
       <c r="H1219" s="24"/>
     </row>
@@ -40502,10 +40501,10 @@
         <v>77</v>
       </c>
       <c r="F1220" s="39" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G1220" s="20" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H1220" s="24"/>
     </row>
@@ -40757,7 +40756,7 @@
         <v>186</v>
       </c>
       <c r="G1230" s="17" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H1230" s="6">
         <v>6</v>
@@ -40780,7 +40779,7 @@
         <v>41</v>
       </c>
       <c r="F1231" s="11" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G1231" s="11" t="s">
         <v>192</v>
@@ -40809,7 +40808,7 @@
         <v>178</v>
       </c>
       <c r="G1232" s="19" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H1232" s="6">
         <v>2</v>
@@ -40861,7 +40860,7 @@
         <v>183</v>
       </c>
       <c r="G1234" s="17" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H1234" s="6">
         <v>0</v>
@@ -40988,10 +40987,10 @@
         <v>11</v>
       </c>
       <c r="F1239" s="20" t="s">
+        <v>201</v>
+      </c>
+      <c r="G1239" s="20" t="s">
         <v>202</v>
-      </c>
-      <c r="G1239" s="20" t="s">
-        <v>203</v>
       </c>
       <c r="H1239" s="6">
         <v>0</v>
@@ -41066,10 +41065,10 @@
         <v>77</v>
       </c>
       <c r="F1242" s="39" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G1242" s="20" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H1242" s="6">
         <v>0</v>
@@ -41147,7 +41146,7 @@
         <v>181</v>
       </c>
       <c r="G1245" s="19" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H1245" s="6">
         <v>0</v>
@@ -41365,7 +41364,7 @@
         <v>186</v>
       </c>
       <c r="G1254" s="17" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H1254" s="24"/>
     </row>
@@ -41413,7 +41412,7 @@
         <v>181</v>
       </c>
       <c r="G1256" s="19" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H1256" s="24"/>
     </row>
@@ -41437,7 +41436,7 @@
         <v>183</v>
       </c>
       <c r="G1257" s="17" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H1257" s="24"/>
     </row>
@@ -41485,7 +41484,7 @@
         <v>178</v>
       </c>
       <c r="G1259" s="19" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H1259" s="24"/>
     </row>
@@ -41506,7 +41505,7 @@
         <v>41</v>
       </c>
       <c r="F1260" s="11" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G1260" s="11" t="s">
         <v>192</v>
@@ -41650,10 +41649,10 @@
         <v>77</v>
       </c>
       <c r="F1266" s="20" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G1266" s="20" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H1266" s="24"/>
     </row>
@@ -41674,10 +41673,10 @@
         <v>11</v>
       </c>
       <c r="F1267" s="20" t="s">
+        <v>201</v>
+      </c>
+      <c r="G1267" s="20" t="s">
         <v>202</v>
-      </c>
-      <c r="G1267" s="20" t="s">
-        <v>203</v>
       </c>
       <c r="H1267" s="24"/>
     </row>
@@ -41883,7 +41882,7 @@
         <v>186</v>
       </c>
       <c r="G1275" s="17" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H1275" s="6">
         <v>1</v>
@@ -41935,7 +41934,7 @@
         <v>183</v>
       </c>
       <c r="G1277" s="17" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H1277" s="6">
         <v>0</v>
@@ -42013,7 +42012,7 @@
         <v>178</v>
       </c>
       <c r="G1280" s="19" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H1280" s="6">
         <v>0</v>
@@ -42166,10 +42165,10 @@
         <v>11</v>
       </c>
       <c r="F1286" s="20" t="s">
+        <v>201</v>
+      </c>
+      <c r="G1286" s="20" t="s">
         <v>202</v>
-      </c>
-      <c r="G1286" s="20" t="s">
-        <v>203</v>
       </c>
       <c r="H1286" s="6">
         <v>0</v>
@@ -42195,7 +42194,7 @@
         <v>181</v>
       </c>
       <c r="G1287" s="19" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H1287" s="6">
         <v>0</v>
@@ -42218,10 +42217,10 @@
         <v>77</v>
       </c>
       <c r="F1288" s="20" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G1288" s="20" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H1288" s="6">
         <v>0</v>
@@ -42244,7 +42243,7 @@
         <v>41</v>
       </c>
       <c r="F1289" s="11" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G1289" s="11" t="s">
         <v>192</v>
@@ -42489,7 +42488,7 @@
         <v>186</v>
       </c>
       <c r="G1299" s="17" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H1299" s="24"/>
     </row>
@@ -42513,7 +42512,7 @@
         <v>181</v>
       </c>
       <c r="G1300" s="19" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H1300" s="24"/>
     </row>
@@ -42561,7 +42560,7 @@
         <v>183</v>
       </c>
       <c r="G1302" s="17" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H1302" s="24"/>
     </row>
@@ -42606,7 +42605,7 @@
         <v>41</v>
       </c>
       <c r="F1304" s="11" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G1304" s="11" t="s">
         <v>192</v>
@@ -42633,7 +42632,7 @@
         <v>178</v>
       </c>
       <c r="G1305" s="19" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H1305" s="24"/>
     </row>
@@ -42726,10 +42725,10 @@
         <v>77</v>
       </c>
       <c r="F1309" s="20" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G1309" s="20" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H1309" s="24"/>
     </row>
@@ -42774,10 +42773,10 @@
         <v>11</v>
       </c>
       <c r="F1311" s="20" t="s">
+        <v>201</v>
+      </c>
+      <c r="G1311" s="20" t="s">
         <v>202</v>
-      </c>
-      <c r="G1311" s="20" t="s">
-        <v>203</v>
       </c>
       <c r="H1311" s="24"/>
     </row>
@@ -42905,7 +42904,7 @@
         <v>186</v>
       </c>
       <c r="G1316" s="17" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H1316" s="6">
         <v>10</v>
@@ -43061,7 +43060,7 @@
         <v>181</v>
       </c>
       <c r="G1322" s="19" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H1322" s="6">
         <v>0</v>
@@ -43084,7 +43083,7 @@
         <v>41</v>
       </c>
       <c r="F1323" s="11" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G1323" s="11" t="s">
         <v>192</v>
@@ -43110,10 +43109,10 @@
         <v>77</v>
       </c>
       <c r="F1324" s="20" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G1324" s="20" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H1324" s="6">
         <v>0</v>
@@ -43139,7 +43138,7 @@
         <v>183</v>
       </c>
       <c r="G1325" s="17" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H1325" s="6">
         <v>0</v>
@@ -43162,10 +43161,10 @@
         <v>11</v>
       </c>
       <c r="F1326" s="20" t="s">
+        <v>201</v>
+      </c>
+      <c r="G1326" s="20" t="s">
         <v>202</v>
-      </c>
-      <c r="G1326" s="20" t="s">
-        <v>203</v>
       </c>
       <c r="H1326" s="6">
         <v>0</v>
@@ -43321,7 +43320,7 @@
         <v>178</v>
       </c>
       <c r="G1332" s="19" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H1332" s="6">
         <v>0</v>
@@ -43565,7 +43564,7 @@
         <v>178</v>
       </c>
       <c r="G1342" s="19" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H1342" s="24"/>
     </row>
@@ -43586,7 +43585,7 @@
         <v>41</v>
       </c>
       <c r="F1343" s="11" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G1343" s="11" t="s">
         <v>192</v>
@@ -43637,7 +43636,7 @@
         <v>183</v>
       </c>
       <c r="G1345" s="17" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H1345" s="24"/>
     </row>
@@ -43661,7 +43660,7 @@
         <v>181</v>
       </c>
       <c r="G1346" s="19" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H1346" s="24"/>
     </row>
@@ -43781,7 +43780,7 @@
         <v>186</v>
       </c>
       <c r="G1351" s="17" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H1351" s="24"/>
     </row>
@@ -43802,10 +43801,10 @@
         <v>11</v>
       </c>
       <c r="F1352" s="20" t="s">
+        <v>201</v>
+      </c>
+      <c r="G1352" s="20" t="s">
         <v>202</v>
-      </c>
-      <c r="G1352" s="20" t="s">
-        <v>203</v>
       </c>
       <c r="H1352" s="24"/>
     </row>
@@ -43826,10 +43825,10 @@
         <v>77</v>
       </c>
       <c r="F1353" s="20" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G1353" s="20" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H1353" s="24"/>
     </row>
@@ -44135,7 +44134,7 @@
         <v>183</v>
       </c>
       <c r="G1365" s="17" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H1365" s="6">
         <v>1</v>
@@ -44161,7 +44160,7 @@
         <v>181</v>
       </c>
       <c r="G1366" s="19" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H1366" s="6">
         <v>0</v>
@@ -44213,7 +44212,7 @@
         <v>178</v>
       </c>
       <c r="G1368" s="19" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H1368" s="6">
         <v>0</v>
@@ -44236,7 +44235,7 @@
         <v>41</v>
       </c>
       <c r="F1369" s="11" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G1369" s="11" t="s">
         <v>192</v>
@@ -44314,10 +44313,10 @@
         <v>11</v>
       </c>
       <c r="F1372" s="20" t="s">
+        <v>201</v>
+      </c>
+      <c r="G1372" s="20" t="s">
         <v>202</v>
-      </c>
-      <c r="G1372" s="20" t="s">
-        <v>203</v>
       </c>
       <c r="H1372" s="6">
         <v>0</v>
@@ -44366,10 +44365,10 @@
         <v>77</v>
       </c>
       <c r="F1374" s="20" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G1374" s="20" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H1374" s="6">
         <v>0</v>
@@ -44447,7 +44446,7 @@
         <v>186</v>
       </c>
       <c r="G1377" s="17" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H1377" s="6">
         <v>0</v>
@@ -44713,7 +44712,7 @@
         <v>178</v>
       </c>
       <c r="G1388" s="19" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H1388" s="24"/>
     </row>
@@ -44737,7 +44736,7 @@
         <v>181</v>
       </c>
       <c r="G1389" s="19" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H1389" s="24"/>
     </row>
@@ -44761,7 +44760,7 @@
         <v>186</v>
       </c>
       <c r="G1390" s="17" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H1390" s="24"/>
     </row>
@@ -44806,7 +44805,7 @@
         <v>41</v>
       </c>
       <c r="F1392" s="11" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G1392" s="11" t="s">
         <v>192</v>
@@ -44857,7 +44856,7 @@
         <v>183</v>
       </c>
       <c r="G1394" s="17" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H1394" s="24"/>
     </row>
@@ -44878,10 +44877,10 @@
         <v>11</v>
       </c>
       <c r="F1395" s="20" t="s">
+        <v>201</v>
+      </c>
+      <c r="G1395" s="20" t="s">
         <v>202</v>
-      </c>
-      <c r="G1395" s="20" t="s">
-        <v>203</v>
       </c>
       <c r="H1395" s="24"/>
     </row>
@@ -44926,10 +44925,10 @@
         <v>77</v>
       </c>
       <c r="F1397" s="20" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G1397" s="20" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H1397" s="24"/>
     </row>
@@ -44981,8 +44980,1680 @@
       </c>
       <c r="H1399" s="24"/>
     </row>
+    <row r="1400" spans="1:8">
+      <c r="A1400" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B1400" s="24">
+        <v>4</v>
+      </c>
+      <c r="C1400" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1400" s="6">
+        <v>1</v>
+      </c>
+      <c r="E1400" s="7">
+        <v>1</v>
+      </c>
+      <c r="F1400" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="G1400" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="H1400" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1401" spans="1:8">
+      <c r="A1401" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B1401" s="24">
+        <v>4</v>
+      </c>
+      <c r="C1401" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1401" s="6">
+        <v>2</v>
+      </c>
+      <c r="E1401" s="7">
+        <v>81</v>
+      </c>
+      <c r="F1401" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="G1401" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="H1401" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1402" spans="1:8">
+      <c r="A1402" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B1402" s="24">
+        <v>4</v>
+      </c>
+      <c r="C1402" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1402" s="6">
+        <v>3</v>
+      </c>
+      <c r="E1402" s="10">
+        <v>16</v>
+      </c>
+      <c r="F1402" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="G1402" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="H1402" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1403" spans="1:8">
+      <c r="A1403" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B1403" s="24">
+        <v>4</v>
+      </c>
+      <c r="C1403" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1403" s="6">
+        <v>4</v>
+      </c>
+      <c r="E1403" s="9">
+        <v>63</v>
+      </c>
+      <c r="F1403" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="G1403" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="H1403" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1404" spans="1:8">
+      <c r="A1404" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B1404" s="24">
+        <v>4</v>
+      </c>
+      <c r="C1404" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1404" s="6">
+        <v>5</v>
+      </c>
+      <c r="E1404" s="8">
+        <v>3</v>
+      </c>
+      <c r="F1404" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="G1404" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="H1404" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1405" spans="1:8">
+      <c r="A1405" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B1405" s="24">
+        <v>4</v>
+      </c>
+      <c r="C1405" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1405" s="6">
+        <v>6</v>
+      </c>
+      <c r="E1405" s="9">
+        <v>12</v>
+      </c>
+      <c r="F1405" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="G1405" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="H1405" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1406" spans="1:8">
+      <c r="A1406" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B1406" s="24">
+        <v>4</v>
+      </c>
+      <c r="C1406" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1406" s="6">
+        <v>7</v>
+      </c>
+      <c r="E1406" s="10">
+        <v>44</v>
+      </c>
+      <c r="F1406" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="G1406" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="H1406" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1407" spans="1:8">
+      <c r="A1407" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B1407" s="24">
+        <v>4</v>
+      </c>
+      <c r="C1407" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1407" s="6">
+        <v>8</v>
+      </c>
+      <c r="E1407" s="13">
+        <v>10</v>
+      </c>
+      <c r="F1407" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="G1407" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="H1407" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1408" spans="1:8">
+      <c r="A1408" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B1408" s="24">
+        <v>4</v>
+      </c>
+      <c r="C1408" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1408" s="6">
+        <v>9</v>
+      </c>
+      <c r="E1408" s="8">
+        <v>6</v>
+      </c>
+      <c r="F1408" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="G1408" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="H1408" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1409" spans="1:8">
+      <c r="A1409" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B1409" s="24">
+        <v>4</v>
+      </c>
+      <c r="C1409" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1409" s="6">
+        <v>10</v>
+      </c>
+      <c r="E1409" s="13">
+        <v>43</v>
+      </c>
+      <c r="F1409" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="G1409" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="H1409" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1410" spans="1:8">
+      <c r="A1410" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B1410" s="24">
+        <v>4</v>
+      </c>
+      <c r="C1410" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1410" s="6">
+        <v>11</v>
+      </c>
+      <c r="E1410" s="17">
+        <v>31</v>
+      </c>
+      <c r="F1410" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="G1410" s="17" t="s">
+        <v>198</v>
+      </c>
+      <c r="H1410" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1411" spans="1:8">
+      <c r="A1411" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B1411" s="24">
+        <v>4</v>
+      </c>
+      <c r="C1411" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1411" s="6">
+        <v>12</v>
+      </c>
+      <c r="E1411" s="17">
+        <v>87</v>
+      </c>
+      <c r="F1411" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="G1411" s="17" t="s">
+        <v>198</v>
+      </c>
+      <c r="H1411" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1412" spans="1:8">
+      <c r="A1412" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B1412" s="24">
+        <v>4</v>
+      </c>
+      <c r="C1412" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1412" s="6">
+        <v>13</v>
+      </c>
+      <c r="E1412" s="12">
+        <v>55</v>
+      </c>
+      <c r="F1412" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="G1412" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="H1412" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1413" spans="1:8">
+      <c r="A1413" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B1413" s="24">
+        <v>4</v>
+      </c>
+      <c r="C1413" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1413" s="6">
+        <v>14</v>
+      </c>
+      <c r="E1413" s="11">
+        <v>30</v>
+      </c>
+      <c r="F1413" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="G1413" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="H1413" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1414" spans="1:8">
+      <c r="A1414" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B1414" s="24">
+        <v>4</v>
+      </c>
+      <c r="C1414" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1414" s="6">
+        <v>15</v>
+      </c>
+      <c r="E1414" s="14">
+        <v>14</v>
+      </c>
+      <c r="F1414" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="G1414" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="H1414" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1415" spans="1:8">
+      <c r="A1415" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B1415" s="24">
+        <v>4</v>
+      </c>
+      <c r="C1415" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1415" s="6">
+        <v>16</v>
+      </c>
+      <c r="E1415" s="20">
+        <v>11</v>
+      </c>
+      <c r="F1415" s="20" t="s">
+        <v>201</v>
+      </c>
+      <c r="G1415" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="H1415" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1416" spans="1:8">
+      <c r="A1416" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B1416" s="24">
+        <v>4</v>
+      </c>
+      <c r="C1416" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1416" s="6">
+        <v>17</v>
+      </c>
+      <c r="E1416" s="14">
+        <v>18</v>
+      </c>
+      <c r="F1416" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="G1416" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="H1416" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1417" spans="1:8">
+      <c r="A1417" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B1417" s="24">
+        <v>4</v>
+      </c>
+      <c r="C1417" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1417" s="6">
+        <v>18</v>
+      </c>
+      <c r="E1417" s="12">
+        <v>23</v>
+      </c>
+      <c r="F1417" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1417" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="H1417" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1418" spans="1:8">
+      <c r="A1418" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B1418" s="24">
+        <v>4</v>
+      </c>
+      <c r="C1418" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1418" s="6">
+        <v>19</v>
+      </c>
+      <c r="E1418" s="20">
+        <v>77</v>
+      </c>
+      <c r="F1418" s="20" t="s">
+        <v>203</v>
+      </c>
+      <c r="G1418" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="H1418" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1419" spans="1:8">
+      <c r="A1419" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B1419" s="24">
+        <v>4</v>
+      </c>
+      <c r="C1419" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1419" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="E1419" s="19">
+        <v>27</v>
+      </c>
+      <c r="F1419" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="G1419" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="H1419" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1420" spans="1:8">
+      <c r="A1420" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B1420" s="24">
+        <v>4</v>
+      </c>
+      <c r="C1420" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1420" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="E1420" s="11">
+        <v>41</v>
+      </c>
+      <c r="F1420" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="G1420" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="H1420" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1421" spans="1:8">
+      <c r="A1421" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B1421" s="24">
+        <v>4</v>
+      </c>
+      <c r="C1421" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1421" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="E1421" s="19">
+        <v>5</v>
+      </c>
+      <c r="F1421" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="G1421" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="H1421" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1422" spans="1:8">
+      <c r="A1422" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1422" s="18">
+        <v>4</v>
+      </c>
+      <c r="C1422" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1422" s="18">
+        <v>1</v>
+      </c>
+      <c r="E1422" s="9">
+        <v>12</v>
+      </c>
+      <c r="F1422" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="G1422" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="H1422" s="24"/>
+    </row>
+    <row r="1423" spans="1:8">
+      <c r="A1423" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1423" s="18">
+        <v>4</v>
+      </c>
+      <c r="C1423" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1423" s="18">
+        <v>2</v>
+      </c>
+      <c r="E1423" s="8">
+        <v>3</v>
+      </c>
+      <c r="F1423" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="G1423" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="H1423" s="24"/>
+    </row>
+    <row r="1424" spans="1:8">
+      <c r="A1424" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1424" s="18">
+        <v>4</v>
+      </c>
+      <c r="C1424" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1424" s="18">
+        <v>3</v>
+      </c>
+      <c r="E1424" s="10">
+        <v>16</v>
+      </c>
+      <c r="F1424" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="G1424" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="H1424" s="24"/>
+    </row>
+    <row r="1425" spans="1:8">
+      <c r="A1425" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1425" s="18">
+        <v>4</v>
+      </c>
+      <c r="C1425" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1425" s="18">
+        <v>4</v>
+      </c>
+      <c r="E1425" s="7">
+        <v>1</v>
+      </c>
+      <c r="F1425" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="G1425" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="H1425" s="24"/>
+    </row>
+    <row r="1426" spans="1:8">
+      <c r="A1426" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1426" s="18">
+        <v>4</v>
+      </c>
+      <c r="C1426" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1426" s="18">
+        <v>5</v>
+      </c>
+      <c r="E1426" s="9">
+        <v>63</v>
+      </c>
+      <c r="F1426" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="G1426" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="H1426" s="24"/>
+    </row>
+    <row r="1427" spans="1:8">
+      <c r="A1427" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1427" s="18">
+        <v>4</v>
+      </c>
+      <c r="C1427" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1427" s="18">
+        <v>6</v>
+      </c>
+      <c r="E1427" s="10">
+        <v>44</v>
+      </c>
+      <c r="F1427" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="G1427" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="H1427" s="24"/>
+    </row>
+    <row r="1428" spans="1:8">
+      <c r="A1428" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1428" s="18">
+        <v>4</v>
+      </c>
+      <c r="C1428" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1428" s="18">
+        <v>7</v>
+      </c>
+      <c r="E1428" s="7">
+        <v>81</v>
+      </c>
+      <c r="F1428" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="G1428" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="H1428" s="24"/>
+    </row>
+    <row r="1429" spans="1:8">
+      <c r="A1429" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1429" s="18">
+        <v>4</v>
+      </c>
+      <c r="C1429" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1429" s="18">
+        <v>8</v>
+      </c>
+      <c r="E1429" s="13">
+        <v>43</v>
+      </c>
+      <c r="F1429" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="G1429" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="H1429" s="24"/>
+    </row>
+    <row r="1430" spans="1:8">
+      <c r="A1430" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1430" s="18">
+        <v>4</v>
+      </c>
+      <c r="C1430" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1430" s="18">
+        <v>9</v>
+      </c>
+      <c r="E1430" s="8">
+        <v>6</v>
+      </c>
+      <c r="F1430" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="G1430" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="H1430" s="24"/>
+    </row>
+    <row r="1431" spans="1:8">
+      <c r="A1431" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1431" s="18">
+        <v>4</v>
+      </c>
+      <c r="C1431" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1431" s="18">
+        <v>10</v>
+      </c>
+      <c r="E1431" s="13">
+        <v>10</v>
+      </c>
+      <c r="F1431" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="G1431" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="H1431" s="24"/>
+    </row>
+    <row r="1432" spans="1:8">
+      <c r="A1432" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1432" s="18">
+        <v>4</v>
+      </c>
+      <c r="C1432" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1432" s="18">
+        <v>11</v>
+      </c>
+      <c r="E1432" s="19">
+        <v>27</v>
+      </c>
+      <c r="F1432" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="G1432" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="H1432" s="24"/>
+    </row>
+    <row r="1433" spans="1:8">
+      <c r="A1433" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1433" s="18">
+        <v>4</v>
+      </c>
+      <c r="C1433" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1433" s="18">
+        <v>12</v>
+      </c>
+      <c r="E1433" s="11">
+        <v>30</v>
+      </c>
+      <c r="F1433" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="G1433" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="H1433" s="24"/>
+    </row>
+    <row r="1434" spans="1:8">
+      <c r="A1434" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1434" s="18">
+        <v>4</v>
+      </c>
+      <c r="C1434" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1434" s="18">
+        <v>13</v>
+      </c>
+      <c r="E1434" s="17">
+        <v>87</v>
+      </c>
+      <c r="F1434" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="G1434" s="17" t="s">
+        <v>198</v>
+      </c>
+      <c r="H1434" s="24"/>
+    </row>
+    <row r="1435" spans="1:8">
+      <c r="A1435" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1435" s="18">
+        <v>4</v>
+      </c>
+      <c r="C1435" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1435" s="18">
+        <v>14</v>
+      </c>
+      <c r="E1435" s="12">
+        <v>55</v>
+      </c>
+      <c r="F1435" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="G1435" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="H1435" s="24"/>
+    </row>
+    <row r="1436" spans="1:8">
+      <c r="A1436" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1436" s="18">
+        <v>4</v>
+      </c>
+      <c r="C1436" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1436" s="18">
+        <v>15</v>
+      </c>
+      <c r="E1436" s="17">
+        <v>31</v>
+      </c>
+      <c r="F1436" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="G1436" s="17" t="s">
+        <v>198</v>
+      </c>
+      <c r="H1436" s="24"/>
+    </row>
+    <row r="1437" spans="1:8">
+      <c r="A1437" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1437" s="18">
+        <v>4</v>
+      </c>
+      <c r="C1437" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1437" s="18">
+        <v>16</v>
+      </c>
+      <c r="E1437" s="12">
+        <v>23</v>
+      </c>
+      <c r="F1437" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1437" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="H1437" s="24"/>
+    </row>
+    <row r="1438" spans="1:8">
+      <c r="A1438" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1438" s="18">
+        <v>4</v>
+      </c>
+      <c r="C1438" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1438" s="18">
+        <v>17</v>
+      </c>
+      <c r="E1438" s="11">
+        <v>41</v>
+      </c>
+      <c r="F1438" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="G1438" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="H1438" s="24"/>
+    </row>
+    <row r="1439" spans="1:8">
+      <c r="A1439" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1439" s="18">
+        <v>4</v>
+      </c>
+      <c r="C1439" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1439" s="18">
+        <v>18</v>
+      </c>
+      <c r="E1439" s="14">
+        <v>14</v>
+      </c>
+      <c r="F1439" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="G1439" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="H1439" s="24"/>
+    </row>
+    <row r="1440" spans="1:8">
+      <c r="A1440" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1440" s="18">
+        <v>4</v>
+      </c>
+      <c r="C1440" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1440" s="18">
+        <v>19</v>
+      </c>
+      <c r="E1440" s="14">
+        <v>18</v>
+      </c>
+      <c r="F1440" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="G1440" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="H1440" s="24"/>
+    </row>
+    <row r="1441" spans="1:8">
+      <c r="A1441" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1441" s="18">
+        <v>4</v>
+      </c>
+      <c r="C1441" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1441" s="18">
+        <v>20</v>
+      </c>
+      <c r="E1441" s="20">
+        <v>77</v>
+      </c>
+      <c r="F1441" s="20" t="s">
+        <v>203</v>
+      </c>
+      <c r="G1441" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="H1441" s="24"/>
+    </row>
+    <row r="1442" spans="1:8">
+      <c r="A1442" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1442" s="18">
+        <v>4</v>
+      </c>
+      <c r="C1442" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1442" s="18">
+        <v>21</v>
+      </c>
+      <c r="E1442" s="20">
+        <v>11</v>
+      </c>
+      <c r="F1442" s="20" t="s">
+        <v>201</v>
+      </c>
+      <c r="G1442" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="H1442" s="24"/>
+    </row>
+    <row r="1443" spans="1:8">
+      <c r="A1443" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1443" s="18">
+        <v>4</v>
+      </c>
+      <c r="C1443" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1443" s="18">
+        <v>22</v>
+      </c>
+      <c r="E1443" s="19">
+        <v>5</v>
+      </c>
+      <c r="F1443" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="G1443" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="H1443" s="24"/>
+    </row>
+    <row r="1444" spans="1:8">
+      <c r="A1444" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B1444" s="24">
+        <v>4</v>
+      </c>
+      <c r="C1444" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1444" s="6">
+        <v>1</v>
+      </c>
+      <c r="E1444" s="9">
+        <v>12</v>
+      </c>
+      <c r="F1444" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="G1444" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="H1444" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1445" spans="1:8">
+      <c r="A1445" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B1445" s="24">
+        <v>4</v>
+      </c>
+      <c r="C1445" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1445" s="6">
+        <v>2</v>
+      </c>
+      <c r="E1445" s="7">
+        <v>1</v>
+      </c>
+      <c r="F1445" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="G1445" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="H1445" s="6">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1446" spans="1:8">
+      <c r="A1446" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B1446" s="24">
+        <v>4</v>
+      </c>
+      <c r="C1446" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1446" s="6">
+        <v>3</v>
+      </c>
+      <c r="E1446" s="7">
+        <v>81</v>
+      </c>
+      <c r="F1446" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="G1446" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="H1446" s="6">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1447" spans="1:8">
+      <c r="A1447" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B1447" s="24">
+        <v>4</v>
+      </c>
+      <c r="C1447" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1447" s="6">
+        <v>4</v>
+      </c>
+      <c r="E1447" s="9">
+        <v>63</v>
+      </c>
+      <c r="F1447" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="G1447" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="H1447" s="6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1448" spans="1:8">
+      <c r="A1448" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B1448" s="24">
+        <v>4</v>
+      </c>
+      <c r="C1448" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1448" s="6">
+        <v>5</v>
+      </c>
+      <c r="E1448" s="8">
+        <v>3</v>
+      </c>
+      <c r="F1448" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="G1448" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="H1448" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1449" spans="1:8">
+      <c r="A1449" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B1449" s="24">
+        <v>4</v>
+      </c>
+      <c r="C1449" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1449" s="6">
+        <v>6</v>
+      </c>
+      <c r="E1449" s="10">
+        <v>44</v>
+      </c>
+      <c r="F1449" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="G1449" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="H1449" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1450" spans="1:8">
+      <c r="A1450" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B1450" s="24">
+        <v>4</v>
+      </c>
+      <c r="C1450" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1450" s="6">
+        <v>7</v>
+      </c>
+      <c r="E1450" s="13">
+        <v>43</v>
+      </c>
+      <c r="F1450" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="G1450" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="H1450" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1451" spans="1:8">
+      <c r="A1451" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B1451" s="24">
+        <v>4</v>
+      </c>
+      <c r="C1451" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1451" s="6">
+        <v>8</v>
+      </c>
+      <c r="E1451" s="10">
+        <v>16</v>
+      </c>
+      <c r="F1451" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="G1451" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="H1451" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1452" spans="1:8">
+      <c r="A1452" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B1452" s="24">
+        <v>4</v>
+      </c>
+      <c r="C1452" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1452" s="6">
+        <v>9</v>
+      </c>
+      <c r="E1452" s="12">
+        <v>55</v>
+      </c>
+      <c r="F1452" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="G1452" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="H1452" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1453" spans="1:8">
+      <c r="A1453" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B1453" s="24">
+        <v>4</v>
+      </c>
+      <c r="C1453" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1453" s="6">
+        <v>10</v>
+      </c>
+      <c r="E1453" s="12">
+        <v>23</v>
+      </c>
+      <c r="F1453" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1453" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="H1453" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1454" spans="1:8">
+      <c r="A1454" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B1454" s="24">
+        <v>4</v>
+      </c>
+      <c r="C1454" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1454" s="6">
+        <v>11</v>
+      </c>
+      <c r="E1454" s="17">
+        <v>87</v>
+      </c>
+      <c r="F1454" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="G1454" s="17" t="s">
+        <v>198</v>
+      </c>
+      <c r="H1454" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1455" spans="1:8">
+      <c r="A1455" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B1455" s="24">
+        <v>4</v>
+      </c>
+      <c r="C1455" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1455" s="6">
+        <v>12</v>
+      </c>
+      <c r="E1455" s="19">
+        <v>5</v>
+      </c>
+      <c r="F1455" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="G1455" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="H1455" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1456" spans="1:8">
+      <c r="A1456" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B1456" s="24">
+        <v>4</v>
+      </c>
+      <c r="C1456" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1456" s="6">
+        <v>13</v>
+      </c>
+      <c r="E1456" s="17">
+        <v>31</v>
+      </c>
+      <c r="F1456" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="G1456" s="17" t="s">
+        <v>198</v>
+      </c>
+      <c r="H1456" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1457" spans="1:8">
+      <c r="A1457" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B1457" s="24">
+        <v>4</v>
+      </c>
+      <c r="C1457" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1457" s="6">
+        <v>14</v>
+      </c>
+      <c r="E1457" s="11">
+        <v>41</v>
+      </c>
+      <c r="F1457" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="G1457" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="H1457" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1458" spans="1:8">
+      <c r="A1458" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B1458" s="24">
+        <v>4</v>
+      </c>
+      <c r="C1458" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1458" s="6">
+        <v>15</v>
+      </c>
+      <c r="E1458" s="14">
+        <v>14</v>
+      </c>
+      <c r="F1458" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="G1458" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="H1458" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1459" spans="1:8">
+      <c r="A1459" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B1459" s="24">
+        <v>4</v>
+      </c>
+      <c r="C1459" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1459" s="6">
+        <v>16</v>
+      </c>
+      <c r="E1459" s="20">
+        <v>11</v>
+      </c>
+      <c r="F1459" s="20" t="s">
+        <v>201</v>
+      </c>
+      <c r="G1459" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="H1459" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1460" spans="1:8">
+      <c r="A1460" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B1460" s="24">
+        <v>4</v>
+      </c>
+      <c r="C1460" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1460" s="6">
+        <v>17</v>
+      </c>
+      <c r="E1460" s="14">
+        <v>18</v>
+      </c>
+      <c r="F1460" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="G1460" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="H1460" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1461" spans="1:8">
+      <c r="A1461" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B1461" s="24">
+        <v>4</v>
+      </c>
+      <c r="C1461" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1461" s="6">
+        <v>18</v>
+      </c>
+      <c r="E1461" s="20">
+        <v>77</v>
+      </c>
+      <c r="F1461" s="20" t="s">
+        <v>203</v>
+      </c>
+      <c r="G1461" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="H1461" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1462" spans="1:8">
+      <c r="A1462" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B1462" s="24">
+        <v>4</v>
+      </c>
+      <c r="C1462" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1462" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="E1462" s="19">
+        <v>27</v>
+      </c>
+      <c r="F1462" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="G1462" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="H1462" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1463" spans="1:8">
+      <c r="A1463" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B1463" s="24">
+        <v>4</v>
+      </c>
+      <c r="C1463" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1463" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="E1463" s="11">
+        <v>30</v>
+      </c>
+      <c r="F1463" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="G1463" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="H1463" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1464" spans="1:8">
+      <c r="A1464" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B1464" s="24">
+        <v>4</v>
+      </c>
+      <c r="C1464" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1464" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="E1464" s="13">
+        <v>10</v>
+      </c>
+      <c r="F1464" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="G1464" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="H1464" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1465" spans="1:8">
+      <c r="A1465" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B1465" s="24">
+        <v>4</v>
+      </c>
+      <c r="C1465" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1465" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="E1465" s="8">
+        <v>6</v>
+      </c>
+      <c r="F1465" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="G1465" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="H1465" s="6">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H1377" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H1465" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -45006,7 +46677,7 @@
         <v>154</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -45030,7 +46701,7 @@
         <v>160</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="5" ht="17" spans="1:2">
@@ -45038,7 +46709,7 @@
         <v>195</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -45062,7 +46733,7 @@
         <v>164</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="9" ht="17" spans="1:2">
@@ -45070,7 +46741,7 @@
         <v>192</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -45110,7 +46781,7 @@
         <v>175</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15" ht="17" spans="1:2">
@@ -45118,7 +46789,7 @@
         <v>194</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -45126,7 +46797,7 @@
         <v>179</v>
       </c>
       <c r="B16" s="22" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="17" ht="17" spans="1:2">
@@ -45134,7 +46805,7 @@
         <v>191</v>
       </c>
       <c r="B17" s="22" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -45155,7 +46826,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="24" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B20" s="22" t="s">
         <v>197</v>
@@ -45163,18 +46834,18 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="22" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B21" s="22" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="22" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B22" s="22" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>
@@ -45207,22 +46878,22 @@
         <v>0</v>
       </c>
       <c r="C1" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>212</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>213</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>29</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -45233,7 +46904,7 @@
         <v>2025</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D2" s="7">
         <v>4</v>
@@ -45259,7 +46930,7 @@
         <v>2025</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D3" s="7">
         <v>81</v>
@@ -45285,7 +46956,7 @@
         <v>2025</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D4" s="8">
         <v>1</v>
@@ -45300,7 +46971,7 @@
         <v>95</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -45311,7 +46982,7 @@
         <v>2025</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D5" s="8">
         <v>22</v>
@@ -45326,7 +46997,7 @@
         <v>44</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -45337,7 +47008,7 @@
         <v>2025</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D6" s="9">
         <v>63</v>
@@ -45363,7 +47034,7 @@
         <v>2025</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D7" s="9">
         <v>12</v>
@@ -45389,7 +47060,7 @@
         <v>2025</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D8" s="10">
         <v>16</v>
@@ -45415,7 +47086,7 @@
         <v>2025</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D9" s="10">
         <v>44</v>
@@ -45441,7 +47112,7 @@
         <v>2025</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D10" s="11">
         <v>30</v>
@@ -45453,10 +47124,10 @@
         <v>192</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -45467,7 +47138,7 @@
         <v>2025</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D11" s="11">
         <v>6</v>
@@ -45479,10 +47150,10 @@
         <v>192</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -45493,7 +47164,7 @@
         <v>2025</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D12" s="12">
         <v>23</v>
@@ -45505,7 +47176,7 @@
         <v>196</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>196</v>
@@ -45519,7 +47190,7 @@
         <v>2025</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D13" s="12">
         <v>55</v>
@@ -45545,7 +47216,7 @@
         <v>2025</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D14" s="13">
         <v>10</v>
@@ -45557,7 +47228,7 @@
         <v>193</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>193</v>
@@ -45571,7 +47242,7 @@
         <v>2025</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D15" s="13">
         <v>43</v>
@@ -45583,7 +47254,7 @@
         <v>193</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>193</v>
@@ -45597,7 +47268,7 @@
         <v>2025</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D16" s="13">
         <v>7</v>
@@ -45623,7 +47294,7 @@
         <v>2025</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D17" s="14">
         <v>18</v>
@@ -45638,7 +47309,7 @@
         <v>75</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -45649,7 +47320,7 @@
         <v>2025</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D18" s="14">
         <v>14</v>
@@ -45664,7 +47335,7 @@
         <v>70</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -45675,7 +47346,7 @@
         <v>2025</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D19" s="15">
         <v>27</v>
@@ -45687,10 +47358,10 @@
         <v>179</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -45701,7 +47372,7 @@
         <v>2025</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D20" s="15">
         <v>5</v>
@@ -45716,7 +47387,7 @@
         <v>119</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -45727,7 +47398,7 @@
         <v>2025</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D21" s="17">
         <v>31</v>
@@ -45736,10 +47407,10 @@
         <v>183</v>
       </c>
       <c r="F21" s="17" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H21" s="4" t="s">
         <v>197</v>
@@ -45753,7 +47424,7 @@
         <v>2025</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D22" s="17">
         <v>87</v>
@@ -45762,7 +47433,7 @@
         <v>186</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G22" s="6" t="s">
         <v>83</v>
@@ -45779,7 +47450,7 @@
         <v>2026</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D23" s="9">
         <v>63</v>
@@ -45805,7 +47476,7 @@
         <v>2026</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D24" s="9">
         <v>12</v>
@@ -45831,7 +47502,7 @@
         <v>2026</v>
       </c>
       <c r="C25" s="18" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D25" s="10">
         <v>16</v>
@@ -45857,7 +47528,7 @@
         <v>2026</v>
       </c>
       <c r="C26" s="18" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D26" s="10">
         <v>44</v>
@@ -45883,7 +47554,7 @@
         <v>2026</v>
       </c>
       <c r="C27" s="18" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D27" s="7">
         <v>1</v>
@@ -45909,7 +47580,7 @@
         <v>2026</v>
       </c>
       <c r="C28" s="18" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D28" s="7">
         <v>81</v>
@@ -45935,7 +47606,7 @@
         <v>2026</v>
       </c>
       <c r="C29" s="18" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D29" s="8">
         <v>3</v>
@@ -45950,7 +47621,7 @@
         <v>95</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -45961,7 +47632,7 @@
         <v>2026</v>
       </c>
       <c r="C30" s="18" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D30" s="8">
         <v>6</v>
@@ -45973,10 +47644,10 @@
         <v>195</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -45987,7 +47658,7 @@
         <v>2026</v>
       </c>
       <c r="C31" s="18" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D31" s="11">
         <v>30</v>
@@ -45999,10 +47670,10 @@
         <v>192</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -46013,13 +47684,13 @@
         <v>2026</v>
       </c>
       <c r="C32" s="18" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D32" s="11">
         <v>41</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F32" s="11" t="s">
         <v>192</v>
@@ -46028,7 +47699,7 @@
         <v>83</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -46039,7 +47710,7 @@
         <v>2026</v>
       </c>
       <c r="C33" s="18" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D33" s="12">
         <v>23</v>
@@ -46051,7 +47722,7 @@
         <v>196</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H33" s="4" t="s">
         <v>196</v>
@@ -46065,7 +47736,7 @@
         <v>2026</v>
       </c>
       <c r="C34" s="18" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D34" s="12">
         <v>55</v>
@@ -46091,7 +47762,7 @@
         <v>2026</v>
       </c>
       <c r="C35" s="18" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D35" s="13">
         <v>10</v>
@@ -46103,7 +47774,7 @@
         <v>193</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H35" s="4" t="s">
         <v>193</v>
@@ -46117,7 +47788,7 @@
         <v>2026</v>
       </c>
       <c r="C36" s="18" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D36" s="13">
         <v>43</v>
@@ -46129,7 +47800,7 @@
         <v>193</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H36" s="4" t="s">
         <v>193</v>
@@ -46143,7 +47814,7 @@
         <v>2026</v>
       </c>
       <c r="C37" s="18" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D37" s="14">
         <v>18</v>
@@ -46158,7 +47829,7 @@
         <v>75</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -46169,7 +47840,7 @@
         <v>2026</v>
       </c>
       <c r="C38" s="18" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D38" s="14">
         <v>14</v>
@@ -46184,7 +47855,7 @@
         <v>70</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -46195,7 +47866,7 @@
         <v>2026</v>
       </c>
       <c r="C39" s="18" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D39" s="19">
         <v>27</v>
@@ -46204,13 +47875,13 @@
         <v>181</v>
       </c>
       <c r="F39" s="19" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -46221,7 +47892,7 @@
         <v>2026</v>
       </c>
       <c r="C40" s="18" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D40" s="19">
         <v>5</v>
@@ -46230,13 +47901,13 @@
         <v>178</v>
       </c>
       <c r="F40" s="19" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G40" s="6" t="s">
         <v>119</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -46247,7 +47918,7 @@
         <v>2026</v>
       </c>
       <c r="C41" s="18" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D41" s="17">
         <v>31</v>
@@ -46256,10 +47927,10 @@
         <v>183</v>
       </c>
       <c r="F41" s="17" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H41" s="4" t="s">
         <v>197</v>
@@ -46273,7 +47944,7 @@
         <v>2026</v>
       </c>
       <c r="C42" s="18" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D42" s="17">
         <v>87</v>
@@ -46282,7 +47953,7 @@
         <v>186</v>
       </c>
       <c r="F42" s="17" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G42" s="6" t="s">
         <v>83</v>
@@ -46299,22 +47970,22 @@
         <v>2026</v>
       </c>
       <c r="C43" s="18" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D43" s="20">
         <v>11</v>
       </c>
       <c r="E43" s="20" t="s">
+        <v>201</v>
+      </c>
+      <c r="F43" s="20" t="s">
         <v>202</v>
-      </c>
-      <c r="F43" s="20" t="s">
-        <v>203</v>
       </c>
       <c r="G43" s="6" t="s">
         <v>115</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -46325,22 +47996,22 @@
         <v>2026</v>
       </c>
       <c r="C44" s="18" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D44" s="20">
         <v>77</v>
       </c>
       <c r="E44" s="20" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F44" s="20" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>
@@ -46372,21 +48043,21 @@
         <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>245</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B2" s="3">
         <v>2025</v>
@@ -46398,35 +48069,35 @@
         <v>157</v>
       </c>
       <c r="E2" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="F2" t="s">
         <v>248</v>
-      </c>
-      <c r="F2" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B3" s="3">
         <v>2025</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>160</v>
       </c>
       <c r="E3" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F3" t="s">
         <v>251</v>
-      </c>
-      <c r="F3" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B4" s="3">
         <v>2025</v>
@@ -46438,15 +48109,15 @@
         <v>162</v>
       </c>
       <c r="E4" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F4" t="s">
         <v>254</v>
-      </c>
-      <c r="F4" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B5" s="3">
         <v>2025</v>
@@ -46458,35 +48129,35 @@
         <v>168</v>
       </c>
       <c r="E5" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="F5" t="s">
         <v>257</v>
-      </c>
-      <c r="F5" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B6" s="3">
         <v>2025</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>164</v>
       </c>
       <c r="E6" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="F6" t="s">
         <v>260</v>
-      </c>
-      <c r="F6" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B7" s="3">
         <v>2025</v>
@@ -46498,15 +48169,15 @@
         <v>166</v>
       </c>
       <c r="E7" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="F7" t="s">
         <v>263</v>
-      </c>
-      <c r="F7" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B8" s="3">
         <v>2025</v>
@@ -46518,55 +48189,55 @@
         <v>171</v>
       </c>
       <c r="E8" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="F8" t="s">
         <v>266</v>
-      </c>
-      <c r="F8" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B9" s="3">
         <v>2025</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>175</v>
       </c>
       <c r="E9" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="F9" t="s">
         <v>269</v>
-      </c>
-      <c r="F9" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B10" s="3">
         <v>2025</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>179</v>
       </c>
       <c r="E10" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="F10" t="s">
         <v>272</v>
-      </c>
-      <c r="F10" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B11" s="3">
         <v>2025</v>
@@ -46578,15 +48249,15 @@
         <v>184</v>
       </c>
       <c r="E11" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="F11" t="s">
         <v>275</v>
-      </c>
-      <c r="F11" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B12" s="3">
         <v>2026</v>
@@ -46598,35 +48269,35 @@
         <v>157</v>
       </c>
       <c r="E12" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="F12" t="s">
         <v>248</v>
-      </c>
-      <c r="F12" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B13" s="3">
         <v>2026</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>160</v>
       </c>
       <c r="E13" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F13" t="s">
         <v>251</v>
-      </c>
-      <c r="F13" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B14" s="3">
         <v>2026</v>
@@ -46638,15 +48309,15 @@
         <v>162</v>
       </c>
       <c r="E14" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F14" t="s">
         <v>254</v>
-      </c>
-      <c r="F14" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B15" s="3">
         <v>2026</v>
@@ -46658,35 +48329,35 @@
         <v>168</v>
       </c>
       <c r="E15" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="F15" t="s">
         <v>257</v>
-      </c>
-      <c r="F15" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B16" s="3">
         <v>2026</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>164</v>
       </c>
       <c r="E16" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="F16" t="s">
         <v>260</v>
-      </c>
-      <c r="F16" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B17" s="3">
         <v>2026</v>
@@ -46698,15 +48369,15 @@
         <v>166</v>
       </c>
       <c r="E17" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="F17" t="s">
         <v>263</v>
-      </c>
-      <c r="F17" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B18" s="3">
         <v>2026</v>
@@ -46718,35 +48389,35 @@
         <v>171</v>
       </c>
       <c r="E18" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="F18" t="s">
         <v>266</v>
-      </c>
-      <c r="F18" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B19" s="3">
         <v>2026</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>175</v>
       </c>
       <c r="E19" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="F19" t="s">
         <v>269</v>
-      </c>
-      <c r="F19" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B20" s="3">
         <v>2026</v>
@@ -46758,50 +48429,50 @@
         <v>184</v>
       </c>
       <c r="E20" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="F20" t="s">
         <v>275</v>
-      </c>
-      <c r="F20" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B21" s="3">
         <v>2026</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E21" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="F21" t="s">
         <v>278</v>
-      </c>
-      <c r="F21" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B22" s="3">
         <v>2026</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E22" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="F22" t="s">
         <v>281</v>
-      </c>
-      <c r="F22" t="s">
-        <v>282</v>
       </c>
     </row>
   </sheetData>

--- a/public/docs/datas/f1.xlsx
+++ b/public/docs/datas/f1.xlsx
@@ -16,7 +16,7 @@
     <sheet name="teams" sheetId="5" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">result!$A$1:$H$1465</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">result!$A$1:$H$1553</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5313" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5586" uniqueCount="282">
   <si>
     <t>year</t>
   </si>
@@ -8453,7 +8453,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R1465"/>
+  <dimension ref="A1:R1553"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="5.57142857142857" customWidth="1"/>
@@ -46652,8 +46652,2208 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1466" spans="1:8">
+      <c r="A1466" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1466" s="18">
+        <v>5</v>
+      </c>
+      <c r="C1466" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1466" s="18">
+        <v>1</v>
+      </c>
+      <c r="E1466" s="9">
+        <v>63</v>
+      </c>
+      <c r="F1466" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="G1466" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="H1466" s="24"/>
+    </row>
+    <row r="1467" spans="1:8">
+      <c r="A1467" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1467" s="18">
+        <v>5</v>
+      </c>
+      <c r="C1467" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1467" s="18">
+        <v>2</v>
+      </c>
+      <c r="E1467" s="9">
+        <v>12</v>
+      </c>
+      <c r="F1467" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="G1467" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="H1467" s="24"/>
+    </row>
+    <row r="1468" spans="1:8">
+      <c r="A1468" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1468" s="18">
+        <v>5</v>
+      </c>
+      <c r="C1468" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1468" s="18">
+        <v>3</v>
+      </c>
+      <c r="E1468" s="7">
+        <v>1</v>
+      </c>
+      <c r="F1468" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="G1468" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="H1468" s="24"/>
+    </row>
+    <row r="1469" spans="1:8">
+      <c r="A1469" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1469" s="18">
+        <v>5</v>
+      </c>
+      <c r="C1469" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1469" s="18">
+        <v>4</v>
+      </c>
+      <c r="E1469" s="7">
+        <v>81</v>
+      </c>
+      <c r="F1469" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="G1469" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="H1469" s="24"/>
+    </row>
+    <row r="1470" spans="1:8">
+      <c r="A1470" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1470" s="18">
+        <v>5</v>
+      </c>
+      <c r="C1470" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1470" s="18">
+        <v>5</v>
+      </c>
+      <c r="E1470" s="10">
+        <v>44</v>
+      </c>
+      <c r="F1470" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="G1470" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="H1470" s="24"/>
+    </row>
+    <row r="1471" spans="1:8">
+      <c r="A1471" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1471" s="18">
+        <v>5</v>
+      </c>
+      <c r="C1471" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1471" s="18">
+        <v>6</v>
+      </c>
+      <c r="E1471" s="10">
+        <v>16</v>
+      </c>
+      <c r="F1471" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="G1471" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="H1471" s="24"/>
+    </row>
+    <row r="1472" spans="1:8">
+      <c r="A1472" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1472" s="18">
+        <v>5</v>
+      </c>
+      <c r="C1472" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1472" s="18">
+        <v>7</v>
+      </c>
+      <c r="E1472" s="8">
+        <v>3</v>
+      </c>
+      <c r="F1472" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="G1472" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="H1472" s="24"/>
+    </row>
+    <row r="1473" spans="1:8">
+      <c r="A1473" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1473" s="18">
+        <v>5</v>
+      </c>
+      <c r="C1473" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1473" s="18">
+        <v>8</v>
+      </c>
+      <c r="E1473" s="8">
+        <v>6</v>
+      </c>
+      <c r="F1473" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="G1473" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="H1473" s="24"/>
+    </row>
+    <row r="1474" spans="1:8">
+      <c r="A1474" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1474" s="18">
+        <v>5</v>
+      </c>
+      <c r="C1474" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1474" s="18">
+        <v>9</v>
+      </c>
+      <c r="E1474" s="11">
+        <v>41</v>
+      </c>
+      <c r="F1474" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="G1474" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="H1474" s="24"/>
+    </row>
+    <row r="1475" spans="1:8">
+      <c r="A1475" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1475" s="18">
+        <v>5</v>
+      </c>
+      <c r="C1475" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1475" s="18">
+        <v>10</v>
+      </c>
+      <c r="E1475" s="12">
+        <v>55</v>
+      </c>
+      <c r="F1475" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="G1475" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="H1475" s="24"/>
+    </row>
+    <row r="1476" spans="1:8">
+      <c r="A1476" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1476" s="18">
+        <v>5</v>
+      </c>
+      <c r="C1476" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1476" s="18">
+        <v>11</v>
+      </c>
+      <c r="E1476" s="19">
+        <v>27</v>
+      </c>
+      <c r="F1476" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="G1476" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="H1476" s="24"/>
+    </row>
+    <row r="1477" spans="1:8">
+      <c r="A1477" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1477" s="18">
+        <v>5</v>
+      </c>
+      <c r="C1477" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1477" s="18">
+        <v>12</v>
+      </c>
+      <c r="E1477" s="19">
+        <v>5</v>
+      </c>
+      <c r="F1477" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="G1477" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="H1477" s="24"/>
+    </row>
+    <row r="1478" spans="1:8">
+      <c r="A1478" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1478" s="18">
+        <v>5</v>
+      </c>
+      <c r="C1478" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1478" s="18">
+        <v>13</v>
+      </c>
+      <c r="E1478" s="13">
+        <v>43</v>
+      </c>
+      <c r="F1478" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="G1478" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="H1478" s="24"/>
+    </row>
+    <row r="1479" spans="1:8">
+      <c r="A1479" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1479" s="18">
+        <v>5</v>
+      </c>
+      <c r="C1479" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1479" s="18">
+        <v>14</v>
+      </c>
+      <c r="E1479" s="17">
+        <v>31</v>
+      </c>
+      <c r="F1479" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="G1479" s="17" t="s">
+        <v>198</v>
+      </c>
+      <c r="H1479" s="24"/>
+    </row>
+    <row r="1480" spans="1:8">
+      <c r="A1480" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1480" s="18">
+        <v>5</v>
+      </c>
+      <c r="C1480" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1480" s="18">
+        <v>15</v>
+      </c>
+      <c r="E1480" s="17">
+        <v>87</v>
+      </c>
+      <c r="F1480" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="G1480" s="17" t="s">
+        <v>198</v>
+      </c>
+      <c r="H1480" s="24"/>
+    </row>
+    <row r="1481" spans="1:8">
+      <c r="A1481" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1481" s="18">
+        <v>5</v>
+      </c>
+      <c r="C1481" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1481" s="18">
+        <v>16</v>
+      </c>
+      <c r="E1481" s="14">
+        <v>14</v>
+      </c>
+      <c r="F1481" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="G1481" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="H1481" s="24"/>
+    </row>
+    <row r="1482" spans="1:8">
+      <c r="A1482" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1482" s="18">
+        <v>5</v>
+      </c>
+      <c r="C1482" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1482" s="18">
+        <v>17</v>
+      </c>
+      <c r="E1482" s="20">
+        <v>11</v>
+      </c>
+      <c r="F1482" s="20" t="s">
+        <v>201</v>
+      </c>
+      <c r="G1482" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="H1482" s="24"/>
+    </row>
+    <row r="1483" spans="1:8">
+      <c r="A1483" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1483" s="18">
+        <v>5</v>
+      </c>
+      <c r="C1483" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1483" s="18">
+        <v>18</v>
+      </c>
+      <c r="E1483" s="14">
+        <v>18</v>
+      </c>
+      <c r="F1483" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="G1483" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="H1483" s="24"/>
+    </row>
+    <row r="1484" spans="1:8">
+      <c r="A1484" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1484" s="18">
+        <v>5</v>
+      </c>
+      <c r="C1484" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1484" s="18">
+        <v>19</v>
+      </c>
+      <c r="E1484" s="13">
+        <v>10</v>
+      </c>
+      <c r="F1484" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="G1484" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="H1484" s="24"/>
+    </row>
+    <row r="1485" spans="1:8">
+      <c r="A1485" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1485" s="18">
+        <v>5</v>
+      </c>
+      <c r="C1485" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1485" s="18">
+        <v>20</v>
+      </c>
+      <c r="E1485" s="20">
+        <v>77</v>
+      </c>
+      <c r="F1485" s="20" t="s">
+        <v>203</v>
+      </c>
+      <c r="G1485" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="H1485" s="24"/>
+    </row>
+    <row r="1486" spans="1:8">
+      <c r="A1486" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1486" s="18">
+        <v>5</v>
+      </c>
+      <c r="C1486" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1486" s="18" t="s">
+        <v>185</v>
+      </c>
+      <c r="E1486" s="12">
+        <v>23</v>
+      </c>
+      <c r="F1486" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1486" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="H1486" s="24"/>
+    </row>
+    <row r="1487" spans="1:8">
+      <c r="A1487" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1487" s="18">
+        <v>5</v>
+      </c>
+      <c r="C1487" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1487" s="18" t="s">
+        <v>185</v>
+      </c>
+      <c r="E1487" s="11">
+        <v>30</v>
+      </c>
+      <c r="F1487" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="G1487" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="H1487" s="24"/>
+    </row>
+    <row r="1488" spans="1:8">
+      <c r="A1488" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B1488" s="24">
+        <v>5</v>
+      </c>
+      <c r="C1488" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1488" s="6">
+        <v>1</v>
+      </c>
+      <c r="E1488" s="9">
+        <v>63</v>
+      </c>
+      <c r="F1488" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="G1488" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="H1488" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1489" spans="1:8">
+      <c r="A1489" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B1489" s="24">
+        <v>5</v>
+      </c>
+      <c r="C1489" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1489" s="6">
+        <v>2</v>
+      </c>
+      <c r="E1489" s="7">
+        <v>1</v>
+      </c>
+      <c r="F1489" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="G1489" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="H1489" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1490" spans="1:8">
+      <c r="A1490" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B1490" s="24">
+        <v>5</v>
+      </c>
+      <c r="C1490" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1490" s="6">
+        <v>3</v>
+      </c>
+      <c r="E1490" s="9">
+        <v>12</v>
+      </c>
+      <c r="F1490" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="G1490" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="H1490" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1491" spans="1:8">
+      <c r="A1491" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B1491" s="24">
+        <v>5</v>
+      </c>
+      <c r="C1491" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1491" s="6">
+        <v>4</v>
+      </c>
+      <c r="E1491" s="7">
+        <v>81</v>
+      </c>
+      <c r="F1491" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="G1491" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="H1491" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1492" spans="1:8">
+      <c r="A1492" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B1492" s="24">
+        <v>5</v>
+      </c>
+      <c r="C1492" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1492" s="6">
+        <v>5</v>
+      </c>
+      <c r="E1492" s="10">
+        <v>16</v>
+      </c>
+      <c r="F1492" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="G1492" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="H1492" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1493" spans="1:8">
+      <c r="A1493" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B1493" s="24">
+        <v>5</v>
+      </c>
+      <c r="C1493" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1493" s="6">
+        <v>6</v>
+      </c>
+      <c r="E1493" s="10">
+        <v>44</v>
+      </c>
+      <c r="F1493" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="G1493" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="H1493" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1494" spans="1:8">
+      <c r="A1494" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B1494" s="24">
+        <v>5</v>
+      </c>
+      <c r="C1494" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1494" s="6">
+        <v>7</v>
+      </c>
+      <c r="E1494" s="8">
+        <v>3</v>
+      </c>
+      <c r="F1494" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="G1494" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="H1494" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1495" spans="1:8">
+      <c r="A1495" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B1495" s="24">
+        <v>5</v>
+      </c>
+      <c r="C1495" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1495" s="6">
+        <v>8</v>
+      </c>
+      <c r="E1495" s="11">
+        <v>41</v>
+      </c>
+      <c r="F1495" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="G1495" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="H1495" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1496" spans="1:8">
+      <c r="A1496" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B1496" s="24">
+        <v>5</v>
+      </c>
+      <c r="C1496" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1496" s="6">
+        <v>9</v>
+      </c>
+      <c r="E1496" s="13">
+        <v>43</v>
+      </c>
+      <c r="F1496" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="G1496" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="H1496" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1497" spans="1:8">
+      <c r="A1497" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B1497" s="24">
+        <v>5</v>
+      </c>
+      <c r="C1497" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1497" s="6">
+        <v>10</v>
+      </c>
+      <c r="E1497" s="12">
+        <v>55</v>
+      </c>
+      <c r="F1497" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="G1497" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="H1497" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1498" spans="1:8">
+      <c r="A1498" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B1498" s="24">
+        <v>5</v>
+      </c>
+      <c r="C1498" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1498" s="6">
+        <v>11</v>
+      </c>
+      <c r="E1498" s="11">
+        <v>30</v>
+      </c>
+      <c r="F1498" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="G1498" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="H1498" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1499" spans="1:8">
+      <c r="A1499" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B1499" s="24">
+        <v>5</v>
+      </c>
+      <c r="C1499" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1499" s="6">
+        <v>12</v>
+      </c>
+      <c r="E1499" s="19">
+        <v>5</v>
+      </c>
+      <c r="F1499" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="G1499" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="H1499" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1500" spans="1:8">
+      <c r="A1500" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B1500" s="24">
+        <v>5</v>
+      </c>
+      <c r="C1500" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1500" s="6">
+        <v>13</v>
+      </c>
+      <c r="E1500" s="17">
+        <v>31</v>
+      </c>
+      <c r="F1500" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="G1500" s="17" t="s">
+        <v>198</v>
+      </c>
+      <c r="H1500" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1501" spans="1:8">
+      <c r="A1501" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B1501" s="24">
+        <v>5</v>
+      </c>
+      <c r="C1501" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1501" s="6">
+        <v>14</v>
+      </c>
+      <c r="E1501" s="20">
+        <v>11</v>
+      </c>
+      <c r="F1501" s="20" t="s">
+        <v>201</v>
+      </c>
+      <c r="G1501" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="H1501" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1502" spans="1:8">
+      <c r="A1502" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B1502" s="24">
+        <v>5</v>
+      </c>
+      <c r="C1502" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1502" s="6">
+        <v>15</v>
+      </c>
+      <c r="E1502" s="19">
+        <v>27</v>
+      </c>
+      <c r="F1502" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="G1502" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="H1502" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1503" spans="1:8">
+      <c r="A1503" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B1503" s="24">
+        <v>5</v>
+      </c>
+      <c r="C1503" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1503" s="6">
+        <v>16</v>
+      </c>
+      <c r="E1503" s="14">
+        <v>18</v>
+      </c>
+      <c r="F1503" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="G1503" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="H1503" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1504" spans="1:8">
+      <c r="A1504" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B1504" s="24">
+        <v>5</v>
+      </c>
+      <c r="C1504" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1504" s="6">
+        <v>17</v>
+      </c>
+      <c r="E1504" s="20">
+        <v>77</v>
+      </c>
+      <c r="F1504" s="20" t="s">
+        <v>203</v>
+      </c>
+      <c r="G1504" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="H1504" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1505" spans="1:8">
+      <c r="A1505" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B1505" s="24">
+        <v>5</v>
+      </c>
+      <c r="C1505" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1505" s="6">
+        <v>18</v>
+      </c>
+      <c r="E1505" s="17">
+        <v>87</v>
+      </c>
+      <c r="F1505" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="G1505" s="17" t="s">
+        <v>198</v>
+      </c>
+      <c r="H1505" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1506" spans="1:8">
+      <c r="A1506" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B1506" s="24">
+        <v>5</v>
+      </c>
+      <c r="C1506" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1506" s="6">
+        <v>19</v>
+      </c>
+      <c r="E1506" s="12">
+        <v>23</v>
+      </c>
+      <c r="F1506" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1506" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="H1506" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1507" spans="1:8">
+      <c r="A1507" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B1507" s="24">
+        <v>5</v>
+      </c>
+      <c r="C1507" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1507" s="6">
+        <v>20</v>
+      </c>
+      <c r="E1507" s="13">
+        <v>10</v>
+      </c>
+      <c r="F1507" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="G1507" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="H1507" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1508" spans="1:8">
+      <c r="A1508" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B1508" s="24">
+        <v>5</v>
+      </c>
+      <c r="C1508" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1508" s="6">
+        <v>21</v>
+      </c>
+      <c r="E1508" s="8">
+        <v>6</v>
+      </c>
+      <c r="F1508" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="G1508" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="H1508" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1509" spans="1:8">
+      <c r="A1509" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B1509" s="24">
+        <v>5</v>
+      </c>
+      <c r="C1509" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1509" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="E1509" s="14">
+        <v>14</v>
+      </c>
+      <c r="F1509" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="G1509" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="H1509" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1510" spans="1:8">
+      <c r="A1510" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1510" s="18">
+        <v>5</v>
+      </c>
+      <c r="C1510" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1510" s="18">
+        <v>1</v>
+      </c>
+      <c r="E1510" s="9">
+        <v>63</v>
+      </c>
+      <c r="F1510" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="G1510" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="H1510" s="24"/>
+    </row>
+    <row r="1511" spans="1:8">
+      <c r="A1511" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1511" s="18">
+        <v>5</v>
+      </c>
+      <c r="C1511" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1511" s="18">
+        <v>2</v>
+      </c>
+      <c r="E1511" s="9">
+        <v>12</v>
+      </c>
+      <c r="F1511" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="G1511" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="H1511" s="24"/>
+    </row>
+    <row r="1512" spans="1:8">
+      <c r="A1512" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1512" s="18">
+        <v>5</v>
+      </c>
+      <c r="C1512" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1512" s="18">
+        <v>3</v>
+      </c>
+      <c r="E1512" s="7">
+        <v>1</v>
+      </c>
+      <c r="F1512" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="G1512" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="H1512" s="24"/>
+    </row>
+    <row r="1513" spans="1:8">
+      <c r="A1513" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1513" s="18">
+        <v>5</v>
+      </c>
+      <c r="C1513" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1513" s="18">
+        <v>4</v>
+      </c>
+      <c r="E1513" s="7">
+        <v>81</v>
+      </c>
+      <c r="F1513" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="G1513" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="H1513" s="24"/>
+    </row>
+    <row r="1514" spans="1:8">
+      <c r="A1514" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1514" s="18">
+        <v>5</v>
+      </c>
+      <c r="C1514" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1514" s="18">
+        <v>5</v>
+      </c>
+      <c r="E1514" s="10">
+        <v>44</v>
+      </c>
+      <c r="F1514" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="G1514" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="H1514" s="24"/>
+    </row>
+    <row r="1515" spans="1:8">
+      <c r="A1515" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1515" s="18">
+        <v>5</v>
+      </c>
+      <c r="C1515" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1515" s="18">
+        <v>6</v>
+      </c>
+      <c r="E1515" s="8">
+        <v>3</v>
+      </c>
+      <c r="F1515" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="G1515" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="H1515" s="24"/>
+    </row>
+    <row r="1516" spans="1:8">
+      <c r="A1516" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1516" s="18">
+        <v>5</v>
+      </c>
+      <c r="C1516" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1516" s="18">
+        <v>7</v>
+      </c>
+      <c r="E1516" s="8">
+        <v>6</v>
+      </c>
+      <c r="F1516" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="G1516" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="H1516" s="24"/>
+    </row>
+    <row r="1517" spans="1:8">
+      <c r="A1517" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1517" s="18">
+        <v>5</v>
+      </c>
+      <c r="C1517" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1517" s="18">
+        <v>8</v>
+      </c>
+      <c r="E1517" s="10">
+        <v>16</v>
+      </c>
+      <c r="F1517" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="G1517" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="H1517" s="24"/>
+    </row>
+    <row r="1518" spans="1:8">
+      <c r="A1518" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1518" s="18">
+        <v>5</v>
+      </c>
+      <c r="C1518" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1518" s="18">
+        <v>9</v>
+      </c>
+      <c r="E1518" s="11">
+        <v>41</v>
+      </c>
+      <c r="F1518" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="G1518" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="H1518" s="24"/>
+    </row>
+    <row r="1519" spans="1:8">
+      <c r="A1519" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1519" s="18">
+        <v>5</v>
+      </c>
+      <c r="C1519" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1519" s="18">
+        <v>10</v>
+      </c>
+      <c r="E1519" s="13">
+        <v>43</v>
+      </c>
+      <c r="F1519" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="G1519" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="H1519" s="24"/>
+    </row>
+    <row r="1520" spans="1:8">
+      <c r="A1520" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1520" s="18">
+        <v>5</v>
+      </c>
+      <c r="C1520" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1520" s="18">
+        <v>11</v>
+      </c>
+      <c r="E1520" s="19">
+        <v>27</v>
+      </c>
+      <c r="F1520" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="G1520" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="H1520" s="24"/>
+    </row>
+    <row r="1521" spans="1:8">
+      <c r="A1521" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1521" s="18">
+        <v>5</v>
+      </c>
+      <c r="C1521" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1521" s="18">
+        <v>12</v>
+      </c>
+      <c r="E1521" s="11">
+        <v>30</v>
+      </c>
+      <c r="F1521" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="G1521" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="H1521" s="24"/>
+    </row>
+    <row r="1522" spans="1:8">
+      <c r="A1522" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1522" s="18">
+        <v>5</v>
+      </c>
+      <c r="C1522" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1522" s="18">
+        <v>13</v>
+      </c>
+      <c r="E1522" s="19">
+        <v>5</v>
+      </c>
+      <c r="F1522" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="G1522" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="H1522" s="24"/>
+    </row>
+    <row r="1523" spans="1:8">
+      <c r="A1523" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1523" s="18">
+        <v>5</v>
+      </c>
+      <c r="C1523" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1523" s="18">
+        <v>14</v>
+      </c>
+      <c r="E1523" s="13">
+        <v>10</v>
+      </c>
+      <c r="F1523" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="G1523" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="H1523" s="24"/>
+    </row>
+    <row r="1524" spans="1:8">
+      <c r="A1524" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1524" s="18">
+        <v>5</v>
+      </c>
+      <c r="C1524" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1524" s="18">
+        <v>15</v>
+      </c>
+      <c r="E1524" s="12">
+        <v>55</v>
+      </c>
+      <c r="F1524" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="G1524" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="H1524" s="24"/>
+    </row>
+    <row r="1525" spans="1:8">
+      <c r="A1525" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1525" s="18">
+        <v>5</v>
+      </c>
+      <c r="C1525" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1525" s="18">
+        <v>16</v>
+      </c>
+      <c r="E1525" s="17">
+        <v>87</v>
+      </c>
+      <c r="F1525" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="G1525" s="17" t="s">
+        <v>198</v>
+      </c>
+      <c r="H1525" s="24"/>
+    </row>
+    <row r="1526" spans="1:8">
+      <c r="A1526" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1526" s="18">
+        <v>5</v>
+      </c>
+      <c r="C1526" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1526" s="18">
+        <v>17</v>
+      </c>
+      <c r="E1526" s="17">
+        <v>31</v>
+      </c>
+      <c r="F1526" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="G1526" s="17" t="s">
+        <v>198</v>
+      </c>
+      <c r="H1526" s="24"/>
+    </row>
+    <row r="1527" spans="1:8">
+      <c r="A1527" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1527" s="18">
+        <v>5</v>
+      </c>
+      <c r="C1527" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1527" s="18">
+        <v>18</v>
+      </c>
+      <c r="E1527" s="12">
+        <v>23</v>
+      </c>
+      <c r="F1527" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1527" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="H1527" s="24"/>
+    </row>
+    <row r="1528" spans="1:8">
+      <c r="A1528" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1528" s="18">
+        <v>5</v>
+      </c>
+      <c r="C1528" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1528" s="18">
+        <v>19</v>
+      </c>
+      <c r="E1528" s="14">
+        <v>14</v>
+      </c>
+      <c r="F1528" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="G1528" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="H1528" s="24"/>
+    </row>
+    <row r="1529" spans="1:8">
+      <c r="A1529" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1529" s="18">
+        <v>5</v>
+      </c>
+      <c r="C1529" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1529" s="18">
+        <v>20</v>
+      </c>
+      <c r="E1529" s="20">
+        <v>11</v>
+      </c>
+      <c r="F1529" s="20" t="s">
+        <v>201</v>
+      </c>
+      <c r="G1529" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="H1529" s="24"/>
+    </row>
+    <row r="1530" spans="1:8">
+      <c r="A1530" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1530" s="18">
+        <v>5</v>
+      </c>
+      <c r="C1530" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1530" s="18">
+        <v>21</v>
+      </c>
+      <c r="E1530" s="14">
+        <v>18</v>
+      </c>
+      <c r="F1530" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="G1530" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="H1530" s="24"/>
+    </row>
+    <row r="1531" spans="1:8">
+      <c r="A1531" s="18">
+        <v>2026</v>
+      </c>
+      <c r="B1531" s="18">
+        <v>5</v>
+      </c>
+      <c r="C1531" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1531" s="18">
+        <v>22</v>
+      </c>
+      <c r="E1531" s="20">
+        <v>77</v>
+      </c>
+      <c r="F1531" s="20" t="s">
+        <v>203</v>
+      </c>
+      <c r="G1531" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="H1531" s="24"/>
+    </row>
+    <row r="1532" spans="1:8">
+      <c r="A1532" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B1532" s="24">
+        <v>5</v>
+      </c>
+      <c r="C1532" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1532" s="6">
+        <v>1</v>
+      </c>
+      <c r="E1532" s="9">
+        <v>12</v>
+      </c>
+      <c r="F1532" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="G1532" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="H1532" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1533" spans